--- a/Documents/削除機能詳細設計書.xlsx
+++ b/Documents/削除機能詳細設計書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Documents\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE02BC29-E686-496D-ACFD-6EF40E6913C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25399FA-3894-40A5-B6D1-4B11DA05EEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="104">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -1419,6 +1419,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1443,35 +1452,158 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1494,29 +1626,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1530,11 +1644,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1542,17 +1656,14 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1566,17 +1677,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1584,155 +1710,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1809,25 +1809,129 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27298D14-6E06-1570-CD95-0D751717F82E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5324475" y="2066925"/>
+          <a:ext cx="2076450" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="800" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>String="jdbc:mysql://localhost:3306/taskdb</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>"</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:colOff>581025</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E2D5615-B300-2A2A-C354-C7B0A9751FEF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{783BD3DC-C918-DBAC-2B2A-5910DB66F40F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1849,8 +1953,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="361950" y="952501"/>
-          <a:ext cx="7772400" cy="4571999"/>
+          <a:off x="523875" y="962025"/>
+          <a:ext cx="7772400" cy="4562475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2362,85 +2466,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2460,46 +2564,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="39"/>
-      <c r="I13" s="37" t="s">
+      <c r="H13" s="42"/>
+      <c r="I13" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="39"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="42"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="37"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="39"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="42"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="37"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="39"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="42"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2508,13 +2612,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3522,1226 +3626,1211 @@
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="5.140625" style="103" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" style="103" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" style="103" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="103"/>
+    <col min="1" max="3" width="5.140625" style="39" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" style="39" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" style="39" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="99" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="100"/>
-      <c r="F1" s="99" t="s">
+      <c r="E1" s="73"/>
+      <c r="F1" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="100"/>
-      <c r="H1" s="101" t="s">
+      <c r="G1" s="73"/>
+      <c r="H1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="101" t="s">
+      <c r="I1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="102" t="s">
+      <c r="J1" s="38" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="107" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="108"/>
-      <c r="F2" s="107" t="s">
+      <c r="E2" s="87"/>
+      <c r="F2" s="86" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="108"/>
-      <c r="H2" s="109">
+      <c r="G2" s="87"/>
+      <c r="H2" s="90">
         <v>45806</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="105"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="114"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="115"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="121" t="s">
+      <c r="A5" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="122"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="123" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="122"/>
-      <c r="I5" s="122"/>
-      <c r="J5" s="124"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="125" t="s">
+      <c r="A6" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="126"/>
-      <c r="C6" s="127"/>
-      <c r="D6" s="128" t="s">
+      <c r="B6" s="49"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="126"/>
-      <c r="F6" s="126"/>
-      <c r="G6" s="126"/>
-      <c r="H6" s="126"/>
-      <c r="I6" s="126"/>
-      <c r="J6" s="129"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="50"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="125" t="s">
+      <c r="A7" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="128" t="s">
+      <c r="B7" s="49"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="129"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="125" t="s">
+      <c r="A8" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="128" t="s">
+      <c r="B8" s="49"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="126"/>
-      <c r="F8" s="126"/>
-      <c r="G8" s="126"/>
-      <c r="H8" s="126"/>
-      <c r="I8" s="126"/>
-      <c r="J8" s="129"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="50"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="130" t="s">
+      <c r="A9" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="131" t="s">
+      <c r="B9" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="127"/>
-      <c r="D9" s="132" t="s">
+      <c r="C9" s="52"/>
+      <c r="D9" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="134"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="135"/>
-      <c r="B10" s="131" t="s">
+      <c r="A10" s="60"/>
+      <c r="B10" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="127"/>
-      <c r="D10" s="128"/>
-      <c r="E10" s="126"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="126"/>
-      <c r="I10" s="126"/>
-      <c r="J10" s="129"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="50"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="136"/>
-      <c r="B11" s="131" t="s">
+      <c r="A11" s="61"/>
+      <c r="B11" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="127"/>
-      <c r="D11" s="128" t="s">
+      <c r="C11" s="52"/>
+      <c r="D11" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="126"/>
-      <c r="F11" s="126"/>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="129"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="50"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="125" t="s">
+      <c r="A12" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="126"/>
-      <c r="C12" s="127"/>
-      <c r="D12" s="132" t="s">
+      <c r="B12" s="49"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="126"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="129"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="50"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="137" t="s">
+      <c r="A13" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="138"/>
-      <c r="C13" s="139"/>
-      <c r="D13" s="140"/>
-      <c r="E13" s="138"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="138"/>
-      <c r="H13" s="138"/>
-      <c r="I13" s="138"/>
-      <c r="J13" s="141"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="17" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="18" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="19" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="20" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="21" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="22" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="23" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="24" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="25" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="26" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="27" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="28" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="29" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="30" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="31" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="32" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="33" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="34" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="35" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="36" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="37" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="38" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="39" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="40" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="41" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="42" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="43" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="44" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="45" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="46" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="47" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="48" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="49" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="50" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="51" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="52" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="53" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="54" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="55" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="58" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="59" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="60" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="61" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="62" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="63" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="64" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="65" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" s="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" s="103" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="17" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="18" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="19" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="20" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="21" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="22" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="23" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="24" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="25" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="26" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="27" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="28" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="29" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="30" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="31" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="32" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="33" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="34" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="35" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="36" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="37" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="38" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="39" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="40" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="41" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="42" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="43" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="44" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="45" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="46" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="47" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="48" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="49" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="50" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="51" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="52" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="53" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="54" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="55" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="56" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="57" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="58" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="59" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="60" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="61" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="62" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="63" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="64" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="65" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="66" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="67" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="68" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="69" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="70" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="71" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="72" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="73" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="74" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="75" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="76" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="77" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="78" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="79" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="80" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="81" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="82" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="83" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="84" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="85" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="86" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="87" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="88" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="89" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="90" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="91" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="92" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="93" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="94" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="95" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="96" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="97" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="98" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="99" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="100" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="101" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="102" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="103" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="104" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="105" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="106" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="107" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="108" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="109" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="110" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="111" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="112" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="113" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="114" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="115" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="116" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="117" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="118" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="119" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="120" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="121" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="122" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="123" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="124" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="125" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="126" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="127" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="128" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="129" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="130" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="131" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="132" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="133" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="134" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="135" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="136" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="137" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="138" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="139" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="140" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="141" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="142" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="143" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="144" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="145" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="146" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="147" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="148" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="149" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="150" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="151" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="152" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="153" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="154" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="155" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="156" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="157" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="158" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="159" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="160" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="161" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="162" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="163" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="164" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="165" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="166" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="167" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="168" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="169" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="170" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="171" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="172" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="173" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="174" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="175" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="176" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="177" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="178" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="179" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="180" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="181" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="182" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="183" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="184" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="185" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="186" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="187" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="188" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="189" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="190" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="191" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="192" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="193" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="194" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="195" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="196" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="197" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="198" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="199" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="200" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="201" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="202" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="203" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="204" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="205" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="206" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="207" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="208" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="209" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="210" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="211" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="212" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="213" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="214" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="215" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="216" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="217" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="218" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="219" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="220" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="221" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="222" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="223" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="224" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="225" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="226" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="227" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="228" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="229" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="230" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="231" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="232" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="233" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="234" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="235" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="236" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="237" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="238" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="239" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="240" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="241" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="242" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="243" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="244" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="245" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="246" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="247" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="248" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="249" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="250" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="251" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="252" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="253" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="254" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="255" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="256" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="257" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="258" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="259" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="260" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="261" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="262" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="263" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="264" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="265" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="266" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="267" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="268" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="269" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="270" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="271" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="272" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="273" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="274" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="275" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="276" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="277" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="278" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="279" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="280" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="281" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="282" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="283" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="284" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="285" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="286" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="287" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="288" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="289" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="290" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="291" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="292" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="293" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="294" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="295" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="296" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="297" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="298" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="299" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="300" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="301" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="302" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="303" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="304" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="305" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="306" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="307" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="308" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="309" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="310" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="311" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="312" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="313" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="314" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="315" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="316" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="317" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="318" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="319" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="320" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="321" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="322" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="323" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="324" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="325" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="326" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="327" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="328" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="329" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="330" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="331" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="332" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="333" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="334" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="335" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="336" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="337" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="338" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="339" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="340" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="341" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="342" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="343" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="344" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="345" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="346" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="347" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="348" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="349" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="350" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="351" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="352" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="353" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="354" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="355" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="356" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="357" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="358" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="359" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="360" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="361" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="362" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="363" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="364" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="365" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="366" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="367" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="368" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="369" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="370" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="371" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="372" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="373" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="374" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="375" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="376" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="377" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="378" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="379" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="380" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="381" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="382" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="383" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="384" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="385" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="386" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="387" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="388" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="389" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="390" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="391" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="392" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="393" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="394" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="395" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="396" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="397" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="398" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="399" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="400" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="401" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="402" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="403" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="404" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="405" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="406" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="407" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="408" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="409" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="410" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="411" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="412" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="413" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="414" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="415" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="416" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="417" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="418" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="419" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="420" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="421" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="422" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="423" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="424" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="425" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="426" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="427" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="428" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="429" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="430" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="431" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="432" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="433" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="434" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="435" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="436" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="437" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="438" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="439" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="440" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="441" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="442" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="443" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="444" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="445" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="446" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="447" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="448" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="449" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="450" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="451" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="452" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="453" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="454" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="455" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="456" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="457" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="458" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="459" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="460" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="461" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="462" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="463" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="464" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="465" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="466" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="467" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="468" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="469" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="470" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="471" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="472" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="473" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="474" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="475" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="476" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="477" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="478" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="479" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="480" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="481" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="482" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="483" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="484" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="485" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="486" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="487" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="488" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="489" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="490" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="491" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="492" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="493" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="494" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="495" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="496" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="497" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="498" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="499" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="500" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="501" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="502" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="503" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="504" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="505" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="506" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="507" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="508" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="509" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="510" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="511" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="512" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="513" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="514" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="515" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="516" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="517" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="518" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="519" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="520" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="521" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="522" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="523" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="524" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="525" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="526" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="527" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="528" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="529" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="530" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="531" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="532" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="533" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="534" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="535" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="536" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="537" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="538" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="539" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="540" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="541" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="542" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="543" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="544" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="545" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="546" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="547" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="548" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="549" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="550" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="551" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="552" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="553" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="554" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="555" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="556" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="557" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="558" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="559" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="560" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="561" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="562" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="563" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="564" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="565" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="566" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="567" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="568" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="569" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="570" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="571" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="572" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="573" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="574" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="575" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="576" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="577" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="578" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="579" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="580" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="581" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="582" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="583" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="584" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="585" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="586" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="587" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="588" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="589" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="590" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="591" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="592" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="593" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="594" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="595" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="596" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="597" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="598" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="599" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="600" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="601" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="602" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="603" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="604" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="605" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="606" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="607" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="608" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="609" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="610" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="611" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="612" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="613" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="614" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="615" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="616" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="617" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="618" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="619" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="620" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="621" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="622" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="623" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="624" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="625" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="626" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="627" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="628" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="629" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="630" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="631" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="632" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="633" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="634" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="635" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="636" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="637" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="638" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="639" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="640" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="641" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="642" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="643" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="644" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="645" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="646" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="647" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="648" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="649" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="650" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="651" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="652" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="653" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="654" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="655" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="656" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="657" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="658" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="659" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="660" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="661" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="662" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="663" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="664" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="665" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="666" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="667" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="668" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="669" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="670" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="671" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="672" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="673" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="674" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="675" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="676" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="677" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="678" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="679" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="680" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="681" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="682" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="683" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="684" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="685" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="686" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="687" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="688" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="689" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="690" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="691" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="692" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="693" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="694" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="695" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="696" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="697" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="698" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="699" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="700" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="701" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="702" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="703" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="704" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="705" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="706" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="707" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="708" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="709" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="710" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="711" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="712" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="713" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="714" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="715" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="716" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="717" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="718" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="719" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="720" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="721" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="722" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="723" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="724" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="725" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="726" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="727" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="728" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="729" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="730" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="731" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="732" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="733" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="734" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="735" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="736" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="737" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="738" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="739" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="740" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="741" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="742" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="743" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="744" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="745" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="746" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="747" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="748" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="749" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="750" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="751" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="752" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="753" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="754" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="755" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="756" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="757" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="758" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="759" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="760" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="761" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="762" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="763" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="764" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="765" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="766" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="767" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="768" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="769" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="770" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="771" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="772" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="773" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="774" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="775" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="776" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="777" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="778" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="779" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="780" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="781" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="782" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="783" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="784" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="785" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="786" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="787" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="788" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="789" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="790" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="791" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="792" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="793" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="794" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="795" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="796" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="797" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="798" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="799" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="800" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="801" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="802" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="803" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="804" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="805" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="806" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="807" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="808" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="809" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="810" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="811" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="812" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="813" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="814" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="815" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="816" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="817" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="818" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="819" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="820" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="821" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="822" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="823" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="824" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="825" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="826" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="827" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="828" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="829" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="830" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="831" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="832" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="833" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="834" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="835" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="836" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="837" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="838" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="839" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="840" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="841" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="842" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="843" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="844" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="845" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="846" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="847" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="848" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="849" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="850" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="851" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="852" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="853" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="854" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="855" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="856" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="857" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="858" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="859" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="860" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="861" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="862" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="863" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="864" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="865" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="866" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="867" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="868" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="869" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="870" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="871" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="872" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="873" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="874" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="875" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="876" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="877" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="878" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="879" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="880" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="881" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="882" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="883" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="884" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="885" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="886" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="887" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="888" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="889" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="890" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="891" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="892" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="893" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="894" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="895" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="896" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="897" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="898" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="899" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="900" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="901" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="902" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="903" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="904" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="905" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="906" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="907" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="908" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="909" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="910" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="911" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="912" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="913" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="914" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="915" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="916" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="917" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="918" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="919" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="920" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="921" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="922" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="923" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="924" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="925" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="926" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="927" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="928" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="929" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="930" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="931" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="932" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="933" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="934" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="935" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="936" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="937" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="938" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="939" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="940" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="941" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="942" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="943" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="944" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="945" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="946" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="947" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="948" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="949" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="950" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="951" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="952" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="953" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="954" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="955" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="956" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="957" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="958" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="959" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="960" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="961" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="962" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="963" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="964" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="965" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="966" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="967" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="968" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="969" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="970" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="971" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="972" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="973" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="974" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="975" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="976" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="977" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="978" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="979" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="980" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="981" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="982" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="983" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="984" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="985" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="986" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="987" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="988" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="989" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="990" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="991" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="992" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="993" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="994" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="995" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="996" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="997" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="998" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="999" s="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1000" s="39" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -4754,6 +4843,21 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4772,19 +4876,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="99"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="107"/>
+      <c r="F1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="62"/>
+      <c r="G1" s="107"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4796,48 +4900,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="101"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70">
+      <c r="E2" s="109"/>
+      <c r="F2" s="108">
         <v>56</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="75">
+      <c r="G2" s="109"/>
+      <c r="H2" s="91">
         <v>45811</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="95"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="101"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="96"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="68"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -6194,19 +6298,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="99"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="107"/>
+      <c r="F1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="62"/>
+      <c r="G1" s="107"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6218,48 +6322,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="101"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="75">
+      <c r="E2" s="109"/>
+      <c r="F2" s="108">
+        <v>56</v>
+      </c>
+      <c r="G2" s="109"/>
+      <c r="H2" s="91">
         <v>45807</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="95"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="101"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="96"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="68"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -7610,19 +7714,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="99"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="107"/>
+      <c r="F1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="62"/>
+      <c r="G1" s="107"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7634,190 +7738,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="101"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70" t="s">
+      <c r="E2" s="109"/>
+      <c r="F2" s="108" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="75">
+      <c r="G2" s="109"/>
+      <c r="H2" s="91">
         <v>45807</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="95"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="101"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="96"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="57"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="67"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="81" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="116" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="50"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="52"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="118"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="82"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="84"/>
+      <c r="A7" s="119"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="120"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="121"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="57"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="85"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="57"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="85"/>
+      <c r="A9" s="101"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="57"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="85"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="85"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="57"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="85"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="57"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="85"/>
+      <c r="A13" s="101"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="52"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="51" t="s">
+      <c r="B15" s="41"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="123" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="42"/>
       <c r="I15" s="14" t="s">
         <v>28</v>
       </c>
@@ -7826,11 +7930,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="42"/>
       <c r="D16" s="14" t="s">
         <v>30</v>
       </c>
@@ -7843,18 +7947,18 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="78" t="s">
+      <c r="H16" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="52"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="76">
+      <c r="A17" s="114">
         <v>1</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="39"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="16" t="s">
         <v>86</v>
       </c>
@@ -7865,16 +7969,16 @@
         <v>93</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="52"/>
+      <c r="H17" s="123"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="76">
+      <c r="A18" s="114">
         <v>2</v>
       </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="39"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="16" t="s">
         <v>87</v>
       </c>
@@ -7887,16 +7991,16 @@
       <c r="G18" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="H18" s="51"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="52"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="76">
+      <c r="A19" s="114">
         <v>3</v>
       </c>
-      <c r="B19" s="38"/>
-      <c r="C19" s="39"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="42"/>
       <c r="D19" s="16" t="s">
         <v>88</v>
       </c>
@@ -7907,16 +8011,16 @@
       <c r="G19" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="H19" s="51"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="52"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="76">
+      <c r="A20" s="114">
         <v>4</v>
       </c>
-      <c r="B20" s="38"/>
-      <c r="C20" s="39"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="16" t="s">
         <v>89</v>
       </c>
@@ -7929,16 +8033,16 @@
       <c r="G20" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="H20" s="51"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="52"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="118"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="76">
+      <c r="A21" s="114">
         <v>5</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="39"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="16" t="s">
         <v>90</v>
       </c>
@@ -7951,16 +8055,16 @@
       <c r="G21" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="51"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="52"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="118"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="76">
+      <c r="A22" s="114">
         <v>6</v>
       </c>
-      <c r="B22" s="38"/>
-      <c r="C22" s="39"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="42"/>
       <c r="D22" s="16" t="s">
         <v>72</v>
       </c>
@@ -7971,16 +8075,16 @@
         <v>72</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="52"/>
+      <c r="H22" s="123"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="118"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="76">
+      <c r="A23" s="114">
         <v>7</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
       <c r="D23" s="18" t="s">
         <v>72</v>
       </c>
@@ -7991,225 +8095,225 @@
         <v>72</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="47"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="127"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="77"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="52"/>
+      <c r="A24" s="115"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="118"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="77"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
+      <c r="A25" s="115"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="123"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="42"/>
       <c r="I25" s="14"/>
       <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="77"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="39"/>
+      <c r="A26" s="115"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="42"/>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="52"/>
+      <c r="H26" s="124"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="118"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="76"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="39"/>
+      <c r="A27" s="114"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="42"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="52"/>
+      <c r="H27" s="123"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="118"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="76"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="39"/>
+      <c r="A28" s="114"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="42"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="52"/>
+      <c r="H28" s="123"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="118"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="76"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="39"/>
+      <c r="A29" s="114"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="42"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="52"/>
+      <c r="H29" s="123"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="118"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="76"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="39"/>
+      <c r="A30" s="114"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="42"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="52"/>
+      <c r="H30" s="123"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="118"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="76"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="39"/>
+      <c r="A31" s="114"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="42"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="52"/>
+      <c r="H31" s="123"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="118"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="76"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="39"/>
+      <c r="A32" s="114"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="42"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="38"/>
-      <c r="J32" s="52"/>
+      <c r="H32" s="123"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="118"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="79"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="53"/>
+      <c r="A33" s="128"/>
+      <c r="B33" s="126"/>
+      <c r="C33" s="129"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="47"/>
+      <c r="H33" s="125"/>
+      <c r="I33" s="126"/>
+      <c r="J33" s="127"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="77"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="52"/>
+      <c r="A34" s="115"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="118"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="77"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="39"/>
+      <c r="A35" s="115"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="123"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="42"/>
       <c r="I35" s="14"/>
       <c r="J35" s="15"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="77"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="39"/>
+      <c r="A36" s="115"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="42"/>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="52"/>
+      <c r="H36" s="124"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="118"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="76"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="39"/>
+      <c r="A37" s="114"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="42"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="52"/>
+      <c r="H37" s="123"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="118"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="76"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="39"/>
+      <c r="A38" s="114"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="42"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="52"/>
+      <c r="H38" s="123"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="118"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="76"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="39"/>
+      <c r="A39" s="114"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="42"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="52"/>
+      <c r="H39" s="123"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="118"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="76"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="39"/>
+      <c r="A40" s="114"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="42"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="38"/>
-      <c r="J40" s="52"/>
+      <c r="H40" s="123"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="118"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="76"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="39"/>
+      <c r="A41" s="114"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="42"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="38"/>
-      <c r="J41" s="52"/>
+      <c r="H41" s="123"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="118"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9172,11 +9276,50 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9193,50 +9336,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9259,19 +9363,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="99"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="107"/>
+      <c r="F1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="62"/>
+      <c r="G1" s="107"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -9283,190 +9387,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="101"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70" t="s">
+      <c r="E2" s="109"/>
+      <c r="F2" s="108" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="75">
+      <c r="G2" s="109"/>
+      <c r="H2" s="91">
         <v>45807</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="95"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="101"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="96"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="57"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="67"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="81" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="116" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="50"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="52"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="118"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="82"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="84"/>
+      <c r="A7" s="119"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="120"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="121"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="57"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="85"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="57"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="85"/>
+      <c r="A9" s="101"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="57"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="85"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="85"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="57"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="85"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="57"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="85"/>
+      <c r="A13" s="101"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="52"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="51" t="s">
+      <c r="B15" s="41"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="123" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="42"/>
       <c r="I15" s="14" t="s">
         <v>28</v>
       </c>
@@ -9475,11 +9579,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="42"/>
       <c r="D16" s="14" t="s">
         <v>30</v>
       </c>
@@ -9492,18 +9596,18 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="78" t="s">
+      <c r="H16" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="52"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="76">
+      <c r="A17" s="114">
         <v>1</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="39"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="16" t="s">
         <v>72</v>
       </c>
@@ -9516,83 +9620,83 @@
       <c r="G17" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="51" t="s">
+      <c r="H17" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="38"/>
-      <c r="J17" s="52"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="76"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="39"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="52"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="76"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="39"/>
+      <c r="A19" s="114"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="42"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="52"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="76"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="39"/>
+      <c r="A20" s="114"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="52"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="118"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="76"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="39"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="52"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="118"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="76"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="39"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="42"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="52"/>
+      <c r="H22" s="123"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="118"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="79"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="53"/>
+      <c r="A23" s="128"/>
+      <c r="B23" s="126"/>
+      <c r="C23" s="129"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="47"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="127"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10573,6 +10677,21 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -10589,21 +10708,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10626,19 +10730,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="99"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="107"/>
+      <c r="F1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="62"/>
+      <c r="G1" s="107"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -10650,190 +10754,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="101"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70" t="s">
+      <c r="E2" s="109"/>
+      <c r="F2" s="108" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="75">
+      <c r="G2" s="109"/>
+      <c r="H2" s="91">
         <v>45805</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="95"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="101"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="96"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="57"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="67"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="81" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="50"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="52"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="118"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="82"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="84"/>
+      <c r="A7" s="119"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="120"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="121"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="57"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="85"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="57"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="85"/>
+      <c r="A9" s="101"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="57"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="85"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="85"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="57"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="85"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="57"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="85"/>
+      <c r="A13" s="101"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="52"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="51" t="s">
+      <c r="B15" s="41"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="123" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="42"/>
       <c r="I15" s="14" t="s">
         <v>28</v>
       </c>
@@ -10842,11 +10946,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="42"/>
       <c r="D16" s="14" t="s">
         <v>30</v>
       </c>
@@ -10859,18 +10963,18 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="78" t="s">
+      <c r="H16" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="52"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="76">
+      <c r="A17" s="114">
         <v>1</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="39"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="16" t="s">
         <v>72</v>
       </c>
@@ -10883,83 +10987,83 @@
       <c r="G17" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="51" t="s">
+      <c r="H17" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="38"/>
-      <c r="J17" s="52"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="76"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="39"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="52"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="76"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="39"/>
+      <c r="A19" s="114"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="42"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="52"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="76"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="39"/>
+      <c r="A20" s="114"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="52"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="118"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="76"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="39"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="52"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="118"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="76"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="39"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="42"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="52"/>
+      <c r="H22" s="123"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="118"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="79"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="53"/>
+      <c r="A23" s="128"/>
+      <c r="B23" s="126"/>
+      <c r="C23" s="129"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="47"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="127"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11940,6 +12044,21 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -11956,21 +12075,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11990,182 +12094,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="69" t="s">
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="69" t="s">
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="69" t="s">
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="69" t="s">
+      <c r="P1" s="107"/>
+      <c r="Q1" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="62"/>
-      <c r="S1" s="69" t="s">
+      <c r="R1" s="107"/>
+      <c r="S1" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="50"/>
+      <c r="T1" s="117"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="70"/>
-      <c r="T2" s="84"/>
+      <c r="A2" s="101"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="109"/>
+      <c r="O2" s="108"/>
+      <c r="P2" s="109"/>
+      <c r="Q2" s="108"/>
+      <c r="R2" s="109"/>
+      <c r="S2" s="108"/>
+      <c r="T2" s="121"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="85"/>
+      <c r="A3" s="101"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="110"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="110"/>
+      <c r="R3" s="102"/>
+      <c r="S3" s="110"/>
+      <c r="T3" s="122"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="94"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="105"/>
+      <c r="O4" s="111"/>
+      <c r="P4" s="105"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="105"/>
+      <c r="S4" s="111"/>
+      <c r="T4" s="134"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="48" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="50"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="117"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="51" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="52"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="118"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="51" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="123" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="52"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="118"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -12364,37 +12468,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="93" t="s">
+      <c r="B15" s="42"/>
+      <c r="C15" s="139" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="78" t="s">
+      <c r="D15" s="42"/>
+      <c r="E15" s="124" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="39"/>
-      <c r="G15" s="78" t="s">
+      <c r="F15" s="42"/>
+      <c r="G15" s="124" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="38"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="78" t="s">
+      <c r="H15" s="41"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="39"/>
-      <c r="L15" s="78" t="s">
+      <c r="K15" s="42"/>
+      <c r="L15" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="38"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="78" t="s">
+      <c r="M15" s="41"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="124" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="39"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="42"/>
       <c r="R15" s="14" t="s">
         <v>52</v>
       </c>
@@ -12406,37 +12510,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="86">
+      <c r="A16" s="137">
         <v>1</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="87" t="s">
+      <c r="B16" s="42"/>
+      <c r="C16" s="138" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="87" t="s">
+      <c r="D16" s="42"/>
+      <c r="E16" s="138" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="92" t="s">
+      <c r="F16" s="42"/>
+      <c r="G16" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="38"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="92" t="s">
+      <c r="H16" s="41"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="130" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="39"/>
-      <c r="L16" s="90" t="s">
+      <c r="K16" s="42"/>
+      <c r="L16" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="38"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="90" t="s">
+      <c r="M16" s="41"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="39"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="42"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -12448,37 +12552,37 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="86">
+      <c r="A17" s="137">
         <v>2</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="87" t="s">
+      <c r="B17" s="42"/>
+      <c r="C17" s="138" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="39"/>
-      <c r="E17" s="87" t="s">
+      <c r="D17" s="42"/>
+      <c r="E17" s="138" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="92" t="s">
+      <c r="F17" s="42"/>
+      <c r="G17" s="130" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="92" t="s">
+      <c r="H17" s="41"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="39"/>
-      <c r="L17" s="90" t="s">
+      <c r="K17" s="42"/>
+      <c r="L17" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="38"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="90" t="s">
+      <c r="M17" s="41"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="132" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="39"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="42"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -12490,23 +12594,23 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="86"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="87"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="92"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="90"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="90"/>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="39"/>
+      <c r="A18" s="137"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="138"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="138"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="130"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="132"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="42"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -12518,23 +12622,23 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="86"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="92"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="90"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="39"/>
+      <c r="A19" s="137"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="138"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="138"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="130"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="132"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="132"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="42"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -12546,23 +12650,23 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="86"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="92"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="92"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="90"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="39"/>
+      <c r="A20" s="137"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="138"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="130"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="130"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="132"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="132"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="42"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="33"/>
@@ -12574,23 +12678,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="86"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="87"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="92"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="90"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="39"/>
+      <c r="A21" s="137"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="138"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="130"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="132"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="42"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -12602,23 +12706,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="86"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="87"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="87"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="92"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="90"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="90"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="39"/>
+      <c r="A22" s="137"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="130"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="130"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="132"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="132"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="42"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -12630,23 +12734,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="86"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="87"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="87"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="90"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="90"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="39"/>
+      <c r="A23" s="137"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="138"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="130"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="132"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="132"/>
+      <c r="P23" s="41"/>
+      <c r="Q23" s="42"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -12658,23 +12762,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="86"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="87"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="92"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="90"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="90"/>
-      <c r="P24" s="38"/>
-      <c r="Q24" s="39"/>
+      <c r="A24" s="137"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="130"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="130"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="132"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="132"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="42"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -12686,23 +12790,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="86"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="87"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="92"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="92"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="90"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="90"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="39"/>
+      <c r="A25" s="137"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="138"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="130"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="130"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="132"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="132"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="42"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -12714,23 +12818,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="86"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="87"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="92"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="92"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="90"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="90"/>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="39"/>
+      <c r="A26" s="137"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="130"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="132"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="132"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="42"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -12742,23 +12846,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="86"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="87"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="92"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="92"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="90"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="90"/>
-      <c r="P27" s="38"/>
-      <c r="Q27" s="39"/>
+      <c r="A27" s="137"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="138"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="130"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="130"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="132"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="132"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="42"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -12770,23 +12874,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="86"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="87"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="92"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="92"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="90"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="90"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="39"/>
+      <c r="A28" s="137"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="130"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="132"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="132"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="42"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -12798,23 +12902,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="86"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="87"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="87"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="92"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="92"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="90"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="90"/>
-      <c r="P29" s="38"/>
-      <c r="Q29" s="39"/>
+      <c r="A29" s="137"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="130"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="130"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="132"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="42"/>
+      <c r="O29" s="132"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="42"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -12826,23 +12930,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="86"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="87"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="87"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="92"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="92"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="90"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="90"/>
-      <c r="P30" s="38"/>
-      <c r="Q30" s="39"/>
+      <c r="A30" s="137"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="130"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="130"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="132"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="42"/>
+      <c r="O30" s="132"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="42"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -12854,23 +12958,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="88"/>
-      <c r="B31" s="53"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="95"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="95"/>
-      <c r="K31" s="53"/>
-      <c r="L31" s="91"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="53"/>
-      <c r="O31" s="91"/>
-      <c r="P31" s="46"/>
-      <c r="Q31" s="53"/>
+      <c r="A31" s="140"/>
+      <c r="B31" s="129"/>
+      <c r="C31" s="141"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="129"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="126"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="131"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="133"/>
+      <c r="M31" s="126"/>
+      <c r="N31" s="129"/>
+      <c r="O31" s="133"/>
+      <c r="P31" s="126"/>
+      <c r="Q31" s="129"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -13868,62 +13972,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -13948,62 +14052,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/削除機能詳細設計書.xlsx
+++ b/Documents/削除機能詳細設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Documents\project\taskUN\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25399FA-3894-40A5-B6D1-4B11DA05EEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932907F1-AEBB-4360-BEB3-B4636498A6D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -564,6 +564,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1452,57 +1453,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1534,6 +1484,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1580,6 +1545,42 @@
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1644,25 +1645,46 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1677,32 +1699,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1710,29 +1717,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1757,22 +1758,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
+      <xdr:colOff>514350</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F252299-C4DE-13E3-B43D-1BF2523B3794}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE3A018D-27DB-1F57-DE9B-FCCFF1F5E845}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1794,7 +1795,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="523875" y="1057275"/>
+          <a:off x="457200" y="1085850"/>
           <a:ext cx="7772400" cy="4295775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3633,19 +3634,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="85" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="85" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="73"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="37" t="s">
         <v>8</v>
       </c>
@@ -3657,190 +3658,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="86" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="90">
+      <c r="G2" s="75"/>
+      <c r="H2" s="78">
         <v>45806</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="51"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="52"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="74" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="75"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="48" t="s">
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="50"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="48" t="s">
+      <c r="B7" s="60"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="63"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="48" t="s">
+      <c r="B8" s="60"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="50"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="63"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="53" t="s">
+      <c r="C9" s="61"/>
+      <c r="D9" s="83" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="64"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="85"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="62" t="s">
+      <c r="A10" s="80"/>
+      <c r="B10" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="50"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="63"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="61"/>
-      <c r="B11" s="62" t="s">
+      <c r="A11" s="81"/>
+      <c r="B11" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="48" t="s">
+      <c r="C11" s="61"/>
+      <c r="D11" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="50"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="63"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="53" t="s">
+      <c r="B12" s="60"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="83" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="50"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="63"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="58"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="89"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="90"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4831,6 +4832,21 @@
     <row r="1000" s="39" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -4843,21 +4859,6 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7782,20 +7783,20 @@
       <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="113"/>
+      <c r="B5" s="123"/>
       <c r="C5" s="107"/>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="124" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="125"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -7809,19 +7810,19 @@
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
-      <c r="J6" s="118"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="119"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="121"/>
+      <c r="A7" s="126"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="101"/>
@@ -7833,7 +7834,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="44"/>
-      <c r="J8" s="122"/>
+      <c r="J8" s="129"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="101"/>
@@ -7845,7 +7846,7 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="44"/>
-      <c r="J9" s="122"/>
+      <c r="J9" s="129"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="101"/>
@@ -7857,7 +7858,7 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="122"/>
+      <c r="J10" s="129"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="101"/>
@@ -7869,7 +7870,7 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
-      <c r="J11" s="122"/>
+      <c r="J11" s="129"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="101"/>
@@ -7881,7 +7882,7 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
-      <c r="J12" s="122"/>
+      <c r="J12" s="129"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="101"/>
@@ -7893,7 +7894,7 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
-      <c r="J13" s="122"/>
+      <c r="J13" s="129"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="115" t="s">
@@ -7907,7 +7908,7 @@
       <c r="G14" s="41"/>
       <c r="H14" s="41"/>
       <c r="I14" s="41"/>
-      <c r="J14" s="118"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="115" t="s">
@@ -7915,7 +7916,7 @@
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="123" t="s">
+      <c r="D15" s="113" t="s">
         <v>84</v>
       </c>
       <c r="E15" s="41"/>
@@ -7947,14 +7948,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="124" t="s">
+      <c r="H16" s="116" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="41"/>
-      <c r="J16" s="118"/>
+      <c r="J16" s="114"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="114">
+      <c r="A17" s="112">
         <v>1</v>
       </c>
       <c r="B17" s="41"/>
@@ -7969,12 +7970,12 @@
         <v>93</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="123"/>
+      <c r="H17" s="113"/>
       <c r="I17" s="41"/>
-      <c r="J17" s="118"/>
+      <c r="J17" s="114"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="114">
+      <c r="A18" s="112">
         <v>2</v>
       </c>
       <c r="B18" s="41"/>
@@ -7991,12 +7992,12 @@
       <c r="G18" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="H18" s="123"/>
+      <c r="H18" s="113"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="118"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="114">
+      <c r="A19" s="112">
         <v>3</v>
       </c>
       <c r="B19" s="41"/>
@@ -8011,12 +8012,12 @@
       <c r="G19" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="H19" s="123"/>
+      <c r="H19" s="113"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="118"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="114">
+      <c r="A20" s="112">
         <v>4</v>
       </c>
       <c r="B20" s="41"/>
@@ -8033,12 +8034,12 @@
       <c r="G20" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="H20" s="123"/>
+      <c r="H20" s="113"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="118"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="114">
+      <c r="A21" s="112">
         <v>5</v>
       </c>
       <c r="B21" s="41"/>
@@ -8055,12 +8056,12 @@
       <c r="G21" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="123"/>
+      <c r="H21" s="113"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="118"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="114">
+      <c r="A22" s="112">
         <v>6</v>
       </c>
       <c r="B22" s="41"/>
@@ -8075,12 +8076,12 @@
         <v>72</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="123"/>
+      <c r="H22" s="113"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="118"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="114">
+      <c r="A23" s="112">
         <v>7</v>
       </c>
       <c r="B23" s="41"/>
@@ -8095,9 +8096,9 @@
         <v>72</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="127"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="121"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
       <c r="A24" s="115"/>
@@ -8109,13 +8110,13 @@
       <c r="G24" s="41"/>
       <c r="H24" s="41"/>
       <c r="I24" s="41"/>
-      <c r="J24" s="118"/>
+      <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
       <c r="A25" s="115"/>
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
-      <c r="D25" s="123"/>
+      <c r="D25" s="113"/>
       <c r="E25" s="41"/>
       <c r="F25" s="41"/>
       <c r="G25" s="41"/>
@@ -8131,93 +8132,93 @@
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="124"/>
+      <c r="H26" s="116"/>
       <c r="I26" s="41"/>
-      <c r="J26" s="118"/>
+      <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="114"/>
+      <c r="A27" s="112"/>
       <c r="B27" s="41"/>
       <c r="C27" s="42"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="123"/>
+      <c r="H27" s="113"/>
       <c r="I27" s="41"/>
-      <c r="J27" s="118"/>
+      <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="114"/>
+      <c r="A28" s="112"/>
       <c r="B28" s="41"/>
       <c r="C28" s="42"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="123"/>
+      <c r="H28" s="113"/>
       <c r="I28" s="41"/>
-      <c r="J28" s="118"/>
+      <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="114"/>
+      <c r="A29" s="112"/>
       <c r="B29" s="41"/>
       <c r="C29" s="42"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
-      <c r="H29" s="123"/>
+      <c r="H29" s="113"/>
       <c r="I29" s="41"/>
-      <c r="J29" s="118"/>
+      <c r="J29" s="114"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="114"/>
+      <c r="A30" s="112"/>
       <c r="B30" s="41"/>
       <c r="C30" s="42"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="123"/>
+      <c r="H30" s="113"/>
       <c r="I30" s="41"/>
-      <c r="J30" s="118"/>
+      <c r="J30" s="114"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="114"/>
+      <c r="A31" s="112"/>
       <c r="B31" s="41"/>
       <c r="C31" s="42"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="123"/>
+      <c r="H31" s="113"/>
       <c r="I31" s="41"/>
-      <c r="J31" s="118"/>
+      <c r="J31" s="114"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="114"/>
+      <c r="A32" s="112"/>
       <c r="B32" s="41"/>
       <c r="C32" s="42"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="123"/>
+      <c r="H32" s="113"/>
       <c r="I32" s="41"/>
-      <c r="J32" s="118"/>
+      <c r="J32" s="114"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="128"/>
-      <c r="B33" s="126"/>
-      <c r="C33" s="129"/>
+      <c r="A33" s="117"/>
+      <c r="B33" s="118"/>
+      <c r="C33" s="119"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
-      <c r="H33" s="125"/>
-      <c r="I33" s="126"/>
-      <c r="J33" s="127"/>
+      <c r="H33" s="120"/>
+      <c r="I33" s="118"/>
+      <c r="J33" s="121"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
       <c r="A34" s="115"/>
@@ -8229,13 +8230,13 @@
       <c r="G34" s="41"/>
       <c r="H34" s="41"/>
       <c r="I34" s="41"/>
-      <c r="J34" s="118"/>
+      <c r="J34" s="114"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
       <c r="A35" s="115"/>
       <c r="B35" s="41"/>
       <c r="C35" s="42"/>
-      <c r="D35" s="123"/>
+      <c r="D35" s="113"/>
       <c r="E35" s="41"/>
       <c r="F35" s="41"/>
       <c r="G35" s="41"/>
@@ -8251,69 +8252,69 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
-      <c r="H36" s="124"/>
+      <c r="H36" s="116"/>
       <c r="I36" s="41"/>
-      <c r="J36" s="118"/>
+      <c r="J36" s="114"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="114"/>
+      <c r="A37" s="112"/>
       <c r="B37" s="41"/>
       <c r="C37" s="42"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="123"/>
+      <c r="H37" s="113"/>
       <c r="I37" s="41"/>
-      <c r="J37" s="118"/>
+      <c r="J37" s="114"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="114"/>
+      <c r="A38" s="112"/>
       <c r="B38" s="41"/>
       <c r="C38" s="42"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="123"/>
+      <c r="H38" s="113"/>
       <c r="I38" s="41"/>
-      <c r="J38" s="118"/>
+      <c r="J38" s="114"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="114"/>
+      <c r="A39" s="112"/>
       <c r="B39" s="41"/>
       <c r="C39" s="42"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="123"/>
+      <c r="H39" s="113"/>
       <c r="I39" s="41"/>
-      <c r="J39" s="118"/>
+      <c r="J39" s="114"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="114"/>
+      <c r="A40" s="112"/>
       <c r="B40" s="41"/>
       <c r="C40" s="42"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="123"/>
+      <c r="H40" s="113"/>
       <c r="I40" s="41"/>
-      <c r="J40" s="118"/>
+      <c r="J40" s="114"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="114"/>
+      <c r="A41" s="112"/>
       <c r="B41" s="41"/>
       <c r="C41" s="42"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="123"/>
+      <c r="H41" s="113"/>
       <c r="I41" s="41"/>
-      <c r="J41" s="118"/>
+      <c r="J41" s="114"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9276,50 +9277,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9336,11 +9298,50 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9431,20 +9432,20 @@
       <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="113"/>
+      <c r="B5" s="123"/>
       <c r="C5" s="107"/>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="124" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="125"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -9458,19 +9459,19 @@
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
-      <c r="J6" s="118"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="119"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="121"/>
+      <c r="A7" s="126"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="101"/>
@@ -9482,7 +9483,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="44"/>
-      <c r="J8" s="122"/>
+      <c r="J8" s="129"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="101"/>
@@ -9494,7 +9495,7 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="44"/>
-      <c r="J9" s="122"/>
+      <c r="J9" s="129"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="101"/>
@@ -9506,7 +9507,7 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="122"/>
+      <c r="J10" s="129"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="101"/>
@@ -9518,7 +9519,7 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
-      <c r="J11" s="122"/>
+      <c r="J11" s="129"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="101"/>
@@ -9530,7 +9531,7 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
-      <c r="J12" s="122"/>
+      <c r="J12" s="129"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="101"/>
@@ -9542,7 +9543,7 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
-      <c r="J13" s="122"/>
+      <c r="J13" s="129"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="115" t="s">
@@ -9556,7 +9557,7 @@
       <c r="G14" s="41"/>
       <c r="H14" s="41"/>
       <c r="I14" s="41"/>
-      <c r="J14" s="118"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="115" t="s">
@@ -9564,7 +9565,7 @@
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="123" t="s">
+      <c r="D15" s="113" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="41"/>
@@ -9596,14 +9597,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="124" t="s">
+      <c r="H16" s="116" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="41"/>
-      <c r="J16" s="118"/>
+      <c r="J16" s="114"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="114">
+      <c r="A17" s="112">
         <v>1</v>
       </c>
       <c r="B17" s="41"/>
@@ -9620,83 +9621,83 @@
       <c r="G17" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="123" t="s">
+      <c r="H17" s="113" t="s">
         <v>75</v>
       </c>
       <c r="I17" s="41"/>
-      <c r="J17" s="118"/>
+      <c r="J17" s="114"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="114"/>
+      <c r="A18" s="112"/>
       <c r="B18" s="41"/>
       <c r="C18" s="42"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="123"/>
+      <c r="H18" s="113"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="118"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="114"/>
+      <c r="A19" s="112"/>
       <c r="B19" s="41"/>
       <c r="C19" s="42"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="123"/>
+      <c r="H19" s="113"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="118"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="114"/>
+      <c r="A20" s="112"/>
       <c r="B20" s="41"/>
       <c r="C20" s="42"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="123"/>
+      <c r="H20" s="113"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="118"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="114"/>
+      <c r="A21" s="112"/>
       <c r="B21" s="41"/>
       <c r="C21" s="42"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="123"/>
+      <c r="H21" s="113"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="118"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="114"/>
+      <c r="A22" s="112"/>
       <c r="B22" s="41"/>
       <c r="C22" s="42"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="123"/>
+      <c r="H22" s="113"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="118"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="128"/>
-      <c r="B23" s="126"/>
-      <c r="C23" s="129"/>
+      <c r="A23" s="117"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="127"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="121"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10677,6 +10678,27 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="A23:C23"/>
@@ -10687,27 +10709,6 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10798,20 +10799,20 @@
       <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="113"/>
+      <c r="B5" s="123"/>
       <c r="C5" s="107"/>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="124" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="125"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -10825,19 +10826,19 @@
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
-      <c r="J6" s="118"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="119"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="121"/>
+      <c r="A7" s="126"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="101"/>
@@ -10849,7 +10850,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="44"/>
-      <c r="J8" s="122"/>
+      <c r="J8" s="129"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="101"/>
@@ -10861,7 +10862,7 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="44"/>
-      <c r="J9" s="122"/>
+      <c r="J9" s="129"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="101"/>
@@ -10873,7 +10874,7 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="122"/>
+      <c r="J10" s="129"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="101"/>
@@ -10885,7 +10886,7 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
-      <c r="J11" s="122"/>
+      <c r="J11" s="129"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="101"/>
@@ -10897,7 +10898,7 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
-      <c r="J12" s="122"/>
+      <c r="J12" s="129"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="101"/>
@@ -10909,7 +10910,7 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
-      <c r="J13" s="122"/>
+      <c r="J13" s="129"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="115" t="s">
@@ -10923,7 +10924,7 @@
       <c r="G14" s="41"/>
       <c r="H14" s="41"/>
       <c r="I14" s="41"/>
-      <c r="J14" s="118"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="115" t="s">
@@ -10931,7 +10932,7 @@
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="123" t="s">
+      <c r="D15" s="113" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="41"/>
@@ -10963,14 +10964,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="124" t="s">
+      <c r="H16" s="116" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="41"/>
-      <c r="J16" s="118"/>
+      <c r="J16" s="114"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="114">
+      <c r="A17" s="112">
         <v>1</v>
       </c>
       <c r="B17" s="41"/>
@@ -10987,83 +10988,83 @@
       <c r="G17" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="123" t="s">
+      <c r="H17" s="113" t="s">
         <v>75</v>
       </c>
       <c r="I17" s="41"/>
-      <c r="J17" s="118"/>
+      <c r="J17" s="114"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="114"/>
+      <c r="A18" s="112"/>
       <c r="B18" s="41"/>
       <c r="C18" s="42"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="123"/>
+      <c r="H18" s="113"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="118"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="114"/>
+      <c r="A19" s="112"/>
       <c r="B19" s="41"/>
       <c r="C19" s="42"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="123"/>
+      <c r="H19" s="113"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="118"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="114"/>
+      <c r="A20" s="112"/>
       <c r="B20" s="41"/>
       <c r="C20" s="42"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="123"/>
+      <c r="H20" s="113"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="118"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="114"/>
+      <c r="A21" s="112"/>
       <c r="B21" s="41"/>
       <c r="C21" s="42"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="123"/>
+      <c r="H21" s="113"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="118"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="114"/>
+      <c r="A22" s="112"/>
       <c r="B22" s="41"/>
       <c r="C22" s="42"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="123"/>
+      <c r="H22" s="113"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="118"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="128"/>
-      <c r="B23" s="126"/>
-      <c r="C23" s="129"/>
+      <c r="A23" s="117"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="127"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="121"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12044,6 +12045,27 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="A23:C23"/>
@@ -12054,27 +12076,6 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12094,7 +12095,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="140" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="99"/>
@@ -12105,14 +12106,14 @@
       <c r="G1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
       <c r="J1" s="107"/>
       <c r="K1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
       <c r="N1" s="107"/>
       <c r="O1" s="106" t="s">
         <v>8</v>
@@ -12125,7 +12126,7 @@
       <c r="S1" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="117"/>
+      <c r="T1" s="125"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="101"/>
@@ -12135,19 +12136,19 @@
       <c r="E2" s="44"/>
       <c r="F2" s="102"/>
       <c r="G2" s="108"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
       <c r="J2" s="109"/>
       <c r="K2" s="108"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
       <c r="N2" s="109"/>
       <c r="O2" s="108"/>
       <c r="P2" s="109"/>
       <c r="Q2" s="108"/>
       <c r="R2" s="109"/>
       <c r="S2" s="108"/>
-      <c r="T2" s="121"/>
+      <c r="T2" s="128"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="101"/>
@@ -12169,7 +12170,7 @@
       <c r="Q3" s="110"/>
       <c r="R3" s="102"/>
       <c r="S3" s="110"/>
-      <c r="T3" s="122"/>
+      <c r="T3" s="129"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="103"/>
@@ -12191,33 +12192,33 @@
       <c r="Q4" s="111"/>
       <c r="R4" s="105"/>
       <c r="S4" s="111"/>
-      <c r="T4" s="134"/>
+      <c r="T4" s="139"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
       <c r="F5" s="107"/>
       <c r="G5" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="113"/>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="113"/>
-      <c r="R5" s="113"/>
-      <c r="S5" s="113"/>
-      <c r="T5" s="117"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="123"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="125"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -12228,7 +12229,7 @@
       <c r="D6" s="41"/>
       <c r="E6" s="41"/>
       <c r="F6" s="42"/>
-      <c r="G6" s="123" t="s">
+      <c r="G6" s="113" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="41"/>
@@ -12243,7 +12244,7 @@
       <c r="Q6" s="41"/>
       <c r="R6" s="41"/>
       <c r="S6" s="41"/>
-      <c r="T6" s="118"/>
+      <c r="T6" s="114"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="115" t="s">
@@ -12254,7 +12255,7 @@
       <c r="D7" s="41"/>
       <c r="E7" s="41"/>
       <c r="F7" s="42"/>
-      <c r="G7" s="123" t="s">
+      <c r="G7" s="113" t="s">
         <v>39</v>
       </c>
       <c r="H7" s="41"/>
@@ -12269,7 +12270,7 @@
       <c r="Q7" s="41"/>
       <c r="R7" s="41"/>
       <c r="S7" s="41"/>
-      <c r="T7" s="118"/>
+      <c r="T7" s="114"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -12472,29 +12473,29 @@
         <v>46</v>
       </c>
       <c r="B15" s="42"/>
-      <c r="C15" s="139" t="s">
+      <c r="C15" s="138" t="s">
         <v>40</v>
       </c>
       <c r="D15" s="42"/>
-      <c r="E15" s="124" t="s">
+      <c r="E15" s="116" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="42"/>
-      <c r="G15" s="124" t="s">
+      <c r="G15" s="116" t="s">
         <v>48</v>
       </c>
       <c r="H15" s="41"/>
       <c r="I15" s="42"/>
-      <c r="J15" s="124" t="s">
+      <c r="J15" s="116" t="s">
         <v>49</v>
       </c>
       <c r="K15" s="42"/>
-      <c r="L15" s="124" t="s">
+      <c r="L15" s="116" t="s">
         <v>50</v>
       </c>
       <c r="M15" s="41"/>
       <c r="N15" s="42"/>
-      <c r="O15" s="124" t="s">
+      <c r="O15" s="116" t="s">
         <v>51</v>
       </c>
       <c r="P15" s="41"/>
@@ -12510,33 +12511,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="137">
+      <c r="A16" s="130">
         <v>1</v>
       </c>
       <c r="B16" s="42"/>
-      <c r="C16" s="138" t="s">
+      <c r="C16" s="131" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="42"/>
-      <c r="E16" s="138" t="s">
+      <c r="E16" s="131" t="s">
         <v>56</v>
       </c>
       <c r="F16" s="42"/>
-      <c r="G16" s="130" t="s">
+      <c r="G16" s="137" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="41"/>
       <c r="I16" s="42"/>
-      <c r="J16" s="130" t="s">
+      <c r="J16" s="137" t="s">
         <v>58</v>
       </c>
       <c r="K16" s="42"/>
-      <c r="L16" s="132" t="s">
+      <c r="L16" s="134" t="s">
         <v>59</v>
       </c>
       <c r="M16" s="41"/>
       <c r="N16" s="42"/>
-      <c r="O16" s="132" t="s">
+      <c r="O16" s="134" t="s">
         <v>60</v>
       </c>
       <c r="P16" s="41"/>
@@ -12552,33 +12553,33 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="137">
+      <c r="A17" s="130">
         <v>2</v>
       </c>
       <c r="B17" s="42"/>
-      <c r="C17" s="138" t="s">
+      <c r="C17" s="131" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="42"/>
-      <c r="E17" s="138" t="s">
+      <c r="E17" s="131" t="s">
         <v>62</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="130" t="s">
+      <c r="G17" s="137" t="s">
         <v>63</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="42"/>
-      <c r="J17" s="130" t="s">
+      <c r="J17" s="137" t="s">
         <v>64</v>
       </c>
       <c r="K17" s="42"/>
-      <c r="L17" s="132" t="s">
+      <c r="L17" s="134" t="s">
         <v>65</v>
       </c>
       <c r="M17" s="41"/>
       <c r="N17" s="42"/>
-      <c r="O17" s="132" t="s">
+      <c r="O17" s="134" t="s">
         <v>66</v>
       </c>
       <c r="P17" s="41"/>
@@ -12594,21 +12595,21 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="137"/>
+      <c r="A18" s="130"/>
       <c r="B18" s="42"/>
-      <c r="C18" s="138"/>
+      <c r="C18" s="131"/>
       <c r="D18" s="42"/>
-      <c r="E18" s="138"/>
+      <c r="E18" s="131"/>
       <c r="F18" s="42"/>
-      <c r="G18" s="130"/>
+      <c r="G18" s="137"/>
       <c r="H18" s="41"/>
       <c r="I18" s="42"/>
-      <c r="J18" s="130"/>
+      <c r="J18" s="137"/>
       <c r="K18" s="42"/>
-      <c r="L18" s="132"/>
+      <c r="L18" s="134"/>
       <c r="M18" s="41"/>
       <c r="N18" s="42"/>
-      <c r="O18" s="132"/>
+      <c r="O18" s="134"/>
       <c r="P18" s="41"/>
       <c r="Q18" s="42"/>
       <c r="R18" s="32"/>
@@ -12622,21 +12623,21 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="137"/>
+      <c r="A19" s="130"/>
       <c r="B19" s="42"/>
-      <c r="C19" s="138"/>
+      <c r="C19" s="131"/>
       <c r="D19" s="42"/>
-      <c r="E19" s="138"/>
+      <c r="E19" s="131"/>
       <c r="F19" s="42"/>
-      <c r="G19" s="130"/>
+      <c r="G19" s="137"/>
       <c r="H19" s="41"/>
       <c r="I19" s="42"/>
-      <c r="J19" s="130"/>
+      <c r="J19" s="137"/>
       <c r="K19" s="42"/>
-      <c r="L19" s="132"/>
+      <c r="L19" s="134"/>
       <c r="M19" s="41"/>
       <c r="N19" s="42"/>
-      <c r="O19" s="132"/>
+      <c r="O19" s="134"/>
       <c r="P19" s="41"/>
       <c r="Q19" s="42"/>
       <c r="R19" s="32"/>
@@ -12650,21 +12651,21 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="137"/>
+      <c r="A20" s="130"/>
       <c r="B20" s="42"/>
-      <c r="C20" s="138"/>
+      <c r="C20" s="131"/>
       <c r="D20" s="42"/>
-      <c r="E20" s="138"/>
+      <c r="E20" s="131"/>
       <c r="F20" s="42"/>
-      <c r="G20" s="130"/>
+      <c r="G20" s="137"/>
       <c r="H20" s="41"/>
       <c r="I20" s="42"/>
-      <c r="J20" s="130"/>
+      <c r="J20" s="137"/>
       <c r="K20" s="42"/>
-      <c r="L20" s="132"/>
+      <c r="L20" s="134"/>
       <c r="M20" s="41"/>
       <c r="N20" s="42"/>
-      <c r="O20" s="132"/>
+      <c r="O20" s="134"/>
       <c r="P20" s="41"/>
       <c r="Q20" s="42"/>
       <c r="R20" s="32"/>
@@ -12678,21 +12679,21 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="137"/>
+      <c r="A21" s="130"/>
       <c r="B21" s="42"/>
-      <c r="C21" s="138"/>
+      <c r="C21" s="131"/>
       <c r="D21" s="42"/>
-      <c r="E21" s="138"/>
+      <c r="E21" s="131"/>
       <c r="F21" s="42"/>
-      <c r="G21" s="130"/>
+      <c r="G21" s="137"/>
       <c r="H21" s="41"/>
       <c r="I21" s="42"/>
-      <c r="J21" s="130"/>
+      <c r="J21" s="137"/>
       <c r="K21" s="42"/>
-      <c r="L21" s="132"/>
+      <c r="L21" s="134"/>
       <c r="M21" s="41"/>
       <c r="N21" s="42"/>
-      <c r="O21" s="132"/>
+      <c r="O21" s="134"/>
       <c r="P21" s="41"/>
       <c r="Q21" s="42"/>
       <c r="R21" s="32"/>
@@ -12706,21 +12707,21 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="137"/>
+      <c r="A22" s="130"/>
       <c r="B22" s="42"/>
-      <c r="C22" s="138"/>
+      <c r="C22" s="131"/>
       <c r="D22" s="42"/>
-      <c r="E22" s="138"/>
+      <c r="E22" s="131"/>
       <c r="F22" s="42"/>
-      <c r="G22" s="130"/>
+      <c r="G22" s="137"/>
       <c r="H22" s="41"/>
       <c r="I22" s="42"/>
-      <c r="J22" s="130"/>
+      <c r="J22" s="137"/>
       <c r="K22" s="42"/>
-      <c r="L22" s="132"/>
+      <c r="L22" s="134"/>
       <c r="M22" s="41"/>
       <c r="N22" s="42"/>
-      <c r="O22" s="132"/>
+      <c r="O22" s="134"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="42"/>
       <c r="R22" s="32"/>
@@ -12734,21 +12735,21 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="137"/>
+      <c r="A23" s="130"/>
       <c r="B23" s="42"/>
-      <c r="C23" s="138"/>
+      <c r="C23" s="131"/>
       <c r="D23" s="42"/>
-      <c r="E23" s="138"/>
+      <c r="E23" s="131"/>
       <c r="F23" s="42"/>
-      <c r="G23" s="130"/>
+      <c r="G23" s="137"/>
       <c r="H23" s="41"/>
       <c r="I23" s="42"/>
-      <c r="J23" s="130"/>
+      <c r="J23" s="137"/>
       <c r="K23" s="42"/>
-      <c r="L23" s="132"/>
+      <c r="L23" s="134"/>
       <c r="M23" s="41"/>
       <c r="N23" s="42"/>
-      <c r="O23" s="132"/>
+      <c r="O23" s="134"/>
       <c r="P23" s="41"/>
       <c r="Q23" s="42"/>
       <c r="R23" s="32"/>
@@ -12762,21 +12763,21 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="137"/>
+      <c r="A24" s="130"/>
       <c r="B24" s="42"/>
-      <c r="C24" s="138"/>
+      <c r="C24" s="131"/>
       <c r="D24" s="42"/>
-      <c r="E24" s="138"/>
+      <c r="E24" s="131"/>
       <c r="F24" s="42"/>
-      <c r="G24" s="130"/>
+      <c r="G24" s="137"/>
       <c r="H24" s="41"/>
       <c r="I24" s="42"/>
-      <c r="J24" s="130"/>
+      <c r="J24" s="137"/>
       <c r="K24" s="42"/>
-      <c r="L24" s="132"/>
+      <c r="L24" s="134"/>
       <c r="M24" s="41"/>
       <c r="N24" s="42"/>
-      <c r="O24" s="132"/>
+      <c r="O24" s="134"/>
       <c r="P24" s="41"/>
       <c r="Q24" s="42"/>
       <c r="R24" s="32"/>
@@ -12790,21 +12791,21 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="137"/>
+      <c r="A25" s="130"/>
       <c r="B25" s="42"/>
-      <c r="C25" s="138"/>
+      <c r="C25" s="131"/>
       <c r="D25" s="42"/>
-      <c r="E25" s="138"/>
+      <c r="E25" s="131"/>
       <c r="F25" s="42"/>
-      <c r="G25" s="130"/>
+      <c r="G25" s="137"/>
       <c r="H25" s="41"/>
       <c r="I25" s="42"/>
-      <c r="J25" s="130"/>
+      <c r="J25" s="137"/>
       <c r="K25" s="42"/>
-      <c r="L25" s="132"/>
+      <c r="L25" s="134"/>
       <c r="M25" s="41"/>
       <c r="N25" s="42"/>
-      <c r="O25" s="132"/>
+      <c r="O25" s="134"/>
       <c r="P25" s="41"/>
       <c r="Q25" s="42"/>
       <c r="R25" s="32"/>
@@ -12818,21 +12819,21 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="137"/>
+      <c r="A26" s="130"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="138"/>
+      <c r="C26" s="131"/>
       <c r="D26" s="42"/>
-      <c r="E26" s="138"/>
+      <c r="E26" s="131"/>
       <c r="F26" s="42"/>
-      <c r="G26" s="130"/>
+      <c r="G26" s="137"/>
       <c r="H26" s="41"/>
       <c r="I26" s="42"/>
-      <c r="J26" s="130"/>
+      <c r="J26" s="137"/>
       <c r="K26" s="42"/>
-      <c r="L26" s="132"/>
+      <c r="L26" s="134"/>
       <c r="M26" s="41"/>
       <c r="N26" s="42"/>
-      <c r="O26" s="132"/>
+      <c r="O26" s="134"/>
       <c r="P26" s="41"/>
       <c r="Q26" s="42"/>
       <c r="R26" s="32"/>
@@ -12846,21 +12847,21 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="137"/>
+      <c r="A27" s="130"/>
       <c r="B27" s="42"/>
-      <c r="C27" s="138"/>
+      <c r="C27" s="131"/>
       <c r="D27" s="42"/>
-      <c r="E27" s="138"/>
+      <c r="E27" s="131"/>
       <c r="F27" s="42"/>
-      <c r="G27" s="130"/>
+      <c r="G27" s="137"/>
       <c r="H27" s="41"/>
       <c r="I27" s="42"/>
-      <c r="J27" s="130"/>
+      <c r="J27" s="137"/>
       <c r="K27" s="42"/>
-      <c r="L27" s="132"/>
+      <c r="L27" s="134"/>
       <c r="M27" s="41"/>
       <c r="N27" s="42"/>
-      <c r="O27" s="132"/>
+      <c r="O27" s="134"/>
       <c r="P27" s="41"/>
       <c r="Q27" s="42"/>
       <c r="R27" s="32"/>
@@ -12874,21 +12875,21 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="137"/>
+      <c r="A28" s="130"/>
       <c r="B28" s="42"/>
-      <c r="C28" s="138"/>
+      <c r="C28" s="131"/>
       <c r="D28" s="42"/>
-      <c r="E28" s="138"/>
+      <c r="E28" s="131"/>
       <c r="F28" s="42"/>
-      <c r="G28" s="130"/>
+      <c r="G28" s="137"/>
       <c r="H28" s="41"/>
       <c r="I28" s="42"/>
-      <c r="J28" s="130"/>
+      <c r="J28" s="137"/>
       <c r="K28" s="42"/>
-      <c r="L28" s="132"/>
+      <c r="L28" s="134"/>
       <c r="M28" s="41"/>
       <c r="N28" s="42"/>
-      <c r="O28" s="132"/>
+      <c r="O28" s="134"/>
       <c r="P28" s="41"/>
       <c r="Q28" s="42"/>
       <c r="R28" s="32"/>
@@ -12902,21 +12903,21 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="137"/>
+      <c r="A29" s="130"/>
       <c r="B29" s="42"/>
-      <c r="C29" s="138"/>
+      <c r="C29" s="131"/>
       <c r="D29" s="42"/>
-      <c r="E29" s="138"/>
+      <c r="E29" s="131"/>
       <c r="F29" s="42"/>
-      <c r="G29" s="130"/>
+      <c r="G29" s="137"/>
       <c r="H29" s="41"/>
       <c r="I29" s="42"/>
-      <c r="J29" s="130"/>
+      <c r="J29" s="137"/>
       <c r="K29" s="42"/>
-      <c r="L29" s="132"/>
+      <c r="L29" s="134"/>
       <c r="M29" s="41"/>
       <c r="N29" s="42"/>
-      <c r="O29" s="132"/>
+      <c r="O29" s="134"/>
       <c r="P29" s="41"/>
       <c r="Q29" s="42"/>
       <c r="R29" s="32"/>
@@ -12930,21 +12931,21 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="137"/>
+      <c r="A30" s="130"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="138"/>
+      <c r="C30" s="131"/>
       <c r="D30" s="42"/>
-      <c r="E30" s="138"/>
+      <c r="E30" s="131"/>
       <c r="F30" s="42"/>
-      <c r="G30" s="130"/>
+      <c r="G30" s="137"/>
       <c r="H30" s="41"/>
       <c r="I30" s="42"/>
-      <c r="J30" s="130"/>
+      <c r="J30" s="137"/>
       <c r="K30" s="42"/>
-      <c r="L30" s="132"/>
+      <c r="L30" s="134"/>
       <c r="M30" s="41"/>
       <c r="N30" s="42"/>
-      <c r="O30" s="132"/>
+      <c r="O30" s="134"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="42"/>
       <c r="R30" s="32"/>
@@ -12958,23 +12959,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="140"/>
-      <c r="B31" s="129"/>
-      <c r="C31" s="141"/>
-      <c r="D31" s="129"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="129"/>
-      <c r="G31" s="131"/>
-      <c r="H31" s="126"/>
-      <c r="I31" s="129"/>
-      <c r="J31" s="131"/>
-      <c r="K31" s="129"/>
-      <c r="L31" s="133"/>
-      <c r="M31" s="126"/>
-      <c r="N31" s="129"/>
-      <c r="O31" s="133"/>
-      <c r="P31" s="126"/>
-      <c r="Q31" s="129"/>
+      <c r="A31" s="132"/>
+      <c r="B31" s="119"/>
+      <c r="C31" s="133"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="133"/>
+      <c r="F31" s="119"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="119"/>
+      <c r="J31" s="141"/>
+      <c r="K31" s="119"/>
+      <c r="L31" s="135"/>
+      <c r="M31" s="118"/>
+      <c r="N31" s="119"/>
+      <c r="O31" s="135"/>
+      <c r="P31" s="118"/>
+      <c r="Q31" s="119"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -13972,6 +13973,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -13996,118 +14109,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/削除機能詳細設計書.xlsx
+++ b/Documents/削除機能詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932907F1-AEBB-4360-BEB3-B4636498A6D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65B9F51-65EC-42B3-844D-77CF81DFE027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="108">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -147,9 +147,6 @@
     <t>テスト対象</t>
   </si>
   <si>
-    <t>ログイン画面</t>
-  </si>
-  <si>
     <t>重要度</t>
   </si>
   <si>
@@ -200,38 +197,6 @@
   <si>
     <t xml:space="preserve">正常系
 </t>
-  </si>
-  <si>
-    <t>URLアクセス</t>
-  </si>
-  <si>
-    <t>なし</t>
-  </si>
-  <si>
-    <t>http://localhost:8080/ans1101/login.html　へアクセスする</t>
-  </si>
-  <si>
-    <t>ログイン画面へ遷移する</t>
-  </si>
-  <si>
-    <t>○</t>
-  </si>
-  <si>
-    <t>異常系</t>
-  </si>
-  <si>
-    <t>ユーザIDがDBに登録されていないときのログインボタン動作</t>
-  </si>
-  <si>
-    <t>・ユーザID：999999
-・パスワード：root</t>
-  </si>
-  <si>
-    <t>ログインするボタンを押下する</t>
-  </si>
-  <si>
-    <t>エラー画面へ遷移する
-エラーの原因がユーザ名が未入力である旨通知する</t>
   </si>
   <si>
     <t>taskUN</t>
@@ -538,6 +503,158 @@
     </rPh>
     <phoneticPr fontId="11"/>
   </si>
+  <si>
+    <t>56期</t>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>山形</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマガタ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク削除画面</t>
+    <rPh sb="3" eb="7">
+      <t>サクジョガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク詳細画面からタスク削除画面へページ遷移</t>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>サクジョガメン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログイン状態かつデータベースに接続されていること</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セツゾク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除するボタンを押下する</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク削除画面が表示される</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>異常系</t>
+    <rPh sb="0" eb="3">
+      <t>イジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインされていない状態でタスク削除画面の表示させる</t>
+    <rPh sb="10" eb="12">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインされていませんというメッセージとログイン画面に誘導するリンクが表示される</t>
+    <rPh sb="24" eb="26">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態であること</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>http://localhost:8081/taskUN/task-delete.jsp</t>
+  </si>
+  <si>
+    <t>タスク削除画面で表示されたタスクを削除する</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>No.1のテストが成功している</t>
+    <rPh sb="9" eb="11">
+      <t>セイコウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク削除成功画面が表示される</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -546,7 +663,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -626,6 +743,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1304,11 +1429,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1453,6 +1579,57 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1486,21 +1663,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1546,42 +1708,6 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1645,59 +1771,80 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1705,38 +1852,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{119D988E-DC8F-4B85-8B51-E312FB7E3DA6}"/>
   </cellStyles>
@@ -3634,19 +3773,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="73"/>
+      <c r="F1" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="73"/>
       <c r="H1" s="37" t="s">
         <v>8</v>
       </c>
@@ -3658,190 +3797,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="78">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="86" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="87"/>
+      <c r="F2" s="86" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="87"/>
+      <c r="H2" s="90">
         <v>45806</v>
       </c>
-      <c r="I2" s="48" t="s">
-        <v>80</v>
-      </c>
-      <c r="J2" s="51"/>
+      <c r="I2" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="52"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="53"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="58"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="63"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="52"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="63"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="58" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="52"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="62" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="63"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="52"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="79" t="s">
+      <c r="A9" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="61"/>
-      <c r="D9" s="83" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="85"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="80"/>
-      <c r="B10" s="82" t="s">
+      <c r="A10" s="60"/>
+      <c r="B10" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="63"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="52"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="81"/>
-      <c r="B11" s="82" t="s">
+      <c r="A11" s="61"/>
+      <c r="B11" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="62" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="63"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="58" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="52"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="60"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="83" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="63"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="52"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="87"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="89"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="90"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="57"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4832,6 +4971,18 @@
     <row r="1000" s="39" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -4847,18 +4998,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4905,7 +5044,7 @@
       <c r="B2" s="44"/>
       <c r="C2" s="102"/>
       <c r="D2" s="108" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E2" s="109"/>
       <c r="F2" s="108">
@@ -4916,7 +5055,7 @@
         <v>45811</v>
       </c>
       <c r="I2" s="94" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="J2" s="95"/>
     </row>
@@ -6327,7 +6466,7 @@
       <c r="B2" s="44"/>
       <c r="C2" s="102"/>
       <c r="D2" s="108" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E2" s="109"/>
       <c r="F2" s="108">
@@ -6338,7 +6477,7 @@
         <v>45807</v>
       </c>
       <c r="I2" s="94" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="J2" s="95"/>
     </row>
@@ -7743,18 +7882,18 @@
       <c r="B2" s="44"/>
       <c r="C2" s="102"/>
       <c r="D2" s="108" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E2" s="109"/>
       <c r="F2" s="108" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G2" s="109"/>
       <c r="H2" s="91">
         <v>45807</v>
       </c>
       <c r="I2" s="94" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="J2" s="95"/>
     </row>
@@ -7783,20 +7922,20 @@
       <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="123"/>
+      <c r="B5" s="113"/>
       <c r="C5" s="107"/>
-      <c r="D5" s="124" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="123"/>
-      <c r="F5" s="123"/>
-      <c r="G5" s="123"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="125"/>
+      <c r="D5" s="116" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -7810,19 +7949,19 @@
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
-      <c r="J6" s="114"/>
+      <c r="J6" s="118"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="126"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
+      <c r="A7" s="119"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="120"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="121"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="101"/>
@@ -7834,7 +7973,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="44"/>
-      <c r="J8" s="129"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="101"/>
@@ -7846,7 +7985,7 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="44"/>
-      <c r="J9" s="129"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="101"/>
@@ -7858,7 +7997,7 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="129"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="101"/>
@@ -7870,7 +8009,7 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
-      <c r="J11" s="129"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="101"/>
@@ -7882,7 +8021,7 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
-      <c r="J12" s="129"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="101"/>
@@ -7894,7 +8033,7 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
-      <c r="J13" s="129"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="115" t="s">
@@ -7908,7 +8047,7 @@
       <c r="G14" s="41"/>
       <c r="H14" s="41"/>
       <c r="I14" s="41"/>
-      <c r="J14" s="114"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="115" t="s">
@@ -7916,8 +8055,8 @@
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="113" t="s">
-        <v>84</v>
+      <c r="D15" s="123" t="s">
+        <v>73</v>
       </c>
       <c r="E15" s="41"/>
       <c r="F15" s="41"/>
@@ -7927,7 +8066,7 @@
         <v>28</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -7948,157 +8087,157 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="116" t="s">
+      <c r="H16" s="124" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="41"/>
-      <c r="J16" s="114"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="112">
+      <c r="A17" s="114">
         <v>1</v>
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="42"/>
       <c r="D17" s="16" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="113"/>
+      <c r="H17" s="123"/>
       <c r="I17" s="41"/>
-      <c r="J17" s="114"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="112">
+      <c r="A18" s="114">
         <v>2</v>
       </c>
       <c r="B18" s="41"/>
       <c r="C18" s="42"/>
       <c r="D18" s="16" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H18" s="113"/>
+        <v>85</v>
+      </c>
+      <c r="H18" s="123"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="114"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="112">
+      <c r="A19" s="114">
         <v>3</v>
       </c>
       <c r="B19" s="41"/>
       <c r="C19" s="42"/>
       <c r="D19" s="16" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="17" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="H19" s="113"/>
+        <v>87</v>
+      </c>
+      <c r="H19" s="123"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="114"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="112">
+      <c r="A20" s="114">
         <v>4</v>
       </c>
       <c r="B20" s="41"/>
       <c r="C20" s="42"/>
       <c r="D20" s="16" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="H20" s="113"/>
+        <v>86</v>
+      </c>
+      <c r="H20" s="123"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="114"/>
+      <c r="J20" s="118"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="112">
+      <c r="A21" s="114">
         <v>5</v>
       </c>
       <c r="B21" s="41"/>
       <c r="C21" s="42"/>
       <c r="D21" s="16" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="H21" s="113"/>
+        <v>88</v>
+      </c>
+      <c r="H21" s="123"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="114"/>
+      <c r="J21" s="118"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="112">
+      <c r="A22" s="114">
         <v>6</v>
       </c>
       <c r="B22" s="41"/>
       <c r="C22" s="42"/>
       <c r="D22" s="16" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="113"/>
+      <c r="H22" s="123"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="114"/>
+      <c r="J22" s="118"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="112">
+      <c r="A23" s="114">
         <v>7</v>
       </c>
       <c r="B23" s="41"/>
       <c r="C23" s="42"/>
       <c r="D23" s="18" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="120"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="121"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="127"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
       <c r="A24" s="115"/>
@@ -8110,13 +8249,13 @@
       <c r="G24" s="41"/>
       <c r="H24" s="41"/>
       <c r="I24" s="41"/>
-      <c r="J24" s="114"/>
+      <c r="J24" s="118"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
       <c r="A25" s="115"/>
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
-      <c r="D25" s="113"/>
+      <c r="D25" s="123"/>
       <c r="E25" s="41"/>
       <c r="F25" s="41"/>
       <c r="G25" s="41"/>
@@ -8132,93 +8271,93 @@
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="116"/>
+      <c r="H26" s="124"/>
       <c r="I26" s="41"/>
-      <c r="J26" s="114"/>
+      <c r="J26" s="118"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="112"/>
+      <c r="A27" s="114"/>
       <c r="B27" s="41"/>
       <c r="C27" s="42"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="113"/>
+      <c r="H27" s="123"/>
       <c r="I27" s="41"/>
-      <c r="J27" s="114"/>
+      <c r="J27" s="118"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="112"/>
+      <c r="A28" s="114"/>
       <c r="B28" s="41"/>
       <c r="C28" s="42"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="113"/>
+      <c r="H28" s="123"/>
       <c r="I28" s="41"/>
-      <c r="J28" s="114"/>
+      <c r="J28" s="118"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="112"/>
+      <c r="A29" s="114"/>
       <c r="B29" s="41"/>
       <c r="C29" s="42"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
-      <c r="H29" s="113"/>
+      <c r="H29" s="123"/>
       <c r="I29" s="41"/>
-      <c r="J29" s="114"/>
+      <c r="J29" s="118"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="112"/>
+      <c r="A30" s="114"/>
       <c r="B30" s="41"/>
       <c r="C30" s="42"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="113"/>
+      <c r="H30" s="123"/>
       <c r="I30" s="41"/>
-      <c r="J30" s="114"/>
+      <c r="J30" s="118"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="112"/>
+      <c r="A31" s="114"/>
       <c r="B31" s="41"/>
       <c r="C31" s="42"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="113"/>
+      <c r="H31" s="123"/>
       <c r="I31" s="41"/>
-      <c r="J31" s="114"/>
+      <c r="J31" s="118"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="112"/>
+      <c r="A32" s="114"/>
       <c r="B32" s="41"/>
       <c r="C32" s="42"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="113"/>
+      <c r="H32" s="123"/>
       <c r="I32" s="41"/>
-      <c r="J32" s="114"/>
+      <c r="J32" s="118"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="117"/>
-      <c r="B33" s="118"/>
-      <c r="C33" s="119"/>
+      <c r="A33" s="128"/>
+      <c r="B33" s="126"/>
+      <c r="C33" s="129"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
-      <c r="H33" s="120"/>
-      <c r="I33" s="118"/>
-      <c r="J33" s="121"/>
+      <c r="H33" s="125"/>
+      <c r="I33" s="126"/>
+      <c r="J33" s="127"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
       <c r="A34" s="115"/>
@@ -8230,13 +8369,13 @@
       <c r="G34" s="41"/>
       <c r="H34" s="41"/>
       <c r="I34" s="41"/>
-      <c r="J34" s="114"/>
+      <c r="J34" s="118"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
       <c r="A35" s="115"/>
       <c r="B35" s="41"/>
       <c r="C35" s="42"/>
-      <c r="D35" s="113"/>
+      <c r="D35" s="123"/>
       <c r="E35" s="41"/>
       <c r="F35" s="41"/>
       <c r="G35" s="41"/>
@@ -8252,69 +8391,69 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
-      <c r="H36" s="116"/>
+      <c r="H36" s="124"/>
       <c r="I36" s="41"/>
-      <c r="J36" s="114"/>
+      <c r="J36" s="118"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="112"/>
+      <c r="A37" s="114"/>
       <c r="B37" s="41"/>
       <c r="C37" s="42"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="113"/>
+      <c r="H37" s="123"/>
       <c r="I37" s="41"/>
-      <c r="J37" s="114"/>
+      <c r="J37" s="118"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="112"/>
+      <c r="A38" s="114"/>
       <c r="B38" s="41"/>
       <c r="C38" s="42"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="113"/>
+      <c r="H38" s="123"/>
       <c r="I38" s="41"/>
-      <c r="J38" s="114"/>
+      <c r="J38" s="118"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="112"/>
+      <c r="A39" s="114"/>
       <c r="B39" s="41"/>
       <c r="C39" s="42"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="113"/>
+      <c r="H39" s="123"/>
       <c r="I39" s="41"/>
-      <c r="J39" s="114"/>
+      <c r="J39" s="118"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="112"/>
+      <c r="A40" s="114"/>
       <c r="B40" s="41"/>
       <c r="C40" s="42"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="113"/>
+      <c r="H40" s="123"/>
       <c r="I40" s="41"/>
-      <c r="J40" s="114"/>
+      <c r="J40" s="118"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="112"/>
+      <c r="A41" s="114"/>
       <c r="B41" s="41"/>
       <c r="C41" s="42"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="113"/>
+      <c r="H41" s="123"/>
       <c r="I41" s="41"/>
-      <c r="J41" s="114"/>
+      <c r="J41" s="118"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9277,11 +9416,50 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9298,50 +9476,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9392,18 +9531,18 @@
       <c r="B2" s="44"/>
       <c r="C2" s="102"/>
       <c r="D2" s="108" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E2" s="109"/>
       <c r="F2" s="108" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G2" s="109"/>
       <c r="H2" s="91">
         <v>45807</v>
       </c>
       <c r="I2" s="94" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="J2" s="95"/>
     </row>
@@ -9432,20 +9571,20 @@
       <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="123"/>
+      <c r="B5" s="113"/>
       <c r="C5" s="107"/>
-      <c r="D5" s="124" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="123"/>
-      <c r="F5" s="123"/>
-      <c r="G5" s="123"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="125"/>
+      <c r="D5" s="116" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -9459,19 +9598,19 @@
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
-      <c r="J6" s="114"/>
+      <c r="J6" s="118"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="126"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
+      <c r="A7" s="119"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="120"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="121"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="101"/>
@@ -9483,7 +9622,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="44"/>
-      <c r="J8" s="129"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="101"/>
@@ -9495,7 +9634,7 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="44"/>
-      <c r="J9" s="129"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="101"/>
@@ -9507,7 +9646,7 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="129"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="101"/>
@@ -9519,7 +9658,7 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
-      <c r="J11" s="129"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="101"/>
@@ -9531,7 +9670,7 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
-      <c r="J12" s="129"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="101"/>
@@ -9543,7 +9682,7 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
-      <c r="J13" s="129"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="115" t="s">
@@ -9557,7 +9696,7 @@
       <c r="G14" s="41"/>
       <c r="H14" s="41"/>
       <c r="I14" s="41"/>
-      <c r="J14" s="114"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="115" t="s">
@@ -9565,8 +9704,8 @@
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="113" t="s">
-        <v>70</v>
+      <c r="D15" s="123" t="s">
+        <v>59</v>
       </c>
       <c r="E15" s="41"/>
       <c r="F15" s="41"/>
@@ -9576,7 +9715,7 @@
         <v>28</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -9597,107 +9736,107 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="116" t="s">
+      <c r="H16" s="124" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="41"/>
-      <c r="J16" s="114"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="112">
+      <c r="A17" s="114">
         <v>1</v>
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="42"/>
       <c r="D17" s="16" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="113" t="s">
-        <v>75</v>
+        <v>63</v>
+      </c>
+      <c r="H17" s="123" t="s">
+        <v>64</v>
       </c>
       <c r="I17" s="41"/>
-      <c r="J17" s="114"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="112"/>
+      <c r="A18" s="114"/>
       <c r="B18" s="41"/>
       <c r="C18" s="42"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="113"/>
+      <c r="H18" s="123"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="114"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="112"/>
+      <c r="A19" s="114"/>
       <c r="B19" s="41"/>
       <c r="C19" s="42"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="113"/>
+      <c r="H19" s="123"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="114"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="112"/>
+      <c r="A20" s="114"/>
       <c r="B20" s="41"/>
       <c r="C20" s="42"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="113"/>
+      <c r="H20" s="123"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="114"/>
+      <c r="J20" s="118"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="112"/>
+      <c r="A21" s="114"/>
       <c r="B21" s="41"/>
       <c r="C21" s="42"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="113"/>
+      <c r="H21" s="123"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="114"/>
+      <c r="J21" s="118"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="112"/>
+      <c r="A22" s="114"/>
       <c r="B22" s="41"/>
       <c r="C22" s="42"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="113"/>
+      <c r="H22" s="123"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="114"/>
+      <c r="J22" s="118"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="117"/>
-      <c r="B23" s="118"/>
-      <c r="C23" s="119"/>
+      <c r="A23" s="128"/>
+      <c r="B23" s="126"/>
+      <c r="C23" s="129"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="120"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="121"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="127"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10678,6 +10817,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -10693,22 +10848,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10759,18 +10898,18 @@
       <c r="B2" s="44"/>
       <c r="C2" s="102"/>
       <c r="D2" s="108" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E2" s="109"/>
       <c r="F2" s="108" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G2" s="109"/>
       <c r="H2" s="91">
         <v>45805</v>
       </c>
       <c r="I2" s="94" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="J2" s="95"/>
     </row>
@@ -10799,20 +10938,20 @@
       <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="123"/>
+      <c r="B5" s="113"/>
       <c r="C5" s="107"/>
-      <c r="D5" s="124" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="123"/>
-      <c r="F5" s="123"/>
-      <c r="G5" s="123"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="125"/>
+      <c r="D5" s="116" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -10826,19 +10965,19 @@
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
-      <c r="J6" s="114"/>
+      <c r="J6" s="118"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="126"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
+      <c r="A7" s="119"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="120"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="121"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="101"/>
@@ -10850,7 +10989,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="44"/>
-      <c r="J8" s="129"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="101"/>
@@ -10862,7 +11001,7 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="44"/>
-      <c r="J9" s="129"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="101"/>
@@ -10874,7 +11013,7 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="129"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="101"/>
@@ -10886,7 +11025,7 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
-      <c r="J11" s="129"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="101"/>
@@ -10898,7 +11037,7 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
-      <c r="J12" s="129"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="101"/>
@@ -10910,7 +11049,7 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
-      <c r="J13" s="129"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="115" t="s">
@@ -10924,7 +11063,7 @@
       <c r="G14" s="41"/>
       <c r="H14" s="41"/>
       <c r="I14" s="41"/>
-      <c r="J14" s="114"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="115" t="s">
@@ -10932,8 +11071,8 @@
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="113" t="s">
-        <v>70</v>
+      <c r="D15" s="123" t="s">
+        <v>59</v>
       </c>
       <c r="E15" s="41"/>
       <c r="F15" s="41"/>
@@ -10943,7 +11082,7 @@
         <v>28</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -10964,107 +11103,107 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="116" t="s">
+      <c r="H16" s="124" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="41"/>
-      <c r="J16" s="114"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="112">
+      <c r="A17" s="114">
         <v>1</v>
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="42"/>
       <c r="D17" s="16" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="113" t="s">
-        <v>75</v>
+        <v>63</v>
+      </c>
+      <c r="H17" s="123" t="s">
+        <v>64</v>
       </c>
       <c r="I17" s="41"/>
-      <c r="J17" s="114"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="112"/>
+      <c r="A18" s="114"/>
       <c r="B18" s="41"/>
       <c r="C18" s="42"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="113"/>
+      <c r="H18" s="123"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="114"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="112"/>
+      <c r="A19" s="114"/>
       <c r="B19" s="41"/>
       <c r="C19" s="42"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="113"/>
+      <c r="H19" s="123"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="114"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="112"/>
+      <c r="A20" s="114"/>
       <c r="B20" s="41"/>
       <c r="C20" s="42"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="113"/>
+      <c r="H20" s="123"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="114"/>
+      <c r="J20" s="118"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="112"/>
+      <c r="A21" s="114"/>
       <c r="B21" s="41"/>
       <c r="C21" s="42"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="113"/>
+      <c r="H21" s="123"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="114"/>
+      <c r="J21" s="118"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="112"/>
+      <c r="A22" s="114"/>
       <c r="B22" s="41"/>
       <c r="C22" s="42"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="113"/>
+      <c r="H22" s="123"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="114"/>
+      <c r="J22" s="118"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="117"/>
-      <c r="B23" s="118"/>
-      <c r="C23" s="119"/>
+      <c r="A23" s="128"/>
+      <c r="B23" s="126"/>
+      <c r="C23" s="129"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="120"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="121"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="127"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12045,6 +12184,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -12060,22 +12215,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12095,7 +12234,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="135" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="99"/>
@@ -12106,14 +12245,14 @@
       <c r="G1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
       <c r="J1" s="107"/>
       <c r="K1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
       <c r="N1" s="107"/>
       <c r="O1" s="106" t="s">
         <v>8</v>
@@ -12126,7 +12265,7 @@
       <c r="S1" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="125"/>
+      <c r="T1" s="117"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="101"/>
@@ -12135,20 +12274,28 @@
       <c r="D2" s="44"/>
       <c r="E2" s="44"/>
       <c r="F2" s="102"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
+      <c r="G2" s="108" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
       <c r="J2" s="109"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
+      <c r="K2" s="108" t="s">
+        <v>93</v>
+      </c>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
       <c r="N2" s="109"/>
-      <c r="O2" s="108"/>
+      <c r="O2" s="142">
+        <v>45821</v>
+      </c>
       <c r="P2" s="109"/>
-      <c r="Q2" s="108"/>
+      <c r="Q2" s="108" t="s">
+        <v>94</v>
+      </c>
       <c r="R2" s="109"/>
       <c r="S2" s="108"/>
-      <c r="T2" s="128"/>
+      <c r="T2" s="121"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="101"/>
@@ -12170,7 +12317,7 @@
       <c r="Q3" s="110"/>
       <c r="R3" s="102"/>
       <c r="S3" s="110"/>
-      <c r="T3" s="129"/>
+      <c r="T3" s="122"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="103"/>
@@ -12192,33 +12339,33 @@
       <c r="Q4" s="111"/>
       <c r="R4" s="105"/>
       <c r="S4" s="111"/>
-      <c r="T4" s="139"/>
+      <c r="T4" s="134"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="123"/>
-      <c r="C5" s="123"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="123"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
       <c r="F5" s="107"/>
       <c r="G5" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="123"/>
-      <c r="K5" s="123"/>
-      <c r="L5" s="123"/>
-      <c r="M5" s="123"/>
-      <c r="N5" s="123"/>
-      <c r="O5" s="123"/>
-      <c r="P5" s="123"/>
-      <c r="Q5" s="123"/>
-      <c r="R5" s="123"/>
-      <c r="S5" s="123"/>
-      <c r="T5" s="125"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="117"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -12229,7 +12376,7 @@
       <c r="D6" s="41"/>
       <c r="E6" s="41"/>
       <c r="F6" s="42"/>
-      <c r="G6" s="113" t="s">
+      <c r="G6" s="123" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="41"/>
@@ -12244,7 +12391,7 @@
       <c r="Q6" s="41"/>
       <c r="R6" s="41"/>
       <c r="S6" s="41"/>
-      <c r="T6" s="114"/>
+      <c r="T6" s="118"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="115" t="s">
@@ -12255,8 +12402,8 @@
       <c r="D7" s="41"/>
       <c r="E7" s="41"/>
       <c r="F7" s="42"/>
-      <c r="G7" s="113" t="s">
-        <v>39</v>
+      <c r="G7" s="123" t="s">
+        <v>95</v>
       </c>
       <c r="H7" s="41"/>
       <c r="I7" s="41"/>
@@ -12270,7 +12417,7 @@
       <c r="Q7" s="41"/>
       <c r="R7" s="41"/>
       <c r="S7" s="41"/>
-      <c r="T7" s="114"/>
+      <c r="T7" s="118"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -12298,11 +12445,11 @@
       <c r="A9" s="20"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="24"/>
@@ -12332,7 +12479,7 @@
       <c r="C10" s="26"/>
       <c r="D10" s="21"/>
       <c r="E10" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="21"/>
       <c r="G10" s="27"/>
@@ -12362,7 +12509,7 @@
       <c r="C11" s="26"/>
       <c r="D11" s="21"/>
       <c r="E11" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" s="21"/>
       <c r="G11" s="27"/>
@@ -12392,7 +12539,7 @@
       <c r="C12" s="26"/>
       <c r="D12" s="21"/>
       <c r="E12" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="21"/>
       <c r="G12" s="27"/>
@@ -12422,7 +12569,7 @@
       <c r="C13" s="28"/>
       <c r="D13" s="29"/>
       <c r="E13" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="29"/>
       <c r="G13" s="30"/>
@@ -12470,75 +12617,75 @@
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
       <c r="A15" s="115" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="139" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="42"/>
+      <c r="E15" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="138" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="116" t="s">
+      <c r="F15" s="42"/>
+      <c r="G15" s="124" t="s">
         <v>47</v>
-      </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="116" t="s">
-        <v>48</v>
       </c>
       <c r="H15" s="41"/>
       <c r="I15" s="42"/>
-      <c r="J15" s="116" t="s">
+      <c r="J15" s="124" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" s="42"/>
+      <c r="L15" s="124" t="s">
         <v>49</v>
-      </c>
-      <c r="K15" s="42"/>
-      <c r="L15" s="116" t="s">
-        <v>50</v>
       </c>
       <c r="M15" s="41"/>
       <c r="N15" s="42"/>
-      <c r="O15" s="116" t="s">
-        <v>51</v>
+      <c r="O15" s="124" t="s">
+        <v>50</v>
       </c>
       <c r="P15" s="41"/>
       <c r="Q15" s="42"/>
       <c r="R15" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="S15" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="S15" s="14" t="s">
+      <c r="T15" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="T15" s="31" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="54.75" customHeight="1">
+      <c r="A16" s="137">
+        <v>1</v>
+      </c>
+      <c r="B16" s="42"/>
+      <c r="C16" s="138" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="130">
-        <v>1</v>
-      </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="131" t="s">
+      <c r="D16" s="42"/>
+      <c r="E16" s="138" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="131" t="s">
-        <v>56</v>
-      </c>
       <c r="F16" s="42"/>
-      <c r="G16" s="137" t="s">
-        <v>57</v>
+      <c r="G16" s="130" t="s">
+        <v>96</v>
       </c>
       <c r="H16" s="41"/>
       <c r="I16" s="42"/>
-      <c r="J16" s="137" t="s">
-        <v>58</v>
-      </c>
-      <c r="K16" s="42"/>
-      <c r="L16" s="134" t="s">
-        <v>59</v>
+      <c r="J16" s="143" t="s">
+        <v>97</v>
+      </c>
+      <c r="K16" s="144"/>
+      <c r="L16" s="132" t="s">
+        <v>98</v>
       </c>
       <c r="M16" s="41"/>
       <c r="N16" s="42"/>
-      <c r="O16" s="134" t="s">
-        <v>60</v>
+      <c r="O16" s="132" t="s">
+        <v>99</v>
       </c>
       <c r="P16" s="41"/>
       <c r="Q16" s="42"/>
@@ -12552,35 +12699,35 @@
       <c r="Y16" s="34"/>
       <c r="Z16" s="34"/>
     </row>
-    <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="130">
+    <row r="17" spans="1:26" ht="54.75" customHeight="1">
+      <c r="A17" s="137">
         <v>2</v>
       </c>
       <c r="B17" s="42"/>
-      <c r="C17" s="131" t="s">
-        <v>61</v>
+      <c r="C17" s="138" t="s">
+        <v>54</v>
       </c>
       <c r="D17" s="42"/>
-      <c r="E17" s="131" t="s">
-        <v>62</v>
+      <c r="E17" s="138" t="s">
+        <v>55</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="137" t="s">
-        <v>63</v>
+      <c r="G17" s="130" t="s">
+        <v>105</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="42"/>
-      <c r="J17" s="137" t="s">
-        <v>64</v>
+      <c r="J17" s="130" t="s">
+        <v>106</v>
       </c>
       <c r="K17" s="42"/>
-      <c r="L17" s="134" t="s">
-        <v>65</v>
+      <c r="L17" s="132" t="s">
+        <v>98</v>
       </c>
       <c r="M17" s="41"/>
       <c r="N17" s="42"/>
-      <c r="O17" s="134" t="s">
-        <v>66</v>
+      <c r="O17" s="132" t="s">
+        <v>107</v>
       </c>
       <c r="P17" s="41"/>
       <c r="Q17" s="42"/>
@@ -12594,22 +12741,36 @@
       <c r="Y17" s="34"/>
       <c r="Z17" s="34"/>
     </row>
-    <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="130"/>
+    <row r="18" spans="1:26" ht="64.5" customHeight="1">
+      <c r="A18" s="137">
+        <v>3</v>
+      </c>
       <c r="B18" s="42"/>
-      <c r="C18" s="131"/>
+      <c r="C18" s="138" t="s">
+        <v>54</v>
+      </c>
       <c r="D18" s="42"/>
-      <c r="E18" s="131"/>
+      <c r="E18" s="138" t="s">
+        <v>100</v>
+      </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="137"/>
+      <c r="G18" s="130" t="s">
+        <v>101</v>
+      </c>
       <c r="H18" s="41"/>
       <c r="I18" s="42"/>
-      <c r="J18" s="137"/>
+      <c r="J18" s="130" t="s">
+        <v>103</v>
+      </c>
       <c r="K18" s="42"/>
-      <c r="L18" s="134"/>
+      <c r="L18" s="145" t="s">
+        <v>104</v>
+      </c>
       <c r="M18" s="41"/>
       <c r="N18" s="42"/>
-      <c r="O18" s="134"/>
+      <c r="O18" s="132" t="s">
+        <v>102</v>
+      </c>
       <c r="P18" s="41"/>
       <c r="Q18" s="42"/>
       <c r="R18" s="32"/>
@@ -12623,21 +12784,21 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="130"/>
+      <c r="A19" s="137"/>
       <c r="B19" s="42"/>
-      <c r="C19" s="131"/>
+      <c r="C19" s="138"/>
       <c r="D19" s="42"/>
-      <c r="E19" s="131"/>
+      <c r="E19" s="138"/>
       <c r="F19" s="42"/>
-      <c r="G19" s="137"/>
+      <c r="G19" s="130"/>
       <c r="H19" s="41"/>
       <c r="I19" s="42"/>
-      <c r="J19" s="137"/>
+      <c r="J19" s="130"/>
       <c r="K19" s="42"/>
-      <c r="L19" s="134"/>
+      <c r="L19" s="132"/>
       <c r="M19" s="41"/>
       <c r="N19" s="42"/>
-      <c r="O19" s="134"/>
+      <c r="O19" s="132"/>
       <c r="P19" s="41"/>
       <c r="Q19" s="42"/>
       <c r="R19" s="32"/>
@@ -12651,21 +12812,21 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="130"/>
+      <c r="A20" s="137"/>
       <c r="B20" s="42"/>
-      <c r="C20" s="131"/>
+      <c r="C20" s="138"/>
       <c r="D20" s="42"/>
-      <c r="E20" s="131"/>
+      <c r="E20" s="138"/>
       <c r="F20" s="42"/>
-      <c r="G20" s="137"/>
+      <c r="G20" s="130"/>
       <c r="H20" s="41"/>
       <c r="I20" s="42"/>
-      <c r="J20" s="137"/>
+      <c r="J20" s="130"/>
       <c r="K20" s="42"/>
-      <c r="L20" s="134"/>
+      <c r="L20" s="132"/>
       <c r="M20" s="41"/>
       <c r="N20" s="42"/>
-      <c r="O20" s="134"/>
+      <c r="O20" s="132"/>
       <c r="P20" s="41"/>
       <c r="Q20" s="42"/>
       <c r="R20" s="32"/>
@@ -12679,21 +12840,21 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="130"/>
+      <c r="A21" s="137"/>
       <c r="B21" s="42"/>
-      <c r="C21" s="131"/>
+      <c r="C21" s="138"/>
       <c r="D21" s="42"/>
-      <c r="E21" s="131"/>
+      <c r="E21" s="138"/>
       <c r="F21" s="42"/>
-      <c r="G21" s="137"/>
+      <c r="G21" s="130"/>
       <c r="H21" s="41"/>
       <c r="I21" s="42"/>
-      <c r="J21" s="137"/>
+      <c r="J21" s="130"/>
       <c r="K21" s="42"/>
-      <c r="L21" s="134"/>
+      <c r="L21" s="132"/>
       <c r="M21" s="41"/>
       <c r="N21" s="42"/>
-      <c r="O21" s="134"/>
+      <c r="O21" s="132"/>
       <c r="P21" s="41"/>
       <c r="Q21" s="42"/>
       <c r="R21" s="32"/>
@@ -12707,21 +12868,21 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="130"/>
+      <c r="A22" s="137"/>
       <c r="B22" s="42"/>
-      <c r="C22" s="131"/>
+      <c r="C22" s="138"/>
       <c r="D22" s="42"/>
-      <c r="E22" s="131"/>
+      <c r="E22" s="138"/>
       <c r="F22" s="42"/>
-      <c r="G22" s="137"/>
+      <c r="G22" s="130"/>
       <c r="H22" s="41"/>
       <c r="I22" s="42"/>
-      <c r="J22" s="137"/>
+      <c r="J22" s="130"/>
       <c r="K22" s="42"/>
-      <c r="L22" s="134"/>
+      <c r="L22" s="132"/>
       <c r="M22" s="41"/>
       <c r="N22" s="42"/>
-      <c r="O22" s="134"/>
+      <c r="O22" s="132"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="42"/>
       <c r="R22" s="32"/>
@@ -12735,21 +12896,21 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="130"/>
+      <c r="A23" s="137"/>
       <c r="B23" s="42"/>
-      <c r="C23" s="131"/>
+      <c r="C23" s="138"/>
       <c r="D23" s="42"/>
-      <c r="E23" s="131"/>
+      <c r="E23" s="138"/>
       <c r="F23" s="42"/>
-      <c r="G23" s="137"/>
+      <c r="G23" s="130"/>
       <c r="H23" s="41"/>
       <c r="I23" s="42"/>
-      <c r="J23" s="137"/>
+      <c r="J23" s="130"/>
       <c r="K23" s="42"/>
-      <c r="L23" s="134"/>
+      <c r="L23" s="132"/>
       <c r="M23" s="41"/>
       <c r="N23" s="42"/>
-      <c r="O23" s="134"/>
+      <c r="O23" s="132"/>
       <c r="P23" s="41"/>
       <c r="Q23" s="42"/>
       <c r="R23" s="32"/>
@@ -12763,21 +12924,21 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="130"/>
+      <c r="A24" s="137"/>
       <c r="B24" s="42"/>
-      <c r="C24" s="131"/>
+      <c r="C24" s="138"/>
       <c r="D24" s="42"/>
-      <c r="E24" s="131"/>
+      <c r="E24" s="138"/>
       <c r="F24" s="42"/>
-      <c r="G24" s="137"/>
+      <c r="G24" s="130"/>
       <c r="H24" s="41"/>
       <c r="I24" s="42"/>
-      <c r="J24" s="137"/>
+      <c r="J24" s="130"/>
       <c r="K24" s="42"/>
-      <c r="L24" s="134"/>
+      <c r="L24" s="132"/>
       <c r="M24" s="41"/>
       <c r="N24" s="42"/>
-      <c r="O24" s="134"/>
+      <c r="O24" s="132"/>
       <c r="P24" s="41"/>
       <c r="Q24" s="42"/>
       <c r="R24" s="32"/>
@@ -12791,21 +12952,21 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="130"/>
+      <c r="A25" s="137"/>
       <c r="B25" s="42"/>
-      <c r="C25" s="131"/>
+      <c r="C25" s="138"/>
       <c r="D25" s="42"/>
-      <c r="E25" s="131"/>
+      <c r="E25" s="138"/>
       <c r="F25" s="42"/>
-      <c r="G25" s="137"/>
+      <c r="G25" s="130"/>
       <c r="H25" s="41"/>
       <c r="I25" s="42"/>
-      <c r="J25" s="137"/>
+      <c r="J25" s="130"/>
       <c r="K25" s="42"/>
-      <c r="L25" s="134"/>
+      <c r="L25" s="132"/>
       <c r="M25" s="41"/>
       <c r="N25" s="42"/>
-      <c r="O25" s="134"/>
+      <c r="O25" s="132"/>
       <c r="P25" s="41"/>
       <c r="Q25" s="42"/>
       <c r="R25" s="32"/>
@@ -12819,21 +12980,21 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="130"/>
+      <c r="A26" s="137"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="131"/>
+      <c r="C26" s="138"/>
       <c r="D26" s="42"/>
-      <c r="E26" s="131"/>
+      <c r="E26" s="138"/>
       <c r="F26" s="42"/>
-      <c r="G26" s="137"/>
+      <c r="G26" s="130"/>
       <c r="H26" s="41"/>
       <c r="I26" s="42"/>
-      <c r="J26" s="137"/>
+      <c r="J26" s="130"/>
       <c r="K26" s="42"/>
-      <c r="L26" s="134"/>
+      <c r="L26" s="132"/>
       <c r="M26" s="41"/>
       <c r="N26" s="42"/>
-      <c r="O26" s="134"/>
+      <c r="O26" s="132"/>
       <c r="P26" s="41"/>
       <c r="Q26" s="42"/>
       <c r="R26" s="32"/>
@@ -12847,21 +13008,21 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="130"/>
+      <c r="A27" s="137"/>
       <c r="B27" s="42"/>
-      <c r="C27" s="131"/>
+      <c r="C27" s="138"/>
       <c r="D27" s="42"/>
-      <c r="E27" s="131"/>
+      <c r="E27" s="138"/>
       <c r="F27" s="42"/>
-      <c r="G27" s="137"/>
+      <c r="G27" s="130"/>
       <c r="H27" s="41"/>
       <c r="I27" s="42"/>
-      <c r="J27" s="137"/>
+      <c r="J27" s="130"/>
       <c r="K27" s="42"/>
-      <c r="L27" s="134"/>
+      <c r="L27" s="132"/>
       <c r="M27" s="41"/>
       <c r="N27" s="42"/>
-      <c r="O27" s="134"/>
+      <c r="O27" s="132"/>
       <c r="P27" s="41"/>
       <c r="Q27" s="42"/>
       <c r="R27" s="32"/>
@@ -12875,21 +13036,21 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="130"/>
+      <c r="A28" s="137"/>
       <c r="B28" s="42"/>
-      <c r="C28" s="131"/>
+      <c r="C28" s="138"/>
       <c r="D28" s="42"/>
-      <c r="E28" s="131"/>
+      <c r="E28" s="138"/>
       <c r="F28" s="42"/>
-      <c r="G28" s="137"/>
+      <c r="G28" s="130"/>
       <c r="H28" s="41"/>
       <c r="I28" s="42"/>
-      <c r="J28" s="137"/>
+      <c r="J28" s="130"/>
       <c r="K28" s="42"/>
-      <c r="L28" s="134"/>
+      <c r="L28" s="132"/>
       <c r="M28" s="41"/>
       <c r="N28" s="42"/>
-      <c r="O28" s="134"/>
+      <c r="O28" s="132"/>
       <c r="P28" s="41"/>
       <c r="Q28" s="42"/>
       <c r="R28" s="32"/>
@@ -12903,21 +13064,21 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="130"/>
+      <c r="A29" s="137"/>
       <c r="B29" s="42"/>
-      <c r="C29" s="131"/>
+      <c r="C29" s="138"/>
       <c r="D29" s="42"/>
-      <c r="E29" s="131"/>
+      <c r="E29" s="138"/>
       <c r="F29" s="42"/>
-      <c r="G29" s="137"/>
+      <c r="G29" s="130"/>
       <c r="H29" s="41"/>
       <c r="I29" s="42"/>
-      <c r="J29" s="137"/>
+      <c r="J29" s="130"/>
       <c r="K29" s="42"/>
-      <c r="L29" s="134"/>
+      <c r="L29" s="132"/>
       <c r="M29" s="41"/>
       <c r="N29" s="42"/>
-      <c r="O29" s="134"/>
+      <c r="O29" s="132"/>
       <c r="P29" s="41"/>
       <c r="Q29" s="42"/>
       <c r="R29" s="32"/>
@@ -12931,21 +13092,21 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="130"/>
+      <c r="A30" s="137"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="131"/>
+      <c r="C30" s="138"/>
       <c r="D30" s="42"/>
-      <c r="E30" s="131"/>
+      <c r="E30" s="138"/>
       <c r="F30" s="42"/>
-      <c r="G30" s="137"/>
+      <c r="G30" s="130"/>
       <c r="H30" s="41"/>
       <c r="I30" s="42"/>
-      <c r="J30" s="137"/>
+      <c r="J30" s="130"/>
       <c r="K30" s="42"/>
-      <c r="L30" s="134"/>
+      <c r="L30" s="132"/>
       <c r="M30" s="41"/>
       <c r="N30" s="42"/>
-      <c r="O30" s="134"/>
+      <c r="O30" s="132"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="42"/>
       <c r="R30" s="32"/>
@@ -12959,23 +13120,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="132"/>
-      <c r="B31" s="119"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="119"/>
-      <c r="J31" s="141"/>
-      <c r="K31" s="119"/>
-      <c r="L31" s="135"/>
-      <c r="M31" s="118"/>
-      <c r="N31" s="119"/>
-      <c r="O31" s="135"/>
-      <c r="P31" s="118"/>
-      <c r="Q31" s="119"/>
+      <c r="A31" s="140"/>
+      <c r="B31" s="129"/>
+      <c r="C31" s="141"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="129"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="126"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="131"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="133"/>
+      <c r="M31" s="126"/>
+      <c r="N31" s="129"/>
+      <c r="O31" s="133"/>
+      <c r="P31" s="126"/>
+      <c r="Q31" s="129"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -13973,62 +14134,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14053,64 +14214,67 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
+  <hyperlinks>
+    <hyperlink ref="L18" r:id="rId1" display="http://localhost:8080/taskUN/task-delete.jsp" xr:uid="{38C81AFB-41F8-4093-85EB-71ACC0BAB2DD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>

--- a/Documents/削除機能詳細設計書.xlsx
+++ b/Documents/削除機能詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65B9F51-65EC-42B3-844D-77CF81DFE027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CC95FB-3FB5-4EBB-BC35-E940D9793321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -21,13 +21,21 @@
     <sheet name="画面設計書-削除完了画面" sheetId="7" r:id="rId6"/>
     <sheet name="画面設計書-削除失敗画面" sheetId="8" r:id="rId7"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
+    <sheet name="JUnitテスト仕様書兼報告書" sheetId="10" r:id="rId9"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="範囲１" localSheetId="8">#REF!</definedName>
+    <definedName name="範囲１">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="123">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -655,6 +663,116 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>JUnitテスト仕様書兼報告書</t>
+    <rPh sb="8" eb="11">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ホウコクショ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>会社名</t>
+    <rPh sb="0" eb="3">
+      <t>カイシャメイ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>コンサイズ</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>実施者</t>
+    <rPh sb="0" eb="2">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <rPh sb="0" eb="2">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>テストクラス</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>検証するメソッド</t>
+    <rPh sb="0" eb="2">
+      <t>ケンショウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>期待する結果</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシビ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>備考・特記事項</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トッキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
 </sst>
 </file>
 
@@ -663,7 +781,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -753,8 +871,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -767,8 +923,14 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="57">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1428,13 +1590,193 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1579,6 +1921,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1589,11 +1964,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1609,9 +2032,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1630,84 +2050,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1771,27 +2113,48 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1804,80 +2167,190 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="57" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="62" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
     <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{119D988E-DC8F-4B85-8B51-E312FB7E3DA6}"/>
+    <cellStyle name="標準_生産計画ED書" xfId="3" xr:uid="{163B9DFD-108E-4647-926A-6DE66DEE9AA9}"/>
+    <cellStyle name="標準_東京理科大DBレイアウト" xfId="4" xr:uid="{CE60439D-A446-444C-B63B-DFF2AEEE066A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2397,6 +2870,24 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="JUnitテスト仕様書兼報告書"/>
+      <sheetName val="別紙"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3773,19 +4264,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="85" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="85" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="73"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="37" t="s">
         <v>8</v>
       </c>
@@ -3797,190 +4288,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="86" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="90">
+      <c r="G2" s="75"/>
+      <c r="H2" s="78">
         <v>45806</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="51"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="52"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="74" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="75"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="58" t="s">
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="52"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="58" t="s">
+      <c r="B7" s="60"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="52"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="63"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="58" t="s">
+      <c r="B8" s="60"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="52"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="63"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="51" t="s">
+      <c r="C9" s="61"/>
+      <c r="D9" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="64"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="89"/>
+      <c r="J9" s="90"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="62" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="52"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="63"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="61"/>
-      <c r="B11" s="62" t="s">
+      <c r="A11" s="87"/>
+      <c r="B11" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="58" t="s">
+      <c r="C11" s="61"/>
+      <c r="D11" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="52"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="63"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="51" t="s">
+      <c r="B12" s="60"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="79" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="52"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="63"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="57"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="84"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4971,18 +5462,6 @@
     <row r="1000" s="39" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -4998,6 +5477,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7922,20 +8413,20 @@
       <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="113"/>
+      <c r="B5" s="123"/>
       <c r="C5" s="107"/>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="124" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="125"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -7949,19 +8440,19 @@
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
-      <c r="J6" s="118"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="119"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="121"/>
+      <c r="A7" s="126"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="101"/>
@@ -7973,7 +8464,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="44"/>
-      <c r="J8" s="122"/>
+      <c r="J8" s="129"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="101"/>
@@ -7985,7 +8476,7 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="44"/>
-      <c r="J9" s="122"/>
+      <c r="J9" s="129"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="101"/>
@@ -7997,7 +8488,7 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="122"/>
+      <c r="J10" s="129"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="101"/>
@@ -8009,7 +8500,7 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
-      <c r="J11" s="122"/>
+      <c r="J11" s="129"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="101"/>
@@ -8021,7 +8512,7 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
-      <c r="J12" s="122"/>
+      <c r="J12" s="129"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="101"/>
@@ -8033,7 +8524,7 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
-      <c r="J13" s="122"/>
+      <c r="J13" s="129"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="115" t="s">
@@ -8047,7 +8538,7 @@
       <c r="G14" s="41"/>
       <c r="H14" s="41"/>
       <c r="I14" s="41"/>
-      <c r="J14" s="118"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="115" t="s">
@@ -8055,7 +8546,7 @@
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="123" t="s">
+      <c r="D15" s="113" t="s">
         <v>73</v>
       </c>
       <c r="E15" s="41"/>
@@ -8087,14 +8578,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="124" t="s">
+      <c r="H16" s="116" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="41"/>
-      <c r="J16" s="118"/>
+      <c r="J16" s="114"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="114">
+      <c r="A17" s="112">
         <v>1</v>
       </c>
       <c r="B17" s="41"/>
@@ -8109,12 +8600,12 @@
         <v>82</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="123"/>
+      <c r="H17" s="113"/>
       <c r="I17" s="41"/>
-      <c r="J17" s="118"/>
+      <c r="J17" s="114"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="114">
+      <c r="A18" s="112">
         <v>2</v>
       </c>
       <c r="B18" s="41"/>
@@ -8131,12 +8622,12 @@
       <c r="G18" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="123"/>
+      <c r="H18" s="113"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="118"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="114">
+      <c r="A19" s="112">
         <v>3</v>
       </c>
       <c r="B19" s="41"/>
@@ -8151,12 +8642,12 @@
       <c r="G19" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="123"/>
+      <c r="H19" s="113"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="118"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="114">
+      <c r="A20" s="112">
         <v>4</v>
       </c>
       <c r="B20" s="41"/>
@@ -8173,12 +8664,12 @@
       <c r="G20" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="123"/>
+      <c r="H20" s="113"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="118"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="114">
+      <c r="A21" s="112">
         <v>5</v>
       </c>
       <c r="B21" s="41"/>
@@ -8195,12 +8686,12 @@
       <c r="G21" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="123"/>
+      <c r="H21" s="113"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="118"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="114">
+      <c r="A22" s="112">
         <v>6</v>
       </c>
       <c r="B22" s="41"/>
@@ -8215,12 +8706,12 @@
         <v>61</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="123"/>
+      <c r="H22" s="113"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="118"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="114">
+      <c r="A23" s="112">
         <v>7</v>
       </c>
       <c r="B23" s="41"/>
@@ -8235,9 +8726,9 @@
         <v>61</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="127"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="121"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
       <c r="A24" s="115"/>
@@ -8249,13 +8740,13 @@
       <c r="G24" s="41"/>
       <c r="H24" s="41"/>
       <c r="I24" s="41"/>
-      <c r="J24" s="118"/>
+      <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
       <c r="A25" s="115"/>
       <c r="B25" s="41"/>
       <c r="C25" s="42"/>
-      <c r="D25" s="123"/>
+      <c r="D25" s="113"/>
       <c r="E25" s="41"/>
       <c r="F25" s="41"/>
       <c r="G25" s="41"/>
@@ -8271,93 +8762,93 @@
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="124"/>
+      <c r="H26" s="116"/>
       <c r="I26" s="41"/>
-      <c r="J26" s="118"/>
+      <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="114"/>
+      <c r="A27" s="112"/>
       <c r="B27" s="41"/>
       <c r="C27" s="42"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="123"/>
+      <c r="H27" s="113"/>
       <c r="I27" s="41"/>
-      <c r="J27" s="118"/>
+      <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="114"/>
+      <c r="A28" s="112"/>
       <c r="B28" s="41"/>
       <c r="C28" s="42"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="123"/>
+      <c r="H28" s="113"/>
       <c r="I28" s="41"/>
-      <c r="J28" s="118"/>
+      <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="114"/>
+      <c r="A29" s="112"/>
       <c r="B29" s="41"/>
       <c r="C29" s="42"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
-      <c r="H29" s="123"/>
+      <c r="H29" s="113"/>
       <c r="I29" s="41"/>
-      <c r="J29" s="118"/>
+      <c r="J29" s="114"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="114"/>
+      <c r="A30" s="112"/>
       <c r="B30" s="41"/>
       <c r="C30" s="42"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="123"/>
+      <c r="H30" s="113"/>
       <c r="I30" s="41"/>
-      <c r="J30" s="118"/>
+      <c r="J30" s="114"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="114"/>
+      <c r="A31" s="112"/>
       <c r="B31" s="41"/>
       <c r="C31" s="42"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="123"/>
+      <c r="H31" s="113"/>
       <c r="I31" s="41"/>
-      <c r="J31" s="118"/>
+      <c r="J31" s="114"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="114"/>
+      <c r="A32" s="112"/>
       <c r="B32" s="41"/>
       <c r="C32" s="42"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="123"/>
+      <c r="H32" s="113"/>
       <c r="I32" s="41"/>
-      <c r="J32" s="118"/>
+      <c r="J32" s="114"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="128"/>
-      <c r="B33" s="126"/>
-      <c r="C33" s="129"/>
+      <c r="A33" s="117"/>
+      <c r="B33" s="118"/>
+      <c r="C33" s="119"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
-      <c r="H33" s="125"/>
-      <c r="I33" s="126"/>
-      <c r="J33" s="127"/>
+      <c r="H33" s="120"/>
+      <c r="I33" s="118"/>
+      <c r="J33" s="121"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
       <c r="A34" s="115"/>
@@ -8369,13 +8860,13 @@
       <c r="G34" s="41"/>
       <c r="H34" s="41"/>
       <c r="I34" s="41"/>
-      <c r="J34" s="118"/>
+      <c r="J34" s="114"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
       <c r="A35" s="115"/>
       <c r="B35" s="41"/>
       <c r="C35" s="42"/>
-      <c r="D35" s="123"/>
+      <c r="D35" s="113"/>
       <c r="E35" s="41"/>
       <c r="F35" s="41"/>
       <c r="G35" s="41"/>
@@ -8391,69 +8882,69 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
-      <c r="H36" s="124"/>
+      <c r="H36" s="116"/>
       <c r="I36" s="41"/>
-      <c r="J36" s="118"/>
+      <c r="J36" s="114"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="114"/>
+      <c r="A37" s="112"/>
       <c r="B37" s="41"/>
       <c r="C37" s="42"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="123"/>
+      <c r="H37" s="113"/>
       <c r="I37" s="41"/>
-      <c r="J37" s="118"/>
+      <c r="J37" s="114"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="114"/>
+      <c r="A38" s="112"/>
       <c r="B38" s="41"/>
       <c r="C38" s="42"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="123"/>
+      <c r="H38" s="113"/>
       <c r="I38" s="41"/>
-      <c r="J38" s="118"/>
+      <c r="J38" s="114"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="114"/>
+      <c r="A39" s="112"/>
       <c r="B39" s="41"/>
       <c r="C39" s="42"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="123"/>
+      <c r="H39" s="113"/>
       <c r="I39" s="41"/>
-      <c r="J39" s="118"/>
+      <c r="J39" s="114"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="114"/>
+      <c r="A40" s="112"/>
       <c r="B40" s="41"/>
       <c r="C40" s="42"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="123"/>
+      <c r="H40" s="113"/>
       <c r="I40" s="41"/>
-      <c r="J40" s="118"/>
+      <c r="J40" s="114"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="114"/>
+      <c r="A41" s="112"/>
       <c r="B41" s="41"/>
       <c r="C41" s="42"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="123"/>
+      <c r="H41" s="113"/>
       <c r="I41" s="41"/>
-      <c r="J41" s="118"/>
+      <c r="J41" s="114"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9416,50 +9907,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9476,11 +9928,50 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9571,20 +10062,20 @@
       <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="113"/>
+      <c r="B5" s="123"/>
       <c r="C5" s="107"/>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="124" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="125"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -9598,19 +10089,19 @@
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
-      <c r="J6" s="118"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="119"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="121"/>
+      <c r="A7" s="126"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="101"/>
@@ -9622,7 +10113,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="44"/>
-      <c r="J8" s="122"/>
+      <c r="J8" s="129"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="101"/>
@@ -9634,7 +10125,7 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="44"/>
-      <c r="J9" s="122"/>
+      <c r="J9" s="129"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="101"/>
@@ -9646,7 +10137,7 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="122"/>
+      <c r="J10" s="129"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="101"/>
@@ -9658,7 +10149,7 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
-      <c r="J11" s="122"/>
+      <c r="J11" s="129"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="101"/>
@@ -9670,7 +10161,7 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
-      <c r="J12" s="122"/>
+      <c r="J12" s="129"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="101"/>
@@ -9682,7 +10173,7 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
-      <c r="J13" s="122"/>
+      <c r="J13" s="129"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="115" t="s">
@@ -9696,7 +10187,7 @@
       <c r="G14" s="41"/>
       <c r="H14" s="41"/>
       <c r="I14" s="41"/>
-      <c r="J14" s="118"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="115" t="s">
@@ -9704,7 +10195,7 @@
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="123" t="s">
+      <c r="D15" s="113" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="41"/>
@@ -9736,14 +10227,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="124" t="s">
+      <c r="H16" s="116" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="41"/>
-      <c r="J16" s="118"/>
+      <c r="J16" s="114"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="114">
+      <c r="A17" s="112">
         <v>1</v>
       </c>
       <c r="B17" s="41"/>
@@ -9760,83 +10251,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="123" t="s">
+      <c r="H17" s="113" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="41"/>
-      <c r="J17" s="118"/>
+      <c r="J17" s="114"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="114"/>
+      <c r="A18" s="112"/>
       <c r="B18" s="41"/>
       <c r="C18" s="42"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="123"/>
+      <c r="H18" s="113"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="118"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="114"/>
+      <c r="A19" s="112"/>
       <c r="B19" s="41"/>
       <c r="C19" s="42"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="123"/>
+      <c r="H19" s="113"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="118"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="114"/>
+      <c r="A20" s="112"/>
       <c r="B20" s="41"/>
       <c r="C20" s="42"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="123"/>
+      <c r="H20" s="113"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="118"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="114"/>
+      <c r="A21" s="112"/>
       <c r="B21" s="41"/>
       <c r="C21" s="42"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="123"/>
+      <c r="H21" s="113"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="118"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="114"/>
+      <c r="A22" s="112"/>
       <c r="B22" s="41"/>
       <c r="C22" s="42"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="123"/>
+      <c r="H22" s="113"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="118"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="128"/>
-      <c r="B23" s="126"/>
-      <c r="C23" s="129"/>
+      <c r="A23" s="117"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="127"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="121"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10817,22 +11308,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -10848,6 +11323,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10938,20 +11429,20 @@
       <c r="J4" s="96"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="113"/>
+      <c r="B5" s="123"/>
       <c r="C5" s="107"/>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="125"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -10965,19 +11456,19 @@
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
-      <c r="J6" s="118"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="119"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="121"/>
+      <c r="A7" s="126"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="101"/>
@@ -10989,7 +11480,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="44"/>
-      <c r="J8" s="122"/>
+      <c r="J8" s="129"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="101"/>
@@ -11001,7 +11492,7 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="44"/>
-      <c r="J9" s="122"/>
+      <c r="J9" s="129"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="101"/>
@@ -11013,7 +11504,7 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="122"/>
+      <c r="J10" s="129"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="101"/>
@@ -11025,7 +11516,7 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
-      <c r="J11" s="122"/>
+      <c r="J11" s="129"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="101"/>
@@ -11037,7 +11528,7 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
-      <c r="J12" s="122"/>
+      <c r="J12" s="129"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="101"/>
@@ -11049,7 +11540,7 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
-      <c r="J13" s="122"/>
+      <c r="J13" s="129"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="115" t="s">
@@ -11063,7 +11554,7 @@
       <c r="G14" s="41"/>
       <c r="H14" s="41"/>
       <c r="I14" s="41"/>
-      <c r="J14" s="118"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="115" t="s">
@@ -11071,7 +11562,7 @@
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="123" t="s">
+      <c r="D15" s="113" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="41"/>
@@ -11103,14 +11594,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="124" t="s">
+      <c r="H16" s="116" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="41"/>
-      <c r="J16" s="118"/>
+      <c r="J16" s="114"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="114">
+      <c r="A17" s="112">
         <v>1</v>
       </c>
       <c r="B17" s="41"/>
@@ -11127,83 +11618,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="123" t="s">
+      <c r="H17" s="113" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="41"/>
-      <c r="J17" s="118"/>
+      <c r="J17" s="114"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="114"/>
+      <c r="A18" s="112"/>
       <c r="B18" s="41"/>
       <c r="C18" s="42"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="123"/>
+      <c r="H18" s="113"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="118"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="114"/>
+      <c r="A19" s="112"/>
       <c r="B19" s="41"/>
       <c r="C19" s="42"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="123"/>
+      <c r="H19" s="113"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="118"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="114"/>
+      <c r="A20" s="112"/>
       <c r="B20" s="41"/>
       <c r="C20" s="42"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="123"/>
+      <c r="H20" s="113"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="118"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="114"/>
+      <c r="A21" s="112"/>
       <c r="B21" s="41"/>
       <c r="C21" s="42"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="123"/>
+      <c r="H21" s="113"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="118"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="114"/>
+      <c r="A22" s="112"/>
       <c r="B22" s="41"/>
       <c r="C22" s="42"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="123"/>
+      <c r="H22" s="113"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="118"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="128"/>
-      <c r="B23" s="126"/>
-      <c r="C23" s="129"/>
+      <c r="A23" s="117"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="127"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="121"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12184,22 +12675,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -12215,6 +12690,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12234,7 +12725,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="141" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="99"/>
@@ -12245,14 +12736,14 @@
       <c r="G1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
       <c r="J1" s="107"/>
       <c r="K1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
       <c r="N1" s="107"/>
       <c r="O1" s="106" t="s">
         <v>8</v>
@@ -12265,7 +12756,7 @@
       <c r="S1" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="117"/>
+      <c r="T1" s="125"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="101"/>
@@ -12277,16 +12768,16 @@
       <c r="G2" s="108" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
       <c r="J2" s="109"/>
       <c r="K2" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
       <c r="N2" s="109"/>
-      <c r="O2" s="142">
+      <c r="O2" s="139">
         <v>45821</v>
       </c>
       <c r="P2" s="109"/>
@@ -12295,7 +12786,7 @@
       </c>
       <c r="R2" s="109"/>
       <c r="S2" s="108"/>
-      <c r="T2" s="121"/>
+      <c r="T2" s="128"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="101"/>
@@ -12317,7 +12808,7 @@
       <c r="Q3" s="110"/>
       <c r="R3" s="102"/>
       <c r="S3" s="110"/>
-      <c r="T3" s="122"/>
+      <c r="T3" s="129"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="103"/>
@@ -12339,33 +12830,33 @@
       <c r="Q4" s="111"/>
       <c r="R4" s="105"/>
       <c r="S4" s="111"/>
-      <c r="T4" s="134"/>
+      <c r="T4" s="140"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
       <c r="F5" s="107"/>
       <c r="G5" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="113"/>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="113"/>
-      <c r="R5" s="113"/>
-      <c r="S5" s="113"/>
-      <c r="T5" s="117"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="123"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="125"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="115" t="s">
@@ -12376,7 +12867,7 @@
       <c r="D6" s="41"/>
       <c r="E6" s="41"/>
       <c r="F6" s="42"/>
-      <c r="G6" s="123" t="s">
+      <c r="G6" s="113" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="41"/>
@@ -12391,7 +12882,7 @@
       <c r="Q6" s="41"/>
       <c r="R6" s="41"/>
       <c r="S6" s="41"/>
-      <c r="T6" s="118"/>
+      <c r="T6" s="114"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="115" t="s">
@@ -12402,7 +12893,7 @@
       <c r="D7" s="41"/>
       <c r="E7" s="41"/>
       <c r="F7" s="42"/>
-      <c r="G7" s="123" t="s">
+      <c r="G7" s="113" t="s">
         <v>95</v>
       </c>
       <c r="H7" s="41"/>
@@ -12417,7 +12908,7 @@
       <c r="Q7" s="41"/>
       <c r="R7" s="41"/>
       <c r="S7" s="41"/>
-      <c r="T7" s="118"/>
+      <c r="T7" s="114"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -12620,29 +13111,29 @@
         <v>45</v>
       </c>
       <c r="B15" s="42"/>
-      <c r="C15" s="139" t="s">
+      <c r="C15" s="138" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="42"/>
-      <c r="E15" s="124" t="s">
+      <c r="E15" s="116" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="42"/>
-      <c r="G15" s="124" t="s">
+      <c r="G15" s="116" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="41"/>
       <c r="I15" s="42"/>
-      <c r="J15" s="124" t="s">
+      <c r="J15" s="116" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="42"/>
-      <c r="L15" s="124" t="s">
+      <c r="L15" s="116" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="41"/>
       <c r="N15" s="42"/>
-      <c r="O15" s="124" t="s">
+      <c r="O15" s="116" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="41"/>
@@ -12658,33 +13149,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A16" s="137">
+      <c r="A16" s="130">
         <v>1</v>
       </c>
       <c r="B16" s="42"/>
-      <c r="C16" s="138" t="s">
+      <c r="C16" s="131" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="42"/>
-      <c r="E16" s="138" t="s">
+      <c r="E16" s="131" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="42"/>
-      <c r="G16" s="130" t="s">
+      <c r="G16" s="137" t="s">
         <v>96</v>
       </c>
       <c r="H16" s="41"/>
       <c r="I16" s="42"/>
-      <c r="J16" s="143" t="s">
+      <c r="J16" s="144" t="s">
         <v>97</v>
       </c>
-      <c r="K16" s="144"/>
-      <c r="L16" s="132" t="s">
+      <c r="K16" s="145"/>
+      <c r="L16" s="134" t="s">
         <v>98</v>
       </c>
       <c r="M16" s="41"/>
       <c r="N16" s="42"/>
-      <c r="O16" s="132" t="s">
+      <c r="O16" s="134" t="s">
         <v>99</v>
       </c>
       <c r="P16" s="41"/>
@@ -12700,33 +13191,33 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A17" s="137">
+      <c r="A17" s="130">
         <v>2</v>
       </c>
       <c r="B17" s="42"/>
-      <c r="C17" s="138" t="s">
+      <c r="C17" s="131" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="42"/>
-      <c r="E17" s="138" t="s">
+      <c r="E17" s="131" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="130" t="s">
+      <c r="G17" s="137" t="s">
         <v>105</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="42"/>
-      <c r="J17" s="130" t="s">
+      <c r="J17" s="137" t="s">
         <v>106</v>
       </c>
       <c r="K17" s="42"/>
-      <c r="L17" s="132" t="s">
+      <c r="L17" s="134" t="s">
         <v>98</v>
       </c>
       <c r="M17" s="41"/>
       <c r="N17" s="42"/>
-      <c r="O17" s="132" t="s">
+      <c r="O17" s="134" t="s">
         <v>107</v>
       </c>
       <c r="P17" s="41"/>
@@ -12742,33 +13233,33 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="64.5" customHeight="1">
-      <c r="A18" s="137">
+      <c r="A18" s="130">
         <v>3</v>
       </c>
       <c r="B18" s="42"/>
-      <c r="C18" s="138" t="s">
+      <c r="C18" s="131" t="s">
         <v>54</v>
       </c>
       <c r="D18" s="42"/>
-      <c r="E18" s="138" t="s">
+      <c r="E18" s="131" t="s">
         <v>100</v>
       </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="130" t="s">
+      <c r="G18" s="137" t="s">
         <v>101</v>
       </c>
       <c r="H18" s="41"/>
       <c r="I18" s="42"/>
-      <c r="J18" s="130" t="s">
+      <c r="J18" s="137" t="s">
         <v>103</v>
       </c>
       <c r="K18" s="42"/>
-      <c r="L18" s="145" t="s">
+      <c r="L18" s="142" t="s">
         <v>104</v>
       </c>
       <c r="M18" s="41"/>
       <c r="N18" s="42"/>
-      <c r="O18" s="132" t="s">
+      <c r="O18" s="134" t="s">
         <v>102</v>
       </c>
       <c r="P18" s="41"/>
@@ -12784,21 +13275,21 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="137"/>
+      <c r="A19" s="130"/>
       <c r="B19" s="42"/>
-      <c r="C19" s="138"/>
+      <c r="C19" s="131"/>
       <c r="D19" s="42"/>
-      <c r="E19" s="138"/>
+      <c r="E19" s="131"/>
       <c r="F19" s="42"/>
-      <c r="G19" s="130"/>
+      <c r="G19" s="137"/>
       <c r="H19" s="41"/>
       <c r="I19" s="42"/>
-      <c r="J19" s="130"/>
+      <c r="J19" s="137"/>
       <c r="K19" s="42"/>
-      <c r="L19" s="132"/>
+      <c r="L19" s="134"/>
       <c r="M19" s="41"/>
       <c r="N19" s="42"/>
-      <c r="O19" s="132"/>
+      <c r="O19" s="134"/>
       <c r="P19" s="41"/>
       <c r="Q19" s="42"/>
       <c r="R19" s="32"/>
@@ -12812,21 +13303,21 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="137"/>
+      <c r="A20" s="130"/>
       <c r="B20" s="42"/>
-      <c r="C20" s="138"/>
+      <c r="C20" s="131"/>
       <c r="D20" s="42"/>
-      <c r="E20" s="138"/>
+      <c r="E20" s="131"/>
       <c r="F20" s="42"/>
-      <c r="G20" s="130"/>
+      <c r="G20" s="137"/>
       <c r="H20" s="41"/>
       <c r="I20" s="42"/>
-      <c r="J20" s="130"/>
+      <c r="J20" s="137"/>
       <c r="K20" s="42"/>
-      <c r="L20" s="132"/>
+      <c r="L20" s="134"/>
       <c r="M20" s="41"/>
       <c r="N20" s="42"/>
-      <c r="O20" s="132"/>
+      <c r="O20" s="134"/>
       <c r="P20" s="41"/>
       <c r="Q20" s="42"/>
       <c r="R20" s="32"/>
@@ -12840,21 +13331,21 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="137"/>
+      <c r="A21" s="130"/>
       <c r="B21" s="42"/>
-      <c r="C21" s="138"/>
+      <c r="C21" s="131"/>
       <c r="D21" s="42"/>
-      <c r="E21" s="138"/>
+      <c r="E21" s="131"/>
       <c r="F21" s="42"/>
-      <c r="G21" s="130"/>
+      <c r="G21" s="137"/>
       <c r="H21" s="41"/>
       <c r="I21" s="42"/>
-      <c r="J21" s="130"/>
+      <c r="J21" s="137"/>
       <c r="K21" s="42"/>
-      <c r="L21" s="132"/>
+      <c r="L21" s="134"/>
       <c r="M21" s="41"/>
       <c r="N21" s="42"/>
-      <c r="O21" s="132"/>
+      <c r="O21" s="134"/>
       <c r="P21" s="41"/>
       <c r="Q21" s="42"/>
       <c r="R21" s="32"/>
@@ -12868,21 +13359,21 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="137"/>
+      <c r="A22" s="130"/>
       <c r="B22" s="42"/>
-      <c r="C22" s="138"/>
+      <c r="C22" s="131"/>
       <c r="D22" s="42"/>
-      <c r="E22" s="138"/>
+      <c r="E22" s="131"/>
       <c r="F22" s="42"/>
-      <c r="G22" s="130"/>
+      <c r="G22" s="137"/>
       <c r="H22" s="41"/>
       <c r="I22" s="42"/>
-      <c r="J22" s="130"/>
+      <c r="J22" s="137"/>
       <c r="K22" s="42"/>
-      <c r="L22" s="132"/>
+      <c r="L22" s="134"/>
       <c r="M22" s="41"/>
       <c r="N22" s="42"/>
-      <c r="O22" s="132"/>
+      <c r="O22" s="134"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="42"/>
       <c r="R22" s="32"/>
@@ -12896,21 +13387,21 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="137"/>
+      <c r="A23" s="130"/>
       <c r="B23" s="42"/>
-      <c r="C23" s="138"/>
+      <c r="C23" s="131"/>
       <c r="D23" s="42"/>
-      <c r="E23" s="138"/>
+      <c r="E23" s="131"/>
       <c r="F23" s="42"/>
-      <c r="G23" s="130"/>
+      <c r="G23" s="137"/>
       <c r="H23" s="41"/>
       <c r="I23" s="42"/>
-      <c r="J23" s="130"/>
+      <c r="J23" s="137"/>
       <c r="K23" s="42"/>
-      <c r="L23" s="132"/>
+      <c r="L23" s="134"/>
       <c r="M23" s="41"/>
       <c r="N23" s="42"/>
-      <c r="O23" s="132"/>
+      <c r="O23" s="134"/>
       <c r="P23" s="41"/>
       <c r="Q23" s="42"/>
       <c r="R23" s="32"/>
@@ -12924,21 +13415,21 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="137"/>
+      <c r="A24" s="130"/>
       <c r="B24" s="42"/>
-      <c r="C24" s="138"/>
+      <c r="C24" s="131"/>
       <c r="D24" s="42"/>
-      <c r="E24" s="138"/>
+      <c r="E24" s="131"/>
       <c r="F24" s="42"/>
-      <c r="G24" s="130"/>
+      <c r="G24" s="137"/>
       <c r="H24" s="41"/>
       <c r="I24" s="42"/>
-      <c r="J24" s="130"/>
+      <c r="J24" s="137"/>
       <c r="K24" s="42"/>
-      <c r="L24" s="132"/>
+      <c r="L24" s="134"/>
       <c r="M24" s="41"/>
       <c r="N24" s="42"/>
-      <c r="O24" s="132"/>
+      <c r="O24" s="134"/>
       <c r="P24" s="41"/>
       <c r="Q24" s="42"/>
       <c r="R24" s="32"/>
@@ -12952,21 +13443,21 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="137"/>
+      <c r="A25" s="130"/>
       <c r="B25" s="42"/>
-      <c r="C25" s="138"/>
+      <c r="C25" s="131"/>
       <c r="D25" s="42"/>
-      <c r="E25" s="138"/>
+      <c r="E25" s="131"/>
       <c r="F25" s="42"/>
-      <c r="G25" s="130"/>
+      <c r="G25" s="137"/>
       <c r="H25" s="41"/>
       <c r="I25" s="42"/>
-      <c r="J25" s="130"/>
+      <c r="J25" s="137"/>
       <c r="K25" s="42"/>
-      <c r="L25" s="132"/>
+      <c r="L25" s="134"/>
       <c r="M25" s="41"/>
       <c r="N25" s="42"/>
-      <c r="O25" s="132"/>
+      <c r="O25" s="134"/>
       <c r="P25" s="41"/>
       <c r="Q25" s="42"/>
       <c r="R25" s="32"/>
@@ -12980,21 +13471,21 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="137"/>
+      <c r="A26" s="130"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="138"/>
+      <c r="C26" s="131"/>
       <c r="D26" s="42"/>
-      <c r="E26" s="138"/>
+      <c r="E26" s="131"/>
       <c r="F26" s="42"/>
-      <c r="G26" s="130"/>
+      <c r="G26" s="137"/>
       <c r="H26" s="41"/>
       <c r="I26" s="42"/>
-      <c r="J26" s="130"/>
+      <c r="J26" s="137"/>
       <c r="K26" s="42"/>
-      <c r="L26" s="132"/>
+      <c r="L26" s="134"/>
       <c r="M26" s="41"/>
       <c r="N26" s="42"/>
-      <c r="O26" s="132"/>
+      <c r="O26" s="134"/>
       <c r="P26" s="41"/>
       <c r="Q26" s="42"/>
       <c r="R26" s="32"/>
@@ -13008,21 +13499,21 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="137"/>
+      <c r="A27" s="130"/>
       <c r="B27" s="42"/>
-      <c r="C27" s="138"/>
+      <c r="C27" s="131"/>
       <c r="D27" s="42"/>
-      <c r="E27" s="138"/>
+      <c r="E27" s="131"/>
       <c r="F27" s="42"/>
-      <c r="G27" s="130"/>
+      <c r="G27" s="137"/>
       <c r="H27" s="41"/>
       <c r="I27" s="42"/>
-      <c r="J27" s="130"/>
+      <c r="J27" s="137"/>
       <c r="K27" s="42"/>
-      <c r="L27" s="132"/>
+      <c r="L27" s="134"/>
       <c r="M27" s="41"/>
       <c r="N27" s="42"/>
-      <c r="O27" s="132"/>
+      <c r="O27" s="134"/>
       <c r="P27" s="41"/>
       <c r="Q27" s="42"/>
       <c r="R27" s="32"/>
@@ -13036,21 +13527,21 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="137"/>
+      <c r="A28" s="130"/>
       <c r="B28" s="42"/>
-      <c r="C28" s="138"/>
+      <c r="C28" s="131"/>
       <c r="D28" s="42"/>
-      <c r="E28" s="138"/>
+      <c r="E28" s="131"/>
       <c r="F28" s="42"/>
-      <c r="G28" s="130"/>
+      <c r="G28" s="137"/>
       <c r="H28" s="41"/>
       <c r="I28" s="42"/>
-      <c r="J28" s="130"/>
+      <c r="J28" s="137"/>
       <c r="K28" s="42"/>
-      <c r="L28" s="132"/>
+      <c r="L28" s="134"/>
       <c r="M28" s="41"/>
       <c r="N28" s="42"/>
-      <c r="O28" s="132"/>
+      <c r="O28" s="134"/>
       <c r="P28" s="41"/>
       <c r="Q28" s="42"/>
       <c r="R28" s="32"/>
@@ -13064,21 +13555,21 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="137"/>
+      <c r="A29" s="130"/>
       <c r="B29" s="42"/>
-      <c r="C29" s="138"/>
+      <c r="C29" s="131"/>
       <c r="D29" s="42"/>
-      <c r="E29" s="138"/>
+      <c r="E29" s="131"/>
       <c r="F29" s="42"/>
-      <c r="G29" s="130"/>
+      <c r="G29" s="137"/>
       <c r="H29" s="41"/>
       <c r="I29" s="42"/>
-      <c r="J29" s="130"/>
+      <c r="J29" s="137"/>
       <c r="K29" s="42"/>
-      <c r="L29" s="132"/>
+      <c r="L29" s="134"/>
       <c r="M29" s="41"/>
       <c r="N29" s="42"/>
-      <c r="O29" s="132"/>
+      <c r="O29" s="134"/>
       <c r="P29" s="41"/>
       <c r="Q29" s="42"/>
       <c r="R29" s="32"/>
@@ -13092,21 +13583,21 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="137"/>
+      <c r="A30" s="130"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="138"/>
+      <c r="C30" s="131"/>
       <c r="D30" s="42"/>
-      <c r="E30" s="138"/>
+      <c r="E30" s="131"/>
       <c r="F30" s="42"/>
-      <c r="G30" s="130"/>
+      <c r="G30" s="137"/>
       <c r="H30" s="41"/>
       <c r="I30" s="42"/>
-      <c r="J30" s="130"/>
+      <c r="J30" s="137"/>
       <c r="K30" s="42"/>
-      <c r="L30" s="132"/>
+      <c r="L30" s="134"/>
       <c r="M30" s="41"/>
       <c r="N30" s="42"/>
-      <c r="O30" s="132"/>
+      <c r="O30" s="134"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="42"/>
       <c r="R30" s="32"/>
@@ -13120,23 +13611,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="140"/>
-      <c r="B31" s="129"/>
-      <c r="C31" s="141"/>
-      <c r="D31" s="129"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="129"/>
-      <c r="G31" s="131"/>
-      <c r="H31" s="126"/>
-      <c r="I31" s="129"/>
-      <c r="J31" s="131"/>
-      <c r="K31" s="129"/>
-      <c r="L31" s="133"/>
-      <c r="M31" s="126"/>
-      <c r="N31" s="129"/>
-      <c r="O31" s="133"/>
-      <c r="P31" s="126"/>
-      <c r="Q31" s="129"/>
+      <c r="A31" s="132"/>
+      <c r="B31" s="119"/>
+      <c r="C31" s="133"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="133"/>
+      <c r="F31" s="119"/>
+      <c r="G31" s="143"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="119"/>
+      <c r="J31" s="143"/>
+      <c r="K31" s="119"/>
+      <c r="L31" s="135"/>
+      <c r="M31" s="118"/>
+      <c r="N31" s="119"/>
+      <c r="O31" s="135"/>
+      <c r="P31" s="118"/>
+      <c r="Q31" s="119"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -14134,6 +14625,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14158,118 +14761,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
@@ -14278,4 +14769,1357 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165D2D18-FBF9-4541-9590-4A3E1B2AA516}">
+  <dimension ref="A1:S52"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" style="154" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="188" customWidth="1"/>
+    <col min="3" max="6" width="8.140625" style="154" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="188" customWidth="1"/>
+    <col min="8" max="13" width="8.140625" style="154" customWidth="1"/>
+    <col min="14" max="19" width="12.140625" style="154" customWidth="1"/>
+    <col min="20" max="16384" width="8" style="154"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A1" s="146" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="146"/>
+      <c r="C1" s="147" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="148"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="153" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" s="150"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="153" t="s">
+        <v>111</v>
+      </c>
+      <c r="R1" s="150" t="s">
+        <v>112</v>
+      </c>
+      <c r="S1" s="152"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A2" s="146"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="147" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="148"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="151"/>
+      <c r="K2" s="151"/>
+      <c r="L2" s="151"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="153" t="s">
+        <v>114</v>
+      </c>
+      <c r="O2" s="155"/>
+      <c r="P2" s="156"/>
+      <c r="Q2" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="R2" s="158">
+        <v>44771</v>
+      </c>
+      <c r="S2" s="159"/>
+    </row>
+    <row r="3" spans="1:19" ht="11.25" customHeight="1">
+      <c r="A3" s="160"/>
+      <c r="B3" s="161"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+      <c r="L3" s="160"/>
+      <c r="M3" s="160"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="160"/>
+      <c r="Q3" s="160"/>
+      <c r="R3" s="160"/>
+      <c r="S3" s="160"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="162" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="163" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="164" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="165"/>
+      <c r="E4" s="165"/>
+      <c r="F4" s="165"/>
+      <c r="G4" s="166"/>
+      <c r="H4" s="164" t="s">
+        <v>119</v>
+      </c>
+      <c r="I4" s="165"/>
+      <c r="J4" s="165"/>
+      <c r="K4" s="165"/>
+      <c r="L4" s="165"/>
+      <c r="M4" s="166"/>
+      <c r="N4" s="164" t="s">
+        <v>120</v>
+      </c>
+      <c r="O4" s="165"/>
+      <c r="P4" s="166"/>
+      <c r="Q4" s="162" t="s">
+        <v>121</v>
+      </c>
+      <c r="R4" s="164" t="s">
+        <v>122</v>
+      </c>
+      <c r="S4" s="166"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" customHeight="1">
+      <c r="A5" s="167"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
+      <c r="H5" s="169"/>
+      <c r="I5" s="169"/>
+      <c r="J5" s="169"/>
+      <c r="K5" s="169"/>
+      <c r="L5" s="169"/>
+      <c r="M5" s="169"/>
+      <c r="N5" s="170"/>
+      <c r="O5" s="171"/>
+      <c r="P5" s="172"/>
+      <c r="Q5" s="167"/>
+      <c r="R5" s="173"/>
+      <c r="S5" s="174"/>
+    </row>
+    <row r="6" spans="1:19" ht="30" customHeight="1">
+      <c r="A6" s="175"/>
+      <c r="B6" s="175"/>
+      <c r="C6" s="176"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="176"/>
+      <c r="H6" s="176"/>
+      <c r="I6" s="176"/>
+      <c r="J6" s="176"/>
+      <c r="K6" s="176"/>
+      <c r="L6" s="176"/>
+      <c r="M6" s="176"/>
+      <c r="N6" s="177"/>
+      <c r="O6" s="178"/>
+      <c r="P6" s="179"/>
+      <c r="Q6" s="180"/>
+      <c r="R6" s="181"/>
+      <c r="S6" s="181"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" customHeight="1">
+      <c r="A7" s="175"/>
+      <c r="B7" s="175"/>
+      <c r="C7" s="176"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="176"/>
+      <c r="F7" s="176"/>
+      <c r="G7" s="176"/>
+      <c r="H7" s="176"/>
+      <c r="I7" s="176"/>
+      <c r="J7" s="176"/>
+      <c r="K7" s="176"/>
+      <c r="L7" s="176"/>
+      <c r="M7" s="176"/>
+      <c r="N7" s="182"/>
+      <c r="O7" s="183"/>
+      <c r="P7" s="184"/>
+      <c r="Q7" s="180"/>
+      <c r="R7" s="181"/>
+      <c r="S7" s="181"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" customHeight="1">
+      <c r="A8" s="175"/>
+      <c r="B8" s="175"/>
+      <c r="C8" s="176"/>
+      <c r="D8" s="176"/>
+      <c r="E8" s="176"/>
+      <c r="F8" s="176"/>
+      <c r="G8" s="176"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="176"/>
+      <c r="K8" s="176"/>
+      <c r="L8" s="176"/>
+      <c r="M8" s="176"/>
+      <c r="N8" s="182"/>
+      <c r="O8" s="183"/>
+      <c r="P8" s="184"/>
+      <c r="Q8" s="180"/>
+      <c r="R8" s="181"/>
+      <c r="S8" s="181"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" customHeight="1">
+      <c r="A9" s="175"/>
+      <c r="B9" s="175"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="176"/>
+      <c r="F9" s="176"/>
+      <c r="G9" s="176"/>
+      <c r="H9" s="176"/>
+      <c r="I9" s="176"/>
+      <c r="J9" s="176"/>
+      <c r="K9" s="176"/>
+      <c r="L9" s="176"/>
+      <c r="M9" s="176"/>
+      <c r="N9" s="182"/>
+      <c r="O9" s="183"/>
+      <c r="P9" s="184"/>
+      <c r="Q9" s="175"/>
+      <c r="R9" s="181"/>
+      <c r="S9" s="181"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" customHeight="1">
+      <c r="A10" s="175"/>
+      <c r="B10" s="175"/>
+      <c r="C10" s="176"/>
+      <c r="D10" s="176"/>
+      <c r="E10" s="176"/>
+      <c r="F10" s="176"/>
+      <c r="G10" s="176"/>
+      <c r="H10" s="185"/>
+      <c r="I10" s="186"/>
+      <c r="J10" s="186"/>
+      <c r="K10" s="186"/>
+      <c r="L10" s="186"/>
+      <c r="M10" s="187"/>
+      <c r="N10" s="182"/>
+      <c r="O10" s="183"/>
+      <c r="P10" s="184"/>
+      <c r="Q10" s="180"/>
+      <c r="R10" s="181"/>
+      <c r="S10" s="181"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" customHeight="1">
+      <c r="A11" s="175"/>
+      <c r="B11" s="175"/>
+      <c r="C11" s="176"/>
+      <c r="D11" s="176"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="185"/>
+      <c r="I11" s="186"/>
+      <c r="J11" s="186"/>
+      <c r="K11" s="186"/>
+      <c r="L11" s="186"/>
+      <c r="M11" s="187"/>
+      <c r="N11" s="182"/>
+      <c r="O11" s="183"/>
+      <c r="P11" s="184"/>
+      <c r="Q11" s="175"/>
+      <c r="R11" s="181"/>
+      <c r="S11" s="181"/>
+    </row>
+    <row r="12" spans="1:19" ht="30" customHeight="1">
+      <c r="A12" s="175"/>
+      <c r="B12" s="175"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="176"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="186"/>
+      <c r="K12" s="186"/>
+      <c r="L12" s="186"/>
+      <c r="M12" s="187"/>
+      <c r="N12" s="182"/>
+      <c r="O12" s="183"/>
+      <c r="P12" s="184"/>
+      <c r="Q12" s="175"/>
+      <c r="R12" s="181"/>
+      <c r="S12" s="181"/>
+    </row>
+    <row r="13" spans="1:19" ht="30" customHeight="1">
+      <c r="A13" s="175"/>
+      <c r="B13" s="175"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="176"/>
+      <c r="H13" s="185"/>
+      <c r="I13" s="186"/>
+      <c r="J13" s="186"/>
+      <c r="K13" s="186"/>
+      <c r="L13" s="186"/>
+      <c r="M13" s="187"/>
+      <c r="N13" s="182"/>
+      <c r="O13" s="183"/>
+      <c r="P13" s="184"/>
+      <c r="Q13" s="175"/>
+      <c r="R13" s="181"/>
+      <c r="S13" s="181"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" customHeight="1">
+      <c r="A14" s="175"/>
+      <c r="B14" s="175"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="176"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="176"/>
+      <c r="G14" s="176"/>
+      <c r="H14" s="185"/>
+      <c r="I14" s="186"/>
+      <c r="J14" s="186"/>
+      <c r="K14" s="186"/>
+      <c r="L14" s="186"/>
+      <c r="M14" s="187"/>
+      <c r="N14" s="182"/>
+      <c r="O14" s="183"/>
+      <c r="P14" s="184"/>
+      <c r="Q14" s="175"/>
+      <c r="R14" s="181"/>
+      <c r="S14" s="181"/>
+    </row>
+    <row r="15" spans="1:19" ht="30" customHeight="1">
+      <c r="A15" s="175"/>
+      <c r="B15" s="175"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="176"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
+      <c r="G15" s="176"/>
+      <c r="H15" s="185"/>
+      <c r="I15" s="186"/>
+      <c r="J15" s="186"/>
+      <c r="K15" s="186"/>
+      <c r="L15" s="186"/>
+      <c r="M15" s="187"/>
+      <c r="N15" s="182"/>
+      <c r="O15" s="183"/>
+      <c r="P15" s="184"/>
+      <c r="Q15" s="175"/>
+      <c r="R15" s="181"/>
+      <c r="S15" s="181"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" customHeight="1">
+      <c r="A16" s="175"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="176"/>
+      <c r="E16" s="176"/>
+      <c r="F16" s="176"/>
+      <c r="G16" s="176"/>
+      <c r="H16" s="185"/>
+      <c r="I16" s="186"/>
+      <c r="J16" s="186"/>
+      <c r="K16" s="186"/>
+      <c r="L16" s="186"/>
+      <c r="M16" s="187"/>
+      <c r="N16" s="182"/>
+      <c r="O16" s="183"/>
+      <c r="P16" s="184"/>
+      <c r="Q16" s="175"/>
+      <c r="R16" s="181"/>
+      <c r="S16" s="181"/>
+    </row>
+    <row r="17" spans="1:19" ht="30" customHeight="1">
+      <c r="A17" s="175"/>
+      <c r="B17" s="175"/>
+      <c r="C17" s="176"/>
+      <c r="D17" s="176"/>
+      <c r="E17" s="176"/>
+      <c r="F17" s="176"/>
+      <c r="G17" s="176"/>
+      <c r="H17" s="185"/>
+      <c r="I17" s="186"/>
+      <c r="J17" s="186"/>
+      <c r="K17" s="186"/>
+      <c r="L17" s="186"/>
+      <c r="M17" s="187"/>
+      <c r="N17" s="182"/>
+      <c r="O17" s="183"/>
+      <c r="P17" s="184"/>
+      <c r="Q17" s="175"/>
+      <c r="R17" s="181"/>
+      <c r="S17" s="181"/>
+    </row>
+    <row r="18" spans="1:19" ht="30" customHeight="1">
+      <c r="A18" s="175"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="176"/>
+      <c r="D18" s="176"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="176"/>
+      <c r="G18" s="176"/>
+      <c r="H18" s="185"/>
+      <c r="I18" s="186"/>
+      <c r="J18" s="186"/>
+      <c r="K18" s="186"/>
+      <c r="L18" s="186"/>
+      <c r="M18" s="187"/>
+      <c r="N18" s="182"/>
+      <c r="O18" s="183"/>
+      <c r="P18" s="184"/>
+      <c r="Q18" s="175"/>
+      <c r="R18" s="181"/>
+      <c r="S18" s="181"/>
+    </row>
+    <row r="19" spans="1:19" ht="30" customHeight="1">
+      <c r="A19" s="175"/>
+      <c r="B19" s="175"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="176"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="176"/>
+      <c r="G19" s="176"/>
+      <c r="H19" s="185"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="186"/>
+      <c r="K19" s="186"/>
+      <c r="L19" s="186"/>
+      <c r="M19" s="187"/>
+      <c r="N19" s="182"/>
+      <c r="O19" s="183"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="175"/>
+      <c r="R19" s="181"/>
+      <c r="S19" s="181"/>
+    </row>
+    <row r="20" spans="1:19" ht="30" customHeight="1">
+      <c r="A20" s="175"/>
+      <c r="B20" s="175"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="176"/>
+      <c r="E20" s="176"/>
+      <c r="F20" s="176"/>
+      <c r="G20" s="176"/>
+      <c r="H20" s="185"/>
+      <c r="I20" s="186"/>
+      <c r="J20" s="186"/>
+      <c r="K20" s="186"/>
+      <c r="L20" s="186"/>
+      <c r="M20" s="187"/>
+      <c r="N20" s="182"/>
+      <c r="O20" s="183"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="175"/>
+      <c r="R20" s="181"/>
+      <c r="S20" s="181"/>
+    </row>
+    <row r="21" spans="1:19" ht="30" customHeight="1">
+      <c r="A21" s="175"/>
+      <c r="B21" s="175"/>
+      <c r="C21" s="176"/>
+      <c r="D21" s="176"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="176"/>
+      <c r="G21" s="176"/>
+      <c r="H21" s="185"/>
+      <c r="I21" s="186"/>
+      <c r="J21" s="186"/>
+      <c r="K21" s="186"/>
+      <c r="L21" s="186"/>
+      <c r="M21" s="187"/>
+      <c r="N21" s="182"/>
+      <c r="O21" s="183"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="175"/>
+      <c r="R21" s="181"/>
+      <c r="S21" s="181"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" customHeight="1">
+      <c r="A22" s="175"/>
+      <c r="B22" s="175"/>
+      <c r="C22" s="176"/>
+      <c r="D22" s="176"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="176"/>
+      <c r="G22" s="176"/>
+      <c r="H22" s="185"/>
+      <c r="I22" s="186"/>
+      <c r="J22" s="186"/>
+      <c r="K22" s="186"/>
+      <c r="L22" s="186"/>
+      <c r="M22" s="187"/>
+      <c r="N22" s="182"/>
+      <c r="O22" s="183"/>
+      <c r="P22" s="184"/>
+      <c r="Q22" s="175"/>
+      <c r="R22" s="181"/>
+      <c r="S22" s="181"/>
+    </row>
+    <row r="23" spans="1:19" ht="30" customHeight="1">
+      <c r="A23" s="175"/>
+      <c r="B23" s="175"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="176"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="176"/>
+      <c r="G23" s="176"/>
+      <c r="H23" s="185"/>
+      <c r="I23" s="186"/>
+      <c r="J23" s="186"/>
+      <c r="K23" s="186"/>
+      <c r="L23" s="186"/>
+      <c r="M23" s="187"/>
+      <c r="N23" s="182"/>
+      <c r="O23" s="183"/>
+      <c r="P23" s="184"/>
+      <c r="Q23" s="175"/>
+      <c r="R23" s="181"/>
+      <c r="S23" s="181"/>
+    </row>
+    <row r="24" spans="1:19" ht="30" customHeight="1">
+      <c r="A24" s="175"/>
+      <c r="B24" s="175"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="176"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="176"/>
+      <c r="G24" s="176"/>
+      <c r="H24" s="185"/>
+      <c r="I24" s="186"/>
+      <c r="J24" s="186"/>
+      <c r="K24" s="186"/>
+      <c r="L24" s="186"/>
+      <c r="M24" s="187"/>
+      <c r="N24" s="182"/>
+      <c r="O24" s="183"/>
+      <c r="P24" s="184"/>
+      <c r="Q24" s="175"/>
+      <c r="R24" s="181"/>
+      <c r="S24" s="181"/>
+    </row>
+    <row r="25" spans="1:19" ht="30" customHeight="1">
+      <c r="A25" s="175"/>
+      <c r="B25" s="175"/>
+      <c r="C25" s="176"/>
+      <c r="D25" s="176"/>
+      <c r="E25" s="176"/>
+      <c r="F25" s="176"/>
+      <c r="G25" s="176"/>
+      <c r="H25" s="185"/>
+      <c r="I25" s="186"/>
+      <c r="J25" s="186"/>
+      <c r="K25" s="186"/>
+      <c r="L25" s="186"/>
+      <c r="M25" s="187"/>
+      <c r="N25" s="182"/>
+      <c r="O25" s="183"/>
+      <c r="P25" s="184"/>
+      <c r="Q25" s="175"/>
+      <c r="R25" s="181"/>
+      <c r="S25" s="181"/>
+    </row>
+    <row r="26" spans="1:19" ht="30" customHeight="1">
+      <c r="A26" s="175"/>
+      <c r="B26" s="175"/>
+      <c r="C26" s="176"/>
+      <c r="D26" s="176"/>
+      <c r="E26" s="176"/>
+      <c r="F26" s="176"/>
+      <c r="G26" s="176"/>
+      <c r="H26" s="185"/>
+      <c r="I26" s="186"/>
+      <c r="J26" s="186"/>
+      <c r="K26" s="186"/>
+      <c r="L26" s="186"/>
+      <c r="M26" s="187"/>
+      <c r="N26" s="182"/>
+      <c r="O26" s="183"/>
+      <c r="P26" s="184"/>
+      <c r="Q26" s="175"/>
+      <c r="R26" s="181"/>
+      <c r="S26" s="181"/>
+    </row>
+    <row r="27" spans="1:19" ht="30" customHeight="1">
+      <c r="A27" s="175"/>
+      <c r="B27" s="175"/>
+      <c r="C27" s="176"/>
+      <c r="D27" s="176"/>
+      <c r="E27" s="176"/>
+      <c r="F27" s="176"/>
+      <c r="G27" s="176"/>
+      <c r="H27" s="185"/>
+      <c r="I27" s="186"/>
+      <c r="J27" s="186"/>
+      <c r="K27" s="186"/>
+      <c r="L27" s="186"/>
+      <c r="M27" s="187"/>
+      <c r="N27" s="182"/>
+      <c r="O27" s="183"/>
+      <c r="P27" s="184"/>
+      <c r="Q27" s="175"/>
+      <c r="R27" s="181"/>
+      <c r="S27" s="181"/>
+    </row>
+    <row r="28" spans="1:19" ht="30" customHeight="1">
+      <c r="A28" s="175"/>
+      <c r="B28" s="175"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="176"/>
+      <c r="E28" s="176"/>
+      <c r="F28" s="176"/>
+      <c r="G28" s="176"/>
+      <c r="H28" s="185"/>
+      <c r="I28" s="186"/>
+      <c r="J28" s="186"/>
+      <c r="K28" s="186"/>
+      <c r="L28" s="186"/>
+      <c r="M28" s="187"/>
+      <c r="N28" s="182"/>
+      <c r="O28" s="183"/>
+      <c r="P28" s="184"/>
+      <c r="Q28" s="175"/>
+      <c r="R28" s="181"/>
+      <c r="S28" s="181"/>
+    </row>
+    <row r="29" spans="1:19" ht="30" customHeight="1">
+      <c r="A29" s="175"/>
+      <c r="B29" s="175"/>
+      <c r="C29" s="176"/>
+      <c r="D29" s="176"/>
+      <c r="E29" s="176"/>
+      <c r="F29" s="176"/>
+      <c r="G29" s="176"/>
+      <c r="H29" s="185"/>
+      <c r="I29" s="186"/>
+      <c r="J29" s="186"/>
+      <c r="K29" s="186"/>
+      <c r="L29" s="186"/>
+      <c r="M29" s="187"/>
+      <c r="N29" s="182"/>
+      <c r="O29" s="183"/>
+      <c r="P29" s="184"/>
+      <c r="Q29" s="175"/>
+      <c r="R29" s="181"/>
+      <c r="S29" s="181"/>
+    </row>
+    <row r="30" spans="1:19" ht="30" customHeight="1">
+      <c r="A30" s="175"/>
+      <c r="B30" s="175"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="176"/>
+      <c r="E30" s="176"/>
+      <c r="F30" s="176"/>
+      <c r="G30" s="176"/>
+      <c r="H30" s="185"/>
+      <c r="I30" s="186"/>
+      <c r="J30" s="186"/>
+      <c r="K30" s="186"/>
+      <c r="L30" s="186"/>
+      <c r="M30" s="187"/>
+      <c r="N30" s="182"/>
+      <c r="O30" s="183"/>
+      <c r="P30" s="184"/>
+      <c r="Q30" s="175"/>
+      <c r="R30" s="181"/>
+      <c r="S30" s="181"/>
+    </row>
+    <row r="31" spans="1:19" ht="30" customHeight="1">
+      <c r="A31" s="175"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="176"/>
+      <c r="D31" s="176"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="176"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="185"/>
+      <c r="I31" s="186"/>
+      <c r="J31" s="186"/>
+      <c r="K31" s="186"/>
+      <c r="L31" s="186"/>
+      <c r="M31" s="187"/>
+      <c r="N31" s="182"/>
+      <c r="O31" s="183"/>
+      <c r="P31" s="184"/>
+      <c r="Q31" s="175"/>
+      <c r="R31" s="181"/>
+      <c r="S31" s="181"/>
+    </row>
+    <row r="32" spans="1:19" ht="30" customHeight="1">
+      <c r="A32" s="175"/>
+      <c r="B32" s="175"/>
+      <c r="C32" s="176"/>
+      <c r="D32" s="176"/>
+      <c r="E32" s="176"/>
+      <c r="F32" s="176"/>
+      <c r="G32" s="176"/>
+      <c r="H32" s="185"/>
+      <c r="I32" s="186"/>
+      <c r="J32" s="186"/>
+      <c r="K32" s="186"/>
+      <c r="L32" s="186"/>
+      <c r="M32" s="187"/>
+      <c r="N32" s="182"/>
+      <c r="O32" s="183"/>
+      <c r="P32" s="184"/>
+      <c r="Q32" s="175"/>
+      <c r="R32" s="181"/>
+      <c r="S32" s="181"/>
+    </row>
+    <row r="33" spans="1:19" ht="30" customHeight="1">
+      <c r="A33" s="175"/>
+      <c r="B33" s="175"/>
+      <c r="C33" s="176"/>
+      <c r="D33" s="176"/>
+      <c r="E33" s="176"/>
+      <c r="F33" s="176"/>
+      <c r="G33" s="176"/>
+      <c r="H33" s="185"/>
+      <c r="I33" s="186"/>
+      <c r="J33" s="186"/>
+      <c r="K33" s="186"/>
+      <c r="L33" s="186"/>
+      <c r="M33" s="187"/>
+      <c r="N33" s="182"/>
+      <c r="O33" s="183"/>
+      <c r="P33" s="184"/>
+      <c r="Q33" s="175"/>
+      <c r="R33" s="181"/>
+      <c r="S33" s="181"/>
+    </row>
+    <row r="34" spans="1:19" ht="30" customHeight="1">
+      <c r="A34" s="175"/>
+      <c r="B34" s="175"/>
+      <c r="C34" s="176"/>
+      <c r="D34" s="176"/>
+      <c r="E34" s="176"/>
+      <c r="F34" s="176"/>
+      <c r="G34" s="176"/>
+      <c r="H34" s="185"/>
+      <c r="I34" s="186"/>
+      <c r="J34" s="186"/>
+      <c r="K34" s="186"/>
+      <c r="L34" s="186"/>
+      <c r="M34" s="187"/>
+      <c r="N34" s="182"/>
+      <c r="O34" s="183"/>
+      <c r="P34" s="184"/>
+      <c r="Q34" s="175"/>
+      <c r="R34" s="181"/>
+      <c r="S34" s="181"/>
+    </row>
+    <row r="35" spans="1:19" ht="30" customHeight="1">
+      <c r="A35" s="175"/>
+      <c r="B35" s="175"/>
+      <c r="C35" s="176"/>
+      <c r="D35" s="176"/>
+      <c r="E35" s="176"/>
+      <c r="F35" s="176"/>
+      <c r="G35" s="176"/>
+      <c r="H35" s="185"/>
+      <c r="I35" s="186"/>
+      <c r="J35" s="186"/>
+      <c r="K35" s="186"/>
+      <c r="L35" s="186"/>
+      <c r="M35" s="187"/>
+      <c r="N35" s="182"/>
+      <c r="O35" s="183"/>
+      <c r="P35" s="184"/>
+      <c r="Q35" s="175"/>
+      <c r="R35" s="181"/>
+      <c r="S35" s="181"/>
+    </row>
+    <row r="36" spans="1:19" ht="30" customHeight="1">
+      <c r="A36" s="175"/>
+      <c r="B36" s="175"/>
+      <c r="C36" s="176"/>
+      <c r="D36" s="176"/>
+      <c r="E36" s="176"/>
+      <c r="F36" s="176"/>
+      <c r="G36" s="176"/>
+      <c r="H36" s="185"/>
+      <c r="I36" s="186"/>
+      <c r="J36" s="186"/>
+      <c r="K36" s="186"/>
+      <c r="L36" s="186"/>
+      <c r="M36" s="187"/>
+      <c r="N36" s="182"/>
+      <c r="O36" s="183"/>
+      <c r="P36" s="184"/>
+      <c r="Q36" s="175"/>
+      <c r="R36" s="181"/>
+      <c r="S36" s="181"/>
+    </row>
+    <row r="37" spans="1:19" ht="30" customHeight="1">
+      <c r="A37" s="175"/>
+      <c r="B37" s="175"/>
+      <c r="C37" s="176"/>
+      <c r="D37" s="176"/>
+      <c r="E37" s="176"/>
+      <c r="F37" s="176"/>
+      <c r="G37" s="176"/>
+      <c r="H37" s="185"/>
+      <c r="I37" s="186"/>
+      <c r="J37" s="186"/>
+      <c r="K37" s="186"/>
+      <c r="L37" s="186"/>
+      <c r="M37" s="187"/>
+      <c r="N37" s="182"/>
+      <c r="O37" s="183"/>
+      <c r="P37" s="184"/>
+      <c r="Q37" s="175"/>
+      <c r="R37" s="181"/>
+      <c r="S37" s="181"/>
+    </row>
+    <row r="38" spans="1:19" ht="30" customHeight="1">
+      <c r="A38" s="175"/>
+      <c r="B38" s="175"/>
+      <c r="C38" s="176"/>
+      <c r="D38" s="176"/>
+      <c r="E38" s="176"/>
+      <c r="F38" s="176"/>
+      <c r="G38" s="176"/>
+      <c r="H38" s="185"/>
+      <c r="I38" s="186"/>
+      <c r="J38" s="186"/>
+      <c r="K38" s="186"/>
+      <c r="L38" s="186"/>
+      <c r="M38" s="187"/>
+      <c r="N38" s="182"/>
+      <c r="O38" s="183"/>
+      <c r="P38" s="184"/>
+      <c r="Q38" s="175"/>
+      <c r="R38" s="181"/>
+      <c r="S38" s="181"/>
+    </row>
+    <row r="39" spans="1:19" ht="30" customHeight="1">
+      <c r="A39" s="175"/>
+      <c r="B39" s="175"/>
+      <c r="C39" s="176"/>
+      <c r="D39" s="176"/>
+      <c r="E39" s="176"/>
+      <c r="F39" s="176"/>
+      <c r="G39" s="176"/>
+      <c r="H39" s="185"/>
+      <c r="I39" s="186"/>
+      <c r="J39" s="186"/>
+      <c r="K39" s="186"/>
+      <c r="L39" s="186"/>
+      <c r="M39" s="187"/>
+      <c r="N39" s="182"/>
+      <c r="O39" s="183"/>
+      <c r="P39" s="184"/>
+      <c r="Q39" s="175"/>
+      <c r="R39" s="181"/>
+      <c r="S39" s="181"/>
+    </row>
+    <row r="40" spans="1:19" ht="30" customHeight="1">
+      <c r="A40" s="175"/>
+      <c r="B40" s="175"/>
+      <c r="C40" s="176"/>
+      <c r="D40" s="176"/>
+      <c r="E40" s="176"/>
+      <c r="F40" s="176"/>
+      <c r="G40" s="176"/>
+      <c r="H40" s="185"/>
+      <c r="I40" s="186"/>
+      <c r="J40" s="186"/>
+      <c r="K40" s="186"/>
+      <c r="L40" s="186"/>
+      <c r="M40" s="187"/>
+      <c r="N40" s="182"/>
+      <c r="O40" s="183"/>
+      <c r="P40" s="184"/>
+      <c r="Q40" s="175"/>
+      <c r="R40" s="181"/>
+      <c r="S40" s="181"/>
+    </row>
+    <row r="41" spans="1:19" ht="30" customHeight="1">
+      <c r="A41" s="175"/>
+      <c r="B41" s="175"/>
+      <c r="C41" s="176"/>
+      <c r="D41" s="176"/>
+      <c r="E41" s="176"/>
+      <c r="F41" s="176"/>
+      <c r="G41" s="176"/>
+      <c r="H41" s="185"/>
+      <c r="I41" s="186"/>
+      <c r="J41" s="186"/>
+      <c r="K41" s="186"/>
+      <c r="L41" s="186"/>
+      <c r="M41" s="187"/>
+      <c r="N41" s="182"/>
+      <c r="O41" s="183"/>
+      <c r="P41" s="184"/>
+      <c r="Q41" s="175"/>
+      <c r="R41" s="181"/>
+      <c r="S41" s="181"/>
+    </row>
+    <row r="42" spans="1:19" ht="30" customHeight="1">
+      <c r="A42" s="175"/>
+      <c r="B42" s="175"/>
+      <c r="C42" s="176"/>
+      <c r="D42" s="176"/>
+      <c r="E42" s="176"/>
+      <c r="F42" s="176"/>
+      <c r="G42" s="176"/>
+      <c r="H42" s="185"/>
+      <c r="I42" s="186"/>
+      <c r="J42" s="186"/>
+      <c r="K42" s="186"/>
+      <c r="L42" s="186"/>
+      <c r="M42" s="187"/>
+      <c r="N42" s="182"/>
+      <c r="O42" s="183"/>
+      <c r="P42" s="184"/>
+      <c r="Q42" s="175"/>
+      <c r="R42" s="181"/>
+      <c r="S42" s="181"/>
+    </row>
+    <row r="43" spans="1:19" ht="30" customHeight="1">
+      <c r="A43" s="175"/>
+      <c r="B43" s="175"/>
+      <c r="C43" s="176"/>
+      <c r="D43" s="176"/>
+      <c r="E43" s="176"/>
+      <c r="F43" s="176"/>
+      <c r="G43" s="176"/>
+      <c r="H43" s="185"/>
+      <c r="I43" s="186"/>
+      <c r="J43" s="186"/>
+      <c r="K43" s="186"/>
+      <c r="L43" s="186"/>
+      <c r="M43" s="187"/>
+      <c r="N43" s="182"/>
+      <c r="O43" s="183"/>
+      <c r="P43" s="184"/>
+      <c r="Q43" s="175"/>
+      <c r="R43" s="181"/>
+      <c r="S43" s="181"/>
+    </row>
+    <row r="44" spans="1:19" ht="30" customHeight="1">
+      <c r="A44" s="175"/>
+      <c r="B44" s="175"/>
+      <c r="C44" s="176"/>
+      <c r="D44" s="176"/>
+      <c r="E44" s="176"/>
+      <c r="F44" s="176"/>
+      <c r="G44" s="176"/>
+      <c r="H44" s="185"/>
+      <c r="I44" s="186"/>
+      <c r="J44" s="186"/>
+      <c r="K44" s="186"/>
+      <c r="L44" s="186"/>
+      <c r="M44" s="187"/>
+      <c r="N44" s="182"/>
+      <c r="O44" s="183"/>
+      <c r="P44" s="184"/>
+      <c r="Q44" s="175"/>
+      <c r="R44" s="181"/>
+      <c r="S44" s="181"/>
+    </row>
+    <row r="45" spans="1:19" ht="30" customHeight="1">
+      <c r="A45" s="175"/>
+      <c r="B45" s="175"/>
+      <c r="C45" s="176"/>
+      <c r="D45" s="176"/>
+      <c r="E45" s="176"/>
+      <c r="F45" s="176"/>
+      <c r="G45" s="176"/>
+      <c r="H45" s="185"/>
+      <c r="I45" s="186"/>
+      <c r="J45" s="186"/>
+      <c r="K45" s="186"/>
+      <c r="L45" s="186"/>
+      <c r="M45" s="187"/>
+      <c r="N45" s="182"/>
+      <c r="O45" s="183"/>
+      <c r="P45" s="184"/>
+      <c r="Q45" s="175"/>
+      <c r="R45" s="181"/>
+      <c r="S45" s="181"/>
+    </row>
+    <row r="46" spans="1:19" ht="30" customHeight="1">
+      <c r="A46" s="175"/>
+      <c r="B46" s="175"/>
+      <c r="C46" s="176"/>
+      <c r="D46" s="176"/>
+      <c r="E46" s="176"/>
+      <c r="F46" s="176"/>
+      <c r="G46" s="176"/>
+      <c r="H46" s="185"/>
+      <c r="I46" s="186"/>
+      <c r="J46" s="186"/>
+      <c r="K46" s="186"/>
+      <c r="L46" s="186"/>
+      <c r="M46" s="187"/>
+      <c r="N46" s="182"/>
+      <c r="O46" s="183"/>
+      <c r="P46" s="184"/>
+      <c r="Q46" s="175"/>
+      <c r="R46" s="181"/>
+      <c r="S46" s="181"/>
+    </row>
+    <row r="47" spans="1:19" ht="30" customHeight="1">
+      <c r="A47" s="175"/>
+      <c r="B47" s="175"/>
+      <c r="C47" s="176"/>
+      <c r="D47" s="176"/>
+      <c r="E47" s="176"/>
+      <c r="F47" s="176"/>
+      <c r="G47" s="176"/>
+      <c r="H47" s="185"/>
+      <c r="I47" s="186"/>
+      <c r="J47" s="186"/>
+      <c r="K47" s="186"/>
+      <c r="L47" s="186"/>
+      <c r="M47" s="187"/>
+      <c r="N47" s="182"/>
+      <c r="O47" s="183"/>
+      <c r="P47" s="184"/>
+      <c r="Q47" s="175"/>
+      <c r="R47" s="181"/>
+      <c r="S47" s="181"/>
+    </row>
+    <row r="48" spans="1:19" ht="30" customHeight="1">
+      <c r="A48" s="175"/>
+      <c r="B48" s="175"/>
+      <c r="C48" s="176"/>
+      <c r="D48" s="176"/>
+      <c r="E48" s="176"/>
+      <c r="F48" s="176"/>
+      <c r="G48" s="176"/>
+      <c r="H48" s="185"/>
+      <c r="I48" s="186"/>
+      <c r="J48" s="186"/>
+      <c r="K48" s="186"/>
+      <c r="L48" s="186"/>
+      <c r="M48" s="187"/>
+      <c r="N48" s="182"/>
+      <c r="O48" s="183"/>
+      <c r="P48" s="184"/>
+      <c r="Q48" s="175"/>
+      <c r="R48" s="181"/>
+      <c r="S48" s="181"/>
+    </row>
+    <row r="49" spans="1:19" ht="30" customHeight="1">
+      <c r="A49" s="175"/>
+      <c r="B49" s="175"/>
+      <c r="C49" s="176"/>
+      <c r="D49" s="176"/>
+      <c r="E49" s="176"/>
+      <c r="F49" s="176"/>
+      <c r="G49" s="176"/>
+      <c r="H49" s="185"/>
+      <c r="I49" s="186"/>
+      <c r="J49" s="186"/>
+      <c r="K49" s="186"/>
+      <c r="L49" s="186"/>
+      <c r="M49" s="187"/>
+      <c r="N49" s="182"/>
+      <c r="O49" s="183"/>
+      <c r="P49" s="184"/>
+      <c r="Q49" s="175"/>
+      <c r="R49" s="181"/>
+      <c r="S49" s="181"/>
+    </row>
+    <row r="50" spans="1:19" ht="30" customHeight="1">
+      <c r="A50" s="175"/>
+      <c r="B50" s="175"/>
+      <c r="C50" s="176"/>
+      <c r="D50" s="176"/>
+      <c r="E50" s="176"/>
+      <c r="F50" s="176"/>
+      <c r="G50" s="176"/>
+      <c r="H50" s="185"/>
+      <c r="I50" s="186"/>
+      <c r="J50" s="186"/>
+      <c r="K50" s="186"/>
+      <c r="L50" s="186"/>
+      <c r="M50" s="187"/>
+      <c r="N50" s="182"/>
+      <c r="O50" s="183"/>
+      <c r="P50" s="184"/>
+      <c r="Q50" s="175"/>
+      <c r="R50" s="181"/>
+      <c r="S50" s="181"/>
+    </row>
+    <row r="51" spans="1:19" ht="30" customHeight="1">
+      <c r="A51" s="175"/>
+      <c r="B51" s="175"/>
+      <c r="C51" s="176"/>
+      <c r="D51" s="176"/>
+      <c r="E51" s="176"/>
+      <c r="F51" s="176"/>
+      <c r="G51" s="176"/>
+      <c r="H51" s="185"/>
+      <c r="I51" s="186"/>
+      <c r="J51" s="186"/>
+      <c r="K51" s="186"/>
+      <c r="L51" s="186"/>
+      <c r="M51" s="187"/>
+      <c r="N51" s="182"/>
+      <c r="O51" s="183"/>
+      <c r="P51" s="184"/>
+      <c r="Q51" s="175"/>
+      <c r="R51" s="181"/>
+      <c r="S51" s="181"/>
+    </row>
+    <row r="52" spans="1:19" ht="30" customHeight="1">
+      <c r="A52" s="175"/>
+      <c r="B52" s="175"/>
+      <c r="C52" s="176"/>
+      <c r="D52" s="176"/>
+      <c r="E52" s="176"/>
+      <c r="F52" s="176"/>
+      <c r="G52" s="176"/>
+      <c r="H52" s="185"/>
+      <c r="I52" s="186"/>
+      <c r="J52" s="186"/>
+      <c r="K52" s="186"/>
+      <c r="L52" s="186"/>
+      <c r="M52" s="187"/>
+      <c r="N52" s="182"/>
+      <c r="O52" s="183"/>
+      <c r="P52" s="184"/>
+      <c r="Q52" s="175"/>
+      <c r="R52" s="181"/>
+      <c r="S52" s="181"/>
+    </row>
+  </sheetData>
+  <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="R2:S2"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
 </file>
--- a/Documents/削除機能詳細設計書.xlsx
+++ b/Documents/削除機能詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91766EC-5528-44A7-93B9-0CFD84348658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB54B0CE-D250-45EC-8F50-7C48A0AC146A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8340" yWindow="660" windowWidth="11415" windowHeight="8955" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="146">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -935,6 +935,50 @@
     <rPh sb="10" eb="12">
       <t>ヒョウジ</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>異常系</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態でのページ表示</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態であること</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/task-delete.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -2058,7 +2102,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2291,6 +2335,57 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2324,21 +2419,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2384,42 +2464,6 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2483,59 +2527,92 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2543,47 +2620,50 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2594,18 +2674,6 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2645,30 +2713,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2698,6 +2742,23 @@
     </xf>
     <xf numFmtId="9" fontId="19" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -9250,19 +9311,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="103" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="86"/>
-      <c r="F1" s="103" t="s">
+      <c r="E1" s="103"/>
+      <c r="F1" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="86"/>
+      <c r="G1" s="103"/>
       <c r="H1" s="37" t="s">
         <v>8</v>
       </c>
@@ -9274,190 +9335,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="97"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="104" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="104" t="s">
+      <c r="E2" s="117"/>
+      <c r="F2" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="105"/>
-      <c r="H2" s="108">
+      <c r="G2" s="117"/>
+      <c r="H2" s="120">
         <v>45806</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="I2" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="81"/>
+      <c r="J2" s="98"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="97"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="82"/>
+      <c r="A3" s="109"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="100"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="112"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="100"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="87" t="s">
+      <c r="B5" s="102"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="104" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="88"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="105"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="92" t="s">
+      <c r="B6" s="79"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="88" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="93"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="82"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="91"/>
-      <c r="D7" s="92" t="s">
+      <c r="B7" s="79"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="90"/>
-      <c r="F7" s="90"/>
-      <c r="G7" s="90"/>
-      <c r="H7" s="90"/>
-      <c r="I7" s="90"/>
-      <c r="J7" s="93"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="82"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="89" t="s">
+      <c r="A8" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="90"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="92" t="s">
+      <c r="B8" s="79"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="93"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="79"/>
+      <c r="J8" s="82"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="115" t="s">
+      <c r="A9" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="118" t="s">
+      <c r="B9" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="91"/>
-      <c r="D9" s="109" t="s">
+      <c r="C9" s="80"/>
+      <c r="D9" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="94"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="116"/>
-      <c r="B10" s="118" t="s">
+      <c r="A10" s="90"/>
+      <c r="B10" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="93"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="82"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="117"/>
-      <c r="B11" s="118" t="s">
+      <c r="A11" s="91"/>
+      <c r="B11" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="91"/>
-      <c r="D11" s="92" t="s">
+      <c r="C11" s="80"/>
+      <c r="D11" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="90"/>
-      <c r="J11" s="93"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="82"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="90"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="109" t="s">
+      <c r="B12" s="79"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="90"/>
-      <c r="J12" s="93"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="82"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="110" t="s">
+      <c r="A13" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="111"/>
-      <c r="C13" s="112"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="114"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="87"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10448,6 +10509,18 @@
     <row r="1000" s="39" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -10463,18 +10536,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -13399,20 +13460,20 @@
       <c r="J4" s="126"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="142" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="153"/>
+      <c r="B5" s="143"/>
       <c r="C5" s="137"/>
-      <c r="D5" s="154" t="s">
+      <c r="D5" s="146" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="155"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="147"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="145" t="s">
@@ -13426,19 +13487,19 @@
       <c r="G6" s="71"/>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="144"/>
+      <c r="J6" s="148"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="156"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="158"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="131"/>
@@ -13450,7 +13511,7 @@
       <c r="G8" s="74"/>
       <c r="H8" s="74"/>
       <c r="I8" s="74"/>
-      <c r="J8" s="159"/>
+      <c r="J8" s="152"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="131"/>
@@ -13462,7 +13523,7 @@
       <c r="G9" s="74"/>
       <c r="H9" s="74"/>
       <c r="I9" s="74"/>
-      <c r="J9" s="159"/>
+      <c r="J9" s="152"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="131"/>
@@ -13474,7 +13535,7 @@
       <c r="G10" s="74"/>
       <c r="H10" s="74"/>
       <c r="I10" s="74"/>
-      <c r="J10" s="159"/>
+      <c r="J10" s="152"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="131"/>
@@ -13486,7 +13547,7 @@
       <c r="G11" s="74"/>
       <c r="H11" s="74"/>
       <c r="I11" s="74"/>
-      <c r="J11" s="159"/>
+      <c r="J11" s="152"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="131"/>
@@ -13498,7 +13559,7 @@
       <c r="G12" s="74"/>
       <c r="H12" s="74"/>
       <c r="I12" s="74"/>
-      <c r="J12" s="159"/>
+      <c r="J12" s="152"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="131"/>
@@ -13510,7 +13571,7 @@
       <c r="G13" s="74"/>
       <c r="H13" s="74"/>
       <c r="I13" s="74"/>
-      <c r="J13" s="159"/>
+      <c r="J13" s="152"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="145" t="s">
@@ -13524,7 +13585,7 @@
       <c r="G14" s="71"/>
       <c r="H14" s="71"/>
       <c r="I14" s="71"/>
-      <c r="J14" s="144"/>
+      <c r="J14" s="148"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="145" t="s">
@@ -13532,7 +13593,7 @@
       </c>
       <c r="B15" s="71"/>
       <c r="C15" s="72"/>
-      <c r="D15" s="143" t="s">
+      <c r="D15" s="153" t="s">
         <v>73</v>
       </c>
       <c r="E15" s="71"/>
@@ -13564,14 +13625,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="146" t="s">
+      <c r="H16" s="154" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="71"/>
-      <c r="J16" s="144"/>
+      <c r="J16" s="148"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="142">
+      <c r="A17" s="144">
         <v>1</v>
       </c>
       <c r="B17" s="71"/>
@@ -13586,12 +13647,12 @@
         <v>82</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="143"/>
+      <c r="H17" s="153"/>
       <c r="I17" s="71"/>
-      <c r="J17" s="144"/>
+      <c r="J17" s="148"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="142">
+      <c r="A18" s="144">
         <v>2</v>
       </c>
       <c r="B18" s="71"/>
@@ -13608,12 +13669,12 @@
       <c r="G18" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="143"/>
+      <c r="H18" s="153"/>
       <c r="I18" s="71"/>
-      <c r="J18" s="144"/>
+      <c r="J18" s="148"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="142">
+      <c r="A19" s="144">
         <v>3</v>
       </c>
       <c r="B19" s="71"/>
@@ -13628,12 +13689,12 @@
       <c r="G19" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="143"/>
+      <c r="H19" s="153"/>
       <c r="I19" s="71"/>
-      <c r="J19" s="144"/>
+      <c r="J19" s="148"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="142">
+      <c r="A20" s="144">
         <v>4</v>
       </c>
       <c r="B20" s="71"/>
@@ -13650,12 +13711,12 @@
       <c r="G20" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="143"/>
+      <c r="H20" s="153"/>
       <c r="I20" s="71"/>
-      <c r="J20" s="144"/>
+      <c r="J20" s="148"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="142">
+      <c r="A21" s="144">
         <v>5</v>
       </c>
       <c r="B21" s="71"/>
@@ -13672,12 +13733,12 @@
       <c r="G21" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="143"/>
+      <c r="H21" s="153"/>
       <c r="I21" s="71"/>
-      <c r="J21" s="144"/>
+      <c r="J21" s="148"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="142">
+      <c r="A22" s="144">
         <v>6</v>
       </c>
       <c r="B22" s="71"/>
@@ -13692,12 +13753,12 @@
         <v>61</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="143"/>
+      <c r="H22" s="153"/>
       <c r="I22" s="71"/>
-      <c r="J22" s="144"/>
+      <c r="J22" s="148"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="142">
+      <c r="A23" s="144">
         <v>7</v>
       </c>
       <c r="B23" s="71"/>
@@ -13712,9 +13773,9 @@
         <v>61</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="148"/>
-      <c r="J23" s="151"/>
+      <c r="H23" s="155"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="157"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
       <c r="A24" s="145"/>
@@ -13726,13 +13787,13 @@
       <c r="G24" s="71"/>
       <c r="H24" s="71"/>
       <c r="I24" s="71"/>
-      <c r="J24" s="144"/>
+      <c r="J24" s="148"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
       <c r="A25" s="145"/>
       <c r="B25" s="71"/>
       <c r="C25" s="72"/>
-      <c r="D25" s="143"/>
+      <c r="D25" s="153"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
@@ -13748,93 +13809,93 @@
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="146"/>
+      <c r="H26" s="154"/>
       <c r="I26" s="71"/>
-      <c r="J26" s="144"/>
+      <c r="J26" s="148"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="142"/>
+      <c r="A27" s="144"/>
       <c r="B27" s="71"/>
       <c r="C27" s="72"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="143"/>
+      <c r="H27" s="153"/>
       <c r="I27" s="71"/>
-      <c r="J27" s="144"/>
+      <c r="J27" s="148"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="142"/>
+      <c r="A28" s="144"/>
       <c r="B28" s="71"/>
       <c r="C28" s="72"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="143"/>
+      <c r="H28" s="153"/>
       <c r="I28" s="71"/>
-      <c r="J28" s="144"/>
+      <c r="J28" s="148"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="142"/>
+      <c r="A29" s="144"/>
       <c r="B29" s="71"/>
       <c r="C29" s="72"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
-      <c r="H29" s="143"/>
+      <c r="H29" s="153"/>
       <c r="I29" s="71"/>
-      <c r="J29" s="144"/>
+      <c r="J29" s="148"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="142"/>
+      <c r="A30" s="144"/>
       <c r="B30" s="71"/>
       <c r="C30" s="72"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="143"/>
+      <c r="H30" s="153"/>
       <c r="I30" s="71"/>
-      <c r="J30" s="144"/>
+      <c r="J30" s="148"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="142"/>
+      <c r="A31" s="144"/>
       <c r="B31" s="71"/>
       <c r="C31" s="72"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="143"/>
+      <c r="H31" s="153"/>
       <c r="I31" s="71"/>
-      <c r="J31" s="144"/>
+      <c r="J31" s="148"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="142"/>
+      <c r="A32" s="144"/>
       <c r="B32" s="71"/>
       <c r="C32" s="72"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="143"/>
+      <c r="H32" s="153"/>
       <c r="I32" s="71"/>
-      <c r="J32" s="144"/>
+      <c r="J32" s="148"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="147"/>
-      <c r="B33" s="148"/>
-      <c r="C33" s="149"/>
+      <c r="A33" s="158"/>
+      <c r="B33" s="156"/>
+      <c r="C33" s="159"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
-      <c r="H33" s="150"/>
-      <c r="I33" s="148"/>
-      <c r="J33" s="151"/>
+      <c r="H33" s="155"/>
+      <c r="I33" s="156"/>
+      <c r="J33" s="157"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
       <c r="A34" s="145"/>
@@ -13846,13 +13907,13 @@
       <c r="G34" s="71"/>
       <c r="H34" s="71"/>
       <c r="I34" s="71"/>
-      <c r="J34" s="144"/>
+      <c r="J34" s="148"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
       <c r="A35" s="145"/>
       <c r="B35" s="71"/>
       <c r="C35" s="72"/>
-      <c r="D35" s="143"/>
+      <c r="D35" s="153"/>
       <c r="E35" s="71"/>
       <c r="F35" s="71"/>
       <c r="G35" s="71"/>
@@ -13868,69 +13929,69 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
-      <c r="H36" s="146"/>
+      <c r="H36" s="154"/>
       <c r="I36" s="71"/>
-      <c r="J36" s="144"/>
+      <c r="J36" s="148"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="142"/>
+      <c r="A37" s="144"/>
       <c r="B37" s="71"/>
       <c r="C37" s="72"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="143"/>
+      <c r="H37" s="153"/>
       <c r="I37" s="71"/>
-      <c r="J37" s="144"/>
+      <c r="J37" s="148"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="142"/>
+      <c r="A38" s="144"/>
       <c r="B38" s="71"/>
       <c r="C38" s="72"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="143"/>
+      <c r="H38" s="153"/>
       <c r="I38" s="71"/>
-      <c r="J38" s="144"/>
+      <c r="J38" s="148"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="142"/>
+      <c r="A39" s="144"/>
       <c r="B39" s="71"/>
       <c r="C39" s="72"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="143"/>
+      <c r="H39" s="153"/>
       <c r="I39" s="71"/>
-      <c r="J39" s="144"/>
+      <c r="J39" s="148"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="142"/>
+      <c r="A40" s="144"/>
       <c r="B40" s="71"/>
       <c r="C40" s="72"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="143"/>
+      <c r="H40" s="153"/>
       <c r="I40" s="71"/>
-      <c r="J40" s="144"/>
+      <c r="J40" s="148"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="142"/>
+      <c r="A41" s="144"/>
       <c r="B41" s="71"/>
       <c r="C41" s="72"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="143"/>
+      <c r="H41" s="153"/>
       <c r="I41" s="71"/>
-      <c r="J41" s="144"/>
+      <c r="J41" s="148"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14893,11 +14954,50 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -14914,50 +15014,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -15048,20 +15109,20 @@
       <c r="J4" s="126"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="142" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="153"/>
+      <c r="B5" s="143"/>
       <c r="C5" s="137"/>
-      <c r="D5" s="154" t="s">
+      <c r="D5" s="146" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="155"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="147"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="145" t="s">
@@ -15075,19 +15136,19 @@
       <c r="G6" s="71"/>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="144"/>
+      <c r="J6" s="148"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="156"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="158"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="131"/>
@@ -15099,7 +15160,7 @@
       <c r="G8" s="74"/>
       <c r="H8" s="74"/>
       <c r="I8" s="74"/>
-      <c r="J8" s="159"/>
+      <c r="J8" s="152"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="131"/>
@@ -15111,7 +15172,7 @@
       <c r="G9" s="74"/>
       <c r="H9" s="74"/>
       <c r="I9" s="74"/>
-      <c r="J9" s="159"/>
+      <c r="J9" s="152"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="131"/>
@@ -15123,7 +15184,7 @@
       <c r="G10" s="74"/>
       <c r="H10" s="74"/>
       <c r="I10" s="74"/>
-      <c r="J10" s="159"/>
+      <c r="J10" s="152"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="131"/>
@@ -15135,7 +15196,7 @@
       <c r="G11" s="74"/>
       <c r="H11" s="74"/>
       <c r="I11" s="74"/>
-      <c r="J11" s="159"/>
+      <c r="J11" s="152"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="131"/>
@@ -15147,7 +15208,7 @@
       <c r="G12" s="74"/>
       <c r="H12" s="74"/>
       <c r="I12" s="74"/>
-      <c r="J12" s="159"/>
+      <c r="J12" s="152"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="131"/>
@@ -15159,7 +15220,7 @@
       <c r="G13" s="74"/>
       <c r="H13" s="74"/>
       <c r="I13" s="74"/>
-      <c r="J13" s="159"/>
+      <c r="J13" s="152"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="145" t="s">
@@ -15173,7 +15234,7 @@
       <c r="G14" s="71"/>
       <c r="H14" s="71"/>
       <c r="I14" s="71"/>
-      <c r="J14" s="144"/>
+      <c r="J14" s="148"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="145" t="s">
@@ -15181,7 +15242,7 @@
       </c>
       <c r="B15" s="71"/>
       <c r="C15" s="72"/>
-      <c r="D15" s="143" t="s">
+      <c r="D15" s="153" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="71"/>
@@ -15213,14 +15274,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="146" t="s">
+      <c r="H16" s="154" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="71"/>
-      <c r="J16" s="144"/>
+      <c r="J16" s="148"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="142">
+      <c r="A17" s="144">
         <v>1</v>
       </c>
       <c r="B17" s="71"/>
@@ -15237,83 +15298,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="143" t="s">
+      <c r="H17" s="153" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="71"/>
-      <c r="J17" s="144"/>
+      <c r="J17" s="148"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="142"/>
+      <c r="A18" s="144"/>
       <c r="B18" s="71"/>
       <c r="C18" s="72"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="143"/>
+      <c r="H18" s="153"/>
       <c r="I18" s="71"/>
-      <c r="J18" s="144"/>
+      <c r="J18" s="148"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="142"/>
+      <c r="A19" s="144"/>
       <c r="B19" s="71"/>
       <c r="C19" s="72"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="143"/>
+      <c r="H19" s="153"/>
       <c r="I19" s="71"/>
-      <c r="J19" s="144"/>
+      <c r="J19" s="148"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="142"/>
+      <c r="A20" s="144"/>
       <c r="B20" s="71"/>
       <c r="C20" s="72"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="143"/>
+      <c r="H20" s="153"/>
       <c r="I20" s="71"/>
-      <c r="J20" s="144"/>
+      <c r="J20" s="148"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="142"/>
+      <c r="A21" s="144"/>
       <c r="B21" s="71"/>
       <c r="C21" s="72"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="143"/>
+      <c r="H21" s="153"/>
       <c r="I21" s="71"/>
-      <c r="J21" s="144"/>
+      <c r="J21" s="148"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="142"/>
+      <c r="A22" s="144"/>
       <c r="B22" s="71"/>
       <c r="C22" s="72"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="143"/>
+      <c r="H22" s="153"/>
       <c r="I22" s="71"/>
-      <c r="J22" s="144"/>
+      <c r="J22" s="148"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="147"/>
-      <c r="B23" s="148"/>
-      <c r="C23" s="149"/>
+      <c r="A23" s="158"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="159"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="148"/>
-      <c r="J23" s="151"/>
+      <c r="H23" s="155"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="157"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -16294,6 +16355,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -16309,22 +16386,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -16415,20 +16476,20 @@
       <c r="J4" s="126"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="142" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="153"/>
+      <c r="B5" s="143"/>
       <c r="C5" s="137"/>
-      <c r="D5" s="154" t="s">
+      <c r="D5" s="146" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="155"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="147"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="145" t="s">
@@ -16442,19 +16503,19 @@
       <c r="G6" s="71"/>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="144"/>
+      <c r="J6" s="148"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="156"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="158"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="131"/>
@@ -16466,7 +16527,7 @@
       <c r="G8" s="74"/>
       <c r="H8" s="74"/>
       <c r="I8" s="74"/>
-      <c r="J8" s="159"/>
+      <c r="J8" s="152"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="131"/>
@@ -16478,7 +16539,7 @@
       <c r="G9" s="74"/>
       <c r="H9" s="74"/>
       <c r="I9" s="74"/>
-      <c r="J9" s="159"/>
+      <c r="J9" s="152"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="131"/>
@@ -16490,7 +16551,7 @@
       <c r="G10" s="74"/>
       <c r="H10" s="74"/>
       <c r="I10" s="74"/>
-      <c r="J10" s="159"/>
+      <c r="J10" s="152"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="131"/>
@@ -16502,7 +16563,7 @@
       <c r="G11" s="74"/>
       <c r="H11" s="74"/>
       <c r="I11" s="74"/>
-      <c r="J11" s="159"/>
+      <c r="J11" s="152"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="131"/>
@@ -16514,7 +16575,7 @@
       <c r="G12" s="74"/>
       <c r="H12" s="74"/>
       <c r="I12" s="74"/>
-      <c r="J12" s="159"/>
+      <c r="J12" s="152"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="131"/>
@@ -16526,7 +16587,7 @@
       <c r="G13" s="74"/>
       <c r="H13" s="74"/>
       <c r="I13" s="74"/>
-      <c r="J13" s="159"/>
+      <c r="J13" s="152"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="145" t="s">
@@ -16540,7 +16601,7 @@
       <c r="G14" s="71"/>
       <c r="H14" s="71"/>
       <c r="I14" s="71"/>
-      <c r="J14" s="144"/>
+      <c r="J14" s="148"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="145" t="s">
@@ -16548,7 +16609,7 @@
       </c>
       <c r="B15" s="71"/>
       <c r="C15" s="72"/>
-      <c r="D15" s="143" t="s">
+      <c r="D15" s="153" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="71"/>
@@ -16580,14 +16641,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="146" t="s">
+      <c r="H16" s="154" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="71"/>
-      <c r="J16" s="144"/>
+      <c r="J16" s="148"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="142">
+      <c r="A17" s="144">
         <v>1</v>
       </c>
       <c r="B17" s="71"/>
@@ -16604,83 +16665,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="143" t="s">
+      <c r="H17" s="153" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="71"/>
-      <c r="J17" s="144"/>
+      <c r="J17" s="148"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="142"/>
+      <c r="A18" s="144"/>
       <c r="B18" s="71"/>
       <c r="C18" s="72"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="143"/>
+      <c r="H18" s="153"/>
       <c r="I18" s="71"/>
-      <c r="J18" s="144"/>
+      <c r="J18" s="148"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="142"/>
+      <c r="A19" s="144"/>
       <c r="B19" s="71"/>
       <c r="C19" s="72"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="143"/>
+      <c r="H19" s="153"/>
       <c r="I19" s="71"/>
-      <c r="J19" s="144"/>
+      <c r="J19" s="148"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="142"/>
+      <c r="A20" s="144"/>
       <c r="B20" s="71"/>
       <c r="C20" s="72"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="143"/>
+      <c r="H20" s="153"/>
       <c r="I20" s="71"/>
-      <c r="J20" s="144"/>
+      <c r="J20" s="148"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="142"/>
+      <c r="A21" s="144"/>
       <c r="B21" s="71"/>
       <c r="C21" s="72"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="143"/>
+      <c r="H21" s="153"/>
       <c r="I21" s="71"/>
-      <c r="J21" s="144"/>
+      <c r="J21" s="148"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="142"/>
+      <c r="A22" s="144"/>
       <c r="B22" s="71"/>
       <c r="C22" s="72"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="143"/>
+      <c r="H22" s="153"/>
       <c r="I22" s="71"/>
-      <c r="J22" s="144"/>
+      <c r="J22" s="148"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="147"/>
-      <c r="B23" s="148"/>
-      <c r="C23" s="149"/>
+      <c r="A23" s="158"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="159"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="148"/>
-      <c r="J23" s="151"/>
+      <c r="H23" s="155"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="157"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -17661,6 +17722,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -17676,22 +17753,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -17711,7 +17772,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="169" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="129"/>
@@ -17722,14 +17783,14 @@
       <c r="G1" s="136" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
       <c r="J1" s="137"/>
       <c r="K1" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="153"/>
-      <c r="M1" s="153"/>
+      <c r="L1" s="143"/>
+      <c r="M1" s="143"/>
       <c r="N1" s="137"/>
       <c r="O1" s="136" t="s">
         <v>8</v>
@@ -17742,7 +17803,7 @@
       <c r="S1" s="136" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="155"/>
+      <c r="T1" s="147"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="131"/>
@@ -17754,16 +17815,16 @@
       <c r="G2" s="138" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
       <c r="J2" s="139"/>
       <c r="K2" s="138" t="s">
         <v>93</v>
       </c>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
+      <c r="L2" s="150"/>
+      <c r="M2" s="150"/>
       <c r="N2" s="139"/>
-      <c r="O2" s="169">
+      <c r="O2" s="167">
         <v>45821</v>
       </c>
       <c r="P2" s="139"/>
@@ -17772,7 +17833,7 @@
       </c>
       <c r="R2" s="139"/>
       <c r="S2" s="138"/>
-      <c r="T2" s="158"/>
+      <c r="T2" s="151"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="131"/>
@@ -17794,7 +17855,7 @@
       <c r="Q3" s="140"/>
       <c r="R3" s="132"/>
       <c r="S3" s="140"/>
-      <c r="T3" s="159"/>
+      <c r="T3" s="152"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="133"/>
@@ -17816,33 +17877,33 @@
       <c r="Q4" s="141"/>
       <c r="R4" s="135"/>
       <c r="S4" s="141"/>
-      <c r="T4" s="170"/>
+      <c r="T4" s="168"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="142" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
+      <c r="B5" s="143"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
       <c r="F5" s="137"/>
-      <c r="G5" s="166" t="s">
+      <c r="G5" s="170" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="153"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="153"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="153"/>
-      <c r="P5" s="153"/>
-      <c r="Q5" s="153"/>
-      <c r="R5" s="153"/>
-      <c r="S5" s="153"/>
-      <c r="T5" s="155"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="143"/>
+      <c r="K5" s="143"/>
+      <c r="L5" s="143"/>
+      <c r="M5" s="143"/>
+      <c r="N5" s="143"/>
+      <c r="O5" s="143"/>
+      <c r="P5" s="143"/>
+      <c r="Q5" s="143"/>
+      <c r="R5" s="143"/>
+      <c r="S5" s="143"/>
+      <c r="T5" s="147"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="145" t="s">
@@ -17853,7 +17914,7 @@
       <c r="D6" s="71"/>
       <c r="E6" s="71"/>
       <c r="F6" s="72"/>
-      <c r="G6" s="143" t="s">
+      <c r="G6" s="153" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="71"/>
@@ -17868,7 +17929,7 @@
       <c r="Q6" s="71"/>
       <c r="R6" s="71"/>
       <c r="S6" s="71"/>
-      <c r="T6" s="144"/>
+      <c r="T6" s="148"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="145" t="s">
@@ -17879,7 +17940,7 @@
       <c r="D7" s="71"/>
       <c r="E7" s="71"/>
       <c r="F7" s="72"/>
-      <c r="G7" s="143" t="s">
+      <c r="G7" s="153" t="s">
         <v>95</v>
       </c>
       <c r="H7" s="71"/>
@@ -17894,7 +17955,7 @@
       <c r="Q7" s="71"/>
       <c r="R7" s="71"/>
       <c r="S7" s="71"/>
-      <c r="T7" s="144"/>
+      <c r="T7" s="148"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -18097,29 +18158,29 @@
         <v>45</v>
       </c>
       <c r="B15" s="72"/>
-      <c r="C15" s="168" t="s">
+      <c r="C15" s="173" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="72"/>
-      <c r="E15" s="146" t="s">
+      <c r="E15" s="154" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="72"/>
-      <c r="G15" s="146" t="s">
+      <c r="G15" s="154" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="71"/>
       <c r="I15" s="72"/>
-      <c r="J15" s="146" t="s">
+      <c r="J15" s="154" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="72"/>
-      <c r="L15" s="146" t="s">
+      <c r="L15" s="154" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="71"/>
       <c r="N15" s="72"/>
-      <c r="O15" s="146" t="s">
+      <c r="O15" s="154" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="71"/>
@@ -18135,27 +18196,27 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A16" s="160">
+      <c r="A16" s="171">
         <v>1</v>
       </c>
       <c r="B16" s="72"/>
-      <c r="C16" s="161" t="s">
+      <c r="C16" s="172" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="72"/>
-      <c r="E16" s="161" t="s">
+      <c r="E16" s="172" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="72"/>
-      <c r="G16" s="167" t="s">
+      <c r="G16" s="160" t="s">
         <v>96</v>
       </c>
       <c r="H16" s="71"/>
       <c r="I16" s="72"/>
-      <c r="J16" s="174" t="s">
+      <c r="J16" s="161" t="s">
         <v>97</v>
       </c>
-      <c r="K16" s="175"/>
+      <c r="K16" s="162"/>
       <c r="L16" s="164" t="s">
         <v>98</v>
       </c>
@@ -18177,24 +18238,24 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A17" s="160">
+      <c r="A17" s="171">
         <v>2</v>
       </c>
       <c r="B17" s="72"/>
-      <c r="C17" s="161" t="s">
+      <c r="C17" s="172" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="72"/>
-      <c r="E17" s="161" t="s">
+      <c r="E17" s="172" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="72"/>
-      <c r="G17" s="167" t="s">
+      <c r="G17" s="160" t="s">
         <v>105</v>
       </c>
       <c r="H17" s="71"/>
       <c r="I17" s="72"/>
-      <c r="J17" s="167" t="s">
+      <c r="J17" s="160" t="s">
         <v>106</v>
       </c>
       <c r="K17" s="72"/>
@@ -18219,28 +18280,28 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="64.5" customHeight="1">
-      <c r="A18" s="160">
+      <c r="A18" s="171">
         <v>3</v>
       </c>
       <c r="B18" s="72"/>
-      <c r="C18" s="161" t="s">
+      <c r="C18" s="172" t="s">
         <v>54</v>
       </c>
       <c r="D18" s="72"/>
-      <c r="E18" s="161" t="s">
+      <c r="E18" s="172" t="s">
         <v>100</v>
       </c>
       <c r="F18" s="72"/>
-      <c r="G18" s="167" t="s">
+      <c r="G18" s="160" t="s">
         <v>101</v>
       </c>
       <c r="H18" s="71"/>
       <c r="I18" s="72"/>
-      <c r="J18" s="167" t="s">
+      <c r="J18" s="160" t="s">
         <v>103</v>
       </c>
       <c r="K18" s="72"/>
-      <c r="L18" s="172" t="s">
+      <c r="L18" s="166" t="s">
         <v>104</v>
       </c>
       <c r="M18" s="71"/>
@@ -18261,24 +18322,24 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="61.5" customHeight="1">
-      <c r="A19" s="160">
+      <c r="A19" s="171">
         <v>4</v>
       </c>
       <c r="B19" s="72"/>
-      <c r="C19" s="161" t="s">
+      <c r="C19" s="172" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="72"/>
-      <c r="E19" s="161" t="s">
+      <c r="E19" s="172" t="s">
         <v>100</v>
       </c>
       <c r="F19" s="72"/>
-      <c r="G19" s="167" t="s">
+      <c r="G19" s="160" t="s">
         <v>139</v>
       </c>
       <c r="H19" s="71"/>
       <c r="I19" s="72"/>
-      <c r="J19" s="167" t="s">
+      <c r="J19" s="160" t="s">
         <v>97</v>
       </c>
       <c r="K19" s="72"/>
@@ -18302,27 +18363,41 @@
       <c r="Y19" s="34"/>
       <c r="Z19" s="34"/>
     </row>
-    <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="160"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="161"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="161"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="167"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="167"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="164"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="164"/>
+    <row r="20" spans="1:26" ht="50.25" customHeight="1">
+      <c r="A20" s="214">
+        <v>7</v>
+      </c>
+      <c r="B20" s="162"/>
+      <c r="C20" s="215" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="162"/>
+      <c r="E20" s="215" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="162"/>
+      <c r="G20" s="161" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="216"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="161" t="s">
+        <v>143</v>
+      </c>
+      <c r="K20" s="162"/>
+      <c r="L20" s="217" t="s">
+        <v>145</v>
+      </c>
+      <c r="M20" s="218"/>
+      <c r="N20" s="218"/>
+      <c r="O20" s="164" t="s">
+        <v>144</v>
+      </c>
       <c r="P20" s="71"/>
       <c r="Q20" s="72"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="32"/>
-      <c r="T20" s="33"/>
+      <c r="R20" s="219"/>
+      <c r="S20" s="219"/>
+      <c r="T20" s="220"/>
       <c r="U20" s="34"/>
       <c r="V20" s="34"/>
       <c r="W20" s="34"/>
@@ -18331,16 +18406,16 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="160"/>
+      <c r="A21" s="171"/>
       <c r="B21" s="72"/>
-      <c r="C21" s="161"/>
+      <c r="C21" s="172"/>
       <c r="D21" s="72"/>
-      <c r="E21" s="161"/>
+      <c r="E21" s="172"/>
       <c r="F21" s="72"/>
-      <c r="G21" s="167"/>
+      <c r="G21" s="160"/>
       <c r="H21" s="71"/>
       <c r="I21" s="72"/>
-      <c r="J21" s="167"/>
+      <c r="J21" s="160"/>
       <c r="K21" s="72"/>
       <c r="L21" s="164"/>
       <c r="M21" s="71"/>
@@ -18359,16 +18434,16 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="160"/>
+      <c r="A22" s="171"/>
       <c r="B22" s="72"/>
-      <c r="C22" s="161"/>
+      <c r="C22" s="172"/>
       <c r="D22" s="72"/>
-      <c r="E22" s="161"/>
+      <c r="E22" s="172"/>
       <c r="F22" s="72"/>
-      <c r="G22" s="167"/>
+      <c r="G22" s="160"/>
       <c r="H22" s="71"/>
       <c r="I22" s="72"/>
-      <c r="J22" s="167"/>
+      <c r="J22" s="160"/>
       <c r="K22" s="72"/>
       <c r="L22" s="164"/>
       <c r="M22" s="71"/>
@@ -18387,16 +18462,16 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="160"/>
+      <c r="A23" s="171"/>
       <c r="B23" s="72"/>
-      <c r="C23" s="161"/>
+      <c r="C23" s="172"/>
       <c r="D23" s="72"/>
-      <c r="E23" s="161"/>
+      <c r="E23" s="172"/>
       <c r="F23" s="72"/>
-      <c r="G23" s="167"/>
+      <c r="G23" s="160"/>
       <c r="H23" s="71"/>
       <c r="I23" s="72"/>
-      <c r="J23" s="167"/>
+      <c r="J23" s="160"/>
       <c r="K23" s="72"/>
       <c r="L23" s="164"/>
       <c r="M23" s="71"/>
@@ -18415,16 +18490,16 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="160"/>
+      <c r="A24" s="171"/>
       <c r="B24" s="72"/>
-      <c r="C24" s="161"/>
+      <c r="C24" s="172"/>
       <c r="D24" s="72"/>
-      <c r="E24" s="161"/>
+      <c r="E24" s="172"/>
       <c r="F24" s="72"/>
-      <c r="G24" s="167"/>
+      <c r="G24" s="160"/>
       <c r="H24" s="71"/>
       <c r="I24" s="72"/>
-      <c r="J24" s="167"/>
+      <c r="J24" s="160"/>
       <c r="K24" s="72"/>
       <c r="L24" s="164"/>
       <c r="M24" s="71"/>
@@ -18443,16 +18518,16 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="160"/>
+      <c r="A25" s="171"/>
       <c r="B25" s="72"/>
-      <c r="C25" s="161"/>
+      <c r="C25" s="172"/>
       <c r="D25" s="72"/>
-      <c r="E25" s="161"/>
+      <c r="E25" s="172"/>
       <c r="F25" s="72"/>
-      <c r="G25" s="167"/>
+      <c r="G25" s="160"/>
       <c r="H25" s="71"/>
       <c r="I25" s="72"/>
-      <c r="J25" s="167"/>
+      <c r="J25" s="160"/>
       <c r="K25" s="72"/>
       <c r="L25" s="164"/>
       <c r="M25" s="71"/>
@@ -18471,16 +18546,16 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="160"/>
+      <c r="A26" s="171"/>
       <c r="B26" s="72"/>
-      <c r="C26" s="161"/>
+      <c r="C26" s="172"/>
       <c r="D26" s="72"/>
-      <c r="E26" s="161"/>
+      <c r="E26" s="172"/>
       <c r="F26" s="72"/>
-      <c r="G26" s="167"/>
+      <c r="G26" s="160"/>
       <c r="H26" s="71"/>
       <c r="I26" s="72"/>
-      <c r="J26" s="167"/>
+      <c r="J26" s="160"/>
       <c r="K26" s="72"/>
       <c r="L26" s="164"/>
       <c r="M26" s="71"/>
@@ -18499,16 +18574,16 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="160"/>
+      <c r="A27" s="171"/>
       <c r="B27" s="72"/>
-      <c r="C27" s="161"/>
+      <c r="C27" s="172"/>
       <c r="D27" s="72"/>
-      <c r="E27" s="161"/>
+      <c r="E27" s="172"/>
       <c r="F27" s="72"/>
-      <c r="G27" s="167"/>
+      <c r="G27" s="160"/>
       <c r="H27" s="71"/>
       <c r="I27" s="72"/>
-      <c r="J27" s="167"/>
+      <c r="J27" s="160"/>
       <c r="K27" s="72"/>
       <c r="L27" s="164"/>
       <c r="M27" s="71"/>
@@ -18527,16 +18602,16 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="160"/>
+      <c r="A28" s="171"/>
       <c r="B28" s="72"/>
-      <c r="C28" s="161"/>
+      <c r="C28" s="172"/>
       <c r="D28" s="72"/>
-      <c r="E28" s="161"/>
+      <c r="E28" s="172"/>
       <c r="F28" s="72"/>
-      <c r="G28" s="167"/>
+      <c r="G28" s="160"/>
       <c r="H28" s="71"/>
       <c r="I28" s="72"/>
-      <c r="J28" s="167"/>
+      <c r="J28" s="160"/>
       <c r="K28" s="72"/>
       <c r="L28" s="164"/>
       <c r="M28" s="71"/>
@@ -18555,16 +18630,16 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="160"/>
+      <c r="A29" s="171"/>
       <c r="B29" s="72"/>
-      <c r="C29" s="161"/>
+      <c r="C29" s="172"/>
       <c r="D29" s="72"/>
-      <c r="E29" s="161"/>
+      <c r="E29" s="172"/>
       <c r="F29" s="72"/>
-      <c r="G29" s="167"/>
+      <c r="G29" s="160"/>
       <c r="H29" s="71"/>
       <c r="I29" s="72"/>
-      <c r="J29" s="167"/>
+      <c r="J29" s="160"/>
       <c r="K29" s="72"/>
       <c r="L29" s="164"/>
       <c r="M29" s="71"/>
@@ -18583,16 +18658,16 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="160"/>
+      <c r="A30" s="171"/>
       <c r="B30" s="72"/>
-      <c r="C30" s="161"/>
+      <c r="C30" s="172"/>
       <c r="D30" s="72"/>
-      <c r="E30" s="161"/>
+      <c r="E30" s="172"/>
       <c r="F30" s="72"/>
-      <c r="G30" s="167"/>
+      <c r="G30" s="160"/>
       <c r="H30" s="71"/>
       <c r="I30" s="72"/>
-      <c r="J30" s="167"/>
+      <c r="J30" s="160"/>
       <c r="K30" s="72"/>
       <c r="L30" s="164"/>
       <c r="M30" s="71"/>
@@ -18611,23 +18686,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="162"/>
-      <c r="B31" s="149"/>
-      <c r="C31" s="163"/>
-      <c r="D31" s="149"/>
-      <c r="E31" s="163"/>
-      <c r="F31" s="149"/>
-      <c r="G31" s="173"/>
-      <c r="H31" s="148"/>
-      <c r="I31" s="149"/>
-      <c r="J31" s="173"/>
-      <c r="K31" s="149"/>
+      <c r="A31" s="174"/>
+      <c r="B31" s="159"/>
+      <c r="C31" s="175"/>
+      <c r="D31" s="159"/>
+      <c r="E31" s="175"/>
+      <c r="F31" s="159"/>
+      <c r="G31" s="163"/>
+      <c r="H31" s="156"/>
+      <c r="I31" s="159"/>
+      <c r="J31" s="163"/>
+      <c r="K31" s="159"/>
       <c r="L31" s="165"/>
-      <c r="M31" s="148"/>
-      <c r="N31" s="149"/>
+      <c r="M31" s="156"/>
+      <c r="N31" s="159"/>
       <c r="O31" s="165"/>
-      <c r="P31" s="148"/>
-      <c r="Q31" s="149"/>
+      <c r="P31" s="156"/>
+      <c r="Q31" s="159"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -19625,62 +19700,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -19705,66 +19780,67 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
     <hyperlink ref="L18" r:id="rId1" display="http://localhost:8080/taskUN/task-delete.jsp" xr:uid="{38C81AFB-41F8-4093-85EB-71ACC0BAB2DD}"/>
+    <hyperlink ref="L20" r:id="rId2" xr:uid="{70E42B72-7AD1-4967-864C-156B0F97FF63}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -19786,70 +19862,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="193" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="186" t="s">
+      <c r="B1" s="193"/>
+      <c r="C1" s="194" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="187"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="189" t="s">
+      <c r="D1" s="195"/>
+      <c r="E1" s="196"/>
+      <c r="F1" s="197" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="190"/>
-      <c r="H1" s="190"/>
-      <c r="I1" s="190"/>
-      <c r="J1" s="190"/>
-      <c r="K1" s="190"/>
-      <c r="L1" s="190"/>
-      <c r="M1" s="191"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="199"/>
       <c r="N1" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="189" t="s">
+      <c r="O1" s="197" t="s">
         <v>94</v>
       </c>
-      <c r="P1" s="191"/>
+      <c r="P1" s="199"/>
       <c r="Q1" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="189" t="s">
+      <c r="R1" s="197" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="191"/>
+      <c r="S1" s="199"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="185"/>
-      <c r="B2" s="185"/>
-      <c r="C2" s="186" t="s">
+      <c r="A2" s="193"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="194" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="187"/>
-      <c r="E2" s="188"/>
-      <c r="F2" s="189" t="s">
+      <c r="D2" s="195"/>
+      <c r="E2" s="196"/>
+      <c r="F2" s="197" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
-      <c r="M2" s="191"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
+      <c r="L2" s="198"/>
+      <c r="M2" s="199"/>
       <c r="N2" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="O2" s="192">
+      <c r="O2" s="200">
         <v>45824</v>
       </c>
-      <c r="P2" s="193"/>
+      <c r="P2" s="201"/>
       <c r="Q2" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="R2" s="194"/>
-      <c r="S2" s="195"/>
+      <c r="R2" s="202"/>
+      <c r="S2" s="203"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="43"/>
@@ -19879,33 +19955,33 @@
       <c r="B4" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="176" t="s">
+      <c r="C4" s="188" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="177"/>
-      <c r="E4" s="177"/>
-      <c r="F4" s="177"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="176" t="s">
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="188" t="s">
         <v>119</v>
       </c>
-      <c r="I4" s="177"/>
-      <c r="J4" s="177"/>
-      <c r="K4" s="177"/>
-      <c r="L4" s="177"/>
-      <c r="M4" s="178"/>
-      <c r="N4" s="176" t="s">
+      <c r="I4" s="189"/>
+      <c r="J4" s="189"/>
+      <c r="K4" s="189"/>
+      <c r="L4" s="189"/>
+      <c r="M4" s="190"/>
+      <c r="N4" s="188" t="s">
         <v>120</v>
       </c>
-      <c r="O4" s="177"/>
-      <c r="P4" s="178"/>
+      <c r="O4" s="189"/>
+      <c r="P4" s="190"/>
       <c r="Q4" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="R4" s="176" t="s">
+      <c r="R4" s="188" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="178"/>
+      <c r="S4" s="190"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="47">
@@ -19914,29 +19990,29 @@
       <c r="B5" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="179" t="s">
+      <c r="C5" s="184" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="179"/>
-      <c r="E5" s="179"/>
-      <c r="F5" s="179"/>
-      <c r="G5" s="179"/>
-      <c r="H5" s="179" t="s">
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184" t="s">
         <v>135</v>
       </c>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
-      <c r="L5" s="179"/>
-      <c r="M5" s="179"/>
-      <c r="N5" s="180" t="s">
+      <c r="I5" s="184"/>
+      <c r="J5" s="184"/>
+      <c r="K5" s="184"/>
+      <c r="L5" s="184"/>
+      <c r="M5" s="184"/>
+      <c r="N5" s="185" t="s">
         <v>136</v>
       </c>
-      <c r="O5" s="181"/>
-      <c r="P5" s="182"/>
+      <c r="O5" s="186"/>
+      <c r="P5" s="187"/>
       <c r="Q5" s="47"/>
-      <c r="R5" s="183"/>
-      <c r="S5" s="184"/>
+      <c r="R5" s="191"/>
+      <c r="S5" s="192"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="49">
@@ -19945,1186 +20021,998 @@
       <c r="B6" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="179" t="s">
+      <c r="C6" s="184" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="179"/>
-      <c r="E6" s="179"/>
-      <c r="F6" s="179"/>
-      <c r="G6" s="179"/>
-      <c r="H6" s="179" t="s">
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="184" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="179"/>
-      <c r="J6" s="179"/>
-      <c r="K6" s="179"/>
-      <c r="L6" s="179"/>
-      <c r="M6" s="179"/>
-      <c r="N6" s="180" t="s">
+      <c r="I6" s="184"/>
+      <c r="J6" s="184"/>
+      <c r="K6" s="184"/>
+      <c r="L6" s="184"/>
+      <c r="M6" s="184"/>
+      <c r="N6" s="185" t="s">
         <v>137</v>
       </c>
-      <c r="O6" s="181"/>
-      <c r="P6" s="182"/>
+      <c r="O6" s="186"/>
+      <c r="P6" s="187"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="200"/>
-      <c r="S6" s="200"/>
+      <c r="R6" s="183"/>
+      <c r="S6" s="183"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="49"/>
       <c r="B7" s="49"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="196"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="196"/>
-      <c r="H7" s="196"/>
-      <c r="I7" s="196"/>
-      <c r="J7" s="196"/>
-      <c r="K7" s="196"/>
-      <c r="L7" s="196"/>
-      <c r="M7" s="196"/>
-      <c r="N7" s="197"/>
-      <c r="O7" s="198"/>
-      <c r="P7" s="199"/>
+      <c r="C7" s="176"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="176"/>
+      <c r="F7" s="176"/>
+      <c r="G7" s="176"/>
+      <c r="H7" s="176"/>
+      <c r="I7" s="176"/>
+      <c r="J7" s="176"/>
+      <c r="K7" s="176"/>
+      <c r="L7" s="176"/>
+      <c r="M7" s="176"/>
+      <c r="N7" s="180"/>
+      <c r="O7" s="181"/>
+      <c r="P7" s="182"/>
       <c r="Q7" s="51"/>
-      <c r="R7" s="200"/>
-      <c r="S7" s="200"/>
+      <c r="R7" s="183"/>
+      <c r="S7" s="183"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="49"/>
       <c r="B8" s="49"/>
-      <c r="C8" s="196"/>
-      <c r="D8" s="196"/>
-      <c r="E8" s="196"/>
-      <c r="F8" s="196"/>
-      <c r="G8" s="196"/>
-      <c r="H8" s="196"/>
-      <c r="I8" s="196"/>
-      <c r="J8" s="196"/>
-      <c r="K8" s="196"/>
-      <c r="L8" s="196"/>
-      <c r="M8" s="196"/>
-      <c r="N8" s="197"/>
-      <c r="O8" s="198"/>
-      <c r="P8" s="199"/>
+      <c r="C8" s="176"/>
+      <c r="D8" s="176"/>
+      <c r="E8" s="176"/>
+      <c r="F8" s="176"/>
+      <c r="G8" s="176"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="176"/>
+      <c r="K8" s="176"/>
+      <c r="L8" s="176"/>
+      <c r="M8" s="176"/>
+      <c r="N8" s="180"/>
+      <c r="O8" s="181"/>
+      <c r="P8" s="182"/>
       <c r="Q8" s="51"/>
-      <c r="R8" s="200"/>
-      <c r="S8" s="200"/>
+      <c r="R8" s="183"/>
+      <c r="S8" s="183"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="49"/>
       <c r="B9" s="49"/>
-      <c r="C9" s="196"/>
-      <c r="D9" s="196"/>
-      <c r="E9" s="196"/>
-      <c r="F9" s="196"/>
-      <c r="G9" s="196"/>
-      <c r="H9" s="196"/>
-      <c r="I9" s="196"/>
-      <c r="J9" s="196"/>
-      <c r="K9" s="196"/>
-      <c r="L9" s="196"/>
-      <c r="M9" s="196"/>
-      <c r="N9" s="197"/>
-      <c r="O9" s="198"/>
-      <c r="P9" s="199"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="176"/>
+      <c r="F9" s="176"/>
+      <c r="G9" s="176"/>
+      <c r="H9" s="176"/>
+      <c r="I9" s="176"/>
+      <c r="J9" s="176"/>
+      <c r="K9" s="176"/>
+      <c r="L9" s="176"/>
+      <c r="M9" s="176"/>
+      <c r="N9" s="180"/>
+      <c r="O9" s="181"/>
+      <c r="P9" s="182"/>
       <c r="Q9" s="49"/>
-      <c r="R9" s="200"/>
-      <c r="S9" s="200"/>
+      <c r="R9" s="183"/>
+      <c r="S9" s="183"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="49"/>
       <c r="B10" s="49"/>
-      <c r="C10" s="196"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="196"/>
-      <c r="F10" s="196"/>
-      <c r="G10" s="196"/>
-      <c r="H10" s="201"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
-      <c r="L10" s="202"/>
-      <c r="M10" s="203"/>
-      <c r="N10" s="197"/>
-      <c r="O10" s="198"/>
-      <c r="P10" s="199"/>
+      <c r="C10" s="176"/>
+      <c r="D10" s="176"/>
+      <c r="E10" s="176"/>
+      <c r="F10" s="176"/>
+      <c r="G10" s="176"/>
+      <c r="H10" s="177"/>
+      <c r="I10" s="178"/>
+      <c r="J10" s="178"/>
+      <c r="K10" s="178"/>
+      <c r="L10" s="178"/>
+      <c r="M10" s="179"/>
+      <c r="N10" s="180"/>
+      <c r="O10" s="181"/>
+      <c r="P10" s="182"/>
       <c r="Q10" s="51"/>
-      <c r="R10" s="200"/>
-      <c r="S10" s="200"/>
+      <c r="R10" s="183"/>
+      <c r="S10" s="183"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="49"/>
       <c r="B11" s="49"/>
-      <c r="C11" s="196"/>
-      <c r="D11" s="196"/>
-      <c r="E11" s="196"/>
-      <c r="F11" s="196"/>
-      <c r="G11" s="196"/>
-      <c r="H11" s="201"/>
-      <c r="I11" s="202"/>
-      <c r="J11" s="202"/>
-      <c r="K11" s="202"/>
-      <c r="L11" s="202"/>
-      <c r="M11" s="203"/>
-      <c r="N11" s="197"/>
-      <c r="O11" s="198"/>
-      <c r="P11" s="199"/>
+      <c r="C11" s="176"/>
+      <c r="D11" s="176"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="177"/>
+      <c r="I11" s="178"/>
+      <c r="J11" s="178"/>
+      <c r="K11" s="178"/>
+      <c r="L11" s="178"/>
+      <c r="M11" s="179"/>
+      <c r="N11" s="180"/>
+      <c r="O11" s="181"/>
+      <c r="P11" s="182"/>
       <c r="Q11" s="49"/>
-      <c r="R11" s="200"/>
-      <c r="S11" s="200"/>
+      <c r="R11" s="183"/>
+      <c r="S11" s="183"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="49"/>
       <c r="B12" s="49"/>
-      <c r="C12" s="196"/>
-      <c r="D12" s="196"/>
-      <c r="E12" s="196"/>
-      <c r="F12" s="196"/>
-      <c r="G12" s="196"/>
-      <c r="H12" s="201"/>
-      <c r="I12" s="202"/>
-      <c r="J12" s="202"/>
-      <c r="K12" s="202"/>
-      <c r="L12" s="202"/>
-      <c r="M12" s="203"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="198"/>
-      <c r="P12" s="199"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="176"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="177"/>
+      <c r="I12" s="178"/>
+      <c r="J12" s="178"/>
+      <c r="K12" s="178"/>
+      <c r="L12" s="178"/>
+      <c r="M12" s="179"/>
+      <c r="N12" s="180"/>
+      <c r="O12" s="181"/>
+      <c r="P12" s="182"/>
       <c r="Q12" s="49"/>
-      <c r="R12" s="200"/>
-      <c r="S12" s="200"/>
+      <c r="R12" s="183"/>
+      <c r="S12" s="183"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="49"/>
       <c r="B13" s="49"/>
-      <c r="C13" s="196"/>
-      <c r="D13" s="196"/>
-      <c r="E13" s="196"/>
-      <c r="F13" s="196"/>
-      <c r="G13" s="196"/>
-      <c r="H13" s="201"/>
-      <c r="I13" s="202"/>
-      <c r="J13" s="202"/>
-      <c r="K13" s="202"/>
-      <c r="L13" s="202"/>
-      <c r="M13" s="203"/>
-      <c r="N13" s="197"/>
-      <c r="O13" s="198"/>
-      <c r="P13" s="199"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="176"/>
+      <c r="H13" s="177"/>
+      <c r="I13" s="178"/>
+      <c r="J13" s="178"/>
+      <c r="K13" s="178"/>
+      <c r="L13" s="178"/>
+      <c r="M13" s="179"/>
+      <c r="N13" s="180"/>
+      <c r="O13" s="181"/>
+      <c r="P13" s="182"/>
       <c r="Q13" s="49"/>
-      <c r="R13" s="200"/>
-      <c r="S13" s="200"/>
+      <c r="R13" s="183"/>
+      <c r="S13" s="183"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="49"/>
       <c r="B14" s="49"/>
-      <c r="C14" s="196"/>
-      <c r="D14" s="196"/>
-      <c r="E14" s="196"/>
-      <c r="F14" s="196"/>
-      <c r="G14" s="196"/>
-      <c r="H14" s="201"/>
-      <c r="I14" s="202"/>
-      <c r="J14" s="202"/>
-      <c r="K14" s="202"/>
-      <c r="L14" s="202"/>
-      <c r="M14" s="203"/>
-      <c r="N14" s="197"/>
-      <c r="O14" s="198"/>
-      <c r="P14" s="199"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="176"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="176"/>
+      <c r="G14" s="176"/>
+      <c r="H14" s="177"/>
+      <c r="I14" s="178"/>
+      <c r="J14" s="178"/>
+      <c r="K14" s="178"/>
+      <c r="L14" s="178"/>
+      <c r="M14" s="179"/>
+      <c r="N14" s="180"/>
+      <c r="O14" s="181"/>
+      <c r="P14" s="182"/>
       <c r="Q14" s="49"/>
-      <c r="R14" s="200"/>
-      <c r="S14" s="200"/>
+      <c r="R14" s="183"/>
+      <c r="S14" s="183"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="49"/>
       <c r="B15" s="49"/>
-      <c r="C15" s="196"/>
-      <c r="D15" s="196"/>
-      <c r="E15" s="196"/>
-      <c r="F15" s="196"/>
-      <c r="G15" s="196"/>
-      <c r="H15" s="201"/>
-      <c r="I15" s="202"/>
-      <c r="J15" s="202"/>
-      <c r="K15" s="202"/>
-      <c r="L15" s="202"/>
-      <c r="M15" s="203"/>
-      <c r="N15" s="197"/>
-      <c r="O15" s="198"/>
-      <c r="P15" s="199"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="176"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
+      <c r="G15" s="176"/>
+      <c r="H15" s="177"/>
+      <c r="I15" s="178"/>
+      <c r="J15" s="178"/>
+      <c r="K15" s="178"/>
+      <c r="L15" s="178"/>
+      <c r="M15" s="179"/>
+      <c r="N15" s="180"/>
+      <c r="O15" s="181"/>
+      <c r="P15" s="182"/>
       <c r="Q15" s="49"/>
-      <c r="R15" s="200"/>
-      <c r="S15" s="200"/>
+      <c r="R15" s="183"/>
+      <c r="S15" s="183"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="49"/>
       <c r="B16" s="49"/>
-      <c r="C16" s="196"/>
-      <c r="D16" s="196"/>
-      <c r="E16" s="196"/>
-      <c r="F16" s="196"/>
-      <c r="G16" s="196"/>
-      <c r="H16" s="201"/>
-      <c r="I16" s="202"/>
-      <c r="J16" s="202"/>
-      <c r="K16" s="202"/>
-      <c r="L16" s="202"/>
-      <c r="M16" s="203"/>
-      <c r="N16" s="197"/>
-      <c r="O16" s="198"/>
-      <c r="P16" s="199"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="176"/>
+      <c r="E16" s="176"/>
+      <c r="F16" s="176"/>
+      <c r="G16" s="176"/>
+      <c r="H16" s="177"/>
+      <c r="I16" s="178"/>
+      <c r="J16" s="178"/>
+      <c r="K16" s="178"/>
+      <c r="L16" s="178"/>
+      <c r="M16" s="179"/>
+      <c r="N16" s="180"/>
+      <c r="O16" s="181"/>
+      <c r="P16" s="182"/>
       <c r="Q16" s="49"/>
-      <c r="R16" s="200"/>
-      <c r="S16" s="200"/>
+      <c r="R16" s="183"/>
+      <c r="S16" s="183"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="49"/>
       <c r="B17" s="49"/>
-      <c r="C17" s="196"/>
-      <c r="D17" s="196"/>
-      <c r="E17" s="196"/>
-      <c r="F17" s="196"/>
-      <c r="G17" s="196"/>
-      <c r="H17" s="201"/>
-      <c r="I17" s="202"/>
-      <c r="J17" s="202"/>
-      <c r="K17" s="202"/>
-      <c r="L17" s="202"/>
-      <c r="M17" s="203"/>
-      <c r="N17" s="197"/>
-      <c r="O17" s="198"/>
-      <c r="P17" s="199"/>
+      <c r="C17" s="176"/>
+      <c r="D17" s="176"/>
+      <c r="E17" s="176"/>
+      <c r="F17" s="176"/>
+      <c r="G17" s="176"/>
+      <c r="H17" s="177"/>
+      <c r="I17" s="178"/>
+      <c r="J17" s="178"/>
+      <c r="K17" s="178"/>
+      <c r="L17" s="178"/>
+      <c r="M17" s="179"/>
+      <c r="N17" s="180"/>
+      <c r="O17" s="181"/>
+      <c r="P17" s="182"/>
       <c r="Q17" s="49"/>
-      <c r="R17" s="200"/>
-      <c r="S17" s="200"/>
+      <c r="R17" s="183"/>
+      <c r="S17" s="183"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="49"/>
       <c r="B18" s="49"/>
-      <c r="C18" s="196"/>
-      <c r="D18" s="196"/>
-      <c r="E18" s="196"/>
-      <c r="F18" s="196"/>
-      <c r="G18" s="196"/>
-      <c r="H18" s="201"/>
-      <c r="I18" s="202"/>
-      <c r="J18" s="202"/>
-      <c r="K18" s="202"/>
-      <c r="L18" s="202"/>
-      <c r="M18" s="203"/>
-      <c r="N18" s="197"/>
-      <c r="O18" s="198"/>
-      <c r="P18" s="199"/>
+      <c r="C18" s="176"/>
+      <c r="D18" s="176"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="176"/>
+      <c r="G18" s="176"/>
+      <c r="H18" s="177"/>
+      <c r="I18" s="178"/>
+      <c r="J18" s="178"/>
+      <c r="K18" s="178"/>
+      <c r="L18" s="178"/>
+      <c r="M18" s="179"/>
+      <c r="N18" s="180"/>
+      <c r="O18" s="181"/>
+      <c r="P18" s="182"/>
       <c r="Q18" s="49"/>
-      <c r="R18" s="200"/>
-      <c r="S18" s="200"/>
+      <c r="R18" s="183"/>
+      <c r="S18" s="183"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="49"/>
       <c r="B19" s="49"/>
-      <c r="C19" s="196"/>
-      <c r="D19" s="196"/>
-      <c r="E19" s="196"/>
-      <c r="F19" s="196"/>
-      <c r="G19" s="196"/>
-      <c r="H19" s="201"/>
-      <c r="I19" s="202"/>
-      <c r="J19" s="202"/>
-      <c r="K19" s="202"/>
-      <c r="L19" s="202"/>
-      <c r="M19" s="203"/>
-      <c r="N19" s="197"/>
-      <c r="O19" s="198"/>
-      <c r="P19" s="199"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="176"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="176"/>
+      <c r="G19" s="176"/>
+      <c r="H19" s="177"/>
+      <c r="I19" s="178"/>
+      <c r="J19" s="178"/>
+      <c r="K19" s="178"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="179"/>
+      <c r="N19" s="180"/>
+      <c r="O19" s="181"/>
+      <c r="P19" s="182"/>
       <c r="Q19" s="49"/>
-      <c r="R19" s="200"/>
-      <c r="S19" s="200"/>
+      <c r="R19" s="183"/>
+      <c r="S19" s="183"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="49"/>
       <c r="B20" s="49"/>
-      <c r="C20" s="196"/>
-      <c r="D20" s="196"/>
-      <c r="E20" s="196"/>
-      <c r="F20" s="196"/>
-      <c r="G20" s="196"/>
-      <c r="H20" s="201"/>
-      <c r="I20" s="202"/>
-      <c r="J20" s="202"/>
-      <c r="K20" s="202"/>
-      <c r="L20" s="202"/>
-      <c r="M20" s="203"/>
-      <c r="N20" s="197"/>
-      <c r="O20" s="198"/>
-      <c r="P20" s="199"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="176"/>
+      <c r="E20" s="176"/>
+      <c r="F20" s="176"/>
+      <c r="G20" s="176"/>
+      <c r="H20" s="177"/>
+      <c r="I20" s="178"/>
+      <c r="J20" s="178"/>
+      <c r="K20" s="178"/>
+      <c r="L20" s="178"/>
+      <c r="M20" s="179"/>
+      <c r="N20" s="180"/>
+      <c r="O20" s="181"/>
+      <c r="P20" s="182"/>
       <c r="Q20" s="49"/>
-      <c r="R20" s="200"/>
-      <c r="S20" s="200"/>
+      <c r="R20" s="183"/>
+      <c r="S20" s="183"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="49"/>
       <c r="B21" s="49"/>
-      <c r="C21" s="196"/>
-      <c r="D21" s="196"/>
-      <c r="E21" s="196"/>
-      <c r="F21" s="196"/>
-      <c r="G21" s="196"/>
-      <c r="H21" s="201"/>
-      <c r="I21" s="202"/>
-      <c r="J21" s="202"/>
-      <c r="K21" s="202"/>
-      <c r="L21" s="202"/>
-      <c r="M21" s="203"/>
-      <c r="N21" s="197"/>
-      <c r="O21" s="198"/>
-      <c r="P21" s="199"/>
+      <c r="C21" s="176"/>
+      <c r="D21" s="176"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="176"/>
+      <c r="G21" s="176"/>
+      <c r="H21" s="177"/>
+      <c r="I21" s="178"/>
+      <c r="J21" s="178"/>
+      <c r="K21" s="178"/>
+      <c r="L21" s="178"/>
+      <c r="M21" s="179"/>
+      <c r="N21" s="180"/>
+      <c r="O21" s="181"/>
+      <c r="P21" s="182"/>
       <c r="Q21" s="49"/>
-      <c r="R21" s="200"/>
-      <c r="S21" s="200"/>
+      <c r="R21" s="183"/>
+      <c r="S21" s="183"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="49"/>
       <c r="B22" s="49"/>
-      <c r="C22" s="196"/>
-      <c r="D22" s="196"/>
-      <c r="E22" s="196"/>
-      <c r="F22" s="196"/>
-      <c r="G22" s="196"/>
-      <c r="H22" s="201"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="202"/>
-      <c r="K22" s="202"/>
-      <c r="L22" s="202"/>
-      <c r="M22" s="203"/>
-      <c r="N22" s="197"/>
-      <c r="O22" s="198"/>
-      <c r="P22" s="199"/>
+      <c r="C22" s="176"/>
+      <c r="D22" s="176"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="176"/>
+      <c r="G22" s="176"/>
+      <c r="H22" s="177"/>
+      <c r="I22" s="178"/>
+      <c r="J22" s="178"/>
+      <c r="K22" s="178"/>
+      <c r="L22" s="178"/>
+      <c r="M22" s="179"/>
+      <c r="N22" s="180"/>
+      <c r="O22" s="181"/>
+      <c r="P22" s="182"/>
       <c r="Q22" s="49"/>
-      <c r="R22" s="200"/>
-      <c r="S22" s="200"/>
+      <c r="R22" s="183"/>
+      <c r="S22" s="183"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="49"/>
       <c r="B23" s="49"/>
-      <c r="C23" s="196"/>
-      <c r="D23" s="196"/>
-      <c r="E23" s="196"/>
-      <c r="F23" s="196"/>
-      <c r="G23" s="196"/>
-      <c r="H23" s="201"/>
-      <c r="I23" s="202"/>
-      <c r="J23" s="202"/>
-      <c r="K23" s="202"/>
-      <c r="L23" s="202"/>
-      <c r="M23" s="203"/>
-      <c r="N23" s="197"/>
-      <c r="O23" s="198"/>
-      <c r="P23" s="199"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="176"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="176"/>
+      <c r="G23" s="176"/>
+      <c r="H23" s="177"/>
+      <c r="I23" s="178"/>
+      <c r="J23" s="178"/>
+      <c r="K23" s="178"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="179"/>
+      <c r="N23" s="180"/>
+      <c r="O23" s="181"/>
+      <c r="P23" s="182"/>
       <c r="Q23" s="49"/>
-      <c r="R23" s="200"/>
-      <c r="S23" s="200"/>
+      <c r="R23" s="183"/>
+      <c r="S23" s="183"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="49"/>
       <c r="B24" s="49"/>
-      <c r="C24" s="196"/>
-      <c r="D24" s="196"/>
-      <c r="E24" s="196"/>
-      <c r="F24" s="196"/>
-      <c r="G24" s="196"/>
-      <c r="H24" s="201"/>
-      <c r="I24" s="202"/>
-      <c r="J24" s="202"/>
-      <c r="K24" s="202"/>
-      <c r="L24" s="202"/>
-      <c r="M24" s="203"/>
-      <c r="N24" s="197"/>
-      <c r="O24" s="198"/>
-      <c r="P24" s="199"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="176"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="176"/>
+      <c r="G24" s="176"/>
+      <c r="H24" s="177"/>
+      <c r="I24" s="178"/>
+      <c r="J24" s="178"/>
+      <c r="K24" s="178"/>
+      <c r="L24" s="178"/>
+      <c r="M24" s="179"/>
+      <c r="N24" s="180"/>
+      <c r="O24" s="181"/>
+      <c r="P24" s="182"/>
       <c r="Q24" s="49"/>
-      <c r="R24" s="200"/>
-      <c r="S24" s="200"/>
+      <c r="R24" s="183"/>
+      <c r="S24" s="183"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="49"/>
       <c r="B25" s="49"/>
-      <c r="C25" s="196"/>
-      <c r="D25" s="196"/>
-      <c r="E25" s="196"/>
-      <c r="F25" s="196"/>
-      <c r="G25" s="196"/>
-      <c r="H25" s="201"/>
-      <c r="I25" s="202"/>
-      <c r="J25" s="202"/>
-      <c r="K25" s="202"/>
-      <c r="L25" s="202"/>
-      <c r="M25" s="203"/>
-      <c r="N25" s="197"/>
-      <c r="O25" s="198"/>
-      <c r="P25" s="199"/>
+      <c r="C25" s="176"/>
+      <c r="D25" s="176"/>
+      <c r="E25" s="176"/>
+      <c r="F25" s="176"/>
+      <c r="G25" s="176"/>
+      <c r="H25" s="177"/>
+      <c r="I25" s="178"/>
+      <c r="J25" s="178"/>
+      <c r="K25" s="178"/>
+      <c r="L25" s="178"/>
+      <c r="M25" s="179"/>
+      <c r="N25" s="180"/>
+      <c r="O25" s="181"/>
+      <c r="P25" s="182"/>
       <c r="Q25" s="49"/>
-      <c r="R25" s="200"/>
-      <c r="S25" s="200"/>
+      <c r="R25" s="183"/>
+      <c r="S25" s="183"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="49"/>
       <c r="B26" s="49"/>
-      <c r="C26" s="196"/>
-      <c r="D26" s="196"/>
-      <c r="E26" s="196"/>
-      <c r="F26" s="196"/>
-      <c r="G26" s="196"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="202"/>
-      <c r="J26" s="202"/>
-      <c r="K26" s="202"/>
-      <c r="L26" s="202"/>
-      <c r="M26" s="203"/>
-      <c r="N26" s="197"/>
-      <c r="O26" s="198"/>
-      <c r="P26" s="199"/>
+      <c r="C26" s="176"/>
+      <c r="D26" s="176"/>
+      <c r="E26" s="176"/>
+      <c r="F26" s="176"/>
+      <c r="G26" s="176"/>
+      <c r="H26" s="177"/>
+      <c r="I26" s="178"/>
+      <c r="J26" s="178"/>
+      <c r="K26" s="178"/>
+      <c r="L26" s="178"/>
+      <c r="M26" s="179"/>
+      <c r="N26" s="180"/>
+      <c r="O26" s="181"/>
+      <c r="P26" s="182"/>
       <c r="Q26" s="49"/>
-      <c r="R26" s="200"/>
-      <c r="S26" s="200"/>
+      <c r="R26" s="183"/>
+      <c r="S26" s="183"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="49"/>
       <c r="B27" s="49"/>
-      <c r="C27" s="196"/>
-      <c r="D27" s="196"/>
-      <c r="E27" s="196"/>
-      <c r="F27" s="196"/>
-      <c r="G27" s="196"/>
-      <c r="H27" s="201"/>
-      <c r="I27" s="202"/>
-      <c r="J27" s="202"/>
-      <c r="K27" s="202"/>
-      <c r="L27" s="202"/>
-      <c r="M27" s="203"/>
-      <c r="N27" s="197"/>
-      <c r="O27" s="198"/>
-      <c r="P27" s="199"/>
+      <c r="C27" s="176"/>
+      <c r="D27" s="176"/>
+      <c r="E27" s="176"/>
+      <c r="F27" s="176"/>
+      <c r="G27" s="176"/>
+      <c r="H27" s="177"/>
+      <c r="I27" s="178"/>
+      <c r="J27" s="178"/>
+      <c r="K27" s="178"/>
+      <c r="L27" s="178"/>
+      <c r="M27" s="179"/>
+      <c r="N27" s="180"/>
+      <c r="O27" s="181"/>
+      <c r="P27" s="182"/>
       <c r="Q27" s="49"/>
-      <c r="R27" s="200"/>
-      <c r="S27" s="200"/>
+      <c r="R27" s="183"/>
+      <c r="S27" s="183"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="49"/>
       <c r="B28" s="49"/>
-      <c r="C28" s="196"/>
-      <c r="D28" s="196"/>
-      <c r="E28" s="196"/>
-      <c r="F28" s="196"/>
-      <c r="G28" s="196"/>
-      <c r="H28" s="201"/>
-      <c r="I28" s="202"/>
-      <c r="J28" s="202"/>
-      <c r="K28" s="202"/>
-      <c r="L28" s="202"/>
-      <c r="M28" s="203"/>
-      <c r="N28" s="197"/>
-      <c r="O28" s="198"/>
-      <c r="P28" s="199"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="176"/>
+      <c r="E28" s="176"/>
+      <c r="F28" s="176"/>
+      <c r="G28" s="176"/>
+      <c r="H28" s="177"/>
+      <c r="I28" s="178"/>
+      <c r="J28" s="178"/>
+      <c r="K28" s="178"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="179"/>
+      <c r="N28" s="180"/>
+      <c r="O28" s="181"/>
+      <c r="P28" s="182"/>
       <c r="Q28" s="49"/>
-      <c r="R28" s="200"/>
-      <c r="S28" s="200"/>
+      <c r="R28" s="183"/>
+      <c r="S28" s="183"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="49"/>
       <c r="B29" s="49"/>
-      <c r="C29" s="196"/>
-      <c r="D29" s="196"/>
-      <c r="E29" s="196"/>
-      <c r="F29" s="196"/>
-      <c r="G29" s="196"/>
-      <c r="H29" s="201"/>
-      <c r="I29" s="202"/>
-      <c r="J29" s="202"/>
-      <c r="K29" s="202"/>
-      <c r="L29" s="202"/>
-      <c r="M29" s="203"/>
-      <c r="N29" s="197"/>
-      <c r="O29" s="198"/>
-      <c r="P29" s="199"/>
+      <c r="C29" s="176"/>
+      <c r="D29" s="176"/>
+      <c r="E29" s="176"/>
+      <c r="F29" s="176"/>
+      <c r="G29" s="176"/>
+      <c r="H29" s="177"/>
+      <c r="I29" s="178"/>
+      <c r="J29" s="178"/>
+      <c r="K29" s="178"/>
+      <c r="L29" s="178"/>
+      <c r="M29" s="179"/>
+      <c r="N29" s="180"/>
+      <c r="O29" s="181"/>
+      <c r="P29" s="182"/>
       <c r="Q29" s="49"/>
-      <c r="R29" s="200"/>
-      <c r="S29" s="200"/>
+      <c r="R29" s="183"/>
+      <c r="S29" s="183"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="49"/>
       <c r="B30" s="49"/>
-      <c r="C30" s="196"/>
-      <c r="D30" s="196"/>
-      <c r="E30" s="196"/>
-      <c r="F30" s="196"/>
-      <c r="G30" s="196"/>
-      <c r="H30" s="201"/>
-      <c r="I30" s="202"/>
-      <c r="J30" s="202"/>
-      <c r="K30" s="202"/>
-      <c r="L30" s="202"/>
-      <c r="M30" s="203"/>
-      <c r="N30" s="197"/>
-      <c r="O30" s="198"/>
-      <c r="P30" s="199"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="176"/>
+      <c r="E30" s="176"/>
+      <c r="F30" s="176"/>
+      <c r="G30" s="176"/>
+      <c r="H30" s="177"/>
+      <c r="I30" s="178"/>
+      <c r="J30" s="178"/>
+      <c r="K30" s="178"/>
+      <c r="L30" s="178"/>
+      <c r="M30" s="179"/>
+      <c r="N30" s="180"/>
+      <c r="O30" s="181"/>
+      <c r="P30" s="182"/>
       <c r="Q30" s="49"/>
-      <c r="R30" s="200"/>
-      <c r="S30" s="200"/>
+      <c r="R30" s="183"/>
+      <c r="S30" s="183"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="49"/>
       <c r="B31" s="49"/>
-      <c r="C31" s="196"/>
-      <c r="D31" s="196"/>
-      <c r="E31" s="196"/>
-      <c r="F31" s="196"/>
-      <c r="G31" s="196"/>
-      <c r="H31" s="201"/>
-      <c r="I31" s="202"/>
-      <c r="J31" s="202"/>
-      <c r="K31" s="202"/>
-      <c r="L31" s="202"/>
-      <c r="M31" s="203"/>
-      <c r="N31" s="197"/>
-      <c r="O31" s="198"/>
-      <c r="P31" s="199"/>
+      <c r="C31" s="176"/>
+      <c r="D31" s="176"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="176"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="177"/>
+      <c r="I31" s="178"/>
+      <c r="J31" s="178"/>
+      <c r="K31" s="178"/>
+      <c r="L31" s="178"/>
+      <c r="M31" s="179"/>
+      <c r="N31" s="180"/>
+      <c r="O31" s="181"/>
+      <c r="P31" s="182"/>
       <c r="Q31" s="49"/>
-      <c r="R31" s="200"/>
-      <c r="S31" s="200"/>
+      <c r="R31" s="183"/>
+      <c r="S31" s="183"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="49"/>
       <c r="B32" s="49"/>
-      <c r="C32" s="196"/>
-      <c r="D32" s="196"/>
-      <c r="E32" s="196"/>
-      <c r="F32" s="196"/>
-      <c r="G32" s="196"/>
-      <c r="H32" s="201"/>
-      <c r="I32" s="202"/>
-      <c r="J32" s="202"/>
-      <c r="K32" s="202"/>
-      <c r="L32" s="202"/>
-      <c r="M32" s="203"/>
-      <c r="N32" s="197"/>
-      <c r="O32" s="198"/>
-      <c r="P32" s="199"/>
+      <c r="C32" s="176"/>
+      <c r="D32" s="176"/>
+      <c r="E32" s="176"/>
+      <c r="F32" s="176"/>
+      <c r="G32" s="176"/>
+      <c r="H32" s="177"/>
+      <c r="I32" s="178"/>
+      <c r="J32" s="178"/>
+      <c r="K32" s="178"/>
+      <c r="L32" s="178"/>
+      <c r="M32" s="179"/>
+      <c r="N32" s="180"/>
+      <c r="O32" s="181"/>
+      <c r="P32" s="182"/>
       <c r="Q32" s="49"/>
-      <c r="R32" s="200"/>
-      <c r="S32" s="200"/>
+      <c r="R32" s="183"/>
+      <c r="S32" s="183"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="49"/>
       <c r="B33" s="49"/>
-      <c r="C33" s="196"/>
-      <c r="D33" s="196"/>
-      <c r="E33" s="196"/>
-      <c r="F33" s="196"/>
-      <c r="G33" s="196"/>
-      <c r="H33" s="201"/>
-      <c r="I33" s="202"/>
-      <c r="J33" s="202"/>
-      <c r="K33" s="202"/>
-      <c r="L33" s="202"/>
-      <c r="M33" s="203"/>
-      <c r="N33" s="197"/>
-      <c r="O33" s="198"/>
-      <c r="P33" s="199"/>
+      <c r="C33" s="176"/>
+      <c r="D33" s="176"/>
+      <c r="E33" s="176"/>
+      <c r="F33" s="176"/>
+      <c r="G33" s="176"/>
+      <c r="H33" s="177"/>
+      <c r="I33" s="178"/>
+      <c r="J33" s="178"/>
+      <c r="K33" s="178"/>
+      <c r="L33" s="178"/>
+      <c r="M33" s="179"/>
+      <c r="N33" s="180"/>
+      <c r="O33" s="181"/>
+      <c r="P33" s="182"/>
       <c r="Q33" s="49"/>
-      <c r="R33" s="200"/>
-      <c r="S33" s="200"/>
+      <c r="R33" s="183"/>
+      <c r="S33" s="183"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="49"/>
       <c r="B34" s="49"/>
-      <c r="C34" s="196"/>
-      <c r="D34" s="196"/>
-      <c r="E34" s="196"/>
-      <c r="F34" s="196"/>
-      <c r="G34" s="196"/>
-      <c r="H34" s="201"/>
-      <c r="I34" s="202"/>
-      <c r="J34" s="202"/>
-      <c r="K34" s="202"/>
-      <c r="L34" s="202"/>
-      <c r="M34" s="203"/>
-      <c r="N34" s="197"/>
-      <c r="O34" s="198"/>
-      <c r="P34" s="199"/>
+      <c r="C34" s="176"/>
+      <c r="D34" s="176"/>
+      <c r="E34" s="176"/>
+      <c r="F34" s="176"/>
+      <c r="G34" s="176"/>
+      <c r="H34" s="177"/>
+      <c r="I34" s="178"/>
+      <c r="J34" s="178"/>
+      <c r="K34" s="178"/>
+      <c r="L34" s="178"/>
+      <c r="M34" s="179"/>
+      <c r="N34" s="180"/>
+      <c r="O34" s="181"/>
+      <c r="P34" s="182"/>
       <c r="Q34" s="49"/>
-      <c r="R34" s="200"/>
-      <c r="S34" s="200"/>
+      <c r="R34" s="183"/>
+      <c r="S34" s="183"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
-      <c r="C35" s="196"/>
-      <c r="D35" s="196"/>
-      <c r="E35" s="196"/>
-      <c r="F35" s="196"/>
-      <c r="G35" s="196"/>
-      <c r="H35" s="201"/>
-      <c r="I35" s="202"/>
-      <c r="J35" s="202"/>
-      <c r="K35" s="202"/>
-      <c r="L35" s="202"/>
-      <c r="M35" s="203"/>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="199"/>
+      <c r="C35" s="176"/>
+      <c r="D35" s="176"/>
+      <c r="E35" s="176"/>
+      <c r="F35" s="176"/>
+      <c r="G35" s="176"/>
+      <c r="H35" s="177"/>
+      <c r="I35" s="178"/>
+      <c r="J35" s="178"/>
+      <c r="K35" s="178"/>
+      <c r="L35" s="178"/>
+      <c r="M35" s="179"/>
+      <c r="N35" s="180"/>
+      <c r="O35" s="181"/>
+      <c r="P35" s="182"/>
       <c r="Q35" s="49"/>
-      <c r="R35" s="200"/>
-      <c r="S35" s="200"/>
+      <c r="R35" s="183"/>
+      <c r="S35" s="183"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="49"/>
       <c r="B36" s="49"/>
-      <c r="C36" s="196"/>
-      <c r="D36" s="196"/>
-      <c r="E36" s="196"/>
-      <c r="F36" s="196"/>
-      <c r="G36" s="196"/>
-      <c r="H36" s="201"/>
-      <c r="I36" s="202"/>
-      <c r="J36" s="202"/>
-      <c r="K36" s="202"/>
-      <c r="L36" s="202"/>
-      <c r="M36" s="203"/>
-      <c r="N36" s="197"/>
-      <c r="O36" s="198"/>
-      <c r="P36" s="199"/>
+      <c r="C36" s="176"/>
+      <c r="D36" s="176"/>
+      <c r="E36" s="176"/>
+      <c r="F36" s="176"/>
+      <c r="G36" s="176"/>
+      <c r="H36" s="177"/>
+      <c r="I36" s="178"/>
+      <c r="J36" s="178"/>
+      <c r="K36" s="178"/>
+      <c r="L36" s="178"/>
+      <c r="M36" s="179"/>
+      <c r="N36" s="180"/>
+      <c r="O36" s="181"/>
+      <c r="P36" s="182"/>
       <c r="Q36" s="49"/>
-      <c r="R36" s="200"/>
-      <c r="S36" s="200"/>
+      <c r="R36" s="183"/>
+      <c r="S36" s="183"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="49"/>
       <c r="B37" s="49"/>
-      <c r="C37" s="196"/>
-      <c r="D37" s="196"/>
-      <c r="E37" s="196"/>
-      <c r="F37" s="196"/>
-      <c r="G37" s="196"/>
-      <c r="H37" s="201"/>
-      <c r="I37" s="202"/>
-      <c r="J37" s="202"/>
-      <c r="K37" s="202"/>
-      <c r="L37" s="202"/>
-      <c r="M37" s="203"/>
-      <c r="N37" s="197"/>
-      <c r="O37" s="198"/>
-      <c r="P37" s="199"/>
+      <c r="C37" s="176"/>
+      <c r="D37" s="176"/>
+      <c r="E37" s="176"/>
+      <c r="F37" s="176"/>
+      <c r="G37" s="176"/>
+      <c r="H37" s="177"/>
+      <c r="I37" s="178"/>
+      <c r="J37" s="178"/>
+      <c r="K37" s="178"/>
+      <c r="L37" s="178"/>
+      <c r="M37" s="179"/>
+      <c r="N37" s="180"/>
+      <c r="O37" s="181"/>
+      <c r="P37" s="182"/>
       <c r="Q37" s="49"/>
-      <c r="R37" s="200"/>
-      <c r="S37" s="200"/>
+      <c r="R37" s="183"/>
+      <c r="S37" s="183"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="49"/>
       <c r="B38" s="49"/>
-      <c r="C38" s="196"/>
-      <c r="D38" s="196"/>
-      <c r="E38" s="196"/>
-      <c r="F38" s="196"/>
-      <c r="G38" s="196"/>
-      <c r="H38" s="201"/>
-      <c r="I38" s="202"/>
-      <c r="J38" s="202"/>
-      <c r="K38" s="202"/>
-      <c r="L38" s="202"/>
-      <c r="M38" s="203"/>
-      <c r="N38" s="197"/>
-      <c r="O38" s="198"/>
-      <c r="P38" s="199"/>
+      <c r="C38" s="176"/>
+      <c r="D38" s="176"/>
+      <c r="E38" s="176"/>
+      <c r="F38" s="176"/>
+      <c r="G38" s="176"/>
+      <c r="H38" s="177"/>
+      <c r="I38" s="178"/>
+      <c r="J38" s="178"/>
+      <c r="K38" s="178"/>
+      <c r="L38" s="178"/>
+      <c r="M38" s="179"/>
+      <c r="N38" s="180"/>
+      <c r="O38" s="181"/>
+      <c r="P38" s="182"/>
       <c r="Q38" s="49"/>
-      <c r="R38" s="200"/>
-      <c r="S38" s="200"/>
+      <c r="R38" s="183"/>
+      <c r="S38" s="183"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="49"/>
       <c r="B39" s="49"/>
-      <c r="C39" s="196"/>
-      <c r="D39" s="196"/>
-      <c r="E39" s="196"/>
-      <c r="F39" s="196"/>
-      <c r="G39" s="196"/>
-      <c r="H39" s="201"/>
-      <c r="I39" s="202"/>
-      <c r="J39" s="202"/>
-      <c r="K39" s="202"/>
-      <c r="L39" s="202"/>
-      <c r="M39" s="203"/>
-      <c r="N39" s="197"/>
-      <c r="O39" s="198"/>
-      <c r="P39" s="199"/>
+      <c r="C39" s="176"/>
+      <c r="D39" s="176"/>
+      <c r="E39" s="176"/>
+      <c r="F39" s="176"/>
+      <c r="G39" s="176"/>
+      <c r="H39" s="177"/>
+      <c r="I39" s="178"/>
+      <c r="J39" s="178"/>
+      <c r="K39" s="178"/>
+      <c r="L39" s="178"/>
+      <c r="M39" s="179"/>
+      <c r="N39" s="180"/>
+      <c r="O39" s="181"/>
+      <c r="P39" s="182"/>
       <c r="Q39" s="49"/>
-      <c r="R39" s="200"/>
-      <c r="S39" s="200"/>
+      <c r="R39" s="183"/>
+      <c r="S39" s="183"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="49"/>
       <c r="B40" s="49"/>
-      <c r="C40" s="196"/>
-      <c r="D40" s="196"/>
-      <c r="E40" s="196"/>
-      <c r="F40" s="196"/>
-      <c r="G40" s="196"/>
-      <c r="H40" s="201"/>
-      <c r="I40" s="202"/>
-      <c r="J40" s="202"/>
-      <c r="K40" s="202"/>
-      <c r="L40" s="202"/>
-      <c r="M40" s="203"/>
-      <c r="N40" s="197"/>
-      <c r="O40" s="198"/>
-      <c r="P40" s="199"/>
+      <c r="C40" s="176"/>
+      <c r="D40" s="176"/>
+      <c r="E40" s="176"/>
+      <c r="F40" s="176"/>
+      <c r="G40" s="176"/>
+      <c r="H40" s="177"/>
+      <c r="I40" s="178"/>
+      <c r="J40" s="178"/>
+      <c r="K40" s="178"/>
+      <c r="L40" s="178"/>
+      <c r="M40" s="179"/>
+      <c r="N40" s="180"/>
+      <c r="O40" s="181"/>
+      <c r="P40" s="182"/>
       <c r="Q40" s="49"/>
-      <c r="R40" s="200"/>
-      <c r="S40" s="200"/>
+      <c r="R40" s="183"/>
+      <c r="S40" s="183"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="49"/>
       <c r="B41" s="49"/>
-      <c r="C41" s="196"/>
-      <c r="D41" s="196"/>
-      <c r="E41" s="196"/>
-      <c r="F41" s="196"/>
-      <c r="G41" s="196"/>
-      <c r="H41" s="201"/>
-      <c r="I41" s="202"/>
-      <c r="J41" s="202"/>
-      <c r="K41" s="202"/>
-      <c r="L41" s="202"/>
-      <c r="M41" s="203"/>
-      <c r="N41" s="197"/>
-      <c r="O41" s="198"/>
-      <c r="P41" s="199"/>
+      <c r="C41" s="176"/>
+      <c r="D41" s="176"/>
+      <c r="E41" s="176"/>
+      <c r="F41" s="176"/>
+      <c r="G41" s="176"/>
+      <c r="H41" s="177"/>
+      <c r="I41" s="178"/>
+      <c r="J41" s="178"/>
+      <c r="K41" s="178"/>
+      <c r="L41" s="178"/>
+      <c r="M41" s="179"/>
+      <c r="N41" s="180"/>
+      <c r="O41" s="181"/>
+      <c r="P41" s="182"/>
       <c r="Q41" s="49"/>
-      <c r="R41" s="200"/>
-      <c r="S41" s="200"/>
+      <c r="R41" s="183"/>
+      <c r="S41" s="183"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="49"/>
       <c r="B42" s="49"/>
-      <c r="C42" s="196"/>
-      <c r="D42" s="196"/>
-      <c r="E42" s="196"/>
-      <c r="F42" s="196"/>
-      <c r="G42" s="196"/>
-      <c r="H42" s="201"/>
-      <c r="I42" s="202"/>
-      <c r="J42" s="202"/>
-      <c r="K42" s="202"/>
-      <c r="L42" s="202"/>
-      <c r="M42" s="203"/>
-      <c r="N42" s="197"/>
-      <c r="O42" s="198"/>
-      <c r="P42" s="199"/>
+      <c r="C42" s="176"/>
+      <c r="D42" s="176"/>
+      <c r="E42" s="176"/>
+      <c r="F42" s="176"/>
+      <c r="G42" s="176"/>
+      <c r="H42" s="177"/>
+      <c r="I42" s="178"/>
+      <c r="J42" s="178"/>
+      <c r="K42" s="178"/>
+      <c r="L42" s="178"/>
+      <c r="M42" s="179"/>
+      <c r="N42" s="180"/>
+      <c r="O42" s="181"/>
+      <c r="P42" s="182"/>
       <c r="Q42" s="49"/>
-      <c r="R42" s="200"/>
-      <c r="S42" s="200"/>
+      <c r="R42" s="183"/>
+      <c r="S42" s="183"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="49"/>
       <c r="B43" s="49"/>
-      <c r="C43" s="196"/>
-      <c r="D43" s="196"/>
-      <c r="E43" s="196"/>
-      <c r="F43" s="196"/>
-      <c r="G43" s="196"/>
-      <c r="H43" s="201"/>
-      <c r="I43" s="202"/>
-      <c r="J43" s="202"/>
-      <c r="K43" s="202"/>
-      <c r="L43" s="202"/>
-      <c r="M43" s="203"/>
-      <c r="N43" s="197"/>
-      <c r="O43" s="198"/>
-      <c r="P43" s="199"/>
+      <c r="C43" s="176"/>
+      <c r="D43" s="176"/>
+      <c r="E43" s="176"/>
+      <c r="F43" s="176"/>
+      <c r="G43" s="176"/>
+      <c r="H43" s="177"/>
+      <c r="I43" s="178"/>
+      <c r="J43" s="178"/>
+      <c r="K43" s="178"/>
+      <c r="L43" s="178"/>
+      <c r="M43" s="179"/>
+      <c r="N43" s="180"/>
+      <c r="O43" s="181"/>
+      <c r="P43" s="182"/>
       <c r="Q43" s="49"/>
-      <c r="R43" s="200"/>
-      <c r="S43" s="200"/>
+      <c r="R43" s="183"/>
+      <c r="S43" s="183"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="49"/>
       <c r="B44" s="49"/>
-      <c r="C44" s="196"/>
-      <c r="D44" s="196"/>
-      <c r="E44" s="196"/>
-      <c r="F44" s="196"/>
-      <c r="G44" s="196"/>
-      <c r="H44" s="201"/>
-      <c r="I44" s="202"/>
-      <c r="J44" s="202"/>
-      <c r="K44" s="202"/>
-      <c r="L44" s="202"/>
-      <c r="M44" s="203"/>
-      <c r="N44" s="197"/>
-      <c r="O44" s="198"/>
-      <c r="P44" s="199"/>
+      <c r="C44" s="176"/>
+      <c r="D44" s="176"/>
+      <c r="E44" s="176"/>
+      <c r="F44" s="176"/>
+      <c r="G44" s="176"/>
+      <c r="H44" s="177"/>
+      <c r="I44" s="178"/>
+      <c r="J44" s="178"/>
+      <c r="K44" s="178"/>
+      <c r="L44" s="178"/>
+      <c r="M44" s="179"/>
+      <c r="N44" s="180"/>
+      <c r="O44" s="181"/>
+      <c r="P44" s="182"/>
       <c r="Q44" s="49"/>
-      <c r="R44" s="200"/>
-      <c r="S44" s="200"/>
+      <c r="R44" s="183"/>
+      <c r="S44" s="183"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="49"/>
       <c r="B45" s="49"/>
-      <c r="C45" s="196"/>
-      <c r="D45" s="196"/>
-      <c r="E45" s="196"/>
-      <c r="F45" s="196"/>
-      <c r="G45" s="196"/>
-      <c r="H45" s="201"/>
-      <c r="I45" s="202"/>
-      <c r="J45" s="202"/>
-      <c r="K45" s="202"/>
-      <c r="L45" s="202"/>
-      <c r="M45" s="203"/>
-      <c r="N45" s="197"/>
-      <c r="O45" s="198"/>
-      <c r="P45" s="199"/>
+      <c r="C45" s="176"/>
+      <c r="D45" s="176"/>
+      <c r="E45" s="176"/>
+      <c r="F45" s="176"/>
+      <c r="G45" s="176"/>
+      <c r="H45" s="177"/>
+      <c r="I45" s="178"/>
+      <c r="J45" s="178"/>
+      <c r="K45" s="178"/>
+      <c r="L45" s="178"/>
+      <c r="M45" s="179"/>
+      <c r="N45" s="180"/>
+      <c r="O45" s="181"/>
+      <c r="P45" s="182"/>
       <c r="Q45" s="49"/>
-      <c r="R45" s="200"/>
-      <c r="S45" s="200"/>
+      <c r="R45" s="183"/>
+      <c r="S45" s="183"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="49"/>
       <c r="B46" s="49"/>
-      <c r="C46" s="196"/>
-      <c r="D46" s="196"/>
-      <c r="E46" s="196"/>
-      <c r="F46" s="196"/>
-      <c r="G46" s="196"/>
-      <c r="H46" s="201"/>
-      <c r="I46" s="202"/>
-      <c r="J46" s="202"/>
-      <c r="K46" s="202"/>
-      <c r="L46" s="202"/>
-      <c r="M46" s="203"/>
-      <c r="N46" s="197"/>
-      <c r="O46" s="198"/>
-      <c r="P46" s="199"/>
+      <c r="C46" s="176"/>
+      <c r="D46" s="176"/>
+      <c r="E46" s="176"/>
+      <c r="F46" s="176"/>
+      <c r="G46" s="176"/>
+      <c r="H46" s="177"/>
+      <c r="I46" s="178"/>
+      <c r="J46" s="178"/>
+      <c r="K46" s="178"/>
+      <c r="L46" s="178"/>
+      <c r="M46" s="179"/>
+      <c r="N46" s="180"/>
+      <c r="O46" s="181"/>
+      <c r="P46" s="182"/>
       <c r="Q46" s="49"/>
-      <c r="R46" s="200"/>
-      <c r="S46" s="200"/>
+      <c r="R46" s="183"/>
+      <c r="S46" s="183"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="49"/>
       <c r="B47" s="49"/>
-      <c r="C47" s="196"/>
-      <c r="D47" s="196"/>
-      <c r="E47" s="196"/>
-      <c r="F47" s="196"/>
-      <c r="G47" s="196"/>
-      <c r="H47" s="201"/>
-      <c r="I47" s="202"/>
-      <c r="J47" s="202"/>
-      <c r="K47" s="202"/>
-      <c r="L47" s="202"/>
-      <c r="M47" s="203"/>
-      <c r="N47" s="197"/>
-      <c r="O47" s="198"/>
-      <c r="P47" s="199"/>
+      <c r="C47" s="176"/>
+      <c r="D47" s="176"/>
+      <c r="E47" s="176"/>
+      <c r="F47" s="176"/>
+      <c r="G47" s="176"/>
+      <c r="H47" s="177"/>
+      <c r="I47" s="178"/>
+      <c r="J47" s="178"/>
+      <c r="K47" s="178"/>
+      <c r="L47" s="178"/>
+      <c r="M47" s="179"/>
+      <c r="N47" s="180"/>
+      <c r="O47" s="181"/>
+      <c r="P47" s="182"/>
       <c r="Q47" s="49"/>
-      <c r="R47" s="200"/>
-      <c r="S47" s="200"/>
+      <c r="R47" s="183"/>
+      <c r="S47" s="183"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="49"/>
       <c r="B48" s="49"/>
-      <c r="C48" s="196"/>
-      <c r="D48" s="196"/>
-      <c r="E48" s="196"/>
-      <c r="F48" s="196"/>
-      <c r="G48" s="196"/>
-      <c r="H48" s="201"/>
-      <c r="I48" s="202"/>
-      <c r="J48" s="202"/>
-      <c r="K48" s="202"/>
-      <c r="L48" s="202"/>
-      <c r="M48" s="203"/>
-      <c r="N48" s="197"/>
-      <c r="O48" s="198"/>
-      <c r="P48" s="199"/>
+      <c r="C48" s="176"/>
+      <c r="D48" s="176"/>
+      <c r="E48" s="176"/>
+      <c r="F48" s="176"/>
+      <c r="G48" s="176"/>
+      <c r="H48" s="177"/>
+      <c r="I48" s="178"/>
+      <c r="J48" s="178"/>
+      <c r="K48" s="178"/>
+      <c r="L48" s="178"/>
+      <c r="M48" s="179"/>
+      <c r="N48" s="180"/>
+      <c r="O48" s="181"/>
+      <c r="P48" s="182"/>
       <c r="Q48" s="49"/>
-      <c r="R48" s="200"/>
-      <c r="S48" s="200"/>
+      <c r="R48" s="183"/>
+      <c r="S48" s="183"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="49"/>
       <c r="B49" s="49"/>
-      <c r="C49" s="196"/>
-      <c r="D49" s="196"/>
-      <c r="E49" s="196"/>
-      <c r="F49" s="196"/>
-      <c r="G49" s="196"/>
-      <c r="H49" s="201"/>
-      <c r="I49" s="202"/>
-      <c r="J49" s="202"/>
-      <c r="K49" s="202"/>
-      <c r="L49" s="202"/>
-      <c r="M49" s="203"/>
-      <c r="N49" s="197"/>
-      <c r="O49" s="198"/>
-      <c r="P49" s="199"/>
+      <c r="C49" s="176"/>
+      <c r="D49" s="176"/>
+      <c r="E49" s="176"/>
+      <c r="F49" s="176"/>
+      <c r="G49" s="176"/>
+      <c r="H49" s="177"/>
+      <c r="I49" s="178"/>
+      <c r="J49" s="178"/>
+      <c r="K49" s="178"/>
+      <c r="L49" s="178"/>
+      <c r="M49" s="179"/>
+      <c r="N49" s="180"/>
+      <c r="O49" s="181"/>
+      <c r="P49" s="182"/>
       <c r="Q49" s="49"/>
-      <c r="R49" s="200"/>
-      <c r="S49" s="200"/>
+      <c r="R49" s="183"/>
+      <c r="S49" s="183"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="49"/>
       <c r="B50" s="49"/>
-      <c r="C50" s="196"/>
-      <c r="D50" s="196"/>
-      <c r="E50" s="196"/>
-      <c r="F50" s="196"/>
-      <c r="G50" s="196"/>
-      <c r="H50" s="201"/>
-      <c r="I50" s="202"/>
-      <c r="J50" s="202"/>
-      <c r="K50" s="202"/>
-      <c r="L50" s="202"/>
-      <c r="M50" s="203"/>
-      <c r="N50" s="197"/>
-      <c r="O50" s="198"/>
-      <c r="P50" s="199"/>
+      <c r="C50" s="176"/>
+      <c r="D50" s="176"/>
+      <c r="E50" s="176"/>
+      <c r="F50" s="176"/>
+      <c r="G50" s="176"/>
+      <c r="H50" s="177"/>
+      <c r="I50" s="178"/>
+      <c r="J50" s="178"/>
+      <c r="K50" s="178"/>
+      <c r="L50" s="178"/>
+      <c r="M50" s="179"/>
+      <c r="N50" s="180"/>
+      <c r="O50" s="181"/>
+      <c r="P50" s="182"/>
       <c r="Q50" s="49"/>
-      <c r="R50" s="200"/>
-      <c r="S50" s="200"/>
+      <c r="R50" s="183"/>
+      <c r="S50" s="183"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="49"/>
       <c r="B51" s="49"/>
-      <c r="C51" s="196"/>
-      <c r="D51" s="196"/>
-      <c r="E51" s="196"/>
-      <c r="F51" s="196"/>
-      <c r="G51" s="196"/>
-      <c r="H51" s="201"/>
-      <c r="I51" s="202"/>
-      <c r="J51" s="202"/>
-      <c r="K51" s="202"/>
-      <c r="L51" s="202"/>
-      <c r="M51" s="203"/>
-      <c r="N51" s="197"/>
-      <c r="O51" s="198"/>
-      <c r="P51" s="199"/>
+      <c r="C51" s="176"/>
+      <c r="D51" s="176"/>
+      <c r="E51" s="176"/>
+      <c r="F51" s="176"/>
+      <c r="G51" s="176"/>
+      <c r="H51" s="177"/>
+      <c r="I51" s="178"/>
+      <c r="J51" s="178"/>
+      <c r="K51" s="178"/>
+      <c r="L51" s="178"/>
+      <c r="M51" s="179"/>
+      <c r="N51" s="180"/>
+      <c r="O51" s="181"/>
+      <c r="P51" s="182"/>
       <c r="Q51" s="49"/>
-      <c r="R51" s="200"/>
-      <c r="S51" s="200"/>
+      <c r="R51" s="183"/>
+      <c r="S51" s="183"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="49"/>
       <c r="B52" s="49"/>
-      <c r="C52" s="196"/>
-      <c r="D52" s="196"/>
-      <c r="E52" s="196"/>
-      <c r="F52" s="196"/>
-      <c r="G52" s="196"/>
-      <c r="H52" s="201"/>
-      <c r="I52" s="202"/>
-      <c r="J52" s="202"/>
-      <c r="K52" s="202"/>
-      <c r="L52" s="202"/>
-      <c r="M52" s="203"/>
-      <c r="N52" s="197"/>
-      <c r="O52" s="198"/>
-      <c r="P52" s="199"/>
+      <c r="C52" s="176"/>
+      <c r="D52" s="176"/>
+      <c r="E52" s="176"/>
+      <c r="F52" s="176"/>
+      <c r="G52" s="176"/>
+      <c r="H52" s="177"/>
+      <c r="I52" s="178"/>
+      <c r="J52" s="178"/>
+      <c r="K52" s="178"/>
+      <c r="L52" s="178"/>
+      <c r="M52" s="179"/>
+      <c r="N52" s="180"/>
+      <c r="O52" s="181"/>
+      <c r="P52" s="182"/>
       <c r="Q52" s="49"/>
-      <c r="R52" s="200"/>
-      <c r="S52" s="200"/>
+      <c r="R52" s="183"/>
+      <c r="S52" s="183"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -21142,6 +21030,194 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/削除機能詳細設計書.xlsx
+++ b/Documents/削除機能詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB54B0CE-D250-45EC-8F50-7C48A0AC146A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98635DC-7275-44E7-A21C-D6E3C26FE992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="660" windowWidth="11415" windowHeight="8955" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -2311,6 +2311,12 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="76" xfId="5" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2335,6 +2341,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2345,11 +2384,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2365,9 +2452,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2386,84 +2470,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2527,27 +2533,48 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2560,79 +2587,141 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2641,78 +2730,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2742,23 +2759,6 @@
     </xf>
     <xf numFmtId="9" fontId="19" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3601,85 +3601,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="74"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="76"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3699,46 +3699,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="74"/>
-      <c r="M8" s="74"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="76"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="70" t="s">
+      <c r="G13" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="72"/>
-      <c r="I13" s="70" t="s">
+      <c r="H13" s="74"/>
+      <c r="I13" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="71"/>
-      <c r="K13" s="72"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="74"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="70"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="74"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="70"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="74"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3747,13 +3747,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="73" t="s">
+      <c r="G17" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
-      <c r="J17" s="74"/>
-      <c r="K17" s="74"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="76"/>
+      <c r="K17" s="76"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4811,23 +4811,23 @@
       <c r="AL1" s="53"/>
       <c r="AM1" s="53"/>
       <c r="AN1" s="53"/>
-      <c r="AO1" s="207" t="s">
+      <c r="AO1" s="214" t="s">
         <v>126</v>
       </c>
-      <c r="AP1" s="207"/>
-      <c r="AQ1" s="207"/>
-      <c r="AR1" s="207"/>
-      <c r="AS1" s="207"/>
-      <c r="AT1" s="208">
+      <c r="AP1" s="214"/>
+      <c r="AQ1" s="214"/>
+      <c r="AR1" s="214"/>
+      <c r="AS1" s="214"/>
+      <c r="AT1" s="215">
         <v>45821</v>
       </c>
-      <c r="AU1" s="209"/>
-      <c r="AV1" s="209"/>
-      <c r="AW1" s="209"/>
-      <c r="AX1" s="209"/>
-      <c r="AY1" s="209"/>
-      <c r="AZ1" s="209"/>
-      <c r="BA1" s="209"/>
+      <c r="AU1" s="216"/>
+      <c r="AV1" s="216"/>
+      <c r="AW1" s="216"/>
+      <c r="AX1" s="216"/>
+      <c r="AY1" s="216"/>
+      <c r="AZ1" s="216"/>
+      <c r="BA1" s="216"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -4873,54 +4873,54 @@
       <c r="AK4" s="60"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="204" t="s">
+      <c r="A5" s="211" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="205"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="205"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="206"/>
-      <c r="G5" s="210" t="s">
+      <c r="B5" s="212"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="213"/>
+      <c r="G5" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="211"/>
-      <c r="L5" s="211"/>
-      <c r="M5" s="211"/>
-      <c r="N5" s="211"/>
-      <c r="O5" s="211"/>
-      <c r="P5" s="211"/>
-      <c r="Q5" s="211"/>
-      <c r="R5" s="211"/>
-      <c r="S5" s="212"/>
+      <c r="H5" s="218"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="218"/>
+      <c r="K5" s="218"/>
+      <c r="L5" s="218"/>
+      <c r="M5" s="218"/>
+      <c r="N5" s="218"/>
+      <c r="O5" s="218"/>
+      <c r="P5" s="218"/>
+      <c r="Q5" s="218"/>
+      <c r="R5" s="218"/>
+      <c r="S5" s="219"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="211" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="205"/>
-      <c r="C6" s="205"/>
-      <c r="D6" s="205"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="206"/>
-      <c r="G6" s="213">
+      <c r="B6" s="212"/>
+      <c r="C6" s="212"/>
+      <c r="D6" s="212"/>
+      <c r="E6" s="212"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="220">
         <v>1</v>
       </c>
-      <c r="H6" s="211"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="211"/>
-      <c r="K6" s="211"/>
-      <c r="L6" s="211"/>
-      <c r="M6" s="211"/>
-      <c r="N6" s="211"/>
-      <c r="O6" s="211"/>
-      <c r="P6" s="211"/>
-      <c r="Q6" s="211"/>
-      <c r="R6" s="211"/>
-      <c r="S6" s="212"/>
+      <c r="H6" s="218"/>
+      <c r="I6" s="218"/>
+      <c r="J6" s="218"/>
+      <c r="K6" s="218"/>
+      <c r="L6" s="218"/>
+      <c r="M6" s="218"/>
+      <c r="N6" s="218"/>
+      <c r="O6" s="218"/>
+      <c r="P6" s="218"/>
+      <c r="Q6" s="218"/>
+      <c r="R6" s="218"/>
+      <c r="S6" s="219"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -4929,61 +4929,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="204" t="s">
+      <c r="A9" s="211" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="205"/>
-      <c r="C9" s="205"/>
-      <c r="D9" s="205"/>
-      <c r="E9" s="205"/>
-      <c r="F9" s="205"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="205"/>
-      <c r="I9" s="205"/>
-      <c r="J9" s="205"/>
-      <c r="K9" s="205"/>
-      <c r="L9" s="205"/>
-      <c r="M9" s="205"/>
-      <c r="N9" s="205"/>
-      <c r="O9" s="205"/>
-      <c r="P9" s="205"/>
-      <c r="Q9" s="205"/>
-      <c r="R9" s="205"/>
-      <c r="S9" s="205"/>
-      <c r="T9" s="205"/>
-      <c r="U9" s="205"/>
-      <c r="V9" s="205"/>
-      <c r="W9" s="205"/>
-      <c r="X9" s="205"/>
-      <c r="Y9" s="205"/>
-      <c r="Z9" s="205"/>
-      <c r="AA9" s="205"/>
-      <c r="AB9" s="205"/>
-      <c r="AC9" s="205"/>
-      <c r="AD9" s="205"/>
-      <c r="AE9" s="205"/>
-      <c r="AF9" s="205"/>
-      <c r="AG9" s="205"/>
-      <c r="AH9" s="205"/>
-      <c r="AI9" s="205"/>
-      <c r="AJ9" s="205"/>
-      <c r="AK9" s="205"/>
-      <c r="AL9" s="205"/>
-      <c r="AM9" s="205"/>
-      <c r="AN9" s="205"/>
-      <c r="AO9" s="205"/>
-      <c r="AP9" s="205"/>
-      <c r="AQ9" s="205"/>
-      <c r="AR9" s="205"/>
-      <c r="AS9" s="205"/>
-      <c r="AT9" s="205"/>
-      <c r="AU9" s="205"/>
-      <c r="AV9" s="205"/>
-      <c r="AW9" s="205"/>
-      <c r="AX9" s="205"/>
-      <c r="AY9" s="205"/>
-      <c r="AZ9" s="205"/>
-      <c r="BA9" s="206"/>
+      <c r="B9" s="212"/>
+      <c r="C9" s="212"/>
+      <c r="D9" s="212"/>
+      <c r="E9" s="212"/>
+      <c r="F9" s="212"/>
+      <c r="G9" s="212"/>
+      <c r="H9" s="212"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="212"/>
+      <c r="K9" s="212"/>
+      <c r="L9" s="212"/>
+      <c r="M9" s="212"/>
+      <c r="N9" s="212"/>
+      <c r="O9" s="212"/>
+      <c r="P9" s="212"/>
+      <c r="Q9" s="212"/>
+      <c r="R9" s="212"/>
+      <c r="S9" s="212"/>
+      <c r="T9" s="212"/>
+      <c r="U9" s="212"/>
+      <c r="V9" s="212"/>
+      <c r="W9" s="212"/>
+      <c r="X9" s="212"/>
+      <c r="Y9" s="212"/>
+      <c r="Z9" s="212"/>
+      <c r="AA9" s="212"/>
+      <c r="AB9" s="212"/>
+      <c r="AC9" s="212"/>
+      <c r="AD9" s="212"/>
+      <c r="AE9" s="212"/>
+      <c r="AF9" s="212"/>
+      <c r="AG9" s="212"/>
+      <c r="AH9" s="212"/>
+      <c r="AI9" s="212"/>
+      <c r="AJ9" s="212"/>
+      <c r="AK9" s="212"/>
+      <c r="AL9" s="212"/>
+      <c r="AM9" s="212"/>
+      <c r="AN9" s="212"/>
+      <c r="AO9" s="212"/>
+      <c r="AP9" s="212"/>
+      <c r="AQ9" s="212"/>
+      <c r="AR9" s="212"/>
+      <c r="AS9" s="212"/>
+      <c r="AT9" s="212"/>
+      <c r="AU9" s="212"/>
+      <c r="AV9" s="212"/>
+      <c r="AW9" s="212"/>
+      <c r="AX9" s="212"/>
+      <c r="AY9" s="212"/>
+      <c r="AZ9" s="212"/>
+      <c r="BA9" s="213"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="62"/>
@@ -8706,61 +8706,61 @@
       <c r="BA102" s="64"/>
     </row>
     <row r="103" spans="1:53" ht="18" customHeight="1">
-      <c r="A103" s="204" t="s">
+      <c r="A103" s="211" t="s">
         <v>132</v>
       </c>
-      <c r="B103" s="205"/>
-      <c r="C103" s="205"/>
-      <c r="D103" s="205"/>
-      <c r="E103" s="205"/>
-      <c r="F103" s="205"/>
-      <c r="G103" s="205"/>
-      <c r="H103" s="205"/>
-      <c r="I103" s="205"/>
-      <c r="J103" s="205"/>
-      <c r="K103" s="205"/>
-      <c r="L103" s="205"/>
-      <c r="M103" s="205"/>
-      <c r="N103" s="205"/>
-      <c r="O103" s="205"/>
-      <c r="P103" s="205"/>
-      <c r="Q103" s="205"/>
-      <c r="R103" s="205"/>
-      <c r="S103" s="205"/>
-      <c r="T103" s="205"/>
-      <c r="U103" s="205"/>
-      <c r="V103" s="205"/>
-      <c r="W103" s="205"/>
-      <c r="X103" s="205"/>
-      <c r="Y103" s="205"/>
-      <c r="Z103" s="205"/>
-      <c r="AA103" s="205"/>
-      <c r="AB103" s="205"/>
-      <c r="AC103" s="205"/>
-      <c r="AD103" s="205"/>
-      <c r="AE103" s="205"/>
-      <c r="AF103" s="205"/>
-      <c r="AG103" s="205"/>
-      <c r="AH103" s="205"/>
-      <c r="AI103" s="205"/>
-      <c r="AJ103" s="205"/>
-      <c r="AK103" s="205"/>
-      <c r="AL103" s="205"/>
-      <c r="AM103" s="205"/>
-      <c r="AN103" s="205"/>
-      <c r="AO103" s="205"/>
-      <c r="AP103" s="205"/>
-      <c r="AQ103" s="205"/>
-      <c r="AR103" s="205"/>
-      <c r="AS103" s="205"/>
-      <c r="AT103" s="205"/>
-      <c r="AU103" s="205"/>
-      <c r="AV103" s="205"/>
-      <c r="AW103" s="205"/>
-      <c r="AX103" s="205"/>
-      <c r="AY103" s="205"/>
-      <c r="AZ103" s="205"/>
-      <c r="BA103" s="206"/>
+      <c r="B103" s="212"/>
+      <c r="C103" s="212"/>
+      <c r="D103" s="212"/>
+      <c r="E103" s="212"/>
+      <c r="F103" s="212"/>
+      <c r="G103" s="212"/>
+      <c r="H103" s="212"/>
+      <c r="I103" s="212"/>
+      <c r="J103" s="212"/>
+      <c r="K103" s="212"/>
+      <c r="L103" s="212"/>
+      <c r="M103" s="212"/>
+      <c r="N103" s="212"/>
+      <c r="O103" s="212"/>
+      <c r="P103" s="212"/>
+      <c r="Q103" s="212"/>
+      <c r="R103" s="212"/>
+      <c r="S103" s="212"/>
+      <c r="T103" s="212"/>
+      <c r="U103" s="212"/>
+      <c r="V103" s="212"/>
+      <c r="W103" s="212"/>
+      <c r="X103" s="212"/>
+      <c r="Y103" s="212"/>
+      <c r="Z103" s="212"/>
+      <c r="AA103" s="212"/>
+      <c r="AB103" s="212"/>
+      <c r="AC103" s="212"/>
+      <c r="AD103" s="212"/>
+      <c r="AE103" s="212"/>
+      <c r="AF103" s="212"/>
+      <c r="AG103" s="212"/>
+      <c r="AH103" s="212"/>
+      <c r="AI103" s="212"/>
+      <c r="AJ103" s="212"/>
+      <c r="AK103" s="212"/>
+      <c r="AL103" s="212"/>
+      <c r="AM103" s="212"/>
+      <c r="AN103" s="212"/>
+      <c r="AO103" s="212"/>
+      <c r="AP103" s="212"/>
+      <c r="AQ103" s="212"/>
+      <c r="AR103" s="212"/>
+      <c r="AS103" s="212"/>
+      <c r="AT103" s="212"/>
+      <c r="AU103" s="212"/>
+      <c r="AV103" s="212"/>
+      <c r="AW103" s="212"/>
+      <c r="AX103" s="212"/>
+      <c r="AY103" s="212"/>
+      <c r="AZ103" s="212"/>
+      <c r="BA103" s="213"/>
     </row>
     <row r="104" spans="1:53" ht="21.95" customHeight="1">
       <c r="A104" s="65"/>
@@ -9083,61 +9083,61 @@
       <c r="BA111" s="64"/>
     </row>
     <row r="112" spans="1:53" ht="18" customHeight="1">
-      <c r="A112" s="204" t="s">
+      <c r="A112" s="211" t="s">
         <v>133</v>
       </c>
-      <c r="B112" s="205"/>
-      <c r="C112" s="205"/>
-      <c r="D112" s="205"/>
-      <c r="E112" s="205"/>
-      <c r="F112" s="205"/>
-      <c r="G112" s="205"/>
-      <c r="H112" s="205"/>
-      <c r="I112" s="205"/>
-      <c r="J112" s="205"/>
-      <c r="K112" s="205"/>
-      <c r="L112" s="205"/>
-      <c r="M112" s="205"/>
-      <c r="N112" s="205"/>
-      <c r="O112" s="205"/>
-      <c r="P112" s="205"/>
-      <c r="Q112" s="205"/>
-      <c r="R112" s="205"/>
-      <c r="S112" s="205"/>
-      <c r="T112" s="205"/>
-      <c r="U112" s="205"/>
-      <c r="V112" s="205"/>
-      <c r="W112" s="205"/>
-      <c r="X112" s="205"/>
-      <c r="Y112" s="205"/>
-      <c r="Z112" s="205"/>
-      <c r="AA112" s="205"/>
-      <c r="AB112" s="205"/>
-      <c r="AC112" s="205"/>
-      <c r="AD112" s="205"/>
-      <c r="AE112" s="205"/>
-      <c r="AF112" s="205"/>
-      <c r="AG112" s="205"/>
-      <c r="AH112" s="205"/>
-      <c r="AI112" s="205"/>
-      <c r="AJ112" s="205"/>
-      <c r="AK112" s="205"/>
-      <c r="AL112" s="205"/>
-      <c r="AM112" s="205"/>
-      <c r="AN112" s="205"/>
-      <c r="AO112" s="205"/>
-      <c r="AP112" s="205"/>
-      <c r="AQ112" s="205"/>
-      <c r="AR112" s="205"/>
-      <c r="AS112" s="205"/>
-      <c r="AT112" s="205"/>
-      <c r="AU112" s="205"/>
-      <c r="AV112" s="205"/>
-      <c r="AW112" s="205"/>
-      <c r="AX112" s="205"/>
-      <c r="AY112" s="205"/>
-      <c r="AZ112" s="205"/>
-      <c r="BA112" s="205"/>
+      <c r="B112" s="212"/>
+      <c r="C112" s="212"/>
+      <c r="D112" s="212"/>
+      <c r="E112" s="212"/>
+      <c r="F112" s="212"/>
+      <c r="G112" s="212"/>
+      <c r="H112" s="212"/>
+      <c r="I112" s="212"/>
+      <c r="J112" s="212"/>
+      <c r="K112" s="212"/>
+      <c r="L112" s="212"/>
+      <c r="M112" s="212"/>
+      <c r="N112" s="212"/>
+      <c r="O112" s="212"/>
+      <c r="P112" s="212"/>
+      <c r="Q112" s="212"/>
+      <c r="R112" s="212"/>
+      <c r="S112" s="212"/>
+      <c r="T112" s="212"/>
+      <c r="U112" s="212"/>
+      <c r="V112" s="212"/>
+      <c r="W112" s="212"/>
+      <c r="X112" s="212"/>
+      <c r="Y112" s="212"/>
+      <c r="Z112" s="212"/>
+      <c r="AA112" s="212"/>
+      <c r="AB112" s="212"/>
+      <c r="AC112" s="212"/>
+      <c r="AD112" s="212"/>
+      <c r="AE112" s="212"/>
+      <c r="AF112" s="212"/>
+      <c r="AG112" s="212"/>
+      <c r="AH112" s="212"/>
+      <c r="AI112" s="212"/>
+      <c r="AJ112" s="212"/>
+      <c r="AK112" s="212"/>
+      <c r="AL112" s="212"/>
+      <c r="AM112" s="212"/>
+      <c r="AN112" s="212"/>
+      <c r="AO112" s="212"/>
+      <c r="AP112" s="212"/>
+      <c r="AQ112" s="212"/>
+      <c r="AR112" s="212"/>
+      <c r="AS112" s="212"/>
+      <c r="AT112" s="212"/>
+      <c r="AU112" s="212"/>
+      <c r="AV112" s="212"/>
+      <c r="AW112" s="212"/>
+      <c r="AX112" s="212"/>
+      <c r="AY112" s="212"/>
+      <c r="AZ112" s="212"/>
+      <c r="BA112" s="212"/>
     </row>
     <row r="113" spans="1:53" ht="21.95" customHeight="1">
       <c r="A113" s="65"/>
@@ -9311,19 +9311,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="115" t="s">
+      <c r="B1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="103"/>
-      <c r="F1" s="115" t="s">
+      <c r="E1" s="88"/>
+      <c r="F1" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="103"/>
+      <c r="G1" s="88"/>
       <c r="H1" s="37" t="s">
         <v>8</v>
       </c>
@@ -9335,190 +9335,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="109"/>
-      <c r="B2" s="110"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="116" t="s">
+      <c r="A2" s="99"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="117"/>
-      <c r="F2" s="116" t="s">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="117"/>
-      <c r="H2" s="120">
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
         <v>45806</v>
       </c>
-      <c r="I2" s="95" t="s">
+      <c r="I2" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="98"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="109"/>
-      <c r="B3" s="110"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="99"/>
+      <c r="A3" s="99"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="112"/>
-      <c r="B4" s="113"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="100"/>
+      <c r="A4" s="102"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="104" t="s">
+      <c r="B5" s="87"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="105"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="90"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="88" t="s">
+      <c r="B6" s="92"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="82"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="95"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="79"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="88" t="s">
+      <c r="B7" s="92"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="82"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="95"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="88" t="s">
+      <c r="B8" s="92"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="82"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="89" t="s">
+      <c r="A9" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="80"/>
-      <c r="D9" s="81" t="s">
+      <c r="C9" s="93"/>
+      <c r="D9" s="111" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="94"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="90"/>
-      <c r="B10" s="92" t="s">
+      <c r="A10" s="118"/>
+      <c r="B10" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="80"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="82"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="91"/>
-      <c r="B11" s="92" t="s">
+      <c r="A11" s="119"/>
+      <c r="B11" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="80"/>
-      <c r="D11" s="88" t="s">
+      <c r="C11" s="93"/>
+      <c r="D11" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="82"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="81" t="s">
+      <c r="B12" s="92"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="82"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="84"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="87"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="113"/>
+      <c r="I13" s="113"/>
+      <c r="J13" s="116"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10509,18 +10509,6 @@
     <row r="1000" s="39" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -10536,6 +10524,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -10554,19 +10554,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="136" t="s">
+      <c r="E1" s="139"/>
+      <c r="F1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="139"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -10578,48 +10578,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="138">
+      <c r="E2" s="141"/>
+      <c r="F2" s="140">
         <v>56</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="121">
+      <c r="G2" s="141"/>
+      <c r="H2" s="123">
         <v>45811</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="125"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="126"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="127"/>
+      <c r="A4" s="135"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="129"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -11976,19 +11976,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="136" t="s">
+      <c r="E1" s="139"/>
+      <c r="F1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="139"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -12000,48 +12000,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="138">
+      <c r="E2" s="141"/>
+      <c r="F2" s="140">
         <v>56</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="121">
+      <c r="G2" s="141"/>
+      <c r="H2" s="123">
         <v>45807</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="125"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="126"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="127"/>
+      <c r="A4" s="135"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="129"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -13392,19 +13392,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="136" t="s">
+      <c r="E1" s="139"/>
+      <c r="F1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="139"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -13416,190 +13416,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="138" t="s">
+      <c r="E2" s="141"/>
+      <c r="F2" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="121">
+      <c r="G2" s="141"/>
+      <c r="H2" s="123">
         <v>45807</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="125"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="126"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="131"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="126"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="142" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="146" t="s">
+      <c r="B5" s="155"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="156" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="147"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="145" t="s">
+      <c r="A6" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="148"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="131"/>
-      <c r="B8" s="74"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="152"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="131"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="152"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="131"/>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="152"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="131"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="152"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="131"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="152"/>
+      <c r="A12" s="133"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="131"/>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="152"/>
+      <c r="A13" s="133"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="145" t="s">
+      <c r="A14" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="148"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="146"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="147" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="153" t="s">
+      <c r="B15" s="73"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="145" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="74"/>
       <c r="I15" s="14" t="s">
         <v>28</v>
       </c>
@@ -13608,11 +13608,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="147" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="74"/>
       <c r="D16" s="14" t="s">
         <v>30</v>
       </c>
@@ -13625,18 +13625,18 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="148" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="148"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="146"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="144">
         <v>1</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="74"/>
       <c r="D17" s="16" t="s">
         <v>75</v>
       </c>
@@ -13647,16 +13647,16 @@
         <v>82</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="153"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="148"/>
+      <c r="H17" s="145"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="146"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="144">
         <v>2</v>
       </c>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="74"/>
       <c r="D18" s="16" t="s">
         <v>76</v>
       </c>
@@ -13669,16 +13669,16 @@
       <c r="G18" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="153"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="148"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="146"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="144">
         <v>3</v>
       </c>
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="74"/>
       <c r="D19" s="16" t="s">
         <v>77</v>
       </c>
@@ -13689,16 +13689,16 @@
       <c r="G19" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="153"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="148"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="146"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="144">
         <v>4</v>
       </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="74"/>
       <c r="D20" s="16" t="s">
         <v>78</v>
       </c>
@@ -13711,16 +13711,16 @@
       <c r="G20" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="153"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="148"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="146"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="144">
         <v>5</v>
       </c>
-      <c r="B21" s="71"/>
-      <c r="C21" s="72"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="74"/>
       <c r="D21" s="16" t="s">
         <v>79</v>
       </c>
@@ -13733,16 +13733,16 @@
       <c r="G21" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="153"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="148"/>
+      <c r="H21" s="145"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="146"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="144">
         <v>6</v>
       </c>
-      <c r="B22" s="71"/>
-      <c r="C22" s="72"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="74"/>
       <c r="D22" s="16" t="s">
         <v>61</v>
       </c>
@@ -13753,16 +13753,16 @@
         <v>61</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="148"/>
+      <c r="H22" s="145"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A23" s="144">
         <v>7</v>
       </c>
-      <c r="B23" s="71"/>
-      <c r="C23" s="72"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="18" t="s">
         <v>61</v>
       </c>
@@ -13773,225 +13773,225 @@
         <v>61</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="155"/>
-      <c r="I23" s="156"/>
-      <c r="J23" s="157"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="145"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="148"/>
+      <c r="A24" s="147"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73"/>
+      <c r="J24" s="146"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="145"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="72"/>
+      <c r="A25" s="147"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="74"/>
       <c r="I25" s="14"/>
       <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="145"/>
-      <c r="B26" s="71"/>
-      <c r="C26" s="72"/>
+      <c r="A26" s="147"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="74"/>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="154"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="148"/>
+      <c r="H26" s="148"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="146"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
       <c r="A27" s="144"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="72"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="74"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="153"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="148"/>
+      <c r="H27" s="145"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="146"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
       <c r="A28" s="144"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="72"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="74"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="153"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="148"/>
+      <c r="H28" s="145"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="146"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
       <c r="A29" s="144"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="72"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="74"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
-      <c r="H29" s="153"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="148"/>
+      <c r="H29" s="145"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="146"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
       <c r="A30" s="144"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="72"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="74"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="153"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="148"/>
+      <c r="H30" s="145"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="146"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
       <c r="A31" s="144"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="72"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="74"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="153"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="148"/>
+      <c r="H31" s="145"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="146"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
       <c r="A32" s="144"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="72"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="74"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="153"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="148"/>
+      <c r="H32" s="145"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="146"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="158"/>
-      <c r="B33" s="156"/>
-      <c r="C33" s="159"/>
+      <c r="A33" s="149"/>
+      <c r="B33" s="150"/>
+      <c r="C33" s="151"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
-      <c r="H33" s="155"/>
-      <c r="I33" s="156"/>
-      <c r="J33" s="157"/>
+      <c r="H33" s="152"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="153"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="145"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="148"/>
+      <c r="A34" s="147"/>
+      <c r="B34" s="73"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="146"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="145"/>
-      <c r="B35" s="71"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="153"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="72"/>
+      <c r="A35" s="147"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="145"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="74"/>
       <c r="I35" s="14"/>
       <c r="J35" s="15"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="145"/>
-      <c r="B36" s="71"/>
-      <c r="C36" s="72"/>
+      <c r="A36" s="147"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="74"/>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
-      <c r="H36" s="154"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="148"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="146"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
       <c r="A37" s="144"/>
-      <c r="B37" s="71"/>
-      <c r="C37" s="72"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="74"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="153"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="148"/>
+      <c r="H37" s="145"/>
+      <c r="I37" s="73"/>
+      <c r="J37" s="146"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
       <c r="A38" s="144"/>
-      <c r="B38" s="71"/>
-      <c r="C38" s="72"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="74"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="153"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="148"/>
+      <c r="H38" s="145"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="146"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
       <c r="A39" s="144"/>
-      <c r="B39" s="71"/>
-      <c r="C39" s="72"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="74"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="153"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="148"/>
+      <c r="H39" s="145"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="146"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
       <c r="A40" s="144"/>
-      <c r="B40" s="71"/>
-      <c r="C40" s="72"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="74"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="153"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="148"/>
+      <c r="H40" s="145"/>
+      <c r="I40" s="73"/>
+      <c r="J40" s="146"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
       <c r="A41" s="144"/>
-      <c r="B41" s="71"/>
-      <c r="C41" s="72"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="74"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="153"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="148"/>
+      <c r="H41" s="145"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="146"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14954,50 +14954,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -15014,11 +14975,50 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -15041,19 +15041,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="136" t="s">
+      <c r="E1" s="139"/>
+      <c r="F1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="139"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -15065,190 +15065,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="138" t="s">
+      <c r="E2" s="141"/>
+      <c r="F2" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="121">
+      <c r="G2" s="141"/>
+      <c r="H2" s="123">
         <v>45807</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="125"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="126"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="131"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="126"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="142" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="146" t="s">
+      <c r="B5" s="155"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="156" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="147"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="145" t="s">
+      <c r="A6" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="148"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="131"/>
-      <c r="B8" s="74"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="152"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="131"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="152"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="131"/>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="152"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="131"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="152"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="131"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="152"/>
+      <c r="A12" s="133"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="131"/>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="152"/>
+      <c r="A13" s="133"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="145" t="s">
+      <c r="A14" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="148"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="146"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="147" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="153" t="s">
+      <c r="B15" s="73"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="145" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="74"/>
       <c r="I15" s="14" t="s">
         <v>28</v>
       </c>
@@ -15257,11 +15257,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="147" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="74"/>
       <c r="D16" s="14" t="s">
         <v>30</v>
       </c>
@@ -15274,18 +15274,18 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="148" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="148"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="146"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="144">
         <v>1</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="74"/>
       <c r="D17" s="16" t="s">
         <v>61</v>
       </c>
@@ -15298,83 +15298,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="153" t="s">
+      <c r="H17" s="145" t="s">
         <v>64</v>
       </c>
-      <c r="I17" s="71"/>
-      <c r="J17" s="148"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="146"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="144"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="74"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="153"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="148"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="146"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="144"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="74"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="153"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="148"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="146"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="144"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="74"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="153"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="148"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="146"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="144"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="72"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="74"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="153"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="148"/>
+      <c r="H21" s="145"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="146"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="144"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="72"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="74"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="148"/>
+      <c r="H22" s="145"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="158"/>
-      <c r="B23" s="156"/>
-      <c r="C23" s="159"/>
+      <c r="A23" s="149"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="151"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="155"/>
-      <c r="I23" s="156"/>
-      <c r="J23" s="157"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -16355,22 +16355,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -16386,6 +16370,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -16408,19 +16408,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="136" t="s">
+      <c r="E1" s="139"/>
+      <c r="F1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="139"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -16432,190 +16432,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="138" t="s">
+      <c r="E2" s="141"/>
+      <c r="F2" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="121">
+      <c r="G2" s="141"/>
+      <c r="H2" s="123">
         <v>45805</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="125"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="126"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="131"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="126"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="142" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="146" t="s">
+      <c r="B5" s="155"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="156" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="147"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="145" t="s">
+      <c r="A6" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="148"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="131"/>
-      <c r="B8" s="74"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="152"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="131"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="152"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="131"/>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="152"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="131"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="152"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="131"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="152"/>
+      <c r="A12" s="133"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="131"/>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="152"/>
+      <c r="A13" s="133"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="145" t="s">
+      <c r="A14" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="148"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="146"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="147" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="153" t="s">
+      <c r="B15" s="73"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="145" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="74"/>
       <c r="I15" s="14" t="s">
         <v>28</v>
       </c>
@@ -16624,11 +16624,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="147" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="74"/>
       <c r="D16" s="14" t="s">
         <v>30</v>
       </c>
@@ -16641,18 +16641,18 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="148" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="148"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="146"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="144">
         <v>1</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="74"/>
       <c r="D17" s="16" t="s">
         <v>61</v>
       </c>
@@ -16665,83 +16665,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="153" t="s">
+      <c r="H17" s="145" t="s">
         <v>64</v>
       </c>
-      <c r="I17" s="71"/>
-      <c r="J17" s="148"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="146"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="144"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="74"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="153"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="148"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="146"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="144"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="74"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="153"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="148"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="146"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="144"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="74"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="153"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="148"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="146"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="144"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="72"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="74"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="153"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="148"/>
+      <c r="H21" s="145"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="146"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="144"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="72"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="74"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="148"/>
+      <c r="H22" s="145"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="158"/>
-      <c r="B23" s="156"/>
-      <c r="C23" s="159"/>
+      <c r="A23" s="149"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="151"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="155"/>
-      <c r="I23" s="156"/>
-      <c r="J23" s="157"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -17722,22 +17722,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -17753,6 +17737,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -17772,190 +17772,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="179" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="136" t="s">
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="136" t="s">
+      <c r="L1" s="155"/>
+      <c r="M1" s="155"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="136" t="s">
+      <c r="P1" s="139"/>
+      <c r="Q1" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="137"/>
-      <c r="S1" s="136" t="s">
+      <c r="R1" s="139"/>
+      <c r="S1" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="147"/>
+      <c r="T1" s="157"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="150"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="138" t="s">
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="140" t="s">
         <v>93</v>
       </c>
-      <c r="L2" s="150"/>
-      <c r="M2" s="150"/>
-      <c r="N2" s="139"/>
-      <c r="O2" s="167">
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="177">
         <v>45821</v>
       </c>
-      <c r="P2" s="139"/>
-      <c r="Q2" s="138" t="s">
+      <c r="P2" s="141"/>
+      <c r="Q2" s="140" t="s">
         <v>94</v>
       </c>
-      <c r="R2" s="139"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="151"/>
+      <c r="R2" s="141"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="160"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="132"/>
-      <c r="O3" s="140"/>
-      <c r="P3" s="132"/>
-      <c r="Q3" s="140"/>
-      <c r="R3" s="132"/>
-      <c r="S3" s="140"/>
-      <c r="T3" s="152"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="142"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="134"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="134"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="134"/>
+      <c r="S3" s="142"/>
+      <c r="T3" s="161"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="141"/>
-      <c r="L4" s="134"/>
-      <c r="M4" s="134"/>
-      <c r="N4" s="135"/>
-      <c r="O4" s="141"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="141"/>
-      <c r="R4" s="135"/>
-      <c r="S4" s="141"/>
-      <c r="T4" s="168"/>
+      <c r="A4" s="135"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="136"/>
+      <c r="M4" s="136"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="137"/>
+      <c r="Q4" s="143"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="143"/>
+      <c r="T4" s="178"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="142" t="s">
+      <c r="A5" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="170" t="s">
+      <c r="B5" s="155"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="139"/>
+      <c r="G5" s="168" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="143"/>
-      <c r="L5" s="143"/>
-      <c r="M5" s="143"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="143"/>
-      <c r="P5" s="143"/>
-      <c r="Q5" s="143"/>
-      <c r="R5" s="143"/>
-      <c r="S5" s="143"/>
-      <c r="T5" s="147"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="155"/>
+      <c r="Q5" s="155"/>
+      <c r="R5" s="155"/>
+      <c r="S5" s="155"/>
+      <c r="T5" s="157"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="145" t="s">
+      <c r="A6" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="153" t="s">
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="148"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="73"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="73"/>
+      <c r="T6" s="146"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="145" t="s">
+      <c r="A7" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="153" t="s">
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="145" t="s">
         <v>95</v>
       </c>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="71"/>
-      <c r="T7" s="148"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="73"/>
+      <c r="Q7" s="73"/>
+      <c r="R7" s="73"/>
+      <c r="S7" s="73"/>
+      <c r="T7" s="146"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -18154,37 +18154,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="147" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="173" t="s">
+      <c r="B15" s="74"/>
+      <c r="C15" s="176" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="72"/>
-      <c r="E15" s="154" t="s">
+      <c r="D15" s="74"/>
+      <c r="E15" s="148" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="72"/>
-      <c r="G15" s="154" t="s">
+      <c r="F15" s="74"/>
+      <c r="G15" s="148" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="71"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="154" t="s">
+      <c r="H15" s="73"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="72"/>
-      <c r="L15" s="154" t="s">
+      <c r="K15" s="74"/>
+      <c r="L15" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="71"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="154" t="s">
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="148" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="72"/>
+      <c r="P15" s="73"/>
+      <c r="Q15" s="74"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -18196,37 +18196,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A16" s="171">
+      <c r="A16" s="162">
         <v>1</v>
       </c>
-      <c r="B16" s="72"/>
-      <c r="C16" s="172" t="s">
+      <c r="B16" s="74"/>
+      <c r="C16" s="163" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="72"/>
-      <c r="E16" s="172" t="s">
+      <c r="D16" s="74"/>
+      <c r="E16" s="163" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="72"/>
-      <c r="G16" s="160" t="s">
+      <c r="F16" s="74"/>
+      <c r="G16" s="181" t="s">
         <v>96</v>
       </c>
-      <c r="H16" s="71"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="161" t="s">
+      <c r="H16" s="73"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="172" t="s">
         <v>97</v>
       </c>
-      <c r="K16" s="162"/>
-      <c r="L16" s="164" t="s">
+      <c r="K16" s="170"/>
+      <c r="L16" s="166" t="s">
         <v>98</v>
       </c>
-      <c r="M16" s="71"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="164" t="s">
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="166" t="s">
         <v>99</v>
       </c>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="72"/>
+      <c r="P16" s="73"/>
+      <c r="Q16" s="74"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -18238,37 +18238,37 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A17" s="171">
+      <c r="A17" s="162">
         <v>2</v>
       </c>
-      <c r="B17" s="72"/>
-      <c r="C17" s="172" t="s">
+      <c r="B17" s="74"/>
+      <c r="C17" s="163" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="72"/>
-      <c r="E17" s="172" t="s">
+      <c r="D17" s="74"/>
+      <c r="E17" s="163" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="72"/>
-      <c r="G17" s="160" t="s">
+      <c r="F17" s="74"/>
+      <c r="G17" s="181" t="s">
         <v>105</v>
       </c>
-      <c r="H17" s="71"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="160" t="s">
+      <c r="H17" s="73"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="181" t="s">
         <v>106</v>
       </c>
-      <c r="K17" s="72"/>
-      <c r="L17" s="164" t="s">
+      <c r="K17" s="74"/>
+      <c r="L17" s="166" t="s">
         <v>98</v>
       </c>
-      <c r="M17" s="71"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="164" t="s">
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="166" t="s">
         <v>107</v>
       </c>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="72"/>
+      <c r="P17" s="73"/>
+      <c r="Q17" s="74"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -18280,37 +18280,37 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="64.5" customHeight="1">
-      <c r="A18" s="171">
+      <c r="A18" s="162">
         <v>3</v>
       </c>
-      <c r="B18" s="72"/>
-      <c r="C18" s="172" t="s">
+      <c r="B18" s="74"/>
+      <c r="C18" s="163" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="72"/>
-      <c r="E18" s="172" t="s">
+      <c r="D18" s="74"/>
+      <c r="E18" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="72"/>
-      <c r="G18" s="160" t="s">
+      <c r="F18" s="74"/>
+      <c r="G18" s="181" t="s">
         <v>101</v>
       </c>
-      <c r="H18" s="71"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="160" t="s">
+      <c r="H18" s="73"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="181" t="s">
         <v>103</v>
       </c>
-      <c r="K18" s="72"/>
-      <c r="L18" s="166" t="s">
+      <c r="K18" s="74"/>
+      <c r="L18" s="180" t="s">
         <v>104</v>
       </c>
-      <c r="M18" s="71"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="164" t="s">
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="166" t="s">
         <v>102</v>
       </c>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="72"/>
+      <c r="P18" s="73"/>
+      <c r="Q18" s="74"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -18322,37 +18322,37 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="61.5" customHeight="1">
-      <c r="A19" s="171">
+      <c r="A19" s="162">
         <v>4</v>
       </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="172" t="s">
+      <c r="B19" s="74"/>
+      <c r="C19" s="163" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="72"/>
-      <c r="E19" s="172" t="s">
+      <c r="D19" s="74"/>
+      <c r="E19" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="72"/>
-      <c r="G19" s="160" t="s">
+      <c r="F19" s="74"/>
+      <c r="G19" s="181" t="s">
         <v>139</v>
       </c>
-      <c r="H19" s="71"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="160" t="s">
+      <c r="H19" s="73"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="181" t="s">
         <v>97</v>
       </c>
-      <c r="K19" s="72"/>
-      <c r="L19" s="164" t="s">
+      <c r="K19" s="74"/>
+      <c r="L19" s="166" t="s">
         <v>98</v>
       </c>
-      <c r="M19" s="71"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="164" t="s">
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="166" t="s">
         <v>140</v>
       </c>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="72"/>
+      <c r="P19" s="73"/>
+      <c r="Q19" s="74"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -18364,40 +18364,40 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A20" s="214">
+      <c r="A20" s="169">
         <v>7</v>
       </c>
-      <c r="B20" s="162"/>
-      <c r="C20" s="215" t="s">
+      <c r="B20" s="170"/>
+      <c r="C20" s="171" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="162"/>
-      <c r="E20" s="215" t="s">
+      <c r="D20" s="170"/>
+      <c r="E20" s="171" t="s">
         <v>141</v>
       </c>
-      <c r="F20" s="162"/>
-      <c r="G20" s="161" t="s">
+      <c r="F20" s="170"/>
+      <c r="G20" s="172" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="216"/>
-      <c r="I20" s="162"/>
-      <c r="J20" s="161" t="s">
+      <c r="H20" s="173"/>
+      <c r="I20" s="170"/>
+      <c r="J20" s="172" t="s">
         <v>143</v>
       </c>
-      <c r="K20" s="162"/>
-      <c r="L20" s="217" t="s">
+      <c r="K20" s="170"/>
+      <c r="L20" s="174" t="s">
         <v>145</v>
       </c>
-      <c r="M20" s="218"/>
-      <c r="N20" s="218"/>
-      <c r="O20" s="164" t="s">
+      <c r="M20" s="175"/>
+      <c r="N20" s="175"/>
+      <c r="O20" s="166" t="s">
         <v>144</v>
       </c>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="219"/>
-      <c r="S20" s="219"/>
-      <c r="T20" s="220"/>
+      <c r="P20" s="73"/>
+      <c r="Q20" s="74"/>
+      <c r="R20" s="70"/>
+      <c r="S20" s="70"/>
+      <c r="T20" s="71"/>
       <c r="U20" s="34"/>
       <c r="V20" s="34"/>
       <c r="W20" s="34"/>
@@ -18406,23 +18406,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="171"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="172"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="172"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="160"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="160"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="164"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="164"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="72"/>
+      <c r="A21" s="162"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="163"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="163"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="181"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="181"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="166"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="166"/>
+      <c r="P21" s="73"/>
+      <c r="Q21" s="74"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -18434,23 +18434,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="171"/>
-      <c r="B22" s="72"/>
-      <c r="C22" s="172"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="172"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="160"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="160"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="164"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="164"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="72"/>
+      <c r="A22" s="162"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="163"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="163"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="181"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="181"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="166"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="166"/>
+      <c r="P22" s="73"/>
+      <c r="Q22" s="74"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -18462,23 +18462,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="171"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="172"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="172"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="160"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="160"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="164"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="164"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="72"/>
+      <c r="A23" s="162"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="163"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="163"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="181"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="74"/>
+      <c r="J23" s="181"/>
+      <c r="K23" s="74"/>
+      <c r="L23" s="166"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="166"/>
+      <c r="P23" s="73"/>
+      <c r="Q23" s="74"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -18490,23 +18490,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="171"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="172"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="172"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="160"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="160"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="164"/>
-      <c r="M24" s="71"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="164"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="72"/>
+      <c r="A24" s="162"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="163"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="163"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="181"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="181"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="166"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="166"/>
+      <c r="P24" s="73"/>
+      <c r="Q24" s="74"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -18518,23 +18518,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="171"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="172"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="172"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="160"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="160"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="164"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="164"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="72"/>
+      <c r="A25" s="162"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="163"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="163"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="181"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="181"/>
+      <c r="K25" s="74"/>
+      <c r="L25" s="166"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="166"/>
+      <c r="P25" s="73"/>
+      <c r="Q25" s="74"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -18546,23 +18546,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="171"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="172"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="172"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="160"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="160"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="164"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="72"/>
-      <c r="O26" s="164"/>
-      <c r="P26" s="71"/>
-      <c r="Q26" s="72"/>
+      <c r="A26" s="162"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="163"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="163"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="181"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="181"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="166"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="166"/>
+      <c r="P26" s="73"/>
+      <c r="Q26" s="74"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -18574,23 +18574,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="171"/>
-      <c r="B27" s="72"/>
-      <c r="C27" s="172"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="172"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="160"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="160"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="164"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="72"/>
-      <c r="O27" s="164"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="72"/>
+      <c r="A27" s="162"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="163"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="163"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="181"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="181"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="166"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="166"/>
+      <c r="P27" s="73"/>
+      <c r="Q27" s="74"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -18602,23 +18602,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="171"/>
-      <c r="B28" s="72"/>
-      <c r="C28" s="172"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="172"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="160"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="160"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="164"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="164"/>
-      <c r="P28" s="71"/>
-      <c r="Q28" s="72"/>
+      <c r="A28" s="162"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="163"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="163"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="181"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="181"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="166"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="166"/>
+      <c r="P28" s="73"/>
+      <c r="Q28" s="74"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -18630,23 +18630,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="171"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="172"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="172"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="160"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="164"/>
-      <c r="M29" s="71"/>
-      <c r="N29" s="72"/>
-      <c r="O29" s="164"/>
-      <c r="P29" s="71"/>
-      <c r="Q29" s="72"/>
+      <c r="A29" s="162"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="163"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="163"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="181"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="181"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="166"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="166"/>
+      <c r="P29" s="73"/>
+      <c r="Q29" s="74"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -18658,23 +18658,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="171"/>
-      <c r="B30" s="72"/>
-      <c r="C30" s="172"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="172"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="160"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="160"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="164"/>
-      <c r="M30" s="71"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="164"/>
-      <c r="P30" s="71"/>
-      <c r="Q30" s="72"/>
+      <c r="A30" s="162"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="163"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="163"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="181"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="181"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="166"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="166"/>
+      <c r="P30" s="73"/>
+      <c r="Q30" s="74"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -18686,23 +18686,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="174"/>
-      <c r="B31" s="159"/>
-      <c r="C31" s="175"/>
-      <c r="D31" s="159"/>
-      <c r="E31" s="175"/>
-      <c r="F31" s="159"/>
-      <c r="G31" s="163"/>
-      <c r="H31" s="156"/>
-      <c r="I31" s="159"/>
-      <c r="J31" s="163"/>
-      <c r="K31" s="159"/>
-      <c r="L31" s="165"/>
-      <c r="M31" s="156"/>
-      <c r="N31" s="159"/>
-      <c r="O31" s="165"/>
-      <c r="P31" s="156"/>
-      <c r="Q31" s="159"/>
+      <c r="A31" s="164"/>
+      <c r="B31" s="151"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="151"/>
+      <c r="E31" s="165"/>
+      <c r="F31" s="151"/>
+      <c r="G31" s="182"/>
+      <c r="H31" s="150"/>
+      <c r="I31" s="151"/>
+      <c r="J31" s="182"/>
+      <c r="K31" s="151"/>
+      <c r="L31" s="167"/>
+      <c r="M31" s="150"/>
+      <c r="N31" s="151"/>
+      <c r="O31" s="167"/>
+      <c r="P31" s="150"/>
+      <c r="Q31" s="151"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -19700,6 +19700,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -19724,118 +19836,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
@@ -19862,70 +19862,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="192" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="194" t="s">
+      <c r="B1" s="192"/>
+      <c r="C1" s="193" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="195"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="197" t="s">
+      <c r="D1" s="194"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="196" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="198"/>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="198"/>
-      <c r="K1" s="198"/>
-      <c r="L1" s="198"/>
-      <c r="M1" s="199"/>
+      <c r="G1" s="197"/>
+      <c r="H1" s="197"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="198"/>
       <c r="N1" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="197" t="s">
+      <c r="O1" s="196" t="s">
         <v>94</v>
       </c>
-      <c r="P1" s="199"/>
+      <c r="P1" s="198"/>
       <c r="Q1" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="197" t="s">
+      <c r="R1" s="196" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="199"/>
+      <c r="S1" s="198"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="193"/>
-      <c r="B2" s="193"/>
-      <c r="C2" s="194" t="s">
+      <c r="A2" s="192"/>
+      <c r="B2" s="192"/>
+      <c r="C2" s="193" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="195"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="197" t="s">
+      <c r="D2" s="194"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="196" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
-      <c r="L2" s="198"/>
-      <c r="M2" s="199"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="197"/>
+      <c r="L2" s="197"/>
+      <c r="M2" s="198"/>
       <c r="N2" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="O2" s="200">
+      <c r="O2" s="199">
         <v>45824</v>
       </c>
-      <c r="P2" s="201"/>
+      <c r="P2" s="200"/>
       <c r="Q2" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="R2" s="202"/>
-      <c r="S2" s="203"/>
+      <c r="R2" s="201"/>
+      <c r="S2" s="202"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="43"/>
@@ -19955,33 +19955,33 @@
       <c r="B4" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="183" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="188" t="s">
+      <c r="D4" s="184"/>
+      <c r="E4" s="184"/>
+      <c r="F4" s="184"/>
+      <c r="G4" s="185"/>
+      <c r="H4" s="183" t="s">
         <v>119</v>
       </c>
-      <c r="I4" s="189"/>
-      <c r="J4" s="189"/>
-      <c r="K4" s="189"/>
-      <c r="L4" s="189"/>
-      <c r="M4" s="190"/>
-      <c r="N4" s="188" t="s">
+      <c r="I4" s="184"/>
+      <c r="J4" s="184"/>
+      <c r="K4" s="184"/>
+      <c r="L4" s="184"/>
+      <c r="M4" s="185"/>
+      <c r="N4" s="183" t="s">
         <v>120</v>
       </c>
-      <c r="O4" s="189"/>
-      <c r="P4" s="190"/>
+      <c r="O4" s="184"/>
+      <c r="P4" s="185"/>
       <c r="Q4" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="R4" s="188" t="s">
+      <c r="R4" s="183" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="190"/>
+      <c r="S4" s="185"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="47">
@@ -19990,29 +19990,29 @@
       <c r="B5" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="184" t="s">
+      <c r="C5" s="186" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
-      <c r="F5" s="184"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="184" t="s">
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
+      <c r="H5" s="186" t="s">
         <v>135</v>
       </c>
-      <c r="I5" s="184"/>
-      <c r="J5" s="184"/>
-      <c r="K5" s="184"/>
-      <c r="L5" s="184"/>
-      <c r="M5" s="184"/>
-      <c r="N5" s="185" t="s">
+      <c r="I5" s="186"/>
+      <c r="J5" s="186"/>
+      <c r="K5" s="186"/>
+      <c r="L5" s="186"/>
+      <c r="M5" s="186"/>
+      <c r="N5" s="187" t="s">
         <v>136</v>
       </c>
-      <c r="O5" s="186"/>
-      <c r="P5" s="187"/>
+      <c r="O5" s="188"/>
+      <c r="P5" s="189"/>
       <c r="Q5" s="47"/>
-      <c r="R5" s="191"/>
-      <c r="S5" s="192"/>
+      <c r="R5" s="190"/>
+      <c r="S5" s="191"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="49">
@@ -20021,998 +20021,1186 @@
       <c r="B6" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="184" t="s">
+      <c r="C6" s="186" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="184"/>
-      <c r="G6" s="184"/>
-      <c r="H6" s="184" t="s">
+      <c r="D6" s="186"/>
+      <c r="E6" s="186"/>
+      <c r="F6" s="186"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="186" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="184"/>
-      <c r="J6" s="184"/>
-      <c r="K6" s="184"/>
-      <c r="L6" s="184"/>
-      <c r="M6" s="184"/>
-      <c r="N6" s="185" t="s">
+      <c r="I6" s="186"/>
+      <c r="J6" s="186"/>
+      <c r="K6" s="186"/>
+      <c r="L6" s="186"/>
+      <c r="M6" s="186"/>
+      <c r="N6" s="187" t="s">
         <v>137</v>
       </c>
-      <c r="O6" s="186"/>
-      <c r="P6" s="187"/>
+      <c r="O6" s="188"/>
+      <c r="P6" s="189"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="183"/>
-      <c r="S6" s="183"/>
+      <c r="R6" s="207"/>
+      <c r="S6" s="207"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="49"/>
       <c r="B7" s="49"/>
-      <c r="C7" s="176"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="176"/>
-      <c r="F7" s="176"/>
-      <c r="G7" s="176"/>
-      <c r="H7" s="176"/>
-      <c r="I7" s="176"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="176"/>
-      <c r="L7" s="176"/>
-      <c r="M7" s="176"/>
-      <c r="N7" s="180"/>
-      <c r="O7" s="181"/>
-      <c r="P7" s="182"/>
+      <c r="C7" s="203"/>
+      <c r="D7" s="203"/>
+      <c r="E7" s="203"/>
+      <c r="F7" s="203"/>
+      <c r="G7" s="203"/>
+      <c r="H7" s="203"/>
+      <c r="I7" s="203"/>
+      <c r="J7" s="203"/>
+      <c r="K7" s="203"/>
+      <c r="L7" s="203"/>
+      <c r="M7" s="203"/>
+      <c r="N7" s="204"/>
+      <c r="O7" s="205"/>
+      <c r="P7" s="206"/>
       <c r="Q7" s="51"/>
-      <c r="R7" s="183"/>
-      <c r="S7" s="183"/>
+      <c r="R7" s="207"/>
+      <c r="S7" s="207"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="49"/>
       <c r="B8" s="49"/>
-      <c r="C8" s="176"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="176"/>
-      <c r="F8" s="176"/>
-      <c r="G8" s="176"/>
-      <c r="H8" s="176"/>
-      <c r="I8" s="176"/>
-      <c r="J8" s="176"/>
-      <c r="K8" s="176"/>
-      <c r="L8" s="176"/>
-      <c r="M8" s="176"/>
-      <c r="N8" s="180"/>
-      <c r="O8" s="181"/>
-      <c r="P8" s="182"/>
+      <c r="C8" s="203"/>
+      <c r="D8" s="203"/>
+      <c r="E8" s="203"/>
+      <c r="F8" s="203"/>
+      <c r="G8" s="203"/>
+      <c r="H8" s="203"/>
+      <c r="I8" s="203"/>
+      <c r="J8" s="203"/>
+      <c r="K8" s="203"/>
+      <c r="L8" s="203"/>
+      <c r="M8" s="203"/>
+      <c r="N8" s="204"/>
+      <c r="O8" s="205"/>
+      <c r="P8" s="206"/>
       <c r="Q8" s="51"/>
-      <c r="R8" s="183"/>
-      <c r="S8" s="183"/>
+      <c r="R8" s="207"/>
+      <c r="S8" s="207"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="49"/>
       <c r="B9" s="49"/>
-      <c r="C9" s="176"/>
-      <c r="D9" s="176"/>
-      <c r="E9" s="176"/>
-      <c r="F9" s="176"/>
-      <c r="G9" s="176"/>
-      <c r="H9" s="176"/>
-      <c r="I9" s="176"/>
-      <c r="J9" s="176"/>
-      <c r="K9" s="176"/>
-      <c r="L9" s="176"/>
-      <c r="M9" s="176"/>
-      <c r="N9" s="180"/>
-      <c r="O9" s="181"/>
-      <c r="P9" s="182"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="203"/>
+      <c r="F9" s="203"/>
+      <c r="G9" s="203"/>
+      <c r="H9" s="203"/>
+      <c r="I9" s="203"/>
+      <c r="J9" s="203"/>
+      <c r="K9" s="203"/>
+      <c r="L9" s="203"/>
+      <c r="M9" s="203"/>
+      <c r="N9" s="204"/>
+      <c r="O9" s="205"/>
+      <c r="P9" s="206"/>
       <c r="Q9" s="49"/>
-      <c r="R9" s="183"/>
-      <c r="S9" s="183"/>
+      <c r="R9" s="207"/>
+      <c r="S9" s="207"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="49"/>
       <c r="B10" s="49"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="176"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
-      <c r="H10" s="177"/>
-      <c r="I10" s="178"/>
-      <c r="J10" s="178"/>
-      <c r="K10" s="178"/>
-      <c r="L10" s="178"/>
-      <c r="M10" s="179"/>
-      <c r="N10" s="180"/>
-      <c r="O10" s="181"/>
-      <c r="P10" s="182"/>
+      <c r="C10" s="203"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="203"/>
+      <c r="G10" s="203"/>
+      <c r="H10" s="208"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="209"/>
+      <c r="L10" s="209"/>
+      <c r="M10" s="210"/>
+      <c r="N10" s="204"/>
+      <c r="O10" s="205"/>
+      <c r="P10" s="206"/>
       <c r="Q10" s="51"/>
-      <c r="R10" s="183"/>
-      <c r="S10" s="183"/>
+      <c r="R10" s="207"/>
+      <c r="S10" s="207"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="49"/>
       <c r="B11" s="49"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="176"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="177"/>
-      <c r="I11" s="178"/>
-      <c r="J11" s="178"/>
-      <c r="K11" s="178"/>
-      <c r="L11" s="178"/>
-      <c r="M11" s="179"/>
-      <c r="N11" s="180"/>
-      <c r="O11" s="181"/>
-      <c r="P11" s="182"/>
+      <c r="C11" s="203"/>
+      <c r="D11" s="203"/>
+      <c r="E11" s="203"/>
+      <c r="F11" s="203"/>
+      <c r="G11" s="203"/>
+      <c r="H11" s="208"/>
+      <c r="I11" s="209"/>
+      <c r="J11" s="209"/>
+      <c r="K11" s="209"/>
+      <c r="L11" s="209"/>
+      <c r="M11" s="210"/>
+      <c r="N11" s="204"/>
+      <c r="O11" s="205"/>
+      <c r="P11" s="206"/>
       <c r="Q11" s="49"/>
-      <c r="R11" s="183"/>
-      <c r="S11" s="183"/>
+      <c r="R11" s="207"/>
+      <c r="S11" s="207"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="49"/>
       <c r="B12" s="49"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="177"/>
-      <c r="I12" s="178"/>
-      <c r="J12" s="178"/>
-      <c r="K12" s="178"/>
-      <c r="L12" s="178"/>
-      <c r="M12" s="179"/>
-      <c r="N12" s="180"/>
-      <c r="O12" s="181"/>
-      <c r="P12" s="182"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="203"/>
+      <c r="H12" s="208"/>
+      <c r="I12" s="209"/>
+      <c r="J12" s="209"/>
+      <c r="K12" s="209"/>
+      <c r="L12" s="209"/>
+      <c r="M12" s="210"/>
+      <c r="N12" s="204"/>
+      <c r="O12" s="205"/>
+      <c r="P12" s="206"/>
       <c r="Q12" s="49"/>
-      <c r="R12" s="183"/>
-      <c r="S12" s="183"/>
+      <c r="R12" s="207"/>
+      <c r="S12" s="207"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="49"/>
       <c r="B13" s="49"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="176"/>
-      <c r="H13" s="177"/>
-      <c r="I13" s="178"/>
-      <c r="J13" s="178"/>
-      <c r="K13" s="178"/>
-      <c r="L13" s="178"/>
-      <c r="M13" s="179"/>
-      <c r="N13" s="180"/>
-      <c r="O13" s="181"/>
-      <c r="P13" s="182"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="203"/>
+      <c r="G13" s="203"/>
+      <c r="H13" s="208"/>
+      <c r="I13" s="209"/>
+      <c r="J13" s="209"/>
+      <c r="K13" s="209"/>
+      <c r="L13" s="209"/>
+      <c r="M13" s="210"/>
+      <c r="N13" s="204"/>
+      <c r="O13" s="205"/>
+      <c r="P13" s="206"/>
       <c r="Q13" s="49"/>
-      <c r="R13" s="183"/>
-      <c r="S13" s="183"/>
+      <c r="R13" s="207"/>
+      <c r="S13" s="207"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="49"/>
       <c r="B14" s="49"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176"/>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="176"/>
-      <c r="H14" s="177"/>
-      <c r="I14" s="178"/>
-      <c r="J14" s="178"/>
-      <c r="K14" s="178"/>
-      <c r="L14" s="178"/>
-      <c r="M14" s="179"/>
-      <c r="N14" s="180"/>
-      <c r="O14" s="181"/>
-      <c r="P14" s="182"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="203"/>
+      <c r="H14" s="208"/>
+      <c r="I14" s="209"/>
+      <c r="J14" s="209"/>
+      <c r="K14" s="209"/>
+      <c r="L14" s="209"/>
+      <c r="M14" s="210"/>
+      <c r="N14" s="204"/>
+      <c r="O14" s="205"/>
+      <c r="P14" s="206"/>
       <c r="Q14" s="49"/>
-      <c r="R14" s="183"/>
-      <c r="S14" s="183"/>
+      <c r="R14" s="207"/>
+      <c r="S14" s="207"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="49"/>
       <c r="B15" s="49"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="176"/>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="176"/>
-      <c r="H15" s="177"/>
-      <c r="I15" s="178"/>
-      <c r="J15" s="178"/>
-      <c r="K15" s="178"/>
-      <c r="L15" s="178"/>
-      <c r="M15" s="179"/>
-      <c r="N15" s="180"/>
-      <c r="O15" s="181"/>
-      <c r="P15" s="182"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="203"/>
+      <c r="H15" s="208"/>
+      <c r="I15" s="209"/>
+      <c r="J15" s="209"/>
+      <c r="K15" s="209"/>
+      <c r="L15" s="209"/>
+      <c r="M15" s="210"/>
+      <c r="N15" s="204"/>
+      <c r="O15" s="205"/>
+      <c r="P15" s="206"/>
       <c r="Q15" s="49"/>
-      <c r="R15" s="183"/>
-      <c r="S15" s="183"/>
+      <c r="R15" s="207"/>
+      <c r="S15" s="207"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="49"/>
       <c r="B16" s="49"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="176"/>
-      <c r="E16" s="176"/>
-      <c r="F16" s="176"/>
-      <c r="G16" s="176"/>
-      <c r="H16" s="177"/>
-      <c r="I16" s="178"/>
-      <c r="J16" s="178"/>
-      <c r="K16" s="178"/>
-      <c r="L16" s="178"/>
-      <c r="M16" s="179"/>
-      <c r="N16" s="180"/>
-      <c r="O16" s="181"/>
-      <c r="P16" s="182"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
+      <c r="F16" s="203"/>
+      <c r="G16" s="203"/>
+      <c r="H16" s="208"/>
+      <c r="I16" s="209"/>
+      <c r="J16" s="209"/>
+      <c r="K16" s="209"/>
+      <c r="L16" s="209"/>
+      <c r="M16" s="210"/>
+      <c r="N16" s="204"/>
+      <c r="O16" s="205"/>
+      <c r="P16" s="206"/>
       <c r="Q16" s="49"/>
-      <c r="R16" s="183"/>
-      <c r="S16" s="183"/>
+      <c r="R16" s="207"/>
+      <c r="S16" s="207"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="49"/>
       <c r="B17" s="49"/>
-      <c r="C17" s="176"/>
-      <c r="D17" s="176"/>
-      <c r="E17" s="176"/>
-      <c r="F17" s="176"/>
-      <c r="G17" s="176"/>
-      <c r="H17" s="177"/>
-      <c r="I17" s="178"/>
-      <c r="J17" s="178"/>
-      <c r="K17" s="178"/>
-      <c r="L17" s="178"/>
-      <c r="M17" s="179"/>
-      <c r="N17" s="180"/>
-      <c r="O17" s="181"/>
-      <c r="P17" s="182"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="203"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="203"/>
+      <c r="G17" s="203"/>
+      <c r="H17" s="208"/>
+      <c r="I17" s="209"/>
+      <c r="J17" s="209"/>
+      <c r="K17" s="209"/>
+      <c r="L17" s="209"/>
+      <c r="M17" s="210"/>
+      <c r="N17" s="204"/>
+      <c r="O17" s="205"/>
+      <c r="P17" s="206"/>
       <c r="Q17" s="49"/>
-      <c r="R17" s="183"/>
-      <c r="S17" s="183"/>
+      <c r="R17" s="207"/>
+      <c r="S17" s="207"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="49"/>
       <c r="B18" s="49"/>
-      <c r="C18" s="176"/>
-      <c r="D18" s="176"/>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
-      <c r="G18" s="176"/>
-      <c r="H18" s="177"/>
-      <c r="I18" s="178"/>
-      <c r="J18" s="178"/>
-      <c r="K18" s="178"/>
-      <c r="L18" s="178"/>
-      <c r="M18" s="179"/>
-      <c r="N18" s="180"/>
-      <c r="O18" s="181"/>
-      <c r="P18" s="182"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="203"/>
+      <c r="G18" s="203"/>
+      <c r="H18" s="208"/>
+      <c r="I18" s="209"/>
+      <c r="J18" s="209"/>
+      <c r="K18" s="209"/>
+      <c r="L18" s="209"/>
+      <c r="M18" s="210"/>
+      <c r="N18" s="204"/>
+      <c r="O18" s="205"/>
+      <c r="P18" s="206"/>
       <c r="Q18" s="49"/>
-      <c r="R18" s="183"/>
-      <c r="S18" s="183"/>
+      <c r="R18" s="207"/>
+      <c r="S18" s="207"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="49"/>
       <c r="B19" s="49"/>
-      <c r="C19" s="176"/>
-      <c r="D19" s="176"/>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
-      <c r="G19" s="176"/>
-      <c r="H19" s="177"/>
-      <c r="I19" s="178"/>
-      <c r="J19" s="178"/>
-      <c r="K19" s="178"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="179"/>
-      <c r="N19" s="180"/>
-      <c r="O19" s="181"/>
-      <c r="P19" s="182"/>
+      <c r="C19" s="203"/>
+      <c r="D19" s="203"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="203"/>
+      <c r="G19" s="203"/>
+      <c r="H19" s="208"/>
+      <c r="I19" s="209"/>
+      <c r="J19" s="209"/>
+      <c r="K19" s="209"/>
+      <c r="L19" s="209"/>
+      <c r="M19" s="210"/>
+      <c r="N19" s="204"/>
+      <c r="O19" s="205"/>
+      <c r="P19" s="206"/>
       <c r="Q19" s="49"/>
-      <c r="R19" s="183"/>
-      <c r="S19" s="183"/>
+      <c r="R19" s="207"/>
+      <c r="S19" s="207"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="49"/>
       <c r="B20" s="49"/>
-      <c r="C20" s="176"/>
-      <c r="D20" s="176"/>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
-      <c r="G20" s="176"/>
-      <c r="H20" s="177"/>
-      <c r="I20" s="178"/>
-      <c r="J20" s="178"/>
-      <c r="K20" s="178"/>
-      <c r="L20" s="178"/>
-      <c r="M20" s="179"/>
-      <c r="N20" s="180"/>
-      <c r="O20" s="181"/>
-      <c r="P20" s="182"/>
+      <c r="C20" s="203"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="203"/>
+      <c r="F20" s="203"/>
+      <c r="G20" s="203"/>
+      <c r="H20" s="208"/>
+      <c r="I20" s="209"/>
+      <c r="J20" s="209"/>
+      <c r="K20" s="209"/>
+      <c r="L20" s="209"/>
+      <c r="M20" s="210"/>
+      <c r="N20" s="204"/>
+      <c r="O20" s="205"/>
+      <c r="P20" s="206"/>
       <c r="Q20" s="49"/>
-      <c r="R20" s="183"/>
-      <c r="S20" s="183"/>
+      <c r="R20" s="207"/>
+      <c r="S20" s="207"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="49"/>
       <c r="B21" s="49"/>
-      <c r="C21" s="176"/>
-      <c r="D21" s="176"/>
-      <c r="E21" s="176"/>
-      <c r="F21" s="176"/>
-      <c r="G21" s="176"/>
-      <c r="H21" s="177"/>
-      <c r="I21" s="178"/>
-      <c r="J21" s="178"/>
-      <c r="K21" s="178"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="179"/>
-      <c r="N21" s="180"/>
-      <c r="O21" s="181"/>
-      <c r="P21" s="182"/>
+      <c r="C21" s="203"/>
+      <c r="D21" s="203"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="203"/>
+      <c r="G21" s="203"/>
+      <c r="H21" s="208"/>
+      <c r="I21" s="209"/>
+      <c r="J21" s="209"/>
+      <c r="K21" s="209"/>
+      <c r="L21" s="209"/>
+      <c r="M21" s="210"/>
+      <c r="N21" s="204"/>
+      <c r="O21" s="205"/>
+      <c r="P21" s="206"/>
       <c r="Q21" s="49"/>
-      <c r="R21" s="183"/>
-      <c r="S21" s="183"/>
+      <c r="R21" s="207"/>
+      <c r="S21" s="207"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="49"/>
       <c r="B22" s="49"/>
-      <c r="C22" s="176"/>
-      <c r="D22" s="176"/>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
-      <c r="G22" s="176"/>
-      <c r="H22" s="177"/>
-      <c r="I22" s="178"/>
-      <c r="J22" s="178"/>
-      <c r="K22" s="178"/>
-      <c r="L22" s="178"/>
-      <c r="M22" s="179"/>
-      <c r="N22" s="180"/>
-      <c r="O22" s="181"/>
-      <c r="P22" s="182"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="203"/>
+      <c r="G22" s="203"/>
+      <c r="H22" s="208"/>
+      <c r="I22" s="209"/>
+      <c r="J22" s="209"/>
+      <c r="K22" s="209"/>
+      <c r="L22" s="209"/>
+      <c r="M22" s="210"/>
+      <c r="N22" s="204"/>
+      <c r="O22" s="205"/>
+      <c r="P22" s="206"/>
       <c r="Q22" s="49"/>
-      <c r="R22" s="183"/>
-      <c r="S22" s="183"/>
+      <c r="R22" s="207"/>
+      <c r="S22" s="207"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="49"/>
       <c r="B23" s="49"/>
-      <c r="C23" s="176"/>
-      <c r="D23" s="176"/>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
-      <c r="G23" s="176"/>
-      <c r="H23" s="177"/>
-      <c r="I23" s="178"/>
-      <c r="J23" s="178"/>
-      <c r="K23" s="178"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="179"/>
-      <c r="N23" s="180"/>
-      <c r="O23" s="181"/>
-      <c r="P23" s="182"/>
+      <c r="C23" s="203"/>
+      <c r="D23" s="203"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="203"/>
+      <c r="G23" s="203"/>
+      <c r="H23" s="208"/>
+      <c r="I23" s="209"/>
+      <c r="J23" s="209"/>
+      <c r="K23" s="209"/>
+      <c r="L23" s="209"/>
+      <c r="M23" s="210"/>
+      <c r="N23" s="204"/>
+      <c r="O23" s="205"/>
+      <c r="P23" s="206"/>
       <c r="Q23" s="49"/>
-      <c r="R23" s="183"/>
-      <c r="S23" s="183"/>
+      <c r="R23" s="207"/>
+      <c r="S23" s="207"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="49"/>
       <c r="B24" s="49"/>
-      <c r="C24" s="176"/>
-      <c r="D24" s="176"/>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
-      <c r="G24" s="176"/>
-      <c r="H24" s="177"/>
-      <c r="I24" s="178"/>
-      <c r="J24" s="178"/>
-      <c r="K24" s="178"/>
-      <c r="L24" s="178"/>
-      <c r="M24" s="179"/>
-      <c r="N24" s="180"/>
-      <c r="O24" s="181"/>
-      <c r="P24" s="182"/>
+      <c r="C24" s="203"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="203"/>
+      <c r="F24" s="203"/>
+      <c r="G24" s="203"/>
+      <c r="H24" s="208"/>
+      <c r="I24" s="209"/>
+      <c r="J24" s="209"/>
+      <c r="K24" s="209"/>
+      <c r="L24" s="209"/>
+      <c r="M24" s="210"/>
+      <c r="N24" s="204"/>
+      <c r="O24" s="205"/>
+      <c r="P24" s="206"/>
       <c r="Q24" s="49"/>
-      <c r="R24" s="183"/>
-      <c r="S24" s="183"/>
+      <c r="R24" s="207"/>
+      <c r="S24" s="207"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="49"/>
       <c r="B25" s="49"/>
-      <c r="C25" s="176"/>
-      <c r="D25" s="176"/>
-      <c r="E25" s="176"/>
-      <c r="F25" s="176"/>
-      <c r="G25" s="176"/>
-      <c r="H25" s="177"/>
-      <c r="I25" s="178"/>
-      <c r="J25" s="178"/>
-      <c r="K25" s="178"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="179"/>
-      <c r="N25" s="180"/>
-      <c r="O25" s="181"/>
-      <c r="P25" s="182"/>
+      <c r="C25" s="203"/>
+      <c r="D25" s="203"/>
+      <c r="E25" s="203"/>
+      <c r="F25" s="203"/>
+      <c r="G25" s="203"/>
+      <c r="H25" s="208"/>
+      <c r="I25" s="209"/>
+      <c r="J25" s="209"/>
+      <c r="K25" s="209"/>
+      <c r="L25" s="209"/>
+      <c r="M25" s="210"/>
+      <c r="N25" s="204"/>
+      <c r="O25" s="205"/>
+      <c r="P25" s="206"/>
       <c r="Q25" s="49"/>
-      <c r="R25" s="183"/>
-      <c r="S25" s="183"/>
+      <c r="R25" s="207"/>
+      <c r="S25" s="207"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="49"/>
       <c r="B26" s="49"/>
-      <c r="C26" s="176"/>
-      <c r="D26" s="176"/>
-      <c r="E26" s="176"/>
-      <c r="F26" s="176"/>
-      <c r="G26" s="176"/>
-      <c r="H26" s="177"/>
-      <c r="I26" s="178"/>
-      <c r="J26" s="178"/>
-      <c r="K26" s="178"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="179"/>
-      <c r="N26" s="180"/>
-      <c r="O26" s="181"/>
-      <c r="P26" s="182"/>
+      <c r="C26" s="203"/>
+      <c r="D26" s="203"/>
+      <c r="E26" s="203"/>
+      <c r="F26" s="203"/>
+      <c r="G26" s="203"/>
+      <c r="H26" s="208"/>
+      <c r="I26" s="209"/>
+      <c r="J26" s="209"/>
+      <c r="K26" s="209"/>
+      <c r="L26" s="209"/>
+      <c r="M26" s="210"/>
+      <c r="N26" s="204"/>
+      <c r="O26" s="205"/>
+      <c r="P26" s="206"/>
       <c r="Q26" s="49"/>
-      <c r="R26" s="183"/>
-      <c r="S26" s="183"/>
+      <c r="R26" s="207"/>
+      <c r="S26" s="207"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="49"/>
       <c r="B27" s="49"/>
-      <c r="C27" s="176"/>
-      <c r="D27" s="176"/>
-      <c r="E27" s="176"/>
-      <c r="F27" s="176"/>
-      <c r="G27" s="176"/>
-      <c r="H27" s="177"/>
-      <c r="I27" s="178"/>
-      <c r="J27" s="178"/>
-      <c r="K27" s="178"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="179"/>
-      <c r="N27" s="180"/>
-      <c r="O27" s="181"/>
-      <c r="P27" s="182"/>
+      <c r="C27" s="203"/>
+      <c r="D27" s="203"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="203"/>
+      <c r="G27" s="203"/>
+      <c r="H27" s="208"/>
+      <c r="I27" s="209"/>
+      <c r="J27" s="209"/>
+      <c r="K27" s="209"/>
+      <c r="L27" s="209"/>
+      <c r="M27" s="210"/>
+      <c r="N27" s="204"/>
+      <c r="O27" s="205"/>
+      <c r="P27" s="206"/>
       <c r="Q27" s="49"/>
-      <c r="R27" s="183"/>
-      <c r="S27" s="183"/>
+      <c r="R27" s="207"/>
+      <c r="S27" s="207"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="49"/>
       <c r="B28" s="49"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="176"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
-      <c r="G28" s="176"/>
-      <c r="H28" s="177"/>
-      <c r="I28" s="178"/>
-      <c r="J28" s="178"/>
-      <c r="K28" s="178"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="179"/>
-      <c r="N28" s="180"/>
-      <c r="O28" s="181"/>
-      <c r="P28" s="182"/>
+      <c r="C28" s="203"/>
+      <c r="D28" s="203"/>
+      <c r="E28" s="203"/>
+      <c r="F28" s="203"/>
+      <c r="G28" s="203"/>
+      <c r="H28" s="208"/>
+      <c r="I28" s="209"/>
+      <c r="J28" s="209"/>
+      <c r="K28" s="209"/>
+      <c r="L28" s="209"/>
+      <c r="M28" s="210"/>
+      <c r="N28" s="204"/>
+      <c r="O28" s="205"/>
+      <c r="P28" s="206"/>
       <c r="Q28" s="49"/>
-      <c r="R28" s="183"/>
-      <c r="S28" s="183"/>
+      <c r="R28" s="207"/>
+      <c r="S28" s="207"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="49"/>
       <c r="B29" s="49"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="176"/>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
-      <c r="G29" s="176"/>
-      <c r="H29" s="177"/>
-      <c r="I29" s="178"/>
-      <c r="J29" s="178"/>
-      <c r="K29" s="178"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="179"/>
-      <c r="N29" s="180"/>
-      <c r="O29" s="181"/>
-      <c r="P29" s="182"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="203"/>
+      <c r="H29" s="208"/>
+      <c r="I29" s="209"/>
+      <c r="J29" s="209"/>
+      <c r="K29" s="209"/>
+      <c r="L29" s="209"/>
+      <c r="M29" s="210"/>
+      <c r="N29" s="204"/>
+      <c r="O29" s="205"/>
+      <c r="P29" s="206"/>
       <c r="Q29" s="49"/>
-      <c r="R29" s="183"/>
-      <c r="S29" s="183"/>
+      <c r="R29" s="207"/>
+      <c r="S29" s="207"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="49"/>
       <c r="B30" s="49"/>
-      <c r="C30" s="176"/>
-      <c r="D30" s="176"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="176"/>
-      <c r="G30" s="176"/>
-      <c r="H30" s="177"/>
-      <c r="I30" s="178"/>
-      <c r="J30" s="178"/>
-      <c r="K30" s="178"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="179"/>
-      <c r="N30" s="180"/>
-      <c r="O30" s="181"/>
-      <c r="P30" s="182"/>
+      <c r="C30" s="203"/>
+      <c r="D30" s="203"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="203"/>
+      <c r="G30" s="203"/>
+      <c r="H30" s="208"/>
+      <c r="I30" s="209"/>
+      <c r="J30" s="209"/>
+      <c r="K30" s="209"/>
+      <c r="L30" s="209"/>
+      <c r="M30" s="210"/>
+      <c r="N30" s="204"/>
+      <c r="O30" s="205"/>
+      <c r="P30" s="206"/>
       <c r="Q30" s="49"/>
-      <c r="R30" s="183"/>
-      <c r="S30" s="183"/>
+      <c r="R30" s="207"/>
+      <c r="S30" s="207"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="49"/>
       <c r="B31" s="49"/>
-      <c r="C31" s="176"/>
-      <c r="D31" s="176"/>
-      <c r="E31" s="176"/>
-      <c r="F31" s="176"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="177"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="178"/>
-      <c r="K31" s="178"/>
-      <c r="L31" s="178"/>
-      <c r="M31" s="179"/>
-      <c r="N31" s="180"/>
-      <c r="O31" s="181"/>
-      <c r="P31" s="182"/>
+      <c r="C31" s="203"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="203"/>
+      <c r="H31" s="208"/>
+      <c r="I31" s="209"/>
+      <c r="J31" s="209"/>
+      <c r="K31" s="209"/>
+      <c r="L31" s="209"/>
+      <c r="M31" s="210"/>
+      <c r="N31" s="204"/>
+      <c r="O31" s="205"/>
+      <c r="P31" s="206"/>
       <c r="Q31" s="49"/>
-      <c r="R31" s="183"/>
-      <c r="S31" s="183"/>
+      <c r="R31" s="207"/>
+      <c r="S31" s="207"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="49"/>
       <c r="B32" s="49"/>
-      <c r="C32" s="176"/>
-      <c r="D32" s="176"/>
-      <c r="E32" s="176"/>
-      <c r="F32" s="176"/>
-      <c r="G32" s="176"/>
-      <c r="H32" s="177"/>
-      <c r="I32" s="178"/>
-      <c r="J32" s="178"/>
-      <c r="K32" s="178"/>
-      <c r="L32" s="178"/>
-      <c r="M32" s="179"/>
-      <c r="N32" s="180"/>
-      <c r="O32" s="181"/>
-      <c r="P32" s="182"/>
+      <c r="C32" s="203"/>
+      <c r="D32" s="203"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="203"/>
+      <c r="G32" s="203"/>
+      <c r="H32" s="208"/>
+      <c r="I32" s="209"/>
+      <c r="J32" s="209"/>
+      <c r="K32" s="209"/>
+      <c r="L32" s="209"/>
+      <c r="M32" s="210"/>
+      <c r="N32" s="204"/>
+      <c r="O32" s="205"/>
+      <c r="P32" s="206"/>
       <c r="Q32" s="49"/>
-      <c r="R32" s="183"/>
-      <c r="S32" s="183"/>
+      <c r="R32" s="207"/>
+      <c r="S32" s="207"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="49"/>
       <c r="B33" s="49"/>
-      <c r="C33" s="176"/>
-      <c r="D33" s="176"/>
-      <c r="E33" s="176"/>
-      <c r="F33" s="176"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="177"/>
-      <c r="I33" s="178"/>
-      <c r="J33" s="178"/>
-      <c r="K33" s="178"/>
-      <c r="L33" s="178"/>
-      <c r="M33" s="179"/>
-      <c r="N33" s="180"/>
-      <c r="O33" s="181"/>
-      <c r="P33" s="182"/>
+      <c r="C33" s="203"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="203"/>
+      <c r="H33" s="208"/>
+      <c r="I33" s="209"/>
+      <c r="J33" s="209"/>
+      <c r="K33" s="209"/>
+      <c r="L33" s="209"/>
+      <c r="M33" s="210"/>
+      <c r="N33" s="204"/>
+      <c r="O33" s="205"/>
+      <c r="P33" s="206"/>
       <c r="Q33" s="49"/>
-      <c r="R33" s="183"/>
-      <c r="S33" s="183"/>
+      <c r="R33" s="207"/>
+      <c r="S33" s="207"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="49"/>
       <c r="B34" s="49"/>
-      <c r="C34" s="176"/>
-      <c r="D34" s="176"/>
-      <c r="E34" s="176"/>
-      <c r="F34" s="176"/>
-      <c r="G34" s="176"/>
-      <c r="H34" s="177"/>
-      <c r="I34" s="178"/>
-      <c r="J34" s="178"/>
-      <c r="K34" s="178"/>
-      <c r="L34" s="178"/>
-      <c r="M34" s="179"/>
-      <c r="N34" s="180"/>
-      <c r="O34" s="181"/>
-      <c r="P34" s="182"/>
+      <c r="C34" s="203"/>
+      <c r="D34" s="203"/>
+      <c r="E34" s="203"/>
+      <c r="F34" s="203"/>
+      <c r="G34" s="203"/>
+      <c r="H34" s="208"/>
+      <c r="I34" s="209"/>
+      <c r="J34" s="209"/>
+      <c r="K34" s="209"/>
+      <c r="L34" s="209"/>
+      <c r="M34" s="210"/>
+      <c r="N34" s="204"/>
+      <c r="O34" s="205"/>
+      <c r="P34" s="206"/>
       <c r="Q34" s="49"/>
-      <c r="R34" s="183"/>
-      <c r="S34" s="183"/>
+      <c r="R34" s="207"/>
+      <c r="S34" s="207"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
-      <c r="C35" s="176"/>
-      <c r="D35" s="176"/>
-      <c r="E35" s="176"/>
-      <c r="F35" s="176"/>
-      <c r="G35" s="176"/>
-      <c r="H35" s="177"/>
-      <c r="I35" s="178"/>
-      <c r="J35" s="178"/>
-      <c r="K35" s="178"/>
-      <c r="L35" s="178"/>
-      <c r="M35" s="179"/>
-      <c r="N35" s="180"/>
-      <c r="O35" s="181"/>
-      <c r="P35" s="182"/>
+      <c r="C35" s="203"/>
+      <c r="D35" s="203"/>
+      <c r="E35" s="203"/>
+      <c r="F35" s="203"/>
+      <c r="G35" s="203"/>
+      <c r="H35" s="208"/>
+      <c r="I35" s="209"/>
+      <c r="J35" s="209"/>
+      <c r="K35" s="209"/>
+      <c r="L35" s="209"/>
+      <c r="M35" s="210"/>
+      <c r="N35" s="204"/>
+      <c r="O35" s="205"/>
+      <c r="P35" s="206"/>
       <c r="Q35" s="49"/>
-      <c r="R35" s="183"/>
-      <c r="S35" s="183"/>
+      <c r="R35" s="207"/>
+      <c r="S35" s="207"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="49"/>
       <c r="B36" s="49"/>
-      <c r="C36" s="176"/>
-      <c r="D36" s="176"/>
-      <c r="E36" s="176"/>
-      <c r="F36" s="176"/>
-      <c r="G36" s="176"/>
-      <c r="H36" s="177"/>
-      <c r="I36" s="178"/>
-      <c r="J36" s="178"/>
-      <c r="K36" s="178"/>
-      <c r="L36" s="178"/>
-      <c r="M36" s="179"/>
-      <c r="N36" s="180"/>
-      <c r="O36" s="181"/>
-      <c r="P36" s="182"/>
+      <c r="C36" s="203"/>
+      <c r="D36" s="203"/>
+      <c r="E36" s="203"/>
+      <c r="F36" s="203"/>
+      <c r="G36" s="203"/>
+      <c r="H36" s="208"/>
+      <c r="I36" s="209"/>
+      <c r="J36" s="209"/>
+      <c r="K36" s="209"/>
+      <c r="L36" s="209"/>
+      <c r="M36" s="210"/>
+      <c r="N36" s="204"/>
+      <c r="O36" s="205"/>
+      <c r="P36" s="206"/>
       <c r="Q36" s="49"/>
-      <c r="R36" s="183"/>
-      <c r="S36" s="183"/>
+      <c r="R36" s="207"/>
+      <c r="S36" s="207"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="49"/>
       <c r="B37" s="49"/>
-      <c r="C37" s="176"/>
-      <c r="D37" s="176"/>
-      <c r="E37" s="176"/>
-      <c r="F37" s="176"/>
-      <c r="G37" s="176"/>
-      <c r="H37" s="177"/>
-      <c r="I37" s="178"/>
-      <c r="J37" s="178"/>
-      <c r="K37" s="178"/>
-      <c r="L37" s="178"/>
-      <c r="M37" s="179"/>
-      <c r="N37" s="180"/>
-      <c r="O37" s="181"/>
-      <c r="P37" s="182"/>
+      <c r="C37" s="203"/>
+      <c r="D37" s="203"/>
+      <c r="E37" s="203"/>
+      <c r="F37" s="203"/>
+      <c r="G37" s="203"/>
+      <c r="H37" s="208"/>
+      <c r="I37" s="209"/>
+      <c r="J37" s="209"/>
+      <c r="K37" s="209"/>
+      <c r="L37" s="209"/>
+      <c r="M37" s="210"/>
+      <c r="N37" s="204"/>
+      <c r="O37" s="205"/>
+      <c r="P37" s="206"/>
       <c r="Q37" s="49"/>
-      <c r="R37" s="183"/>
-      <c r="S37" s="183"/>
+      <c r="R37" s="207"/>
+      <c r="S37" s="207"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="49"/>
       <c r="B38" s="49"/>
-      <c r="C38" s="176"/>
-      <c r="D38" s="176"/>
-      <c r="E38" s="176"/>
-      <c r="F38" s="176"/>
-      <c r="G38" s="176"/>
-      <c r="H38" s="177"/>
-      <c r="I38" s="178"/>
-      <c r="J38" s="178"/>
-      <c r="K38" s="178"/>
-      <c r="L38" s="178"/>
-      <c r="M38" s="179"/>
-      <c r="N38" s="180"/>
-      <c r="O38" s="181"/>
-      <c r="P38" s="182"/>
+      <c r="C38" s="203"/>
+      <c r="D38" s="203"/>
+      <c r="E38" s="203"/>
+      <c r="F38" s="203"/>
+      <c r="G38" s="203"/>
+      <c r="H38" s="208"/>
+      <c r="I38" s="209"/>
+      <c r="J38" s="209"/>
+      <c r="K38" s="209"/>
+      <c r="L38" s="209"/>
+      <c r="M38" s="210"/>
+      <c r="N38" s="204"/>
+      <c r="O38" s="205"/>
+      <c r="P38" s="206"/>
       <c r="Q38" s="49"/>
-      <c r="R38" s="183"/>
-      <c r="S38" s="183"/>
+      <c r="R38" s="207"/>
+      <c r="S38" s="207"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="49"/>
       <c r="B39" s="49"/>
-      <c r="C39" s="176"/>
-      <c r="D39" s="176"/>
-      <c r="E39" s="176"/>
-      <c r="F39" s="176"/>
-      <c r="G39" s="176"/>
-      <c r="H39" s="177"/>
-      <c r="I39" s="178"/>
-      <c r="J39" s="178"/>
-      <c r="K39" s="178"/>
-      <c r="L39" s="178"/>
-      <c r="M39" s="179"/>
-      <c r="N39" s="180"/>
-      <c r="O39" s="181"/>
-      <c r="P39" s="182"/>
+      <c r="C39" s="203"/>
+      <c r="D39" s="203"/>
+      <c r="E39" s="203"/>
+      <c r="F39" s="203"/>
+      <c r="G39" s="203"/>
+      <c r="H39" s="208"/>
+      <c r="I39" s="209"/>
+      <c r="J39" s="209"/>
+      <c r="K39" s="209"/>
+      <c r="L39" s="209"/>
+      <c r="M39" s="210"/>
+      <c r="N39" s="204"/>
+      <c r="O39" s="205"/>
+      <c r="P39" s="206"/>
       <c r="Q39" s="49"/>
-      <c r="R39" s="183"/>
-      <c r="S39" s="183"/>
+      <c r="R39" s="207"/>
+      <c r="S39" s="207"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="49"/>
       <c r="B40" s="49"/>
-      <c r="C40" s="176"/>
-      <c r="D40" s="176"/>
-      <c r="E40" s="176"/>
-      <c r="F40" s="176"/>
-      <c r="G40" s="176"/>
-      <c r="H40" s="177"/>
-      <c r="I40" s="178"/>
-      <c r="J40" s="178"/>
-      <c r="K40" s="178"/>
-      <c r="L40" s="178"/>
-      <c r="M40" s="179"/>
-      <c r="N40" s="180"/>
-      <c r="O40" s="181"/>
-      <c r="P40" s="182"/>
+      <c r="C40" s="203"/>
+      <c r="D40" s="203"/>
+      <c r="E40" s="203"/>
+      <c r="F40" s="203"/>
+      <c r="G40" s="203"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="209"/>
+      <c r="J40" s="209"/>
+      <c r="K40" s="209"/>
+      <c r="L40" s="209"/>
+      <c r="M40" s="210"/>
+      <c r="N40" s="204"/>
+      <c r="O40" s="205"/>
+      <c r="P40" s="206"/>
       <c r="Q40" s="49"/>
-      <c r="R40" s="183"/>
-      <c r="S40" s="183"/>
+      <c r="R40" s="207"/>
+      <c r="S40" s="207"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="49"/>
       <c r="B41" s="49"/>
-      <c r="C41" s="176"/>
-      <c r="D41" s="176"/>
-      <c r="E41" s="176"/>
-      <c r="F41" s="176"/>
-      <c r="G41" s="176"/>
-      <c r="H41" s="177"/>
-      <c r="I41" s="178"/>
-      <c r="J41" s="178"/>
-      <c r="K41" s="178"/>
-      <c r="L41" s="178"/>
-      <c r="M41" s="179"/>
-      <c r="N41" s="180"/>
-      <c r="O41" s="181"/>
-      <c r="P41" s="182"/>
+      <c r="C41" s="203"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="203"/>
+      <c r="F41" s="203"/>
+      <c r="G41" s="203"/>
+      <c r="H41" s="208"/>
+      <c r="I41" s="209"/>
+      <c r="J41" s="209"/>
+      <c r="K41" s="209"/>
+      <c r="L41" s="209"/>
+      <c r="M41" s="210"/>
+      <c r="N41" s="204"/>
+      <c r="O41" s="205"/>
+      <c r="P41" s="206"/>
       <c r="Q41" s="49"/>
-      <c r="R41" s="183"/>
-      <c r="S41" s="183"/>
+      <c r="R41" s="207"/>
+      <c r="S41" s="207"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="49"/>
       <c r="B42" s="49"/>
-      <c r="C42" s="176"/>
-      <c r="D42" s="176"/>
-      <c r="E42" s="176"/>
-      <c r="F42" s="176"/>
-      <c r="G42" s="176"/>
-      <c r="H42" s="177"/>
-      <c r="I42" s="178"/>
-      <c r="J42" s="178"/>
-      <c r="K42" s="178"/>
-      <c r="L42" s="178"/>
-      <c r="M42" s="179"/>
-      <c r="N42" s="180"/>
-      <c r="O42" s="181"/>
-      <c r="P42" s="182"/>
+      <c r="C42" s="203"/>
+      <c r="D42" s="203"/>
+      <c r="E42" s="203"/>
+      <c r="F42" s="203"/>
+      <c r="G42" s="203"/>
+      <c r="H42" s="208"/>
+      <c r="I42" s="209"/>
+      <c r="J42" s="209"/>
+      <c r="K42" s="209"/>
+      <c r="L42" s="209"/>
+      <c r="M42" s="210"/>
+      <c r="N42" s="204"/>
+      <c r="O42" s="205"/>
+      <c r="P42" s="206"/>
       <c r="Q42" s="49"/>
-      <c r="R42" s="183"/>
-      <c r="S42" s="183"/>
+      <c r="R42" s="207"/>
+      <c r="S42" s="207"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="49"/>
       <c r="B43" s="49"/>
-      <c r="C43" s="176"/>
-      <c r="D43" s="176"/>
-      <c r="E43" s="176"/>
-      <c r="F43" s="176"/>
-      <c r="G43" s="176"/>
-      <c r="H43" s="177"/>
-      <c r="I43" s="178"/>
-      <c r="J43" s="178"/>
-      <c r="K43" s="178"/>
-      <c r="L43" s="178"/>
-      <c r="M43" s="179"/>
-      <c r="N43" s="180"/>
-      <c r="O43" s="181"/>
-      <c r="P43" s="182"/>
+      <c r="C43" s="203"/>
+      <c r="D43" s="203"/>
+      <c r="E43" s="203"/>
+      <c r="F43" s="203"/>
+      <c r="G43" s="203"/>
+      <c r="H43" s="208"/>
+      <c r="I43" s="209"/>
+      <c r="J43" s="209"/>
+      <c r="K43" s="209"/>
+      <c r="L43" s="209"/>
+      <c r="M43" s="210"/>
+      <c r="N43" s="204"/>
+      <c r="O43" s="205"/>
+      <c r="P43" s="206"/>
       <c r="Q43" s="49"/>
-      <c r="R43" s="183"/>
-      <c r="S43" s="183"/>
+      <c r="R43" s="207"/>
+      <c r="S43" s="207"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="49"/>
       <c r="B44" s="49"/>
-      <c r="C44" s="176"/>
-      <c r="D44" s="176"/>
-      <c r="E44" s="176"/>
-      <c r="F44" s="176"/>
-      <c r="G44" s="176"/>
-      <c r="H44" s="177"/>
-      <c r="I44" s="178"/>
-      <c r="J44" s="178"/>
-      <c r="K44" s="178"/>
-      <c r="L44" s="178"/>
-      <c r="M44" s="179"/>
-      <c r="N44" s="180"/>
-      <c r="O44" s="181"/>
-      <c r="P44" s="182"/>
+      <c r="C44" s="203"/>
+      <c r="D44" s="203"/>
+      <c r="E44" s="203"/>
+      <c r="F44" s="203"/>
+      <c r="G44" s="203"/>
+      <c r="H44" s="208"/>
+      <c r="I44" s="209"/>
+      <c r="J44" s="209"/>
+      <c r="K44" s="209"/>
+      <c r="L44" s="209"/>
+      <c r="M44" s="210"/>
+      <c r="N44" s="204"/>
+      <c r="O44" s="205"/>
+      <c r="P44" s="206"/>
       <c r="Q44" s="49"/>
-      <c r="R44" s="183"/>
-      <c r="S44" s="183"/>
+      <c r="R44" s="207"/>
+      <c r="S44" s="207"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="49"/>
       <c r="B45" s="49"/>
-      <c r="C45" s="176"/>
-      <c r="D45" s="176"/>
-      <c r="E45" s="176"/>
-      <c r="F45" s="176"/>
-      <c r="G45" s="176"/>
-      <c r="H45" s="177"/>
-      <c r="I45" s="178"/>
-      <c r="J45" s="178"/>
-      <c r="K45" s="178"/>
-      <c r="L45" s="178"/>
-      <c r="M45" s="179"/>
-      <c r="N45" s="180"/>
-      <c r="O45" s="181"/>
-      <c r="P45" s="182"/>
+      <c r="C45" s="203"/>
+      <c r="D45" s="203"/>
+      <c r="E45" s="203"/>
+      <c r="F45" s="203"/>
+      <c r="G45" s="203"/>
+      <c r="H45" s="208"/>
+      <c r="I45" s="209"/>
+      <c r="J45" s="209"/>
+      <c r="K45" s="209"/>
+      <c r="L45" s="209"/>
+      <c r="M45" s="210"/>
+      <c r="N45" s="204"/>
+      <c r="O45" s="205"/>
+      <c r="P45" s="206"/>
       <c r="Q45" s="49"/>
-      <c r="R45" s="183"/>
-      <c r="S45" s="183"/>
+      <c r="R45" s="207"/>
+      <c r="S45" s="207"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="49"/>
       <c r="B46" s="49"/>
-      <c r="C46" s="176"/>
-      <c r="D46" s="176"/>
-      <c r="E46" s="176"/>
-      <c r="F46" s="176"/>
-      <c r="G46" s="176"/>
-      <c r="H46" s="177"/>
-      <c r="I46" s="178"/>
-      <c r="J46" s="178"/>
-      <c r="K46" s="178"/>
-      <c r="L46" s="178"/>
-      <c r="M46" s="179"/>
-      <c r="N46" s="180"/>
-      <c r="O46" s="181"/>
-      <c r="P46" s="182"/>
+      <c r="C46" s="203"/>
+      <c r="D46" s="203"/>
+      <c r="E46" s="203"/>
+      <c r="F46" s="203"/>
+      <c r="G46" s="203"/>
+      <c r="H46" s="208"/>
+      <c r="I46" s="209"/>
+      <c r="J46" s="209"/>
+      <c r="K46" s="209"/>
+      <c r="L46" s="209"/>
+      <c r="M46" s="210"/>
+      <c r="N46" s="204"/>
+      <c r="O46" s="205"/>
+      <c r="P46" s="206"/>
       <c r="Q46" s="49"/>
-      <c r="R46" s="183"/>
-      <c r="S46" s="183"/>
+      <c r="R46" s="207"/>
+      <c r="S46" s="207"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="49"/>
       <c r="B47" s="49"/>
-      <c r="C47" s="176"/>
-      <c r="D47" s="176"/>
-      <c r="E47" s="176"/>
-      <c r="F47" s="176"/>
-      <c r="G47" s="176"/>
-      <c r="H47" s="177"/>
-      <c r="I47" s="178"/>
-      <c r="J47" s="178"/>
-      <c r="K47" s="178"/>
-      <c r="L47" s="178"/>
-      <c r="M47" s="179"/>
-      <c r="N47" s="180"/>
-      <c r="O47" s="181"/>
-      <c r="P47" s="182"/>
+      <c r="C47" s="203"/>
+      <c r="D47" s="203"/>
+      <c r="E47" s="203"/>
+      <c r="F47" s="203"/>
+      <c r="G47" s="203"/>
+      <c r="H47" s="208"/>
+      <c r="I47" s="209"/>
+      <c r="J47" s="209"/>
+      <c r="K47" s="209"/>
+      <c r="L47" s="209"/>
+      <c r="M47" s="210"/>
+      <c r="N47" s="204"/>
+      <c r="O47" s="205"/>
+      <c r="P47" s="206"/>
       <c r="Q47" s="49"/>
-      <c r="R47" s="183"/>
-      <c r="S47" s="183"/>
+      <c r="R47" s="207"/>
+      <c r="S47" s="207"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="49"/>
       <c r="B48" s="49"/>
-      <c r="C48" s="176"/>
-      <c r="D48" s="176"/>
-      <c r="E48" s="176"/>
-      <c r="F48" s="176"/>
-      <c r="G48" s="176"/>
-      <c r="H48" s="177"/>
-      <c r="I48" s="178"/>
-      <c r="J48" s="178"/>
-      <c r="K48" s="178"/>
-      <c r="L48" s="178"/>
-      <c r="M48" s="179"/>
-      <c r="N48" s="180"/>
-      <c r="O48" s="181"/>
-      <c r="P48" s="182"/>
+      <c r="C48" s="203"/>
+      <c r="D48" s="203"/>
+      <c r="E48" s="203"/>
+      <c r="F48" s="203"/>
+      <c r="G48" s="203"/>
+      <c r="H48" s="208"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="209"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="209"/>
+      <c r="M48" s="210"/>
+      <c r="N48" s="204"/>
+      <c r="O48" s="205"/>
+      <c r="P48" s="206"/>
       <c r="Q48" s="49"/>
-      <c r="R48" s="183"/>
-      <c r="S48" s="183"/>
+      <c r="R48" s="207"/>
+      <c r="S48" s="207"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="49"/>
       <c r="B49" s="49"/>
-      <c r="C49" s="176"/>
-      <c r="D49" s="176"/>
-      <c r="E49" s="176"/>
-      <c r="F49" s="176"/>
-      <c r="G49" s="176"/>
-      <c r="H49" s="177"/>
-      <c r="I49" s="178"/>
-      <c r="J49" s="178"/>
-      <c r="K49" s="178"/>
-      <c r="L49" s="178"/>
-      <c r="M49" s="179"/>
-      <c r="N49" s="180"/>
-      <c r="O49" s="181"/>
-      <c r="P49" s="182"/>
+      <c r="C49" s="203"/>
+      <c r="D49" s="203"/>
+      <c r="E49" s="203"/>
+      <c r="F49" s="203"/>
+      <c r="G49" s="203"/>
+      <c r="H49" s="208"/>
+      <c r="I49" s="209"/>
+      <c r="J49" s="209"/>
+      <c r="K49" s="209"/>
+      <c r="L49" s="209"/>
+      <c r="M49" s="210"/>
+      <c r="N49" s="204"/>
+      <c r="O49" s="205"/>
+      <c r="P49" s="206"/>
       <c r="Q49" s="49"/>
-      <c r="R49" s="183"/>
-      <c r="S49" s="183"/>
+      <c r="R49" s="207"/>
+      <c r="S49" s="207"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="49"/>
       <c r="B50" s="49"/>
-      <c r="C50" s="176"/>
-      <c r="D50" s="176"/>
-      <c r="E50" s="176"/>
-      <c r="F50" s="176"/>
-      <c r="G50" s="176"/>
-      <c r="H50" s="177"/>
-      <c r="I50" s="178"/>
-      <c r="J50" s="178"/>
-      <c r="K50" s="178"/>
-      <c r="L50" s="178"/>
-      <c r="M50" s="179"/>
-      <c r="N50" s="180"/>
-      <c r="O50" s="181"/>
-      <c r="P50" s="182"/>
+      <c r="C50" s="203"/>
+      <c r="D50" s="203"/>
+      <c r="E50" s="203"/>
+      <c r="F50" s="203"/>
+      <c r="G50" s="203"/>
+      <c r="H50" s="208"/>
+      <c r="I50" s="209"/>
+      <c r="J50" s="209"/>
+      <c r="K50" s="209"/>
+      <c r="L50" s="209"/>
+      <c r="M50" s="210"/>
+      <c r="N50" s="204"/>
+      <c r="O50" s="205"/>
+      <c r="P50" s="206"/>
       <c r="Q50" s="49"/>
-      <c r="R50" s="183"/>
-      <c r="S50" s="183"/>
+      <c r="R50" s="207"/>
+      <c r="S50" s="207"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="49"/>
       <c r="B51" s="49"/>
-      <c r="C51" s="176"/>
-      <c r="D51" s="176"/>
-      <c r="E51" s="176"/>
-      <c r="F51" s="176"/>
-      <c r="G51" s="176"/>
-      <c r="H51" s="177"/>
-      <c r="I51" s="178"/>
-      <c r="J51" s="178"/>
-      <c r="K51" s="178"/>
-      <c r="L51" s="178"/>
-      <c r="M51" s="179"/>
-      <c r="N51" s="180"/>
-      <c r="O51" s="181"/>
-      <c r="P51" s="182"/>
+      <c r="C51" s="203"/>
+      <c r="D51" s="203"/>
+      <c r="E51" s="203"/>
+      <c r="F51" s="203"/>
+      <c r="G51" s="203"/>
+      <c r="H51" s="208"/>
+      <c r="I51" s="209"/>
+      <c r="J51" s="209"/>
+      <c r="K51" s="209"/>
+      <c r="L51" s="209"/>
+      <c r="M51" s="210"/>
+      <c r="N51" s="204"/>
+      <c r="O51" s="205"/>
+      <c r="P51" s="206"/>
       <c r="Q51" s="49"/>
-      <c r="R51" s="183"/>
-      <c r="S51" s="183"/>
+      <c r="R51" s="207"/>
+      <c r="S51" s="207"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="49"/>
       <c r="B52" s="49"/>
-      <c r="C52" s="176"/>
-      <c r="D52" s="176"/>
-      <c r="E52" s="176"/>
-      <c r="F52" s="176"/>
-      <c r="G52" s="176"/>
-      <c r="H52" s="177"/>
-      <c r="I52" s="178"/>
-      <c r="J52" s="178"/>
-      <c r="K52" s="178"/>
-      <c r="L52" s="178"/>
-      <c r="M52" s="179"/>
-      <c r="N52" s="180"/>
-      <c r="O52" s="181"/>
-      <c r="P52" s="182"/>
+      <c r="C52" s="203"/>
+      <c r="D52" s="203"/>
+      <c r="E52" s="203"/>
+      <c r="F52" s="203"/>
+      <c r="G52" s="203"/>
+      <c r="H52" s="208"/>
+      <c r="I52" s="209"/>
+      <c r="J52" s="209"/>
+      <c r="K52" s="209"/>
+      <c r="L52" s="209"/>
+      <c r="M52" s="210"/>
+      <c r="N52" s="204"/>
+      <c r="O52" s="205"/>
+      <c r="P52" s="206"/>
       <c r="Q52" s="49"/>
-      <c r="R52" s="183"/>
-      <c r="S52" s="183"/>
+      <c r="R52" s="207"/>
+      <c r="S52" s="207"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -21030,194 +21218,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/削除機能詳細設計書.xlsx
+++ b/Documents/削除機能詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98635DC-7275-44E7-A21C-D6E3C26FE992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DE2C13-C554-41CE-B429-E6E3F8694936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -959,26 +959,11 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
-    <rPh sb="20" eb="22">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>シタ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ユウドウ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ヒョウジ</t>
-    </rPh>
+    <t>http://localhost:8080/taskUN/task-delete.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>http://localhost:8080/taskUN/task-delete.jsp</t>
+    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -2341,6 +2326,57 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2374,21 +2410,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2434,42 +2455,6 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2533,71 +2518,71 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2605,20 +2590,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2628,23 +2619,53 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2655,18 +2676,6 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2705,30 +2714,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9311,19 +9296,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="105" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="88"/>
-      <c r="F1" s="105" t="s">
+      <c r="E1" s="105"/>
+      <c r="F1" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="88"/>
+      <c r="G1" s="105"/>
       <c r="H1" s="37" t="s">
         <v>8</v>
       </c>
@@ -9335,190 +9320,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="99"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="106" t="s">
+      <c r="A2" s="111"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="107"/>
-      <c r="F2" s="106" t="s">
+      <c r="E2" s="119"/>
+      <c r="F2" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="107"/>
-      <c r="H2" s="110">
+      <c r="G2" s="119"/>
+      <c r="H2" s="122">
         <v>45806</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="97" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="100"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="99"/>
-      <c r="B3" s="100"/>
-      <c r="C3" s="101"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="84"/>
+      <c r="A3" s="111"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="101"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="114"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="89" t="s">
+      <c r="B5" s="104"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="90"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="107"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="94" t="s">
+      <c r="B6" s="81"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="95"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="84"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="94" t="s">
+      <c r="B7" s="81"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="95"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="84"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="92"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="94" t="s">
+      <c r="B8" s="81"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="92"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="92"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="95"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="84"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="117" t="s">
+      <c r="A9" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="93"/>
-      <c r="D9" s="111" t="s">
+      <c r="C9" s="82"/>
+      <c r="D9" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="96"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="120" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="93"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="95"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="84"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="120" t="s">
+      <c r="A11" s="93"/>
+      <c r="B11" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="93"/>
-      <c r="D11" s="94" t="s">
+      <c r="C11" s="82"/>
+      <c r="D11" s="90" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="92"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="95"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="84"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="91" t="s">
+      <c r="A12" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="92"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="111" t="s">
+      <c r="B12" s="81"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="83" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="92"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="92"/>
-      <c r="H12" s="92"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="95"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="84"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="112" t="s">
+      <c r="A13" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="113"/>
-      <c r="C13" s="114"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="113"/>
-      <c r="F13" s="113"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="113"/>
-      <c r="J13" s="116"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10509,6 +10494,18 @@
     <row r="1000" s="39" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -10524,18 +10521,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -13460,20 +13445,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="154" t="s">
+      <c r="A5" s="144" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="155"/>
+      <c r="B5" s="145"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="156" t="s">
+      <c r="D5" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="157"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="149"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -13487,19 +13472,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="146"/>
+      <c r="J6" s="150"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="158"/>
-      <c r="B7" s="159"/>
-      <c r="C7" s="159"/>
-      <c r="D7" s="159"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="159"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="159"/>
-      <c r="I7" s="159"/>
-      <c r="J7" s="160"/>
+      <c r="A7" s="151"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="152"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="152"/>
+      <c r="I7" s="152"/>
+      <c r="J7" s="153"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -13511,7 +13496,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="161"/>
+      <c r="J8" s="154"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -13523,7 +13508,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="161"/>
+      <c r="J9" s="154"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -13535,7 +13520,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="161"/>
+      <c r="J10" s="154"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -13547,7 +13532,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="161"/>
+      <c r="J11" s="154"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -13559,7 +13544,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="161"/>
+      <c r="J12" s="154"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -13571,7 +13556,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="161"/>
+      <c r="J13" s="154"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -13585,7 +13570,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="146"/>
+      <c r="J14" s="150"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="147" t="s">
@@ -13593,7 +13578,7 @@
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="74"/>
-      <c r="D15" s="145" t="s">
+      <c r="D15" s="155" t="s">
         <v>73</v>
       </c>
       <c r="E15" s="73"/>
@@ -13625,14 +13610,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="148" t="s">
+      <c r="H16" s="156" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="73"/>
-      <c r="J16" s="146"/>
+      <c r="J16" s="150"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="144">
+      <c r="A17" s="146">
         <v>1</v>
       </c>
       <c r="B17" s="73"/>
@@ -13647,12 +13632,12 @@
         <v>82</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="145"/>
+      <c r="H17" s="155"/>
       <c r="I17" s="73"/>
-      <c r="J17" s="146"/>
+      <c r="J17" s="150"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="144">
+      <c r="A18" s="146">
         <v>2</v>
       </c>
       <c r="B18" s="73"/>
@@ -13669,12 +13654,12 @@
       <c r="G18" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="145"/>
+      <c r="H18" s="155"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="146"/>
+      <c r="J18" s="150"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="144">
+      <c r="A19" s="146">
         <v>3</v>
       </c>
       <c r="B19" s="73"/>
@@ -13689,12 +13674,12 @@
       <c r="G19" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="145"/>
+      <c r="H19" s="155"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="146"/>
+      <c r="J19" s="150"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="144">
+      <c r="A20" s="146">
         <v>4</v>
       </c>
       <c r="B20" s="73"/>
@@ -13711,12 +13696,12 @@
       <c r="G20" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="145"/>
+      <c r="H20" s="155"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="146"/>
+      <c r="J20" s="150"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="144">
+      <c r="A21" s="146">
         <v>5</v>
       </c>
       <c r="B21" s="73"/>
@@ -13733,12 +13718,12 @@
       <c r="G21" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="145"/>
+      <c r="H21" s="155"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="146"/>
+      <c r="J21" s="150"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="144">
+      <c r="A22" s="146">
         <v>6</v>
       </c>
       <c r="B22" s="73"/>
@@ -13753,12 +13738,12 @@
         <v>61</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="145"/>
+      <c r="H22" s="155"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="146"/>
+      <c r="J22" s="150"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="144">
+      <c r="A23" s="146">
         <v>7</v>
       </c>
       <c r="B23" s="73"/>
@@ -13773,9 +13758,9 @@
         <v>61</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="152"/>
-      <c r="I23" s="150"/>
-      <c r="J23" s="153"/>
+      <c r="H23" s="157"/>
+      <c r="I23" s="158"/>
+      <c r="J23" s="159"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
       <c r="A24" s="147"/>
@@ -13787,13 +13772,13 @@
       <c r="G24" s="73"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73"/>
-      <c r="J24" s="146"/>
+      <c r="J24" s="150"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
       <c r="A25" s="147"/>
       <c r="B25" s="73"/>
       <c r="C25" s="74"/>
-      <c r="D25" s="145"/>
+      <c r="D25" s="155"/>
       <c r="E25" s="73"/>
       <c r="F25" s="73"/>
       <c r="G25" s="73"/>
@@ -13809,93 +13794,93 @@
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="148"/>
+      <c r="H26" s="156"/>
       <c r="I26" s="73"/>
-      <c r="J26" s="146"/>
+      <c r="J26" s="150"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="144"/>
+      <c r="A27" s="146"/>
       <c r="B27" s="73"/>
       <c r="C27" s="74"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="145"/>
+      <c r="H27" s="155"/>
       <c r="I27" s="73"/>
-      <c r="J27" s="146"/>
+      <c r="J27" s="150"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="144"/>
+      <c r="A28" s="146"/>
       <c r="B28" s="73"/>
       <c r="C28" s="74"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="145"/>
+      <c r="H28" s="155"/>
       <c r="I28" s="73"/>
-      <c r="J28" s="146"/>
+      <c r="J28" s="150"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="144"/>
+      <c r="A29" s="146"/>
       <c r="B29" s="73"/>
       <c r="C29" s="74"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
-      <c r="H29" s="145"/>
+      <c r="H29" s="155"/>
       <c r="I29" s="73"/>
-      <c r="J29" s="146"/>
+      <c r="J29" s="150"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="144"/>
+      <c r="A30" s="146"/>
       <c r="B30" s="73"/>
       <c r="C30" s="74"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="145"/>
+      <c r="H30" s="155"/>
       <c r="I30" s="73"/>
-      <c r="J30" s="146"/>
+      <c r="J30" s="150"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="144"/>
+      <c r="A31" s="146"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="145"/>
+      <c r="H31" s="155"/>
       <c r="I31" s="73"/>
-      <c r="J31" s="146"/>
+      <c r="J31" s="150"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="144"/>
+      <c r="A32" s="146"/>
       <c r="B32" s="73"/>
       <c r="C32" s="74"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="145"/>
+      <c r="H32" s="155"/>
       <c r="I32" s="73"/>
-      <c r="J32" s="146"/>
+      <c r="J32" s="150"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="149"/>
-      <c r="B33" s="150"/>
-      <c r="C33" s="151"/>
+      <c r="A33" s="160"/>
+      <c r="B33" s="158"/>
+      <c r="C33" s="161"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
-      <c r="H33" s="152"/>
-      <c r="I33" s="150"/>
-      <c r="J33" s="153"/>
+      <c r="H33" s="157"/>
+      <c r="I33" s="158"/>
+      <c r="J33" s="159"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
       <c r="A34" s="147"/>
@@ -13907,13 +13892,13 @@
       <c r="G34" s="73"/>
       <c r="H34" s="73"/>
       <c r="I34" s="73"/>
-      <c r="J34" s="146"/>
+      <c r="J34" s="150"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
       <c r="A35" s="147"/>
       <c r="B35" s="73"/>
       <c r="C35" s="74"/>
-      <c r="D35" s="145"/>
+      <c r="D35" s="155"/>
       <c r="E35" s="73"/>
       <c r="F35" s="73"/>
       <c r="G35" s="73"/>
@@ -13929,69 +13914,69 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
-      <c r="H36" s="148"/>
+      <c r="H36" s="156"/>
       <c r="I36" s="73"/>
-      <c r="J36" s="146"/>
+      <c r="J36" s="150"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="144"/>
+      <c r="A37" s="146"/>
       <c r="B37" s="73"/>
       <c r="C37" s="74"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="145"/>
+      <c r="H37" s="155"/>
       <c r="I37" s="73"/>
-      <c r="J37" s="146"/>
+      <c r="J37" s="150"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="144"/>
+      <c r="A38" s="146"/>
       <c r="B38" s="73"/>
       <c r="C38" s="74"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="145"/>
+      <c r="H38" s="155"/>
       <c r="I38" s="73"/>
-      <c r="J38" s="146"/>
+      <c r="J38" s="150"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="144"/>
+      <c r="A39" s="146"/>
       <c r="B39" s="73"/>
       <c r="C39" s="74"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="145"/>
+      <c r="H39" s="155"/>
       <c r="I39" s="73"/>
-      <c r="J39" s="146"/>
+      <c r="J39" s="150"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="144"/>
+      <c r="A40" s="146"/>
       <c r="B40" s="73"/>
       <c r="C40" s="74"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="145"/>
+      <c r="H40" s="155"/>
       <c r="I40" s="73"/>
-      <c r="J40" s="146"/>
+      <c r="J40" s="150"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="144"/>
+      <c r="A41" s="146"/>
       <c r="B41" s="73"/>
       <c r="C41" s="74"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="145"/>
+      <c r="H41" s="155"/>
       <c r="I41" s="73"/>
-      <c r="J41" s="146"/>
+      <c r="J41" s="150"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14954,11 +14939,50 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -14975,50 +14999,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -15109,20 +15094,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="154" t="s">
+      <c r="A5" s="144" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="155"/>
+      <c r="B5" s="145"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="156" t="s">
+      <c r="D5" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="157"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="149"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -15136,19 +15121,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="146"/>
+      <c r="J6" s="150"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="158"/>
-      <c r="B7" s="159"/>
-      <c r="C7" s="159"/>
-      <c r="D7" s="159"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="159"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="159"/>
-      <c r="I7" s="159"/>
-      <c r="J7" s="160"/>
+      <c r="A7" s="151"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="152"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="152"/>
+      <c r="I7" s="152"/>
+      <c r="J7" s="153"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -15160,7 +15145,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="161"/>
+      <c r="J8" s="154"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -15172,7 +15157,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="161"/>
+      <c r="J9" s="154"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -15184,7 +15169,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="161"/>
+      <c r="J10" s="154"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -15196,7 +15181,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="161"/>
+      <c r="J11" s="154"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -15208,7 +15193,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="161"/>
+      <c r="J12" s="154"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -15220,7 +15205,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="161"/>
+      <c r="J13" s="154"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -15234,7 +15219,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="146"/>
+      <c r="J14" s="150"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="147" t="s">
@@ -15242,7 +15227,7 @@
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="74"/>
-      <c r="D15" s="145" t="s">
+      <c r="D15" s="155" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="73"/>
@@ -15274,14 +15259,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="148" t="s">
+      <c r="H16" s="156" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="73"/>
-      <c r="J16" s="146"/>
+      <c r="J16" s="150"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="144">
+      <c r="A17" s="146">
         <v>1</v>
       </c>
       <c r="B17" s="73"/>
@@ -15298,83 +15283,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="145" t="s">
+      <c r="H17" s="155" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="73"/>
-      <c r="J17" s="146"/>
+      <c r="J17" s="150"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="144"/>
+      <c r="A18" s="146"/>
       <c r="B18" s="73"/>
       <c r="C18" s="74"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="145"/>
+      <c r="H18" s="155"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="146"/>
+      <c r="J18" s="150"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="144"/>
+      <c r="A19" s="146"/>
       <c r="B19" s="73"/>
       <c r="C19" s="74"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="145"/>
+      <c r="H19" s="155"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="146"/>
+      <c r="J19" s="150"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="144"/>
+      <c r="A20" s="146"/>
       <c r="B20" s="73"/>
       <c r="C20" s="74"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="145"/>
+      <c r="H20" s="155"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="146"/>
+      <c r="J20" s="150"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="144"/>
+      <c r="A21" s="146"/>
       <c r="B21" s="73"/>
       <c r="C21" s="74"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="145"/>
+      <c r="H21" s="155"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="146"/>
+      <c r="J21" s="150"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="144"/>
+      <c r="A22" s="146"/>
       <c r="B22" s="73"/>
       <c r="C22" s="74"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="145"/>
+      <c r="H22" s="155"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="146"/>
+      <c r="J22" s="150"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="149"/>
-      <c r="B23" s="150"/>
-      <c r="C23" s="151"/>
+      <c r="A23" s="160"/>
+      <c r="B23" s="158"/>
+      <c r="C23" s="161"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="152"/>
-      <c r="I23" s="150"/>
-      <c r="J23" s="153"/>
+      <c r="H23" s="157"/>
+      <c r="I23" s="158"/>
+      <c r="J23" s="159"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -16355,6 +16340,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -16370,22 +16371,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -16476,20 +16461,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="154" t="s">
+      <c r="A5" s="144" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="155"/>
+      <c r="B5" s="145"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="156" t="s">
+      <c r="D5" s="148" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="157"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="149"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -16503,19 +16488,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="146"/>
+      <c r="J6" s="150"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="158"/>
-      <c r="B7" s="159"/>
-      <c r="C7" s="159"/>
-      <c r="D7" s="159"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="159"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="159"/>
-      <c r="I7" s="159"/>
-      <c r="J7" s="160"/>
+      <c r="A7" s="151"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="152"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="152"/>
+      <c r="I7" s="152"/>
+      <c r="J7" s="153"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -16527,7 +16512,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="161"/>
+      <c r="J8" s="154"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -16539,7 +16524,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="161"/>
+      <c r="J9" s="154"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -16551,7 +16536,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="161"/>
+      <c r="J10" s="154"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -16563,7 +16548,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="161"/>
+      <c r="J11" s="154"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -16575,7 +16560,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="161"/>
+      <c r="J12" s="154"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -16587,7 +16572,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="161"/>
+      <c r="J13" s="154"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -16601,7 +16586,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="146"/>
+      <c r="J14" s="150"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="147" t="s">
@@ -16609,7 +16594,7 @@
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="74"/>
-      <c r="D15" s="145" t="s">
+      <c r="D15" s="155" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="73"/>
@@ -16641,14 +16626,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="148" t="s">
+      <c r="H16" s="156" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="73"/>
-      <c r="J16" s="146"/>
+      <c r="J16" s="150"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="144">
+      <c r="A17" s="146">
         <v>1</v>
       </c>
       <c r="B17" s="73"/>
@@ -16665,83 +16650,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="145" t="s">
+      <c r="H17" s="155" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="73"/>
-      <c r="J17" s="146"/>
+      <c r="J17" s="150"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="144"/>
+      <c r="A18" s="146"/>
       <c r="B18" s="73"/>
       <c r="C18" s="74"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="145"/>
+      <c r="H18" s="155"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="146"/>
+      <c r="J18" s="150"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="144"/>
+      <c r="A19" s="146"/>
       <c r="B19" s="73"/>
       <c r="C19" s="74"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="145"/>
+      <c r="H19" s="155"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="146"/>
+      <c r="J19" s="150"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="144"/>
+      <c r="A20" s="146"/>
       <c r="B20" s="73"/>
       <c r="C20" s="74"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="145"/>
+      <c r="H20" s="155"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="146"/>
+      <c r="J20" s="150"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="144"/>
+      <c r="A21" s="146"/>
       <c r="B21" s="73"/>
       <c r="C21" s="74"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="145"/>
+      <c r="H21" s="155"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="146"/>
+      <c r="J21" s="150"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="144"/>
+      <c r="A22" s="146"/>
       <c r="B22" s="73"/>
       <c r="C22" s="74"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="145"/>
+      <c r="H22" s="155"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="146"/>
+      <c r="J22" s="150"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="149"/>
-      <c r="B23" s="150"/>
-      <c r="C23" s="151"/>
+      <c r="A23" s="160"/>
+      <c r="B23" s="158"/>
+      <c r="C23" s="161"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="152"/>
-      <c r="I23" s="150"/>
-      <c r="J23" s="153"/>
+      <c r="H23" s="157"/>
+      <c r="I23" s="158"/>
+      <c r="J23" s="159"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -17722,6 +17707,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -17737,22 +17738,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -17772,7 +17757,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="171" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="131"/>
@@ -17783,14 +17768,14 @@
       <c r="G1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
       <c r="J1" s="139"/>
       <c r="K1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="155"/>
-      <c r="M1" s="155"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
       <c r="N1" s="139"/>
       <c r="O1" s="138" t="s">
         <v>8</v>
@@ -17803,7 +17788,7 @@
       <c r="S1" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="157"/>
+      <c r="T1" s="149"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="133"/>
@@ -17815,16 +17800,16 @@
       <c r="G2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
       <c r="J2" s="141"/>
       <c r="K2" s="140" t="s">
         <v>93</v>
       </c>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
       <c r="N2" s="141"/>
-      <c r="O2" s="177">
+      <c r="O2" s="169">
         <v>45821</v>
       </c>
       <c r="P2" s="141"/>
@@ -17833,7 +17818,7 @@
       </c>
       <c r="R2" s="141"/>
       <c r="S2" s="140"/>
-      <c r="T2" s="160"/>
+      <c r="T2" s="153"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="133"/>
@@ -17855,7 +17840,7 @@
       <c r="Q3" s="142"/>
       <c r="R3" s="134"/>
       <c r="S3" s="142"/>
-      <c r="T3" s="161"/>
+      <c r="T3" s="154"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="135"/>
@@ -17877,33 +17862,33 @@
       <c r="Q4" s="143"/>
       <c r="R4" s="137"/>
       <c r="S4" s="143"/>
-      <c r="T4" s="178"/>
+      <c r="T4" s="170"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="154" t="s">
+      <c r="A5" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="155"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
+      <c r="B5" s="145"/>
+      <c r="C5" s="145"/>
+      <c r="D5" s="145"/>
+      <c r="E5" s="145"/>
       <c r="F5" s="139"/>
-      <c r="G5" s="168" t="s">
+      <c r="G5" s="172" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="155"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="155"/>
-      <c r="N5" s="155"/>
-      <c r="O5" s="155"/>
-      <c r="P5" s="155"/>
-      <c r="Q5" s="155"/>
-      <c r="R5" s="155"/>
-      <c r="S5" s="155"/>
-      <c r="T5" s="157"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="145"/>
+      <c r="K5" s="145"/>
+      <c r="L5" s="145"/>
+      <c r="M5" s="145"/>
+      <c r="N5" s="145"/>
+      <c r="O5" s="145"/>
+      <c r="P5" s="145"/>
+      <c r="Q5" s="145"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="145"/>
+      <c r="T5" s="149"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -17914,7 +17899,7 @@
       <c r="D6" s="73"/>
       <c r="E6" s="73"/>
       <c r="F6" s="74"/>
-      <c r="G6" s="145" t="s">
+      <c r="G6" s="155" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="73"/>
@@ -17929,7 +17914,7 @@
       <c r="Q6" s="73"/>
       <c r="R6" s="73"/>
       <c r="S6" s="73"/>
-      <c r="T6" s="146"/>
+      <c r="T6" s="150"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="147" t="s">
@@ -17940,7 +17925,7 @@
       <c r="D7" s="73"/>
       <c r="E7" s="73"/>
       <c r="F7" s="74"/>
-      <c r="G7" s="145" t="s">
+      <c r="G7" s="155" t="s">
         <v>95</v>
       </c>
       <c r="H7" s="73"/>
@@ -17955,7 +17940,7 @@
       <c r="Q7" s="73"/>
       <c r="R7" s="73"/>
       <c r="S7" s="73"/>
-      <c r="T7" s="146"/>
+      <c r="T7" s="150"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -18158,29 +18143,29 @@
         <v>45</v>
       </c>
       <c r="B15" s="74"/>
-      <c r="C15" s="176" t="s">
+      <c r="C15" s="178" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="74"/>
-      <c r="E15" s="148" t="s">
+      <c r="E15" s="156" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="74"/>
-      <c r="G15" s="148" t="s">
+      <c r="G15" s="156" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="73"/>
       <c r="I15" s="74"/>
-      <c r="J15" s="148" t="s">
+      <c r="J15" s="156" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="74"/>
-      <c r="L15" s="148" t="s">
+      <c r="L15" s="156" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="73"/>
       <c r="N15" s="74"/>
-      <c r="O15" s="148" t="s">
+      <c r="O15" s="156" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="73"/>
@@ -18196,27 +18181,27 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A16" s="162">
+      <c r="A16" s="179">
         <v>1</v>
       </c>
       <c r="B16" s="74"/>
-      <c r="C16" s="163" t="s">
+      <c r="C16" s="180" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="74"/>
-      <c r="E16" s="163" t="s">
+      <c r="E16" s="180" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="74"/>
-      <c r="G16" s="181" t="s">
+      <c r="G16" s="162" t="s">
         <v>96</v>
       </c>
       <c r="H16" s="73"/>
       <c r="I16" s="74"/>
-      <c r="J16" s="172" t="s">
+      <c r="J16" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="K16" s="170"/>
+      <c r="K16" s="164"/>
       <c r="L16" s="166" t="s">
         <v>98</v>
       </c>
@@ -18238,24 +18223,24 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A17" s="162">
+      <c r="A17" s="179">
         <v>2</v>
       </c>
       <c r="B17" s="74"/>
-      <c r="C17" s="163" t="s">
+      <c r="C17" s="180" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="74"/>
-      <c r="E17" s="163" t="s">
+      <c r="E17" s="180" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="74"/>
-      <c r="G17" s="181" t="s">
+      <c r="G17" s="162" t="s">
         <v>105</v>
       </c>
       <c r="H17" s="73"/>
       <c r="I17" s="74"/>
-      <c r="J17" s="181" t="s">
+      <c r="J17" s="162" t="s">
         <v>106</v>
       </c>
       <c r="K17" s="74"/>
@@ -18280,28 +18265,28 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="64.5" customHeight="1">
-      <c r="A18" s="162">
+      <c r="A18" s="179">
         <v>3</v>
       </c>
       <c r="B18" s="74"/>
-      <c r="C18" s="163" t="s">
+      <c r="C18" s="180" t="s">
         <v>54</v>
       </c>
       <c r="D18" s="74"/>
-      <c r="E18" s="163" t="s">
+      <c r="E18" s="180" t="s">
         <v>100</v>
       </c>
       <c r="F18" s="74"/>
-      <c r="G18" s="181" t="s">
+      <c r="G18" s="162" t="s">
         <v>101</v>
       </c>
       <c r="H18" s="73"/>
       <c r="I18" s="74"/>
-      <c r="J18" s="181" t="s">
+      <c r="J18" s="162" t="s">
         <v>103</v>
       </c>
       <c r="K18" s="74"/>
-      <c r="L18" s="180" t="s">
+      <c r="L18" s="168" t="s">
         <v>104</v>
       </c>
       <c r="M18" s="73"/>
@@ -18322,24 +18307,24 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="61.5" customHeight="1">
-      <c r="A19" s="162">
+      <c r="A19" s="179">
         <v>4</v>
       </c>
       <c r="B19" s="74"/>
-      <c r="C19" s="163" t="s">
+      <c r="C19" s="180" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="74"/>
-      <c r="E19" s="163" t="s">
+      <c r="E19" s="180" t="s">
         <v>100</v>
       </c>
       <c r="F19" s="74"/>
-      <c r="G19" s="181" t="s">
+      <c r="G19" s="162" t="s">
         <v>139</v>
       </c>
       <c r="H19" s="73"/>
       <c r="I19" s="74"/>
-      <c r="J19" s="181" t="s">
+      <c r="J19" s="162" t="s">
         <v>97</v>
       </c>
       <c r="K19" s="74"/>
@@ -18364,34 +18349,34 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A20" s="169">
+      <c r="A20" s="173">
         <v>7</v>
       </c>
-      <c r="B20" s="170"/>
-      <c r="C20" s="171" t="s">
+      <c r="B20" s="164"/>
+      <c r="C20" s="174" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="170"/>
-      <c r="E20" s="171" t="s">
+      <c r="D20" s="164"/>
+      <c r="E20" s="174" t="s">
         <v>141</v>
       </c>
-      <c r="F20" s="170"/>
-      <c r="G20" s="172" t="s">
+      <c r="F20" s="164"/>
+      <c r="G20" s="163" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="173"/>
-      <c r="I20" s="170"/>
-      <c r="J20" s="172" t="s">
+      <c r="H20" s="175"/>
+      <c r="I20" s="164"/>
+      <c r="J20" s="163" t="s">
         <v>143</v>
       </c>
-      <c r="K20" s="170"/>
-      <c r="L20" s="174" t="s">
+      <c r="K20" s="164"/>
+      <c r="L20" s="176" t="s">
+        <v>144</v>
+      </c>
+      <c r="M20" s="177"/>
+      <c r="N20" s="177"/>
+      <c r="O20" s="166" t="s">
         <v>145</v>
-      </c>
-      <c r="M20" s="175"/>
-      <c r="N20" s="175"/>
-      <c r="O20" s="166" t="s">
-        <v>144</v>
       </c>
       <c r="P20" s="73"/>
       <c r="Q20" s="74"/>
@@ -18406,16 +18391,16 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="162"/>
+      <c r="A21" s="179"/>
       <c r="B21" s="74"/>
-      <c r="C21" s="163"/>
+      <c r="C21" s="180"/>
       <c r="D21" s="74"/>
-      <c r="E21" s="163"/>
+      <c r="E21" s="180"/>
       <c r="F21" s="74"/>
-      <c r="G21" s="181"/>
+      <c r="G21" s="162"/>
       <c r="H21" s="73"/>
       <c r="I21" s="74"/>
-      <c r="J21" s="181"/>
+      <c r="J21" s="162"/>
       <c r="K21" s="74"/>
       <c r="L21" s="166"/>
       <c r="M21" s="73"/>
@@ -18434,16 +18419,16 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="162"/>
+      <c r="A22" s="179"/>
       <c r="B22" s="74"/>
-      <c r="C22" s="163"/>
+      <c r="C22" s="180"/>
       <c r="D22" s="74"/>
-      <c r="E22" s="163"/>
+      <c r="E22" s="180"/>
       <c r="F22" s="74"/>
-      <c r="G22" s="181"/>
+      <c r="G22" s="162"/>
       <c r="H22" s="73"/>
       <c r="I22" s="74"/>
-      <c r="J22" s="181"/>
+      <c r="J22" s="162"/>
       <c r="K22" s="74"/>
       <c r="L22" s="166"/>
       <c r="M22" s="73"/>
@@ -18462,16 +18447,16 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="162"/>
+      <c r="A23" s="179"/>
       <c r="B23" s="74"/>
-      <c r="C23" s="163"/>
+      <c r="C23" s="180"/>
       <c r="D23" s="74"/>
-      <c r="E23" s="163"/>
+      <c r="E23" s="180"/>
       <c r="F23" s="74"/>
-      <c r="G23" s="181"/>
+      <c r="G23" s="162"/>
       <c r="H23" s="73"/>
       <c r="I23" s="74"/>
-      <c r="J23" s="181"/>
+      <c r="J23" s="162"/>
       <c r="K23" s="74"/>
       <c r="L23" s="166"/>
       <c r="M23" s="73"/>
@@ -18490,16 +18475,16 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="162"/>
+      <c r="A24" s="179"/>
       <c r="B24" s="74"/>
-      <c r="C24" s="163"/>
+      <c r="C24" s="180"/>
       <c r="D24" s="74"/>
-      <c r="E24" s="163"/>
+      <c r="E24" s="180"/>
       <c r="F24" s="74"/>
-      <c r="G24" s="181"/>
+      <c r="G24" s="162"/>
       <c r="H24" s="73"/>
       <c r="I24" s="74"/>
-      <c r="J24" s="181"/>
+      <c r="J24" s="162"/>
       <c r="K24" s="74"/>
       <c r="L24" s="166"/>
       <c r="M24" s="73"/>
@@ -18518,16 +18503,16 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="162"/>
+      <c r="A25" s="179"/>
       <c r="B25" s="74"/>
-      <c r="C25" s="163"/>
+      <c r="C25" s="180"/>
       <c r="D25" s="74"/>
-      <c r="E25" s="163"/>
+      <c r="E25" s="180"/>
       <c r="F25" s="74"/>
-      <c r="G25" s="181"/>
+      <c r="G25" s="162"/>
       <c r="H25" s="73"/>
       <c r="I25" s="74"/>
-      <c r="J25" s="181"/>
+      <c r="J25" s="162"/>
       <c r="K25" s="74"/>
       <c r="L25" s="166"/>
       <c r="M25" s="73"/>
@@ -18546,16 +18531,16 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="162"/>
+      <c r="A26" s="179"/>
       <c r="B26" s="74"/>
-      <c r="C26" s="163"/>
+      <c r="C26" s="180"/>
       <c r="D26" s="74"/>
-      <c r="E26" s="163"/>
+      <c r="E26" s="180"/>
       <c r="F26" s="74"/>
-      <c r="G26" s="181"/>
+      <c r="G26" s="162"/>
       <c r="H26" s="73"/>
       <c r="I26" s="74"/>
-      <c r="J26" s="181"/>
+      <c r="J26" s="162"/>
       <c r="K26" s="74"/>
       <c r="L26" s="166"/>
       <c r="M26" s="73"/>
@@ -18574,16 +18559,16 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="162"/>
+      <c r="A27" s="179"/>
       <c r="B27" s="74"/>
-      <c r="C27" s="163"/>
+      <c r="C27" s="180"/>
       <c r="D27" s="74"/>
-      <c r="E27" s="163"/>
+      <c r="E27" s="180"/>
       <c r="F27" s="74"/>
-      <c r="G27" s="181"/>
+      <c r="G27" s="162"/>
       <c r="H27" s="73"/>
       <c r="I27" s="74"/>
-      <c r="J27" s="181"/>
+      <c r="J27" s="162"/>
       <c r="K27" s="74"/>
       <c r="L27" s="166"/>
       <c r="M27" s="73"/>
@@ -18602,16 +18587,16 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="162"/>
+      <c r="A28" s="179"/>
       <c r="B28" s="74"/>
-      <c r="C28" s="163"/>
+      <c r="C28" s="180"/>
       <c r="D28" s="74"/>
-      <c r="E28" s="163"/>
+      <c r="E28" s="180"/>
       <c r="F28" s="74"/>
-      <c r="G28" s="181"/>
+      <c r="G28" s="162"/>
       <c r="H28" s="73"/>
       <c r="I28" s="74"/>
-      <c r="J28" s="181"/>
+      <c r="J28" s="162"/>
       <c r="K28" s="74"/>
       <c r="L28" s="166"/>
       <c r="M28" s="73"/>
@@ -18630,16 +18615,16 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="162"/>
+      <c r="A29" s="179"/>
       <c r="B29" s="74"/>
-      <c r="C29" s="163"/>
+      <c r="C29" s="180"/>
       <c r="D29" s="74"/>
-      <c r="E29" s="163"/>
+      <c r="E29" s="180"/>
       <c r="F29" s="74"/>
-      <c r="G29" s="181"/>
+      <c r="G29" s="162"/>
       <c r="H29" s="73"/>
       <c r="I29" s="74"/>
-      <c r="J29" s="181"/>
+      <c r="J29" s="162"/>
       <c r="K29" s="74"/>
       <c r="L29" s="166"/>
       <c r="M29" s="73"/>
@@ -18658,16 +18643,16 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="162"/>
+      <c r="A30" s="179"/>
       <c r="B30" s="74"/>
-      <c r="C30" s="163"/>
+      <c r="C30" s="180"/>
       <c r="D30" s="74"/>
-      <c r="E30" s="163"/>
+      <c r="E30" s="180"/>
       <c r="F30" s="74"/>
-      <c r="G30" s="181"/>
+      <c r="G30" s="162"/>
       <c r="H30" s="73"/>
       <c r="I30" s="74"/>
-      <c r="J30" s="181"/>
+      <c r="J30" s="162"/>
       <c r="K30" s="74"/>
       <c r="L30" s="166"/>
       <c r="M30" s="73"/>
@@ -18686,23 +18671,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="164"/>
-      <c r="B31" s="151"/>
-      <c r="C31" s="165"/>
-      <c r="D31" s="151"/>
-      <c r="E31" s="165"/>
-      <c r="F31" s="151"/>
-      <c r="G31" s="182"/>
-      <c r="H31" s="150"/>
-      <c r="I31" s="151"/>
-      <c r="J31" s="182"/>
-      <c r="K31" s="151"/>
+      <c r="A31" s="181"/>
+      <c r="B31" s="161"/>
+      <c r="C31" s="182"/>
+      <c r="D31" s="161"/>
+      <c r="E31" s="182"/>
+      <c r="F31" s="161"/>
+      <c r="G31" s="165"/>
+      <c r="H31" s="158"/>
+      <c r="I31" s="161"/>
+      <c r="J31" s="165"/>
+      <c r="K31" s="161"/>
       <c r="L31" s="167"/>
-      <c r="M31" s="150"/>
-      <c r="N31" s="151"/>
+      <c r="M31" s="158"/>
+      <c r="N31" s="161"/>
       <c r="O31" s="167"/>
-      <c r="P31" s="150"/>
-      <c r="Q31" s="151"/>
+      <c r="P31" s="158"/>
+      <c r="Q31" s="161"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -19700,62 +19685,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -19780,62 +19765,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
@@ -19862,70 +19847,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="193" t="s">
+      <c r="B1" s="200"/>
+      <c r="C1" s="201" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="194"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="196" t="s">
+      <c r="D1" s="202"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="204" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="198"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="206"/>
       <c r="N1" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="196" t="s">
+      <c r="O1" s="204" t="s">
         <v>94</v>
       </c>
-      <c r="P1" s="198"/>
+      <c r="P1" s="206"/>
       <c r="Q1" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="196" t="s">
+      <c r="R1" s="204" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="198"/>
+      <c r="S1" s="206"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="192"/>
-      <c r="B2" s="192"/>
-      <c r="C2" s="193" t="s">
+      <c r="A2" s="200"/>
+      <c r="B2" s="200"/>
+      <c r="C2" s="201" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="194"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="196" t="s">
+      <c r="D2" s="202"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="204" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="197"/>
-      <c r="H2" s="197"/>
-      <c r="I2" s="197"/>
-      <c r="J2" s="197"/>
-      <c r="K2" s="197"/>
-      <c r="L2" s="197"/>
-      <c r="M2" s="198"/>
+      <c r="G2" s="205"/>
+      <c r="H2" s="205"/>
+      <c r="I2" s="205"/>
+      <c r="J2" s="205"/>
+      <c r="K2" s="205"/>
+      <c r="L2" s="205"/>
+      <c r="M2" s="206"/>
       <c r="N2" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="O2" s="199">
+      <c r="O2" s="207">
         <v>45824</v>
       </c>
-      <c r="P2" s="200"/>
+      <c r="P2" s="208"/>
       <c r="Q2" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="R2" s="201"/>
-      <c r="S2" s="202"/>
+      <c r="R2" s="209"/>
+      <c r="S2" s="210"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="43"/>
@@ -19955,33 +19940,33 @@
       <c r="B4" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="183" t="s">
+      <c r="C4" s="195" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="185"/>
-      <c r="H4" s="183" t="s">
+      <c r="D4" s="196"/>
+      <c r="E4" s="196"/>
+      <c r="F4" s="196"/>
+      <c r="G4" s="197"/>
+      <c r="H4" s="195" t="s">
         <v>119</v>
       </c>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
-      <c r="M4" s="185"/>
-      <c r="N4" s="183" t="s">
+      <c r="I4" s="196"/>
+      <c r="J4" s="196"/>
+      <c r="K4" s="196"/>
+      <c r="L4" s="196"/>
+      <c r="M4" s="197"/>
+      <c r="N4" s="195" t="s">
         <v>120</v>
       </c>
-      <c r="O4" s="184"/>
-      <c r="P4" s="185"/>
+      <c r="O4" s="196"/>
+      <c r="P4" s="197"/>
       <c r="Q4" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="R4" s="183" t="s">
+      <c r="R4" s="195" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="185"/>
+      <c r="S4" s="197"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="47">
@@ -19990,29 +19975,29 @@
       <c r="B5" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="186" t="s">
+      <c r="C5" s="191" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
-      <c r="G5" s="186"/>
-      <c r="H5" s="186" t="s">
+      <c r="D5" s="191"/>
+      <c r="E5" s="191"/>
+      <c r="F5" s="191"/>
+      <c r="G5" s="191"/>
+      <c r="H5" s="191" t="s">
         <v>135</v>
       </c>
-      <c r="I5" s="186"/>
-      <c r="J5" s="186"/>
-      <c r="K5" s="186"/>
-      <c r="L5" s="186"/>
-      <c r="M5" s="186"/>
-      <c r="N5" s="187" t="s">
+      <c r="I5" s="191"/>
+      <c r="J5" s="191"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="192" t="s">
         <v>136</v>
       </c>
-      <c r="O5" s="188"/>
-      <c r="P5" s="189"/>
+      <c r="O5" s="193"/>
+      <c r="P5" s="194"/>
       <c r="Q5" s="47"/>
-      <c r="R5" s="190"/>
-      <c r="S5" s="191"/>
+      <c r="R5" s="198"/>
+      <c r="S5" s="199"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="49">
@@ -20021,1186 +20006,998 @@
       <c r="B6" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="186" t="s">
+      <c r="C6" s="191" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
-      <c r="H6" s="186" t="s">
+      <c r="D6" s="191"/>
+      <c r="E6" s="191"/>
+      <c r="F6" s="191"/>
+      <c r="G6" s="191"/>
+      <c r="H6" s="191" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="186"/>
-      <c r="J6" s="186"/>
-      <c r="K6" s="186"/>
-      <c r="L6" s="186"/>
-      <c r="M6" s="186"/>
-      <c r="N6" s="187" t="s">
+      <c r="I6" s="191"/>
+      <c r="J6" s="191"/>
+      <c r="K6" s="191"/>
+      <c r="L6" s="191"/>
+      <c r="M6" s="191"/>
+      <c r="N6" s="192" t="s">
         <v>137</v>
       </c>
-      <c r="O6" s="188"/>
-      <c r="P6" s="189"/>
+      <c r="O6" s="193"/>
+      <c r="P6" s="194"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="207"/>
-      <c r="S6" s="207"/>
+      <c r="R6" s="190"/>
+      <c r="S6" s="190"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="49"/>
       <c r="B7" s="49"/>
-      <c r="C7" s="203"/>
-      <c r="D7" s="203"/>
-      <c r="E7" s="203"/>
-      <c r="F7" s="203"/>
-      <c r="G7" s="203"/>
-      <c r="H7" s="203"/>
-      <c r="I7" s="203"/>
-      <c r="J7" s="203"/>
-      <c r="K7" s="203"/>
-      <c r="L7" s="203"/>
-      <c r="M7" s="203"/>
-      <c r="N7" s="204"/>
-      <c r="O7" s="205"/>
-      <c r="P7" s="206"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="183"/>
+      <c r="F7" s="183"/>
+      <c r="G7" s="183"/>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183"/>
+      <c r="K7" s="183"/>
+      <c r="L7" s="183"/>
+      <c r="M7" s="183"/>
+      <c r="N7" s="187"/>
+      <c r="O7" s="188"/>
+      <c r="P7" s="189"/>
       <c r="Q7" s="51"/>
-      <c r="R7" s="207"/>
-      <c r="S7" s="207"/>
+      <c r="R7" s="190"/>
+      <c r="S7" s="190"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="49"/>
       <c r="B8" s="49"/>
-      <c r="C8" s="203"/>
-      <c r="D8" s="203"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="203"/>
-      <c r="G8" s="203"/>
-      <c r="H8" s="203"/>
-      <c r="I8" s="203"/>
-      <c r="J8" s="203"/>
-      <c r="K8" s="203"/>
-      <c r="L8" s="203"/>
-      <c r="M8" s="203"/>
-      <c r="N8" s="204"/>
-      <c r="O8" s="205"/>
-      <c r="P8" s="206"/>
+      <c r="C8" s="183"/>
+      <c r="D8" s="183"/>
+      <c r="E8" s="183"/>
+      <c r="F8" s="183"/>
+      <c r="G8" s="183"/>
+      <c r="H8" s="183"/>
+      <c r="I8" s="183"/>
+      <c r="J8" s="183"/>
+      <c r="K8" s="183"/>
+      <c r="L8" s="183"/>
+      <c r="M8" s="183"/>
+      <c r="N8" s="187"/>
+      <c r="O8" s="188"/>
+      <c r="P8" s="189"/>
       <c r="Q8" s="51"/>
-      <c r="R8" s="207"/>
-      <c r="S8" s="207"/>
+      <c r="R8" s="190"/>
+      <c r="S8" s="190"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="49"/>
       <c r="B9" s="49"/>
-      <c r="C9" s="203"/>
-      <c r="D9" s="203"/>
-      <c r="E9" s="203"/>
-      <c r="F9" s="203"/>
-      <c r="G9" s="203"/>
-      <c r="H9" s="203"/>
-      <c r="I9" s="203"/>
-      <c r="J9" s="203"/>
-      <c r="K9" s="203"/>
-      <c r="L9" s="203"/>
-      <c r="M9" s="203"/>
-      <c r="N9" s="204"/>
-      <c r="O9" s="205"/>
-      <c r="P9" s="206"/>
+      <c r="C9" s="183"/>
+      <c r="D9" s="183"/>
+      <c r="E9" s="183"/>
+      <c r="F9" s="183"/>
+      <c r="G9" s="183"/>
+      <c r="H9" s="183"/>
+      <c r="I9" s="183"/>
+      <c r="J9" s="183"/>
+      <c r="K9" s="183"/>
+      <c r="L9" s="183"/>
+      <c r="M9" s="183"/>
+      <c r="N9" s="187"/>
+      <c r="O9" s="188"/>
+      <c r="P9" s="189"/>
       <c r="Q9" s="49"/>
-      <c r="R9" s="207"/>
-      <c r="S9" s="207"/>
+      <c r="R9" s="190"/>
+      <c r="S9" s="190"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="49"/>
       <c r="B10" s="49"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="203"/>
-      <c r="E10" s="203"/>
-      <c r="F10" s="203"/>
-      <c r="G10" s="203"/>
-      <c r="H10" s="208"/>
-      <c r="I10" s="209"/>
-      <c r="J10" s="209"/>
-      <c r="K10" s="209"/>
-      <c r="L10" s="209"/>
-      <c r="M10" s="210"/>
-      <c r="N10" s="204"/>
-      <c r="O10" s="205"/>
-      <c r="P10" s="206"/>
+      <c r="C10" s="183"/>
+      <c r="D10" s="183"/>
+      <c r="E10" s="183"/>
+      <c r="F10" s="183"/>
+      <c r="G10" s="183"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="185"/>
+      <c r="J10" s="185"/>
+      <c r="K10" s="185"/>
+      <c r="L10" s="185"/>
+      <c r="M10" s="186"/>
+      <c r="N10" s="187"/>
+      <c r="O10" s="188"/>
+      <c r="P10" s="189"/>
       <c r="Q10" s="51"/>
-      <c r="R10" s="207"/>
-      <c r="S10" s="207"/>
+      <c r="R10" s="190"/>
+      <c r="S10" s="190"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="49"/>
       <c r="B11" s="49"/>
-      <c r="C11" s="203"/>
-      <c r="D11" s="203"/>
-      <c r="E11" s="203"/>
-      <c r="F11" s="203"/>
-      <c r="G11" s="203"/>
-      <c r="H11" s="208"/>
-      <c r="I11" s="209"/>
-      <c r="J11" s="209"/>
-      <c r="K11" s="209"/>
-      <c r="L11" s="209"/>
-      <c r="M11" s="210"/>
-      <c r="N11" s="204"/>
-      <c r="O11" s="205"/>
-      <c r="P11" s="206"/>
+      <c r="C11" s="183"/>
+      <c r="D11" s="183"/>
+      <c r="E11" s="183"/>
+      <c r="F11" s="183"/>
+      <c r="G11" s="183"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="185"/>
+      <c r="J11" s="185"/>
+      <c r="K11" s="185"/>
+      <c r="L11" s="185"/>
+      <c r="M11" s="186"/>
+      <c r="N11" s="187"/>
+      <c r="O11" s="188"/>
+      <c r="P11" s="189"/>
       <c r="Q11" s="49"/>
-      <c r="R11" s="207"/>
-      <c r="S11" s="207"/>
+      <c r="R11" s="190"/>
+      <c r="S11" s="190"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="49"/>
       <c r="B12" s="49"/>
-      <c r="C12" s="203"/>
-      <c r="D12" s="203"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="203"/>
-      <c r="G12" s="203"/>
-      <c r="H12" s="208"/>
-      <c r="I12" s="209"/>
-      <c r="J12" s="209"/>
-      <c r="K12" s="209"/>
-      <c r="L12" s="209"/>
-      <c r="M12" s="210"/>
-      <c r="N12" s="204"/>
-      <c r="O12" s="205"/>
-      <c r="P12" s="206"/>
+      <c r="C12" s="183"/>
+      <c r="D12" s="183"/>
+      <c r="E12" s="183"/>
+      <c r="F12" s="183"/>
+      <c r="G12" s="183"/>
+      <c r="H12" s="184"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="185"/>
+      <c r="L12" s="185"/>
+      <c r="M12" s="186"/>
+      <c r="N12" s="187"/>
+      <c r="O12" s="188"/>
+      <c r="P12" s="189"/>
       <c r="Q12" s="49"/>
-      <c r="R12" s="207"/>
-      <c r="S12" s="207"/>
+      <c r="R12" s="190"/>
+      <c r="S12" s="190"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="49"/>
       <c r="B13" s="49"/>
-      <c r="C13" s="203"/>
-      <c r="D13" s="203"/>
-      <c r="E13" s="203"/>
-      <c r="F13" s="203"/>
-      <c r="G13" s="203"/>
-      <c r="H13" s="208"/>
-      <c r="I13" s="209"/>
-      <c r="J13" s="209"/>
-      <c r="K13" s="209"/>
-      <c r="L13" s="209"/>
-      <c r="M13" s="210"/>
-      <c r="N13" s="204"/>
-      <c r="O13" s="205"/>
-      <c r="P13" s="206"/>
+      <c r="C13" s="183"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="183"/>
+      <c r="F13" s="183"/>
+      <c r="G13" s="183"/>
+      <c r="H13" s="184"/>
+      <c r="I13" s="185"/>
+      <c r="J13" s="185"/>
+      <c r="K13" s="185"/>
+      <c r="L13" s="185"/>
+      <c r="M13" s="186"/>
+      <c r="N13" s="187"/>
+      <c r="O13" s="188"/>
+      <c r="P13" s="189"/>
       <c r="Q13" s="49"/>
-      <c r="R13" s="207"/>
-      <c r="S13" s="207"/>
+      <c r="R13" s="190"/>
+      <c r="S13" s="190"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="49"/>
       <c r="B14" s="49"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="203"/>
-      <c r="F14" s="203"/>
-      <c r="G14" s="203"/>
-      <c r="H14" s="208"/>
-      <c r="I14" s="209"/>
-      <c r="J14" s="209"/>
-      <c r="K14" s="209"/>
-      <c r="L14" s="209"/>
-      <c r="M14" s="210"/>
-      <c r="N14" s="204"/>
-      <c r="O14" s="205"/>
-      <c r="P14" s="206"/>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="183"/>
+      <c r="F14" s="183"/>
+      <c r="G14" s="183"/>
+      <c r="H14" s="184"/>
+      <c r="I14" s="185"/>
+      <c r="J14" s="185"/>
+      <c r="K14" s="185"/>
+      <c r="L14" s="185"/>
+      <c r="M14" s="186"/>
+      <c r="N14" s="187"/>
+      <c r="O14" s="188"/>
+      <c r="P14" s="189"/>
       <c r="Q14" s="49"/>
-      <c r="R14" s="207"/>
-      <c r="S14" s="207"/>
+      <c r="R14" s="190"/>
+      <c r="S14" s="190"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="49"/>
       <c r="B15" s="49"/>
-      <c r="C15" s="203"/>
-      <c r="D15" s="203"/>
-      <c r="E15" s="203"/>
-      <c r="F15" s="203"/>
-      <c r="G15" s="203"/>
-      <c r="H15" s="208"/>
-      <c r="I15" s="209"/>
-      <c r="J15" s="209"/>
-      <c r="K15" s="209"/>
-      <c r="L15" s="209"/>
-      <c r="M15" s="210"/>
-      <c r="N15" s="204"/>
-      <c r="O15" s="205"/>
-      <c r="P15" s="206"/>
+      <c r="C15" s="183"/>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="183"/>
+      <c r="H15" s="184"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="185"/>
+      <c r="M15" s="186"/>
+      <c r="N15" s="187"/>
+      <c r="O15" s="188"/>
+      <c r="P15" s="189"/>
       <c r="Q15" s="49"/>
-      <c r="R15" s="207"/>
-      <c r="S15" s="207"/>
+      <c r="R15" s="190"/>
+      <c r="S15" s="190"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="49"/>
       <c r="B16" s="49"/>
-      <c r="C16" s="203"/>
-      <c r="D16" s="203"/>
-      <c r="E16" s="203"/>
-      <c r="F16" s="203"/>
-      <c r="G16" s="203"/>
-      <c r="H16" s="208"/>
-      <c r="I16" s="209"/>
-      <c r="J16" s="209"/>
-      <c r="K16" s="209"/>
-      <c r="L16" s="209"/>
-      <c r="M16" s="210"/>
-      <c r="N16" s="204"/>
-      <c r="O16" s="205"/>
-      <c r="P16" s="206"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="F16" s="183"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="184"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="185"/>
+      <c r="K16" s="185"/>
+      <c r="L16" s="185"/>
+      <c r="M16" s="186"/>
+      <c r="N16" s="187"/>
+      <c r="O16" s="188"/>
+      <c r="P16" s="189"/>
       <c r="Q16" s="49"/>
-      <c r="R16" s="207"/>
-      <c r="S16" s="207"/>
+      <c r="R16" s="190"/>
+      <c r="S16" s="190"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="49"/>
       <c r="B17" s="49"/>
-      <c r="C17" s="203"/>
-      <c r="D17" s="203"/>
-      <c r="E17" s="203"/>
-      <c r="F17" s="203"/>
-      <c r="G17" s="203"/>
-      <c r="H17" s="208"/>
-      <c r="I17" s="209"/>
-      <c r="J17" s="209"/>
-      <c r="K17" s="209"/>
-      <c r="L17" s="209"/>
-      <c r="M17" s="210"/>
-      <c r="N17" s="204"/>
-      <c r="O17" s="205"/>
-      <c r="P17" s="206"/>
+      <c r="C17" s="183"/>
+      <c r="D17" s="183"/>
+      <c r="E17" s="183"/>
+      <c r="F17" s="183"/>
+      <c r="G17" s="183"/>
+      <c r="H17" s="184"/>
+      <c r="I17" s="185"/>
+      <c r="J17" s="185"/>
+      <c r="K17" s="185"/>
+      <c r="L17" s="185"/>
+      <c r="M17" s="186"/>
+      <c r="N17" s="187"/>
+      <c r="O17" s="188"/>
+      <c r="P17" s="189"/>
       <c r="Q17" s="49"/>
-      <c r="R17" s="207"/>
-      <c r="S17" s="207"/>
+      <c r="R17" s="190"/>
+      <c r="S17" s="190"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="49"/>
       <c r="B18" s="49"/>
-      <c r="C18" s="203"/>
-      <c r="D18" s="203"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="203"/>
-      <c r="G18" s="203"/>
-      <c r="H18" s="208"/>
-      <c r="I18" s="209"/>
-      <c r="J18" s="209"/>
-      <c r="K18" s="209"/>
-      <c r="L18" s="209"/>
-      <c r="M18" s="210"/>
-      <c r="N18" s="204"/>
-      <c r="O18" s="205"/>
-      <c r="P18" s="206"/>
+      <c r="C18" s="183"/>
+      <c r="D18" s="183"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="183"/>
+      <c r="G18" s="183"/>
+      <c r="H18" s="184"/>
+      <c r="I18" s="185"/>
+      <c r="J18" s="185"/>
+      <c r="K18" s="185"/>
+      <c r="L18" s="185"/>
+      <c r="M18" s="186"/>
+      <c r="N18" s="187"/>
+      <c r="O18" s="188"/>
+      <c r="P18" s="189"/>
       <c r="Q18" s="49"/>
-      <c r="R18" s="207"/>
-      <c r="S18" s="207"/>
+      <c r="R18" s="190"/>
+      <c r="S18" s="190"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="49"/>
       <c r="B19" s="49"/>
-      <c r="C19" s="203"/>
-      <c r="D19" s="203"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="203"/>
-      <c r="G19" s="203"/>
-      <c r="H19" s="208"/>
-      <c r="I19" s="209"/>
-      <c r="J19" s="209"/>
-      <c r="K19" s="209"/>
-      <c r="L19" s="209"/>
-      <c r="M19" s="210"/>
-      <c r="N19" s="204"/>
-      <c r="O19" s="205"/>
-      <c r="P19" s="206"/>
+      <c r="C19" s="183"/>
+      <c r="D19" s="183"/>
+      <c r="E19" s="183"/>
+      <c r="F19" s="183"/>
+      <c r="G19" s="183"/>
+      <c r="H19" s="184"/>
+      <c r="I19" s="185"/>
+      <c r="J19" s="185"/>
+      <c r="K19" s="185"/>
+      <c r="L19" s="185"/>
+      <c r="M19" s="186"/>
+      <c r="N19" s="187"/>
+      <c r="O19" s="188"/>
+      <c r="P19" s="189"/>
       <c r="Q19" s="49"/>
-      <c r="R19" s="207"/>
-      <c r="S19" s="207"/>
+      <c r="R19" s="190"/>
+      <c r="S19" s="190"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="49"/>
       <c r="B20" s="49"/>
-      <c r="C20" s="203"/>
-      <c r="D20" s="203"/>
-      <c r="E20" s="203"/>
-      <c r="F20" s="203"/>
-      <c r="G20" s="203"/>
-      <c r="H20" s="208"/>
-      <c r="I20" s="209"/>
-      <c r="J20" s="209"/>
-      <c r="K20" s="209"/>
-      <c r="L20" s="209"/>
-      <c r="M20" s="210"/>
-      <c r="N20" s="204"/>
-      <c r="O20" s="205"/>
-      <c r="P20" s="206"/>
+      <c r="C20" s="183"/>
+      <c r="D20" s="183"/>
+      <c r="E20" s="183"/>
+      <c r="F20" s="183"/>
+      <c r="G20" s="183"/>
+      <c r="H20" s="184"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="185"/>
+      <c r="K20" s="185"/>
+      <c r="L20" s="185"/>
+      <c r="M20" s="186"/>
+      <c r="N20" s="187"/>
+      <c r="O20" s="188"/>
+      <c r="P20" s="189"/>
       <c r="Q20" s="49"/>
-      <c r="R20" s="207"/>
-      <c r="S20" s="207"/>
+      <c r="R20" s="190"/>
+      <c r="S20" s="190"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="49"/>
       <c r="B21" s="49"/>
-      <c r="C21" s="203"/>
-      <c r="D21" s="203"/>
-      <c r="E21" s="203"/>
-      <c r="F21" s="203"/>
-      <c r="G21" s="203"/>
-      <c r="H21" s="208"/>
-      <c r="I21" s="209"/>
-      <c r="J21" s="209"/>
-      <c r="K21" s="209"/>
-      <c r="L21" s="209"/>
-      <c r="M21" s="210"/>
-      <c r="N21" s="204"/>
-      <c r="O21" s="205"/>
-      <c r="P21" s="206"/>
+      <c r="C21" s="183"/>
+      <c r="D21" s="183"/>
+      <c r="E21" s="183"/>
+      <c r="F21" s="183"/>
+      <c r="G21" s="183"/>
+      <c r="H21" s="184"/>
+      <c r="I21" s="185"/>
+      <c r="J21" s="185"/>
+      <c r="K21" s="185"/>
+      <c r="L21" s="185"/>
+      <c r="M21" s="186"/>
+      <c r="N21" s="187"/>
+      <c r="O21" s="188"/>
+      <c r="P21" s="189"/>
       <c r="Q21" s="49"/>
-      <c r="R21" s="207"/>
-      <c r="S21" s="207"/>
+      <c r="R21" s="190"/>
+      <c r="S21" s="190"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="49"/>
       <c r="B22" s="49"/>
-      <c r="C22" s="203"/>
-      <c r="D22" s="203"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="203"/>
-      <c r="G22" s="203"/>
-      <c r="H22" s="208"/>
-      <c r="I22" s="209"/>
-      <c r="J22" s="209"/>
-      <c r="K22" s="209"/>
-      <c r="L22" s="209"/>
-      <c r="M22" s="210"/>
-      <c r="N22" s="204"/>
-      <c r="O22" s="205"/>
-      <c r="P22" s="206"/>
+      <c r="C22" s="183"/>
+      <c r="D22" s="183"/>
+      <c r="E22" s="183"/>
+      <c r="F22" s="183"/>
+      <c r="G22" s="183"/>
+      <c r="H22" s="184"/>
+      <c r="I22" s="185"/>
+      <c r="J22" s="185"/>
+      <c r="K22" s="185"/>
+      <c r="L22" s="185"/>
+      <c r="M22" s="186"/>
+      <c r="N22" s="187"/>
+      <c r="O22" s="188"/>
+      <c r="P22" s="189"/>
       <c r="Q22" s="49"/>
-      <c r="R22" s="207"/>
-      <c r="S22" s="207"/>
+      <c r="R22" s="190"/>
+      <c r="S22" s="190"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="49"/>
       <c r="B23" s="49"/>
-      <c r="C23" s="203"/>
-      <c r="D23" s="203"/>
-      <c r="E23" s="203"/>
-      <c r="F23" s="203"/>
-      <c r="G23" s="203"/>
-      <c r="H23" s="208"/>
-      <c r="I23" s="209"/>
-      <c r="J23" s="209"/>
-      <c r="K23" s="209"/>
-      <c r="L23" s="209"/>
-      <c r="M23" s="210"/>
-      <c r="N23" s="204"/>
-      <c r="O23" s="205"/>
-      <c r="P23" s="206"/>
+      <c r="C23" s="183"/>
+      <c r="D23" s="183"/>
+      <c r="E23" s="183"/>
+      <c r="F23" s="183"/>
+      <c r="G23" s="183"/>
+      <c r="H23" s="184"/>
+      <c r="I23" s="185"/>
+      <c r="J23" s="185"/>
+      <c r="K23" s="185"/>
+      <c r="L23" s="185"/>
+      <c r="M23" s="186"/>
+      <c r="N23" s="187"/>
+      <c r="O23" s="188"/>
+      <c r="P23" s="189"/>
       <c r="Q23" s="49"/>
-      <c r="R23" s="207"/>
-      <c r="S23" s="207"/>
+      <c r="R23" s="190"/>
+      <c r="S23" s="190"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="49"/>
       <c r="B24" s="49"/>
-      <c r="C24" s="203"/>
-      <c r="D24" s="203"/>
-      <c r="E24" s="203"/>
-      <c r="F24" s="203"/>
-      <c r="G24" s="203"/>
-      <c r="H24" s="208"/>
-      <c r="I24" s="209"/>
-      <c r="J24" s="209"/>
-      <c r="K24" s="209"/>
-      <c r="L24" s="209"/>
-      <c r="M24" s="210"/>
-      <c r="N24" s="204"/>
-      <c r="O24" s="205"/>
-      <c r="P24" s="206"/>
+      <c r="C24" s="183"/>
+      <c r="D24" s="183"/>
+      <c r="E24" s="183"/>
+      <c r="F24" s="183"/>
+      <c r="G24" s="183"/>
+      <c r="H24" s="184"/>
+      <c r="I24" s="185"/>
+      <c r="J24" s="185"/>
+      <c r="K24" s="185"/>
+      <c r="L24" s="185"/>
+      <c r="M24" s="186"/>
+      <c r="N24" s="187"/>
+      <c r="O24" s="188"/>
+      <c r="P24" s="189"/>
       <c r="Q24" s="49"/>
-      <c r="R24" s="207"/>
-      <c r="S24" s="207"/>
+      <c r="R24" s="190"/>
+      <c r="S24" s="190"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="49"/>
       <c r="B25" s="49"/>
-      <c r="C25" s="203"/>
-      <c r="D25" s="203"/>
-      <c r="E25" s="203"/>
-      <c r="F25" s="203"/>
-      <c r="G25" s="203"/>
-      <c r="H25" s="208"/>
-      <c r="I25" s="209"/>
-      <c r="J25" s="209"/>
-      <c r="K25" s="209"/>
-      <c r="L25" s="209"/>
-      <c r="M25" s="210"/>
-      <c r="N25" s="204"/>
-      <c r="O25" s="205"/>
-      <c r="P25" s="206"/>
+      <c r="C25" s="183"/>
+      <c r="D25" s="183"/>
+      <c r="E25" s="183"/>
+      <c r="F25" s="183"/>
+      <c r="G25" s="183"/>
+      <c r="H25" s="184"/>
+      <c r="I25" s="185"/>
+      <c r="J25" s="185"/>
+      <c r="K25" s="185"/>
+      <c r="L25" s="185"/>
+      <c r="M25" s="186"/>
+      <c r="N25" s="187"/>
+      <c r="O25" s="188"/>
+      <c r="P25" s="189"/>
       <c r="Q25" s="49"/>
-      <c r="R25" s="207"/>
-      <c r="S25" s="207"/>
+      <c r="R25" s="190"/>
+      <c r="S25" s="190"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="49"/>
       <c r="B26" s="49"/>
-      <c r="C26" s="203"/>
-      <c r="D26" s="203"/>
-      <c r="E26" s="203"/>
-      <c r="F26" s="203"/>
-      <c r="G26" s="203"/>
-      <c r="H26" s="208"/>
-      <c r="I26" s="209"/>
-      <c r="J26" s="209"/>
-      <c r="K26" s="209"/>
-      <c r="L26" s="209"/>
-      <c r="M26" s="210"/>
-      <c r="N26" s="204"/>
-      <c r="O26" s="205"/>
-      <c r="P26" s="206"/>
+      <c r="C26" s="183"/>
+      <c r="D26" s="183"/>
+      <c r="E26" s="183"/>
+      <c r="F26" s="183"/>
+      <c r="G26" s="183"/>
+      <c r="H26" s="184"/>
+      <c r="I26" s="185"/>
+      <c r="J26" s="185"/>
+      <c r="K26" s="185"/>
+      <c r="L26" s="185"/>
+      <c r="M26" s="186"/>
+      <c r="N26" s="187"/>
+      <c r="O26" s="188"/>
+      <c r="P26" s="189"/>
       <c r="Q26" s="49"/>
-      <c r="R26" s="207"/>
-      <c r="S26" s="207"/>
+      <c r="R26" s="190"/>
+      <c r="S26" s="190"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="49"/>
       <c r="B27" s="49"/>
-      <c r="C27" s="203"/>
-      <c r="D27" s="203"/>
-      <c r="E27" s="203"/>
-      <c r="F27" s="203"/>
-      <c r="G27" s="203"/>
-      <c r="H27" s="208"/>
-      <c r="I27" s="209"/>
-      <c r="J27" s="209"/>
-      <c r="K27" s="209"/>
-      <c r="L27" s="209"/>
-      <c r="M27" s="210"/>
-      <c r="N27" s="204"/>
-      <c r="O27" s="205"/>
-      <c r="P27" s="206"/>
+      <c r="C27" s="183"/>
+      <c r="D27" s="183"/>
+      <c r="E27" s="183"/>
+      <c r="F27" s="183"/>
+      <c r="G27" s="183"/>
+      <c r="H27" s="184"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="185"/>
+      <c r="K27" s="185"/>
+      <c r="L27" s="185"/>
+      <c r="M27" s="186"/>
+      <c r="N27" s="187"/>
+      <c r="O27" s="188"/>
+      <c r="P27" s="189"/>
       <c r="Q27" s="49"/>
-      <c r="R27" s="207"/>
-      <c r="S27" s="207"/>
+      <c r="R27" s="190"/>
+      <c r="S27" s="190"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="49"/>
       <c r="B28" s="49"/>
-      <c r="C28" s="203"/>
-      <c r="D28" s="203"/>
-      <c r="E28" s="203"/>
-      <c r="F28" s="203"/>
-      <c r="G28" s="203"/>
-      <c r="H28" s="208"/>
-      <c r="I28" s="209"/>
-      <c r="J28" s="209"/>
-      <c r="K28" s="209"/>
-      <c r="L28" s="209"/>
-      <c r="M28" s="210"/>
-      <c r="N28" s="204"/>
-      <c r="O28" s="205"/>
-      <c r="P28" s="206"/>
+      <c r="C28" s="183"/>
+      <c r="D28" s="183"/>
+      <c r="E28" s="183"/>
+      <c r="F28" s="183"/>
+      <c r="G28" s="183"/>
+      <c r="H28" s="184"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="185"/>
+      <c r="K28" s="185"/>
+      <c r="L28" s="185"/>
+      <c r="M28" s="186"/>
+      <c r="N28" s="187"/>
+      <c r="O28" s="188"/>
+      <c r="P28" s="189"/>
       <c r="Q28" s="49"/>
-      <c r="R28" s="207"/>
-      <c r="S28" s="207"/>
+      <c r="R28" s="190"/>
+      <c r="S28" s="190"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="49"/>
       <c r="B29" s="49"/>
-      <c r="C29" s="203"/>
-      <c r="D29" s="203"/>
-      <c r="E29" s="203"/>
-      <c r="F29" s="203"/>
-      <c r="G29" s="203"/>
-      <c r="H29" s="208"/>
-      <c r="I29" s="209"/>
-      <c r="J29" s="209"/>
-      <c r="K29" s="209"/>
-      <c r="L29" s="209"/>
-      <c r="M29" s="210"/>
-      <c r="N29" s="204"/>
-      <c r="O29" s="205"/>
-      <c r="P29" s="206"/>
+      <c r="C29" s="183"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="183"/>
+      <c r="F29" s="183"/>
+      <c r="G29" s="183"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="185"/>
+      <c r="J29" s="185"/>
+      <c r="K29" s="185"/>
+      <c r="L29" s="185"/>
+      <c r="M29" s="186"/>
+      <c r="N29" s="187"/>
+      <c r="O29" s="188"/>
+      <c r="P29" s="189"/>
       <c r="Q29" s="49"/>
-      <c r="R29" s="207"/>
-      <c r="S29" s="207"/>
+      <c r="R29" s="190"/>
+      <c r="S29" s="190"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="49"/>
       <c r="B30" s="49"/>
-      <c r="C30" s="203"/>
-      <c r="D30" s="203"/>
-      <c r="E30" s="203"/>
-      <c r="F30" s="203"/>
-      <c r="G30" s="203"/>
-      <c r="H30" s="208"/>
-      <c r="I30" s="209"/>
-      <c r="J30" s="209"/>
-      <c r="K30" s="209"/>
-      <c r="L30" s="209"/>
-      <c r="M30" s="210"/>
-      <c r="N30" s="204"/>
-      <c r="O30" s="205"/>
-      <c r="P30" s="206"/>
+      <c r="C30" s="183"/>
+      <c r="D30" s="183"/>
+      <c r="E30" s="183"/>
+      <c r="F30" s="183"/>
+      <c r="G30" s="183"/>
+      <c r="H30" s="184"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="185"/>
+      <c r="K30" s="185"/>
+      <c r="L30" s="185"/>
+      <c r="M30" s="186"/>
+      <c r="N30" s="187"/>
+      <c r="O30" s="188"/>
+      <c r="P30" s="189"/>
       <c r="Q30" s="49"/>
-      <c r="R30" s="207"/>
-      <c r="S30" s="207"/>
+      <c r="R30" s="190"/>
+      <c r="S30" s="190"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="49"/>
       <c r="B31" s="49"/>
-      <c r="C31" s="203"/>
-      <c r="D31" s="203"/>
-      <c r="E31" s="203"/>
-      <c r="F31" s="203"/>
-      <c r="G31" s="203"/>
-      <c r="H31" s="208"/>
-      <c r="I31" s="209"/>
-      <c r="J31" s="209"/>
-      <c r="K31" s="209"/>
-      <c r="L31" s="209"/>
-      <c r="M31" s="210"/>
-      <c r="N31" s="204"/>
-      <c r="O31" s="205"/>
-      <c r="P31" s="206"/>
+      <c r="C31" s="183"/>
+      <c r="D31" s="183"/>
+      <c r="E31" s="183"/>
+      <c r="F31" s="183"/>
+      <c r="G31" s="183"/>
+      <c r="H31" s="184"/>
+      <c r="I31" s="185"/>
+      <c r="J31" s="185"/>
+      <c r="K31" s="185"/>
+      <c r="L31" s="185"/>
+      <c r="M31" s="186"/>
+      <c r="N31" s="187"/>
+      <c r="O31" s="188"/>
+      <c r="P31" s="189"/>
       <c r="Q31" s="49"/>
-      <c r="R31" s="207"/>
-      <c r="S31" s="207"/>
+      <c r="R31" s="190"/>
+      <c r="S31" s="190"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="49"/>
       <c r="B32" s="49"/>
-      <c r="C32" s="203"/>
-      <c r="D32" s="203"/>
-      <c r="E32" s="203"/>
-      <c r="F32" s="203"/>
-      <c r="G32" s="203"/>
-      <c r="H32" s="208"/>
-      <c r="I32" s="209"/>
-      <c r="J32" s="209"/>
-      <c r="K32" s="209"/>
-      <c r="L32" s="209"/>
-      <c r="M32" s="210"/>
-      <c r="N32" s="204"/>
-      <c r="O32" s="205"/>
-      <c r="P32" s="206"/>
+      <c r="C32" s="183"/>
+      <c r="D32" s="183"/>
+      <c r="E32" s="183"/>
+      <c r="F32" s="183"/>
+      <c r="G32" s="183"/>
+      <c r="H32" s="184"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="185"/>
+      <c r="K32" s="185"/>
+      <c r="L32" s="185"/>
+      <c r="M32" s="186"/>
+      <c r="N32" s="187"/>
+      <c r="O32" s="188"/>
+      <c r="P32" s="189"/>
       <c r="Q32" s="49"/>
-      <c r="R32" s="207"/>
-      <c r="S32" s="207"/>
+      <c r="R32" s="190"/>
+      <c r="S32" s="190"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="49"/>
       <c r="B33" s="49"/>
-      <c r="C33" s="203"/>
-      <c r="D33" s="203"/>
-      <c r="E33" s="203"/>
-      <c r="F33" s="203"/>
-      <c r="G33" s="203"/>
-      <c r="H33" s="208"/>
-      <c r="I33" s="209"/>
-      <c r="J33" s="209"/>
-      <c r="K33" s="209"/>
-      <c r="L33" s="209"/>
-      <c r="M33" s="210"/>
-      <c r="N33" s="204"/>
-      <c r="O33" s="205"/>
-      <c r="P33" s="206"/>
+      <c r="C33" s="183"/>
+      <c r="D33" s="183"/>
+      <c r="E33" s="183"/>
+      <c r="F33" s="183"/>
+      <c r="G33" s="183"/>
+      <c r="H33" s="184"/>
+      <c r="I33" s="185"/>
+      <c r="J33" s="185"/>
+      <c r="K33" s="185"/>
+      <c r="L33" s="185"/>
+      <c r="M33" s="186"/>
+      <c r="N33" s="187"/>
+      <c r="O33" s="188"/>
+      <c r="P33" s="189"/>
       <c r="Q33" s="49"/>
-      <c r="R33" s="207"/>
-      <c r="S33" s="207"/>
+      <c r="R33" s="190"/>
+      <c r="S33" s="190"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="49"/>
       <c r="B34" s="49"/>
-      <c r="C34" s="203"/>
-      <c r="D34" s="203"/>
-      <c r="E34" s="203"/>
-      <c r="F34" s="203"/>
-      <c r="G34" s="203"/>
-      <c r="H34" s="208"/>
-      <c r="I34" s="209"/>
-      <c r="J34" s="209"/>
-      <c r="K34" s="209"/>
-      <c r="L34" s="209"/>
-      <c r="M34" s="210"/>
-      <c r="N34" s="204"/>
-      <c r="O34" s="205"/>
-      <c r="P34" s="206"/>
+      <c r="C34" s="183"/>
+      <c r="D34" s="183"/>
+      <c r="E34" s="183"/>
+      <c r="F34" s="183"/>
+      <c r="G34" s="183"/>
+      <c r="H34" s="184"/>
+      <c r="I34" s="185"/>
+      <c r="J34" s="185"/>
+      <c r="K34" s="185"/>
+      <c r="L34" s="185"/>
+      <c r="M34" s="186"/>
+      <c r="N34" s="187"/>
+      <c r="O34" s="188"/>
+      <c r="P34" s="189"/>
       <c r="Q34" s="49"/>
-      <c r="R34" s="207"/>
-      <c r="S34" s="207"/>
+      <c r="R34" s="190"/>
+      <c r="S34" s="190"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
-      <c r="C35" s="203"/>
-      <c r="D35" s="203"/>
-      <c r="E35" s="203"/>
-      <c r="F35" s="203"/>
-      <c r="G35" s="203"/>
-      <c r="H35" s="208"/>
-      <c r="I35" s="209"/>
-      <c r="J35" s="209"/>
-      <c r="K35" s="209"/>
-      <c r="L35" s="209"/>
-      <c r="M35" s="210"/>
-      <c r="N35" s="204"/>
-      <c r="O35" s="205"/>
-      <c r="P35" s="206"/>
+      <c r="C35" s="183"/>
+      <c r="D35" s="183"/>
+      <c r="E35" s="183"/>
+      <c r="F35" s="183"/>
+      <c r="G35" s="183"/>
+      <c r="H35" s="184"/>
+      <c r="I35" s="185"/>
+      <c r="J35" s="185"/>
+      <c r="K35" s="185"/>
+      <c r="L35" s="185"/>
+      <c r="M35" s="186"/>
+      <c r="N35" s="187"/>
+      <c r="O35" s="188"/>
+      <c r="P35" s="189"/>
       <c r="Q35" s="49"/>
-      <c r="R35" s="207"/>
-      <c r="S35" s="207"/>
+      <c r="R35" s="190"/>
+      <c r="S35" s="190"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="49"/>
       <c r="B36" s="49"/>
-      <c r="C36" s="203"/>
-      <c r="D36" s="203"/>
-      <c r="E36" s="203"/>
-      <c r="F36" s="203"/>
-      <c r="G36" s="203"/>
-      <c r="H36" s="208"/>
-      <c r="I36" s="209"/>
-      <c r="J36" s="209"/>
-      <c r="K36" s="209"/>
-      <c r="L36" s="209"/>
-      <c r="M36" s="210"/>
-      <c r="N36" s="204"/>
-      <c r="O36" s="205"/>
-      <c r="P36" s="206"/>
+      <c r="C36" s="183"/>
+      <c r="D36" s="183"/>
+      <c r="E36" s="183"/>
+      <c r="F36" s="183"/>
+      <c r="G36" s="183"/>
+      <c r="H36" s="184"/>
+      <c r="I36" s="185"/>
+      <c r="J36" s="185"/>
+      <c r="K36" s="185"/>
+      <c r="L36" s="185"/>
+      <c r="M36" s="186"/>
+      <c r="N36" s="187"/>
+      <c r="O36" s="188"/>
+      <c r="P36" s="189"/>
       <c r="Q36" s="49"/>
-      <c r="R36" s="207"/>
-      <c r="S36" s="207"/>
+      <c r="R36" s="190"/>
+      <c r="S36" s="190"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="49"/>
       <c r="B37" s="49"/>
-      <c r="C37" s="203"/>
-      <c r="D37" s="203"/>
-      <c r="E37" s="203"/>
-      <c r="F37" s="203"/>
-      <c r="G37" s="203"/>
-      <c r="H37" s="208"/>
-      <c r="I37" s="209"/>
-      <c r="J37" s="209"/>
-      <c r="K37" s="209"/>
-      <c r="L37" s="209"/>
-      <c r="M37" s="210"/>
-      <c r="N37" s="204"/>
-      <c r="O37" s="205"/>
-      <c r="P37" s="206"/>
+      <c r="C37" s="183"/>
+      <c r="D37" s="183"/>
+      <c r="E37" s="183"/>
+      <c r="F37" s="183"/>
+      <c r="G37" s="183"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="185"/>
+      <c r="J37" s="185"/>
+      <c r="K37" s="185"/>
+      <c r="L37" s="185"/>
+      <c r="M37" s="186"/>
+      <c r="N37" s="187"/>
+      <c r="O37" s="188"/>
+      <c r="P37" s="189"/>
       <c r="Q37" s="49"/>
-      <c r="R37" s="207"/>
-      <c r="S37" s="207"/>
+      <c r="R37" s="190"/>
+      <c r="S37" s="190"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="49"/>
       <c r="B38" s="49"/>
-      <c r="C38" s="203"/>
-      <c r="D38" s="203"/>
-      <c r="E38" s="203"/>
-      <c r="F38" s="203"/>
-      <c r="G38" s="203"/>
-      <c r="H38" s="208"/>
-      <c r="I38" s="209"/>
-      <c r="J38" s="209"/>
-      <c r="K38" s="209"/>
-      <c r="L38" s="209"/>
-      <c r="M38" s="210"/>
-      <c r="N38" s="204"/>
-      <c r="O38" s="205"/>
-      <c r="P38" s="206"/>
+      <c r="C38" s="183"/>
+      <c r="D38" s="183"/>
+      <c r="E38" s="183"/>
+      <c r="F38" s="183"/>
+      <c r="G38" s="183"/>
+      <c r="H38" s="184"/>
+      <c r="I38" s="185"/>
+      <c r="J38" s="185"/>
+      <c r="K38" s="185"/>
+      <c r="L38" s="185"/>
+      <c r="M38" s="186"/>
+      <c r="N38" s="187"/>
+      <c r="O38" s="188"/>
+      <c r="P38" s="189"/>
       <c r="Q38" s="49"/>
-      <c r="R38" s="207"/>
-      <c r="S38" s="207"/>
+      <c r="R38" s="190"/>
+      <c r="S38" s="190"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="49"/>
       <c r="B39" s="49"/>
-      <c r="C39" s="203"/>
-      <c r="D39" s="203"/>
-      <c r="E39" s="203"/>
-      <c r="F39" s="203"/>
-      <c r="G39" s="203"/>
-      <c r="H39" s="208"/>
-      <c r="I39" s="209"/>
-      <c r="J39" s="209"/>
-      <c r="K39" s="209"/>
-      <c r="L39" s="209"/>
-      <c r="M39" s="210"/>
-      <c r="N39" s="204"/>
-      <c r="O39" s="205"/>
-      <c r="P39" s="206"/>
+      <c r="C39" s="183"/>
+      <c r="D39" s="183"/>
+      <c r="E39" s="183"/>
+      <c r="F39" s="183"/>
+      <c r="G39" s="183"/>
+      <c r="H39" s="184"/>
+      <c r="I39" s="185"/>
+      <c r="J39" s="185"/>
+      <c r="K39" s="185"/>
+      <c r="L39" s="185"/>
+      <c r="M39" s="186"/>
+      <c r="N39" s="187"/>
+      <c r="O39" s="188"/>
+      <c r="P39" s="189"/>
       <c r="Q39" s="49"/>
-      <c r="R39" s="207"/>
-      <c r="S39" s="207"/>
+      <c r="R39" s="190"/>
+      <c r="S39" s="190"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="49"/>
       <c r="B40" s="49"/>
-      <c r="C40" s="203"/>
-      <c r="D40" s="203"/>
-      <c r="E40" s="203"/>
-      <c r="F40" s="203"/>
-      <c r="G40" s="203"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="209"/>
-      <c r="J40" s="209"/>
-      <c r="K40" s="209"/>
-      <c r="L40" s="209"/>
-      <c r="M40" s="210"/>
-      <c r="N40" s="204"/>
-      <c r="O40" s="205"/>
-      <c r="P40" s="206"/>
+      <c r="C40" s="183"/>
+      <c r="D40" s="183"/>
+      <c r="E40" s="183"/>
+      <c r="F40" s="183"/>
+      <c r="G40" s="183"/>
+      <c r="H40" s="184"/>
+      <c r="I40" s="185"/>
+      <c r="J40" s="185"/>
+      <c r="K40" s="185"/>
+      <c r="L40" s="185"/>
+      <c r="M40" s="186"/>
+      <c r="N40" s="187"/>
+      <c r="O40" s="188"/>
+      <c r="P40" s="189"/>
       <c r="Q40" s="49"/>
-      <c r="R40" s="207"/>
-      <c r="S40" s="207"/>
+      <c r="R40" s="190"/>
+      <c r="S40" s="190"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="49"/>
       <c r="B41" s="49"/>
-      <c r="C41" s="203"/>
-      <c r="D41" s="203"/>
-      <c r="E41" s="203"/>
-      <c r="F41" s="203"/>
-      <c r="G41" s="203"/>
-      <c r="H41" s="208"/>
-      <c r="I41" s="209"/>
-      <c r="J41" s="209"/>
-      <c r="K41" s="209"/>
-      <c r="L41" s="209"/>
-      <c r="M41" s="210"/>
-      <c r="N41" s="204"/>
-      <c r="O41" s="205"/>
-      <c r="P41" s="206"/>
+      <c r="C41" s="183"/>
+      <c r="D41" s="183"/>
+      <c r="E41" s="183"/>
+      <c r="F41" s="183"/>
+      <c r="G41" s="183"/>
+      <c r="H41" s="184"/>
+      <c r="I41" s="185"/>
+      <c r="J41" s="185"/>
+      <c r="K41" s="185"/>
+      <c r="L41" s="185"/>
+      <c r="M41" s="186"/>
+      <c r="N41" s="187"/>
+      <c r="O41" s="188"/>
+      <c r="P41" s="189"/>
       <c r="Q41" s="49"/>
-      <c r="R41" s="207"/>
-      <c r="S41" s="207"/>
+      <c r="R41" s="190"/>
+      <c r="S41" s="190"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="49"/>
       <c r="B42" s="49"/>
-      <c r="C42" s="203"/>
-      <c r="D42" s="203"/>
-      <c r="E42" s="203"/>
-      <c r="F42" s="203"/>
-      <c r="G42" s="203"/>
-      <c r="H42" s="208"/>
-      <c r="I42" s="209"/>
-      <c r="J42" s="209"/>
-      <c r="K42" s="209"/>
-      <c r="L42" s="209"/>
-      <c r="M42" s="210"/>
-      <c r="N42" s="204"/>
-      <c r="O42" s="205"/>
-      <c r="P42" s="206"/>
+      <c r="C42" s="183"/>
+      <c r="D42" s="183"/>
+      <c r="E42" s="183"/>
+      <c r="F42" s="183"/>
+      <c r="G42" s="183"/>
+      <c r="H42" s="184"/>
+      <c r="I42" s="185"/>
+      <c r="J42" s="185"/>
+      <c r="K42" s="185"/>
+      <c r="L42" s="185"/>
+      <c r="M42" s="186"/>
+      <c r="N42" s="187"/>
+      <c r="O42" s="188"/>
+      <c r="P42" s="189"/>
       <c r="Q42" s="49"/>
-      <c r="R42" s="207"/>
-      <c r="S42" s="207"/>
+      <c r="R42" s="190"/>
+      <c r="S42" s="190"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="49"/>
       <c r="B43" s="49"/>
-      <c r="C43" s="203"/>
-      <c r="D43" s="203"/>
-      <c r="E43" s="203"/>
-      <c r="F43" s="203"/>
-      <c r="G43" s="203"/>
-      <c r="H43" s="208"/>
-      <c r="I43" s="209"/>
-      <c r="J43" s="209"/>
-      <c r="K43" s="209"/>
-      <c r="L43" s="209"/>
-      <c r="M43" s="210"/>
-      <c r="N43" s="204"/>
-      <c r="O43" s="205"/>
-      <c r="P43" s="206"/>
+      <c r="C43" s="183"/>
+      <c r="D43" s="183"/>
+      <c r="E43" s="183"/>
+      <c r="F43" s="183"/>
+      <c r="G43" s="183"/>
+      <c r="H43" s="184"/>
+      <c r="I43" s="185"/>
+      <c r="J43" s="185"/>
+      <c r="K43" s="185"/>
+      <c r="L43" s="185"/>
+      <c r="M43" s="186"/>
+      <c r="N43" s="187"/>
+      <c r="O43" s="188"/>
+      <c r="P43" s="189"/>
       <c r="Q43" s="49"/>
-      <c r="R43" s="207"/>
-      <c r="S43" s="207"/>
+      <c r="R43" s="190"/>
+      <c r="S43" s="190"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="49"/>
       <c r="B44" s="49"/>
-      <c r="C44" s="203"/>
-      <c r="D44" s="203"/>
-      <c r="E44" s="203"/>
-      <c r="F44" s="203"/>
-      <c r="G44" s="203"/>
-      <c r="H44" s="208"/>
-      <c r="I44" s="209"/>
-      <c r="J44" s="209"/>
-      <c r="K44" s="209"/>
-      <c r="L44" s="209"/>
-      <c r="M44" s="210"/>
-      <c r="N44" s="204"/>
-      <c r="O44" s="205"/>
-      <c r="P44" s="206"/>
+      <c r="C44" s="183"/>
+      <c r="D44" s="183"/>
+      <c r="E44" s="183"/>
+      <c r="F44" s="183"/>
+      <c r="G44" s="183"/>
+      <c r="H44" s="184"/>
+      <c r="I44" s="185"/>
+      <c r="J44" s="185"/>
+      <c r="K44" s="185"/>
+      <c r="L44" s="185"/>
+      <c r="M44" s="186"/>
+      <c r="N44" s="187"/>
+      <c r="O44" s="188"/>
+      <c r="P44" s="189"/>
       <c r="Q44" s="49"/>
-      <c r="R44" s="207"/>
-      <c r="S44" s="207"/>
+      <c r="R44" s="190"/>
+      <c r="S44" s="190"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="49"/>
       <c r="B45" s="49"/>
-      <c r="C45" s="203"/>
-      <c r="D45" s="203"/>
-      <c r="E45" s="203"/>
-      <c r="F45" s="203"/>
-      <c r="G45" s="203"/>
-      <c r="H45" s="208"/>
-      <c r="I45" s="209"/>
-      <c r="J45" s="209"/>
-      <c r="K45" s="209"/>
-      <c r="L45" s="209"/>
-      <c r="M45" s="210"/>
-      <c r="N45" s="204"/>
-      <c r="O45" s="205"/>
-      <c r="P45" s="206"/>
+      <c r="C45" s="183"/>
+      <c r="D45" s="183"/>
+      <c r="E45" s="183"/>
+      <c r="F45" s="183"/>
+      <c r="G45" s="183"/>
+      <c r="H45" s="184"/>
+      <c r="I45" s="185"/>
+      <c r="J45" s="185"/>
+      <c r="K45" s="185"/>
+      <c r="L45" s="185"/>
+      <c r="M45" s="186"/>
+      <c r="N45" s="187"/>
+      <c r="O45" s="188"/>
+      <c r="P45" s="189"/>
       <c r="Q45" s="49"/>
-      <c r="R45" s="207"/>
-      <c r="S45" s="207"/>
+      <c r="R45" s="190"/>
+      <c r="S45" s="190"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="49"/>
       <c r="B46" s="49"/>
-      <c r="C46" s="203"/>
-      <c r="D46" s="203"/>
-      <c r="E46" s="203"/>
-      <c r="F46" s="203"/>
-      <c r="G46" s="203"/>
-      <c r="H46" s="208"/>
-      <c r="I46" s="209"/>
-      <c r="J46" s="209"/>
-      <c r="K46" s="209"/>
-      <c r="L46" s="209"/>
-      <c r="M46" s="210"/>
-      <c r="N46" s="204"/>
-      <c r="O46" s="205"/>
-      <c r="P46" s="206"/>
+      <c r="C46" s="183"/>
+      <c r="D46" s="183"/>
+      <c r="E46" s="183"/>
+      <c r="F46" s="183"/>
+      <c r="G46" s="183"/>
+      <c r="H46" s="184"/>
+      <c r="I46" s="185"/>
+      <c r="J46" s="185"/>
+      <c r="K46" s="185"/>
+      <c r="L46" s="185"/>
+      <c r="M46" s="186"/>
+      <c r="N46" s="187"/>
+      <c r="O46" s="188"/>
+      <c r="P46" s="189"/>
       <c r="Q46" s="49"/>
-      <c r="R46" s="207"/>
-      <c r="S46" s="207"/>
+      <c r="R46" s="190"/>
+      <c r="S46" s="190"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="49"/>
       <c r="B47" s="49"/>
-      <c r="C47" s="203"/>
-      <c r="D47" s="203"/>
-      <c r="E47" s="203"/>
-      <c r="F47" s="203"/>
-      <c r="G47" s="203"/>
-      <c r="H47" s="208"/>
-      <c r="I47" s="209"/>
-      <c r="J47" s="209"/>
-      <c r="K47" s="209"/>
-      <c r="L47" s="209"/>
-      <c r="M47" s="210"/>
-      <c r="N47" s="204"/>
-      <c r="O47" s="205"/>
-      <c r="P47" s="206"/>
+      <c r="C47" s="183"/>
+      <c r="D47" s="183"/>
+      <c r="E47" s="183"/>
+      <c r="F47" s="183"/>
+      <c r="G47" s="183"/>
+      <c r="H47" s="184"/>
+      <c r="I47" s="185"/>
+      <c r="J47" s="185"/>
+      <c r="K47" s="185"/>
+      <c r="L47" s="185"/>
+      <c r="M47" s="186"/>
+      <c r="N47" s="187"/>
+      <c r="O47" s="188"/>
+      <c r="P47" s="189"/>
       <c r="Q47" s="49"/>
-      <c r="R47" s="207"/>
-      <c r="S47" s="207"/>
+      <c r="R47" s="190"/>
+      <c r="S47" s="190"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="49"/>
       <c r="B48" s="49"/>
-      <c r="C48" s="203"/>
-      <c r="D48" s="203"/>
-      <c r="E48" s="203"/>
-      <c r="F48" s="203"/>
-      <c r="G48" s="203"/>
-      <c r="H48" s="208"/>
-      <c r="I48" s="209"/>
-      <c r="J48" s="209"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="209"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="204"/>
-      <c r="O48" s="205"/>
-      <c r="P48" s="206"/>
+      <c r="C48" s="183"/>
+      <c r="D48" s="183"/>
+      <c r="E48" s="183"/>
+      <c r="F48" s="183"/>
+      <c r="G48" s="183"/>
+      <c r="H48" s="184"/>
+      <c r="I48" s="185"/>
+      <c r="J48" s="185"/>
+      <c r="K48" s="185"/>
+      <c r="L48" s="185"/>
+      <c r="M48" s="186"/>
+      <c r="N48" s="187"/>
+      <c r="O48" s="188"/>
+      <c r="P48" s="189"/>
       <c r="Q48" s="49"/>
-      <c r="R48" s="207"/>
-      <c r="S48" s="207"/>
+      <c r="R48" s="190"/>
+      <c r="S48" s="190"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="49"/>
       <c r="B49" s="49"/>
-      <c r="C49" s="203"/>
-      <c r="D49" s="203"/>
-      <c r="E49" s="203"/>
-      <c r="F49" s="203"/>
-      <c r="G49" s="203"/>
-      <c r="H49" s="208"/>
-      <c r="I49" s="209"/>
-      <c r="J49" s="209"/>
-      <c r="K49" s="209"/>
-      <c r="L49" s="209"/>
-      <c r="M49" s="210"/>
-      <c r="N49" s="204"/>
-      <c r="O49" s="205"/>
-      <c r="P49" s="206"/>
+      <c r="C49" s="183"/>
+      <c r="D49" s="183"/>
+      <c r="E49" s="183"/>
+      <c r="F49" s="183"/>
+      <c r="G49" s="183"/>
+      <c r="H49" s="184"/>
+      <c r="I49" s="185"/>
+      <c r="J49" s="185"/>
+      <c r="K49" s="185"/>
+      <c r="L49" s="185"/>
+      <c r="M49" s="186"/>
+      <c r="N49" s="187"/>
+      <c r="O49" s="188"/>
+      <c r="P49" s="189"/>
       <c r="Q49" s="49"/>
-      <c r="R49" s="207"/>
-      <c r="S49" s="207"/>
+      <c r="R49" s="190"/>
+      <c r="S49" s="190"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="49"/>
       <c r="B50" s="49"/>
-      <c r="C50" s="203"/>
-      <c r="D50" s="203"/>
-      <c r="E50" s="203"/>
-      <c r="F50" s="203"/>
-      <c r="G50" s="203"/>
-      <c r="H50" s="208"/>
-      <c r="I50" s="209"/>
-      <c r="J50" s="209"/>
-      <c r="K50" s="209"/>
-      <c r="L50" s="209"/>
-      <c r="M50" s="210"/>
-      <c r="N50" s="204"/>
-      <c r="O50" s="205"/>
-      <c r="P50" s="206"/>
+      <c r="C50" s="183"/>
+      <c r="D50" s="183"/>
+      <c r="E50" s="183"/>
+      <c r="F50" s="183"/>
+      <c r="G50" s="183"/>
+      <c r="H50" s="184"/>
+      <c r="I50" s="185"/>
+      <c r="J50" s="185"/>
+      <c r="K50" s="185"/>
+      <c r="L50" s="185"/>
+      <c r="M50" s="186"/>
+      <c r="N50" s="187"/>
+      <c r="O50" s="188"/>
+      <c r="P50" s="189"/>
       <c r="Q50" s="49"/>
-      <c r="R50" s="207"/>
-      <c r="S50" s="207"/>
+      <c r="R50" s="190"/>
+      <c r="S50" s="190"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="49"/>
       <c r="B51" s="49"/>
-      <c r="C51" s="203"/>
-      <c r="D51" s="203"/>
-      <c r="E51" s="203"/>
-      <c r="F51" s="203"/>
-      <c r="G51" s="203"/>
-      <c r="H51" s="208"/>
-      <c r="I51" s="209"/>
-      <c r="J51" s="209"/>
-      <c r="K51" s="209"/>
-      <c r="L51" s="209"/>
-      <c r="M51" s="210"/>
-      <c r="N51" s="204"/>
-      <c r="O51" s="205"/>
-      <c r="P51" s="206"/>
+      <c r="C51" s="183"/>
+      <c r="D51" s="183"/>
+      <c r="E51" s="183"/>
+      <c r="F51" s="183"/>
+      <c r="G51" s="183"/>
+      <c r="H51" s="184"/>
+      <c r="I51" s="185"/>
+      <c r="J51" s="185"/>
+      <c r="K51" s="185"/>
+      <c r="L51" s="185"/>
+      <c r="M51" s="186"/>
+      <c r="N51" s="187"/>
+      <c r="O51" s="188"/>
+      <c r="P51" s="189"/>
       <c r="Q51" s="49"/>
-      <c r="R51" s="207"/>
-      <c r="S51" s="207"/>
+      <c r="R51" s="190"/>
+      <c r="S51" s="190"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="49"/>
       <c r="B52" s="49"/>
-      <c r="C52" s="203"/>
-      <c r="D52" s="203"/>
-      <c r="E52" s="203"/>
-      <c r="F52" s="203"/>
-      <c r="G52" s="203"/>
-      <c r="H52" s="208"/>
-      <c r="I52" s="209"/>
-      <c r="J52" s="209"/>
-      <c r="K52" s="209"/>
-      <c r="L52" s="209"/>
-      <c r="M52" s="210"/>
-      <c r="N52" s="204"/>
-      <c r="O52" s="205"/>
-      <c r="P52" s="206"/>
+      <c r="C52" s="183"/>
+      <c r="D52" s="183"/>
+      <c r="E52" s="183"/>
+      <c r="F52" s="183"/>
+      <c r="G52" s="183"/>
+      <c r="H52" s="184"/>
+      <c r="I52" s="185"/>
+      <c r="J52" s="185"/>
+      <c r="K52" s="185"/>
+      <c r="L52" s="185"/>
+      <c r="M52" s="186"/>
+      <c r="N52" s="187"/>
+      <c r="O52" s="188"/>
+      <c r="P52" s="189"/>
       <c r="Q52" s="49"/>
-      <c r="R52" s="207"/>
-      <c r="S52" s="207"/>
+      <c r="R52" s="190"/>
+      <c r="S52" s="190"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -21218,6 +21015,194 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/削除機能詳細設計書.xlsx
+++ b/Documents/削除機能詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91766EC-5528-44A7-93B9-0CFD84348658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DE2C13-C554-41CE-B429-E6E3F8694936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="146">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -935,6 +935,35 @@
     <rPh sb="10" eb="12">
       <t>ヒョウジ</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>異常系</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態でのページ表示</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態であること</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/task-delete.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -2058,7 +2087,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2267,6 +2296,12 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="76" xfId="5" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2291,6 +2326,57 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2324,21 +2410,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2384,42 +2455,6 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2483,59 +2518,106 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2549,41 +2631,41 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2594,18 +2676,6 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2644,30 +2714,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3540,85 +3586,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="74"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="76"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3638,46 +3684,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="74"/>
-      <c r="M8" s="74"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="76"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="70" t="s">
+      <c r="G13" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="72"/>
-      <c r="I13" s="70" t="s">
+      <c r="H13" s="74"/>
+      <c r="I13" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="71"/>
-      <c r="K13" s="72"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="74"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="70"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="74"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="70"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="74"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3686,13 +3732,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="73" t="s">
+      <c r="G17" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
-      <c r="J17" s="74"/>
-      <c r="K17" s="74"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="76"/>
+      <c r="K17" s="76"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4750,23 +4796,23 @@
       <c r="AL1" s="53"/>
       <c r="AM1" s="53"/>
       <c r="AN1" s="53"/>
-      <c r="AO1" s="207" t="s">
+      <c r="AO1" s="214" t="s">
         <v>126</v>
       </c>
-      <c r="AP1" s="207"/>
-      <c r="AQ1" s="207"/>
-      <c r="AR1" s="207"/>
-      <c r="AS1" s="207"/>
-      <c r="AT1" s="208">
+      <c r="AP1" s="214"/>
+      <c r="AQ1" s="214"/>
+      <c r="AR1" s="214"/>
+      <c r="AS1" s="214"/>
+      <c r="AT1" s="215">
         <v>45821</v>
       </c>
-      <c r="AU1" s="209"/>
-      <c r="AV1" s="209"/>
-      <c r="AW1" s="209"/>
-      <c r="AX1" s="209"/>
-      <c r="AY1" s="209"/>
-      <c r="AZ1" s="209"/>
-      <c r="BA1" s="209"/>
+      <c r="AU1" s="216"/>
+      <c r="AV1" s="216"/>
+      <c r="AW1" s="216"/>
+      <c r="AX1" s="216"/>
+      <c r="AY1" s="216"/>
+      <c r="AZ1" s="216"/>
+      <c r="BA1" s="216"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -4812,54 +4858,54 @@
       <c r="AK4" s="60"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="204" t="s">
+      <c r="A5" s="211" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="205"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="205"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="206"/>
-      <c r="G5" s="210" t="s">
+      <c r="B5" s="212"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="213"/>
+      <c r="G5" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="211"/>
-      <c r="L5" s="211"/>
-      <c r="M5" s="211"/>
-      <c r="N5" s="211"/>
-      <c r="O5" s="211"/>
-      <c r="P5" s="211"/>
-      <c r="Q5" s="211"/>
-      <c r="R5" s="211"/>
-      <c r="S5" s="212"/>
+      <c r="H5" s="218"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="218"/>
+      <c r="K5" s="218"/>
+      <c r="L5" s="218"/>
+      <c r="M5" s="218"/>
+      <c r="N5" s="218"/>
+      <c r="O5" s="218"/>
+      <c r="P5" s="218"/>
+      <c r="Q5" s="218"/>
+      <c r="R5" s="218"/>
+      <c r="S5" s="219"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="211" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="205"/>
-      <c r="C6" s="205"/>
-      <c r="D6" s="205"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="206"/>
-      <c r="G6" s="213">
+      <c r="B6" s="212"/>
+      <c r="C6" s="212"/>
+      <c r="D6" s="212"/>
+      <c r="E6" s="212"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="220">
         <v>1</v>
       </c>
-      <c r="H6" s="211"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="211"/>
-      <c r="K6" s="211"/>
-      <c r="L6" s="211"/>
-      <c r="M6" s="211"/>
-      <c r="N6" s="211"/>
-      <c r="O6" s="211"/>
-      <c r="P6" s="211"/>
-      <c r="Q6" s="211"/>
-      <c r="R6" s="211"/>
-      <c r="S6" s="212"/>
+      <c r="H6" s="218"/>
+      <c r="I6" s="218"/>
+      <c r="J6" s="218"/>
+      <c r="K6" s="218"/>
+      <c r="L6" s="218"/>
+      <c r="M6" s="218"/>
+      <c r="N6" s="218"/>
+      <c r="O6" s="218"/>
+      <c r="P6" s="218"/>
+      <c r="Q6" s="218"/>
+      <c r="R6" s="218"/>
+      <c r="S6" s="219"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -4868,61 +4914,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="204" t="s">
+      <c r="A9" s="211" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="205"/>
-      <c r="C9" s="205"/>
-      <c r="D9" s="205"/>
-      <c r="E9" s="205"/>
-      <c r="F9" s="205"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="205"/>
-      <c r="I9" s="205"/>
-      <c r="J9" s="205"/>
-      <c r="K9" s="205"/>
-      <c r="L9" s="205"/>
-      <c r="M9" s="205"/>
-      <c r="N9" s="205"/>
-      <c r="O9" s="205"/>
-      <c r="P9" s="205"/>
-      <c r="Q9" s="205"/>
-      <c r="R9" s="205"/>
-      <c r="S9" s="205"/>
-      <c r="T9" s="205"/>
-      <c r="U9" s="205"/>
-      <c r="V9" s="205"/>
-      <c r="W9" s="205"/>
-      <c r="X9" s="205"/>
-      <c r="Y9" s="205"/>
-      <c r="Z9" s="205"/>
-      <c r="AA9" s="205"/>
-      <c r="AB9" s="205"/>
-      <c r="AC9" s="205"/>
-      <c r="AD9" s="205"/>
-      <c r="AE9" s="205"/>
-      <c r="AF9" s="205"/>
-      <c r="AG9" s="205"/>
-      <c r="AH9" s="205"/>
-      <c r="AI9" s="205"/>
-      <c r="AJ9" s="205"/>
-      <c r="AK9" s="205"/>
-      <c r="AL9" s="205"/>
-      <c r="AM9" s="205"/>
-      <c r="AN9" s="205"/>
-      <c r="AO9" s="205"/>
-      <c r="AP9" s="205"/>
-      <c r="AQ9" s="205"/>
-      <c r="AR9" s="205"/>
-      <c r="AS9" s="205"/>
-      <c r="AT9" s="205"/>
-      <c r="AU9" s="205"/>
-      <c r="AV9" s="205"/>
-      <c r="AW9" s="205"/>
-      <c r="AX9" s="205"/>
-      <c r="AY9" s="205"/>
-      <c r="AZ9" s="205"/>
-      <c r="BA9" s="206"/>
+      <c r="B9" s="212"/>
+      <c r="C9" s="212"/>
+      <c r="D9" s="212"/>
+      <c r="E9" s="212"/>
+      <c r="F9" s="212"/>
+      <c r="G9" s="212"/>
+      <c r="H9" s="212"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="212"/>
+      <c r="K9" s="212"/>
+      <c r="L9" s="212"/>
+      <c r="M9" s="212"/>
+      <c r="N9" s="212"/>
+      <c r="O9" s="212"/>
+      <c r="P9" s="212"/>
+      <c r="Q9" s="212"/>
+      <c r="R9" s="212"/>
+      <c r="S9" s="212"/>
+      <c r="T9" s="212"/>
+      <c r="U9" s="212"/>
+      <c r="V9" s="212"/>
+      <c r="W9" s="212"/>
+      <c r="X9" s="212"/>
+      <c r="Y9" s="212"/>
+      <c r="Z9" s="212"/>
+      <c r="AA9" s="212"/>
+      <c r="AB9" s="212"/>
+      <c r="AC9" s="212"/>
+      <c r="AD9" s="212"/>
+      <c r="AE9" s="212"/>
+      <c r="AF9" s="212"/>
+      <c r="AG9" s="212"/>
+      <c r="AH9" s="212"/>
+      <c r="AI9" s="212"/>
+      <c r="AJ9" s="212"/>
+      <c r="AK9" s="212"/>
+      <c r="AL9" s="212"/>
+      <c r="AM9" s="212"/>
+      <c r="AN9" s="212"/>
+      <c r="AO9" s="212"/>
+      <c r="AP9" s="212"/>
+      <c r="AQ9" s="212"/>
+      <c r="AR9" s="212"/>
+      <c r="AS9" s="212"/>
+      <c r="AT9" s="212"/>
+      <c r="AU9" s="212"/>
+      <c r="AV9" s="212"/>
+      <c r="AW9" s="212"/>
+      <c r="AX9" s="212"/>
+      <c r="AY9" s="212"/>
+      <c r="AZ9" s="212"/>
+      <c r="BA9" s="213"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="62"/>
@@ -8645,61 +8691,61 @@
       <c r="BA102" s="64"/>
     </row>
     <row r="103" spans="1:53" ht="18" customHeight="1">
-      <c r="A103" s="204" t="s">
+      <c r="A103" s="211" t="s">
         <v>132</v>
       </c>
-      <c r="B103" s="205"/>
-      <c r="C103" s="205"/>
-      <c r="D103" s="205"/>
-      <c r="E103" s="205"/>
-      <c r="F103" s="205"/>
-      <c r="G103" s="205"/>
-      <c r="H103" s="205"/>
-      <c r="I103" s="205"/>
-      <c r="J103" s="205"/>
-      <c r="K103" s="205"/>
-      <c r="L103" s="205"/>
-      <c r="M103" s="205"/>
-      <c r="N103" s="205"/>
-      <c r="O103" s="205"/>
-      <c r="P103" s="205"/>
-      <c r="Q103" s="205"/>
-      <c r="R103" s="205"/>
-      <c r="S103" s="205"/>
-      <c r="T103" s="205"/>
-      <c r="U103" s="205"/>
-      <c r="V103" s="205"/>
-      <c r="W103" s="205"/>
-      <c r="X103" s="205"/>
-      <c r="Y103" s="205"/>
-      <c r="Z103" s="205"/>
-      <c r="AA103" s="205"/>
-      <c r="AB103" s="205"/>
-      <c r="AC103" s="205"/>
-      <c r="AD103" s="205"/>
-      <c r="AE103" s="205"/>
-      <c r="AF103" s="205"/>
-      <c r="AG103" s="205"/>
-      <c r="AH103" s="205"/>
-      <c r="AI103" s="205"/>
-      <c r="AJ103" s="205"/>
-      <c r="AK103" s="205"/>
-      <c r="AL103" s="205"/>
-      <c r="AM103" s="205"/>
-      <c r="AN103" s="205"/>
-      <c r="AO103" s="205"/>
-      <c r="AP103" s="205"/>
-      <c r="AQ103" s="205"/>
-      <c r="AR103" s="205"/>
-      <c r="AS103" s="205"/>
-      <c r="AT103" s="205"/>
-      <c r="AU103" s="205"/>
-      <c r="AV103" s="205"/>
-      <c r="AW103" s="205"/>
-      <c r="AX103" s="205"/>
-      <c r="AY103" s="205"/>
-      <c r="AZ103" s="205"/>
-      <c r="BA103" s="206"/>
+      <c r="B103" s="212"/>
+      <c r="C103" s="212"/>
+      <c r="D103" s="212"/>
+      <c r="E103" s="212"/>
+      <c r="F103" s="212"/>
+      <c r="G103" s="212"/>
+      <c r="H103" s="212"/>
+      <c r="I103" s="212"/>
+      <c r="J103" s="212"/>
+      <c r="K103" s="212"/>
+      <c r="L103" s="212"/>
+      <c r="M103" s="212"/>
+      <c r="N103" s="212"/>
+      <c r="O103" s="212"/>
+      <c r="P103" s="212"/>
+      <c r="Q103" s="212"/>
+      <c r="R103" s="212"/>
+      <c r="S103" s="212"/>
+      <c r="T103" s="212"/>
+      <c r="U103" s="212"/>
+      <c r="V103" s="212"/>
+      <c r="W103" s="212"/>
+      <c r="X103" s="212"/>
+      <c r="Y103" s="212"/>
+      <c r="Z103" s="212"/>
+      <c r="AA103" s="212"/>
+      <c r="AB103" s="212"/>
+      <c r="AC103" s="212"/>
+      <c r="AD103" s="212"/>
+      <c r="AE103" s="212"/>
+      <c r="AF103" s="212"/>
+      <c r="AG103" s="212"/>
+      <c r="AH103" s="212"/>
+      <c r="AI103" s="212"/>
+      <c r="AJ103" s="212"/>
+      <c r="AK103" s="212"/>
+      <c r="AL103" s="212"/>
+      <c r="AM103" s="212"/>
+      <c r="AN103" s="212"/>
+      <c r="AO103" s="212"/>
+      <c r="AP103" s="212"/>
+      <c r="AQ103" s="212"/>
+      <c r="AR103" s="212"/>
+      <c r="AS103" s="212"/>
+      <c r="AT103" s="212"/>
+      <c r="AU103" s="212"/>
+      <c r="AV103" s="212"/>
+      <c r="AW103" s="212"/>
+      <c r="AX103" s="212"/>
+      <c r="AY103" s="212"/>
+      <c r="AZ103" s="212"/>
+      <c r="BA103" s="213"/>
     </row>
     <row r="104" spans="1:53" ht="21.95" customHeight="1">
       <c r="A104" s="65"/>
@@ -9022,61 +9068,61 @@
       <c r="BA111" s="64"/>
     </row>
     <row r="112" spans="1:53" ht="18" customHeight="1">
-      <c r="A112" s="204" t="s">
+      <c r="A112" s="211" t="s">
         <v>133</v>
       </c>
-      <c r="B112" s="205"/>
-      <c r="C112" s="205"/>
-      <c r="D112" s="205"/>
-      <c r="E112" s="205"/>
-      <c r="F112" s="205"/>
-      <c r="G112" s="205"/>
-      <c r="H112" s="205"/>
-      <c r="I112" s="205"/>
-      <c r="J112" s="205"/>
-      <c r="K112" s="205"/>
-      <c r="L112" s="205"/>
-      <c r="M112" s="205"/>
-      <c r="N112" s="205"/>
-      <c r="O112" s="205"/>
-      <c r="P112" s="205"/>
-      <c r="Q112" s="205"/>
-      <c r="R112" s="205"/>
-      <c r="S112" s="205"/>
-      <c r="T112" s="205"/>
-      <c r="U112" s="205"/>
-      <c r="V112" s="205"/>
-      <c r="W112" s="205"/>
-      <c r="X112" s="205"/>
-      <c r="Y112" s="205"/>
-      <c r="Z112" s="205"/>
-      <c r="AA112" s="205"/>
-      <c r="AB112" s="205"/>
-      <c r="AC112" s="205"/>
-      <c r="AD112" s="205"/>
-      <c r="AE112" s="205"/>
-      <c r="AF112" s="205"/>
-      <c r="AG112" s="205"/>
-      <c r="AH112" s="205"/>
-      <c r="AI112" s="205"/>
-      <c r="AJ112" s="205"/>
-      <c r="AK112" s="205"/>
-      <c r="AL112" s="205"/>
-      <c r="AM112" s="205"/>
-      <c r="AN112" s="205"/>
-      <c r="AO112" s="205"/>
-      <c r="AP112" s="205"/>
-      <c r="AQ112" s="205"/>
-      <c r="AR112" s="205"/>
-      <c r="AS112" s="205"/>
-      <c r="AT112" s="205"/>
-      <c r="AU112" s="205"/>
-      <c r="AV112" s="205"/>
-      <c r="AW112" s="205"/>
-      <c r="AX112" s="205"/>
-      <c r="AY112" s="205"/>
-      <c r="AZ112" s="205"/>
-      <c r="BA112" s="205"/>
+      <c r="B112" s="212"/>
+      <c r="C112" s="212"/>
+      <c r="D112" s="212"/>
+      <c r="E112" s="212"/>
+      <c r="F112" s="212"/>
+      <c r="G112" s="212"/>
+      <c r="H112" s="212"/>
+      <c r="I112" s="212"/>
+      <c r="J112" s="212"/>
+      <c r="K112" s="212"/>
+      <c r="L112" s="212"/>
+      <c r="M112" s="212"/>
+      <c r="N112" s="212"/>
+      <c r="O112" s="212"/>
+      <c r="P112" s="212"/>
+      <c r="Q112" s="212"/>
+      <c r="R112" s="212"/>
+      <c r="S112" s="212"/>
+      <c r="T112" s="212"/>
+      <c r="U112" s="212"/>
+      <c r="V112" s="212"/>
+      <c r="W112" s="212"/>
+      <c r="X112" s="212"/>
+      <c r="Y112" s="212"/>
+      <c r="Z112" s="212"/>
+      <c r="AA112" s="212"/>
+      <c r="AB112" s="212"/>
+      <c r="AC112" s="212"/>
+      <c r="AD112" s="212"/>
+      <c r="AE112" s="212"/>
+      <c r="AF112" s="212"/>
+      <c r="AG112" s="212"/>
+      <c r="AH112" s="212"/>
+      <c r="AI112" s="212"/>
+      <c r="AJ112" s="212"/>
+      <c r="AK112" s="212"/>
+      <c r="AL112" s="212"/>
+      <c r="AM112" s="212"/>
+      <c r="AN112" s="212"/>
+      <c r="AO112" s="212"/>
+      <c r="AP112" s="212"/>
+      <c r="AQ112" s="212"/>
+      <c r="AR112" s="212"/>
+      <c r="AS112" s="212"/>
+      <c r="AT112" s="212"/>
+      <c r="AU112" s="212"/>
+      <c r="AV112" s="212"/>
+      <c r="AW112" s="212"/>
+      <c r="AX112" s="212"/>
+      <c r="AY112" s="212"/>
+      <c r="AZ112" s="212"/>
+      <c r="BA112" s="212"/>
     </row>
     <row r="113" spans="1:53" ht="21.95" customHeight="1">
       <c r="A113" s="65"/>
@@ -9250,19 +9296,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="103" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="86"/>
-      <c r="F1" s="103" t="s">
+      <c r="E1" s="105"/>
+      <c r="F1" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="86"/>
+      <c r="G1" s="105"/>
       <c r="H1" s="37" t="s">
         <v>8</v>
       </c>
@@ -9274,190 +9320,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="97"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="104" t="s">
+      <c r="A2" s="111"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="104" t="s">
+      <c r="E2" s="119"/>
+      <c r="F2" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="105"/>
-      <c r="H2" s="108">
+      <c r="G2" s="119"/>
+      <c r="H2" s="122">
         <v>45806</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="I2" s="97" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="81"/>
+      <c r="J2" s="100"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="97"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="82"/>
+      <c r="A3" s="111"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="101"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="100"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="114"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="87" t="s">
+      <c r="B5" s="104"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="88"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="107"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="92" t="s">
+      <c r="B6" s="81"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="93"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="84"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="91"/>
-      <c r="D7" s="92" t="s">
+      <c r="B7" s="81"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="90"/>
-      <c r="F7" s="90"/>
-      <c r="G7" s="90"/>
-      <c r="H7" s="90"/>
-      <c r="I7" s="90"/>
-      <c r="J7" s="93"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="84"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="89" t="s">
+      <c r="A8" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="90"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="92" t="s">
+      <c r="B8" s="81"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="93"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="84"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="115" t="s">
+      <c r="A9" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="118" t="s">
+      <c r="B9" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="91"/>
-      <c r="D9" s="109" t="s">
+      <c r="C9" s="82"/>
+      <c r="D9" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="96"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="116"/>
-      <c r="B10" s="118" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="93"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="84"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="117"/>
-      <c r="B11" s="118" t="s">
+      <c r="A11" s="93"/>
+      <c r="B11" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="91"/>
-      <c r="D11" s="92" t="s">
+      <c r="C11" s="82"/>
+      <c r="D11" s="90" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="90"/>
-      <c r="J11" s="93"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="84"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="90"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="109" t="s">
+      <c r="B12" s="81"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="83" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="90"/>
-      <c r="J12" s="93"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="84"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="110" t="s">
+      <c r="A13" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="111"/>
-      <c r="C13" s="112"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="114"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10448,6 +10494,18 @@
     <row r="1000" s="39" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -10463,18 +10521,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -10493,19 +10539,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="136" t="s">
+      <c r="E1" s="139"/>
+      <c r="F1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="139"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -10517,48 +10563,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="138">
+      <c r="E2" s="141"/>
+      <c r="F2" s="140">
         <v>56</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="121">
+      <c r="G2" s="141"/>
+      <c r="H2" s="123">
         <v>45811</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="125"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="126"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="127"/>
+      <c r="A4" s="135"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="129"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -11915,19 +11961,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="136" t="s">
+      <c r="E1" s="139"/>
+      <c r="F1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="139"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11939,48 +11985,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="138">
+      <c r="E2" s="141"/>
+      <c r="F2" s="140">
         <v>56</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="121">
+      <c r="G2" s="141"/>
+      <c r="H2" s="123">
         <v>45807</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="125"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="126"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="127"/>
+      <c r="A4" s="135"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="129"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -13331,19 +13377,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="136" t="s">
+      <c r="E1" s="139"/>
+      <c r="F1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="139"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -13355,190 +13401,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="138" t="s">
+      <c r="E2" s="141"/>
+      <c r="F2" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="121">
+      <c r="G2" s="141"/>
+      <c r="H2" s="123">
         <v>45807</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="125"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="126"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="131"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="126"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="144" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="154" t="s">
+      <c r="B5" s="145"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="155"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="149"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="145" t="s">
+      <c r="A6" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="144"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="150"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="156"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="158"/>
+      <c r="A7" s="151"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="152"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="152"/>
+      <c r="I7" s="152"/>
+      <c r="J7" s="153"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="131"/>
-      <c r="B8" s="74"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="159"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="154"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="131"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="159"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="154"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="131"/>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="159"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="154"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="131"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="159"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="154"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="131"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="159"/>
+      <c r="A12" s="133"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="154"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="131"/>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="159"/>
+      <c r="A13" s="133"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="154"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="145" t="s">
+      <c r="A14" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="144"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="150"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="147" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="143" t="s">
+      <c r="B15" s="73"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="155" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="74"/>
       <c r="I15" s="14" t="s">
         <v>28</v>
       </c>
@@ -13547,11 +13593,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="147" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="74"/>
       <c r="D16" s="14" t="s">
         <v>30</v>
       </c>
@@ -13564,18 +13610,18 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="146" t="s">
+      <c r="H16" s="156" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="144"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="150"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="142">
+      <c r="A17" s="146">
         <v>1</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="74"/>
       <c r="D17" s="16" t="s">
         <v>75</v>
       </c>
@@ -13586,16 +13632,16 @@
         <v>82</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="143"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="144"/>
+      <c r="H17" s="155"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="150"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="142">
+      <c r="A18" s="146">
         <v>2</v>
       </c>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="74"/>
       <c r="D18" s="16" t="s">
         <v>76</v>
       </c>
@@ -13608,16 +13654,16 @@
       <c r="G18" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="143"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="144"/>
+      <c r="H18" s="155"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="150"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="142">
+      <c r="A19" s="146">
         <v>3</v>
       </c>
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="74"/>
       <c r="D19" s="16" t="s">
         <v>77</v>
       </c>
@@ -13628,16 +13674,16 @@
       <c r="G19" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="143"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="144"/>
+      <c r="H19" s="155"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="150"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="142">
+      <c r="A20" s="146">
         <v>4</v>
       </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="74"/>
       <c r="D20" s="16" t="s">
         <v>78</v>
       </c>
@@ -13650,16 +13696,16 @@
       <c r="G20" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="143"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="144"/>
+      <c r="H20" s="155"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="150"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="142">
+      <c r="A21" s="146">
         <v>5</v>
       </c>
-      <c r="B21" s="71"/>
-      <c r="C21" s="72"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="74"/>
       <c r="D21" s="16" t="s">
         <v>79</v>
       </c>
@@ -13672,16 +13718,16 @@
       <c r="G21" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="143"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="144"/>
+      <c r="H21" s="155"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="150"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="142">
+      <c r="A22" s="146">
         <v>6</v>
       </c>
-      <c r="B22" s="71"/>
-      <c r="C22" s="72"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="74"/>
       <c r="D22" s="16" t="s">
         <v>61</v>
       </c>
@@ -13692,16 +13738,16 @@
         <v>61</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="144"/>
+      <c r="H22" s="155"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="150"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="142">
+      <c r="A23" s="146">
         <v>7</v>
       </c>
-      <c r="B23" s="71"/>
-      <c r="C23" s="72"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="18" t="s">
         <v>61</v>
       </c>
@@ -13712,225 +13758,225 @@
         <v>61</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="148"/>
-      <c r="J23" s="151"/>
+      <c r="H23" s="157"/>
+      <c r="I23" s="158"/>
+      <c r="J23" s="159"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="145"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="144"/>
+      <c r="A24" s="147"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73"/>
+      <c r="J24" s="150"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="145"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="143"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="72"/>
+      <c r="A25" s="147"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="155"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="74"/>
       <c r="I25" s="14"/>
       <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="145"/>
-      <c r="B26" s="71"/>
-      <c r="C26" s="72"/>
+      <c r="A26" s="147"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="74"/>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="146"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="144"/>
+      <c r="H26" s="156"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="150"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="142"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="72"/>
+      <c r="A27" s="146"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="74"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="143"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="144"/>
+      <c r="H27" s="155"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="150"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="142"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="72"/>
+      <c r="A28" s="146"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="74"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="143"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="144"/>
+      <c r="H28" s="155"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="150"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="142"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="72"/>
+      <c r="A29" s="146"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="74"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
-      <c r="H29" s="143"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="144"/>
+      <c r="H29" s="155"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="150"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="142"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="72"/>
+      <c r="A30" s="146"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="74"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="143"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="144"/>
+      <c r="H30" s="155"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="150"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="142"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="72"/>
+      <c r="A31" s="146"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="74"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="143"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="144"/>
+      <c r="H31" s="155"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="150"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="142"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="72"/>
+      <c r="A32" s="146"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="74"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="143"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="144"/>
+      <c r="H32" s="155"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="150"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="147"/>
-      <c r="B33" s="148"/>
-      <c r="C33" s="149"/>
+      <c r="A33" s="160"/>
+      <c r="B33" s="158"/>
+      <c r="C33" s="161"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
-      <c r="H33" s="150"/>
-      <c r="I33" s="148"/>
-      <c r="J33" s="151"/>
+      <c r="H33" s="157"/>
+      <c r="I33" s="158"/>
+      <c r="J33" s="159"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="145"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="144"/>
+      <c r="A34" s="147"/>
+      <c r="B34" s="73"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="150"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="145"/>
-      <c r="B35" s="71"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="143"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="72"/>
+      <c r="A35" s="147"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="155"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="74"/>
       <c r="I35" s="14"/>
       <c r="J35" s="15"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="145"/>
-      <c r="B36" s="71"/>
-      <c r="C36" s="72"/>
+      <c r="A36" s="147"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="74"/>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
-      <c r="H36" s="146"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="144"/>
+      <c r="H36" s="156"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="150"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="142"/>
-      <c r="B37" s="71"/>
-      <c r="C37" s="72"/>
+      <c r="A37" s="146"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="74"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="143"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="144"/>
+      <c r="H37" s="155"/>
+      <c r="I37" s="73"/>
+      <c r="J37" s="150"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="142"/>
-      <c r="B38" s="71"/>
-      <c r="C38" s="72"/>
+      <c r="A38" s="146"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="74"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="143"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="144"/>
+      <c r="H38" s="155"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="150"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="142"/>
-      <c r="B39" s="71"/>
-      <c r="C39" s="72"/>
+      <c r="A39" s="146"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="74"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="143"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="144"/>
+      <c r="H39" s="155"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="150"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="142"/>
-      <c r="B40" s="71"/>
-      <c r="C40" s="72"/>
+      <c r="A40" s="146"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="74"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="143"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="144"/>
+      <c r="H40" s="155"/>
+      <c r="I40" s="73"/>
+      <c r="J40" s="150"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="142"/>
-      <c r="B41" s="71"/>
-      <c r="C41" s="72"/>
+      <c r="A41" s="146"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="74"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="143"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="144"/>
+      <c r="H41" s="155"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="150"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14893,11 +14939,50 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -14914,50 +14999,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14980,19 +15026,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="136" t="s">
+      <c r="E1" s="139"/>
+      <c r="F1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="139"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -15004,190 +15050,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="138" t="s">
+      <c r="E2" s="141"/>
+      <c r="F2" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="121">
+      <c r="G2" s="141"/>
+      <c r="H2" s="123">
         <v>45807</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="125"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="126"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="131"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="126"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="144" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="154" t="s">
+      <c r="B5" s="145"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="155"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="149"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="145" t="s">
+      <c r="A6" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="144"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="150"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="156"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="158"/>
+      <c r="A7" s="151"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="152"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="152"/>
+      <c r="I7" s="152"/>
+      <c r="J7" s="153"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="131"/>
-      <c r="B8" s="74"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="159"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="154"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="131"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="159"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="154"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="131"/>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="159"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="154"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="131"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="159"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="154"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="131"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="159"/>
+      <c r="A12" s="133"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="154"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="131"/>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="159"/>
+      <c r="A13" s="133"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="154"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="145" t="s">
+      <c r="A14" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="144"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="150"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="147" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="143" t="s">
+      <c r="B15" s="73"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="74"/>
       <c r="I15" s="14" t="s">
         <v>28</v>
       </c>
@@ -15196,11 +15242,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="147" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="74"/>
       <c r="D16" s="14" t="s">
         <v>30</v>
       </c>
@@ -15213,18 +15259,18 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="146" t="s">
+      <c r="H16" s="156" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="144"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="150"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="142">
+      <c r="A17" s="146">
         <v>1</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="74"/>
       <c r="D17" s="16" t="s">
         <v>61</v>
       </c>
@@ -15237,83 +15283,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="143" t="s">
+      <c r="H17" s="155" t="s">
         <v>64</v>
       </c>
-      <c r="I17" s="71"/>
-      <c r="J17" s="144"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="150"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="142"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="74"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="143"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="144"/>
+      <c r="H18" s="155"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="150"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="142"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
+      <c r="A19" s="146"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="74"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="143"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="144"/>
+      <c r="H19" s="155"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="150"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="142"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
+      <c r="A20" s="146"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="74"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="143"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="144"/>
+      <c r="H20" s="155"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="150"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="142"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="72"/>
+      <c r="A21" s="146"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="74"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="144"/>
+      <c r="H21" s="155"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="150"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="142"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="72"/>
+      <c r="A22" s="146"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="74"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="144"/>
+      <c r="H22" s="155"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="150"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="147"/>
-      <c r="B23" s="148"/>
-      <c r="C23" s="149"/>
+      <c r="A23" s="160"/>
+      <c r="B23" s="158"/>
+      <c r="C23" s="161"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="148"/>
-      <c r="J23" s="151"/>
+      <c r="H23" s="157"/>
+      <c r="I23" s="158"/>
+      <c r="J23" s="159"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -16294,6 +16340,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -16309,22 +16371,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -16347,19 +16393,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="136" t="s">
+      <c r="E1" s="139"/>
+      <c r="F1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="139"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -16371,190 +16417,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="138" t="s">
+      <c r="E2" s="141"/>
+      <c r="F2" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="121">
+      <c r="G2" s="141"/>
+      <c r="H2" s="123">
         <v>45805</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="125"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="126"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="131"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="126"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="144" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="154" t="s">
+      <c r="B5" s="145"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="148" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="155"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="149"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="145" t="s">
+      <c r="A6" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="144"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="150"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="156"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="158"/>
+      <c r="A7" s="151"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="152"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="152"/>
+      <c r="I7" s="152"/>
+      <c r="J7" s="153"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="131"/>
-      <c r="B8" s="74"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="159"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="154"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="131"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="159"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="154"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="131"/>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="159"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="154"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="131"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="159"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="154"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="131"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="159"/>
+      <c r="A12" s="133"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="154"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="131"/>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="159"/>
+      <c r="A13" s="133"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="154"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="145" t="s">
+      <c r="A14" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="144"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="150"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="147" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="143" t="s">
+      <c r="B15" s="73"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="74"/>
       <c r="I15" s="14" t="s">
         <v>28</v>
       </c>
@@ -16563,11 +16609,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="147" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="74"/>
       <c r="D16" s="14" t="s">
         <v>30</v>
       </c>
@@ -16580,18 +16626,18 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="146" t="s">
+      <c r="H16" s="156" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="144"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="150"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="142">
+      <c r="A17" s="146">
         <v>1</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="74"/>
       <c r="D17" s="16" t="s">
         <v>61</v>
       </c>
@@ -16604,83 +16650,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="143" t="s">
+      <c r="H17" s="155" t="s">
         <v>64</v>
       </c>
-      <c r="I17" s="71"/>
-      <c r="J17" s="144"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="150"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="142"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="74"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="143"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="144"/>
+      <c r="H18" s="155"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="150"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="142"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
+      <c r="A19" s="146"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="74"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="143"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="144"/>
+      <c r="H19" s="155"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="150"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="142"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
+      <c r="A20" s="146"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="74"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="143"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="144"/>
+      <c r="H20" s="155"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="150"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="142"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="72"/>
+      <c r="A21" s="146"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="74"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="144"/>
+      <c r="H21" s="155"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="150"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="142"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="72"/>
+      <c r="A22" s="146"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="74"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="144"/>
+      <c r="H22" s="155"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="150"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="147"/>
-      <c r="B23" s="148"/>
-      <c r="C23" s="149"/>
+      <c r="A23" s="160"/>
+      <c r="B23" s="158"/>
+      <c r="C23" s="161"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="148"/>
-      <c r="J23" s="151"/>
+      <c r="H23" s="157"/>
+      <c r="I23" s="158"/>
+      <c r="J23" s="159"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -17661,6 +17707,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -17676,22 +17738,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -17714,187 +17760,187 @@
       <c r="A1" s="171" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="136" t="s">
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="153"/>
-      <c r="M1" s="153"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="136" t="s">
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="136" t="s">
+      <c r="P1" s="139"/>
+      <c r="Q1" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="137"/>
-      <c r="S1" s="136" t="s">
+      <c r="R1" s="139"/>
+      <c r="S1" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="155"/>
+      <c r="T1" s="149"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="138" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="138" t="s">
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="140" t="s">
         <v>93</v>
       </c>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="139"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="141"/>
       <c r="O2" s="169">
         <v>45821</v>
       </c>
-      <c r="P2" s="139"/>
-      <c r="Q2" s="138" t="s">
+      <c r="P2" s="141"/>
+      <c r="Q2" s="140" t="s">
         <v>94</v>
       </c>
-      <c r="R2" s="139"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="158"/>
+      <c r="R2" s="141"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="153"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="132"/>
-      <c r="O3" s="140"/>
-      <c r="P3" s="132"/>
-      <c r="Q3" s="140"/>
-      <c r="R3" s="132"/>
-      <c r="S3" s="140"/>
-      <c r="T3" s="159"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="142"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="134"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="134"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="134"/>
+      <c r="S3" s="142"/>
+      <c r="T3" s="154"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="141"/>
-      <c r="L4" s="134"/>
-      <c r="M4" s="134"/>
-      <c r="N4" s="135"/>
-      <c r="O4" s="141"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="141"/>
-      <c r="R4" s="135"/>
-      <c r="S4" s="141"/>
+      <c r="A4" s="135"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="136"/>
+      <c r="M4" s="136"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="137"/>
+      <c r="Q4" s="143"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="143"/>
       <c r="T4" s="170"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="166" t="s">
+      <c r="B5" s="145"/>
+      <c r="C5" s="145"/>
+      <c r="D5" s="145"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="139"/>
+      <c r="G5" s="172" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="153"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="153"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="153"/>
-      <c r="P5" s="153"/>
-      <c r="Q5" s="153"/>
-      <c r="R5" s="153"/>
-      <c r="S5" s="153"/>
-      <c r="T5" s="155"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="145"/>
+      <c r="K5" s="145"/>
+      <c r="L5" s="145"/>
+      <c r="M5" s="145"/>
+      <c r="N5" s="145"/>
+      <c r="O5" s="145"/>
+      <c r="P5" s="145"/>
+      <c r="Q5" s="145"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="145"/>
+      <c r="T5" s="149"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="145" t="s">
+      <c r="A6" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="143" t="s">
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="144"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="73"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="73"/>
+      <c r="T6" s="150"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="145" t="s">
+      <c r="A7" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="143" t="s">
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="155" t="s">
         <v>95</v>
       </c>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="71"/>
-      <c r="T7" s="144"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="73"/>
+      <c r="Q7" s="73"/>
+      <c r="R7" s="73"/>
+      <c r="S7" s="73"/>
+      <c r="T7" s="150"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -18093,37 +18139,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="147" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="168" t="s">
+      <c r="B15" s="74"/>
+      <c r="C15" s="178" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="72"/>
-      <c r="E15" s="146" t="s">
+      <c r="D15" s="74"/>
+      <c r="E15" s="156" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="72"/>
-      <c r="G15" s="146" t="s">
+      <c r="F15" s="74"/>
+      <c r="G15" s="156" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="71"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="146" t="s">
+      <c r="H15" s="73"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="156" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="72"/>
-      <c r="L15" s="146" t="s">
+      <c r="K15" s="74"/>
+      <c r="L15" s="156" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="71"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="146" t="s">
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="156" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="72"/>
+      <c r="P15" s="73"/>
+      <c r="Q15" s="74"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -18135,37 +18181,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A16" s="160">
+      <c r="A16" s="179">
         <v>1</v>
       </c>
-      <c r="B16" s="72"/>
-      <c r="C16" s="161" t="s">
+      <c r="B16" s="74"/>
+      <c r="C16" s="180" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="72"/>
-      <c r="E16" s="161" t="s">
+      <c r="D16" s="74"/>
+      <c r="E16" s="180" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="72"/>
-      <c r="G16" s="167" t="s">
+      <c r="F16" s="74"/>
+      <c r="G16" s="162" t="s">
         <v>96</v>
       </c>
-      <c r="H16" s="71"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="174" t="s">
+      <c r="H16" s="73"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="K16" s="175"/>
-      <c r="L16" s="164" t="s">
+      <c r="K16" s="164"/>
+      <c r="L16" s="166" t="s">
         <v>98</v>
       </c>
-      <c r="M16" s="71"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="164" t="s">
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="166" t="s">
         <v>99</v>
       </c>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="72"/>
+      <c r="P16" s="73"/>
+      <c r="Q16" s="74"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -18177,37 +18223,37 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A17" s="160">
+      <c r="A17" s="179">
         <v>2</v>
       </c>
-      <c r="B17" s="72"/>
-      <c r="C17" s="161" t="s">
+      <c r="B17" s="74"/>
+      <c r="C17" s="180" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="72"/>
-      <c r="E17" s="161" t="s">
+      <c r="D17" s="74"/>
+      <c r="E17" s="180" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="72"/>
-      <c r="G17" s="167" t="s">
+      <c r="F17" s="74"/>
+      <c r="G17" s="162" t="s">
         <v>105</v>
       </c>
-      <c r="H17" s="71"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="167" t="s">
+      <c r="H17" s="73"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="162" t="s">
         <v>106</v>
       </c>
-      <c r="K17" s="72"/>
-      <c r="L17" s="164" t="s">
+      <c r="K17" s="74"/>
+      <c r="L17" s="166" t="s">
         <v>98</v>
       </c>
-      <c r="M17" s="71"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="164" t="s">
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="166" t="s">
         <v>107</v>
       </c>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="72"/>
+      <c r="P17" s="73"/>
+      <c r="Q17" s="74"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -18219,37 +18265,37 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="64.5" customHeight="1">
-      <c r="A18" s="160">
+      <c r="A18" s="179">
         <v>3</v>
       </c>
-      <c r="B18" s="72"/>
-      <c r="C18" s="161" t="s">
+      <c r="B18" s="74"/>
+      <c r="C18" s="180" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="72"/>
-      <c r="E18" s="161" t="s">
+      <c r="D18" s="74"/>
+      <c r="E18" s="180" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="72"/>
-      <c r="G18" s="167" t="s">
+      <c r="F18" s="74"/>
+      <c r="G18" s="162" t="s">
         <v>101</v>
       </c>
-      <c r="H18" s="71"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="167" t="s">
+      <c r="H18" s="73"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="162" t="s">
         <v>103</v>
       </c>
-      <c r="K18" s="72"/>
-      <c r="L18" s="172" t="s">
+      <c r="K18" s="74"/>
+      <c r="L18" s="168" t="s">
         <v>104</v>
       </c>
-      <c r="M18" s="71"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="164" t="s">
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="166" t="s">
         <v>102</v>
       </c>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="72"/>
+      <c r="P18" s="73"/>
+      <c r="Q18" s="74"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -18261,37 +18307,37 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="61.5" customHeight="1">
-      <c r="A19" s="160">
+      <c r="A19" s="179">
         <v>4</v>
       </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="161" t="s">
+      <c r="B19" s="74"/>
+      <c r="C19" s="180" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="72"/>
-      <c r="E19" s="161" t="s">
+      <c r="D19" s="74"/>
+      <c r="E19" s="180" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="72"/>
-      <c r="G19" s="167" t="s">
+      <c r="F19" s="74"/>
+      <c r="G19" s="162" t="s">
         <v>139</v>
       </c>
-      <c r="H19" s="71"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="167" t="s">
+      <c r="H19" s="73"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="162" t="s">
         <v>97</v>
       </c>
-      <c r="K19" s="72"/>
-      <c r="L19" s="164" t="s">
+      <c r="K19" s="74"/>
+      <c r="L19" s="166" t="s">
         <v>98</v>
       </c>
-      <c r="M19" s="71"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="164" t="s">
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="166" t="s">
         <v>140</v>
       </c>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="72"/>
+      <c r="P19" s="73"/>
+      <c r="Q19" s="74"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -18302,27 +18348,41 @@
       <c r="Y19" s="34"/>
       <c r="Z19" s="34"/>
     </row>
-    <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="160"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="161"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="161"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="167"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="167"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="164"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="164"/>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="32"/>
-      <c r="T20" s="33"/>
+    <row r="20" spans="1:26" ht="50.25" customHeight="1">
+      <c r="A20" s="173">
+        <v>7</v>
+      </c>
+      <c r="B20" s="164"/>
+      <c r="C20" s="174" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="164"/>
+      <c r="E20" s="174" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="164"/>
+      <c r="G20" s="163" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="175"/>
+      <c r="I20" s="164"/>
+      <c r="J20" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="K20" s="164"/>
+      <c r="L20" s="176" t="s">
+        <v>144</v>
+      </c>
+      <c r="M20" s="177"/>
+      <c r="N20" s="177"/>
+      <c r="O20" s="166" t="s">
+        <v>145</v>
+      </c>
+      <c r="P20" s="73"/>
+      <c r="Q20" s="74"/>
+      <c r="R20" s="70"/>
+      <c r="S20" s="70"/>
+      <c r="T20" s="71"/>
       <c r="U20" s="34"/>
       <c r="V20" s="34"/>
       <c r="W20" s="34"/>
@@ -18331,23 +18391,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="160"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="161"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="161"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="167"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="167"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="164"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="164"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="72"/>
+      <c r="A21" s="179"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="180"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="180"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="162"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="162"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="166"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="166"/>
+      <c r="P21" s="73"/>
+      <c r="Q21" s="74"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -18359,23 +18419,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="160"/>
-      <c r="B22" s="72"/>
-      <c r="C22" s="161"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="161"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="167"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="167"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="164"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="164"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="72"/>
+      <c r="A22" s="179"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="180"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="180"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="162"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="166"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="166"/>
+      <c r="P22" s="73"/>
+      <c r="Q22" s="74"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -18387,23 +18447,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="160"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="161"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="161"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="167"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="167"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="164"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="164"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="72"/>
+      <c r="A23" s="179"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="180"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="180"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="162"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="74"/>
+      <c r="J23" s="162"/>
+      <c r="K23" s="74"/>
+      <c r="L23" s="166"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="166"/>
+      <c r="P23" s="73"/>
+      <c r="Q23" s="74"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -18415,23 +18475,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="160"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="161"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="161"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="167"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="167"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="164"/>
-      <c r="M24" s="71"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="164"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="72"/>
+      <c r="A24" s="179"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="180"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="180"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="162"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="162"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="166"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="166"/>
+      <c r="P24" s="73"/>
+      <c r="Q24" s="74"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -18443,23 +18503,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="160"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="161"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="161"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="167"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="167"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="164"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="164"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="72"/>
+      <c r="A25" s="179"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="180"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="180"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="162"/>
+      <c r="K25" s="74"/>
+      <c r="L25" s="166"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="166"/>
+      <c r="P25" s="73"/>
+      <c r="Q25" s="74"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -18471,23 +18531,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="160"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="161"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="161"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="167"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="167"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="164"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="72"/>
-      <c r="O26" s="164"/>
-      <c r="P26" s="71"/>
-      <c r="Q26" s="72"/>
+      <c r="A26" s="179"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="180"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="180"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="162"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="162"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="166"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="166"/>
+      <c r="P26" s="73"/>
+      <c r="Q26" s="74"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -18499,23 +18559,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="160"/>
-      <c r="B27" s="72"/>
-      <c r="C27" s="161"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="161"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="167"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="167"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="164"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="72"/>
-      <c r="O27" s="164"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="72"/>
+      <c r="A27" s="179"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="180"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="180"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="162"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="162"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="166"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="166"/>
+      <c r="P27" s="73"/>
+      <c r="Q27" s="74"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -18527,23 +18587,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="160"/>
-      <c r="B28" s="72"/>
-      <c r="C28" s="161"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="161"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="167"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="167"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="164"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="164"/>
-      <c r="P28" s="71"/>
-      <c r="Q28" s="72"/>
+      <c r="A28" s="179"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="180"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="180"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="162"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="162"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="166"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="166"/>
+      <c r="P28" s="73"/>
+      <c r="Q28" s="74"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -18555,23 +18615,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="160"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="161"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="161"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="167"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="167"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="164"/>
-      <c r="M29" s="71"/>
-      <c r="N29" s="72"/>
-      <c r="O29" s="164"/>
-      <c r="P29" s="71"/>
-      <c r="Q29" s="72"/>
+      <c r="A29" s="179"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="180"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="180"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="162"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="162"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="166"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="166"/>
+      <c r="P29" s="73"/>
+      <c r="Q29" s="74"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -18583,23 +18643,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="160"/>
-      <c r="B30" s="72"/>
-      <c r="C30" s="161"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="161"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="167"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="167"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="164"/>
-      <c r="M30" s="71"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="164"/>
-      <c r="P30" s="71"/>
-      <c r="Q30" s="72"/>
+      <c r="A30" s="179"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="180"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="180"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="162"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="162"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="166"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="166"/>
+      <c r="P30" s="73"/>
+      <c r="Q30" s="74"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -18611,23 +18671,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="162"/>
-      <c r="B31" s="149"/>
-      <c r="C31" s="163"/>
-      <c r="D31" s="149"/>
-      <c r="E31" s="163"/>
-      <c r="F31" s="149"/>
-      <c r="G31" s="173"/>
-      <c r="H31" s="148"/>
-      <c r="I31" s="149"/>
-      <c r="J31" s="173"/>
-      <c r="K31" s="149"/>
-      <c r="L31" s="165"/>
-      <c r="M31" s="148"/>
-      <c r="N31" s="149"/>
-      <c r="O31" s="165"/>
-      <c r="P31" s="148"/>
-      <c r="Q31" s="149"/>
+      <c r="A31" s="181"/>
+      <c r="B31" s="161"/>
+      <c r="C31" s="182"/>
+      <c r="D31" s="161"/>
+      <c r="E31" s="182"/>
+      <c r="F31" s="161"/>
+      <c r="G31" s="165"/>
+      <c r="H31" s="158"/>
+      <c r="I31" s="161"/>
+      <c r="J31" s="165"/>
+      <c r="K31" s="161"/>
+      <c r="L31" s="167"/>
+      <c r="M31" s="158"/>
+      <c r="N31" s="161"/>
+      <c r="O31" s="167"/>
+      <c r="P31" s="158"/>
+      <c r="Q31" s="161"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -19625,62 +19685,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -19705,66 +19765,67 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
     <hyperlink ref="L18" r:id="rId1" display="http://localhost:8080/taskUN/task-delete.jsp" xr:uid="{38C81AFB-41F8-4093-85EB-71ACC0BAB2DD}"/>
+    <hyperlink ref="L20" r:id="rId2" xr:uid="{70E42B72-7AD1-4967-864C-156B0F97FF63}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -19786,70 +19847,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="186" t="s">
+      <c r="B1" s="200"/>
+      <c r="C1" s="201" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="187"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="189" t="s">
+      <c r="D1" s="202"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="204" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="190"/>
-      <c r="H1" s="190"/>
-      <c r="I1" s="190"/>
-      <c r="J1" s="190"/>
-      <c r="K1" s="190"/>
-      <c r="L1" s="190"/>
-      <c r="M1" s="191"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="206"/>
       <c r="N1" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="189" t="s">
+      <c r="O1" s="204" t="s">
         <v>94</v>
       </c>
-      <c r="P1" s="191"/>
+      <c r="P1" s="206"/>
       <c r="Q1" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="189" t="s">
+      <c r="R1" s="204" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="191"/>
+      <c r="S1" s="206"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="185"/>
-      <c r="B2" s="185"/>
-      <c r="C2" s="186" t="s">
+      <c r="A2" s="200"/>
+      <c r="B2" s="200"/>
+      <c r="C2" s="201" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="187"/>
-      <c r="E2" s="188"/>
-      <c r="F2" s="189" t="s">
+      <c r="D2" s="202"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="204" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
-      <c r="M2" s="191"/>
+      <c r="G2" s="205"/>
+      <c r="H2" s="205"/>
+      <c r="I2" s="205"/>
+      <c r="J2" s="205"/>
+      <c r="K2" s="205"/>
+      <c r="L2" s="205"/>
+      <c r="M2" s="206"/>
       <c r="N2" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="O2" s="192">
+      <c r="O2" s="207">
         <v>45824</v>
       </c>
-      <c r="P2" s="193"/>
+      <c r="P2" s="208"/>
       <c r="Q2" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="R2" s="194"/>
-      <c r="S2" s="195"/>
+      <c r="R2" s="209"/>
+      <c r="S2" s="210"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="43"/>
@@ -19879,33 +19940,33 @@
       <c r="B4" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="176" t="s">
+      <c r="C4" s="195" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="177"/>
-      <c r="E4" s="177"/>
-      <c r="F4" s="177"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="176" t="s">
+      <c r="D4" s="196"/>
+      <c r="E4" s="196"/>
+      <c r="F4" s="196"/>
+      <c r="G4" s="197"/>
+      <c r="H4" s="195" t="s">
         <v>119</v>
       </c>
-      <c r="I4" s="177"/>
-      <c r="J4" s="177"/>
-      <c r="K4" s="177"/>
-      <c r="L4" s="177"/>
-      <c r="M4" s="178"/>
-      <c r="N4" s="176" t="s">
+      <c r="I4" s="196"/>
+      <c r="J4" s="196"/>
+      <c r="K4" s="196"/>
+      <c r="L4" s="196"/>
+      <c r="M4" s="197"/>
+      <c r="N4" s="195" t="s">
         <v>120</v>
       </c>
-      <c r="O4" s="177"/>
-      <c r="P4" s="178"/>
+      <c r="O4" s="196"/>
+      <c r="P4" s="197"/>
       <c r="Q4" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="R4" s="176" t="s">
+      <c r="R4" s="195" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="178"/>
+      <c r="S4" s="197"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="47">
@@ -19914,29 +19975,29 @@
       <c r="B5" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="179" t="s">
+      <c r="C5" s="191" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="179"/>
-      <c r="E5" s="179"/>
-      <c r="F5" s="179"/>
-      <c r="G5" s="179"/>
-      <c r="H5" s="179" t="s">
+      <c r="D5" s="191"/>
+      <c r="E5" s="191"/>
+      <c r="F5" s="191"/>
+      <c r="G5" s="191"/>
+      <c r="H5" s="191" t="s">
         <v>135</v>
       </c>
-      <c r="I5" s="179"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="179"/>
-      <c r="L5" s="179"/>
-      <c r="M5" s="179"/>
-      <c r="N5" s="180" t="s">
+      <c r="I5" s="191"/>
+      <c r="J5" s="191"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="192" t="s">
         <v>136</v>
       </c>
-      <c r="O5" s="181"/>
-      <c r="P5" s="182"/>
+      <c r="O5" s="193"/>
+      <c r="P5" s="194"/>
       <c r="Q5" s="47"/>
-      <c r="R5" s="183"/>
-      <c r="S5" s="184"/>
+      <c r="R5" s="198"/>
+      <c r="S5" s="199"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="49">
@@ -19945,1186 +20006,998 @@
       <c r="B6" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="179" t="s">
+      <c r="C6" s="191" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="179"/>
-      <c r="E6" s="179"/>
-      <c r="F6" s="179"/>
-      <c r="G6" s="179"/>
-      <c r="H6" s="179" t="s">
+      <c r="D6" s="191"/>
+      <c r="E6" s="191"/>
+      <c r="F6" s="191"/>
+      <c r="G6" s="191"/>
+      <c r="H6" s="191" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="179"/>
-      <c r="J6" s="179"/>
-      <c r="K6" s="179"/>
-      <c r="L6" s="179"/>
-      <c r="M6" s="179"/>
-      <c r="N6" s="180" t="s">
+      <c r="I6" s="191"/>
+      <c r="J6" s="191"/>
+      <c r="K6" s="191"/>
+      <c r="L6" s="191"/>
+      <c r="M6" s="191"/>
+      <c r="N6" s="192" t="s">
         <v>137</v>
       </c>
-      <c r="O6" s="181"/>
-      <c r="P6" s="182"/>
+      <c r="O6" s="193"/>
+      <c r="P6" s="194"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="200"/>
-      <c r="S6" s="200"/>
+      <c r="R6" s="190"/>
+      <c r="S6" s="190"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="49"/>
       <c r="B7" s="49"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="196"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="196"/>
-      <c r="H7" s="196"/>
-      <c r="I7" s="196"/>
-      <c r="J7" s="196"/>
-      <c r="K7" s="196"/>
-      <c r="L7" s="196"/>
-      <c r="M7" s="196"/>
-      <c r="N7" s="197"/>
-      <c r="O7" s="198"/>
-      <c r="P7" s="199"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="183"/>
+      <c r="F7" s="183"/>
+      <c r="G7" s="183"/>
+      <c r="H7" s="183"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183"/>
+      <c r="K7" s="183"/>
+      <c r="L7" s="183"/>
+      <c r="M7" s="183"/>
+      <c r="N7" s="187"/>
+      <c r="O7" s="188"/>
+      <c r="P7" s="189"/>
       <c r="Q7" s="51"/>
-      <c r="R7" s="200"/>
-      <c r="S7" s="200"/>
+      <c r="R7" s="190"/>
+      <c r="S7" s="190"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="49"/>
       <c r="B8" s="49"/>
-      <c r="C8" s="196"/>
-      <c r="D8" s="196"/>
-      <c r="E8" s="196"/>
-      <c r="F8" s="196"/>
-      <c r="G8" s="196"/>
-      <c r="H8" s="196"/>
-      <c r="I8" s="196"/>
-      <c r="J8" s="196"/>
-      <c r="K8" s="196"/>
-      <c r="L8" s="196"/>
-      <c r="M8" s="196"/>
-      <c r="N8" s="197"/>
-      <c r="O8" s="198"/>
-      <c r="P8" s="199"/>
+      <c r="C8" s="183"/>
+      <c r="D8" s="183"/>
+      <c r="E8" s="183"/>
+      <c r="F8" s="183"/>
+      <c r="G8" s="183"/>
+      <c r="H8" s="183"/>
+      <c r="I8" s="183"/>
+      <c r="J8" s="183"/>
+      <c r="K8" s="183"/>
+      <c r="L8" s="183"/>
+      <c r="M8" s="183"/>
+      <c r="N8" s="187"/>
+      <c r="O8" s="188"/>
+      <c r="P8" s="189"/>
       <c r="Q8" s="51"/>
-      <c r="R8" s="200"/>
-      <c r="S8" s="200"/>
+      <c r="R8" s="190"/>
+      <c r="S8" s="190"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="49"/>
       <c r="B9" s="49"/>
-      <c r="C9" s="196"/>
-      <c r="D9" s="196"/>
-      <c r="E9" s="196"/>
-      <c r="F9" s="196"/>
-      <c r="G9" s="196"/>
-      <c r="H9" s="196"/>
-      <c r="I9" s="196"/>
-      <c r="J9" s="196"/>
-      <c r="K9" s="196"/>
-      <c r="L9" s="196"/>
-      <c r="M9" s="196"/>
-      <c r="N9" s="197"/>
-      <c r="O9" s="198"/>
-      <c r="P9" s="199"/>
+      <c r="C9" s="183"/>
+      <c r="D9" s="183"/>
+      <c r="E9" s="183"/>
+      <c r="F9" s="183"/>
+      <c r="G9" s="183"/>
+      <c r="H9" s="183"/>
+      <c r="I9" s="183"/>
+      <c r="J9" s="183"/>
+      <c r="K9" s="183"/>
+      <c r="L9" s="183"/>
+      <c r="M9" s="183"/>
+      <c r="N9" s="187"/>
+      <c r="O9" s="188"/>
+      <c r="P9" s="189"/>
       <c r="Q9" s="49"/>
-      <c r="R9" s="200"/>
-      <c r="S9" s="200"/>
+      <c r="R9" s="190"/>
+      <c r="S9" s="190"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="49"/>
       <c r="B10" s="49"/>
-      <c r="C10" s="196"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="196"/>
-      <c r="F10" s="196"/>
-      <c r="G10" s="196"/>
-      <c r="H10" s="201"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
-      <c r="L10" s="202"/>
-      <c r="M10" s="203"/>
-      <c r="N10" s="197"/>
-      <c r="O10" s="198"/>
-      <c r="P10" s="199"/>
+      <c r="C10" s="183"/>
+      <c r="D10" s="183"/>
+      <c r="E10" s="183"/>
+      <c r="F10" s="183"/>
+      <c r="G10" s="183"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="185"/>
+      <c r="J10" s="185"/>
+      <c r="K10" s="185"/>
+      <c r="L10" s="185"/>
+      <c r="M10" s="186"/>
+      <c r="N10" s="187"/>
+      <c r="O10" s="188"/>
+      <c r="P10" s="189"/>
       <c r="Q10" s="51"/>
-      <c r="R10" s="200"/>
-      <c r="S10" s="200"/>
+      <c r="R10" s="190"/>
+      <c r="S10" s="190"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="49"/>
       <c r="B11" s="49"/>
-      <c r="C11" s="196"/>
-      <c r="D11" s="196"/>
-      <c r="E11" s="196"/>
-      <c r="F11" s="196"/>
-      <c r="G11" s="196"/>
-      <c r="H11" s="201"/>
-      <c r="I11" s="202"/>
-      <c r="J11" s="202"/>
-      <c r="K11" s="202"/>
-      <c r="L11" s="202"/>
-      <c r="M11" s="203"/>
-      <c r="N11" s="197"/>
-      <c r="O11" s="198"/>
-      <c r="P11" s="199"/>
+      <c r="C11" s="183"/>
+      <c r="D11" s="183"/>
+      <c r="E11" s="183"/>
+      <c r="F11" s="183"/>
+      <c r="G11" s="183"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="185"/>
+      <c r="J11" s="185"/>
+      <c r="K11" s="185"/>
+      <c r="L11" s="185"/>
+      <c r="M11" s="186"/>
+      <c r="N11" s="187"/>
+      <c r="O11" s="188"/>
+      <c r="P11" s="189"/>
       <c r="Q11" s="49"/>
-      <c r="R11" s="200"/>
-      <c r="S11" s="200"/>
+      <c r="R11" s="190"/>
+      <c r="S11" s="190"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="49"/>
       <c r="B12" s="49"/>
-      <c r="C12" s="196"/>
-      <c r="D12" s="196"/>
-      <c r="E12" s="196"/>
-      <c r="F12" s="196"/>
-      <c r="G12" s="196"/>
-      <c r="H12" s="201"/>
-      <c r="I12" s="202"/>
-      <c r="J12" s="202"/>
-      <c r="K12" s="202"/>
-      <c r="L12" s="202"/>
-      <c r="M12" s="203"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="198"/>
-      <c r="P12" s="199"/>
+      <c r="C12" s="183"/>
+      <c r="D12" s="183"/>
+      <c r="E12" s="183"/>
+      <c r="F12" s="183"/>
+      <c r="G12" s="183"/>
+      <c r="H12" s="184"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="185"/>
+      <c r="L12" s="185"/>
+      <c r="M12" s="186"/>
+      <c r="N12" s="187"/>
+      <c r="O12" s="188"/>
+      <c r="P12" s="189"/>
       <c r="Q12" s="49"/>
-      <c r="R12" s="200"/>
-      <c r="S12" s="200"/>
+      <c r="R12" s="190"/>
+      <c r="S12" s="190"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="49"/>
       <c r="B13" s="49"/>
-      <c r="C13" s="196"/>
-      <c r="D13" s="196"/>
-      <c r="E13" s="196"/>
-      <c r="F13" s="196"/>
-      <c r="G13" s="196"/>
-      <c r="H13" s="201"/>
-      <c r="I13" s="202"/>
-      <c r="J13" s="202"/>
-      <c r="K13" s="202"/>
-      <c r="L13" s="202"/>
-      <c r="M13" s="203"/>
-      <c r="N13" s="197"/>
-      <c r="O13" s="198"/>
-      <c r="P13" s="199"/>
+      <c r="C13" s="183"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="183"/>
+      <c r="F13" s="183"/>
+      <c r="G13" s="183"/>
+      <c r="H13" s="184"/>
+      <c r="I13" s="185"/>
+      <c r="J13" s="185"/>
+      <c r="K13" s="185"/>
+      <c r="L13" s="185"/>
+      <c r="M13" s="186"/>
+      <c r="N13" s="187"/>
+      <c r="O13" s="188"/>
+      <c r="P13" s="189"/>
       <c r="Q13" s="49"/>
-      <c r="R13" s="200"/>
-      <c r="S13" s="200"/>
+      <c r="R13" s="190"/>
+      <c r="S13" s="190"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="49"/>
       <c r="B14" s="49"/>
-      <c r="C14" s="196"/>
-      <c r="D14" s="196"/>
-      <c r="E14" s="196"/>
-      <c r="F14" s="196"/>
-      <c r="G14" s="196"/>
-      <c r="H14" s="201"/>
-      <c r="I14" s="202"/>
-      <c r="J14" s="202"/>
-      <c r="K14" s="202"/>
-      <c r="L14" s="202"/>
-      <c r="M14" s="203"/>
-      <c r="N14" s="197"/>
-      <c r="O14" s="198"/>
-      <c r="P14" s="199"/>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="183"/>
+      <c r="F14" s="183"/>
+      <c r="G14" s="183"/>
+      <c r="H14" s="184"/>
+      <c r="I14" s="185"/>
+      <c r="J14" s="185"/>
+      <c r="K14" s="185"/>
+      <c r="L14" s="185"/>
+      <c r="M14" s="186"/>
+      <c r="N14" s="187"/>
+      <c r="O14" s="188"/>
+      <c r="P14" s="189"/>
       <c r="Q14" s="49"/>
-      <c r="R14" s="200"/>
-      <c r="S14" s="200"/>
+      <c r="R14" s="190"/>
+      <c r="S14" s="190"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="49"/>
       <c r="B15" s="49"/>
-      <c r="C15" s="196"/>
-      <c r="D15" s="196"/>
-      <c r="E15" s="196"/>
-      <c r="F15" s="196"/>
-      <c r="G15" s="196"/>
-      <c r="H15" s="201"/>
-      <c r="I15" s="202"/>
-      <c r="J15" s="202"/>
-      <c r="K15" s="202"/>
-      <c r="L15" s="202"/>
-      <c r="M15" s="203"/>
-      <c r="N15" s="197"/>
-      <c r="O15" s="198"/>
-      <c r="P15" s="199"/>
+      <c r="C15" s="183"/>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="183"/>
+      <c r="H15" s="184"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="185"/>
+      <c r="M15" s="186"/>
+      <c r="N15" s="187"/>
+      <c r="O15" s="188"/>
+      <c r="P15" s="189"/>
       <c r="Q15" s="49"/>
-      <c r="R15" s="200"/>
-      <c r="S15" s="200"/>
+      <c r="R15" s="190"/>
+      <c r="S15" s="190"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="49"/>
       <c r="B16" s="49"/>
-      <c r="C16" s="196"/>
-      <c r="D16" s="196"/>
-      <c r="E16" s="196"/>
-      <c r="F16" s="196"/>
-      <c r="G16" s="196"/>
-      <c r="H16" s="201"/>
-      <c r="I16" s="202"/>
-      <c r="J16" s="202"/>
-      <c r="K16" s="202"/>
-      <c r="L16" s="202"/>
-      <c r="M16" s="203"/>
-      <c r="N16" s="197"/>
-      <c r="O16" s="198"/>
-      <c r="P16" s="199"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="F16" s="183"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="184"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="185"/>
+      <c r="K16" s="185"/>
+      <c r="L16" s="185"/>
+      <c r="M16" s="186"/>
+      <c r="N16" s="187"/>
+      <c r="O16" s="188"/>
+      <c r="P16" s="189"/>
       <c r="Q16" s="49"/>
-      <c r="R16" s="200"/>
-      <c r="S16" s="200"/>
+      <c r="R16" s="190"/>
+      <c r="S16" s="190"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="49"/>
       <c r="B17" s="49"/>
-      <c r="C17" s="196"/>
-      <c r="D17" s="196"/>
-      <c r="E17" s="196"/>
-      <c r="F17" s="196"/>
-      <c r="G17" s="196"/>
-      <c r="H17" s="201"/>
-      <c r="I17" s="202"/>
-      <c r="J17" s="202"/>
-      <c r="K17" s="202"/>
-      <c r="L17" s="202"/>
-      <c r="M17" s="203"/>
-      <c r="N17" s="197"/>
-      <c r="O17" s="198"/>
-      <c r="P17" s="199"/>
+      <c r="C17" s="183"/>
+      <c r="D17" s="183"/>
+      <c r="E17" s="183"/>
+      <c r="F17" s="183"/>
+      <c r="G17" s="183"/>
+      <c r="H17" s="184"/>
+      <c r="I17" s="185"/>
+      <c r="J17" s="185"/>
+      <c r="K17" s="185"/>
+      <c r="L17" s="185"/>
+      <c r="M17" s="186"/>
+      <c r="N17" s="187"/>
+      <c r="O17" s="188"/>
+      <c r="P17" s="189"/>
       <c r="Q17" s="49"/>
-      <c r="R17" s="200"/>
-      <c r="S17" s="200"/>
+      <c r="R17" s="190"/>
+      <c r="S17" s="190"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="49"/>
       <c r="B18" s="49"/>
-      <c r="C18" s="196"/>
-      <c r="D18" s="196"/>
-      <c r="E18" s="196"/>
-      <c r="F18" s="196"/>
-      <c r="G18" s="196"/>
-      <c r="H18" s="201"/>
-      <c r="I18" s="202"/>
-      <c r="J18" s="202"/>
-      <c r="K18" s="202"/>
-      <c r="L18" s="202"/>
-      <c r="M18" s="203"/>
-      <c r="N18" s="197"/>
-      <c r="O18" s="198"/>
-      <c r="P18" s="199"/>
+      <c r="C18" s="183"/>
+      <c r="D18" s="183"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="183"/>
+      <c r="G18" s="183"/>
+      <c r="H18" s="184"/>
+      <c r="I18" s="185"/>
+      <c r="J18" s="185"/>
+      <c r="K18" s="185"/>
+      <c r="L18" s="185"/>
+      <c r="M18" s="186"/>
+      <c r="N18" s="187"/>
+      <c r="O18" s="188"/>
+      <c r="P18" s="189"/>
       <c r="Q18" s="49"/>
-      <c r="R18" s="200"/>
-      <c r="S18" s="200"/>
+      <c r="R18" s="190"/>
+      <c r="S18" s="190"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="49"/>
       <c r="B19" s="49"/>
-      <c r="C19" s="196"/>
-      <c r="D19" s="196"/>
-      <c r="E19" s="196"/>
-      <c r="F19" s="196"/>
-      <c r="G19" s="196"/>
-      <c r="H19" s="201"/>
-      <c r="I19" s="202"/>
-      <c r="J19" s="202"/>
-      <c r="K19" s="202"/>
-      <c r="L19" s="202"/>
-      <c r="M19" s="203"/>
-      <c r="N19" s="197"/>
-      <c r="O19" s="198"/>
-      <c r="P19" s="199"/>
+      <c r="C19" s="183"/>
+      <c r="D19" s="183"/>
+      <c r="E19" s="183"/>
+      <c r="F19" s="183"/>
+      <c r="G19" s="183"/>
+      <c r="H19" s="184"/>
+      <c r="I19" s="185"/>
+      <c r="J19" s="185"/>
+      <c r="K19" s="185"/>
+      <c r="L19" s="185"/>
+      <c r="M19" s="186"/>
+      <c r="N19" s="187"/>
+      <c r="O19" s="188"/>
+      <c r="P19" s="189"/>
       <c r="Q19" s="49"/>
-      <c r="R19" s="200"/>
-      <c r="S19" s="200"/>
+      <c r="R19" s="190"/>
+      <c r="S19" s="190"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="49"/>
       <c r="B20" s="49"/>
-      <c r="C20" s="196"/>
-      <c r="D20" s="196"/>
-      <c r="E20" s="196"/>
-      <c r="F20" s="196"/>
-      <c r="G20" s="196"/>
-      <c r="H20" s="201"/>
-      <c r="I20" s="202"/>
-      <c r="J20" s="202"/>
-      <c r="K20" s="202"/>
-      <c r="L20" s="202"/>
-      <c r="M20" s="203"/>
-      <c r="N20" s="197"/>
-      <c r="O20" s="198"/>
-      <c r="P20" s="199"/>
+      <c r="C20" s="183"/>
+      <c r="D20" s="183"/>
+      <c r="E20" s="183"/>
+      <c r="F20" s="183"/>
+      <c r="G20" s="183"/>
+      <c r="H20" s="184"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="185"/>
+      <c r="K20" s="185"/>
+      <c r="L20" s="185"/>
+      <c r="M20" s="186"/>
+      <c r="N20" s="187"/>
+      <c r="O20" s="188"/>
+      <c r="P20" s="189"/>
       <c r="Q20" s="49"/>
-      <c r="R20" s="200"/>
-      <c r="S20" s="200"/>
+      <c r="R20" s="190"/>
+      <c r="S20" s="190"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="49"/>
       <c r="B21" s="49"/>
-      <c r="C21" s="196"/>
-      <c r="D21" s="196"/>
-      <c r="E21" s="196"/>
-      <c r="F21" s="196"/>
-      <c r="G21" s="196"/>
-      <c r="H21" s="201"/>
-      <c r="I21" s="202"/>
-      <c r="J21" s="202"/>
-      <c r="K21" s="202"/>
-      <c r="L21" s="202"/>
-      <c r="M21" s="203"/>
-      <c r="N21" s="197"/>
-      <c r="O21" s="198"/>
-      <c r="P21" s="199"/>
+      <c r="C21" s="183"/>
+      <c r="D21" s="183"/>
+      <c r="E21" s="183"/>
+      <c r="F21" s="183"/>
+      <c r="G21" s="183"/>
+      <c r="H21" s="184"/>
+      <c r="I21" s="185"/>
+      <c r="J21" s="185"/>
+      <c r="K21" s="185"/>
+      <c r="L21" s="185"/>
+      <c r="M21" s="186"/>
+      <c r="N21" s="187"/>
+      <c r="O21" s="188"/>
+      <c r="P21" s="189"/>
       <c r="Q21" s="49"/>
-      <c r="R21" s="200"/>
-      <c r="S21" s="200"/>
+      <c r="R21" s="190"/>
+      <c r="S21" s="190"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="49"/>
       <c r="B22" s="49"/>
-      <c r="C22" s="196"/>
-      <c r="D22" s="196"/>
-      <c r="E22" s="196"/>
-      <c r="F22" s="196"/>
-      <c r="G22" s="196"/>
-      <c r="H22" s="201"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="202"/>
-      <c r="K22" s="202"/>
-      <c r="L22" s="202"/>
-      <c r="M22" s="203"/>
-      <c r="N22" s="197"/>
-      <c r="O22" s="198"/>
-      <c r="P22" s="199"/>
+      <c r="C22" s="183"/>
+      <c r="D22" s="183"/>
+      <c r="E22" s="183"/>
+      <c r="F22" s="183"/>
+      <c r="G22" s="183"/>
+      <c r="H22" s="184"/>
+      <c r="I22" s="185"/>
+      <c r="J22" s="185"/>
+      <c r="K22" s="185"/>
+      <c r="L22" s="185"/>
+      <c r="M22" s="186"/>
+      <c r="N22" s="187"/>
+      <c r="O22" s="188"/>
+      <c r="P22" s="189"/>
       <c r="Q22" s="49"/>
-      <c r="R22" s="200"/>
-      <c r="S22" s="200"/>
+      <c r="R22" s="190"/>
+      <c r="S22" s="190"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="49"/>
       <c r="B23" s="49"/>
-      <c r="C23" s="196"/>
-      <c r="D23" s="196"/>
-      <c r="E23" s="196"/>
-      <c r="F23" s="196"/>
-      <c r="G23" s="196"/>
-      <c r="H23" s="201"/>
-      <c r="I23" s="202"/>
-      <c r="J23" s="202"/>
-      <c r="K23" s="202"/>
-      <c r="L23" s="202"/>
-      <c r="M23" s="203"/>
-      <c r="N23" s="197"/>
-      <c r="O23" s="198"/>
-      <c r="P23" s="199"/>
+      <c r="C23" s="183"/>
+      <c r="D23" s="183"/>
+      <c r="E23" s="183"/>
+      <c r="F23" s="183"/>
+      <c r="G23" s="183"/>
+      <c r="H23" s="184"/>
+      <c r="I23" s="185"/>
+      <c r="J23" s="185"/>
+      <c r="K23" s="185"/>
+      <c r="L23" s="185"/>
+      <c r="M23" s="186"/>
+      <c r="N23" s="187"/>
+      <c r="O23" s="188"/>
+      <c r="P23" s="189"/>
       <c r="Q23" s="49"/>
-      <c r="R23" s="200"/>
-      <c r="S23" s="200"/>
+      <c r="R23" s="190"/>
+      <c r="S23" s="190"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="49"/>
       <c r="B24" s="49"/>
-      <c r="C24" s="196"/>
-      <c r="D24" s="196"/>
-      <c r="E24" s="196"/>
-      <c r="F24" s="196"/>
-      <c r="G24" s="196"/>
-      <c r="H24" s="201"/>
-      <c r="I24" s="202"/>
-      <c r="J24" s="202"/>
-      <c r="K24" s="202"/>
-      <c r="L24" s="202"/>
-      <c r="M24" s="203"/>
-      <c r="N24" s="197"/>
-      <c r="O24" s="198"/>
-      <c r="P24" s="199"/>
+      <c r="C24" s="183"/>
+      <c r="D24" s="183"/>
+      <c r="E24" s="183"/>
+      <c r="F24" s="183"/>
+      <c r="G24" s="183"/>
+      <c r="H24" s="184"/>
+      <c r="I24" s="185"/>
+      <c r="J24" s="185"/>
+      <c r="K24" s="185"/>
+      <c r="L24" s="185"/>
+      <c r="M24" s="186"/>
+      <c r="N24" s="187"/>
+      <c r="O24" s="188"/>
+      <c r="P24" s="189"/>
       <c r="Q24" s="49"/>
-      <c r="R24" s="200"/>
-      <c r="S24" s="200"/>
+      <c r="R24" s="190"/>
+      <c r="S24" s="190"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="49"/>
       <c r="B25" s="49"/>
-      <c r="C25" s="196"/>
-      <c r="D25" s="196"/>
-      <c r="E25" s="196"/>
-      <c r="F25" s="196"/>
-      <c r="G25" s="196"/>
-      <c r="H25" s="201"/>
-      <c r="I25" s="202"/>
-      <c r="J25" s="202"/>
-      <c r="K25" s="202"/>
-      <c r="L25" s="202"/>
-      <c r="M25" s="203"/>
-      <c r="N25" s="197"/>
-      <c r="O25" s="198"/>
-      <c r="P25" s="199"/>
+      <c r="C25" s="183"/>
+      <c r="D25" s="183"/>
+      <c r="E25" s="183"/>
+      <c r="F25" s="183"/>
+      <c r="G25" s="183"/>
+      <c r="H25" s="184"/>
+      <c r="I25" s="185"/>
+      <c r="J25" s="185"/>
+      <c r="K25" s="185"/>
+      <c r="L25" s="185"/>
+      <c r="M25" s="186"/>
+      <c r="N25" s="187"/>
+      <c r="O25" s="188"/>
+      <c r="P25" s="189"/>
       <c r="Q25" s="49"/>
-      <c r="R25" s="200"/>
-      <c r="S25" s="200"/>
+      <c r="R25" s="190"/>
+      <c r="S25" s="190"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="49"/>
       <c r="B26" s="49"/>
-      <c r="C26" s="196"/>
-      <c r="D26" s="196"/>
-      <c r="E26" s="196"/>
-      <c r="F26" s="196"/>
-      <c r="G26" s="196"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="202"/>
-      <c r="J26" s="202"/>
-      <c r="K26" s="202"/>
-      <c r="L26" s="202"/>
-      <c r="M26" s="203"/>
-      <c r="N26" s="197"/>
-      <c r="O26" s="198"/>
-      <c r="P26" s="199"/>
+      <c r="C26" s="183"/>
+      <c r="D26" s="183"/>
+      <c r="E26" s="183"/>
+      <c r="F26" s="183"/>
+      <c r="G26" s="183"/>
+      <c r="H26" s="184"/>
+      <c r="I26" s="185"/>
+      <c r="J26" s="185"/>
+      <c r="K26" s="185"/>
+      <c r="L26" s="185"/>
+      <c r="M26" s="186"/>
+      <c r="N26" s="187"/>
+      <c r="O26" s="188"/>
+      <c r="P26" s="189"/>
       <c r="Q26" s="49"/>
-      <c r="R26" s="200"/>
-      <c r="S26" s="200"/>
+      <c r="R26" s="190"/>
+      <c r="S26" s="190"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="49"/>
       <c r="B27" s="49"/>
-      <c r="C27" s="196"/>
-      <c r="D27" s="196"/>
-      <c r="E27" s="196"/>
-      <c r="F27" s="196"/>
-      <c r="G27" s="196"/>
-      <c r="H27" s="201"/>
-      <c r="I27" s="202"/>
-      <c r="J27" s="202"/>
-      <c r="K27" s="202"/>
-      <c r="L27" s="202"/>
-      <c r="M27" s="203"/>
-      <c r="N27" s="197"/>
-      <c r="O27" s="198"/>
-      <c r="P27" s="199"/>
+      <c r="C27" s="183"/>
+      <c r="D27" s="183"/>
+      <c r="E27" s="183"/>
+      <c r="F27" s="183"/>
+      <c r="G27" s="183"/>
+      <c r="H27" s="184"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="185"/>
+      <c r="K27" s="185"/>
+      <c r="L27" s="185"/>
+      <c r="M27" s="186"/>
+      <c r="N27" s="187"/>
+      <c r="O27" s="188"/>
+      <c r="P27" s="189"/>
       <c r="Q27" s="49"/>
-      <c r="R27" s="200"/>
-      <c r="S27" s="200"/>
+      <c r="R27" s="190"/>
+      <c r="S27" s="190"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="49"/>
       <c r="B28" s="49"/>
-      <c r="C28" s="196"/>
-      <c r="D28" s="196"/>
-      <c r="E28" s="196"/>
-      <c r="F28" s="196"/>
-      <c r="G28" s="196"/>
-      <c r="H28" s="201"/>
-      <c r="I28" s="202"/>
-      <c r="J28" s="202"/>
-      <c r="K28" s="202"/>
-      <c r="L28" s="202"/>
-      <c r="M28" s="203"/>
-      <c r="N28" s="197"/>
-      <c r="O28" s="198"/>
-      <c r="P28" s="199"/>
+      <c r="C28" s="183"/>
+      <c r="D28" s="183"/>
+      <c r="E28" s="183"/>
+      <c r="F28" s="183"/>
+      <c r="G28" s="183"/>
+      <c r="H28" s="184"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="185"/>
+      <c r="K28" s="185"/>
+      <c r="L28" s="185"/>
+      <c r="M28" s="186"/>
+      <c r="N28" s="187"/>
+      <c r="O28" s="188"/>
+      <c r="P28" s="189"/>
       <c r="Q28" s="49"/>
-      <c r="R28" s="200"/>
-      <c r="S28" s="200"/>
+      <c r="R28" s="190"/>
+      <c r="S28" s="190"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="49"/>
       <c r="B29" s="49"/>
-      <c r="C29" s="196"/>
-      <c r="D29" s="196"/>
-      <c r="E29" s="196"/>
-      <c r="F29" s="196"/>
-      <c r="G29" s="196"/>
-      <c r="H29" s="201"/>
-      <c r="I29" s="202"/>
-      <c r="J29" s="202"/>
-      <c r="K29" s="202"/>
-      <c r="L29" s="202"/>
-      <c r="M29" s="203"/>
-      <c r="N29" s="197"/>
-      <c r="O29" s="198"/>
-      <c r="P29" s="199"/>
+      <c r="C29" s="183"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="183"/>
+      <c r="F29" s="183"/>
+      <c r="G29" s="183"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="185"/>
+      <c r="J29" s="185"/>
+      <c r="K29" s="185"/>
+      <c r="L29" s="185"/>
+      <c r="M29" s="186"/>
+      <c r="N29" s="187"/>
+      <c r="O29" s="188"/>
+      <c r="P29" s="189"/>
       <c r="Q29" s="49"/>
-      <c r="R29" s="200"/>
-      <c r="S29" s="200"/>
+      <c r="R29" s="190"/>
+      <c r="S29" s="190"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="49"/>
       <c r="B30" s="49"/>
-      <c r="C30" s="196"/>
-      <c r="D30" s="196"/>
-      <c r="E30" s="196"/>
-      <c r="F30" s="196"/>
-      <c r="G30" s="196"/>
-      <c r="H30" s="201"/>
-      <c r="I30" s="202"/>
-      <c r="J30" s="202"/>
-      <c r="K30" s="202"/>
-      <c r="L30" s="202"/>
-      <c r="M30" s="203"/>
-      <c r="N30" s="197"/>
-      <c r="O30" s="198"/>
-      <c r="P30" s="199"/>
+      <c r="C30" s="183"/>
+      <c r="D30" s="183"/>
+      <c r="E30" s="183"/>
+      <c r="F30" s="183"/>
+      <c r="G30" s="183"/>
+      <c r="H30" s="184"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="185"/>
+      <c r="K30" s="185"/>
+      <c r="L30" s="185"/>
+      <c r="M30" s="186"/>
+      <c r="N30" s="187"/>
+      <c r="O30" s="188"/>
+      <c r="P30" s="189"/>
       <c r="Q30" s="49"/>
-      <c r="R30" s="200"/>
-      <c r="S30" s="200"/>
+      <c r="R30" s="190"/>
+      <c r="S30" s="190"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="49"/>
       <c r="B31" s="49"/>
-      <c r="C31" s="196"/>
-      <c r="D31" s="196"/>
-      <c r="E31" s="196"/>
-      <c r="F31" s="196"/>
-      <c r="G31" s="196"/>
-      <c r="H31" s="201"/>
-      <c r="I31" s="202"/>
-      <c r="J31" s="202"/>
-      <c r="K31" s="202"/>
-      <c r="L31" s="202"/>
-      <c r="M31" s="203"/>
-      <c r="N31" s="197"/>
-      <c r="O31" s="198"/>
-      <c r="P31" s="199"/>
+      <c r="C31" s="183"/>
+      <c r="D31" s="183"/>
+      <c r="E31" s="183"/>
+      <c r="F31" s="183"/>
+      <c r="G31" s="183"/>
+      <c r="H31" s="184"/>
+      <c r="I31" s="185"/>
+      <c r="J31" s="185"/>
+      <c r="K31" s="185"/>
+      <c r="L31" s="185"/>
+      <c r="M31" s="186"/>
+      <c r="N31" s="187"/>
+      <c r="O31" s="188"/>
+      <c r="P31" s="189"/>
       <c r="Q31" s="49"/>
-      <c r="R31" s="200"/>
-      <c r="S31" s="200"/>
+      <c r="R31" s="190"/>
+      <c r="S31" s="190"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="49"/>
       <c r="B32" s="49"/>
-      <c r="C32" s="196"/>
-      <c r="D32" s="196"/>
-      <c r="E32" s="196"/>
-      <c r="F32" s="196"/>
-      <c r="G32" s="196"/>
-      <c r="H32" s="201"/>
-      <c r="I32" s="202"/>
-      <c r="J32" s="202"/>
-      <c r="K32" s="202"/>
-      <c r="L32" s="202"/>
-      <c r="M32" s="203"/>
-      <c r="N32" s="197"/>
-      <c r="O32" s="198"/>
-      <c r="P32" s="199"/>
+      <c r="C32" s="183"/>
+      <c r="D32" s="183"/>
+      <c r="E32" s="183"/>
+      <c r="F32" s="183"/>
+      <c r="G32" s="183"/>
+      <c r="H32" s="184"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="185"/>
+      <c r="K32" s="185"/>
+      <c r="L32" s="185"/>
+      <c r="M32" s="186"/>
+      <c r="N32" s="187"/>
+      <c r="O32" s="188"/>
+      <c r="P32" s="189"/>
       <c r="Q32" s="49"/>
-      <c r="R32" s="200"/>
-      <c r="S32" s="200"/>
+      <c r="R32" s="190"/>
+      <c r="S32" s="190"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="49"/>
       <c r="B33" s="49"/>
-      <c r="C33" s="196"/>
-      <c r="D33" s="196"/>
-      <c r="E33" s="196"/>
-      <c r="F33" s="196"/>
-      <c r="G33" s="196"/>
-      <c r="H33" s="201"/>
-      <c r="I33" s="202"/>
-      <c r="J33" s="202"/>
-      <c r="K33" s="202"/>
-      <c r="L33" s="202"/>
-      <c r="M33" s="203"/>
-      <c r="N33" s="197"/>
-      <c r="O33" s="198"/>
-      <c r="P33" s="199"/>
+      <c r="C33" s="183"/>
+      <c r="D33" s="183"/>
+      <c r="E33" s="183"/>
+      <c r="F33" s="183"/>
+      <c r="G33" s="183"/>
+      <c r="H33" s="184"/>
+      <c r="I33" s="185"/>
+      <c r="J33" s="185"/>
+      <c r="K33" s="185"/>
+      <c r="L33" s="185"/>
+      <c r="M33" s="186"/>
+      <c r="N33" s="187"/>
+      <c r="O33" s="188"/>
+      <c r="P33" s="189"/>
       <c r="Q33" s="49"/>
-      <c r="R33" s="200"/>
-      <c r="S33" s="200"/>
+      <c r="R33" s="190"/>
+      <c r="S33" s="190"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="49"/>
       <c r="B34" s="49"/>
-      <c r="C34" s="196"/>
-      <c r="D34" s="196"/>
-      <c r="E34" s="196"/>
-      <c r="F34" s="196"/>
-      <c r="G34" s="196"/>
-      <c r="H34" s="201"/>
-      <c r="I34" s="202"/>
-      <c r="J34" s="202"/>
-      <c r="K34" s="202"/>
-      <c r="L34" s="202"/>
-      <c r="M34" s="203"/>
-      <c r="N34" s="197"/>
-      <c r="O34" s="198"/>
-      <c r="P34" s="199"/>
+      <c r="C34" s="183"/>
+      <c r="D34" s="183"/>
+      <c r="E34" s="183"/>
+      <c r="F34" s="183"/>
+      <c r="G34" s="183"/>
+      <c r="H34" s="184"/>
+      <c r="I34" s="185"/>
+      <c r="J34" s="185"/>
+      <c r="K34" s="185"/>
+      <c r="L34" s="185"/>
+      <c r="M34" s="186"/>
+      <c r="N34" s="187"/>
+      <c r="O34" s="188"/>
+      <c r="P34" s="189"/>
       <c r="Q34" s="49"/>
-      <c r="R34" s="200"/>
-      <c r="S34" s="200"/>
+      <c r="R34" s="190"/>
+      <c r="S34" s="190"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
-      <c r="C35" s="196"/>
-      <c r="D35" s="196"/>
-      <c r="E35" s="196"/>
-      <c r="F35" s="196"/>
-      <c r="G35" s="196"/>
-      <c r="H35" s="201"/>
-      <c r="I35" s="202"/>
-      <c r="J35" s="202"/>
-      <c r="K35" s="202"/>
-      <c r="L35" s="202"/>
-      <c r="M35" s="203"/>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="199"/>
+      <c r="C35" s="183"/>
+      <c r="D35" s="183"/>
+      <c r="E35" s="183"/>
+      <c r="F35" s="183"/>
+      <c r="G35" s="183"/>
+      <c r="H35" s="184"/>
+      <c r="I35" s="185"/>
+      <c r="J35" s="185"/>
+      <c r="K35" s="185"/>
+      <c r="L35" s="185"/>
+      <c r="M35" s="186"/>
+      <c r="N35" s="187"/>
+      <c r="O35" s="188"/>
+      <c r="P35" s="189"/>
       <c r="Q35" s="49"/>
-      <c r="R35" s="200"/>
-      <c r="S35" s="200"/>
+      <c r="R35" s="190"/>
+      <c r="S35" s="190"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="49"/>
       <c r="B36" s="49"/>
-      <c r="C36" s="196"/>
-      <c r="D36" s="196"/>
-      <c r="E36" s="196"/>
-      <c r="F36" s="196"/>
-      <c r="G36" s="196"/>
-      <c r="H36" s="201"/>
-      <c r="I36" s="202"/>
-      <c r="J36" s="202"/>
-      <c r="K36" s="202"/>
-      <c r="L36" s="202"/>
-      <c r="M36" s="203"/>
-      <c r="N36" s="197"/>
-      <c r="O36" s="198"/>
-      <c r="P36" s="199"/>
+      <c r="C36" s="183"/>
+      <c r="D36" s="183"/>
+      <c r="E36" s="183"/>
+      <c r="F36" s="183"/>
+      <c r="G36" s="183"/>
+      <c r="H36" s="184"/>
+      <c r="I36" s="185"/>
+      <c r="J36" s="185"/>
+      <c r="K36" s="185"/>
+      <c r="L36" s="185"/>
+      <c r="M36" s="186"/>
+      <c r="N36" s="187"/>
+      <c r="O36" s="188"/>
+      <c r="P36" s="189"/>
       <c r="Q36" s="49"/>
-      <c r="R36" s="200"/>
-      <c r="S36" s="200"/>
+      <c r="R36" s="190"/>
+      <c r="S36" s="190"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="49"/>
       <c r="B37" s="49"/>
-      <c r="C37" s="196"/>
-      <c r="D37" s="196"/>
-      <c r="E37" s="196"/>
-      <c r="F37" s="196"/>
-      <c r="G37" s="196"/>
-      <c r="H37" s="201"/>
-      <c r="I37" s="202"/>
-      <c r="J37" s="202"/>
-      <c r="K37" s="202"/>
-      <c r="L37" s="202"/>
-      <c r="M37" s="203"/>
-      <c r="N37" s="197"/>
-      <c r="O37" s="198"/>
-      <c r="P37" s="199"/>
+      <c r="C37" s="183"/>
+      <c r="D37" s="183"/>
+      <c r="E37" s="183"/>
+      <c r="F37" s="183"/>
+      <c r="G37" s="183"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="185"/>
+      <c r="J37" s="185"/>
+      <c r="K37" s="185"/>
+      <c r="L37" s="185"/>
+      <c r="M37" s="186"/>
+      <c r="N37" s="187"/>
+      <c r="O37" s="188"/>
+      <c r="P37" s="189"/>
       <c r="Q37" s="49"/>
-      <c r="R37" s="200"/>
-      <c r="S37" s="200"/>
+      <c r="R37" s="190"/>
+      <c r="S37" s="190"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="49"/>
       <c r="B38" s="49"/>
-      <c r="C38" s="196"/>
-      <c r="D38" s="196"/>
-      <c r="E38" s="196"/>
-      <c r="F38" s="196"/>
-      <c r="G38" s="196"/>
-      <c r="H38" s="201"/>
-      <c r="I38" s="202"/>
-      <c r="J38" s="202"/>
-      <c r="K38" s="202"/>
-      <c r="L38" s="202"/>
-      <c r="M38" s="203"/>
-      <c r="N38" s="197"/>
-      <c r="O38" s="198"/>
-      <c r="P38" s="199"/>
+      <c r="C38" s="183"/>
+      <c r="D38" s="183"/>
+      <c r="E38" s="183"/>
+      <c r="F38" s="183"/>
+      <c r="G38" s="183"/>
+      <c r="H38" s="184"/>
+      <c r="I38" s="185"/>
+      <c r="J38" s="185"/>
+      <c r="K38" s="185"/>
+      <c r="L38" s="185"/>
+      <c r="M38" s="186"/>
+      <c r="N38" s="187"/>
+      <c r="O38" s="188"/>
+      <c r="P38" s="189"/>
       <c r="Q38" s="49"/>
-      <c r="R38" s="200"/>
-      <c r="S38" s="200"/>
+      <c r="R38" s="190"/>
+      <c r="S38" s="190"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="49"/>
       <c r="B39" s="49"/>
-      <c r="C39" s="196"/>
-      <c r="D39" s="196"/>
-      <c r="E39" s="196"/>
-      <c r="F39" s="196"/>
-      <c r="G39" s="196"/>
-      <c r="H39" s="201"/>
-      <c r="I39" s="202"/>
-      <c r="J39" s="202"/>
-      <c r="K39" s="202"/>
-      <c r="L39" s="202"/>
-      <c r="M39" s="203"/>
-      <c r="N39" s="197"/>
-      <c r="O39" s="198"/>
-      <c r="P39" s="199"/>
+      <c r="C39" s="183"/>
+      <c r="D39" s="183"/>
+      <c r="E39" s="183"/>
+      <c r="F39" s="183"/>
+      <c r="G39" s="183"/>
+      <c r="H39" s="184"/>
+      <c r="I39" s="185"/>
+      <c r="J39" s="185"/>
+      <c r="K39" s="185"/>
+      <c r="L39" s="185"/>
+      <c r="M39" s="186"/>
+      <c r="N39" s="187"/>
+      <c r="O39" s="188"/>
+      <c r="P39" s="189"/>
       <c r="Q39" s="49"/>
-      <c r="R39" s="200"/>
-      <c r="S39" s="200"/>
+      <c r="R39" s="190"/>
+      <c r="S39" s="190"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="49"/>
       <c r="B40" s="49"/>
-      <c r="C40" s="196"/>
-      <c r="D40" s="196"/>
-      <c r="E40" s="196"/>
-      <c r="F40" s="196"/>
-      <c r="G40" s="196"/>
-      <c r="H40" s="201"/>
-      <c r="I40" s="202"/>
-      <c r="J40" s="202"/>
-      <c r="K40" s="202"/>
-      <c r="L40" s="202"/>
-      <c r="M40" s="203"/>
-      <c r="N40" s="197"/>
-      <c r="O40" s="198"/>
-      <c r="P40" s="199"/>
+      <c r="C40" s="183"/>
+      <c r="D40" s="183"/>
+      <c r="E40" s="183"/>
+      <c r="F40" s="183"/>
+      <c r="G40" s="183"/>
+      <c r="H40" s="184"/>
+      <c r="I40" s="185"/>
+      <c r="J40" s="185"/>
+      <c r="K40" s="185"/>
+      <c r="L40" s="185"/>
+      <c r="M40" s="186"/>
+      <c r="N40" s="187"/>
+      <c r="O40" s="188"/>
+      <c r="P40" s="189"/>
       <c r="Q40" s="49"/>
-      <c r="R40" s="200"/>
-      <c r="S40" s="200"/>
+      <c r="R40" s="190"/>
+      <c r="S40" s="190"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="49"/>
       <c r="B41" s="49"/>
-      <c r="C41" s="196"/>
-      <c r="D41" s="196"/>
-      <c r="E41" s="196"/>
-      <c r="F41" s="196"/>
-      <c r="G41" s="196"/>
-      <c r="H41" s="201"/>
-      <c r="I41" s="202"/>
-      <c r="J41" s="202"/>
-      <c r="K41" s="202"/>
-      <c r="L41" s="202"/>
-      <c r="M41" s="203"/>
-      <c r="N41" s="197"/>
-      <c r="O41" s="198"/>
-      <c r="P41" s="199"/>
+      <c r="C41" s="183"/>
+      <c r="D41" s="183"/>
+      <c r="E41" s="183"/>
+      <c r="F41" s="183"/>
+      <c r="G41" s="183"/>
+      <c r="H41" s="184"/>
+      <c r="I41" s="185"/>
+      <c r="J41" s="185"/>
+      <c r="K41" s="185"/>
+      <c r="L41" s="185"/>
+      <c r="M41" s="186"/>
+      <c r="N41" s="187"/>
+      <c r="O41" s="188"/>
+      <c r="P41" s="189"/>
       <c r="Q41" s="49"/>
-      <c r="R41" s="200"/>
-      <c r="S41" s="200"/>
+      <c r="R41" s="190"/>
+      <c r="S41" s="190"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="49"/>
       <c r="B42" s="49"/>
-      <c r="C42" s="196"/>
-      <c r="D42" s="196"/>
-      <c r="E42" s="196"/>
-      <c r="F42" s="196"/>
-      <c r="G42" s="196"/>
-      <c r="H42" s="201"/>
-      <c r="I42" s="202"/>
-      <c r="J42" s="202"/>
-      <c r="K42" s="202"/>
-      <c r="L42" s="202"/>
-      <c r="M42" s="203"/>
-      <c r="N42" s="197"/>
-      <c r="O42" s="198"/>
-      <c r="P42" s="199"/>
+      <c r="C42" s="183"/>
+      <c r="D42" s="183"/>
+      <c r="E42" s="183"/>
+      <c r="F42" s="183"/>
+      <c r="G42" s="183"/>
+      <c r="H42" s="184"/>
+      <c r="I42" s="185"/>
+      <c r="J42" s="185"/>
+      <c r="K42" s="185"/>
+      <c r="L42" s="185"/>
+      <c r="M42" s="186"/>
+      <c r="N42" s="187"/>
+      <c r="O42" s="188"/>
+      <c r="P42" s="189"/>
       <c r="Q42" s="49"/>
-      <c r="R42" s="200"/>
-      <c r="S42" s="200"/>
+      <c r="R42" s="190"/>
+      <c r="S42" s="190"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="49"/>
       <c r="B43" s="49"/>
-      <c r="C43" s="196"/>
-      <c r="D43" s="196"/>
-      <c r="E43" s="196"/>
-      <c r="F43" s="196"/>
-      <c r="G43" s="196"/>
-      <c r="H43" s="201"/>
-      <c r="I43" s="202"/>
-      <c r="J43" s="202"/>
-      <c r="K43" s="202"/>
-      <c r="L43" s="202"/>
-      <c r="M43" s="203"/>
-      <c r="N43" s="197"/>
-      <c r="O43" s="198"/>
-      <c r="P43" s="199"/>
+      <c r="C43" s="183"/>
+      <c r="D43" s="183"/>
+      <c r="E43" s="183"/>
+      <c r="F43" s="183"/>
+      <c r="G43" s="183"/>
+      <c r="H43" s="184"/>
+      <c r="I43" s="185"/>
+      <c r="J43" s="185"/>
+      <c r="K43" s="185"/>
+      <c r="L43" s="185"/>
+      <c r="M43" s="186"/>
+      <c r="N43" s="187"/>
+      <c r="O43" s="188"/>
+      <c r="P43" s="189"/>
       <c r="Q43" s="49"/>
-      <c r="R43" s="200"/>
-      <c r="S43" s="200"/>
+      <c r="R43" s="190"/>
+      <c r="S43" s="190"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="49"/>
       <c r="B44" s="49"/>
-      <c r="C44" s="196"/>
-      <c r="D44" s="196"/>
-      <c r="E44" s="196"/>
-      <c r="F44" s="196"/>
-      <c r="G44" s="196"/>
-      <c r="H44" s="201"/>
-      <c r="I44" s="202"/>
-      <c r="J44" s="202"/>
-      <c r="K44" s="202"/>
-      <c r="L44" s="202"/>
-      <c r="M44" s="203"/>
-      <c r="N44" s="197"/>
-      <c r="O44" s="198"/>
-      <c r="P44" s="199"/>
+      <c r="C44" s="183"/>
+      <c r="D44" s="183"/>
+      <c r="E44" s="183"/>
+      <c r="F44" s="183"/>
+      <c r="G44" s="183"/>
+      <c r="H44" s="184"/>
+      <c r="I44" s="185"/>
+      <c r="J44" s="185"/>
+      <c r="K44" s="185"/>
+      <c r="L44" s="185"/>
+      <c r="M44" s="186"/>
+      <c r="N44" s="187"/>
+      <c r="O44" s="188"/>
+      <c r="P44" s="189"/>
       <c r="Q44" s="49"/>
-      <c r="R44" s="200"/>
-      <c r="S44" s="200"/>
+      <c r="R44" s="190"/>
+      <c r="S44" s="190"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="49"/>
       <c r="B45" s="49"/>
-      <c r="C45" s="196"/>
-      <c r="D45" s="196"/>
-      <c r="E45" s="196"/>
-      <c r="F45" s="196"/>
-      <c r="G45" s="196"/>
-      <c r="H45" s="201"/>
-      <c r="I45" s="202"/>
-      <c r="J45" s="202"/>
-      <c r="K45" s="202"/>
-      <c r="L45" s="202"/>
-      <c r="M45" s="203"/>
-      <c r="N45" s="197"/>
-      <c r="O45" s="198"/>
-      <c r="P45" s="199"/>
+      <c r="C45" s="183"/>
+      <c r="D45" s="183"/>
+      <c r="E45" s="183"/>
+      <c r="F45" s="183"/>
+      <c r="G45" s="183"/>
+      <c r="H45" s="184"/>
+      <c r="I45" s="185"/>
+      <c r="J45" s="185"/>
+      <c r="K45" s="185"/>
+      <c r="L45" s="185"/>
+      <c r="M45" s="186"/>
+      <c r="N45" s="187"/>
+      <c r="O45" s="188"/>
+      <c r="P45" s="189"/>
       <c r="Q45" s="49"/>
-      <c r="R45" s="200"/>
-      <c r="S45" s="200"/>
+      <c r="R45" s="190"/>
+      <c r="S45" s="190"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="49"/>
       <c r="B46" s="49"/>
-      <c r="C46" s="196"/>
-      <c r="D46" s="196"/>
-      <c r="E46" s="196"/>
-      <c r="F46" s="196"/>
-      <c r="G46" s="196"/>
-      <c r="H46" s="201"/>
-      <c r="I46" s="202"/>
-      <c r="J46" s="202"/>
-      <c r="K46" s="202"/>
-      <c r="L46" s="202"/>
-      <c r="M46" s="203"/>
-      <c r="N46" s="197"/>
-      <c r="O46" s="198"/>
-      <c r="P46" s="199"/>
+      <c r="C46" s="183"/>
+      <c r="D46" s="183"/>
+      <c r="E46" s="183"/>
+      <c r="F46" s="183"/>
+      <c r="G46" s="183"/>
+      <c r="H46" s="184"/>
+      <c r="I46" s="185"/>
+      <c r="J46" s="185"/>
+      <c r="K46" s="185"/>
+      <c r="L46" s="185"/>
+      <c r="M46" s="186"/>
+      <c r="N46" s="187"/>
+      <c r="O46" s="188"/>
+      <c r="P46" s="189"/>
       <c r="Q46" s="49"/>
-      <c r="R46" s="200"/>
-      <c r="S46" s="200"/>
+      <c r="R46" s="190"/>
+      <c r="S46" s="190"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="49"/>
       <c r="B47" s="49"/>
-      <c r="C47" s="196"/>
-      <c r="D47" s="196"/>
-      <c r="E47" s="196"/>
-      <c r="F47" s="196"/>
-      <c r="G47" s="196"/>
-      <c r="H47" s="201"/>
-      <c r="I47" s="202"/>
-      <c r="J47" s="202"/>
-      <c r="K47" s="202"/>
-      <c r="L47" s="202"/>
-      <c r="M47" s="203"/>
-      <c r="N47" s="197"/>
-      <c r="O47" s="198"/>
-      <c r="P47" s="199"/>
+      <c r="C47" s="183"/>
+      <c r="D47" s="183"/>
+      <c r="E47" s="183"/>
+      <c r="F47" s="183"/>
+      <c r="G47" s="183"/>
+      <c r="H47" s="184"/>
+      <c r="I47" s="185"/>
+      <c r="J47" s="185"/>
+      <c r="K47" s="185"/>
+      <c r="L47" s="185"/>
+      <c r="M47" s="186"/>
+      <c r="N47" s="187"/>
+      <c r="O47" s="188"/>
+      <c r="P47" s="189"/>
       <c r="Q47" s="49"/>
-      <c r="R47" s="200"/>
-      <c r="S47" s="200"/>
+      <c r="R47" s="190"/>
+      <c r="S47" s="190"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="49"/>
       <c r="B48" s="49"/>
-      <c r="C48" s="196"/>
-      <c r="D48" s="196"/>
-      <c r="E48" s="196"/>
-      <c r="F48" s="196"/>
-      <c r="G48" s="196"/>
-      <c r="H48" s="201"/>
-      <c r="I48" s="202"/>
-      <c r="J48" s="202"/>
-      <c r="K48" s="202"/>
-      <c r="L48" s="202"/>
-      <c r="M48" s="203"/>
-      <c r="N48" s="197"/>
-      <c r="O48" s="198"/>
-      <c r="P48" s="199"/>
+      <c r="C48" s="183"/>
+      <c r="D48" s="183"/>
+      <c r="E48" s="183"/>
+      <c r="F48" s="183"/>
+      <c r="G48" s="183"/>
+      <c r="H48" s="184"/>
+      <c r="I48" s="185"/>
+      <c r="J48" s="185"/>
+      <c r="K48" s="185"/>
+      <c r="L48" s="185"/>
+      <c r="M48" s="186"/>
+      <c r="N48" s="187"/>
+      <c r="O48" s="188"/>
+      <c r="P48" s="189"/>
       <c r="Q48" s="49"/>
-      <c r="R48" s="200"/>
-      <c r="S48" s="200"/>
+      <c r="R48" s="190"/>
+      <c r="S48" s="190"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="49"/>
       <c r="B49" s="49"/>
-      <c r="C49" s="196"/>
-      <c r="D49" s="196"/>
-      <c r="E49" s="196"/>
-      <c r="F49" s="196"/>
-      <c r="G49" s="196"/>
-      <c r="H49" s="201"/>
-      <c r="I49" s="202"/>
-      <c r="J49" s="202"/>
-      <c r="K49" s="202"/>
-      <c r="L49" s="202"/>
-      <c r="M49" s="203"/>
-      <c r="N49" s="197"/>
-      <c r="O49" s="198"/>
-      <c r="P49" s="199"/>
+      <c r="C49" s="183"/>
+      <c r="D49" s="183"/>
+      <c r="E49" s="183"/>
+      <c r="F49" s="183"/>
+      <c r="G49" s="183"/>
+      <c r="H49" s="184"/>
+      <c r="I49" s="185"/>
+      <c r="J49" s="185"/>
+      <c r="K49" s="185"/>
+      <c r="L49" s="185"/>
+      <c r="M49" s="186"/>
+      <c r="N49" s="187"/>
+      <c r="O49" s="188"/>
+      <c r="P49" s="189"/>
       <c r="Q49" s="49"/>
-      <c r="R49" s="200"/>
-      <c r="S49" s="200"/>
+      <c r="R49" s="190"/>
+      <c r="S49" s="190"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="49"/>
       <c r="B50" s="49"/>
-      <c r="C50" s="196"/>
-      <c r="D50" s="196"/>
-      <c r="E50" s="196"/>
-      <c r="F50" s="196"/>
-      <c r="G50" s="196"/>
-      <c r="H50" s="201"/>
-      <c r="I50" s="202"/>
-      <c r="J50" s="202"/>
-      <c r="K50" s="202"/>
-      <c r="L50" s="202"/>
-      <c r="M50" s="203"/>
-      <c r="N50" s="197"/>
-      <c r="O50" s="198"/>
-      <c r="P50" s="199"/>
+      <c r="C50" s="183"/>
+      <c r="D50" s="183"/>
+      <c r="E50" s="183"/>
+      <c r="F50" s="183"/>
+      <c r="G50" s="183"/>
+      <c r="H50" s="184"/>
+      <c r="I50" s="185"/>
+      <c r="J50" s="185"/>
+      <c r="K50" s="185"/>
+      <c r="L50" s="185"/>
+      <c r="M50" s="186"/>
+      <c r="N50" s="187"/>
+      <c r="O50" s="188"/>
+      <c r="P50" s="189"/>
       <c r="Q50" s="49"/>
-      <c r="R50" s="200"/>
-      <c r="S50" s="200"/>
+      <c r="R50" s="190"/>
+      <c r="S50" s="190"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="49"/>
       <c r="B51" s="49"/>
-      <c r="C51" s="196"/>
-      <c r="D51" s="196"/>
-      <c r="E51" s="196"/>
-      <c r="F51" s="196"/>
-      <c r="G51" s="196"/>
-      <c r="H51" s="201"/>
-      <c r="I51" s="202"/>
-      <c r="J51" s="202"/>
-      <c r="K51" s="202"/>
-      <c r="L51" s="202"/>
-      <c r="M51" s="203"/>
-      <c r="N51" s="197"/>
-      <c r="O51" s="198"/>
-      <c r="P51" s="199"/>
+      <c r="C51" s="183"/>
+      <c r="D51" s="183"/>
+      <c r="E51" s="183"/>
+      <c r="F51" s="183"/>
+      <c r="G51" s="183"/>
+      <c r="H51" s="184"/>
+      <c r="I51" s="185"/>
+      <c r="J51" s="185"/>
+      <c r="K51" s="185"/>
+      <c r="L51" s="185"/>
+      <c r="M51" s="186"/>
+      <c r="N51" s="187"/>
+      <c r="O51" s="188"/>
+      <c r="P51" s="189"/>
       <c r="Q51" s="49"/>
-      <c r="R51" s="200"/>
-      <c r="S51" s="200"/>
+      <c r="R51" s="190"/>
+      <c r="S51" s="190"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="49"/>
       <c r="B52" s="49"/>
-      <c r="C52" s="196"/>
-      <c r="D52" s="196"/>
-      <c r="E52" s="196"/>
-      <c r="F52" s="196"/>
-      <c r="G52" s="196"/>
-      <c r="H52" s="201"/>
-      <c r="I52" s="202"/>
-      <c r="J52" s="202"/>
-      <c r="K52" s="202"/>
-      <c r="L52" s="202"/>
-      <c r="M52" s="203"/>
-      <c r="N52" s="197"/>
-      <c r="O52" s="198"/>
-      <c r="P52" s="199"/>
+      <c r="C52" s="183"/>
+      <c r="D52" s="183"/>
+      <c r="E52" s="183"/>
+      <c r="F52" s="183"/>
+      <c r="G52" s="183"/>
+      <c r="H52" s="184"/>
+      <c r="I52" s="185"/>
+      <c r="J52" s="185"/>
+      <c r="K52" s="185"/>
+      <c r="L52" s="185"/>
+      <c r="M52" s="186"/>
+      <c r="N52" s="187"/>
+      <c r="O52" s="188"/>
+      <c r="P52" s="189"/>
       <c r="Q52" s="49"/>
-      <c r="R52" s="200"/>
-      <c r="S52" s="200"/>
+      <c r="R52" s="190"/>
+      <c r="S52" s="190"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -21142,6 +21015,194 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/削除機能詳細設計書.xlsx
+++ b/Documents/削除機能詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DE2C13-C554-41CE-B429-E6E3F8694936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1DF024-0903-4EFD-B4B7-35398CBC5246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2087,7 +2087,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2326,6 +2326,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2336,11 +2369,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2356,9 +2437,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2377,84 +2455,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2518,27 +2518,48 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2551,65 +2572,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2619,22 +2610,100 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2642,78 +2711,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4796,23 +4793,23 @@
       <c r="AL1" s="53"/>
       <c r="AM1" s="53"/>
       <c r="AN1" s="53"/>
-      <c r="AO1" s="214" t="s">
+      <c r="AO1" s="213" t="s">
         <v>126</v>
       </c>
-      <c r="AP1" s="214"/>
-      <c r="AQ1" s="214"/>
-      <c r="AR1" s="214"/>
-      <c r="AS1" s="214"/>
-      <c r="AT1" s="215">
+      <c r="AP1" s="213"/>
+      <c r="AQ1" s="213"/>
+      <c r="AR1" s="213"/>
+      <c r="AS1" s="213"/>
+      <c r="AT1" s="214">
         <v>45821</v>
       </c>
-      <c r="AU1" s="216"/>
-      <c r="AV1" s="216"/>
-      <c r="AW1" s="216"/>
-      <c r="AX1" s="216"/>
-      <c r="AY1" s="216"/>
-      <c r="AZ1" s="216"/>
-      <c r="BA1" s="216"/>
+      <c r="AU1" s="215"/>
+      <c r="AV1" s="215"/>
+      <c r="AW1" s="215"/>
+      <c r="AX1" s="215"/>
+      <c r="AY1" s="215"/>
+      <c r="AZ1" s="215"/>
+      <c r="BA1" s="215"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -4858,54 +4855,54 @@
       <c r="AK4" s="60"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="211" t="s">
+      <c r="A5" s="210" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="212"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
-      <c r="F5" s="213"/>
-      <c r="G5" s="217" t="s">
+      <c r="B5" s="211"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="216" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="218"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="218"/>
-      <c r="K5" s="218"/>
-      <c r="L5" s="218"/>
-      <c r="M5" s="218"/>
-      <c r="N5" s="218"/>
-      <c r="O5" s="218"/>
-      <c r="P5" s="218"/>
-      <c r="Q5" s="218"/>
-      <c r="R5" s="218"/>
-      <c r="S5" s="219"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
+      <c r="L5" s="217"/>
+      <c r="M5" s="217"/>
+      <c r="N5" s="217"/>
+      <c r="O5" s="217"/>
+      <c r="P5" s="217"/>
+      <c r="Q5" s="217"/>
+      <c r="R5" s="217"/>
+      <c r="S5" s="218"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="211" t="s">
+      <c r="A6" s="210" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="212"/>
-      <c r="C6" s="212"/>
-      <c r="D6" s="212"/>
-      <c r="E6" s="212"/>
-      <c r="F6" s="213"/>
-      <c r="G6" s="220">
+      <c r="B6" s="211"/>
+      <c r="C6" s="211"/>
+      <c r="D6" s="211"/>
+      <c r="E6" s="211"/>
+      <c r="F6" s="212"/>
+      <c r="G6" s="219">
         <v>1</v>
       </c>
-      <c r="H6" s="218"/>
-      <c r="I6" s="218"/>
-      <c r="J6" s="218"/>
-      <c r="K6" s="218"/>
-      <c r="L6" s="218"/>
-      <c r="M6" s="218"/>
-      <c r="N6" s="218"/>
-      <c r="O6" s="218"/>
-      <c r="P6" s="218"/>
-      <c r="Q6" s="218"/>
-      <c r="R6" s="218"/>
-      <c r="S6" s="219"/>
+      <c r="H6" s="217"/>
+      <c r="I6" s="217"/>
+      <c r="J6" s="217"/>
+      <c r="K6" s="217"/>
+      <c r="L6" s="217"/>
+      <c r="M6" s="217"/>
+      <c r="N6" s="217"/>
+      <c r="O6" s="217"/>
+      <c r="P6" s="217"/>
+      <c r="Q6" s="217"/>
+      <c r="R6" s="217"/>
+      <c r="S6" s="218"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -4914,61 +4911,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="211" t="s">
+      <c r="A9" s="210" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="212"/>
-      <c r="C9" s="212"/>
-      <c r="D9" s="212"/>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="212"/>
-      <c r="H9" s="212"/>
-      <c r="I9" s="212"/>
-      <c r="J9" s="212"/>
-      <c r="K9" s="212"/>
-      <c r="L9" s="212"/>
-      <c r="M9" s="212"/>
-      <c r="N9" s="212"/>
-      <c r="O9" s="212"/>
-      <c r="P9" s="212"/>
-      <c r="Q9" s="212"/>
-      <c r="R9" s="212"/>
-      <c r="S9" s="212"/>
-      <c r="T9" s="212"/>
-      <c r="U9" s="212"/>
-      <c r="V9" s="212"/>
-      <c r="W9" s="212"/>
-      <c r="X9" s="212"/>
-      <c r="Y9" s="212"/>
-      <c r="Z9" s="212"/>
-      <c r="AA9" s="212"/>
-      <c r="AB9" s="212"/>
-      <c r="AC9" s="212"/>
-      <c r="AD9" s="212"/>
-      <c r="AE9" s="212"/>
-      <c r="AF9" s="212"/>
-      <c r="AG9" s="212"/>
-      <c r="AH9" s="212"/>
-      <c r="AI9" s="212"/>
-      <c r="AJ9" s="212"/>
-      <c r="AK9" s="212"/>
-      <c r="AL9" s="212"/>
-      <c r="AM9" s="212"/>
-      <c r="AN9" s="212"/>
-      <c r="AO9" s="212"/>
-      <c r="AP9" s="212"/>
-      <c r="AQ9" s="212"/>
-      <c r="AR9" s="212"/>
-      <c r="AS9" s="212"/>
-      <c r="AT9" s="212"/>
-      <c r="AU9" s="212"/>
-      <c r="AV9" s="212"/>
-      <c r="AW9" s="212"/>
-      <c r="AX9" s="212"/>
-      <c r="AY9" s="212"/>
-      <c r="AZ9" s="212"/>
-      <c r="BA9" s="213"/>
+      <c r="B9" s="211"/>
+      <c r="C9" s="211"/>
+      <c r="D9" s="211"/>
+      <c r="E9" s="211"/>
+      <c r="F9" s="211"/>
+      <c r="G9" s="211"/>
+      <c r="H9" s="211"/>
+      <c r="I9" s="211"/>
+      <c r="J9" s="211"/>
+      <c r="K9" s="211"/>
+      <c r="L9" s="211"/>
+      <c r="M9" s="211"/>
+      <c r="N9" s="211"/>
+      <c r="O9" s="211"/>
+      <c r="P9" s="211"/>
+      <c r="Q9" s="211"/>
+      <c r="R9" s="211"/>
+      <c r="S9" s="211"/>
+      <c r="T9" s="211"/>
+      <c r="U9" s="211"/>
+      <c r="V9" s="211"/>
+      <c r="W9" s="211"/>
+      <c r="X9" s="211"/>
+      <c r="Y9" s="211"/>
+      <c r="Z9" s="211"/>
+      <c r="AA9" s="211"/>
+      <c r="AB9" s="211"/>
+      <c r="AC9" s="211"/>
+      <c r="AD9" s="211"/>
+      <c r="AE9" s="211"/>
+      <c r="AF9" s="211"/>
+      <c r="AG9" s="211"/>
+      <c r="AH9" s="211"/>
+      <c r="AI9" s="211"/>
+      <c r="AJ9" s="211"/>
+      <c r="AK9" s="211"/>
+      <c r="AL9" s="211"/>
+      <c r="AM9" s="211"/>
+      <c r="AN9" s="211"/>
+      <c r="AO9" s="211"/>
+      <c r="AP9" s="211"/>
+      <c r="AQ9" s="211"/>
+      <c r="AR9" s="211"/>
+      <c r="AS9" s="211"/>
+      <c r="AT9" s="211"/>
+      <c r="AU9" s="211"/>
+      <c r="AV9" s="211"/>
+      <c r="AW9" s="211"/>
+      <c r="AX9" s="211"/>
+      <c r="AY9" s="211"/>
+      <c r="AZ9" s="211"/>
+      <c r="BA9" s="212"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="62"/>
@@ -8691,61 +8688,61 @@
       <c r="BA102" s="64"/>
     </row>
     <row r="103" spans="1:53" ht="18" customHeight="1">
-      <c r="A103" s="211" t="s">
+      <c r="A103" s="210" t="s">
         <v>132</v>
       </c>
-      <c r="B103" s="212"/>
-      <c r="C103" s="212"/>
-      <c r="D103" s="212"/>
-      <c r="E103" s="212"/>
-      <c r="F103" s="212"/>
-      <c r="G103" s="212"/>
-      <c r="H103" s="212"/>
-      <c r="I103" s="212"/>
-      <c r="J103" s="212"/>
-      <c r="K103" s="212"/>
-      <c r="L103" s="212"/>
-      <c r="M103" s="212"/>
-      <c r="N103" s="212"/>
-      <c r="O103" s="212"/>
-      <c r="P103" s="212"/>
-      <c r="Q103" s="212"/>
-      <c r="R103" s="212"/>
-      <c r="S103" s="212"/>
-      <c r="T103" s="212"/>
-      <c r="U103" s="212"/>
-      <c r="V103" s="212"/>
-      <c r="W103" s="212"/>
-      <c r="X103" s="212"/>
-      <c r="Y103" s="212"/>
-      <c r="Z103" s="212"/>
-      <c r="AA103" s="212"/>
-      <c r="AB103" s="212"/>
-      <c r="AC103" s="212"/>
-      <c r="AD103" s="212"/>
-      <c r="AE103" s="212"/>
-      <c r="AF103" s="212"/>
-      <c r="AG103" s="212"/>
-      <c r="AH103" s="212"/>
-      <c r="AI103" s="212"/>
-      <c r="AJ103" s="212"/>
-      <c r="AK103" s="212"/>
-      <c r="AL103" s="212"/>
-      <c r="AM103" s="212"/>
-      <c r="AN103" s="212"/>
-      <c r="AO103" s="212"/>
-      <c r="AP103" s="212"/>
-      <c r="AQ103" s="212"/>
-      <c r="AR103" s="212"/>
-      <c r="AS103" s="212"/>
-      <c r="AT103" s="212"/>
-      <c r="AU103" s="212"/>
-      <c r="AV103" s="212"/>
-      <c r="AW103" s="212"/>
-      <c r="AX103" s="212"/>
-      <c r="AY103" s="212"/>
-      <c r="AZ103" s="212"/>
-      <c r="BA103" s="213"/>
+      <c r="B103" s="211"/>
+      <c r="C103" s="211"/>
+      <c r="D103" s="211"/>
+      <c r="E103" s="211"/>
+      <c r="F103" s="211"/>
+      <c r="G103" s="211"/>
+      <c r="H103" s="211"/>
+      <c r="I103" s="211"/>
+      <c r="J103" s="211"/>
+      <c r="K103" s="211"/>
+      <c r="L103" s="211"/>
+      <c r="M103" s="211"/>
+      <c r="N103" s="211"/>
+      <c r="O103" s="211"/>
+      <c r="P103" s="211"/>
+      <c r="Q103" s="211"/>
+      <c r="R103" s="211"/>
+      <c r="S103" s="211"/>
+      <c r="T103" s="211"/>
+      <c r="U103" s="211"/>
+      <c r="V103" s="211"/>
+      <c r="W103" s="211"/>
+      <c r="X103" s="211"/>
+      <c r="Y103" s="211"/>
+      <c r="Z103" s="211"/>
+      <c r="AA103" s="211"/>
+      <c r="AB103" s="211"/>
+      <c r="AC103" s="211"/>
+      <c r="AD103" s="211"/>
+      <c r="AE103" s="211"/>
+      <c r="AF103" s="211"/>
+      <c r="AG103" s="211"/>
+      <c r="AH103" s="211"/>
+      <c r="AI103" s="211"/>
+      <c r="AJ103" s="211"/>
+      <c r="AK103" s="211"/>
+      <c r="AL103" s="211"/>
+      <c r="AM103" s="211"/>
+      <c r="AN103" s="211"/>
+      <c r="AO103" s="211"/>
+      <c r="AP103" s="211"/>
+      <c r="AQ103" s="211"/>
+      <c r="AR103" s="211"/>
+      <c r="AS103" s="211"/>
+      <c r="AT103" s="211"/>
+      <c r="AU103" s="211"/>
+      <c r="AV103" s="211"/>
+      <c r="AW103" s="211"/>
+      <c r="AX103" s="211"/>
+      <c r="AY103" s="211"/>
+      <c r="AZ103" s="211"/>
+      <c r="BA103" s="212"/>
     </row>
     <row r="104" spans="1:53" ht="21.95" customHeight="1">
       <c r="A104" s="65"/>
@@ -9068,61 +9065,61 @@
       <c r="BA111" s="64"/>
     </row>
     <row r="112" spans="1:53" ht="18" customHeight="1">
-      <c r="A112" s="211" t="s">
+      <c r="A112" s="210" t="s">
         <v>133</v>
       </c>
-      <c r="B112" s="212"/>
-      <c r="C112" s="212"/>
-      <c r="D112" s="212"/>
-      <c r="E112" s="212"/>
-      <c r="F112" s="212"/>
-      <c r="G112" s="212"/>
-      <c r="H112" s="212"/>
-      <c r="I112" s="212"/>
-      <c r="J112" s="212"/>
-      <c r="K112" s="212"/>
-      <c r="L112" s="212"/>
-      <c r="M112" s="212"/>
-      <c r="N112" s="212"/>
-      <c r="O112" s="212"/>
-      <c r="P112" s="212"/>
-      <c r="Q112" s="212"/>
-      <c r="R112" s="212"/>
-      <c r="S112" s="212"/>
-      <c r="T112" s="212"/>
-      <c r="U112" s="212"/>
-      <c r="V112" s="212"/>
-      <c r="W112" s="212"/>
-      <c r="X112" s="212"/>
-      <c r="Y112" s="212"/>
-      <c r="Z112" s="212"/>
-      <c r="AA112" s="212"/>
-      <c r="AB112" s="212"/>
-      <c r="AC112" s="212"/>
-      <c r="AD112" s="212"/>
-      <c r="AE112" s="212"/>
-      <c r="AF112" s="212"/>
-      <c r="AG112" s="212"/>
-      <c r="AH112" s="212"/>
-      <c r="AI112" s="212"/>
-      <c r="AJ112" s="212"/>
-      <c r="AK112" s="212"/>
-      <c r="AL112" s="212"/>
-      <c r="AM112" s="212"/>
-      <c r="AN112" s="212"/>
-      <c r="AO112" s="212"/>
-      <c r="AP112" s="212"/>
-      <c r="AQ112" s="212"/>
-      <c r="AR112" s="212"/>
-      <c r="AS112" s="212"/>
-      <c r="AT112" s="212"/>
-      <c r="AU112" s="212"/>
-      <c r="AV112" s="212"/>
-      <c r="AW112" s="212"/>
-      <c r="AX112" s="212"/>
-      <c r="AY112" s="212"/>
-      <c r="AZ112" s="212"/>
-      <c r="BA112" s="212"/>
+      <c r="B112" s="211"/>
+      <c r="C112" s="211"/>
+      <c r="D112" s="211"/>
+      <c r="E112" s="211"/>
+      <c r="F112" s="211"/>
+      <c r="G112" s="211"/>
+      <c r="H112" s="211"/>
+      <c r="I112" s="211"/>
+      <c r="J112" s="211"/>
+      <c r="K112" s="211"/>
+      <c r="L112" s="211"/>
+      <c r="M112" s="211"/>
+      <c r="N112" s="211"/>
+      <c r="O112" s="211"/>
+      <c r="P112" s="211"/>
+      <c r="Q112" s="211"/>
+      <c r="R112" s="211"/>
+      <c r="S112" s="211"/>
+      <c r="T112" s="211"/>
+      <c r="U112" s="211"/>
+      <c r="V112" s="211"/>
+      <c r="W112" s="211"/>
+      <c r="X112" s="211"/>
+      <c r="Y112" s="211"/>
+      <c r="Z112" s="211"/>
+      <c r="AA112" s="211"/>
+      <c r="AB112" s="211"/>
+      <c r="AC112" s="211"/>
+      <c r="AD112" s="211"/>
+      <c r="AE112" s="211"/>
+      <c r="AF112" s="211"/>
+      <c r="AG112" s="211"/>
+      <c r="AH112" s="211"/>
+      <c r="AI112" s="211"/>
+      <c r="AJ112" s="211"/>
+      <c r="AK112" s="211"/>
+      <c r="AL112" s="211"/>
+      <c r="AM112" s="211"/>
+      <c r="AN112" s="211"/>
+      <c r="AO112" s="211"/>
+      <c r="AP112" s="211"/>
+      <c r="AQ112" s="211"/>
+      <c r="AR112" s="211"/>
+      <c r="AS112" s="211"/>
+      <c r="AT112" s="211"/>
+      <c r="AU112" s="211"/>
+      <c r="AV112" s="211"/>
+      <c r="AW112" s="211"/>
+      <c r="AX112" s="211"/>
+      <c r="AY112" s="211"/>
+      <c r="AZ112" s="211"/>
+      <c r="BA112" s="211"/>
     </row>
     <row r="113" spans="1:53" ht="21.95" customHeight="1">
       <c r="A113" s="65"/>
@@ -9296,19 +9293,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="117" t="s">
+      <c r="B1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="105"/>
-      <c r="F1" s="117" t="s">
+      <c r="E1" s="88"/>
+      <c r="F1" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="105"/>
+      <c r="G1" s="88"/>
       <c r="H1" s="37" t="s">
         <v>8</v>
       </c>
@@ -9320,190 +9317,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="111"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="118" t="s">
+      <c r="A2" s="99"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="119"/>
-      <c r="F2" s="118" t="s">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="119"/>
-      <c r="H2" s="122">
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
         <v>45806</v>
       </c>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="100"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="111"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="113"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="101"/>
+      <c r="A3" s="99"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="114"/>
-      <c r="B4" s="115"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="102"/>
+      <c r="A4" s="102"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="104"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="106" t="s">
+      <c r="B5" s="87"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="107"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="90"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="90" t="s">
+      <c r="B6" s="92"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="84"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="95"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="90" t="s">
+      <c r="B7" s="92"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="84"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="95"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="81"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="90" t="s">
+      <c r="B8" s="92"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="84"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="91" t="s">
+      <c r="A9" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="82"/>
-      <c r="D9" s="83" t="s">
+      <c r="C9" s="93"/>
+      <c r="D9" s="111" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="96"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="94" t="s">
+      <c r="A10" s="118"/>
+      <c r="B10" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="82"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="84"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="94" t="s">
+      <c r="A11" s="119"/>
+      <c r="B11" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="82"/>
-      <c r="D11" s="90" t="s">
+      <c r="C11" s="93"/>
+      <c r="D11" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="84"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="80" t="s">
+      <c r="A12" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="81"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="83" t="s">
+      <c r="B12" s="92"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="84"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="87"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="89"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="113"/>
+      <c r="I13" s="113"/>
+      <c r="J13" s="116"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10494,18 +10491,6 @@
     <row r="1000" s="39" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -10521,6 +10506,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -13445,20 +13442,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="148" t="s">
+      <c r="D5" s="156" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="149"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -13472,19 +13469,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="150"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="153"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -13496,7 +13493,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="154"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -13508,7 +13505,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="154"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -13520,7 +13517,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="154"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -13532,7 +13529,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="154"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -13544,7 +13541,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="154"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -13556,7 +13553,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="154"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -13570,7 +13567,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="150"/>
+      <c r="J14" s="146"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="147" t="s">
@@ -13578,7 +13575,7 @@
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="74"/>
-      <c r="D15" s="155" t="s">
+      <c r="D15" s="145" t="s">
         <v>73</v>
       </c>
       <c r="E15" s="73"/>
@@ -13610,14 +13607,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="156" t="s">
+      <c r="H16" s="148" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="73"/>
-      <c r="J16" s="150"/>
+      <c r="J16" s="146"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="146">
+      <c r="A17" s="144">
         <v>1</v>
       </c>
       <c r="B17" s="73"/>
@@ -13632,12 +13629,12 @@
         <v>82</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="155"/>
+      <c r="H17" s="145"/>
       <c r="I17" s="73"/>
-      <c r="J17" s="150"/>
+      <c r="J17" s="146"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="146">
+      <c r="A18" s="144">
         <v>2</v>
       </c>
       <c r="B18" s="73"/>
@@ -13654,12 +13651,12 @@
       <c r="G18" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="155"/>
+      <c r="H18" s="145"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="150"/>
+      <c r="J18" s="146"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="146">
+      <c r="A19" s="144">
         <v>3</v>
       </c>
       <c r="B19" s="73"/>
@@ -13674,12 +13671,12 @@
       <c r="G19" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="155"/>
+      <c r="H19" s="145"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="150"/>
+      <c r="J19" s="146"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="146">
+      <c r="A20" s="144">
         <v>4</v>
       </c>
       <c r="B20" s="73"/>
@@ -13696,12 +13693,12 @@
       <c r="G20" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="155"/>
+      <c r="H20" s="145"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="150"/>
+      <c r="J20" s="146"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="146">
+      <c r="A21" s="144">
         <v>5</v>
       </c>
       <c r="B21" s="73"/>
@@ -13718,12 +13715,12 @@
       <c r="G21" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="155"/>
+      <c r="H21" s="145"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="150"/>
+      <c r="J21" s="146"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="146">
+      <c r="A22" s="144">
         <v>6</v>
       </c>
       <c r="B22" s="73"/>
@@ -13738,12 +13735,12 @@
         <v>61</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="155"/>
+      <c r="H22" s="145"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="150"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="146">
+      <c r="A23" s="144">
         <v>7</v>
       </c>
       <c r="B23" s="73"/>
@@ -13758,9 +13755,9 @@
         <v>61</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="158"/>
-      <c r="J23" s="159"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
       <c r="A24" s="147"/>
@@ -13772,13 +13769,13 @@
       <c r="G24" s="73"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73"/>
-      <c r="J24" s="150"/>
+      <c r="J24" s="146"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
       <c r="A25" s="147"/>
       <c r="B25" s="73"/>
       <c r="C25" s="74"/>
-      <c r="D25" s="155"/>
+      <c r="D25" s="145"/>
       <c r="E25" s="73"/>
       <c r="F25" s="73"/>
       <c r="G25" s="73"/>
@@ -13794,93 +13791,93 @@
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="156"/>
+      <c r="H26" s="148"/>
       <c r="I26" s="73"/>
-      <c r="J26" s="150"/>
+      <c r="J26" s="146"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="146"/>
+      <c r="A27" s="144"/>
       <c r="B27" s="73"/>
       <c r="C27" s="74"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="155"/>
+      <c r="H27" s="145"/>
       <c r="I27" s="73"/>
-      <c r="J27" s="150"/>
+      <c r="J27" s="146"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="146"/>
+      <c r="A28" s="144"/>
       <c r="B28" s="73"/>
       <c r="C28" s="74"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="155"/>
+      <c r="H28" s="145"/>
       <c r="I28" s="73"/>
-      <c r="J28" s="150"/>
+      <c r="J28" s="146"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="146"/>
+      <c r="A29" s="144"/>
       <c r="B29" s="73"/>
       <c r="C29" s="74"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
-      <c r="H29" s="155"/>
+      <c r="H29" s="145"/>
       <c r="I29" s="73"/>
-      <c r="J29" s="150"/>
+      <c r="J29" s="146"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="146"/>
+      <c r="A30" s="144"/>
       <c r="B30" s="73"/>
       <c r="C30" s="74"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="155"/>
+      <c r="H30" s="145"/>
       <c r="I30" s="73"/>
-      <c r="J30" s="150"/>
+      <c r="J30" s="146"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="146"/>
+      <c r="A31" s="144"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="155"/>
+      <c r="H31" s="145"/>
       <c r="I31" s="73"/>
-      <c r="J31" s="150"/>
+      <c r="J31" s="146"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="146"/>
+      <c r="A32" s="144"/>
       <c r="B32" s="73"/>
       <c r="C32" s="74"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="155"/>
+      <c r="H32" s="145"/>
       <c r="I32" s="73"/>
-      <c r="J32" s="150"/>
+      <c r="J32" s="146"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="160"/>
-      <c r="B33" s="158"/>
-      <c r="C33" s="161"/>
+      <c r="A33" s="149"/>
+      <c r="B33" s="150"/>
+      <c r="C33" s="151"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
-      <c r="H33" s="157"/>
-      <c r="I33" s="158"/>
-      <c r="J33" s="159"/>
+      <c r="H33" s="152"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="153"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
       <c r="A34" s="147"/>
@@ -13892,13 +13889,13 @@
       <c r="G34" s="73"/>
       <c r="H34" s="73"/>
       <c r="I34" s="73"/>
-      <c r="J34" s="150"/>
+      <c r="J34" s="146"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
       <c r="A35" s="147"/>
       <c r="B35" s="73"/>
       <c r="C35" s="74"/>
-      <c r="D35" s="155"/>
+      <c r="D35" s="145"/>
       <c r="E35" s="73"/>
       <c r="F35" s="73"/>
       <c r="G35" s="73"/>
@@ -13914,69 +13911,69 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
-      <c r="H36" s="156"/>
+      <c r="H36" s="148"/>
       <c r="I36" s="73"/>
-      <c r="J36" s="150"/>
+      <c r="J36" s="146"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="146"/>
+      <c r="A37" s="144"/>
       <c r="B37" s="73"/>
       <c r="C37" s="74"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="155"/>
+      <c r="H37" s="145"/>
       <c r="I37" s="73"/>
-      <c r="J37" s="150"/>
+      <c r="J37" s="146"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="146"/>
+      <c r="A38" s="144"/>
       <c r="B38" s="73"/>
       <c r="C38" s="74"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="155"/>
+      <c r="H38" s="145"/>
       <c r="I38" s="73"/>
-      <c r="J38" s="150"/>
+      <c r="J38" s="146"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="146"/>
+      <c r="A39" s="144"/>
       <c r="B39" s="73"/>
       <c r="C39" s="74"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="155"/>
+      <c r="H39" s="145"/>
       <c r="I39" s="73"/>
-      <c r="J39" s="150"/>
+      <c r="J39" s="146"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="146"/>
+      <c r="A40" s="144"/>
       <c r="B40" s="73"/>
       <c r="C40" s="74"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="155"/>
+      <c r="H40" s="145"/>
       <c r="I40" s="73"/>
-      <c r="J40" s="150"/>
+      <c r="J40" s="146"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="146"/>
+      <c r="A41" s="144"/>
       <c r="B41" s="73"/>
       <c r="C41" s="74"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="155"/>
+      <c r="H41" s="145"/>
       <c r="I41" s="73"/>
-      <c r="J41" s="150"/>
+      <c r="J41" s="146"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14939,50 +14936,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -14999,11 +14957,50 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -15094,20 +15091,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="148" t="s">
+      <c r="D5" s="156" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="149"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -15121,19 +15118,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="150"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="153"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -15145,7 +15142,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="154"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -15157,7 +15154,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="154"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -15169,7 +15166,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="154"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -15181,7 +15178,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="154"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -15193,7 +15190,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="154"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -15205,7 +15202,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="154"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -15219,7 +15216,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="150"/>
+      <c r="J14" s="146"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="147" t="s">
@@ -15227,7 +15224,7 @@
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="74"/>
-      <c r="D15" s="155" t="s">
+      <c r="D15" s="145" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="73"/>
@@ -15259,14 +15256,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="156" t="s">
+      <c r="H16" s="148" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="73"/>
-      <c r="J16" s="150"/>
+      <c r="J16" s="146"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="146">
+      <c r="A17" s="144">
         <v>1</v>
       </c>
       <c r="B17" s="73"/>
@@ -15283,83 +15280,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="155" t="s">
+      <c r="H17" s="145" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="73"/>
-      <c r="J17" s="150"/>
+      <c r="J17" s="146"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="146"/>
+      <c r="A18" s="144"/>
       <c r="B18" s="73"/>
       <c r="C18" s="74"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="155"/>
+      <c r="H18" s="145"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="150"/>
+      <c r="J18" s="146"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="146"/>
+      <c r="A19" s="144"/>
       <c r="B19" s="73"/>
       <c r="C19" s="74"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="155"/>
+      <c r="H19" s="145"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="150"/>
+      <c r="J19" s="146"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="146"/>
+      <c r="A20" s="144"/>
       <c r="B20" s="73"/>
       <c r="C20" s="74"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="155"/>
+      <c r="H20" s="145"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="150"/>
+      <c r="J20" s="146"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="146"/>
+      <c r="A21" s="144"/>
       <c r="B21" s="73"/>
       <c r="C21" s="74"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="155"/>
+      <c r="H21" s="145"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="150"/>
+      <c r="J21" s="146"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="146"/>
+      <c r="A22" s="144"/>
       <c r="B22" s="73"/>
       <c r="C22" s="74"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="155"/>
+      <c r="H22" s="145"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="150"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="160"/>
-      <c r="B23" s="158"/>
-      <c r="C23" s="161"/>
+      <c r="A23" s="149"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="151"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="158"/>
-      <c r="J23" s="159"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -16340,22 +16337,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -16371,6 +16352,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -16461,20 +16458,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="148" t="s">
+      <c r="D5" s="156" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="149"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -16488,19 +16485,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="150"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="153"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -16512,7 +16509,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="154"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -16524,7 +16521,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="154"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -16536,7 +16533,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="154"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -16548,7 +16545,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="154"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -16560,7 +16557,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="154"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -16572,7 +16569,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="154"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -16586,7 +16583,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="150"/>
+      <c r="J14" s="146"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="147" t="s">
@@ -16594,7 +16591,7 @@
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="74"/>
-      <c r="D15" s="155" t="s">
+      <c r="D15" s="145" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="73"/>
@@ -16626,14 +16623,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="156" t="s">
+      <c r="H16" s="148" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="73"/>
-      <c r="J16" s="150"/>
+      <c r="J16" s="146"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="146">
+      <c r="A17" s="144">
         <v>1</v>
       </c>
       <c r="B17" s="73"/>
@@ -16650,83 +16647,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="155" t="s">
+      <c r="H17" s="145" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="73"/>
-      <c r="J17" s="150"/>
+      <c r="J17" s="146"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="146"/>
+      <c r="A18" s="144"/>
       <c r="B18" s="73"/>
       <c r="C18" s="74"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="155"/>
+      <c r="H18" s="145"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="150"/>
+      <c r="J18" s="146"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="146"/>
+      <c r="A19" s="144"/>
       <c r="B19" s="73"/>
       <c r="C19" s="74"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="155"/>
+      <c r="H19" s="145"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="150"/>
+      <c r="J19" s="146"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="146"/>
+      <c r="A20" s="144"/>
       <c r="B20" s="73"/>
       <c r="C20" s="74"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="155"/>
+      <c r="H20" s="145"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="150"/>
+      <c r="J20" s="146"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="146"/>
+      <c r="A21" s="144"/>
       <c r="B21" s="73"/>
       <c r="C21" s="74"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="155"/>
+      <c r="H21" s="145"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="150"/>
+      <c r="J21" s="146"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="146"/>
+      <c r="A22" s="144"/>
       <c r="B22" s="73"/>
       <c r="C22" s="74"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="155"/>
+      <c r="H22" s="145"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="150"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="160"/>
-      <c r="B23" s="158"/>
-      <c r="C23" s="161"/>
+      <c r="A23" s="149"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="151"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="158"/>
-      <c r="J23" s="159"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -17707,22 +17704,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -17738,6 +17719,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -17757,7 +17754,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="178" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="131"/>
@@ -17768,14 +17765,14 @@
       <c r="G1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
       <c r="J1" s="139"/>
       <c r="K1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
+      <c r="L1" s="155"/>
+      <c r="M1" s="155"/>
       <c r="N1" s="139"/>
       <c r="O1" s="138" t="s">
         <v>8</v>
@@ -17788,7 +17785,7 @@
       <c r="S1" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="149"/>
+      <c r="T1" s="157"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="133"/>
@@ -17800,16 +17797,16 @@
       <c r="G2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
       <c r="J2" s="141"/>
       <c r="K2" s="140" t="s">
         <v>93</v>
       </c>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
       <c r="N2" s="141"/>
-      <c r="O2" s="169">
+      <c r="O2" s="176">
         <v>45821</v>
       </c>
       <c r="P2" s="141"/>
@@ -17818,7 +17815,7 @@
       </c>
       <c r="R2" s="141"/>
       <c r="S2" s="140"/>
-      <c r="T2" s="153"/>
+      <c r="T2" s="160"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="133"/>
@@ -17840,7 +17837,7 @@
       <c r="Q3" s="142"/>
       <c r="R3" s="134"/>
       <c r="S3" s="142"/>
-      <c r="T3" s="154"/>
+      <c r="T3" s="161"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="135"/>
@@ -17862,33 +17859,33 @@
       <c r="Q4" s="143"/>
       <c r="R4" s="137"/>
       <c r="S4" s="143"/>
-      <c r="T4" s="170"/>
+      <c r="T4" s="177"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="145"/>
+      <c r="B5" s="155"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
       <c r="F5" s="139"/>
-      <c r="G5" s="172" t="s">
+      <c r="G5" s="168" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="145"/>
-      <c r="K5" s="145"/>
-      <c r="L5" s="145"/>
-      <c r="M5" s="145"/>
-      <c r="N5" s="145"/>
-      <c r="O5" s="145"/>
-      <c r="P5" s="145"/>
-      <c r="Q5" s="145"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="145"/>
-      <c r="T5" s="149"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="155"/>
+      <c r="Q5" s="155"/>
+      <c r="R5" s="155"/>
+      <c r="S5" s="155"/>
+      <c r="T5" s="157"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -17899,7 +17896,7 @@
       <c r="D6" s="73"/>
       <c r="E6" s="73"/>
       <c r="F6" s="74"/>
-      <c r="G6" s="155" t="s">
+      <c r="G6" s="145" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="73"/>
@@ -17914,7 +17911,7 @@
       <c r="Q6" s="73"/>
       <c r="R6" s="73"/>
       <c r="S6" s="73"/>
-      <c r="T6" s="150"/>
+      <c r="T6" s="146"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="147" t="s">
@@ -17925,7 +17922,7 @@
       <c r="D7" s="73"/>
       <c r="E7" s="73"/>
       <c r="F7" s="74"/>
-      <c r="G7" s="155" t="s">
+      <c r="G7" s="145" t="s">
         <v>95</v>
       </c>
       <c r="H7" s="73"/>
@@ -17940,7 +17937,7 @@
       <c r="Q7" s="73"/>
       <c r="R7" s="73"/>
       <c r="S7" s="73"/>
-      <c r="T7" s="150"/>
+      <c r="T7" s="146"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -18143,29 +18140,29 @@
         <v>45</v>
       </c>
       <c r="B15" s="74"/>
-      <c r="C15" s="178" t="s">
+      <c r="C15" s="175" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="74"/>
-      <c r="E15" s="156" t="s">
+      <c r="E15" s="148" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="74"/>
-      <c r="G15" s="156" t="s">
+      <c r="G15" s="148" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="73"/>
       <c r="I15" s="74"/>
-      <c r="J15" s="156" t="s">
+      <c r="J15" s="148" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="74"/>
-      <c r="L15" s="156" t="s">
+      <c r="L15" s="148" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="73"/>
       <c r="N15" s="74"/>
-      <c r="O15" s="156" t="s">
+      <c r="O15" s="148" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="73"/>
@@ -18181,27 +18178,27 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A16" s="179">
+      <c r="A16" s="162">
         <v>1</v>
       </c>
       <c r="B16" s="74"/>
-      <c r="C16" s="180" t="s">
+      <c r="C16" s="163" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="74"/>
-      <c r="E16" s="180" t="s">
+      <c r="E16" s="163" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="74"/>
-      <c r="G16" s="162" t="s">
+      <c r="G16" s="180" t="s">
         <v>96</v>
       </c>
       <c r="H16" s="73"/>
       <c r="I16" s="74"/>
-      <c r="J16" s="163" t="s">
+      <c r="J16" s="171" t="s">
         <v>97</v>
       </c>
-      <c r="K16" s="164"/>
+      <c r="K16" s="169"/>
       <c r="L16" s="166" t="s">
         <v>98</v>
       </c>
@@ -18223,24 +18220,24 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A17" s="179">
+      <c r="A17" s="162">
         <v>2</v>
       </c>
       <c r="B17" s="74"/>
-      <c r="C17" s="180" t="s">
+      <c r="C17" s="163" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="74"/>
-      <c r="E17" s="180" t="s">
+      <c r="E17" s="163" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="74"/>
-      <c r="G17" s="162" t="s">
+      <c r="G17" s="180" t="s">
         <v>105</v>
       </c>
       <c r="H17" s="73"/>
       <c r="I17" s="74"/>
-      <c r="J17" s="162" t="s">
+      <c r="J17" s="180" t="s">
         <v>106</v>
       </c>
       <c r="K17" s="74"/>
@@ -18265,28 +18262,28 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="64.5" customHeight="1">
-      <c r="A18" s="179">
+      <c r="A18" s="162">
         <v>3</v>
       </c>
       <c r="B18" s="74"/>
-      <c r="C18" s="180" t="s">
+      <c r="C18" s="163" t="s">
         <v>54</v>
       </c>
       <c r="D18" s="74"/>
-      <c r="E18" s="180" t="s">
+      <c r="E18" s="163" t="s">
         <v>100</v>
       </c>
       <c r="F18" s="74"/>
-      <c r="G18" s="162" t="s">
+      <c r="G18" s="180" t="s">
         <v>101</v>
       </c>
       <c r="H18" s="73"/>
       <c r="I18" s="74"/>
-      <c r="J18" s="162" t="s">
+      <c r="J18" s="180" t="s">
         <v>103</v>
       </c>
       <c r="K18" s="74"/>
-      <c r="L18" s="168" t="s">
+      <c r="L18" s="179" t="s">
         <v>104</v>
       </c>
       <c r="M18" s="73"/>
@@ -18307,24 +18304,24 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="61.5" customHeight="1">
-      <c r="A19" s="179">
+      <c r="A19" s="162">
         <v>4</v>
       </c>
       <c r="B19" s="74"/>
-      <c r="C19" s="180" t="s">
+      <c r="C19" s="163" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="74"/>
-      <c r="E19" s="180" t="s">
+      <c r="E19" s="163" t="s">
         <v>100</v>
       </c>
       <c r="F19" s="74"/>
-      <c r="G19" s="162" t="s">
+      <c r="G19" s="180" t="s">
         <v>139</v>
       </c>
       <c r="H19" s="73"/>
       <c r="I19" s="74"/>
-      <c r="J19" s="162" t="s">
+      <c r="J19" s="180" t="s">
         <v>97</v>
       </c>
       <c r="K19" s="74"/>
@@ -18349,32 +18346,32 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A20" s="173">
-        <v>7</v>
-      </c>
-      <c r="B20" s="164"/>
-      <c r="C20" s="174" t="s">
+      <c r="A20" s="162">
+        <v>5</v>
+      </c>
+      <c r="B20" s="74"/>
+      <c r="C20" s="170" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="164"/>
-      <c r="E20" s="174" t="s">
+      <c r="D20" s="169"/>
+      <c r="E20" s="170" t="s">
         <v>141</v>
       </c>
-      <c r="F20" s="164"/>
-      <c r="G20" s="163" t="s">
+      <c r="F20" s="169"/>
+      <c r="G20" s="171" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="175"/>
-      <c r="I20" s="164"/>
-      <c r="J20" s="163" t="s">
+      <c r="H20" s="172"/>
+      <c r="I20" s="169"/>
+      <c r="J20" s="171" t="s">
         <v>143</v>
       </c>
-      <c r="K20" s="164"/>
-      <c r="L20" s="176" t="s">
+      <c r="K20" s="169"/>
+      <c r="L20" s="173" t="s">
         <v>144</v>
       </c>
-      <c r="M20" s="177"/>
-      <c r="N20" s="177"/>
+      <c r="M20" s="174"/>
+      <c r="N20" s="174"/>
       <c r="O20" s="166" t="s">
         <v>145</v>
       </c>
@@ -18391,16 +18388,16 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="179"/>
+      <c r="A21" s="162"/>
       <c r="B21" s="74"/>
-      <c r="C21" s="180"/>
+      <c r="C21" s="163"/>
       <c r="D21" s="74"/>
-      <c r="E21" s="180"/>
+      <c r="E21" s="163"/>
       <c r="F21" s="74"/>
-      <c r="G21" s="162"/>
+      <c r="G21" s="180"/>
       <c r="H21" s="73"/>
       <c r="I21" s="74"/>
-      <c r="J21" s="162"/>
+      <c r="J21" s="180"/>
       <c r="K21" s="74"/>
       <c r="L21" s="166"/>
       <c r="M21" s="73"/>
@@ -18419,16 +18416,16 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="179"/>
+      <c r="A22" s="162"/>
       <c r="B22" s="74"/>
-      <c r="C22" s="180"/>
+      <c r="C22" s="163"/>
       <c r="D22" s="74"/>
-      <c r="E22" s="180"/>
+      <c r="E22" s="163"/>
       <c r="F22" s="74"/>
-      <c r="G22" s="162"/>
+      <c r="G22" s="180"/>
       <c r="H22" s="73"/>
       <c r="I22" s="74"/>
-      <c r="J22" s="162"/>
+      <c r="J22" s="180"/>
       <c r="K22" s="74"/>
       <c r="L22" s="166"/>
       <c r="M22" s="73"/>
@@ -18447,16 +18444,16 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="179"/>
+      <c r="A23" s="162"/>
       <c r="B23" s="74"/>
-      <c r="C23" s="180"/>
+      <c r="C23" s="163"/>
       <c r="D23" s="74"/>
-      <c r="E23" s="180"/>
+      <c r="E23" s="163"/>
       <c r="F23" s="74"/>
-      <c r="G23" s="162"/>
+      <c r="G23" s="180"/>
       <c r="H23" s="73"/>
       <c r="I23" s="74"/>
-      <c r="J23" s="162"/>
+      <c r="J23" s="180"/>
       <c r="K23" s="74"/>
       <c r="L23" s="166"/>
       <c r="M23" s="73"/>
@@ -18475,16 +18472,16 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="179"/>
+      <c r="A24" s="162"/>
       <c r="B24" s="74"/>
-      <c r="C24" s="180"/>
+      <c r="C24" s="163"/>
       <c r="D24" s="74"/>
-      <c r="E24" s="180"/>
+      <c r="E24" s="163"/>
       <c r="F24" s="74"/>
-      <c r="G24" s="162"/>
+      <c r="G24" s="180"/>
       <c r="H24" s="73"/>
       <c r="I24" s="74"/>
-      <c r="J24" s="162"/>
+      <c r="J24" s="180"/>
       <c r="K24" s="74"/>
       <c r="L24" s="166"/>
       <c r="M24" s="73"/>
@@ -18503,16 +18500,16 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="179"/>
+      <c r="A25" s="162"/>
       <c r="B25" s="74"/>
-      <c r="C25" s="180"/>
+      <c r="C25" s="163"/>
       <c r="D25" s="74"/>
-      <c r="E25" s="180"/>
+      <c r="E25" s="163"/>
       <c r="F25" s="74"/>
-      <c r="G25" s="162"/>
+      <c r="G25" s="180"/>
       <c r="H25" s="73"/>
       <c r="I25" s="74"/>
-      <c r="J25" s="162"/>
+      <c r="J25" s="180"/>
       <c r="K25" s="74"/>
       <c r="L25" s="166"/>
       <c r="M25" s="73"/>
@@ -18531,16 +18528,16 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="179"/>
+      <c r="A26" s="162"/>
       <c r="B26" s="74"/>
-      <c r="C26" s="180"/>
+      <c r="C26" s="163"/>
       <c r="D26" s="74"/>
-      <c r="E26" s="180"/>
+      <c r="E26" s="163"/>
       <c r="F26" s="74"/>
-      <c r="G26" s="162"/>
+      <c r="G26" s="180"/>
       <c r="H26" s="73"/>
       <c r="I26" s="74"/>
-      <c r="J26" s="162"/>
+      <c r="J26" s="180"/>
       <c r="K26" s="74"/>
       <c r="L26" s="166"/>
       <c r="M26" s="73"/>
@@ -18559,16 +18556,16 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="179"/>
+      <c r="A27" s="162"/>
       <c r="B27" s="74"/>
-      <c r="C27" s="180"/>
+      <c r="C27" s="163"/>
       <c r="D27" s="74"/>
-      <c r="E27" s="180"/>
+      <c r="E27" s="163"/>
       <c r="F27" s="74"/>
-      <c r="G27" s="162"/>
+      <c r="G27" s="180"/>
       <c r="H27" s="73"/>
       <c r="I27" s="74"/>
-      <c r="J27" s="162"/>
+      <c r="J27" s="180"/>
       <c r="K27" s="74"/>
       <c r="L27" s="166"/>
       <c r="M27" s="73"/>
@@ -18587,16 +18584,16 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="179"/>
+      <c r="A28" s="162"/>
       <c r="B28" s="74"/>
-      <c r="C28" s="180"/>
+      <c r="C28" s="163"/>
       <c r="D28" s="74"/>
-      <c r="E28" s="180"/>
+      <c r="E28" s="163"/>
       <c r="F28" s="74"/>
-      <c r="G28" s="162"/>
+      <c r="G28" s="180"/>
       <c r="H28" s="73"/>
       <c r="I28" s="74"/>
-      <c r="J28" s="162"/>
+      <c r="J28" s="180"/>
       <c r="K28" s="74"/>
       <c r="L28" s="166"/>
       <c r="M28" s="73"/>
@@ -18615,16 +18612,16 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="179"/>
+      <c r="A29" s="162"/>
       <c r="B29" s="74"/>
-      <c r="C29" s="180"/>
+      <c r="C29" s="163"/>
       <c r="D29" s="74"/>
-      <c r="E29" s="180"/>
+      <c r="E29" s="163"/>
       <c r="F29" s="74"/>
-      <c r="G29" s="162"/>
+      <c r="G29" s="180"/>
       <c r="H29" s="73"/>
       <c r="I29" s="74"/>
-      <c r="J29" s="162"/>
+      <c r="J29" s="180"/>
       <c r="K29" s="74"/>
       <c r="L29" s="166"/>
       <c r="M29" s="73"/>
@@ -18643,16 +18640,16 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="179"/>
+      <c r="A30" s="162"/>
       <c r="B30" s="74"/>
-      <c r="C30" s="180"/>
+      <c r="C30" s="163"/>
       <c r="D30" s="74"/>
-      <c r="E30" s="180"/>
+      <c r="E30" s="163"/>
       <c r="F30" s="74"/>
-      <c r="G30" s="162"/>
+      <c r="G30" s="180"/>
       <c r="H30" s="73"/>
       <c r="I30" s="74"/>
-      <c r="J30" s="162"/>
+      <c r="J30" s="180"/>
       <c r="K30" s="74"/>
       <c r="L30" s="166"/>
       <c r="M30" s="73"/>
@@ -18671,23 +18668,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="181"/>
-      <c r="B31" s="161"/>
-      <c r="C31" s="182"/>
-      <c r="D31" s="161"/>
-      <c r="E31" s="182"/>
-      <c r="F31" s="161"/>
-      <c r="G31" s="165"/>
-      <c r="H31" s="158"/>
-      <c r="I31" s="161"/>
-      <c r="J31" s="165"/>
-      <c r="K31" s="161"/>
+      <c r="A31" s="164"/>
+      <c r="B31" s="151"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="151"/>
+      <c r="E31" s="165"/>
+      <c r="F31" s="151"/>
+      <c r="G31" s="181"/>
+      <c r="H31" s="150"/>
+      <c r="I31" s="151"/>
+      <c r="J31" s="181"/>
+      <c r="K31" s="151"/>
       <c r="L31" s="167"/>
-      <c r="M31" s="158"/>
-      <c r="N31" s="161"/>
+      <c r="M31" s="150"/>
+      <c r="N31" s="151"/>
       <c r="O31" s="167"/>
-      <c r="P31" s="158"/>
-      <c r="Q31" s="161"/>
+      <c r="P31" s="150"/>
+      <c r="Q31" s="151"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -19685,6 +19682,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -19709,118 +19818,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
@@ -19847,70 +19844,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="191" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="201" t="s">
+      <c r="B1" s="191"/>
+      <c r="C1" s="192" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="202"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="204" t="s">
+      <c r="D1" s="193"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="195" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="205"/>
-      <c r="H1" s="205"/>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
-      <c r="K1" s="205"/>
-      <c r="L1" s="205"/>
-      <c r="M1" s="206"/>
+      <c r="G1" s="196"/>
+      <c r="H1" s="196"/>
+      <c r="I1" s="196"/>
+      <c r="J1" s="196"/>
+      <c r="K1" s="196"/>
+      <c r="L1" s="196"/>
+      <c r="M1" s="197"/>
       <c r="N1" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="204" t="s">
+      <c r="O1" s="195" t="s">
         <v>94</v>
       </c>
-      <c r="P1" s="206"/>
+      <c r="P1" s="197"/>
       <c r="Q1" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="204" t="s">
+      <c r="R1" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="206"/>
+      <c r="S1" s="197"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="200"/>
-      <c r="B2" s="200"/>
-      <c r="C2" s="201" t="s">
+      <c r="A2" s="191"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="192" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="202"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="204" t="s">
+      <c r="D2" s="193"/>
+      <c r="E2" s="194"/>
+      <c r="F2" s="195" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="205"/>
-      <c r="H2" s="205"/>
-      <c r="I2" s="205"/>
-      <c r="J2" s="205"/>
-      <c r="K2" s="205"/>
-      <c r="L2" s="205"/>
-      <c r="M2" s="206"/>
+      <c r="G2" s="196"/>
+      <c r="H2" s="196"/>
+      <c r="I2" s="196"/>
+      <c r="J2" s="196"/>
+      <c r="K2" s="196"/>
+      <c r="L2" s="196"/>
+      <c r="M2" s="197"/>
       <c r="N2" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="O2" s="207">
+      <c r="O2" s="198">
         <v>45824</v>
       </c>
-      <c r="P2" s="208"/>
+      <c r="P2" s="199"/>
       <c r="Q2" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="R2" s="209"/>
-      <c r="S2" s="210"/>
+      <c r="R2" s="200"/>
+      <c r="S2" s="201"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="43"/>
@@ -19940,33 +19937,33 @@
       <c r="B4" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="182" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="196"/>
-      <c r="E4" s="196"/>
-      <c r="F4" s="196"/>
-      <c r="G4" s="197"/>
-      <c r="H4" s="195" t="s">
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="184"/>
+      <c r="H4" s="182" t="s">
         <v>119</v>
       </c>
-      <c r="I4" s="196"/>
-      <c r="J4" s="196"/>
-      <c r="K4" s="196"/>
-      <c r="L4" s="196"/>
-      <c r="M4" s="197"/>
-      <c r="N4" s="195" t="s">
+      <c r="I4" s="183"/>
+      <c r="J4" s="183"/>
+      <c r="K4" s="183"/>
+      <c r="L4" s="183"/>
+      <c r="M4" s="184"/>
+      <c r="N4" s="182" t="s">
         <v>120</v>
       </c>
-      <c r="O4" s="196"/>
-      <c r="P4" s="197"/>
+      <c r="O4" s="183"/>
+      <c r="P4" s="184"/>
       <c r="Q4" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="R4" s="195" t="s">
+      <c r="R4" s="182" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="197"/>
+      <c r="S4" s="184"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="47">
@@ -19975,29 +19972,29 @@
       <c r="B5" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="191" t="s">
+      <c r="C5" s="185" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="191"/>
-      <c r="E5" s="191"/>
-      <c r="F5" s="191"/>
-      <c r="G5" s="191"/>
-      <c r="H5" s="191" t="s">
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="185" t="s">
         <v>135</v>
       </c>
-      <c r="I5" s="191"/>
-      <c r="J5" s="191"/>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="191"/>
-      <c r="N5" s="192" t="s">
+      <c r="I5" s="185"/>
+      <c r="J5" s="185"/>
+      <c r="K5" s="185"/>
+      <c r="L5" s="185"/>
+      <c r="M5" s="185"/>
+      <c r="N5" s="186" t="s">
         <v>136</v>
       </c>
-      <c r="O5" s="193"/>
-      <c r="P5" s="194"/>
+      <c r="O5" s="187"/>
+      <c r="P5" s="188"/>
       <c r="Q5" s="47"/>
-      <c r="R5" s="198"/>
-      <c r="S5" s="199"/>
+      <c r="R5" s="189"/>
+      <c r="S5" s="190"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="49">
@@ -20006,998 +20003,1186 @@
       <c r="B6" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="191" t="s">
+      <c r="C6" s="185" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="191"/>
-      <c r="E6" s="191"/>
-      <c r="F6" s="191"/>
-      <c r="G6" s="191"/>
-      <c r="H6" s="191" t="s">
+      <c r="D6" s="185"/>
+      <c r="E6" s="185"/>
+      <c r="F6" s="185"/>
+      <c r="G6" s="185"/>
+      <c r="H6" s="185" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="191"/>
-      <c r="J6" s="191"/>
-      <c r="K6" s="191"/>
-      <c r="L6" s="191"/>
-      <c r="M6" s="191"/>
-      <c r="N6" s="192" t="s">
+      <c r="I6" s="185"/>
+      <c r="J6" s="185"/>
+      <c r="K6" s="185"/>
+      <c r="L6" s="185"/>
+      <c r="M6" s="185"/>
+      <c r="N6" s="186" t="s">
         <v>137</v>
       </c>
-      <c r="O6" s="193"/>
-      <c r="P6" s="194"/>
+      <c r="O6" s="187"/>
+      <c r="P6" s="188"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="190"/>
-      <c r="S6" s="190"/>
+      <c r="R6" s="206"/>
+      <c r="S6" s="206"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="49"/>
       <c r="B7" s="49"/>
-      <c r="C7" s="183"/>
-      <c r="D7" s="183"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="183"/>
-      <c r="G7" s="183"/>
-      <c r="H7" s="183"/>
-      <c r="I7" s="183"/>
-      <c r="J7" s="183"/>
-      <c r="K7" s="183"/>
-      <c r="L7" s="183"/>
-      <c r="M7" s="183"/>
-      <c r="N7" s="187"/>
-      <c r="O7" s="188"/>
-      <c r="P7" s="189"/>
+      <c r="C7" s="202"/>
+      <c r="D7" s="202"/>
+      <c r="E7" s="202"/>
+      <c r="F7" s="202"/>
+      <c r="G7" s="202"/>
+      <c r="H7" s="202"/>
+      <c r="I7" s="202"/>
+      <c r="J7" s="202"/>
+      <c r="K7" s="202"/>
+      <c r="L7" s="202"/>
+      <c r="M7" s="202"/>
+      <c r="N7" s="203"/>
+      <c r="O7" s="204"/>
+      <c r="P7" s="205"/>
       <c r="Q7" s="51"/>
-      <c r="R7" s="190"/>
-      <c r="S7" s="190"/>
+      <c r="R7" s="206"/>
+      <c r="S7" s="206"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="49"/>
       <c r="B8" s="49"/>
-      <c r="C8" s="183"/>
-      <c r="D8" s="183"/>
-      <c r="E8" s="183"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="183"/>
-      <c r="H8" s="183"/>
-      <c r="I8" s="183"/>
-      <c r="J8" s="183"/>
-      <c r="K8" s="183"/>
-      <c r="L8" s="183"/>
-      <c r="M8" s="183"/>
-      <c r="N8" s="187"/>
-      <c r="O8" s="188"/>
-      <c r="P8" s="189"/>
+      <c r="C8" s="202"/>
+      <c r="D8" s="202"/>
+      <c r="E8" s="202"/>
+      <c r="F8" s="202"/>
+      <c r="G8" s="202"/>
+      <c r="H8" s="202"/>
+      <c r="I8" s="202"/>
+      <c r="J8" s="202"/>
+      <c r="K8" s="202"/>
+      <c r="L8" s="202"/>
+      <c r="M8" s="202"/>
+      <c r="N8" s="203"/>
+      <c r="O8" s="204"/>
+      <c r="P8" s="205"/>
       <c r="Q8" s="51"/>
-      <c r="R8" s="190"/>
-      <c r="S8" s="190"/>
+      <c r="R8" s="206"/>
+      <c r="S8" s="206"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="49"/>
       <c r="B9" s="49"/>
-      <c r="C9" s="183"/>
-      <c r="D9" s="183"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="183"/>
-      <c r="G9" s="183"/>
-      <c r="H9" s="183"/>
-      <c r="I9" s="183"/>
-      <c r="J9" s="183"/>
-      <c r="K9" s="183"/>
-      <c r="L9" s="183"/>
-      <c r="M9" s="183"/>
-      <c r="N9" s="187"/>
-      <c r="O9" s="188"/>
-      <c r="P9" s="189"/>
+      <c r="C9" s="202"/>
+      <c r="D9" s="202"/>
+      <c r="E9" s="202"/>
+      <c r="F9" s="202"/>
+      <c r="G9" s="202"/>
+      <c r="H9" s="202"/>
+      <c r="I9" s="202"/>
+      <c r="J9" s="202"/>
+      <c r="K9" s="202"/>
+      <c r="L9" s="202"/>
+      <c r="M9" s="202"/>
+      <c r="N9" s="203"/>
+      <c r="O9" s="204"/>
+      <c r="P9" s="205"/>
       <c r="Q9" s="49"/>
-      <c r="R9" s="190"/>
-      <c r="S9" s="190"/>
+      <c r="R9" s="206"/>
+      <c r="S9" s="206"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="49"/>
       <c r="B10" s="49"/>
-      <c r="C10" s="183"/>
-      <c r="D10" s="183"/>
-      <c r="E10" s="183"/>
-      <c r="F10" s="183"/>
-      <c r="G10" s="183"/>
-      <c r="H10" s="184"/>
-      <c r="I10" s="185"/>
-      <c r="J10" s="185"/>
-      <c r="K10" s="185"/>
-      <c r="L10" s="185"/>
-      <c r="M10" s="186"/>
-      <c r="N10" s="187"/>
-      <c r="O10" s="188"/>
-      <c r="P10" s="189"/>
+      <c r="C10" s="202"/>
+      <c r="D10" s="202"/>
+      <c r="E10" s="202"/>
+      <c r="F10" s="202"/>
+      <c r="G10" s="202"/>
+      <c r="H10" s="207"/>
+      <c r="I10" s="208"/>
+      <c r="J10" s="208"/>
+      <c r="K10" s="208"/>
+      <c r="L10" s="208"/>
+      <c r="M10" s="209"/>
+      <c r="N10" s="203"/>
+      <c r="O10" s="204"/>
+      <c r="P10" s="205"/>
       <c r="Q10" s="51"/>
-      <c r="R10" s="190"/>
-      <c r="S10" s="190"/>
+      <c r="R10" s="206"/>
+      <c r="S10" s="206"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="49"/>
       <c r="B11" s="49"/>
-      <c r="C11" s="183"/>
-      <c r="D11" s="183"/>
-      <c r="E11" s="183"/>
-      <c r="F11" s="183"/>
-      <c r="G11" s="183"/>
-      <c r="H11" s="184"/>
-      <c r="I11" s="185"/>
-      <c r="J11" s="185"/>
-      <c r="K11" s="185"/>
-      <c r="L11" s="185"/>
-      <c r="M11" s="186"/>
-      <c r="N11" s="187"/>
-      <c r="O11" s="188"/>
-      <c r="P11" s="189"/>
+      <c r="C11" s="202"/>
+      <c r="D11" s="202"/>
+      <c r="E11" s="202"/>
+      <c r="F11" s="202"/>
+      <c r="G11" s="202"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="208"/>
+      <c r="J11" s="208"/>
+      <c r="K11" s="208"/>
+      <c r="L11" s="208"/>
+      <c r="M11" s="209"/>
+      <c r="N11" s="203"/>
+      <c r="O11" s="204"/>
+      <c r="P11" s="205"/>
       <c r="Q11" s="49"/>
-      <c r="R11" s="190"/>
-      <c r="S11" s="190"/>
+      <c r="R11" s="206"/>
+      <c r="S11" s="206"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="49"/>
       <c r="B12" s="49"/>
-      <c r="C12" s="183"/>
-      <c r="D12" s="183"/>
-      <c r="E12" s="183"/>
-      <c r="F12" s="183"/>
-      <c r="G12" s="183"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="185"/>
-      <c r="L12" s="185"/>
-      <c r="M12" s="186"/>
-      <c r="N12" s="187"/>
-      <c r="O12" s="188"/>
-      <c r="P12" s="189"/>
+      <c r="C12" s="202"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="202"/>
+      <c r="G12" s="202"/>
+      <c r="H12" s="207"/>
+      <c r="I12" s="208"/>
+      <c r="J12" s="208"/>
+      <c r="K12" s="208"/>
+      <c r="L12" s="208"/>
+      <c r="M12" s="209"/>
+      <c r="N12" s="203"/>
+      <c r="O12" s="204"/>
+      <c r="P12" s="205"/>
       <c r="Q12" s="49"/>
-      <c r="R12" s="190"/>
-      <c r="S12" s="190"/>
+      <c r="R12" s="206"/>
+      <c r="S12" s="206"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="49"/>
       <c r="B13" s="49"/>
-      <c r="C13" s="183"/>
-      <c r="D13" s="183"/>
-      <c r="E13" s="183"/>
-      <c r="F13" s="183"/>
-      <c r="G13" s="183"/>
-      <c r="H13" s="184"/>
-      <c r="I13" s="185"/>
-      <c r="J13" s="185"/>
-      <c r="K13" s="185"/>
-      <c r="L13" s="185"/>
-      <c r="M13" s="186"/>
-      <c r="N13" s="187"/>
-      <c r="O13" s="188"/>
-      <c r="P13" s="189"/>
+      <c r="C13" s="202"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="202"/>
+      <c r="F13" s="202"/>
+      <c r="G13" s="202"/>
+      <c r="H13" s="207"/>
+      <c r="I13" s="208"/>
+      <c r="J13" s="208"/>
+      <c r="K13" s="208"/>
+      <c r="L13" s="208"/>
+      <c r="M13" s="209"/>
+      <c r="N13" s="203"/>
+      <c r="O13" s="204"/>
+      <c r="P13" s="205"/>
       <c r="Q13" s="49"/>
-      <c r="R13" s="190"/>
-      <c r="S13" s="190"/>
+      <c r="R13" s="206"/>
+      <c r="S13" s="206"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="49"/>
       <c r="B14" s="49"/>
-      <c r="C14" s="183"/>
-      <c r="D14" s="183"/>
-      <c r="E14" s="183"/>
-      <c r="F14" s="183"/>
-      <c r="G14" s="183"/>
-      <c r="H14" s="184"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="185"/>
-      <c r="K14" s="185"/>
-      <c r="L14" s="185"/>
-      <c r="M14" s="186"/>
-      <c r="N14" s="187"/>
-      <c r="O14" s="188"/>
-      <c r="P14" s="189"/>
+      <c r="C14" s="202"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="202"/>
+      <c r="F14" s="202"/>
+      <c r="G14" s="202"/>
+      <c r="H14" s="207"/>
+      <c r="I14" s="208"/>
+      <c r="J14" s="208"/>
+      <c r="K14" s="208"/>
+      <c r="L14" s="208"/>
+      <c r="M14" s="209"/>
+      <c r="N14" s="203"/>
+      <c r="O14" s="204"/>
+      <c r="P14" s="205"/>
       <c r="Q14" s="49"/>
-      <c r="R14" s="190"/>
-      <c r="S14" s="190"/>
+      <c r="R14" s="206"/>
+      <c r="S14" s="206"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="49"/>
       <c r="B15" s="49"/>
-      <c r="C15" s="183"/>
-      <c r="D15" s="183"/>
-      <c r="E15" s="183"/>
-      <c r="F15" s="183"/>
-      <c r="G15" s="183"/>
-      <c r="H15" s="184"/>
-      <c r="I15" s="185"/>
-      <c r="J15" s="185"/>
-      <c r="K15" s="185"/>
-      <c r="L15" s="185"/>
-      <c r="M15" s="186"/>
-      <c r="N15" s="187"/>
-      <c r="O15" s="188"/>
-      <c r="P15" s="189"/>
+      <c r="C15" s="202"/>
+      <c r="D15" s="202"/>
+      <c r="E15" s="202"/>
+      <c r="F15" s="202"/>
+      <c r="G15" s="202"/>
+      <c r="H15" s="207"/>
+      <c r="I15" s="208"/>
+      <c r="J15" s="208"/>
+      <c r="K15" s="208"/>
+      <c r="L15" s="208"/>
+      <c r="M15" s="209"/>
+      <c r="N15" s="203"/>
+      <c r="O15" s="204"/>
+      <c r="P15" s="205"/>
       <c r="Q15" s="49"/>
-      <c r="R15" s="190"/>
-      <c r="S15" s="190"/>
+      <c r="R15" s="206"/>
+      <c r="S15" s="206"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="49"/>
       <c r="B16" s="49"/>
-      <c r="C16" s="183"/>
-      <c r="D16" s="183"/>
-      <c r="E16" s="183"/>
-      <c r="F16" s="183"/>
-      <c r="G16" s="183"/>
-      <c r="H16" s="184"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="185"/>
-      <c r="K16" s="185"/>
-      <c r="L16" s="185"/>
-      <c r="M16" s="186"/>
-      <c r="N16" s="187"/>
-      <c r="O16" s="188"/>
-      <c r="P16" s="189"/>
+      <c r="C16" s="202"/>
+      <c r="D16" s="202"/>
+      <c r="E16" s="202"/>
+      <c r="F16" s="202"/>
+      <c r="G16" s="202"/>
+      <c r="H16" s="207"/>
+      <c r="I16" s="208"/>
+      <c r="J16" s="208"/>
+      <c r="K16" s="208"/>
+      <c r="L16" s="208"/>
+      <c r="M16" s="209"/>
+      <c r="N16" s="203"/>
+      <c r="O16" s="204"/>
+      <c r="P16" s="205"/>
       <c r="Q16" s="49"/>
-      <c r="R16" s="190"/>
-      <c r="S16" s="190"/>
+      <c r="R16" s="206"/>
+      <c r="S16" s="206"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="49"/>
       <c r="B17" s="49"/>
-      <c r="C17" s="183"/>
-      <c r="D17" s="183"/>
-      <c r="E17" s="183"/>
-      <c r="F17" s="183"/>
-      <c r="G17" s="183"/>
-      <c r="H17" s="184"/>
-      <c r="I17" s="185"/>
-      <c r="J17" s="185"/>
-      <c r="K17" s="185"/>
-      <c r="L17" s="185"/>
-      <c r="M17" s="186"/>
-      <c r="N17" s="187"/>
-      <c r="O17" s="188"/>
-      <c r="P17" s="189"/>
+      <c r="C17" s="202"/>
+      <c r="D17" s="202"/>
+      <c r="E17" s="202"/>
+      <c r="F17" s="202"/>
+      <c r="G17" s="202"/>
+      <c r="H17" s="207"/>
+      <c r="I17" s="208"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="208"/>
+      <c r="L17" s="208"/>
+      <c r="M17" s="209"/>
+      <c r="N17" s="203"/>
+      <c r="O17" s="204"/>
+      <c r="P17" s="205"/>
       <c r="Q17" s="49"/>
-      <c r="R17" s="190"/>
-      <c r="S17" s="190"/>
+      <c r="R17" s="206"/>
+      <c r="S17" s="206"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="49"/>
       <c r="B18" s="49"/>
-      <c r="C18" s="183"/>
-      <c r="D18" s="183"/>
-      <c r="E18" s="183"/>
-      <c r="F18" s="183"/>
-      <c r="G18" s="183"/>
-      <c r="H18" s="184"/>
-      <c r="I18" s="185"/>
-      <c r="J18" s="185"/>
-      <c r="K18" s="185"/>
-      <c r="L18" s="185"/>
-      <c r="M18" s="186"/>
-      <c r="N18" s="187"/>
-      <c r="O18" s="188"/>
-      <c r="P18" s="189"/>
+      <c r="C18" s="202"/>
+      <c r="D18" s="202"/>
+      <c r="E18" s="202"/>
+      <c r="F18" s="202"/>
+      <c r="G18" s="202"/>
+      <c r="H18" s="207"/>
+      <c r="I18" s="208"/>
+      <c r="J18" s="208"/>
+      <c r="K18" s="208"/>
+      <c r="L18" s="208"/>
+      <c r="M18" s="209"/>
+      <c r="N18" s="203"/>
+      <c r="O18" s="204"/>
+      <c r="P18" s="205"/>
       <c r="Q18" s="49"/>
-      <c r="R18" s="190"/>
-      <c r="S18" s="190"/>
+      <c r="R18" s="206"/>
+      <c r="S18" s="206"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="49"/>
       <c r="B19" s="49"/>
-      <c r="C19" s="183"/>
-      <c r="D19" s="183"/>
-      <c r="E19" s="183"/>
-      <c r="F19" s="183"/>
-      <c r="G19" s="183"/>
-      <c r="H19" s="184"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="185"/>
-      <c r="K19" s="185"/>
-      <c r="L19" s="185"/>
-      <c r="M19" s="186"/>
-      <c r="N19" s="187"/>
-      <c r="O19" s="188"/>
-      <c r="P19" s="189"/>
+      <c r="C19" s="202"/>
+      <c r="D19" s="202"/>
+      <c r="E19" s="202"/>
+      <c r="F19" s="202"/>
+      <c r="G19" s="202"/>
+      <c r="H19" s="207"/>
+      <c r="I19" s="208"/>
+      <c r="J19" s="208"/>
+      <c r="K19" s="208"/>
+      <c r="L19" s="208"/>
+      <c r="M19" s="209"/>
+      <c r="N19" s="203"/>
+      <c r="O19" s="204"/>
+      <c r="P19" s="205"/>
       <c r="Q19" s="49"/>
-      <c r="R19" s="190"/>
-      <c r="S19" s="190"/>
+      <c r="R19" s="206"/>
+      <c r="S19" s="206"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="49"/>
       <c r="B20" s="49"/>
-      <c r="C20" s="183"/>
-      <c r="D20" s="183"/>
-      <c r="E20" s="183"/>
-      <c r="F20" s="183"/>
-      <c r="G20" s="183"/>
-      <c r="H20" s="184"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="185"/>
-      <c r="K20" s="185"/>
-      <c r="L20" s="185"/>
-      <c r="M20" s="186"/>
-      <c r="N20" s="187"/>
-      <c r="O20" s="188"/>
-      <c r="P20" s="189"/>
+      <c r="C20" s="202"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="202"/>
+      <c r="F20" s="202"/>
+      <c r="G20" s="202"/>
+      <c r="H20" s="207"/>
+      <c r="I20" s="208"/>
+      <c r="J20" s="208"/>
+      <c r="K20" s="208"/>
+      <c r="L20" s="208"/>
+      <c r="M20" s="209"/>
+      <c r="N20" s="203"/>
+      <c r="O20" s="204"/>
+      <c r="P20" s="205"/>
       <c r="Q20" s="49"/>
-      <c r="R20" s="190"/>
-      <c r="S20" s="190"/>
+      <c r="R20" s="206"/>
+      <c r="S20" s="206"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="49"/>
       <c r="B21" s="49"/>
-      <c r="C21" s="183"/>
-      <c r="D21" s="183"/>
-      <c r="E21" s="183"/>
-      <c r="F21" s="183"/>
-      <c r="G21" s="183"/>
-      <c r="H21" s="184"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="185"/>
-      <c r="K21" s="185"/>
-      <c r="L21" s="185"/>
-      <c r="M21" s="186"/>
-      <c r="N21" s="187"/>
-      <c r="O21" s="188"/>
-      <c r="P21" s="189"/>
+      <c r="C21" s="202"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="202"/>
+      <c r="F21" s="202"/>
+      <c r="G21" s="202"/>
+      <c r="H21" s="207"/>
+      <c r="I21" s="208"/>
+      <c r="J21" s="208"/>
+      <c r="K21" s="208"/>
+      <c r="L21" s="208"/>
+      <c r="M21" s="209"/>
+      <c r="N21" s="203"/>
+      <c r="O21" s="204"/>
+      <c r="P21" s="205"/>
       <c r="Q21" s="49"/>
-      <c r="R21" s="190"/>
-      <c r="S21" s="190"/>
+      <c r="R21" s="206"/>
+      <c r="S21" s="206"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="49"/>
       <c r="B22" s="49"/>
-      <c r="C22" s="183"/>
-      <c r="D22" s="183"/>
-      <c r="E22" s="183"/>
-      <c r="F22" s="183"/>
-      <c r="G22" s="183"/>
-      <c r="H22" s="184"/>
-      <c r="I22" s="185"/>
-      <c r="J22" s="185"/>
-      <c r="K22" s="185"/>
-      <c r="L22" s="185"/>
-      <c r="M22" s="186"/>
-      <c r="N22" s="187"/>
-      <c r="O22" s="188"/>
-      <c r="P22" s="189"/>
+      <c r="C22" s="202"/>
+      <c r="D22" s="202"/>
+      <c r="E22" s="202"/>
+      <c r="F22" s="202"/>
+      <c r="G22" s="202"/>
+      <c r="H22" s="207"/>
+      <c r="I22" s="208"/>
+      <c r="J22" s="208"/>
+      <c r="K22" s="208"/>
+      <c r="L22" s="208"/>
+      <c r="M22" s="209"/>
+      <c r="N22" s="203"/>
+      <c r="O22" s="204"/>
+      <c r="P22" s="205"/>
       <c r="Q22" s="49"/>
-      <c r="R22" s="190"/>
-      <c r="S22" s="190"/>
+      <c r="R22" s="206"/>
+      <c r="S22" s="206"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="49"/>
       <c r="B23" s="49"/>
-      <c r="C23" s="183"/>
-      <c r="D23" s="183"/>
-      <c r="E23" s="183"/>
-      <c r="F23" s="183"/>
-      <c r="G23" s="183"/>
-      <c r="H23" s="184"/>
-      <c r="I23" s="185"/>
-      <c r="J23" s="185"/>
-      <c r="K23" s="185"/>
-      <c r="L23" s="185"/>
-      <c r="M23" s="186"/>
-      <c r="N23" s="187"/>
-      <c r="O23" s="188"/>
-      <c r="P23" s="189"/>
+      <c r="C23" s="202"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="202"/>
+      <c r="F23" s="202"/>
+      <c r="G23" s="202"/>
+      <c r="H23" s="207"/>
+      <c r="I23" s="208"/>
+      <c r="J23" s="208"/>
+      <c r="K23" s="208"/>
+      <c r="L23" s="208"/>
+      <c r="M23" s="209"/>
+      <c r="N23" s="203"/>
+      <c r="O23" s="204"/>
+      <c r="P23" s="205"/>
       <c r="Q23" s="49"/>
-      <c r="R23" s="190"/>
-      <c r="S23" s="190"/>
+      <c r="R23" s="206"/>
+      <c r="S23" s="206"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="49"/>
       <c r="B24" s="49"/>
-      <c r="C24" s="183"/>
-      <c r="D24" s="183"/>
-      <c r="E24" s="183"/>
-      <c r="F24" s="183"/>
-      <c r="G24" s="183"/>
-      <c r="H24" s="184"/>
-      <c r="I24" s="185"/>
-      <c r="J24" s="185"/>
-      <c r="K24" s="185"/>
-      <c r="L24" s="185"/>
-      <c r="M24" s="186"/>
-      <c r="N24" s="187"/>
-      <c r="O24" s="188"/>
-      <c r="P24" s="189"/>
+      <c r="C24" s="202"/>
+      <c r="D24" s="202"/>
+      <c r="E24" s="202"/>
+      <c r="F24" s="202"/>
+      <c r="G24" s="202"/>
+      <c r="H24" s="207"/>
+      <c r="I24" s="208"/>
+      <c r="J24" s="208"/>
+      <c r="K24" s="208"/>
+      <c r="L24" s="208"/>
+      <c r="M24" s="209"/>
+      <c r="N24" s="203"/>
+      <c r="O24" s="204"/>
+      <c r="P24" s="205"/>
       <c r="Q24" s="49"/>
-      <c r="R24" s="190"/>
-      <c r="S24" s="190"/>
+      <c r="R24" s="206"/>
+      <c r="S24" s="206"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="49"/>
       <c r="B25" s="49"/>
-      <c r="C25" s="183"/>
-      <c r="D25" s="183"/>
-      <c r="E25" s="183"/>
-      <c r="F25" s="183"/>
-      <c r="G25" s="183"/>
-      <c r="H25" s="184"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="185"/>
-      <c r="K25" s="185"/>
-      <c r="L25" s="185"/>
-      <c r="M25" s="186"/>
-      <c r="N25" s="187"/>
-      <c r="O25" s="188"/>
-      <c r="P25" s="189"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="202"/>
+      <c r="G25" s="202"/>
+      <c r="H25" s="207"/>
+      <c r="I25" s="208"/>
+      <c r="J25" s="208"/>
+      <c r="K25" s="208"/>
+      <c r="L25" s="208"/>
+      <c r="M25" s="209"/>
+      <c r="N25" s="203"/>
+      <c r="O25" s="204"/>
+      <c r="P25" s="205"/>
       <c r="Q25" s="49"/>
-      <c r="R25" s="190"/>
-      <c r="S25" s="190"/>
+      <c r="R25" s="206"/>
+      <c r="S25" s="206"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="49"/>
       <c r="B26" s="49"/>
-      <c r="C26" s="183"/>
-      <c r="D26" s="183"/>
-      <c r="E26" s="183"/>
-      <c r="F26" s="183"/>
-      <c r="G26" s="183"/>
-      <c r="H26" s="184"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="185"/>
-      <c r="K26" s="185"/>
-      <c r="L26" s="185"/>
-      <c r="M26" s="186"/>
-      <c r="N26" s="187"/>
-      <c r="O26" s="188"/>
-      <c r="P26" s="189"/>
+      <c r="C26" s="202"/>
+      <c r="D26" s="202"/>
+      <c r="E26" s="202"/>
+      <c r="F26" s="202"/>
+      <c r="G26" s="202"/>
+      <c r="H26" s="207"/>
+      <c r="I26" s="208"/>
+      <c r="J26" s="208"/>
+      <c r="K26" s="208"/>
+      <c r="L26" s="208"/>
+      <c r="M26" s="209"/>
+      <c r="N26" s="203"/>
+      <c r="O26" s="204"/>
+      <c r="P26" s="205"/>
       <c r="Q26" s="49"/>
-      <c r="R26" s="190"/>
-      <c r="S26" s="190"/>
+      <c r="R26" s="206"/>
+      <c r="S26" s="206"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="49"/>
       <c r="B27" s="49"/>
-      <c r="C27" s="183"/>
-      <c r="D27" s="183"/>
-      <c r="E27" s="183"/>
-      <c r="F27" s="183"/>
-      <c r="G27" s="183"/>
-      <c r="H27" s="184"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="185"/>
-      <c r="K27" s="185"/>
-      <c r="L27" s="185"/>
-      <c r="M27" s="186"/>
-      <c r="N27" s="187"/>
-      <c r="O27" s="188"/>
-      <c r="P27" s="189"/>
+      <c r="C27" s="202"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="202"/>
+      <c r="F27" s="202"/>
+      <c r="G27" s="202"/>
+      <c r="H27" s="207"/>
+      <c r="I27" s="208"/>
+      <c r="J27" s="208"/>
+      <c r="K27" s="208"/>
+      <c r="L27" s="208"/>
+      <c r="M27" s="209"/>
+      <c r="N27" s="203"/>
+      <c r="O27" s="204"/>
+      <c r="P27" s="205"/>
       <c r="Q27" s="49"/>
-      <c r="R27" s="190"/>
-      <c r="S27" s="190"/>
+      <c r="R27" s="206"/>
+      <c r="S27" s="206"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="49"/>
       <c r="B28" s="49"/>
-      <c r="C28" s="183"/>
-      <c r="D28" s="183"/>
-      <c r="E28" s="183"/>
-      <c r="F28" s="183"/>
-      <c r="G28" s="183"/>
-      <c r="H28" s="184"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="185"/>
-      <c r="K28" s="185"/>
-      <c r="L28" s="185"/>
-      <c r="M28" s="186"/>
-      <c r="N28" s="187"/>
-      <c r="O28" s="188"/>
-      <c r="P28" s="189"/>
+      <c r="C28" s="202"/>
+      <c r="D28" s="202"/>
+      <c r="E28" s="202"/>
+      <c r="F28" s="202"/>
+      <c r="G28" s="202"/>
+      <c r="H28" s="207"/>
+      <c r="I28" s="208"/>
+      <c r="J28" s="208"/>
+      <c r="K28" s="208"/>
+      <c r="L28" s="208"/>
+      <c r="M28" s="209"/>
+      <c r="N28" s="203"/>
+      <c r="O28" s="204"/>
+      <c r="P28" s="205"/>
       <c r="Q28" s="49"/>
-      <c r="R28" s="190"/>
-      <c r="S28" s="190"/>
+      <c r="R28" s="206"/>
+      <c r="S28" s="206"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="49"/>
       <c r="B29" s="49"/>
-      <c r="C29" s="183"/>
-      <c r="D29" s="183"/>
-      <c r="E29" s="183"/>
-      <c r="F29" s="183"/>
-      <c r="G29" s="183"/>
-      <c r="H29" s="184"/>
-      <c r="I29" s="185"/>
-      <c r="J29" s="185"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="185"/>
-      <c r="M29" s="186"/>
-      <c r="N29" s="187"/>
-      <c r="O29" s="188"/>
-      <c r="P29" s="189"/>
+      <c r="C29" s="202"/>
+      <c r="D29" s="202"/>
+      <c r="E29" s="202"/>
+      <c r="F29" s="202"/>
+      <c r="G29" s="202"/>
+      <c r="H29" s="207"/>
+      <c r="I29" s="208"/>
+      <c r="J29" s="208"/>
+      <c r="K29" s="208"/>
+      <c r="L29" s="208"/>
+      <c r="M29" s="209"/>
+      <c r="N29" s="203"/>
+      <c r="O29" s="204"/>
+      <c r="P29" s="205"/>
       <c r="Q29" s="49"/>
-      <c r="R29" s="190"/>
-      <c r="S29" s="190"/>
+      <c r="R29" s="206"/>
+      <c r="S29" s="206"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="49"/>
       <c r="B30" s="49"/>
-      <c r="C30" s="183"/>
-      <c r="D30" s="183"/>
-      <c r="E30" s="183"/>
-      <c r="F30" s="183"/>
-      <c r="G30" s="183"/>
-      <c r="H30" s="184"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="185"/>
-      <c r="K30" s="185"/>
-      <c r="L30" s="185"/>
-      <c r="M30" s="186"/>
-      <c r="N30" s="187"/>
-      <c r="O30" s="188"/>
-      <c r="P30" s="189"/>
+      <c r="C30" s="202"/>
+      <c r="D30" s="202"/>
+      <c r="E30" s="202"/>
+      <c r="F30" s="202"/>
+      <c r="G30" s="202"/>
+      <c r="H30" s="207"/>
+      <c r="I30" s="208"/>
+      <c r="J30" s="208"/>
+      <c r="K30" s="208"/>
+      <c r="L30" s="208"/>
+      <c r="M30" s="209"/>
+      <c r="N30" s="203"/>
+      <c r="O30" s="204"/>
+      <c r="P30" s="205"/>
       <c r="Q30" s="49"/>
-      <c r="R30" s="190"/>
-      <c r="S30" s="190"/>
+      <c r="R30" s="206"/>
+      <c r="S30" s="206"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="49"/>
       <c r="B31" s="49"/>
-      <c r="C31" s="183"/>
-      <c r="D31" s="183"/>
-      <c r="E31" s="183"/>
-      <c r="F31" s="183"/>
-      <c r="G31" s="183"/>
-      <c r="H31" s="184"/>
-      <c r="I31" s="185"/>
-      <c r="J31" s="185"/>
-      <c r="K31" s="185"/>
-      <c r="L31" s="185"/>
-      <c r="M31" s="186"/>
-      <c r="N31" s="187"/>
-      <c r="O31" s="188"/>
-      <c r="P31" s="189"/>
+      <c r="C31" s="202"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="202"/>
+      <c r="F31" s="202"/>
+      <c r="G31" s="202"/>
+      <c r="H31" s="207"/>
+      <c r="I31" s="208"/>
+      <c r="J31" s="208"/>
+      <c r="K31" s="208"/>
+      <c r="L31" s="208"/>
+      <c r="M31" s="209"/>
+      <c r="N31" s="203"/>
+      <c r="O31" s="204"/>
+      <c r="P31" s="205"/>
       <c r="Q31" s="49"/>
-      <c r="R31" s="190"/>
-      <c r="S31" s="190"/>
+      <c r="R31" s="206"/>
+      <c r="S31" s="206"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="49"/>
       <c r="B32" s="49"/>
-      <c r="C32" s="183"/>
-      <c r="D32" s="183"/>
-      <c r="E32" s="183"/>
-      <c r="F32" s="183"/>
-      <c r="G32" s="183"/>
-      <c r="H32" s="184"/>
-      <c r="I32" s="185"/>
-      <c r="J32" s="185"/>
-      <c r="K32" s="185"/>
-      <c r="L32" s="185"/>
-      <c r="M32" s="186"/>
-      <c r="N32" s="187"/>
-      <c r="O32" s="188"/>
-      <c r="P32" s="189"/>
+      <c r="C32" s="202"/>
+      <c r="D32" s="202"/>
+      <c r="E32" s="202"/>
+      <c r="F32" s="202"/>
+      <c r="G32" s="202"/>
+      <c r="H32" s="207"/>
+      <c r="I32" s="208"/>
+      <c r="J32" s="208"/>
+      <c r="K32" s="208"/>
+      <c r="L32" s="208"/>
+      <c r="M32" s="209"/>
+      <c r="N32" s="203"/>
+      <c r="O32" s="204"/>
+      <c r="P32" s="205"/>
       <c r="Q32" s="49"/>
-      <c r="R32" s="190"/>
-      <c r="S32" s="190"/>
+      <c r="R32" s="206"/>
+      <c r="S32" s="206"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="49"/>
       <c r="B33" s="49"/>
-      <c r="C33" s="183"/>
-      <c r="D33" s="183"/>
-      <c r="E33" s="183"/>
-      <c r="F33" s="183"/>
-      <c r="G33" s="183"/>
-      <c r="H33" s="184"/>
-      <c r="I33" s="185"/>
-      <c r="J33" s="185"/>
-      <c r="K33" s="185"/>
-      <c r="L33" s="185"/>
-      <c r="M33" s="186"/>
-      <c r="N33" s="187"/>
-      <c r="O33" s="188"/>
-      <c r="P33" s="189"/>
+      <c r="C33" s="202"/>
+      <c r="D33" s="202"/>
+      <c r="E33" s="202"/>
+      <c r="F33" s="202"/>
+      <c r="G33" s="202"/>
+      <c r="H33" s="207"/>
+      <c r="I33" s="208"/>
+      <c r="J33" s="208"/>
+      <c r="K33" s="208"/>
+      <c r="L33" s="208"/>
+      <c r="M33" s="209"/>
+      <c r="N33" s="203"/>
+      <c r="O33" s="204"/>
+      <c r="P33" s="205"/>
       <c r="Q33" s="49"/>
-      <c r="R33" s="190"/>
-      <c r="S33" s="190"/>
+      <c r="R33" s="206"/>
+      <c r="S33" s="206"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="49"/>
       <c r="B34" s="49"/>
-      <c r="C34" s="183"/>
-      <c r="D34" s="183"/>
-      <c r="E34" s="183"/>
-      <c r="F34" s="183"/>
-      <c r="G34" s="183"/>
-      <c r="H34" s="184"/>
-      <c r="I34" s="185"/>
-      <c r="J34" s="185"/>
-      <c r="K34" s="185"/>
-      <c r="L34" s="185"/>
-      <c r="M34" s="186"/>
-      <c r="N34" s="187"/>
-      <c r="O34" s="188"/>
-      <c r="P34" s="189"/>
+      <c r="C34" s="202"/>
+      <c r="D34" s="202"/>
+      <c r="E34" s="202"/>
+      <c r="F34" s="202"/>
+      <c r="G34" s="202"/>
+      <c r="H34" s="207"/>
+      <c r="I34" s="208"/>
+      <c r="J34" s="208"/>
+      <c r="K34" s="208"/>
+      <c r="L34" s="208"/>
+      <c r="M34" s="209"/>
+      <c r="N34" s="203"/>
+      <c r="O34" s="204"/>
+      <c r="P34" s="205"/>
       <c r="Q34" s="49"/>
-      <c r="R34" s="190"/>
-      <c r="S34" s="190"/>
+      <c r="R34" s="206"/>
+      <c r="S34" s="206"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
-      <c r="C35" s="183"/>
-      <c r="D35" s="183"/>
-      <c r="E35" s="183"/>
-      <c r="F35" s="183"/>
-      <c r="G35" s="183"/>
-      <c r="H35" s="184"/>
-      <c r="I35" s="185"/>
-      <c r="J35" s="185"/>
-      <c r="K35" s="185"/>
-      <c r="L35" s="185"/>
-      <c r="M35" s="186"/>
-      <c r="N35" s="187"/>
-      <c r="O35" s="188"/>
-      <c r="P35" s="189"/>
+      <c r="C35" s="202"/>
+      <c r="D35" s="202"/>
+      <c r="E35" s="202"/>
+      <c r="F35" s="202"/>
+      <c r="G35" s="202"/>
+      <c r="H35" s="207"/>
+      <c r="I35" s="208"/>
+      <c r="J35" s="208"/>
+      <c r="K35" s="208"/>
+      <c r="L35" s="208"/>
+      <c r="M35" s="209"/>
+      <c r="N35" s="203"/>
+      <c r="O35" s="204"/>
+      <c r="P35" s="205"/>
       <c r="Q35" s="49"/>
-      <c r="R35" s="190"/>
-      <c r="S35" s="190"/>
+      <c r="R35" s="206"/>
+      <c r="S35" s="206"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="49"/>
       <c r="B36" s="49"/>
-      <c r="C36" s="183"/>
-      <c r="D36" s="183"/>
-      <c r="E36" s="183"/>
-      <c r="F36" s="183"/>
-      <c r="G36" s="183"/>
-      <c r="H36" s="184"/>
-      <c r="I36" s="185"/>
-      <c r="J36" s="185"/>
-      <c r="K36" s="185"/>
-      <c r="L36" s="185"/>
-      <c r="M36" s="186"/>
-      <c r="N36" s="187"/>
-      <c r="O36" s="188"/>
-      <c r="P36" s="189"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="207"/>
+      <c r="I36" s="208"/>
+      <c r="J36" s="208"/>
+      <c r="K36" s="208"/>
+      <c r="L36" s="208"/>
+      <c r="M36" s="209"/>
+      <c r="N36" s="203"/>
+      <c r="O36" s="204"/>
+      <c r="P36" s="205"/>
       <c r="Q36" s="49"/>
-      <c r="R36" s="190"/>
-      <c r="S36" s="190"/>
+      <c r="R36" s="206"/>
+      <c r="S36" s="206"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="49"/>
       <c r="B37" s="49"/>
-      <c r="C37" s="183"/>
-      <c r="D37" s="183"/>
-      <c r="E37" s="183"/>
-      <c r="F37" s="183"/>
-      <c r="G37" s="183"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="185"/>
-      <c r="J37" s="185"/>
-      <c r="K37" s="185"/>
-      <c r="L37" s="185"/>
-      <c r="M37" s="186"/>
-      <c r="N37" s="187"/>
-      <c r="O37" s="188"/>
-      <c r="P37" s="189"/>
+      <c r="C37" s="202"/>
+      <c r="D37" s="202"/>
+      <c r="E37" s="202"/>
+      <c r="F37" s="202"/>
+      <c r="G37" s="202"/>
+      <c r="H37" s="207"/>
+      <c r="I37" s="208"/>
+      <c r="J37" s="208"/>
+      <c r="K37" s="208"/>
+      <c r="L37" s="208"/>
+      <c r="M37" s="209"/>
+      <c r="N37" s="203"/>
+      <c r="O37" s="204"/>
+      <c r="P37" s="205"/>
       <c r="Q37" s="49"/>
-      <c r="R37" s="190"/>
-      <c r="S37" s="190"/>
+      <c r="R37" s="206"/>
+      <c r="S37" s="206"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="49"/>
       <c r="B38" s="49"/>
-      <c r="C38" s="183"/>
-      <c r="D38" s="183"/>
-      <c r="E38" s="183"/>
-      <c r="F38" s="183"/>
-      <c r="G38" s="183"/>
-      <c r="H38" s="184"/>
-      <c r="I38" s="185"/>
-      <c r="J38" s="185"/>
-      <c r="K38" s="185"/>
-      <c r="L38" s="185"/>
-      <c r="M38" s="186"/>
-      <c r="N38" s="187"/>
-      <c r="O38" s="188"/>
-      <c r="P38" s="189"/>
+      <c r="C38" s="202"/>
+      <c r="D38" s="202"/>
+      <c r="E38" s="202"/>
+      <c r="F38" s="202"/>
+      <c r="G38" s="202"/>
+      <c r="H38" s="207"/>
+      <c r="I38" s="208"/>
+      <c r="J38" s="208"/>
+      <c r="K38" s="208"/>
+      <c r="L38" s="208"/>
+      <c r="M38" s="209"/>
+      <c r="N38" s="203"/>
+      <c r="O38" s="204"/>
+      <c r="P38" s="205"/>
       <c r="Q38" s="49"/>
-      <c r="R38" s="190"/>
-      <c r="S38" s="190"/>
+      <c r="R38" s="206"/>
+      <c r="S38" s="206"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="49"/>
       <c r="B39" s="49"/>
-      <c r="C39" s="183"/>
-      <c r="D39" s="183"/>
-      <c r="E39" s="183"/>
-      <c r="F39" s="183"/>
-      <c r="G39" s="183"/>
-      <c r="H39" s="184"/>
-      <c r="I39" s="185"/>
-      <c r="J39" s="185"/>
-      <c r="K39" s="185"/>
-      <c r="L39" s="185"/>
-      <c r="M39" s="186"/>
-      <c r="N39" s="187"/>
-      <c r="O39" s="188"/>
-      <c r="P39" s="189"/>
+      <c r="C39" s="202"/>
+      <c r="D39" s="202"/>
+      <c r="E39" s="202"/>
+      <c r="F39" s="202"/>
+      <c r="G39" s="202"/>
+      <c r="H39" s="207"/>
+      <c r="I39" s="208"/>
+      <c r="J39" s="208"/>
+      <c r="K39" s="208"/>
+      <c r="L39" s="208"/>
+      <c r="M39" s="209"/>
+      <c r="N39" s="203"/>
+      <c r="O39" s="204"/>
+      <c r="P39" s="205"/>
       <c r="Q39" s="49"/>
-      <c r="R39" s="190"/>
-      <c r="S39" s="190"/>
+      <c r="R39" s="206"/>
+      <c r="S39" s="206"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="49"/>
       <c r="B40" s="49"/>
-      <c r="C40" s="183"/>
-      <c r="D40" s="183"/>
-      <c r="E40" s="183"/>
-      <c r="F40" s="183"/>
-      <c r="G40" s="183"/>
-      <c r="H40" s="184"/>
-      <c r="I40" s="185"/>
-      <c r="J40" s="185"/>
-      <c r="K40" s="185"/>
-      <c r="L40" s="185"/>
-      <c r="M40" s="186"/>
-      <c r="N40" s="187"/>
-      <c r="O40" s="188"/>
-      <c r="P40" s="189"/>
+      <c r="C40" s="202"/>
+      <c r="D40" s="202"/>
+      <c r="E40" s="202"/>
+      <c r="F40" s="202"/>
+      <c r="G40" s="202"/>
+      <c r="H40" s="207"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="209"/>
+      <c r="N40" s="203"/>
+      <c r="O40" s="204"/>
+      <c r="P40" s="205"/>
       <c r="Q40" s="49"/>
-      <c r="R40" s="190"/>
-      <c r="S40" s="190"/>
+      <c r="R40" s="206"/>
+      <c r="S40" s="206"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="49"/>
       <c r="B41" s="49"/>
-      <c r="C41" s="183"/>
-      <c r="D41" s="183"/>
-      <c r="E41" s="183"/>
-      <c r="F41" s="183"/>
-      <c r="G41" s="183"/>
-      <c r="H41" s="184"/>
-      <c r="I41" s="185"/>
-      <c r="J41" s="185"/>
-      <c r="K41" s="185"/>
-      <c r="L41" s="185"/>
-      <c r="M41" s="186"/>
-      <c r="N41" s="187"/>
-      <c r="O41" s="188"/>
-      <c r="P41" s="189"/>
+      <c r="C41" s="202"/>
+      <c r="D41" s="202"/>
+      <c r="E41" s="202"/>
+      <c r="F41" s="202"/>
+      <c r="G41" s="202"/>
+      <c r="H41" s="207"/>
+      <c r="I41" s="208"/>
+      <c r="J41" s="208"/>
+      <c r="K41" s="208"/>
+      <c r="L41" s="208"/>
+      <c r="M41" s="209"/>
+      <c r="N41" s="203"/>
+      <c r="O41" s="204"/>
+      <c r="P41" s="205"/>
       <c r="Q41" s="49"/>
-      <c r="R41" s="190"/>
-      <c r="S41" s="190"/>
+      <c r="R41" s="206"/>
+      <c r="S41" s="206"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="49"/>
       <c r="B42" s="49"/>
-      <c r="C42" s="183"/>
-      <c r="D42" s="183"/>
-      <c r="E42" s="183"/>
-      <c r="F42" s="183"/>
-      <c r="G42" s="183"/>
-      <c r="H42" s="184"/>
-      <c r="I42" s="185"/>
-      <c r="J42" s="185"/>
-      <c r="K42" s="185"/>
-      <c r="L42" s="185"/>
-      <c r="M42" s="186"/>
-      <c r="N42" s="187"/>
-      <c r="O42" s="188"/>
-      <c r="P42" s="189"/>
+      <c r="C42" s="202"/>
+      <c r="D42" s="202"/>
+      <c r="E42" s="202"/>
+      <c r="F42" s="202"/>
+      <c r="G42" s="202"/>
+      <c r="H42" s="207"/>
+      <c r="I42" s="208"/>
+      <c r="J42" s="208"/>
+      <c r="K42" s="208"/>
+      <c r="L42" s="208"/>
+      <c r="M42" s="209"/>
+      <c r="N42" s="203"/>
+      <c r="O42" s="204"/>
+      <c r="P42" s="205"/>
       <c r="Q42" s="49"/>
-      <c r="R42" s="190"/>
-      <c r="S42" s="190"/>
+      <c r="R42" s="206"/>
+      <c r="S42" s="206"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="49"/>
       <c r="B43" s="49"/>
-      <c r="C43" s="183"/>
-      <c r="D43" s="183"/>
-      <c r="E43" s="183"/>
-      <c r="F43" s="183"/>
-      <c r="G43" s="183"/>
-      <c r="H43" s="184"/>
-      <c r="I43" s="185"/>
-      <c r="J43" s="185"/>
-      <c r="K43" s="185"/>
-      <c r="L43" s="185"/>
-      <c r="M43" s="186"/>
-      <c r="N43" s="187"/>
-      <c r="O43" s="188"/>
-      <c r="P43" s="189"/>
+      <c r="C43" s="202"/>
+      <c r="D43" s="202"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="202"/>
+      <c r="G43" s="202"/>
+      <c r="H43" s="207"/>
+      <c r="I43" s="208"/>
+      <c r="J43" s="208"/>
+      <c r="K43" s="208"/>
+      <c r="L43" s="208"/>
+      <c r="M43" s="209"/>
+      <c r="N43" s="203"/>
+      <c r="O43" s="204"/>
+      <c r="P43" s="205"/>
       <c r="Q43" s="49"/>
-      <c r="R43" s="190"/>
-      <c r="S43" s="190"/>
+      <c r="R43" s="206"/>
+      <c r="S43" s="206"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="49"/>
       <c r="B44" s="49"/>
-      <c r="C44" s="183"/>
-      <c r="D44" s="183"/>
-      <c r="E44" s="183"/>
-      <c r="F44" s="183"/>
-      <c r="G44" s="183"/>
-      <c r="H44" s="184"/>
-      <c r="I44" s="185"/>
-      <c r="J44" s="185"/>
-      <c r="K44" s="185"/>
-      <c r="L44" s="185"/>
-      <c r="M44" s="186"/>
-      <c r="N44" s="187"/>
-      <c r="O44" s="188"/>
-      <c r="P44" s="189"/>
+      <c r="C44" s="202"/>
+      <c r="D44" s="202"/>
+      <c r="E44" s="202"/>
+      <c r="F44" s="202"/>
+      <c r="G44" s="202"/>
+      <c r="H44" s="207"/>
+      <c r="I44" s="208"/>
+      <c r="J44" s="208"/>
+      <c r="K44" s="208"/>
+      <c r="L44" s="208"/>
+      <c r="M44" s="209"/>
+      <c r="N44" s="203"/>
+      <c r="O44" s="204"/>
+      <c r="P44" s="205"/>
       <c r="Q44" s="49"/>
-      <c r="R44" s="190"/>
-      <c r="S44" s="190"/>
+      <c r="R44" s="206"/>
+      <c r="S44" s="206"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="49"/>
       <c r="B45" s="49"/>
-      <c r="C45" s="183"/>
-      <c r="D45" s="183"/>
-      <c r="E45" s="183"/>
-      <c r="F45" s="183"/>
-      <c r="G45" s="183"/>
-      <c r="H45" s="184"/>
-      <c r="I45" s="185"/>
-      <c r="J45" s="185"/>
-      <c r="K45" s="185"/>
-      <c r="L45" s="185"/>
-      <c r="M45" s="186"/>
-      <c r="N45" s="187"/>
-      <c r="O45" s="188"/>
-      <c r="P45" s="189"/>
+      <c r="C45" s="202"/>
+      <c r="D45" s="202"/>
+      <c r="E45" s="202"/>
+      <c r="F45" s="202"/>
+      <c r="G45" s="202"/>
+      <c r="H45" s="207"/>
+      <c r="I45" s="208"/>
+      <c r="J45" s="208"/>
+      <c r="K45" s="208"/>
+      <c r="L45" s="208"/>
+      <c r="M45" s="209"/>
+      <c r="N45" s="203"/>
+      <c r="O45" s="204"/>
+      <c r="P45" s="205"/>
       <c r="Q45" s="49"/>
-      <c r="R45" s="190"/>
-      <c r="S45" s="190"/>
+      <c r="R45" s="206"/>
+      <c r="S45" s="206"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="49"/>
       <c r="B46" s="49"/>
-      <c r="C46" s="183"/>
-      <c r="D46" s="183"/>
-      <c r="E46" s="183"/>
-      <c r="F46" s="183"/>
-      <c r="G46" s="183"/>
-      <c r="H46" s="184"/>
-      <c r="I46" s="185"/>
-      <c r="J46" s="185"/>
-      <c r="K46" s="185"/>
-      <c r="L46" s="185"/>
-      <c r="M46" s="186"/>
-      <c r="N46" s="187"/>
-      <c r="O46" s="188"/>
-      <c r="P46" s="189"/>
+      <c r="C46" s="202"/>
+      <c r="D46" s="202"/>
+      <c r="E46" s="202"/>
+      <c r="F46" s="202"/>
+      <c r="G46" s="202"/>
+      <c r="H46" s="207"/>
+      <c r="I46" s="208"/>
+      <c r="J46" s="208"/>
+      <c r="K46" s="208"/>
+      <c r="L46" s="208"/>
+      <c r="M46" s="209"/>
+      <c r="N46" s="203"/>
+      <c r="O46" s="204"/>
+      <c r="P46" s="205"/>
       <c r="Q46" s="49"/>
-      <c r="R46" s="190"/>
-      <c r="S46" s="190"/>
+      <c r="R46" s="206"/>
+      <c r="S46" s="206"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="49"/>
       <c r="B47" s="49"/>
-      <c r="C47" s="183"/>
-      <c r="D47" s="183"/>
-      <c r="E47" s="183"/>
-      <c r="F47" s="183"/>
-      <c r="G47" s="183"/>
-      <c r="H47" s="184"/>
-      <c r="I47" s="185"/>
-      <c r="J47" s="185"/>
-      <c r="K47" s="185"/>
-      <c r="L47" s="185"/>
-      <c r="M47" s="186"/>
-      <c r="N47" s="187"/>
-      <c r="O47" s="188"/>
-      <c r="P47" s="189"/>
+      <c r="C47" s="202"/>
+      <c r="D47" s="202"/>
+      <c r="E47" s="202"/>
+      <c r="F47" s="202"/>
+      <c r="G47" s="202"/>
+      <c r="H47" s="207"/>
+      <c r="I47" s="208"/>
+      <c r="J47" s="208"/>
+      <c r="K47" s="208"/>
+      <c r="L47" s="208"/>
+      <c r="M47" s="209"/>
+      <c r="N47" s="203"/>
+      <c r="O47" s="204"/>
+      <c r="P47" s="205"/>
       <c r="Q47" s="49"/>
-      <c r="R47" s="190"/>
-      <c r="S47" s="190"/>
+      <c r="R47" s="206"/>
+      <c r="S47" s="206"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="49"/>
       <c r="B48" s="49"/>
-      <c r="C48" s="183"/>
-      <c r="D48" s="183"/>
-      <c r="E48" s="183"/>
-      <c r="F48" s="183"/>
-      <c r="G48" s="183"/>
-      <c r="H48" s="184"/>
-      <c r="I48" s="185"/>
-      <c r="J48" s="185"/>
-      <c r="K48" s="185"/>
-      <c r="L48" s="185"/>
-      <c r="M48" s="186"/>
-      <c r="N48" s="187"/>
-      <c r="O48" s="188"/>
-      <c r="P48" s="189"/>
+      <c r="C48" s="202"/>
+      <c r="D48" s="202"/>
+      <c r="E48" s="202"/>
+      <c r="F48" s="202"/>
+      <c r="G48" s="202"/>
+      <c r="H48" s="207"/>
+      <c r="I48" s="208"/>
+      <c r="J48" s="208"/>
+      <c r="K48" s="208"/>
+      <c r="L48" s="208"/>
+      <c r="M48" s="209"/>
+      <c r="N48" s="203"/>
+      <c r="O48" s="204"/>
+      <c r="P48" s="205"/>
       <c r="Q48" s="49"/>
-      <c r="R48" s="190"/>
-      <c r="S48" s="190"/>
+      <c r="R48" s="206"/>
+      <c r="S48" s="206"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="49"/>
       <c r="B49" s="49"/>
-      <c r="C49" s="183"/>
-      <c r="D49" s="183"/>
-      <c r="E49" s="183"/>
-      <c r="F49" s="183"/>
-      <c r="G49" s="183"/>
-      <c r="H49" s="184"/>
-      <c r="I49" s="185"/>
-      <c r="J49" s="185"/>
-      <c r="K49" s="185"/>
-      <c r="L49" s="185"/>
-      <c r="M49" s="186"/>
-      <c r="N49" s="187"/>
-      <c r="O49" s="188"/>
-      <c r="P49" s="189"/>
+      <c r="C49" s="202"/>
+      <c r="D49" s="202"/>
+      <c r="E49" s="202"/>
+      <c r="F49" s="202"/>
+      <c r="G49" s="202"/>
+      <c r="H49" s="207"/>
+      <c r="I49" s="208"/>
+      <c r="J49" s="208"/>
+      <c r="K49" s="208"/>
+      <c r="L49" s="208"/>
+      <c r="M49" s="209"/>
+      <c r="N49" s="203"/>
+      <c r="O49" s="204"/>
+      <c r="P49" s="205"/>
       <c r="Q49" s="49"/>
-      <c r="R49" s="190"/>
-      <c r="S49" s="190"/>
+      <c r="R49" s="206"/>
+      <c r="S49" s="206"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="49"/>
       <c r="B50" s="49"/>
-      <c r="C50" s="183"/>
-      <c r="D50" s="183"/>
-      <c r="E50" s="183"/>
-      <c r="F50" s="183"/>
-      <c r="G50" s="183"/>
-      <c r="H50" s="184"/>
-      <c r="I50" s="185"/>
-      <c r="J50" s="185"/>
-      <c r="K50" s="185"/>
-      <c r="L50" s="185"/>
-      <c r="M50" s="186"/>
-      <c r="N50" s="187"/>
-      <c r="O50" s="188"/>
-      <c r="P50" s="189"/>
+      <c r="C50" s="202"/>
+      <c r="D50" s="202"/>
+      <c r="E50" s="202"/>
+      <c r="F50" s="202"/>
+      <c r="G50" s="202"/>
+      <c r="H50" s="207"/>
+      <c r="I50" s="208"/>
+      <c r="J50" s="208"/>
+      <c r="K50" s="208"/>
+      <c r="L50" s="208"/>
+      <c r="M50" s="209"/>
+      <c r="N50" s="203"/>
+      <c r="O50" s="204"/>
+      <c r="P50" s="205"/>
       <c r="Q50" s="49"/>
-      <c r="R50" s="190"/>
-      <c r="S50" s="190"/>
+      <c r="R50" s="206"/>
+      <c r="S50" s="206"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="49"/>
       <c r="B51" s="49"/>
-      <c r="C51" s="183"/>
-      <c r="D51" s="183"/>
-      <c r="E51" s="183"/>
-      <c r="F51" s="183"/>
-      <c r="G51" s="183"/>
-      <c r="H51" s="184"/>
-      <c r="I51" s="185"/>
-      <c r="J51" s="185"/>
-      <c r="K51" s="185"/>
-      <c r="L51" s="185"/>
-      <c r="M51" s="186"/>
-      <c r="N51" s="187"/>
-      <c r="O51" s="188"/>
-      <c r="P51" s="189"/>
+      <c r="C51" s="202"/>
+      <c r="D51" s="202"/>
+      <c r="E51" s="202"/>
+      <c r="F51" s="202"/>
+      <c r="G51" s="202"/>
+      <c r="H51" s="207"/>
+      <c r="I51" s="208"/>
+      <c r="J51" s="208"/>
+      <c r="K51" s="208"/>
+      <c r="L51" s="208"/>
+      <c r="M51" s="209"/>
+      <c r="N51" s="203"/>
+      <c r="O51" s="204"/>
+      <c r="P51" s="205"/>
       <c r="Q51" s="49"/>
-      <c r="R51" s="190"/>
-      <c r="S51" s="190"/>
+      <c r="R51" s="206"/>
+      <c r="S51" s="206"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="49"/>
       <c r="B52" s="49"/>
-      <c r="C52" s="183"/>
-      <c r="D52" s="183"/>
-      <c r="E52" s="183"/>
-      <c r="F52" s="183"/>
-      <c r="G52" s="183"/>
-      <c r="H52" s="184"/>
-      <c r="I52" s="185"/>
-      <c r="J52" s="185"/>
-      <c r="K52" s="185"/>
-      <c r="L52" s="185"/>
-      <c r="M52" s="186"/>
-      <c r="N52" s="187"/>
-      <c r="O52" s="188"/>
-      <c r="P52" s="189"/>
+      <c r="C52" s="202"/>
+      <c r="D52" s="202"/>
+      <c r="E52" s="202"/>
+      <c r="F52" s="202"/>
+      <c r="G52" s="202"/>
+      <c r="H52" s="207"/>
+      <c r="I52" s="208"/>
+      <c r="J52" s="208"/>
+      <c r="K52" s="208"/>
+      <c r="L52" s="208"/>
+      <c r="M52" s="209"/>
+      <c r="N52" s="203"/>
+      <c r="O52" s="204"/>
+      <c r="P52" s="205"/>
       <c r="Q52" s="49"/>
-      <c r="R52" s="190"/>
-      <c r="S52" s="190"/>
+      <c r="R52" s="206"/>
+      <c r="S52" s="206"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -21015,194 +21200,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/削除機能詳細設計書.xlsx
+++ b/Documents/削除機能詳細設計書.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Documents\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Documents\project\プロジェクト演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB530C3-C96D-4228-99C2-AE28B543FA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3680E53D-4F47-4626-859E-5F8564F49EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="151">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -890,10 +890,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>TaskDAO.Java</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>削除ボタンを押下後、タスク削除成功画面でブラウザバックし、もう一度削除ボタンを押下する</t>
     <rPh sb="0" eb="2">
       <t>サクジョ</t>
@@ -975,6 +971,31 @@
     <rPh sb="0" eb="2">
       <t>ヤマモト</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>CommentDAOTest</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>deleteAllComment(int taskId)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除するタスクに付いていたコメントを削除する</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>TaskDAO.Java,CommentDAO.java</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -2337,6 +2358,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2347,11 +2401,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2367,9 +2469,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2388,84 +2487,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2529,27 +2550,48 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2562,65 +2604,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2630,19 +2642,100 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2650,78 +2743,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2780,22 +2801,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE3A018D-27DB-1F57-DE9B-FCCFF1F5E845}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4FE9935-9F86-BE75-6EEF-369AF02ECC44}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2817,8 +2838,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="457200" y="1085850"/>
-          <a:ext cx="7772400" cy="4295775"/>
+          <a:off x="590550" y="1143000"/>
+          <a:ext cx="7762875" cy="4305300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2938,23 +2959,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>95251</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
+      <xdr:colOff>952500</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>76201</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{783BD3DC-C918-DBAC-2B2A-5910DB66F40F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40019F9E-0E22-8487-F111-D551D0F9420F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2976,8 +2997,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="523875" y="962025"/>
-          <a:ext cx="7772400" cy="4562475"/>
+          <a:off x="895350" y="1009651"/>
+          <a:ext cx="7772400" cy="4514850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3286,16 +3307,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>164784</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>40822</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>219212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>50</xdr:col>
-      <xdr:colOff>108857</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>108856</xdr:rowOff>
+      <xdr:colOff>163286</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3324,7 +3345,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="394607" y="2777355"/>
+          <a:off x="449036" y="2287498"/>
           <a:ext cx="9919607" cy="3209787"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3336,16 +3357,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>40822</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>40822</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>122465</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>176894</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>76890</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>258536</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>158532</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>122466</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3374,8 +3395,108 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2898322" y="9184822"/>
+          <a:off x="530679" y="10137323"/>
           <a:ext cx="4934639" cy="2122714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>217715</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>138792</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>258536</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{556C325B-0B25-23FD-4E10-190465F8DA43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="326571" y="5823858"/>
+          <a:ext cx="7772400" cy="3034392"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>122465</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>15437</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>62830</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2AB2AB-0C43-D83D-C01F-C2A977C5FEE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6245679" y="10232572"/>
+          <a:ext cx="3362794" cy="1695687"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4751,7 +4872,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A8BAD46-6E3B-4441-A751-911B04EB9F0C}">
-  <dimension ref="A1:BA115"/>
+  <dimension ref="A1:BA119"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="3" style="58" customWidth="1"/>
@@ -4812,7 +4933,7 @@
       <c r="AR1" s="213"/>
       <c r="AS1" s="213"/>
       <c r="AT1" s="214">
-        <v>45821</v>
+        <v>45827</v>
       </c>
       <c r="AU1" s="215"/>
       <c r="AV1" s="215"/>
@@ -4875,7 +4996,7 @@
       <c r="E5" s="211"/>
       <c r="F5" s="212"/>
       <c r="G5" s="216" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="H5" s="217"/>
       <c r="I5" s="217"/>
@@ -5979,97 +6100,80 @@
       <c r="BA34" s="64"/>
     </row>
     <row r="35" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A35" s="210" t="s">
-        <v>132</v>
-      </c>
-      <c r="B35" s="211"/>
-      <c r="C35" s="211"/>
-      <c r="D35" s="211"/>
-      <c r="E35" s="211"/>
-      <c r="F35" s="211"/>
-      <c r="G35" s="211"/>
-      <c r="H35" s="211"/>
-      <c r="I35" s="211"/>
-      <c r="J35" s="211"/>
-      <c r="K35" s="211"/>
-      <c r="L35" s="211"/>
-      <c r="M35" s="211"/>
-      <c r="N35" s="211"/>
-      <c r="O35" s="211"/>
-      <c r="P35" s="211"/>
-      <c r="Q35" s="211"/>
-      <c r="R35" s="211"/>
-      <c r="S35" s="211"/>
-      <c r="T35" s="211"/>
-      <c r="U35" s="211"/>
-      <c r="V35" s="211"/>
-      <c r="W35" s="211"/>
-      <c r="X35" s="211"/>
-      <c r="Y35" s="211"/>
-      <c r="Z35" s="211"/>
-      <c r="AA35" s="211"/>
-      <c r="AB35" s="211"/>
-      <c r="AC35" s="211"/>
-      <c r="AD35" s="211"/>
-      <c r="AE35" s="211"/>
-      <c r="AF35" s="211"/>
-      <c r="AG35" s="211"/>
-      <c r="AH35" s="211"/>
-      <c r="AI35" s="211"/>
-      <c r="AJ35" s="211"/>
-      <c r="AK35" s="211"/>
-      <c r="AL35" s="211"/>
-      <c r="AM35" s="211"/>
-      <c r="AN35" s="211"/>
-      <c r="AO35" s="211"/>
-      <c r="AP35" s="211"/>
-      <c r="AQ35" s="211"/>
-      <c r="AR35" s="211"/>
-      <c r="AS35" s="211"/>
-      <c r="AT35" s="211"/>
-      <c r="AU35" s="211"/>
-      <c r="AV35" s="211"/>
-      <c r="AW35" s="211"/>
-      <c r="AX35" s="211"/>
-      <c r="AY35" s="211"/>
-      <c r="AZ35" s="211"/>
-      <c r="BA35" s="212"/>
+      <c r="A35" s="62"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="63"/>
+      <c r="P35" s="63"/>
+      <c r="Q35" s="63"/>
+      <c r="R35" s="63"/>
+      <c r="S35" s="63"/>
+      <c r="T35" s="63"/>
+      <c r="U35" s="63"/>
+      <c r="V35" s="63"/>
+      <c r="W35" s="63"/>
+      <c r="X35" s="63"/>
+      <c r="Y35" s="63"/>
+      <c r="Z35" s="63"/>
+      <c r="AA35" s="63"/>
+      <c r="AB35" s="63"/>
+      <c r="AC35" s="63"/>
+      <c r="AD35" s="63"/>
+      <c r="AE35" s="63"/>
+      <c r="AF35" s="63"/>
+      <c r="AG35" s="63"/>
+      <c r="AH35" s="63"/>
+      <c r="AI35" s="63"/>
+      <c r="AJ35" s="63"/>
+      <c r="AK35" s="63"/>
+      <c r="BA35" s="64"/>
     </row>
     <row r="36" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A36" s="65"/>
-      <c r="B36" s="66"/>
-      <c r="C36" s="66"/>
-      <c r="D36" s="66"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="66"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="66"/>
-      <c r="J36" s="66"/>
-      <c r="K36" s="66"/>
-      <c r="L36" s="66"/>
-      <c r="M36" s="66"/>
-      <c r="N36" s="66"/>
-      <c r="O36" s="66"/>
-      <c r="P36" s="66"/>
-      <c r="Q36" s="66"/>
-      <c r="R36" s="66"/>
-      <c r="S36" s="66"/>
-      <c r="T36" s="66"/>
-      <c r="U36" s="66"/>
-      <c r="V36" s="66"/>
-      <c r="W36" s="66"/>
-      <c r="X36" s="66"/>
-      <c r="Y36" s="66"/>
-      <c r="Z36" s="66"/>
-      <c r="AA36" s="66"/>
-      <c r="AB36" s="66"/>
-      <c r="AC36" s="66"/>
-      <c r="AD36" s="66"/>
-      <c r="AE36" s="66"/>
-      <c r="AF36" s="66"/>
-      <c r="AG36" s="66"/>
-      <c r="AH36" s="66"/>
+      <c r="A36" s="62"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="63"/>
+      <c r="K36" s="63"/>
+      <c r="L36" s="63"/>
+      <c r="M36" s="63"/>
+      <c r="N36" s="63"/>
+      <c r="O36" s="63"/>
+      <c r="P36" s="63"/>
+      <c r="Q36" s="63"/>
+      <c r="R36" s="63"/>
+      <c r="S36" s="63"/>
+      <c r="T36" s="63"/>
+      <c r="U36" s="63"/>
+      <c r="V36" s="63"/>
+      <c r="W36" s="63"/>
+      <c r="X36" s="63"/>
+      <c r="Y36" s="63"/>
+      <c r="Z36" s="63"/>
+      <c r="AA36" s="63"/>
+      <c r="AB36" s="63"/>
+      <c r="AC36" s="63"/>
+      <c r="AD36" s="63"/>
+      <c r="AE36" s="63"/>
+      <c r="AF36" s="63"/>
+      <c r="AG36" s="63"/>
+      <c r="AH36" s="63"/>
       <c r="AI36" s="63"/>
       <c r="AJ36" s="63"/>
       <c r="AK36" s="63"/>
@@ -6116,80 +6220,97 @@
       <c r="BA37" s="64"/>
     </row>
     <row r="38" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A38" s="62"/>
-      <c r="B38" s="63"/>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="63"/>
-      <c r="J38" s="63"/>
-      <c r="K38" s="63"/>
-      <c r="L38" s="63"/>
-      <c r="M38" s="63"/>
-      <c r="N38" s="63"/>
-      <c r="O38" s="63"/>
-      <c r="P38" s="63"/>
-      <c r="Q38" s="63"/>
-      <c r="R38" s="63"/>
-      <c r="S38" s="63"/>
-      <c r="T38" s="63"/>
-      <c r="U38" s="63"/>
-      <c r="V38" s="63"/>
-      <c r="W38" s="63"/>
-      <c r="X38" s="63"/>
-      <c r="Y38" s="63"/>
-      <c r="Z38" s="63"/>
-      <c r="AA38" s="63"/>
-      <c r="AB38" s="63"/>
-      <c r="AC38" s="63"/>
-      <c r="AD38" s="63"/>
-      <c r="AE38" s="63"/>
-      <c r="AF38" s="63"/>
-      <c r="AG38" s="63"/>
-      <c r="AH38" s="63"/>
-      <c r="AI38" s="63"/>
-      <c r="AJ38" s="63"/>
-      <c r="AK38" s="63"/>
-      <c r="BA38" s="64"/>
+      <c r="A38" s="210" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" s="211"/>
+      <c r="C38" s="211"/>
+      <c r="D38" s="211"/>
+      <c r="E38" s="211"/>
+      <c r="F38" s="211"/>
+      <c r="G38" s="211"/>
+      <c r="H38" s="211"/>
+      <c r="I38" s="211"/>
+      <c r="J38" s="211"/>
+      <c r="K38" s="211"/>
+      <c r="L38" s="211"/>
+      <c r="M38" s="211"/>
+      <c r="N38" s="211"/>
+      <c r="O38" s="211"/>
+      <c r="P38" s="211"/>
+      <c r="Q38" s="211"/>
+      <c r="R38" s="211"/>
+      <c r="S38" s="211"/>
+      <c r="T38" s="211"/>
+      <c r="U38" s="211"/>
+      <c r="V38" s="211"/>
+      <c r="W38" s="211"/>
+      <c r="X38" s="211"/>
+      <c r="Y38" s="211"/>
+      <c r="Z38" s="211"/>
+      <c r="AA38" s="211"/>
+      <c r="AB38" s="211"/>
+      <c r="AC38" s="211"/>
+      <c r="AD38" s="211"/>
+      <c r="AE38" s="211"/>
+      <c r="AF38" s="211"/>
+      <c r="AG38" s="211"/>
+      <c r="AH38" s="211"/>
+      <c r="AI38" s="211"/>
+      <c r="AJ38" s="211"/>
+      <c r="AK38" s="211"/>
+      <c r="AL38" s="211"/>
+      <c r="AM38" s="211"/>
+      <c r="AN38" s="211"/>
+      <c r="AO38" s="211"/>
+      <c r="AP38" s="211"/>
+      <c r="AQ38" s="211"/>
+      <c r="AR38" s="211"/>
+      <c r="AS38" s="211"/>
+      <c r="AT38" s="211"/>
+      <c r="AU38" s="211"/>
+      <c r="AV38" s="211"/>
+      <c r="AW38" s="211"/>
+      <c r="AX38" s="211"/>
+      <c r="AY38" s="211"/>
+      <c r="AZ38" s="211"/>
+      <c r="BA38" s="212"/>
     </row>
     <row r="39" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A39" s="62"/>
-      <c r="B39" s="63"/>
-      <c r="C39" s="63"/>
-      <c r="D39" s="63"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="63"/>
-      <c r="I39" s="63"/>
-      <c r="J39" s="63"/>
-      <c r="K39" s="63"/>
-      <c r="L39" s="63"/>
-      <c r="M39" s="63"/>
-      <c r="N39" s="63"/>
-      <c r="O39" s="63"/>
-      <c r="P39" s="63"/>
-      <c r="Q39" s="63"/>
-      <c r="R39" s="63"/>
-      <c r="S39" s="63"/>
-      <c r="T39" s="63"/>
-      <c r="U39" s="63"/>
-      <c r="V39" s="63"/>
-      <c r="W39" s="63"/>
-      <c r="X39" s="63"/>
-      <c r="Y39" s="63"/>
-      <c r="Z39" s="63"/>
-      <c r="AA39" s="63"/>
-      <c r="AB39" s="63"/>
-      <c r="AC39" s="63"/>
-      <c r="AD39" s="63"/>
-      <c r="AE39" s="63"/>
-      <c r="AF39" s="63"/>
-      <c r="AG39" s="63"/>
-      <c r="AH39" s="63"/>
+      <c r="A39" s="65"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="66"/>
+      <c r="J39" s="66"/>
+      <c r="K39" s="66"/>
+      <c r="L39" s="66"/>
+      <c r="M39" s="66"/>
+      <c r="N39" s="66"/>
+      <c r="O39" s="66"/>
+      <c r="P39" s="66"/>
+      <c r="Q39" s="66"/>
+      <c r="R39" s="66"/>
+      <c r="S39" s="66"/>
+      <c r="T39" s="66"/>
+      <c r="U39" s="66"/>
+      <c r="V39" s="66"/>
+      <c r="W39" s="66"/>
+      <c r="X39" s="66"/>
+      <c r="Y39" s="66"/>
+      <c r="Z39" s="66"/>
+      <c r="AA39" s="66"/>
+      <c r="AB39" s="66"/>
+      <c r="AC39" s="66"/>
+      <c r="AD39" s="66"/>
+      <c r="AE39" s="66"/>
+      <c r="AF39" s="66"/>
+      <c r="AG39" s="66"/>
+      <c r="AH39" s="66"/>
       <c r="AI39" s="63"/>
       <c r="AJ39" s="63"/>
       <c r="AK39" s="63"/>
@@ -6316,139 +6437,122 @@
       <c r="BA42" s="64"/>
     </row>
     <row r="43" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A43" s="67"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="68"/>
-      <c r="L43" s="68"/>
-      <c r="M43" s="68"/>
-      <c r="N43" s="68"/>
-      <c r="O43" s="68"/>
-      <c r="P43" s="68"/>
-      <c r="Q43" s="68"/>
-      <c r="R43" s="68"/>
-      <c r="S43" s="68"/>
-      <c r="T43" s="68"/>
-      <c r="U43" s="68"/>
-      <c r="V43" s="68"/>
-      <c r="W43" s="68"/>
-      <c r="X43" s="68"/>
-      <c r="Y43" s="68"/>
-      <c r="Z43" s="68"/>
-      <c r="AA43" s="68"/>
-      <c r="AB43" s="68"/>
-      <c r="AC43" s="68"/>
-      <c r="AD43" s="68"/>
-      <c r="AE43" s="68"/>
-      <c r="AF43" s="68"/>
-      <c r="AG43" s="68"/>
-      <c r="AH43" s="68"/>
-      <c r="AI43" s="68"/>
-      <c r="AJ43" s="68"/>
+      <c r="A43" s="62"/>
+      <c r="B43" s="63"/>
+      <c r="C43" s="63"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
+      <c r="F43" s="63"/>
+      <c r="G43" s="63"/>
+      <c r="H43" s="63"/>
+      <c r="I43" s="63"/>
+      <c r="J43" s="63"/>
+      <c r="K43" s="63"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="63"/>
+      <c r="N43" s="63"/>
+      <c r="O43" s="63"/>
+      <c r="P43" s="63"/>
+      <c r="Q43" s="63"/>
+      <c r="R43" s="63"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="63"/>
+      <c r="U43" s="63"/>
+      <c r="V43" s="63"/>
+      <c r="W43" s="63"/>
+      <c r="X43" s="63"/>
+      <c r="Y43" s="63"/>
+      <c r="Z43" s="63"/>
+      <c r="AA43" s="63"/>
+      <c r="AB43" s="63"/>
+      <c r="AC43" s="63"/>
+      <c r="AD43" s="63"/>
+      <c r="AE43" s="63"/>
+      <c r="AF43" s="63"/>
+      <c r="AG43" s="63"/>
+      <c r="AH43" s="63"/>
+      <c r="AI43" s="63"/>
+      <c r="AJ43" s="63"/>
       <c r="AK43" s="63"/>
       <c r="BA43" s="64"/>
     </row>
     <row r="44" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A44" s="210" t="s">
-        <v>133</v>
-      </c>
-      <c r="B44" s="211"/>
-      <c r="C44" s="211"/>
-      <c r="D44" s="211"/>
-      <c r="E44" s="211"/>
-      <c r="F44" s="211"/>
-      <c r="G44" s="211"/>
-      <c r="H44" s="211"/>
-      <c r="I44" s="211"/>
-      <c r="J44" s="211"/>
-      <c r="K44" s="211"/>
-      <c r="L44" s="211"/>
-      <c r="M44" s="211"/>
-      <c r="N44" s="211"/>
-      <c r="O44" s="211"/>
-      <c r="P44" s="211"/>
-      <c r="Q44" s="211"/>
-      <c r="R44" s="211"/>
-      <c r="S44" s="211"/>
-      <c r="T44" s="211"/>
-      <c r="U44" s="211"/>
-      <c r="V44" s="211"/>
-      <c r="W44" s="211"/>
-      <c r="X44" s="211"/>
-      <c r="Y44" s="211"/>
-      <c r="Z44" s="211"/>
-      <c r="AA44" s="211"/>
-      <c r="AB44" s="211"/>
-      <c r="AC44" s="211"/>
-      <c r="AD44" s="211"/>
-      <c r="AE44" s="211"/>
-      <c r="AF44" s="211"/>
-      <c r="AG44" s="211"/>
-      <c r="AH44" s="211"/>
-      <c r="AI44" s="211"/>
-      <c r="AJ44" s="211"/>
-      <c r="AK44" s="211"/>
-      <c r="AL44" s="211"/>
-      <c r="AM44" s="211"/>
-      <c r="AN44" s="211"/>
-      <c r="AO44" s="211"/>
-      <c r="AP44" s="211"/>
-      <c r="AQ44" s="211"/>
-      <c r="AR44" s="211"/>
-      <c r="AS44" s="211"/>
-      <c r="AT44" s="211"/>
-      <c r="AU44" s="211"/>
-      <c r="AV44" s="211"/>
-      <c r="AW44" s="211"/>
-      <c r="AX44" s="211"/>
-      <c r="AY44" s="211"/>
-      <c r="AZ44" s="211"/>
-      <c r="BA44" s="211"/>
+      <c r="A44" s="62"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
+      <c r="K44" s="63"/>
+      <c r="L44" s="63"/>
+      <c r="M44" s="63"/>
+      <c r="N44" s="63"/>
+      <c r="O44" s="63"/>
+      <c r="P44" s="63"/>
+      <c r="Q44" s="63"/>
+      <c r="R44" s="63"/>
+      <c r="S44" s="63"/>
+      <c r="T44" s="63"/>
+      <c r="U44" s="63"/>
+      <c r="V44" s="63"/>
+      <c r="W44" s="63"/>
+      <c r="X44" s="63"/>
+      <c r="Y44" s="63"/>
+      <c r="Z44" s="63"/>
+      <c r="AA44" s="63"/>
+      <c r="AB44" s="63"/>
+      <c r="AC44" s="63"/>
+      <c r="AD44" s="63"/>
+      <c r="AE44" s="63"/>
+      <c r="AF44" s="63"/>
+      <c r="AG44" s="63"/>
+      <c r="AH44" s="63"/>
+      <c r="AI44" s="63"/>
+      <c r="AJ44" s="63"/>
+      <c r="AK44" s="63"/>
+      <c r="BA44" s="64"/>
     </row>
     <row r="45" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A45" s="65"/>
-      <c r="B45" s="66"/>
-      <c r="C45" s="66"/>
-      <c r="D45" s="66"/>
-      <c r="E45" s="66"/>
-      <c r="F45" s="66"/>
-      <c r="G45" s="66"/>
-      <c r="H45" s="66"/>
-      <c r="I45" s="66"/>
-      <c r="J45" s="66"/>
-      <c r="K45" s="66"/>
-      <c r="L45" s="66"/>
-      <c r="M45" s="66"/>
-      <c r="N45" s="66"/>
-      <c r="O45" s="66"/>
-      <c r="P45" s="66"/>
-      <c r="Q45" s="66"/>
-      <c r="R45" s="66"/>
-      <c r="S45" s="66"/>
-      <c r="T45" s="66"/>
-      <c r="U45" s="66"/>
-      <c r="V45" s="66"/>
-      <c r="W45" s="66"/>
-      <c r="X45" s="66"/>
-      <c r="Y45" s="66"/>
-      <c r="Z45" s="66"/>
-      <c r="AA45" s="66"/>
-      <c r="AB45" s="66"/>
-      <c r="AC45" s="66"/>
-      <c r="AD45" s="66"/>
-      <c r="AE45" s="66"/>
-      <c r="AF45" s="66"/>
-      <c r="AG45" s="66"/>
-      <c r="AH45" s="66"/>
-      <c r="AI45" s="66"/>
-      <c r="AJ45" s="66"/>
+      <c r="A45" s="62"/>
+      <c r="B45" s="63"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="63"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="63"/>
+      <c r="L45" s="63"/>
+      <c r="M45" s="63"/>
+      <c r="N45" s="63"/>
+      <c r="O45" s="63"/>
+      <c r="P45" s="63"/>
+      <c r="Q45" s="63"/>
+      <c r="R45" s="63"/>
+      <c r="S45" s="63"/>
+      <c r="T45" s="63"/>
+      <c r="U45" s="63"/>
+      <c r="V45" s="63"/>
+      <c r="W45" s="63"/>
+      <c r="X45" s="63"/>
+      <c r="Y45" s="63"/>
+      <c r="Z45" s="63"/>
+      <c r="AA45" s="63"/>
+      <c r="AB45" s="63"/>
+      <c r="AC45" s="63"/>
+      <c r="AD45" s="63"/>
+      <c r="AE45" s="63"/>
+      <c r="AF45" s="63"/>
+      <c r="AG45" s="63"/>
+      <c r="AH45" s="63"/>
+      <c r="AI45" s="63"/>
+      <c r="AJ45" s="63"/>
       <c r="AK45" s="63"/>
       <c r="BA45" s="64"/>
     </row>
@@ -6529,41 +6633,214 @@
       <c r="AH47" s="68"/>
       <c r="AI47" s="68"/>
       <c r="AJ47" s="68"/>
-      <c r="AK47" s="68"/>
-      <c r="AL47" s="53"/>
-      <c r="AM47" s="53"/>
-      <c r="AN47" s="53"/>
-      <c r="AO47" s="53"/>
-      <c r="AP47" s="53"/>
-      <c r="AQ47" s="53"/>
-      <c r="AR47" s="53"/>
-      <c r="AS47" s="53"/>
-      <c r="AT47" s="53"/>
-      <c r="AU47" s="53"/>
-      <c r="AV47" s="53"/>
-      <c r="AW47" s="53"/>
-      <c r="AX47" s="53"/>
-      <c r="AY47" s="53"/>
-      <c r="AZ47" s="53"/>
-      <c r="BA47" s="69"/>
-    </row>
-    <row r="48" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="49" ht="21.95" customHeight="1"/>
-    <row r="50" ht="21.95" customHeight="1"/>
-    <row r="51" ht="21.95" customHeight="1"/>
-    <row r="52" ht="21.95" customHeight="1"/>
-    <row r="53" ht="21.95" customHeight="1"/>
-    <row r="54" ht="21.95" customHeight="1"/>
-    <row r="55" ht="21.95" customHeight="1"/>
-    <row r="56" ht="21.95" customHeight="1"/>
-    <row r="57" ht="21.95" customHeight="1"/>
-    <row r="58" ht="21.95" customHeight="1"/>
-    <row r="59" ht="21.95" customHeight="1"/>
-    <row r="60" ht="21.95" customHeight="1"/>
-    <row r="61" ht="21.95" customHeight="1"/>
-    <row r="62" ht="21.95" customHeight="1"/>
-    <row r="63" ht="21.95" customHeight="1"/>
-    <row r="64" ht="21.95" customHeight="1"/>
+      <c r="AK47" s="63"/>
+      <c r="BA47" s="64"/>
+    </row>
+    <row r="48" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A48" s="210" t="s">
+        <v>133</v>
+      </c>
+      <c r="B48" s="211"/>
+      <c r="C48" s="211"/>
+      <c r="D48" s="211"/>
+      <c r="E48" s="211"/>
+      <c r="F48" s="211"/>
+      <c r="G48" s="211"/>
+      <c r="H48" s="211"/>
+      <c r="I48" s="211"/>
+      <c r="J48" s="211"/>
+      <c r="K48" s="211"/>
+      <c r="L48" s="211"/>
+      <c r="M48" s="211"/>
+      <c r="N48" s="211"/>
+      <c r="O48" s="211"/>
+      <c r="P48" s="211"/>
+      <c r="Q48" s="211"/>
+      <c r="R48" s="211"/>
+      <c r="S48" s="211"/>
+      <c r="T48" s="211"/>
+      <c r="U48" s="211"/>
+      <c r="V48" s="211"/>
+      <c r="W48" s="211"/>
+      <c r="X48" s="211"/>
+      <c r="Y48" s="211"/>
+      <c r="Z48" s="211"/>
+      <c r="AA48" s="211"/>
+      <c r="AB48" s="211"/>
+      <c r="AC48" s="211"/>
+      <c r="AD48" s="211"/>
+      <c r="AE48" s="211"/>
+      <c r="AF48" s="211"/>
+      <c r="AG48" s="211"/>
+      <c r="AH48" s="211"/>
+      <c r="AI48" s="211"/>
+      <c r="AJ48" s="211"/>
+      <c r="AK48" s="211"/>
+      <c r="AL48" s="211"/>
+      <c r="AM48" s="211"/>
+      <c r="AN48" s="211"/>
+      <c r="AO48" s="211"/>
+      <c r="AP48" s="211"/>
+      <c r="AQ48" s="211"/>
+      <c r="AR48" s="211"/>
+      <c r="AS48" s="211"/>
+      <c r="AT48" s="211"/>
+      <c r="AU48" s="211"/>
+      <c r="AV48" s="211"/>
+      <c r="AW48" s="211"/>
+      <c r="AX48" s="211"/>
+      <c r="AY48" s="211"/>
+      <c r="AZ48" s="211"/>
+      <c r="BA48" s="211"/>
+    </row>
+    <row r="49" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A49" s="65"/>
+      <c r="B49" s="66"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66"/>
+      <c r="G49" s="66"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="66"/>
+      <c r="J49" s="66"/>
+      <c r="K49" s="66"/>
+      <c r="L49" s="66"/>
+      <c r="M49" s="66"/>
+      <c r="N49" s="66"/>
+      <c r="O49" s="66"/>
+      <c r="P49" s="66"/>
+      <c r="Q49" s="66"/>
+      <c r="R49" s="66"/>
+      <c r="S49" s="66"/>
+      <c r="T49" s="66"/>
+      <c r="U49" s="66"/>
+      <c r="V49" s="66"/>
+      <c r="W49" s="66"/>
+      <c r="X49" s="66"/>
+      <c r="Y49" s="66"/>
+      <c r="Z49" s="66"/>
+      <c r="AA49" s="66"/>
+      <c r="AB49" s="66"/>
+      <c r="AC49" s="66"/>
+      <c r="AD49" s="66"/>
+      <c r="AE49" s="66"/>
+      <c r="AF49" s="66"/>
+      <c r="AG49" s="66"/>
+      <c r="AH49" s="66"/>
+      <c r="AI49" s="66"/>
+      <c r="AJ49" s="66"/>
+      <c r="AK49" s="63"/>
+      <c r="BA49" s="64"/>
+    </row>
+    <row r="50" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A50" s="62"/>
+      <c r="B50" s="63"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="63"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="63"/>
+      <c r="J50" s="63"/>
+      <c r="K50" s="63"/>
+      <c r="L50" s="63"/>
+      <c r="M50" s="63"/>
+      <c r="N50" s="63"/>
+      <c r="O50" s="63"/>
+      <c r="P50" s="63"/>
+      <c r="Q50" s="63"/>
+      <c r="R50" s="63"/>
+      <c r="S50" s="63"/>
+      <c r="T50" s="63"/>
+      <c r="U50" s="63"/>
+      <c r="V50" s="63"/>
+      <c r="W50" s="63"/>
+      <c r="X50" s="63"/>
+      <c r="Y50" s="63"/>
+      <c r="Z50" s="63"/>
+      <c r="AA50" s="63"/>
+      <c r="AB50" s="63"/>
+      <c r="AC50" s="63"/>
+      <c r="AD50" s="63"/>
+      <c r="AE50" s="63"/>
+      <c r="AF50" s="63"/>
+      <c r="AG50" s="63"/>
+      <c r="AH50" s="63"/>
+      <c r="AI50" s="63"/>
+      <c r="AJ50" s="63"/>
+      <c r="AK50" s="63"/>
+      <c r="BA50" s="64"/>
+    </row>
+    <row r="51" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A51" s="67"/>
+      <c r="B51" s="68"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="68"/>
+      <c r="E51" s="68"/>
+      <c r="F51" s="68"/>
+      <c r="G51" s="68"/>
+      <c r="H51" s="68"/>
+      <c r="I51" s="68"/>
+      <c r="J51" s="68"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="68"/>
+      <c r="M51" s="68"/>
+      <c r="N51" s="68"/>
+      <c r="O51" s="68"/>
+      <c r="P51" s="68"/>
+      <c r="Q51" s="68"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="68"/>
+      <c r="T51" s="68"/>
+      <c r="U51" s="68"/>
+      <c r="V51" s="68"/>
+      <c r="W51" s="68"/>
+      <c r="X51" s="68"/>
+      <c r="Y51" s="68"/>
+      <c r="Z51" s="68"/>
+      <c r="AA51" s="68"/>
+      <c r="AB51" s="68"/>
+      <c r="AC51" s="68"/>
+      <c r="AD51" s="68"/>
+      <c r="AE51" s="68"/>
+      <c r="AF51" s="68"/>
+      <c r="AG51" s="68"/>
+      <c r="AH51" s="68"/>
+      <c r="AI51" s="68"/>
+      <c r="AJ51" s="68"/>
+      <c r="AK51" s="68"/>
+      <c r="AL51" s="53"/>
+      <c r="AM51" s="53"/>
+      <c r="AN51" s="53"/>
+      <c r="AO51" s="53"/>
+      <c r="AP51" s="53"/>
+      <c r="AQ51" s="53"/>
+      <c r="AR51" s="53"/>
+      <c r="AS51" s="53"/>
+      <c r="AT51" s="53"/>
+      <c r="AU51" s="53"/>
+      <c r="AV51" s="53"/>
+      <c r="AW51" s="53"/>
+      <c r="AX51" s="53"/>
+      <c r="AY51" s="53"/>
+      <c r="AZ51" s="53"/>
+      <c r="BA51" s="69"/>
+    </row>
+    <row r="52" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="53" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="54" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="55" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="56" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="57" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="58" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="59" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="60" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="61" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="62" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="63" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="64" spans="1:53" ht="21.95" customHeight="1"/>
     <row r="65" ht="21.95" customHeight="1"/>
     <row r="66" ht="21.95" customHeight="1"/>
     <row r="67" ht="21.95" customHeight="1"/>
@@ -6602,24 +6879,28 @@
     <row r="100" ht="21.95" customHeight="1"/>
     <row r="101" ht="21.95" customHeight="1"/>
     <row r="102" ht="21.95" customHeight="1"/>
-    <row r="103" ht="18" customHeight="1"/>
+    <row r="103" ht="21.95" customHeight="1"/>
     <row r="104" ht="21.95" customHeight="1"/>
     <row r="105" ht="21.95" customHeight="1"/>
     <row r="106" ht="21.95" customHeight="1"/>
-    <row r="107" ht="21.95" customHeight="1"/>
+    <row r="107" ht="18" customHeight="1"/>
     <row r="108" ht="21.95" customHeight="1"/>
     <row r="109" ht="21.95" customHeight="1"/>
     <row r="110" ht="21.95" customHeight="1"/>
-    <row r="111" ht="87.75" customHeight="1"/>
-    <row r="112" ht="18" customHeight="1"/>
+    <row r="111" ht="21.95" customHeight="1"/>
+    <row r="112" ht="21.95" customHeight="1"/>
     <row r="113" ht="21.95" customHeight="1"/>
     <row r="114" ht="21.95" customHeight="1"/>
-    <row r="115" ht="21.95" customHeight="1"/>
+    <row r="115" ht="87.75" customHeight="1"/>
+    <row r="116" ht="18" customHeight="1"/>
+    <row r="117" ht="21.95" customHeight="1"/>
+    <row r="118" ht="21.95" customHeight="1"/>
+    <row r="119" ht="21.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A9:BA9"/>
-    <mergeCell ref="A35:BA35"/>
-    <mergeCell ref="A44:BA44"/>
+    <mergeCell ref="A38:BA38"/>
+    <mergeCell ref="A48:BA48"/>
     <mergeCell ref="AO1:AS1"/>
     <mergeCell ref="AT1:BA1"/>
     <mergeCell ref="A5:F5"/>
@@ -6630,7 +6911,7 @@
   <phoneticPr fontId="8"/>
   <dataValidations count="2">
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1:AS1" xr:uid="{0B6E2588-4DB7-48F6-A034-AB68AD3491CD}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:O1 I1:L1 A45:AK47 G5:G6 V1 AC1 AE1 A36:AK43 A10:AK34" xr:uid="{94DF0F81-F128-419A-A32E-C8512CFD4DD1}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:O1 I1:L1 A49:AK51 G5:G6 V1 AC1 AE1 A39:AK47 A10:AK37" xr:uid="{94DF0F81-F128-419A-A32E-C8512CFD4DD1}"/>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -6652,19 +6933,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="117" t="s">
+      <c r="B1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="105"/>
-      <c r="F1" s="117" t="s">
+      <c r="E1" s="88"/>
+      <c r="F1" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="105"/>
+      <c r="G1" s="88"/>
       <c r="H1" s="37" t="s">
         <v>8</v>
       </c>
@@ -6676,190 +6957,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="111"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="118" t="s">
+      <c r="A2" s="99"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="119"/>
-      <c r="F2" s="118" t="s">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="119"/>
-      <c r="H2" s="122">
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
         <v>45806</v>
       </c>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="100"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="111"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="113"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="101"/>
+      <c r="A3" s="99"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="114"/>
-      <c r="B4" s="115"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="102"/>
+      <c r="A4" s="102"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="104"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="106" t="s">
+      <c r="B5" s="87"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="107"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="90"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="90" t="s">
+      <c r="B6" s="92"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="84"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="95"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="90" t="s">
+      <c r="B7" s="92"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="84"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="95"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="81"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="90" t="s">
+      <c r="B8" s="92"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="84"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="91" t="s">
+      <c r="A9" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="82"/>
-      <c r="D9" s="83" t="s">
+      <c r="C9" s="93"/>
+      <c r="D9" s="111" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="96"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="94" t="s">
+      <c r="A10" s="118"/>
+      <c r="B10" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="82"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="84"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="94" t="s">
+      <c r="A11" s="119"/>
+      <c r="B11" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="82"/>
-      <c r="D11" s="90" t="s">
+      <c r="C11" s="93"/>
+      <c r="D11" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="84"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="80" t="s">
+      <c r="A12" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="81"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="83" t="s">
+      <c r="B12" s="92"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="84"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="87"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="89"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="113"/>
+      <c r="I13" s="113"/>
+      <c r="J13" s="116"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7850,18 +8131,6 @@
     <row r="1000" s="39" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -7877,6 +8146,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -10801,20 +11082,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="148" t="s">
+      <c r="D5" s="156" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="149"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -10828,19 +11109,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="150"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="153"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -10852,7 +11133,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="154"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -10864,7 +11145,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="154"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -10876,7 +11157,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="154"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -10888,7 +11169,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="154"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -10900,7 +11181,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="154"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -10912,7 +11193,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="154"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -10926,7 +11207,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="150"/>
+      <c r="J14" s="146"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="147" t="s">
@@ -10934,7 +11215,7 @@
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="74"/>
-      <c r="D15" s="155" t="s">
+      <c r="D15" s="145" t="s">
         <v>73</v>
       </c>
       <c r="E15" s="73"/>
@@ -10966,14 +11247,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="156" t="s">
+      <c r="H16" s="148" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="73"/>
-      <c r="J16" s="150"/>
+      <c r="J16" s="146"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="146">
+      <c r="A17" s="144">
         <v>1</v>
       </c>
       <c r="B17" s="73"/>
@@ -10988,12 +11269,12 @@
         <v>82</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="155"/>
+      <c r="H17" s="145"/>
       <c r="I17" s="73"/>
-      <c r="J17" s="150"/>
+      <c r="J17" s="146"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="146">
+      <c r="A18" s="144">
         <v>2</v>
       </c>
       <c r="B18" s="73"/>
@@ -11010,12 +11291,12 @@
       <c r="G18" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="155"/>
+      <c r="H18" s="145"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="150"/>
+      <c r="J18" s="146"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="146">
+      <c r="A19" s="144">
         <v>3</v>
       </c>
       <c r="B19" s="73"/>
@@ -11030,12 +11311,12 @@
       <c r="G19" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="155"/>
+      <c r="H19" s="145"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="150"/>
+      <c r="J19" s="146"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="146">
+      <c r="A20" s="144">
         <v>4</v>
       </c>
       <c r="B20" s="73"/>
@@ -11052,12 +11333,12 @@
       <c r="G20" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="155"/>
+      <c r="H20" s="145"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="150"/>
+      <c r="J20" s="146"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="146">
+      <c r="A21" s="144">
         <v>5</v>
       </c>
       <c r="B21" s="73"/>
@@ -11074,12 +11355,12 @@
       <c r="G21" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="155"/>
+      <c r="H21" s="145"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="150"/>
+      <c r="J21" s="146"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="146">
+      <c r="A22" s="144">
         <v>6</v>
       </c>
       <c r="B22" s="73"/>
@@ -11094,12 +11375,12 @@
         <v>61</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="155"/>
+      <c r="H22" s="145"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="150"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="146">
+      <c r="A23" s="144">
         <v>7</v>
       </c>
       <c r="B23" s="73"/>
@@ -11114,9 +11395,9 @@
         <v>61</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="158"/>
-      <c r="J23" s="159"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
       <c r="A24" s="147"/>
@@ -11128,13 +11409,13 @@
       <c r="G24" s="73"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73"/>
-      <c r="J24" s="150"/>
+      <c r="J24" s="146"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
       <c r="A25" s="147"/>
       <c r="B25" s="73"/>
       <c r="C25" s="74"/>
-      <c r="D25" s="155"/>
+      <c r="D25" s="145"/>
       <c r="E25" s="73"/>
       <c r="F25" s="73"/>
       <c r="G25" s="73"/>
@@ -11150,93 +11431,93 @@
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="156"/>
+      <c r="H26" s="148"/>
       <c r="I26" s="73"/>
-      <c r="J26" s="150"/>
+      <c r="J26" s="146"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="146"/>
+      <c r="A27" s="144"/>
       <c r="B27" s="73"/>
       <c r="C27" s="74"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="155"/>
+      <c r="H27" s="145"/>
       <c r="I27" s="73"/>
-      <c r="J27" s="150"/>
+      <c r="J27" s="146"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="146"/>
+      <c r="A28" s="144"/>
       <c r="B28" s="73"/>
       <c r="C28" s="74"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="155"/>
+      <c r="H28" s="145"/>
       <c r="I28" s="73"/>
-      <c r="J28" s="150"/>
+      <c r="J28" s="146"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="146"/>
+      <c r="A29" s="144"/>
       <c r="B29" s="73"/>
       <c r="C29" s="74"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
-      <c r="H29" s="155"/>
+      <c r="H29" s="145"/>
       <c r="I29" s="73"/>
-      <c r="J29" s="150"/>
+      <c r="J29" s="146"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="146"/>
+      <c r="A30" s="144"/>
       <c r="B30" s="73"/>
       <c r="C30" s="74"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="155"/>
+      <c r="H30" s="145"/>
       <c r="I30" s="73"/>
-      <c r="J30" s="150"/>
+      <c r="J30" s="146"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="146"/>
+      <c r="A31" s="144"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="155"/>
+      <c r="H31" s="145"/>
       <c r="I31" s="73"/>
-      <c r="J31" s="150"/>
+      <c r="J31" s="146"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="146"/>
+      <c r="A32" s="144"/>
       <c r="B32" s="73"/>
       <c r="C32" s="74"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="155"/>
+      <c r="H32" s="145"/>
       <c r="I32" s="73"/>
-      <c r="J32" s="150"/>
+      <c r="J32" s="146"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="160"/>
-      <c r="B33" s="158"/>
-      <c r="C33" s="161"/>
+      <c r="A33" s="149"/>
+      <c r="B33" s="150"/>
+      <c r="C33" s="151"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
-      <c r="H33" s="157"/>
-      <c r="I33" s="158"/>
-      <c r="J33" s="159"/>
+      <c r="H33" s="152"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="153"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
       <c r="A34" s="147"/>
@@ -11248,13 +11529,13 @@
       <c r="G34" s="73"/>
       <c r="H34" s="73"/>
       <c r="I34" s="73"/>
-      <c r="J34" s="150"/>
+      <c r="J34" s="146"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
       <c r="A35" s="147"/>
       <c r="B35" s="73"/>
       <c r="C35" s="74"/>
-      <c r="D35" s="155"/>
+      <c r="D35" s="145"/>
       <c r="E35" s="73"/>
       <c r="F35" s="73"/>
       <c r="G35" s="73"/>
@@ -11270,69 +11551,69 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
-      <c r="H36" s="156"/>
+      <c r="H36" s="148"/>
       <c r="I36" s="73"/>
-      <c r="J36" s="150"/>
+      <c r="J36" s="146"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="146"/>
+      <c r="A37" s="144"/>
       <c r="B37" s="73"/>
       <c r="C37" s="74"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="155"/>
+      <c r="H37" s="145"/>
       <c r="I37" s="73"/>
-      <c r="J37" s="150"/>
+      <c r="J37" s="146"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="146"/>
+      <c r="A38" s="144"/>
       <c r="B38" s="73"/>
       <c r="C38" s="74"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="155"/>
+      <c r="H38" s="145"/>
       <c r="I38" s="73"/>
-      <c r="J38" s="150"/>
+      <c r="J38" s="146"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="146"/>
+      <c r="A39" s="144"/>
       <c r="B39" s="73"/>
       <c r="C39" s="74"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="155"/>
+      <c r="H39" s="145"/>
       <c r="I39" s="73"/>
-      <c r="J39" s="150"/>
+      <c r="J39" s="146"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="146"/>
+      <c r="A40" s="144"/>
       <c r="B40" s="73"/>
       <c r="C40" s="74"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="155"/>
+      <c r="H40" s="145"/>
       <c r="I40" s="73"/>
-      <c r="J40" s="150"/>
+      <c r="J40" s="146"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="146"/>
+      <c r="A41" s="144"/>
       <c r="B41" s="73"/>
       <c r="C41" s="74"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="155"/>
+      <c r="H41" s="145"/>
       <c r="I41" s="73"/>
-      <c r="J41" s="150"/>
+      <c r="J41" s="146"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12295,50 +12576,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12355,11 +12597,50 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12450,20 +12731,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="148" t="s">
+      <c r="D5" s="156" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="149"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -12477,19 +12758,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="150"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="153"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -12501,7 +12782,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="154"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -12513,7 +12794,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="154"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -12525,7 +12806,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="154"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -12537,7 +12818,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="154"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -12549,7 +12830,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="154"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -12561,7 +12842,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="154"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -12575,7 +12856,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="150"/>
+      <c r="J14" s="146"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="147" t="s">
@@ -12583,7 +12864,7 @@
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="74"/>
-      <c r="D15" s="155" t="s">
+      <c r="D15" s="145" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="73"/>
@@ -12615,14 +12896,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="156" t="s">
+      <c r="H16" s="148" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="73"/>
-      <c r="J16" s="150"/>
+      <c r="J16" s="146"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="146">
+      <c r="A17" s="144">
         <v>1</v>
       </c>
       <c r="B17" s="73"/>
@@ -12639,83 +12920,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="155" t="s">
+      <c r="H17" s="145" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="73"/>
-      <c r="J17" s="150"/>
+      <c r="J17" s="146"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="146"/>
+      <c r="A18" s="144"/>
       <c r="B18" s="73"/>
       <c r="C18" s="74"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="155"/>
+      <c r="H18" s="145"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="150"/>
+      <c r="J18" s="146"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="146"/>
+      <c r="A19" s="144"/>
       <c r="B19" s="73"/>
       <c r="C19" s="74"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="155"/>
+      <c r="H19" s="145"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="150"/>
+      <c r="J19" s="146"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="146"/>
+      <c r="A20" s="144"/>
       <c r="B20" s="73"/>
       <c r="C20" s="74"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="155"/>
+      <c r="H20" s="145"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="150"/>
+      <c r="J20" s="146"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="146"/>
+      <c r="A21" s="144"/>
       <c r="B21" s="73"/>
       <c r="C21" s="74"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="155"/>
+      <c r="H21" s="145"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="150"/>
+      <c r="J21" s="146"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="146"/>
+      <c r="A22" s="144"/>
       <c r="B22" s="73"/>
       <c r="C22" s="74"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="155"/>
+      <c r="H22" s="145"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="150"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="160"/>
-      <c r="B23" s="158"/>
-      <c r="C23" s="161"/>
+      <c r="A23" s="149"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="151"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="158"/>
-      <c r="J23" s="159"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13696,22 +13977,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -13727,6 +13992,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13817,20 +14098,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="148" t="s">
+      <c r="D5" s="156" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="149"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -13844,19 +14125,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="150"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="153"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -13868,7 +14149,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="154"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -13880,7 +14161,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="154"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -13892,7 +14173,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="154"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -13904,7 +14185,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="154"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -13916,7 +14197,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="154"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -13928,7 +14209,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="154"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -13942,7 +14223,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="150"/>
+      <c r="J14" s="146"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="147" t="s">
@@ -13950,7 +14231,7 @@
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="74"/>
-      <c r="D15" s="155" t="s">
+      <c r="D15" s="145" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="73"/>
@@ -13982,14 +14263,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="156" t="s">
+      <c r="H16" s="148" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="73"/>
-      <c r="J16" s="150"/>
+      <c r="J16" s="146"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="146">
+      <c r="A17" s="144">
         <v>1</v>
       </c>
       <c r="B17" s="73"/>
@@ -14006,83 +14287,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="155" t="s">
+      <c r="H17" s="145" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="73"/>
-      <c r="J17" s="150"/>
+      <c r="J17" s="146"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="146"/>
+      <c r="A18" s="144"/>
       <c r="B18" s="73"/>
       <c r="C18" s="74"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="155"/>
+      <c r="H18" s="145"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="150"/>
+      <c r="J18" s="146"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="146"/>
+      <c r="A19" s="144"/>
       <c r="B19" s="73"/>
       <c r="C19" s="74"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="155"/>
+      <c r="H19" s="145"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="150"/>
+      <c r="J19" s="146"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="146"/>
+      <c r="A20" s="144"/>
       <c r="B20" s="73"/>
       <c r="C20" s="74"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="155"/>
+      <c r="H20" s="145"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="150"/>
+      <c r="J20" s="146"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="146"/>
+      <c r="A21" s="144"/>
       <c r="B21" s="73"/>
       <c r="C21" s="74"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="155"/>
+      <c r="H21" s="145"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="150"/>
+      <c r="J21" s="146"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="146"/>
+      <c r="A22" s="144"/>
       <c r="B22" s="73"/>
       <c r="C22" s="74"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="155"/>
+      <c r="H22" s="145"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="150"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="160"/>
-      <c r="B23" s="158"/>
-      <c r="C23" s="161"/>
+      <c r="A23" s="149"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="151"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="158"/>
-      <c r="J23" s="159"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -15063,22 +15344,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -15094,6 +15359,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -15104,7 +15385,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Z1000"/>
+  <dimension ref="A1:Z1001"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="2.85546875" customWidth="1"/>
@@ -15113,7 +15394,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="178" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="131"/>
@@ -15124,14 +15405,14 @@
       <c r="G1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
       <c r="J1" s="139"/>
       <c r="K1" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
+      <c r="L1" s="155"/>
+      <c r="M1" s="155"/>
       <c r="N1" s="139"/>
       <c r="O1" s="138" t="s">
         <v>8</v>
@@ -15144,7 +15425,7 @@
       <c r="S1" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="149"/>
+      <c r="T1" s="157"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="133"/>
@@ -15156,16 +15437,16 @@
       <c r="G2" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
       <c r="J2" s="141"/>
       <c r="K2" s="140" t="s">
         <v>93</v>
       </c>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
       <c r="N2" s="141"/>
-      <c r="O2" s="169">
+      <c r="O2" s="176">
         <v>45821</v>
       </c>
       <c r="P2" s="141"/>
@@ -15174,7 +15455,7 @@
       </c>
       <c r="R2" s="141"/>
       <c r="S2" s="140"/>
-      <c r="T2" s="153"/>
+      <c r="T2" s="160"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="133"/>
@@ -15196,7 +15477,7 @@
       <c r="Q3" s="142"/>
       <c r="R3" s="134"/>
       <c r="S3" s="142"/>
-      <c r="T3" s="154"/>
+      <c r="T3" s="161"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="135"/>
@@ -15218,33 +15499,33 @@
       <c r="Q4" s="143"/>
       <c r="R4" s="137"/>
       <c r="S4" s="143"/>
-      <c r="T4" s="170"/>
+      <c r="T4" s="177"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="145"/>
+      <c r="B5" s="155"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
       <c r="F5" s="139"/>
-      <c r="G5" s="172" t="s">
+      <c r="G5" s="168" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="145"/>
-      <c r="K5" s="145"/>
-      <c r="L5" s="145"/>
-      <c r="M5" s="145"/>
-      <c r="N5" s="145"/>
-      <c r="O5" s="145"/>
-      <c r="P5" s="145"/>
-      <c r="Q5" s="145"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="145"/>
-      <c r="T5" s="149"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="155"/>
+      <c r="Q5" s="155"/>
+      <c r="R5" s="155"/>
+      <c r="S5" s="155"/>
+      <c r="T5" s="157"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -15255,7 +15536,7 @@
       <c r="D6" s="73"/>
       <c r="E6" s="73"/>
       <c r="F6" s="74"/>
-      <c r="G6" s="155" t="s">
+      <c r="G6" s="145" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="73"/>
@@ -15270,7 +15551,7 @@
       <c r="Q6" s="73"/>
       <c r="R6" s="73"/>
       <c r="S6" s="73"/>
-      <c r="T6" s="150"/>
+      <c r="T6" s="146"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="147" t="s">
@@ -15281,7 +15562,7 @@
       <c r="D7" s="73"/>
       <c r="E7" s="73"/>
       <c r="F7" s="74"/>
-      <c r="G7" s="155" t="s">
+      <c r="G7" s="145" t="s">
         <v>95</v>
       </c>
       <c r="H7" s="73"/>
@@ -15296,7 +15577,7 @@
       <c r="Q7" s="73"/>
       <c r="R7" s="73"/>
       <c r="S7" s="73"/>
-      <c r="T7" s="150"/>
+      <c r="T7" s="146"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -15499,29 +15780,29 @@
         <v>45</v>
       </c>
       <c r="B15" s="74"/>
-      <c r="C15" s="178" t="s">
+      <c r="C15" s="175" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="74"/>
-      <c r="E15" s="156" t="s">
+      <c r="E15" s="148" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="74"/>
-      <c r="G15" s="156" t="s">
+      <c r="G15" s="148" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="73"/>
       <c r="I15" s="74"/>
-      <c r="J15" s="156" t="s">
+      <c r="J15" s="148" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="74"/>
-      <c r="L15" s="156" t="s">
+      <c r="L15" s="148" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="73"/>
       <c r="N15" s="74"/>
-      <c r="O15" s="156" t="s">
+      <c r="O15" s="148" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="73"/>
@@ -15537,27 +15818,27 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A16" s="173">
+      <c r="A16" s="162">
         <v>1</v>
       </c>
       <c r="B16" s="74"/>
-      <c r="C16" s="179" t="s">
+      <c r="C16" s="163" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="74"/>
-      <c r="E16" s="179" t="s">
+      <c r="E16" s="163" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="74"/>
-      <c r="G16" s="162" t="s">
+      <c r="G16" s="180" t="s">
         <v>96</v>
       </c>
       <c r="H16" s="73"/>
       <c r="I16" s="74"/>
-      <c r="J16" s="163" t="s">
+      <c r="J16" s="171" t="s">
         <v>97</v>
       </c>
-      <c r="K16" s="164"/>
+      <c r="K16" s="170"/>
       <c r="L16" s="166" t="s">
         <v>98</v>
       </c>
@@ -15572,10 +15853,10 @@
         <v>45825</v>
       </c>
       <c r="S16" s="32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T16" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U16" s="34"/>
       <c r="V16" s="34"/>
@@ -15585,24 +15866,24 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A17" s="173">
+      <c r="A17" s="162">
         <v>2</v>
       </c>
       <c r="B17" s="74"/>
-      <c r="C17" s="179" t="s">
+      <c r="C17" s="163" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="74"/>
-      <c r="E17" s="179" t="s">
+      <c r="E17" s="163" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="74"/>
-      <c r="G17" s="162" t="s">
+      <c r="G17" s="180" t="s">
         <v>105</v>
       </c>
       <c r="H17" s="73"/>
       <c r="I17" s="74"/>
-      <c r="J17" s="162" t="s">
+      <c r="J17" s="180" t="s">
         <v>106</v>
       </c>
       <c r="K17" s="74"/>
@@ -15620,10 +15901,10 @@
         <v>45825</v>
       </c>
       <c r="S17" s="32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T17" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U17" s="34"/>
       <c r="V17" s="34"/>
@@ -15632,46 +15913,46 @@
       <c r="Y17" s="34"/>
       <c r="Z17" s="34"/>
     </row>
-    <row r="18" spans="1:26" ht="64.5" customHeight="1">
-      <c r="A18" s="173">
+    <row r="18" spans="1:26" ht="54.75" customHeight="1">
+      <c r="A18" s="162">
         <v>3</v>
       </c>
       <c r="B18" s="74"/>
-      <c r="C18" s="179" t="s">
+      <c r="C18" s="163" t="s">
         <v>54</v>
       </c>
       <c r="D18" s="74"/>
-      <c r="E18" s="179" t="s">
-        <v>100</v>
+      <c r="E18" s="163" t="s">
+        <v>55</v>
       </c>
       <c r="F18" s="74"/>
-      <c r="G18" s="162" t="s">
-        <v>101</v>
+      <c r="G18" s="180" t="s">
+        <v>149</v>
       </c>
       <c r="H18" s="73"/>
       <c r="I18" s="74"/>
-      <c r="J18" s="162" t="s">
-        <v>103</v>
+      <c r="J18" s="180" t="s">
+        <v>106</v>
       </c>
       <c r="K18" s="74"/>
-      <c r="L18" s="168" t="s">
-        <v>104</v>
+      <c r="L18" s="166" t="s">
+        <v>98</v>
       </c>
       <c r="M18" s="73"/>
       <c r="N18" s="74"/>
       <c r="O18" s="166" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="P18" s="73"/>
       <c r="Q18" s="74"/>
       <c r="R18" s="70">
-        <v>45825</v>
+        <v>45827</v>
       </c>
       <c r="S18" s="32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T18" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U18" s="34"/>
       <c r="V18" s="34"/>
@@ -15680,35 +15961,35 @@
       <c r="Y18" s="34"/>
       <c r="Z18" s="34"/>
     </row>
-    <row r="19" spans="1:26" ht="61.5" customHeight="1">
-      <c r="A19" s="173">
+    <row r="19" spans="1:26" ht="64.5" customHeight="1">
+      <c r="A19" s="162">
         <v>4</v>
       </c>
       <c r="B19" s="74"/>
-      <c r="C19" s="179" t="s">
+      <c r="C19" s="163" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="74"/>
-      <c r="E19" s="179" t="s">
+      <c r="E19" s="163" t="s">
         <v>100</v>
       </c>
       <c r="F19" s="74"/>
-      <c r="G19" s="162" t="s">
-        <v>139</v>
+      <c r="G19" s="180" t="s">
+        <v>101</v>
       </c>
       <c r="H19" s="73"/>
       <c r="I19" s="74"/>
-      <c r="J19" s="162" t="s">
-        <v>97</v>
+      <c r="J19" s="180" t="s">
+        <v>103</v>
       </c>
       <c r="K19" s="74"/>
-      <c r="L19" s="166" t="s">
-        <v>98</v>
+      <c r="L19" s="179" t="s">
+        <v>104</v>
       </c>
       <c r="M19" s="73"/>
       <c r="N19" s="74"/>
       <c r="O19" s="166" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="P19" s="73"/>
       <c r="Q19" s="74"/>
@@ -15716,10 +15997,10 @@
         <v>45825</v>
       </c>
       <c r="S19" s="32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T19" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U19" s="34"/>
       <c r="V19" s="34"/>
@@ -15728,35 +16009,35 @@
       <c r="Y19" s="34"/>
       <c r="Z19" s="34"/>
     </row>
-    <row r="20" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A20" s="173">
+    <row r="20" spans="1:26" ht="61.5" customHeight="1">
+      <c r="A20" s="162">
         <v>5</v>
       </c>
       <c r="B20" s="74"/>
-      <c r="C20" s="174" t="s">
+      <c r="C20" s="163" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="164"/>
-      <c r="E20" s="174" t="s">
-        <v>141</v>
-      </c>
-      <c r="F20" s="164"/>
-      <c r="G20" s="163" t="s">
-        <v>142</v>
-      </c>
-      <c r="H20" s="175"/>
-      <c r="I20" s="164"/>
-      <c r="J20" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="K20" s="164"/>
-      <c r="L20" s="176" t="s">
-        <v>144</v>
-      </c>
-      <c r="M20" s="177"/>
-      <c r="N20" s="177"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="163" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="74"/>
+      <c r="G20" s="180" t="s">
+        <v>138</v>
+      </c>
+      <c r="H20" s="73"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="180" t="s">
+        <v>97</v>
+      </c>
+      <c r="K20" s="74"/>
+      <c r="L20" s="166" t="s">
+        <v>98</v>
+      </c>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
       <c r="O20" s="166" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="P20" s="73"/>
       <c r="Q20" s="74"/>
@@ -15764,10 +16045,10 @@
         <v>45825</v>
       </c>
       <c r="S20" s="32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T20" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U20" s="34"/>
       <c r="V20" s="34"/>
@@ -15776,27 +16057,47 @@
       <c r="Y20" s="34"/>
       <c r="Z20" s="34"/>
     </row>
-    <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="173"/>
+    <row r="21" spans="1:26" ht="50.25" customHeight="1">
+      <c r="A21" s="162">
+        <v>6</v>
+      </c>
       <c r="B21" s="74"/>
-      <c r="C21" s="179"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="179"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="162"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="162"/>
-      <c r="K21" s="74"/>
-      <c r="L21" s="166"/>
-      <c r="M21" s="73"/>
-      <c r="N21" s="74"/>
-      <c r="O21" s="166"/>
+      <c r="C21" s="169" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="170"/>
+      <c r="E21" s="169" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" s="170"/>
+      <c r="G21" s="171" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="172"/>
+      <c r="I21" s="170"/>
+      <c r="J21" s="171" t="s">
+        <v>142</v>
+      </c>
+      <c r="K21" s="170"/>
+      <c r="L21" s="173" t="s">
+        <v>143</v>
+      </c>
+      <c r="M21" s="174"/>
+      <c r="N21" s="174"/>
+      <c r="O21" s="166" t="s">
+        <v>144</v>
+      </c>
       <c r="P21" s="73"/>
       <c r="Q21" s="74"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="32"/>
-      <c r="T21" s="33"/>
+      <c r="R21" s="70">
+        <v>45825</v>
+      </c>
+      <c r="S21" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="T21" s="33" t="s">
+        <v>145</v>
+      </c>
       <c r="U21" s="34"/>
       <c r="V21" s="34"/>
       <c r="W21" s="34"/>
@@ -15805,16 +16106,16 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="173"/>
+      <c r="A22" s="162"/>
       <c r="B22" s="74"/>
-      <c r="C22" s="179"/>
+      <c r="C22" s="163"/>
       <c r="D22" s="74"/>
-      <c r="E22" s="179"/>
+      <c r="E22" s="163"/>
       <c r="F22" s="74"/>
-      <c r="G22" s="162"/>
+      <c r="G22" s="180"/>
       <c r="H22" s="73"/>
       <c r="I22" s="74"/>
-      <c r="J22" s="162"/>
+      <c r="J22" s="180"/>
       <c r="K22" s="74"/>
       <c r="L22" s="166"/>
       <c r="M22" s="73"/>
@@ -15833,16 +16134,16 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="173"/>
+      <c r="A23" s="162"/>
       <c r="B23" s="74"/>
-      <c r="C23" s="179"/>
+      <c r="C23" s="163"/>
       <c r="D23" s="74"/>
-      <c r="E23" s="179"/>
+      <c r="E23" s="163"/>
       <c r="F23" s="74"/>
-      <c r="G23" s="162"/>
+      <c r="G23" s="180"/>
       <c r="H23" s="73"/>
       <c r="I23" s="74"/>
-      <c r="J23" s="162"/>
+      <c r="J23" s="180"/>
       <c r="K23" s="74"/>
       <c r="L23" s="166"/>
       <c r="M23" s="73"/>
@@ -15861,16 +16162,16 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="173"/>
+      <c r="A24" s="162"/>
       <c r="B24" s="74"/>
-      <c r="C24" s="179"/>
+      <c r="C24" s="163"/>
       <c r="D24" s="74"/>
-      <c r="E24" s="179"/>
+      <c r="E24" s="163"/>
       <c r="F24" s="74"/>
-      <c r="G24" s="162"/>
+      <c r="G24" s="180"/>
       <c r="H24" s="73"/>
       <c r="I24" s="74"/>
-      <c r="J24" s="162"/>
+      <c r="J24" s="180"/>
       <c r="K24" s="74"/>
       <c r="L24" s="166"/>
       <c r="M24" s="73"/>
@@ -15889,16 +16190,16 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="173"/>
+      <c r="A25" s="162"/>
       <c r="B25" s="74"/>
-      <c r="C25" s="179"/>
+      <c r="C25" s="163"/>
       <c r="D25" s="74"/>
-      <c r="E25" s="179"/>
+      <c r="E25" s="163"/>
       <c r="F25" s="74"/>
-      <c r="G25" s="162"/>
+      <c r="G25" s="180"/>
       <c r="H25" s="73"/>
       <c r="I25" s="74"/>
-      <c r="J25" s="162"/>
+      <c r="J25" s="180"/>
       <c r="K25" s="74"/>
       <c r="L25" s="166"/>
       <c r="M25" s="73"/>
@@ -15917,16 +16218,16 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="173"/>
+      <c r="A26" s="162"/>
       <c r="B26" s="74"/>
-      <c r="C26" s="179"/>
+      <c r="C26" s="163"/>
       <c r="D26" s="74"/>
-      <c r="E26" s="179"/>
+      <c r="E26" s="163"/>
       <c r="F26" s="74"/>
-      <c r="G26" s="162"/>
+      <c r="G26" s="180"/>
       <c r="H26" s="73"/>
       <c r="I26" s="74"/>
-      <c r="J26" s="162"/>
+      <c r="J26" s="180"/>
       <c r="K26" s="74"/>
       <c r="L26" s="166"/>
       <c r="M26" s="73"/>
@@ -15945,16 +16246,16 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="173"/>
+      <c r="A27" s="162"/>
       <c r="B27" s="74"/>
-      <c r="C27" s="179"/>
+      <c r="C27" s="163"/>
       <c r="D27" s="74"/>
-      <c r="E27" s="179"/>
+      <c r="E27" s="163"/>
       <c r="F27" s="74"/>
-      <c r="G27" s="162"/>
+      <c r="G27" s="180"/>
       <c r="H27" s="73"/>
       <c r="I27" s="74"/>
-      <c r="J27" s="162"/>
+      <c r="J27" s="180"/>
       <c r="K27" s="74"/>
       <c r="L27" s="166"/>
       <c r="M27" s="73"/>
@@ -15973,16 +16274,16 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="173"/>
+      <c r="A28" s="162"/>
       <c r="B28" s="74"/>
-      <c r="C28" s="179"/>
+      <c r="C28" s="163"/>
       <c r="D28" s="74"/>
-      <c r="E28" s="179"/>
+      <c r="E28" s="163"/>
       <c r="F28" s="74"/>
-      <c r="G28" s="162"/>
+      <c r="G28" s="180"/>
       <c r="H28" s="73"/>
       <c r="I28" s="74"/>
-      <c r="J28" s="162"/>
+      <c r="J28" s="180"/>
       <c r="K28" s="74"/>
       <c r="L28" s="166"/>
       <c r="M28" s="73"/>
@@ -16001,16 +16302,16 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="173"/>
+      <c r="A29" s="162"/>
       <c r="B29" s="74"/>
-      <c r="C29" s="179"/>
+      <c r="C29" s="163"/>
       <c r="D29" s="74"/>
-      <c r="E29" s="179"/>
+      <c r="E29" s="163"/>
       <c r="F29" s="74"/>
-      <c r="G29" s="162"/>
+      <c r="G29" s="180"/>
       <c r="H29" s="73"/>
       <c r="I29" s="74"/>
-      <c r="J29" s="162"/>
+      <c r="J29" s="180"/>
       <c r="K29" s="74"/>
       <c r="L29" s="166"/>
       <c r="M29" s="73"/>
@@ -16029,16 +16330,16 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="173"/>
+      <c r="A30" s="162"/>
       <c r="B30" s="74"/>
-      <c r="C30" s="179"/>
+      <c r="C30" s="163"/>
       <c r="D30" s="74"/>
-      <c r="E30" s="179"/>
+      <c r="E30" s="163"/>
       <c r="F30" s="74"/>
-      <c r="G30" s="162"/>
+      <c r="G30" s="180"/>
       <c r="H30" s="73"/>
       <c r="I30" s="74"/>
-      <c r="J30" s="162"/>
+      <c r="J30" s="180"/>
       <c r="K30" s="74"/>
       <c r="L30" s="166"/>
       <c r="M30" s="73"/>
@@ -16057,26 +16358,26 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="180"/>
-      <c r="B31" s="161"/>
-      <c r="C31" s="181"/>
-      <c r="D31" s="161"/>
-      <c r="E31" s="181"/>
-      <c r="F31" s="161"/>
-      <c r="G31" s="165"/>
-      <c r="H31" s="158"/>
-      <c r="I31" s="161"/>
-      <c r="J31" s="165"/>
-      <c r="K31" s="161"/>
-      <c r="L31" s="167"/>
-      <c r="M31" s="158"/>
-      <c r="N31" s="161"/>
-      <c r="O31" s="167"/>
-      <c r="P31" s="158"/>
-      <c r="Q31" s="161"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="36"/>
+      <c r="A31" s="162"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="163"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="163"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="180"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="180"/>
+      <c r="K31" s="74"/>
+      <c r="L31" s="166"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="166"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="74"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="33"/>
       <c r="U31" s="34"/>
       <c r="V31" s="34"/>
       <c r="W31" s="34"/>
@@ -16085,13 +16386,32 @@
       <c r="Z31" s="34"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
+      <c r="A32" s="164"/>
+      <c r="B32" s="151"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="151"/>
+      <c r="E32" s="165"/>
+      <c r="F32" s="151"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="150"/>
+      <c r="I32" s="151"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="151"/>
+      <c r="L32" s="167"/>
+      <c r="M32" s="150"/>
+      <c r="N32" s="151"/>
+      <c r="O32" s="167"/>
+      <c r="P32" s="150"/>
+      <c r="Q32" s="151"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="35"/>
+      <c r="T32" s="36"/>
+      <c r="U32" s="34"/>
+      <c r="V32" s="34"/>
+      <c r="W32" s="34"/>
+      <c r="X32" s="34"/>
+      <c r="Y32" s="34"/>
+      <c r="Z32" s="34"/>
     </row>
     <row r="33" spans="4:10" ht="12.75" customHeight="1">
       <c r="D33" s="3"/>
@@ -16102,7 +16422,15 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="34" spans="4:10" ht="12.75" customHeight="1">
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+    </row>
     <row r="35" spans="4:10" ht="12.75" customHeight="1"/>
     <row r="36" spans="4:10" ht="12.75" customHeight="1"/>
     <row r="37" spans="4:10" ht="12.75" customHeight="1"/>
@@ -17069,88 +17397,61 @@
     <row r="998" ht="12.75" customHeight="1"/>
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
+    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="136">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
+  <mergeCells count="143">
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G19:I19"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="J20:K20"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L19:N19"/>
     <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="L26:N26"/>
     <mergeCell ref="K2:N4"/>
     <mergeCell ref="O2:P4"/>
     <mergeCell ref="Q2:R4"/>
@@ -17162,56 +17463,91 @@
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
     <mergeCell ref="G21:I21"/>
     <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O32:Q32"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A30:B30"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
-    <hyperlink ref="L18" r:id="rId1" display="http://localhost:8080/taskUN/task-delete.jsp" xr:uid="{38C81AFB-41F8-4093-85EB-71ACC0BAB2DD}"/>
-    <hyperlink ref="L20" r:id="rId2" xr:uid="{70E42B72-7AD1-4967-864C-156B0F97FF63}"/>
+    <hyperlink ref="L19" r:id="rId1" display="http://localhost:8080/taskUN/task-delete.jsp" xr:uid="{38C81AFB-41F8-4093-85EB-71ACC0BAB2DD}"/>
+    <hyperlink ref="L21" r:id="rId2" xr:uid="{70E42B72-7AD1-4967-864C-156B0F97FF63}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -17233,70 +17569,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="191" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="200" t="s">
+      <c r="B1" s="191"/>
+      <c r="C1" s="192" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="201"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="203" t="s">
+      <c r="D1" s="193"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="195" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="204"/>
-      <c r="M1" s="205"/>
+      <c r="G1" s="196"/>
+      <c r="H1" s="196"/>
+      <c r="I1" s="196"/>
+      <c r="J1" s="196"/>
+      <c r="K1" s="196"/>
+      <c r="L1" s="196"/>
+      <c r="M1" s="197"/>
       <c r="N1" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="203" t="s">
+      <c r="O1" s="195" t="s">
         <v>94</v>
       </c>
-      <c r="P1" s="205"/>
+      <c r="P1" s="197"/>
       <c r="Q1" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="203" t="s">
+      <c r="R1" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="205"/>
+      <c r="S1" s="197"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="199"/>
-      <c r="B2" s="199"/>
-      <c r="C2" s="200" t="s">
+      <c r="A2" s="191"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="192" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="201"/>
-      <c r="E2" s="202"/>
-      <c r="F2" s="203" t="s">
+      <c r="D2" s="193"/>
+      <c r="E2" s="194"/>
+      <c r="F2" s="195" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="204"/>
-      <c r="H2" s="204"/>
-      <c r="I2" s="204"/>
-      <c r="J2" s="204"/>
-      <c r="K2" s="204"/>
-      <c r="L2" s="204"/>
-      <c r="M2" s="205"/>
+      <c r="G2" s="196"/>
+      <c r="H2" s="196"/>
+      <c r="I2" s="196"/>
+      <c r="J2" s="196"/>
+      <c r="K2" s="196"/>
+      <c r="L2" s="196"/>
+      <c r="M2" s="197"/>
       <c r="N2" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="O2" s="206">
+      <c r="O2" s="198">
         <v>45824</v>
       </c>
-      <c r="P2" s="207"/>
+      <c r="P2" s="199"/>
       <c r="Q2" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="R2" s="208"/>
-      <c r="S2" s="209"/>
+      <c r="R2" s="200"/>
+      <c r="S2" s="201"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="43"/>
@@ -17326,33 +17662,33 @@
       <c r="B4" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="194" t="s">
+      <c r="C4" s="182" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="196"/>
-      <c r="H4" s="194" t="s">
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="184"/>
+      <c r="H4" s="182" t="s">
         <v>119</v>
       </c>
-      <c r="I4" s="195"/>
-      <c r="J4" s="195"/>
-      <c r="K4" s="195"/>
-      <c r="L4" s="195"/>
-      <c r="M4" s="196"/>
-      <c r="N4" s="194" t="s">
+      <c r="I4" s="183"/>
+      <c r="J4" s="183"/>
+      <c r="K4" s="183"/>
+      <c r="L4" s="183"/>
+      <c r="M4" s="184"/>
+      <c r="N4" s="182" t="s">
         <v>120</v>
       </c>
-      <c r="O4" s="195"/>
-      <c r="P4" s="196"/>
+      <c r="O4" s="183"/>
+      <c r="P4" s="184"/>
       <c r="Q4" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="R4" s="194" t="s">
+      <c r="R4" s="182" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="196"/>
+      <c r="S4" s="184"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="47">
@@ -17361,31 +17697,31 @@
       <c r="B5" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="190" t="s">
+      <c r="C5" s="185" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="190"/>
-      <c r="E5" s="190"/>
-      <c r="F5" s="190"/>
-      <c r="G5" s="190"/>
-      <c r="H5" s="190" t="s">
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="185" t="s">
         <v>135</v>
       </c>
-      <c r="I5" s="190"/>
-      <c r="J5" s="190"/>
-      <c r="K5" s="190"/>
-      <c r="L5" s="190"/>
-      <c r="M5" s="190"/>
-      <c r="N5" s="191" t="s">
+      <c r="I5" s="185"/>
+      <c r="J5" s="185"/>
+      <c r="K5" s="185"/>
+      <c r="L5" s="185"/>
+      <c r="M5" s="185"/>
+      <c r="N5" s="186" t="s">
         <v>136</v>
       </c>
-      <c r="O5" s="192"/>
-      <c r="P5" s="193"/>
+      <c r="O5" s="187"/>
+      <c r="P5" s="188"/>
       <c r="Q5" s="71">
         <v>45825</v>
       </c>
-      <c r="R5" s="197"/>
-      <c r="S5" s="198"/>
+      <c r="R5" s="189"/>
+      <c r="S5" s="190"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="49">
@@ -17394,1000 +17730,1212 @@
       <c r="B6" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="190" t="s">
+      <c r="C6" s="185" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="190"/>
-      <c r="E6" s="190"/>
-      <c r="F6" s="190"/>
-      <c r="G6" s="190"/>
-      <c r="H6" s="190" t="s">
+      <c r="D6" s="185"/>
+      <c r="E6" s="185"/>
+      <c r="F6" s="185"/>
+      <c r="G6" s="185"/>
+      <c r="H6" s="185" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="190"/>
-      <c r="J6" s="190"/>
-      <c r="K6" s="190"/>
-      <c r="L6" s="190"/>
-      <c r="M6" s="190"/>
-      <c r="N6" s="191" t="s">
+      <c r="I6" s="185"/>
+      <c r="J6" s="185"/>
+      <c r="K6" s="185"/>
+      <c r="L6" s="185"/>
+      <c r="M6" s="185"/>
+      <c r="N6" s="186" t="s">
         <v>137</v>
       </c>
-      <c r="O6" s="192"/>
-      <c r="P6" s="193"/>
+      <c r="O6" s="187"/>
+      <c r="P6" s="188"/>
       <c r="Q6" s="71">
         <v>45825</v>
       </c>
-      <c r="R6" s="189"/>
-      <c r="S6" s="189"/>
+      <c r="R6" s="206"/>
+      <c r="S6" s="206"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
-      <c r="A7" s="49"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="182"/>
-      <c r="D7" s="182"/>
-      <c r="E7" s="182"/>
-      <c r="F7" s="182"/>
-      <c r="G7" s="182"/>
-      <c r="H7" s="182"/>
-      <c r="I7" s="182"/>
-      <c r="J7" s="182"/>
-      <c r="K7" s="182"/>
-      <c r="L7" s="182"/>
-      <c r="M7" s="182"/>
-      <c r="N7" s="186"/>
+      <c r="A7" s="49">
+        <v>3</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="202" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="202"/>
+      <c r="E7" s="202"/>
+      <c r="F7" s="202"/>
+      <c r="G7" s="202"/>
+      <c r="H7" s="202" t="s">
+        <v>148</v>
+      </c>
+      <c r="I7" s="202"/>
+      <c r="J7" s="202"/>
+      <c r="K7" s="202"/>
+      <c r="L7" s="202"/>
+      <c r="M7" s="202"/>
+      <c r="N7" s="186" t="s">
+        <v>136</v>
+      </c>
       <c r="O7" s="187"/>
       <c r="P7" s="188"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="189"/>
-      <c r="S7" s="189"/>
+      <c r="Q7" s="71">
+        <v>45827</v>
+      </c>
+      <c r="R7" s="206"/>
+      <c r="S7" s="206"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
-      <c r="A8" s="49"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="182"/>
-      <c r="D8" s="182"/>
-      <c r="E8" s="182"/>
-      <c r="F8" s="182"/>
-      <c r="G8" s="182"/>
-      <c r="H8" s="182"/>
-      <c r="I8" s="182"/>
-      <c r="J8" s="182"/>
-      <c r="K8" s="182"/>
-      <c r="L8" s="182"/>
-      <c r="M8" s="182"/>
-      <c r="N8" s="186"/>
+      <c r="A8" s="49">
+        <v>3</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="202" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="202"/>
+      <c r="E8" s="202"/>
+      <c r="F8" s="202"/>
+      <c r="G8" s="202"/>
+      <c r="H8" s="202" t="s">
+        <v>148</v>
+      </c>
+      <c r="I8" s="202"/>
+      <c r="J8" s="202"/>
+      <c r="K8" s="202"/>
+      <c r="L8" s="202"/>
+      <c r="M8" s="202"/>
+      <c r="N8" s="186" t="s">
+        <v>137</v>
+      </c>
       <c r="O8" s="187"/>
       <c r="P8" s="188"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="189"/>
-      <c r="S8" s="189"/>
+      <c r="Q8" s="71">
+        <v>45827</v>
+      </c>
+      <c r="R8" s="206"/>
+      <c r="S8" s="206"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="49"/>
       <c r="B9" s="49"/>
-      <c r="C9" s="182"/>
-      <c r="D9" s="182"/>
-      <c r="E9" s="182"/>
-      <c r="F9" s="182"/>
-      <c r="G9" s="182"/>
-      <c r="H9" s="182"/>
-      <c r="I9" s="182"/>
-      <c r="J9" s="182"/>
-      <c r="K9" s="182"/>
-      <c r="L9" s="182"/>
-      <c r="M9" s="182"/>
-      <c r="N9" s="186"/>
-      <c r="O9" s="187"/>
-      <c r="P9" s="188"/>
+      <c r="C9" s="202"/>
+      <c r="D9" s="202"/>
+      <c r="E9" s="202"/>
+      <c r="F9" s="202"/>
+      <c r="G9" s="202"/>
+      <c r="H9" s="202"/>
+      <c r="I9" s="202"/>
+      <c r="J9" s="202"/>
+      <c r="K9" s="202"/>
+      <c r="L9" s="202"/>
+      <c r="M9" s="202"/>
+      <c r="N9" s="203"/>
+      <c r="O9" s="204"/>
+      <c r="P9" s="205"/>
       <c r="Q9" s="49"/>
-      <c r="R9" s="189"/>
-      <c r="S9" s="189"/>
+      <c r="R9" s="206"/>
+      <c r="S9" s="206"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="49"/>
       <c r="B10" s="49"/>
-      <c r="C10" s="182"/>
-      <c r="D10" s="182"/>
-      <c r="E10" s="182"/>
-      <c r="F10" s="182"/>
-      <c r="G10" s="182"/>
-      <c r="H10" s="183"/>
-      <c r="I10" s="184"/>
-      <c r="J10" s="184"/>
-      <c r="K10" s="184"/>
-      <c r="L10" s="184"/>
-      <c r="M10" s="185"/>
-      <c r="N10" s="186"/>
-      <c r="O10" s="187"/>
-      <c r="P10" s="188"/>
+      <c r="C10" s="202"/>
+      <c r="D10" s="202"/>
+      <c r="E10" s="202"/>
+      <c r="F10" s="202"/>
+      <c r="G10" s="202"/>
+      <c r="H10" s="207"/>
+      <c r="I10" s="208"/>
+      <c r="J10" s="208"/>
+      <c r="K10" s="208"/>
+      <c r="L10" s="208"/>
+      <c r="M10" s="209"/>
+      <c r="N10" s="203"/>
+      <c r="O10" s="204"/>
+      <c r="P10" s="205"/>
       <c r="Q10" s="51"/>
-      <c r="R10" s="189"/>
-      <c r="S10" s="189"/>
+      <c r="R10" s="206"/>
+      <c r="S10" s="206"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="49"/>
       <c r="B11" s="49"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="182"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="183"/>
-      <c r="I11" s="184"/>
-      <c r="J11" s="184"/>
-      <c r="K11" s="184"/>
-      <c r="L11" s="184"/>
-      <c r="M11" s="185"/>
-      <c r="N11" s="186"/>
-      <c r="O11" s="187"/>
-      <c r="P11" s="188"/>
+      <c r="C11" s="202"/>
+      <c r="D11" s="202"/>
+      <c r="E11" s="202"/>
+      <c r="F11" s="202"/>
+      <c r="G11" s="202"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="208"/>
+      <c r="J11" s="208"/>
+      <c r="K11" s="208"/>
+      <c r="L11" s="208"/>
+      <c r="M11" s="209"/>
+      <c r="N11" s="203"/>
+      <c r="O11" s="204"/>
+      <c r="P11" s="205"/>
       <c r="Q11" s="49"/>
-      <c r="R11" s="189"/>
-      <c r="S11" s="189"/>
+      <c r="R11" s="206"/>
+      <c r="S11" s="206"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="49"/>
       <c r="B12" s="49"/>
-      <c r="C12" s="182"/>
-      <c r="D12" s="182"/>
-      <c r="E12" s="182"/>
-      <c r="F12" s="182"/>
-      <c r="G12" s="182"/>
-      <c r="H12" s="183"/>
-      <c r="I12" s="184"/>
-      <c r="J12" s="184"/>
-      <c r="K12" s="184"/>
-      <c r="L12" s="184"/>
-      <c r="M12" s="185"/>
-      <c r="N12" s="186"/>
-      <c r="O12" s="187"/>
-      <c r="P12" s="188"/>
+      <c r="C12" s="202"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="202"/>
+      <c r="G12" s="202"/>
+      <c r="H12" s="207"/>
+      <c r="I12" s="208"/>
+      <c r="J12" s="208"/>
+      <c r="K12" s="208"/>
+      <c r="L12" s="208"/>
+      <c r="M12" s="209"/>
+      <c r="N12" s="203"/>
+      <c r="O12" s="204"/>
+      <c r="P12" s="205"/>
       <c r="Q12" s="49"/>
-      <c r="R12" s="189"/>
-      <c r="S12" s="189"/>
+      <c r="R12" s="206"/>
+      <c r="S12" s="206"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="49"/>
       <c r="B13" s="49"/>
-      <c r="C13" s="182"/>
-      <c r="D13" s="182"/>
-      <c r="E13" s="182"/>
-      <c r="F13" s="182"/>
-      <c r="G13" s="182"/>
-      <c r="H13" s="183"/>
-      <c r="I13" s="184"/>
-      <c r="J13" s="184"/>
-      <c r="K13" s="184"/>
-      <c r="L13" s="184"/>
-      <c r="M13" s="185"/>
-      <c r="N13" s="186"/>
-      <c r="O13" s="187"/>
-      <c r="P13" s="188"/>
+      <c r="C13" s="202"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="202"/>
+      <c r="F13" s="202"/>
+      <c r="G13" s="202"/>
+      <c r="H13" s="207"/>
+      <c r="I13" s="208"/>
+      <c r="J13" s="208"/>
+      <c r="K13" s="208"/>
+      <c r="L13" s="208"/>
+      <c r="M13" s="209"/>
+      <c r="N13" s="203"/>
+      <c r="O13" s="204"/>
+      <c r="P13" s="205"/>
       <c r="Q13" s="49"/>
-      <c r="R13" s="189"/>
-      <c r="S13" s="189"/>
+      <c r="R13" s="206"/>
+      <c r="S13" s="206"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="49"/>
       <c r="B14" s="49"/>
-      <c r="C14" s="182"/>
-      <c r="D14" s="182"/>
-      <c r="E14" s="182"/>
-      <c r="F14" s="182"/>
-      <c r="G14" s="182"/>
-      <c r="H14" s="183"/>
-      <c r="I14" s="184"/>
-      <c r="J14" s="184"/>
-      <c r="K14" s="184"/>
-      <c r="L14" s="184"/>
-      <c r="M14" s="185"/>
-      <c r="N14" s="186"/>
-      <c r="O14" s="187"/>
-      <c r="P14" s="188"/>
+      <c r="C14" s="202"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="202"/>
+      <c r="F14" s="202"/>
+      <c r="G14" s="202"/>
+      <c r="H14" s="207"/>
+      <c r="I14" s="208"/>
+      <c r="J14" s="208"/>
+      <c r="K14" s="208"/>
+      <c r="L14" s="208"/>
+      <c r="M14" s="209"/>
+      <c r="N14" s="203"/>
+      <c r="O14" s="204"/>
+      <c r="P14" s="205"/>
       <c r="Q14" s="49"/>
-      <c r="R14" s="189"/>
-      <c r="S14" s="189"/>
+      <c r="R14" s="206"/>
+      <c r="S14" s="206"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="49"/>
       <c r="B15" s="49"/>
-      <c r="C15" s="182"/>
-      <c r="D15" s="182"/>
-      <c r="E15" s="182"/>
-      <c r="F15" s="182"/>
-      <c r="G15" s="182"/>
-      <c r="H15" s="183"/>
-      <c r="I15" s="184"/>
-      <c r="J15" s="184"/>
-      <c r="K15" s="184"/>
-      <c r="L15" s="184"/>
-      <c r="M15" s="185"/>
-      <c r="N15" s="186"/>
-      <c r="O15" s="187"/>
-      <c r="P15" s="188"/>
+      <c r="C15" s="202"/>
+      <c r="D15" s="202"/>
+      <c r="E15" s="202"/>
+      <c r="F15" s="202"/>
+      <c r="G15" s="202"/>
+      <c r="H15" s="207"/>
+      <c r="I15" s="208"/>
+      <c r="J15" s="208"/>
+      <c r="K15" s="208"/>
+      <c r="L15" s="208"/>
+      <c r="M15" s="209"/>
+      <c r="N15" s="203"/>
+      <c r="O15" s="204"/>
+      <c r="P15" s="205"/>
       <c r="Q15" s="49"/>
-      <c r="R15" s="189"/>
-      <c r="S15" s="189"/>
+      <c r="R15" s="206"/>
+      <c r="S15" s="206"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="49"/>
       <c r="B16" s="49"/>
-      <c r="C16" s="182"/>
-      <c r="D16" s="182"/>
-      <c r="E16" s="182"/>
-      <c r="F16" s="182"/>
-      <c r="G16" s="182"/>
-      <c r="H16" s="183"/>
-      <c r="I16" s="184"/>
-      <c r="J16" s="184"/>
-      <c r="K16" s="184"/>
-      <c r="L16" s="184"/>
-      <c r="M16" s="185"/>
-      <c r="N16" s="186"/>
-      <c r="O16" s="187"/>
-      <c r="P16" s="188"/>
+      <c r="C16" s="202"/>
+      <c r="D16" s="202"/>
+      <c r="E16" s="202"/>
+      <c r="F16" s="202"/>
+      <c r="G16" s="202"/>
+      <c r="H16" s="207"/>
+      <c r="I16" s="208"/>
+      <c r="J16" s="208"/>
+      <c r="K16" s="208"/>
+      <c r="L16" s="208"/>
+      <c r="M16" s="209"/>
+      <c r="N16" s="203"/>
+      <c r="O16" s="204"/>
+      <c r="P16" s="205"/>
       <c r="Q16" s="49"/>
-      <c r="R16" s="189"/>
-      <c r="S16" s="189"/>
+      <c r="R16" s="206"/>
+      <c r="S16" s="206"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="49"/>
       <c r="B17" s="49"/>
-      <c r="C17" s="182"/>
-      <c r="D17" s="182"/>
-      <c r="E17" s="182"/>
-      <c r="F17" s="182"/>
-      <c r="G17" s="182"/>
-      <c r="H17" s="183"/>
-      <c r="I17" s="184"/>
-      <c r="J17" s="184"/>
-      <c r="K17" s="184"/>
-      <c r="L17" s="184"/>
-      <c r="M17" s="185"/>
-      <c r="N17" s="186"/>
-      <c r="O17" s="187"/>
-      <c r="P17" s="188"/>
+      <c r="C17" s="202"/>
+      <c r="D17" s="202"/>
+      <c r="E17" s="202"/>
+      <c r="F17" s="202"/>
+      <c r="G17" s="202"/>
+      <c r="H17" s="207"/>
+      <c r="I17" s="208"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="208"/>
+      <c r="L17" s="208"/>
+      <c r="M17" s="209"/>
+      <c r="N17" s="203"/>
+      <c r="O17" s="204"/>
+      <c r="P17" s="205"/>
       <c r="Q17" s="49"/>
-      <c r="R17" s="189"/>
-      <c r="S17" s="189"/>
+      <c r="R17" s="206"/>
+      <c r="S17" s="206"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="49"/>
       <c r="B18" s="49"/>
-      <c r="C18" s="182"/>
-      <c r="D18" s="182"/>
-      <c r="E18" s="182"/>
-      <c r="F18" s="182"/>
-      <c r="G18" s="182"/>
-      <c r="H18" s="183"/>
-      <c r="I18" s="184"/>
-      <c r="J18" s="184"/>
-      <c r="K18" s="184"/>
-      <c r="L18" s="184"/>
-      <c r="M18" s="185"/>
-      <c r="N18" s="186"/>
-      <c r="O18" s="187"/>
-      <c r="P18" s="188"/>
+      <c r="C18" s="202"/>
+      <c r="D18" s="202"/>
+      <c r="E18" s="202"/>
+      <c r="F18" s="202"/>
+      <c r="G18" s="202"/>
+      <c r="H18" s="207"/>
+      <c r="I18" s="208"/>
+      <c r="J18" s="208"/>
+      <c r="K18" s="208"/>
+      <c r="L18" s="208"/>
+      <c r="M18" s="209"/>
+      <c r="N18" s="203"/>
+      <c r="O18" s="204"/>
+      <c r="P18" s="205"/>
       <c r="Q18" s="49"/>
-      <c r="R18" s="189"/>
-      <c r="S18" s="189"/>
+      <c r="R18" s="206"/>
+      <c r="S18" s="206"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="49"/>
       <c r="B19" s="49"/>
-      <c r="C19" s="182"/>
-      <c r="D19" s="182"/>
-      <c r="E19" s="182"/>
-      <c r="F19" s="182"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="183"/>
-      <c r="I19" s="184"/>
-      <c r="J19" s="184"/>
-      <c r="K19" s="184"/>
-      <c r="L19" s="184"/>
-      <c r="M19" s="185"/>
-      <c r="N19" s="186"/>
-      <c r="O19" s="187"/>
-      <c r="P19" s="188"/>
+      <c r="C19" s="202"/>
+      <c r="D19" s="202"/>
+      <c r="E19" s="202"/>
+      <c r="F19" s="202"/>
+      <c r="G19" s="202"/>
+      <c r="H19" s="207"/>
+      <c r="I19" s="208"/>
+      <c r="J19" s="208"/>
+      <c r="K19" s="208"/>
+      <c r="L19" s="208"/>
+      <c r="M19" s="209"/>
+      <c r="N19" s="203"/>
+      <c r="O19" s="204"/>
+      <c r="P19" s="205"/>
       <c r="Q19" s="49"/>
-      <c r="R19" s="189"/>
-      <c r="S19" s="189"/>
+      <c r="R19" s="206"/>
+      <c r="S19" s="206"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="49"/>
       <c r="B20" s="49"/>
-      <c r="C20" s="182"/>
-      <c r="D20" s="182"/>
-      <c r="E20" s="182"/>
-      <c r="F20" s="182"/>
-      <c r="G20" s="182"/>
-      <c r="H20" s="183"/>
-      <c r="I20" s="184"/>
-      <c r="J20" s="184"/>
-      <c r="K20" s="184"/>
-      <c r="L20" s="184"/>
-      <c r="M20" s="185"/>
-      <c r="N20" s="186"/>
-      <c r="O20" s="187"/>
-      <c r="P20" s="188"/>
+      <c r="C20" s="202"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="202"/>
+      <c r="F20" s="202"/>
+      <c r="G20" s="202"/>
+      <c r="H20" s="207"/>
+      <c r="I20" s="208"/>
+      <c r="J20" s="208"/>
+      <c r="K20" s="208"/>
+      <c r="L20" s="208"/>
+      <c r="M20" s="209"/>
+      <c r="N20" s="203"/>
+      <c r="O20" s="204"/>
+      <c r="P20" s="205"/>
       <c r="Q20" s="49"/>
-      <c r="R20" s="189"/>
-      <c r="S20" s="189"/>
+      <c r="R20" s="206"/>
+      <c r="S20" s="206"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="49"/>
       <c r="B21" s="49"/>
-      <c r="C21" s="182"/>
-      <c r="D21" s="182"/>
-      <c r="E21" s="182"/>
-      <c r="F21" s="182"/>
-      <c r="G21" s="182"/>
-      <c r="H21" s="183"/>
-      <c r="I21" s="184"/>
-      <c r="J21" s="184"/>
-      <c r="K21" s="184"/>
-      <c r="L21" s="184"/>
-      <c r="M21" s="185"/>
-      <c r="N21" s="186"/>
-      <c r="O21" s="187"/>
-      <c r="P21" s="188"/>
+      <c r="C21" s="202"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="202"/>
+      <c r="F21" s="202"/>
+      <c r="G21" s="202"/>
+      <c r="H21" s="207"/>
+      <c r="I21" s="208"/>
+      <c r="J21" s="208"/>
+      <c r="K21" s="208"/>
+      <c r="L21" s="208"/>
+      <c r="M21" s="209"/>
+      <c r="N21" s="203"/>
+      <c r="O21" s="204"/>
+      <c r="P21" s="205"/>
       <c r="Q21" s="49"/>
-      <c r="R21" s="189"/>
-      <c r="S21" s="189"/>
+      <c r="R21" s="206"/>
+      <c r="S21" s="206"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="49"/>
       <c r="B22" s="49"/>
-      <c r="C22" s="182"/>
-      <c r="D22" s="182"/>
-      <c r="E22" s="182"/>
-      <c r="F22" s="182"/>
-      <c r="G22" s="182"/>
-      <c r="H22" s="183"/>
-      <c r="I22" s="184"/>
-      <c r="J22" s="184"/>
-      <c r="K22" s="184"/>
-      <c r="L22" s="184"/>
-      <c r="M22" s="185"/>
-      <c r="N22" s="186"/>
-      <c r="O22" s="187"/>
-      <c r="P22" s="188"/>
+      <c r="C22" s="202"/>
+      <c r="D22" s="202"/>
+      <c r="E22" s="202"/>
+      <c r="F22" s="202"/>
+      <c r="G22" s="202"/>
+      <c r="H22" s="207"/>
+      <c r="I22" s="208"/>
+      <c r="J22" s="208"/>
+      <c r="K22" s="208"/>
+      <c r="L22" s="208"/>
+      <c r="M22" s="209"/>
+      <c r="N22" s="203"/>
+      <c r="O22" s="204"/>
+      <c r="P22" s="205"/>
       <c r="Q22" s="49"/>
-      <c r="R22" s="189"/>
-      <c r="S22" s="189"/>
+      <c r="R22" s="206"/>
+      <c r="S22" s="206"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="49"/>
       <c r="B23" s="49"/>
-      <c r="C23" s="182"/>
-      <c r="D23" s="182"/>
-      <c r="E23" s="182"/>
-      <c r="F23" s="182"/>
-      <c r="G23" s="182"/>
-      <c r="H23" s="183"/>
-      <c r="I23" s="184"/>
-      <c r="J23" s="184"/>
-      <c r="K23" s="184"/>
-      <c r="L23" s="184"/>
-      <c r="M23" s="185"/>
-      <c r="N23" s="186"/>
-      <c r="O23" s="187"/>
-      <c r="P23" s="188"/>
+      <c r="C23" s="202"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="202"/>
+      <c r="F23" s="202"/>
+      <c r="G23" s="202"/>
+      <c r="H23" s="207"/>
+      <c r="I23" s="208"/>
+      <c r="J23" s="208"/>
+      <c r="K23" s="208"/>
+      <c r="L23" s="208"/>
+      <c r="M23" s="209"/>
+      <c r="N23" s="203"/>
+      <c r="O23" s="204"/>
+      <c r="P23" s="205"/>
       <c r="Q23" s="49"/>
-      <c r="R23" s="189"/>
-      <c r="S23" s="189"/>
+      <c r="R23" s="206"/>
+      <c r="S23" s="206"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="49"/>
       <c r="B24" s="49"/>
-      <c r="C24" s="182"/>
-      <c r="D24" s="182"/>
-      <c r="E24" s="182"/>
-      <c r="F24" s="182"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="183"/>
-      <c r="I24" s="184"/>
-      <c r="J24" s="184"/>
-      <c r="K24" s="184"/>
-      <c r="L24" s="184"/>
-      <c r="M24" s="185"/>
-      <c r="N24" s="186"/>
-      <c r="O24" s="187"/>
-      <c r="P24" s="188"/>
+      <c r="C24" s="202"/>
+      <c r="D24" s="202"/>
+      <c r="E24" s="202"/>
+      <c r="F24" s="202"/>
+      <c r="G24" s="202"/>
+      <c r="H24" s="207"/>
+      <c r="I24" s="208"/>
+      <c r="J24" s="208"/>
+      <c r="K24" s="208"/>
+      <c r="L24" s="208"/>
+      <c r="M24" s="209"/>
+      <c r="N24" s="203"/>
+      <c r="O24" s="204"/>
+      <c r="P24" s="205"/>
       <c r="Q24" s="49"/>
-      <c r="R24" s="189"/>
-      <c r="S24" s="189"/>
+      <c r="R24" s="206"/>
+      <c r="S24" s="206"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="49"/>
       <c r="B25" s="49"/>
-      <c r="C25" s="182"/>
-      <c r="D25" s="182"/>
-      <c r="E25" s="182"/>
-      <c r="F25" s="182"/>
-      <c r="G25" s="182"/>
-      <c r="H25" s="183"/>
-      <c r="I25" s="184"/>
-      <c r="J25" s="184"/>
-      <c r="K25" s="184"/>
-      <c r="L25" s="184"/>
-      <c r="M25" s="185"/>
-      <c r="N25" s="186"/>
-      <c r="O25" s="187"/>
-      <c r="P25" s="188"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="202"/>
+      <c r="G25" s="202"/>
+      <c r="H25" s="207"/>
+      <c r="I25" s="208"/>
+      <c r="J25" s="208"/>
+      <c r="K25" s="208"/>
+      <c r="L25" s="208"/>
+      <c r="M25" s="209"/>
+      <c r="N25" s="203"/>
+      <c r="O25" s="204"/>
+      <c r="P25" s="205"/>
       <c r="Q25" s="49"/>
-      <c r="R25" s="189"/>
-      <c r="S25" s="189"/>
+      <c r="R25" s="206"/>
+      <c r="S25" s="206"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="49"/>
       <c r="B26" s="49"/>
-      <c r="C26" s="182"/>
-      <c r="D26" s="182"/>
-      <c r="E26" s="182"/>
-      <c r="F26" s="182"/>
-      <c r="G26" s="182"/>
-      <c r="H26" s="183"/>
-      <c r="I26" s="184"/>
-      <c r="J26" s="184"/>
-      <c r="K26" s="184"/>
-      <c r="L26" s="184"/>
-      <c r="M26" s="185"/>
-      <c r="N26" s="186"/>
-      <c r="O26" s="187"/>
-      <c r="P26" s="188"/>
+      <c r="C26" s="202"/>
+      <c r="D26" s="202"/>
+      <c r="E26" s="202"/>
+      <c r="F26" s="202"/>
+      <c r="G26" s="202"/>
+      <c r="H26" s="207"/>
+      <c r="I26" s="208"/>
+      <c r="J26" s="208"/>
+      <c r="K26" s="208"/>
+      <c r="L26" s="208"/>
+      <c r="M26" s="209"/>
+      <c r="N26" s="203"/>
+      <c r="O26" s="204"/>
+      <c r="P26" s="205"/>
       <c r="Q26" s="49"/>
-      <c r="R26" s="189"/>
-      <c r="S26" s="189"/>
+      <c r="R26" s="206"/>
+      <c r="S26" s="206"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="49"/>
       <c r="B27" s="49"/>
-      <c r="C27" s="182"/>
-      <c r="D27" s="182"/>
-      <c r="E27" s="182"/>
-      <c r="F27" s="182"/>
-      <c r="G27" s="182"/>
-      <c r="H27" s="183"/>
-      <c r="I27" s="184"/>
-      <c r="J27" s="184"/>
-      <c r="K27" s="184"/>
-      <c r="L27" s="184"/>
-      <c r="M27" s="185"/>
-      <c r="N27" s="186"/>
-      <c r="O27" s="187"/>
-      <c r="P27" s="188"/>
+      <c r="C27" s="202"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="202"/>
+      <c r="F27" s="202"/>
+      <c r="G27" s="202"/>
+      <c r="H27" s="207"/>
+      <c r="I27" s="208"/>
+      <c r="J27" s="208"/>
+      <c r="K27" s="208"/>
+      <c r="L27" s="208"/>
+      <c r="M27" s="209"/>
+      <c r="N27" s="203"/>
+      <c r="O27" s="204"/>
+      <c r="P27" s="205"/>
       <c r="Q27" s="49"/>
-      <c r="R27" s="189"/>
-      <c r="S27" s="189"/>
+      <c r="R27" s="206"/>
+      <c r="S27" s="206"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="49"/>
       <c r="B28" s="49"/>
-      <c r="C28" s="182"/>
-      <c r="D28" s="182"/>
-      <c r="E28" s="182"/>
-      <c r="F28" s="182"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="183"/>
-      <c r="I28" s="184"/>
-      <c r="J28" s="184"/>
-      <c r="K28" s="184"/>
-      <c r="L28" s="184"/>
-      <c r="M28" s="185"/>
-      <c r="N28" s="186"/>
-      <c r="O28" s="187"/>
-      <c r="P28" s="188"/>
+      <c r="C28" s="202"/>
+      <c r="D28" s="202"/>
+      <c r="E28" s="202"/>
+      <c r="F28" s="202"/>
+      <c r="G28" s="202"/>
+      <c r="H28" s="207"/>
+      <c r="I28" s="208"/>
+      <c r="J28" s="208"/>
+      <c r="K28" s="208"/>
+      <c r="L28" s="208"/>
+      <c r="M28" s="209"/>
+      <c r="N28" s="203"/>
+      <c r="O28" s="204"/>
+      <c r="P28" s="205"/>
       <c r="Q28" s="49"/>
-      <c r="R28" s="189"/>
-      <c r="S28" s="189"/>
+      <c r="R28" s="206"/>
+      <c r="S28" s="206"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="49"/>
       <c r="B29" s="49"/>
-      <c r="C29" s="182"/>
-      <c r="D29" s="182"/>
-      <c r="E29" s="182"/>
-      <c r="F29" s="182"/>
-      <c r="G29" s="182"/>
-      <c r="H29" s="183"/>
-      <c r="I29" s="184"/>
-      <c r="J29" s="184"/>
-      <c r="K29" s="184"/>
-      <c r="L29" s="184"/>
-      <c r="M29" s="185"/>
-      <c r="N29" s="186"/>
-      <c r="O29" s="187"/>
-      <c r="P29" s="188"/>
+      <c r="C29" s="202"/>
+      <c r="D29" s="202"/>
+      <c r="E29" s="202"/>
+      <c r="F29" s="202"/>
+      <c r="G29" s="202"/>
+      <c r="H29" s="207"/>
+      <c r="I29" s="208"/>
+      <c r="J29" s="208"/>
+      <c r="K29" s="208"/>
+      <c r="L29" s="208"/>
+      <c r="M29" s="209"/>
+      <c r="N29" s="203"/>
+      <c r="O29" s="204"/>
+      <c r="P29" s="205"/>
       <c r="Q29" s="49"/>
-      <c r="R29" s="189"/>
-      <c r="S29" s="189"/>
+      <c r="R29" s="206"/>
+      <c r="S29" s="206"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="49"/>
       <c r="B30" s="49"/>
-      <c r="C30" s="182"/>
-      <c r="D30" s="182"/>
-      <c r="E30" s="182"/>
-      <c r="F30" s="182"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="183"/>
-      <c r="I30" s="184"/>
-      <c r="J30" s="184"/>
-      <c r="K30" s="184"/>
-      <c r="L30" s="184"/>
-      <c r="M30" s="185"/>
-      <c r="N30" s="186"/>
-      <c r="O30" s="187"/>
-      <c r="P30" s="188"/>
+      <c r="C30" s="202"/>
+      <c r="D30" s="202"/>
+      <c r="E30" s="202"/>
+      <c r="F30" s="202"/>
+      <c r="G30" s="202"/>
+      <c r="H30" s="207"/>
+      <c r="I30" s="208"/>
+      <c r="J30" s="208"/>
+      <c r="K30" s="208"/>
+      <c r="L30" s="208"/>
+      <c r="M30" s="209"/>
+      <c r="N30" s="203"/>
+      <c r="O30" s="204"/>
+      <c r="P30" s="205"/>
       <c r="Q30" s="49"/>
-      <c r="R30" s="189"/>
-      <c r="S30" s="189"/>
+      <c r="R30" s="206"/>
+      <c r="S30" s="206"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="49"/>
       <c r="B31" s="49"/>
-      <c r="C31" s="182"/>
-      <c r="D31" s="182"/>
-      <c r="E31" s="182"/>
-      <c r="F31" s="182"/>
-      <c r="G31" s="182"/>
-      <c r="H31" s="183"/>
-      <c r="I31" s="184"/>
-      <c r="J31" s="184"/>
-      <c r="K31" s="184"/>
-      <c r="L31" s="184"/>
-      <c r="M31" s="185"/>
-      <c r="N31" s="186"/>
-      <c r="O31" s="187"/>
-      <c r="P31" s="188"/>
+      <c r="C31" s="202"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="202"/>
+      <c r="F31" s="202"/>
+      <c r="G31" s="202"/>
+      <c r="H31" s="207"/>
+      <c r="I31" s="208"/>
+      <c r="J31" s="208"/>
+      <c r="K31" s="208"/>
+      <c r="L31" s="208"/>
+      <c r="M31" s="209"/>
+      <c r="N31" s="203"/>
+      <c r="O31" s="204"/>
+      <c r="P31" s="205"/>
       <c r="Q31" s="49"/>
-      <c r="R31" s="189"/>
-      <c r="S31" s="189"/>
+      <c r="R31" s="206"/>
+      <c r="S31" s="206"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="49"/>
       <c r="B32" s="49"/>
-      <c r="C32" s="182"/>
-      <c r="D32" s="182"/>
-      <c r="E32" s="182"/>
-      <c r="F32" s="182"/>
-      <c r="G32" s="182"/>
-      <c r="H32" s="183"/>
-      <c r="I32" s="184"/>
-      <c r="J32" s="184"/>
-      <c r="K32" s="184"/>
-      <c r="L32" s="184"/>
-      <c r="M32" s="185"/>
-      <c r="N32" s="186"/>
-      <c r="O32" s="187"/>
-      <c r="P32" s="188"/>
+      <c r="C32" s="202"/>
+      <c r="D32" s="202"/>
+      <c r="E32" s="202"/>
+      <c r="F32" s="202"/>
+      <c r="G32" s="202"/>
+      <c r="H32" s="207"/>
+      <c r="I32" s="208"/>
+      <c r="J32" s="208"/>
+      <c r="K32" s="208"/>
+      <c r="L32" s="208"/>
+      <c r="M32" s="209"/>
+      <c r="N32" s="203"/>
+      <c r="O32" s="204"/>
+      <c r="P32" s="205"/>
       <c r="Q32" s="49"/>
-      <c r="R32" s="189"/>
-      <c r="S32" s="189"/>
+      <c r="R32" s="206"/>
+      <c r="S32" s="206"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="49"/>
       <c r="B33" s="49"/>
-      <c r="C33" s="182"/>
-      <c r="D33" s="182"/>
-      <c r="E33" s="182"/>
-      <c r="F33" s="182"/>
-      <c r="G33" s="182"/>
-      <c r="H33" s="183"/>
-      <c r="I33" s="184"/>
-      <c r="J33" s="184"/>
-      <c r="K33" s="184"/>
-      <c r="L33" s="184"/>
-      <c r="M33" s="185"/>
-      <c r="N33" s="186"/>
-      <c r="O33" s="187"/>
-      <c r="P33" s="188"/>
+      <c r="C33" s="202"/>
+      <c r="D33" s="202"/>
+      <c r="E33" s="202"/>
+      <c r="F33" s="202"/>
+      <c r="G33" s="202"/>
+      <c r="H33" s="207"/>
+      <c r="I33" s="208"/>
+      <c r="J33" s="208"/>
+      <c r="K33" s="208"/>
+      <c r="L33" s="208"/>
+      <c r="M33" s="209"/>
+      <c r="N33" s="203"/>
+      <c r="O33" s="204"/>
+      <c r="P33" s="205"/>
       <c r="Q33" s="49"/>
-      <c r="R33" s="189"/>
-      <c r="S33" s="189"/>
+      <c r="R33" s="206"/>
+      <c r="S33" s="206"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="49"/>
       <c r="B34" s="49"/>
-      <c r="C34" s="182"/>
-      <c r="D34" s="182"/>
-      <c r="E34" s="182"/>
-      <c r="F34" s="182"/>
-      <c r="G34" s="182"/>
-      <c r="H34" s="183"/>
-      <c r="I34" s="184"/>
-      <c r="J34" s="184"/>
-      <c r="K34" s="184"/>
-      <c r="L34" s="184"/>
-      <c r="M34" s="185"/>
-      <c r="N34" s="186"/>
-      <c r="O34" s="187"/>
-      <c r="P34" s="188"/>
+      <c r="C34" s="202"/>
+      <c r="D34" s="202"/>
+      <c r="E34" s="202"/>
+      <c r="F34" s="202"/>
+      <c r="G34" s="202"/>
+      <c r="H34" s="207"/>
+      <c r="I34" s="208"/>
+      <c r="J34" s="208"/>
+      <c r="K34" s="208"/>
+      <c r="L34" s="208"/>
+      <c r="M34" s="209"/>
+      <c r="N34" s="203"/>
+      <c r="O34" s="204"/>
+      <c r="P34" s="205"/>
       <c r="Q34" s="49"/>
-      <c r="R34" s="189"/>
-      <c r="S34" s="189"/>
+      <c r="R34" s="206"/>
+      <c r="S34" s="206"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
-      <c r="C35" s="182"/>
-      <c r="D35" s="182"/>
-      <c r="E35" s="182"/>
-      <c r="F35" s="182"/>
-      <c r="G35" s="182"/>
-      <c r="H35" s="183"/>
-      <c r="I35" s="184"/>
-      <c r="J35" s="184"/>
-      <c r="K35" s="184"/>
-      <c r="L35" s="184"/>
-      <c r="M35" s="185"/>
-      <c r="N35" s="186"/>
-      <c r="O35" s="187"/>
-      <c r="P35" s="188"/>
+      <c r="C35" s="202"/>
+      <c r="D35" s="202"/>
+      <c r="E35" s="202"/>
+      <c r="F35" s="202"/>
+      <c r="G35" s="202"/>
+      <c r="H35" s="207"/>
+      <c r="I35" s="208"/>
+      <c r="J35" s="208"/>
+      <c r="K35" s="208"/>
+      <c r="L35" s="208"/>
+      <c r="M35" s="209"/>
+      <c r="N35" s="203"/>
+      <c r="O35" s="204"/>
+      <c r="P35" s="205"/>
       <c r="Q35" s="49"/>
-      <c r="R35" s="189"/>
-      <c r="S35" s="189"/>
+      <c r="R35" s="206"/>
+      <c r="S35" s="206"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="49"/>
       <c r="B36" s="49"/>
-      <c r="C36" s="182"/>
-      <c r="D36" s="182"/>
-      <c r="E36" s="182"/>
-      <c r="F36" s="182"/>
-      <c r="G36" s="182"/>
-      <c r="H36" s="183"/>
-      <c r="I36" s="184"/>
-      <c r="J36" s="184"/>
-      <c r="K36" s="184"/>
-      <c r="L36" s="184"/>
-      <c r="M36" s="185"/>
-      <c r="N36" s="186"/>
-      <c r="O36" s="187"/>
-      <c r="P36" s="188"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="207"/>
+      <c r="I36" s="208"/>
+      <c r="J36" s="208"/>
+      <c r="K36" s="208"/>
+      <c r="L36" s="208"/>
+      <c r="M36" s="209"/>
+      <c r="N36" s="203"/>
+      <c r="O36" s="204"/>
+      <c r="P36" s="205"/>
       <c r="Q36" s="49"/>
-      <c r="R36" s="189"/>
-      <c r="S36" s="189"/>
+      <c r="R36" s="206"/>
+      <c r="S36" s="206"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="49"/>
       <c r="B37" s="49"/>
-      <c r="C37" s="182"/>
-      <c r="D37" s="182"/>
-      <c r="E37" s="182"/>
-      <c r="F37" s="182"/>
-      <c r="G37" s="182"/>
-      <c r="H37" s="183"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="184"/>
-      <c r="L37" s="184"/>
-      <c r="M37" s="185"/>
-      <c r="N37" s="186"/>
-      <c r="O37" s="187"/>
-      <c r="P37" s="188"/>
+      <c r="C37" s="202"/>
+      <c r="D37" s="202"/>
+      <c r="E37" s="202"/>
+      <c r="F37" s="202"/>
+      <c r="G37" s="202"/>
+      <c r="H37" s="207"/>
+      <c r="I37" s="208"/>
+      <c r="J37" s="208"/>
+      <c r="K37" s="208"/>
+      <c r="L37" s="208"/>
+      <c r="M37" s="209"/>
+      <c r="N37" s="203"/>
+      <c r="O37" s="204"/>
+      <c r="P37" s="205"/>
       <c r="Q37" s="49"/>
-      <c r="R37" s="189"/>
-      <c r="S37" s="189"/>
+      <c r="R37" s="206"/>
+      <c r="S37" s="206"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="49"/>
       <c r="B38" s="49"/>
-      <c r="C38" s="182"/>
-      <c r="D38" s="182"/>
-      <c r="E38" s="182"/>
-      <c r="F38" s="182"/>
-      <c r="G38" s="182"/>
-      <c r="H38" s="183"/>
-      <c r="I38" s="184"/>
-      <c r="J38" s="184"/>
-      <c r="K38" s="184"/>
-      <c r="L38" s="184"/>
-      <c r="M38" s="185"/>
-      <c r="N38" s="186"/>
-      <c r="O38" s="187"/>
-      <c r="P38" s="188"/>
+      <c r="C38" s="202"/>
+      <c r="D38" s="202"/>
+      <c r="E38" s="202"/>
+      <c r="F38" s="202"/>
+      <c r="G38" s="202"/>
+      <c r="H38" s="207"/>
+      <c r="I38" s="208"/>
+      <c r="J38" s="208"/>
+      <c r="K38" s="208"/>
+      <c r="L38" s="208"/>
+      <c r="M38" s="209"/>
+      <c r="N38" s="203"/>
+      <c r="O38" s="204"/>
+      <c r="P38" s="205"/>
       <c r="Q38" s="49"/>
-      <c r="R38" s="189"/>
-      <c r="S38" s="189"/>
+      <c r="R38" s="206"/>
+      <c r="S38" s="206"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="49"/>
       <c r="B39" s="49"/>
-      <c r="C39" s="182"/>
-      <c r="D39" s="182"/>
-      <c r="E39" s="182"/>
-      <c r="F39" s="182"/>
-      <c r="G39" s="182"/>
-      <c r="H39" s="183"/>
-      <c r="I39" s="184"/>
-      <c r="J39" s="184"/>
-      <c r="K39" s="184"/>
-      <c r="L39" s="184"/>
-      <c r="M39" s="185"/>
-      <c r="N39" s="186"/>
-      <c r="O39" s="187"/>
-      <c r="P39" s="188"/>
+      <c r="C39" s="202"/>
+      <c r="D39" s="202"/>
+      <c r="E39" s="202"/>
+      <c r="F39" s="202"/>
+      <c r="G39" s="202"/>
+      <c r="H39" s="207"/>
+      <c r="I39" s="208"/>
+      <c r="J39" s="208"/>
+      <c r="K39" s="208"/>
+      <c r="L39" s="208"/>
+      <c r="M39" s="209"/>
+      <c r="N39" s="203"/>
+      <c r="O39" s="204"/>
+      <c r="P39" s="205"/>
       <c r="Q39" s="49"/>
-      <c r="R39" s="189"/>
-      <c r="S39" s="189"/>
+      <c r="R39" s="206"/>
+      <c r="S39" s="206"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="49"/>
       <c r="B40" s="49"/>
-      <c r="C40" s="182"/>
-      <c r="D40" s="182"/>
-      <c r="E40" s="182"/>
-      <c r="F40" s="182"/>
-      <c r="G40" s="182"/>
-      <c r="H40" s="183"/>
-      <c r="I40" s="184"/>
-      <c r="J40" s="184"/>
-      <c r="K40" s="184"/>
-      <c r="L40" s="184"/>
-      <c r="M40" s="185"/>
-      <c r="N40" s="186"/>
-      <c r="O40" s="187"/>
-      <c r="P40" s="188"/>
+      <c r="C40" s="202"/>
+      <c r="D40" s="202"/>
+      <c r="E40" s="202"/>
+      <c r="F40" s="202"/>
+      <c r="G40" s="202"/>
+      <c r="H40" s="207"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="209"/>
+      <c r="N40" s="203"/>
+      <c r="O40" s="204"/>
+      <c r="P40" s="205"/>
       <c r="Q40" s="49"/>
-      <c r="R40" s="189"/>
-      <c r="S40" s="189"/>
+      <c r="R40" s="206"/>
+      <c r="S40" s="206"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="49"/>
       <c r="B41" s="49"/>
-      <c r="C41" s="182"/>
-      <c r="D41" s="182"/>
-      <c r="E41" s="182"/>
-      <c r="F41" s="182"/>
-      <c r="G41" s="182"/>
-      <c r="H41" s="183"/>
-      <c r="I41" s="184"/>
-      <c r="J41" s="184"/>
-      <c r="K41" s="184"/>
-      <c r="L41" s="184"/>
-      <c r="M41" s="185"/>
-      <c r="N41" s="186"/>
-      <c r="O41" s="187"/>
-      <c r="P41" s="188"/>
+      <c r="C41" s="202"/>
+      <c r="D41" s="202"/>
+      <c r="E41" s="202"/>
+      <c r="F41" s="202"/>
+      <c r="G41" s="202"/>
+      <c r="H41" s="207"/>
+      <c r="I41" s="208"/>
+      <c r="J41" s="208"/>
+      <c r="K41" s="208"/>
+      <c r="L41" s="208"/>
+      <c r="M41" s="209"/>
+      <c r="N41" s="203"/>
+      <c r="O41" s="204"/>
+      <c r="P41" s="205"/>
       <c r="Q41" s="49"/>
-      <c r="R41" s="189"/>
-      <c r="S41" s="189"/>
+      <c r="R41" s="206"/>
+      <c r="S41" s="206"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="49"/>
       <c r="B42" s="49"/>
-      <c r="C42" s="182"/>
-      <c r="D42" s="182"/>
-      <c r="E42" s="182"/>
-      <c r="F42" s="182"/>
-      <c r="G42" s="182"/>
-      <c r="H42" s="183"/>
-      <c r="I42" s="184"/>
-      <c r="J42" s="184"/>
-      <c r="K42" s="184"/>
-      <c r="L42" s="184"/>
-      <c r="M42" s="185"/>
-      <c r="N42" s="186"/>
-      <c r="O42" s="187"/>
-      <c r="P42" s="188"/>
+      <c r="C42" s="202"/>
+      <c r="D42" s="202"/>
+      <c r="E42" s="202"/>
+      <c r="F42" s="202"/>
+      <c r="G42" s="202"/>
+      <c r="H42" s="207"/>
+      <c r="I42" s="208"/>
+      <c r="J42" s="208"/>
+      <c r="K42" s="208"/>
+      <c r="L42" s="208"/>
+      <c r="M42" s="209"/>
+      <c r="N42" s="203"/>
+      <c r="O42" s="204"/>
+      <c r="P42" s="205"/>
       <c r="Q42" s="49"/>
-      <c r="R42" s="189"/>
-      <c r="S42" s="189"/>
+      <c r="R42" s="206"/>
+      <c r="S42" s="206"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="49"/>
       <c r="B43" s="49"/>
-      <c r="C43" s="182"/>
-      <c r="D43" s="182"/>
-      <c r="E43" s="182"/>
-      <c r="F43" s="182"/>
-      <c r="G43" s="182"/>
-      <c r="H43" s="183"/>
-      <c r="I43" s="184"/>
-      <c r="J43" s="184"/>
-      <c r="K43" s="184"/>
-      <c r="L43" s="184"/>
-      <c r="M43" s="185"/>
-      <c r="N43" s="186"/>
-      <c r="O43" s="187"/>
-      <c r="P43" s="188"/>
+      <c r="C43" s="202"/>
+      <c r="D43" s="202"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="202"/>
+      <c r="G43" s="202"/>
+      <c r="H43" s="207"/>
+      <c r="I43" s="208"/>
+      <c r="J43" s="208"/>
+      <c r="K43" s="208"/>
+      <c r="L43" s="208"/>
+      <c r="M43" s="209"/>
+      <c r="N43" s="203"/>
+      <c r="O43" s="204"/>
+      <c r="P43" s="205"/>
       <c r="Q43" s="49"/>
-      <c r="R43" s="189"/>
-      <c r="S43" s="189"/>
+      <c r="R43" s="206"/>
+      <c r="S43" s="206"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="49"/>
       <c r="B44" s="49"/>
-      <c r="C44" s="182"/>
-      <c r="D44" s="182"/>
-      <c r="E44" s="182"/>
-      <c r="F44" s="182"/>
-      <c r="G44" s="182"/>
-      <c r="H44" s="183"/>
-      <c r="I44" s="184"/>
-      <c r="J44" s="184"/>
-      <c r="K44" s="184"/>
-      <c r="L44" s="184"/>
-      <c r="M44" s="185"/>
-      <c r="N44" s="186"/>
-      <c r="O44" s="187"/>
-      <c r="P44" s="188"/>
+      <c r="C44" s="202"/>
+      <c r="D44" s="202"/>
+      <c r="E44" s="202"/>
+      <c r="F44" s="202"/>
+      <c r="G44" s="202"/>
+      <c r="H44" s="207"/>
+      <c r="I44" s="208"/>
+      <c r="J44" s="208"/>
+      <c r="K44" s="208"/>
+      <c r="L44" s="208"/>
+      <c r="M44" s="209"/>
+      <c r="N44" s="203"/>
+      <c r="O44" s="204"/>
+      <c r="P44" s="205"/>
       <c r="Q44" s="49"/>
-      <c r="R44" s="189"/>
-      <c r="S44" s="189"/>
+      <c r="R44" s="206"/>
+      <c r="S44" s="206"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="49"/>
       <c r="B45" s="49"/>
-      <c r="C45" s="182"/>
-      <c r="D45" s="182"/>
-      <c r="E45" s="182"/>
-      <c r="F45" s="182"/>
-      <c r="G45" s="182"/>
-      <c r="H45" s="183"/>
-      <c r="I45" s="184"/>
-      <c r="J45" s="184"/>
-      <c r="K45" s="184"/>
-      <c r="L45" s="184"/>
-      <c r="M45" s="185"/>
-      <c r="N45" s="186"/>
-      <c r="O45" s="187"/>
-      <c r="P45" s="188"/>
+      <c r="C45" s="202"/>
+      <c r="D45" s="202"/>
+      <c r="E45" s="202"/>
+      <c r="F45" s="202"/>
+      <c r="G45" s="202"/>
+      <c r="H45" s="207"/>
+      <c r="I45" s="208"/>
+      <c r="J45" s="208"/>
+      <c r="K45" s="208"/>
+      <c r="L45" s="208"/>
+      <c r="M45" s="209"/>
+      <c r="N45" s="203"/>
+      <c r="O45" s="204"/>
+      <c r="P45" s="205"/>
       <c r="Q45" s="49"/>
-      <c r="R45" s="189"/>
-      <c r="S45" s="189"/>
+      <c r="R45" s="206"/>
+      <c r="S45" s="206"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="49"/>
       <c r="B46" s="49"/>
-      <c r="C46" s="182"/>
-      <c r="D46" s="182"/>
-      <c r="E46" s="182"/>
-      <c r="F46" s="182"/>
-      <c r="G46" s="182"/>
-      <c r="H46" s="183"/>
-      <c r="I46" s="184"/>
-      <c r="J46" s="184"/>
-      <c r="K46" s="184"/>
-      <c r="L46" s="184"/>
-      <c r="M46" s="185"/>
-      <c r="N46" s="186"/>
-      <c r="O46" s="187"/>
-      <c r="P46" s="188"/>
+      <c r="C46" s="202"/>
+      <c r="D46" s="202"/>
+      <c r="E46" s="202"/>
+      <c r="F46" s="202"/>
+      <c r="G46" s="202"/>
+      <c r="H46" s="207"/>
+      <c r="I46" s="208"/>
+      <c r="J46" s="208"/>
+      <c r="K46" s="208"/>
+      <c r="L46" s="208"/>
+      <c r="M46" s="209"/>
+      <c r="N46" s="203"/>
+      <c r="O46" s="204"/>
+      <c r="P46" s="205"/>
       <c r="Q46" s="49"/>
-      <c r="R46" s="189"/>
-      <c r="S46" s="189"/>
+      <c r="R46" s="206"/>
+      <c r="S46" s="206"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="49"/>
       <c r="B47" s="49"/>
-      <c r="C47" s="182"/>
-      <c r="D47" s="182"/>
-      <c r="E47" s="182"/>
-      <c r="F47" s="182"/>
-      <c r="G47" s="182"/>
-      <c r="H47" s="183"/>
-      <c r="I47" s="184"/>
-      <c r="J47" s="184"/>
-      <c r="K47" s="184"/>
-      <c r="L47" s="184"/>
-      <c r="M47" s="185"/>
-      <c r="N47" s="186"/>
-      <c r="O47" s="187"/>
-      <c r="P47" s="188"/>
+      <c r="C47" s="202"/>
+      <c r="D47" s="202"/>
+      <c r="E47" s="202"/>
+      <c r="F47" s="202"/>
+      <c r="G47" s="202"/>
+      <c r="H47" s="207"/>
+      <c r="I47" s="208"/>
+      <c r="J47" s="208"/>
+      <c r="K47" s="208"/>
+      <c r="L47" s="208"/>
+      <c r="M47" s="209"/>
+      <c r="N47" s="203"/>
+      <c r="O47" s="204"/>
+      <c r="P47" s="205"/>
       <c r="Q47" s="49"/>
-      <c r="R47" s="189"/>
-      <c r="S47" s="189"/>
+      <c r="R47" s="206"/>
+      <c r="S47" s="206"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="49"/>
       <c r="B48" s="49"/>
-      <c r="C48" s="182"/>
-      <c r="D48" s="182"/>
-      <c r="E48" s="182"/>
-      <c r="F48" s="182"/>
-      <c r="G48" s="182"/>
-      <c r="H48" s="183"/>
-      <c r="I48" s="184"/>
-      <c r="J48" s="184"/>
-      <c r="K48" s="184"/>
-      <c r="L48" s="184"/>
-      <c r="M48" s="185"/>
-      <c r="N48" s="186"/>
-      <c r="O48" s="187"/>
-      <c r="P48" s="188"/>
+      <c r="C48" s="202"/>
+      <c r="D48" s="202"/>
+      <c r="E48" s="202"/>
+      <c r="F48" s="202"/>
+      <c r="G48" s="202"/>
+      <c r="H48" s="207"/>
+      <c r="I48" s="208"/>
+      <c r="J48" s="208"/>
+      <c r="K48" s="208"/>
+      <c r="L48" s="208"/>
+      <c r="M48" s="209"/>
+      <c r="N48" s="203"/>
+      <c r="O48" s="204"/>
+      <c r="P48" s="205"/>
       <c r="Q48" s="49"/>
-      <c r="R48" s="189"/>
-      <c r="S48" s="189"/>
+      <c r="R48" s="206"/>
+      <c r="S48" s="206"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="49"/>
       <c r="B49" s="49"/>
-      <c r="C49" s="182"/>
-      <c r="D49" s="182"/>
-      <c r="E49" s="182"/>
-      <c r="F49" s="182"/>
-      <c r="G49" s="182"/>
-      <c r="H49" s="183"/>
-      <c r="I49" s="184"/>
-      <c r="J49" s="184"/>
-      <c r="K49" s="184"/>
-      <c r="L49" s="184"/>
-      <c r="M49" s="185"/>
-      <c r="N49" s="186"/>
-      <c r="O49" s="187"/>
-      <c r="P49" s="188"/>
+      <c r="C49" s="202"/>
+      <c r="D49" s="202"/>
+      <c r="E49" s="202"/>
+      <c r="F49" s="202"/>
+      <c r="G49" s="202"/>
+      <c r="H49" s="207"/>
+      <c r="I49" s="208"/>
+      <c r="J49" s="208"/>
+      <c r="K49" s="208"/>
+      <c r="L49" s="208"/>
+      <c r="M49" s="209"/>
+      <c r="N49" s="203"/>
+      <c r="O49" s="204"/>
+      <c r="P49" s="205"/>
       <c r="Q49" s="49"/>
-      <c r="R49" s="189"/>
-      <c r="S49" s="189"/>
+      <c r="R49" s="206"/>
+      <c r="S49" s="206"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="49"/>
       <c r="B50" s="49"/>
-      <c r="C50" s="182"/>
-      <c r="D50" s="182"/>
-      <c r="E50" s="182"/>
-      <c r="F50" s="182"/>
-      <c r="G50" s="182"/>
-      <c r="H50" s="183"/>
-      <c r="I50" s="184"/>
-      <c r="J50" s="184"/>
-      <c r="K50" s="184"/>
-      <c r="L50" s="184"/>
-      <c r="M50" s="185"/>
-      <c r="N50" s="186"/>
-      <c r="O50" s="187"/>
-      <c r="P50" s="188"/>
+      <c r="C50" s="202"/>
+      <c r="D50" s="202"/>
+      <c r="E50" s="202"/>
+      <c r="F50" s="202"/>
+      <c r="G50" s="202"/>
+      <c r="H50" s="207"/>
+      <c r="I50" s="208"/>
+      <c r="J50" s="208"/>
+      <c r="K50" s="208"/>
+      <c r="L50" s="208"/>
+      <c r="M50" s="209"/>
+      <c r="N50" s="203"/>
+      <c r="O50" s="204"/>
+      <c r="P50" s="205"/>
       <c r="Q50" s="49"/>
-      <c r="R50" s="189"/>
-      <c r="S50" s="189"/>
+      <c r="R50" s="206"/>
+      <c r="S50" s="206"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="49"/>
       <c r="B51" s="49"/>
-      <c r="C51" s="182"/>
-      <c r="D51" s="182"/>
-      <c r="E51" s="182"/>
-      <c r="F51" s="182"/>
-      <c r="G51" s="182"/>
-      <c r="H51" s="183"/>
-      <c r="I51" s="184"/>
-      <c r="J51" s="184"/>
-      <c r="K51" s="184"/>
-      <c r="L51" s="184"/>
-      <c r="M51" s="185"/>
-      <c r="N51" s="186"/>
-      <c r="O51" s="187"/>
-      <c r="P51" s="188"/>
+      <c r="C51" s="202"/>
+      <c r="D51" s="202"/>
+      <c r="E51" s="202"/>
+      <c r="F51" s="202"/>
+      <c r="G51" s="202"/>
+      <c r="H51" s="207"/>
+      <c r="I51" s="208"/>
+      <c r="J51" s="208"/>
+      <c r="K51" s="208"/>
+      <c r="L51" s="208"/>
+      <c r="M51" s="209"/>
+      <c r="N51" s="203"/>
+      <c r="O51" s="204"/>
+      <c r="P51" s="205"/>
       <c r="Q51" s="49"/>
-      <c r="R51" s="189"/>
-      <c r="S51" s="189"/>
+      <c r="R51" s="206"/>
+      <c r="S51" s="206"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="49"/>
       <c r="B52" s="49"/>
-      <c r="C52" s="182"/>
-      <c r="D52" s="182"/>
-      <c r="E52" s="182"/>
-      <c r="F52" s="182"/>
-      <c r="G52" s="182"/>
-      <c r="H52" s="183"/>
-      <c r="I52" s="184"/>
-      <c r="J52" s="184"/>
-      <c r="K52" s="184"/>
-      <c r="L52" s="184"/>
-      <c r="M52" s="185"/>
-      <c r="N52" s="186"/>
-      <c r="O52" s="187"/>
-      <c r="P52" s="188"/>
+      <c r="C52" s="202"/>
+      <c r="D52" s="202"/>
+      <c r="E52" s="202"/>
+      <c r="F52" s="202"/>
+      <c r="G52" s="202"/>
+      <c r="H52" s="207"/>
+      <c r="I52" s="208"/>
+      <c r="J52" s="208"/>
+      <c r="K52" s="208"/>
+      <c r="L52" s="208"/>
+      <c r="M52" s="209"/>
+      <c r="N52" s="203"/>
+      <c r="O52" s="204"/>
+      <c r="P52" s="205"/>
       <c r="Q52" s="49"/>
-      <c r="R52" s="189"/>
-      <c r="S52" s="189"/>
+      <c r="R52" s="206"/>
+      <c r="S52" s="206"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -18405,194 +18953,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/削除機能詳細設計書.xlsx
+++ b/Documents/削除機能詳細設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Documents\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB530C3-C96D-4228-99C2-AE28B543FA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1DF024-0903-4EFD-B4B7-35398CBC5246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="146">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -964,17 +964,6 @@
   </si>
   <si>
     <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>〇</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>山本(あ)</t>
-    <rPh sb="0" eb="2">
-      <t>ヤマモト</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -2307,11 +2296,11 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="76" xfId="5" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="56" fontId="17" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2337,6 +2326,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2347,11 +2369,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2367,9 +2437,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2388,84 +2455,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2529,27 +2518,48 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2562,65 +2572,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2630,19 +2610,100 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2650,78 +2711,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3336,16 +3325,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>40822</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>40822</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>122464</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>76890</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>258536</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>131318</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>1008679</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3374,8 +3363,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2898322" y="9184822"/>
-          <a:ext cx="4934639" cy="2122714"/>
+          <a:off x="2544536" y="27731357"/>
+          <a:ext cx="4934639" cy="2791215"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5979,97 +5968,80 @@
       <c r="BA34" s="64"/>
     </row>
     <row r="35" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A35" s="210" t="s">
-        <v>132</v>
-      </c>
-      <c r="B35" s="211"/>
-      <c r="C35" s="211"/>
-      <c r="D35" s="211"/>
-      <c r="E35" s="211"/>
-      <c r="F35" s="211"/>
-      <c r="G35" s="211"/>
-      <c r="H35" s="211"/>
-      <c r="I35" s="211"/>
-      <c r="J35" s="211"/>
-      <c r="K35" s="211"/>
-      <c r="L35" s="211"/>
-      <c r="M35" s="211"/>
-      <c r="N35" s="211"/>
-      <c r="O35" s="211"/>
-      <c r="P35" s="211"/>
-      <c r="Q35" s="211"/>
-      <c r="R35" s="211"/>
-      <c r="S35" s="211"/>
-      <c r="T35" s="211"/>
-      <c r="U35" s="211"/>
-      <c r="V35" s="211"/>
-      <c r="W35" s="211"/>
-      <c r="X35" s="211"/>
-      <c r="Y35" s="211"/>
-      <c r="Z35" s="211"/>
-      <c r="AA35" s="211"/>
-      <c r="AB35" s="211"/>
-      <c r="AC35" s="211"/>
-      <c r="AD35" s="211"/>
-      <c r="AE35" s="211"/>
-      <c r="AF35" s="211"/>
-      <c r="AG35" s="211"/>
-      <c r="AH35" s="211"/>
-      <c r="AI35" s="211"/>
-      <c r="AJ35" s="211"/>
-      <c r="AK35" s="211"/>
-      <c r="AL35" s="211"/>
-      <c r="AM35" s="211"/>
-      <c r="AN35" s="211"/>
-      <c r="AO35" s="211"/>
-      <c r="AP35" s="211"/>
-      <c r="AQ35" s="211"/>
-      <c r="AR35" s="211"/>
-      <c r="AS35" s="211"/>
-      <c r="AT35" s="211"/>
-      <c r="AU35" s="211"/>
-      <c r="AV35" s="211"/>
-      <c r="AW35" s="211"/>
-      <c r="AX35" s="211"/>
-      <c r="AY35" s="211"/>
-      <c r="AZ35" s="211"/>
-      <c r="BA35" s="212"/>
+      <c r="A35" s="62"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="63"/>
+      <c r="P35" s="63"/>
+      <c r="Q35" s="63"/>
+      <c r="R35" s="63"/>
+      <c r="S35" s="63"/>
+      <c r="T35" s="63"/>
+      <c r="U35" s="63"/>
+      <c r="V35" s="63"/>
+      <c r="W35" s="63"/>
+      <c r="X35" s="63"/>
+      <c r="Y35" s="63"/>
+      <c r="Z35" s="63"/>
+      <c r="AA35" s="63"/>
+      <c r="AB35" s="63"/>
+      <c r="AC35" s="63"/>
+      <c r="AD35" s="63"/>
+      <c r="AE35" s="63"/>
+      <c r="AF35" s="63"/>
+      <c r="AG35" s="63"/>
+      <c r="AH35" s="63"/>
+      <c r="AI35" s="63"/>
+      <c r="AJ35" s="63"/>
+      <c r="AK35" s="63"/>
+      <c r="BA35" s="64"/>
     </row>
     <row r="36" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A36" s="65"/>
-      <c r="B36" s="66"/>
-      <c r="C36" s="66"/>
-      <c r="D36" s="66"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="66"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="66"/>
-      <c r="J36" s="66"/>
-      <c r="K36" s="66"/>
-      <c r="L36" s="66"/>
-      <c r="M36" s="66"/>
-      <c r="N36" s="66"/>
-      <c r="O36" s="66"/>
-      <c r="P36" s="66"/>
-      <c r="Q36" s="66"/>
-      <c r="R36" s="66"/>
-      <c r="S36" s="66"/>
-      <c r="T36" s="66"/>
-      <c r="U36" s="66"/>
-      <c r="V36" s="66"/>
-      <c r="W36" s="66"/>
-      <c r="X36" s="66"/>
-      <c r="Y36" s="66"/>
-      <c r="Z36" s="66"/>
-      <c r="AA36" s="66"/>
-      <c r="AB36" s="66"/>
-      <c r="AC36" s="66"/>
-      <c r="AD36" s="66"/>
-      <c r="AE36" s="66"/>
-      <c r="AF36" s="66"/>
-      <c r="AG36" s="66"/>
-      <c r="AH36" s="66"/>
+      <c r="A36" s="62"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="63"/>
+      <c r="K36" s="63"/>
+      <c r="L36" s="63"/>
+      <c r="M36" s="63"/>
+      <c r="N36" s="63"/>
+      <c r="O36" s="63"/>
+      <c r="P36" s="63"/>
+      <c r="Q36" s="63"/>
+      <c r="R36" s="63"/>
+      <c r="S36" s="63"/>
+      <c r="T36" s="63"/>
+      <c r="U36" s="63"/>
+      <c r="V36" s="63"/>
+      <c r="W36" s="63"/>
+      <c r="X36" s="63"/>
+      <c r="Y36" s="63"/>
+      <c r="Z36" s="63"/>
+      <c r="AA36" s="63"/>
+      <c r="AB36" s="63"/>
+      <c r="AC36" s="63"/>
+      <c r="AD36" s="63"/>
+      <c r="AE36" s="63"/>
+      <c r="AF36" s="63"/>
+      <c r="AG36" s="63"/>
+      <c r="AH36" s="63"/>
       <c r="AI36" s="63"/>
       <c r="AJ36" s="63"/>
       <c r="AK36" s="63"/>
@@ -6316,139 +6288,122 @@
       <c r="BA42" s="64"/>
     </row>
     <row r="43" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A43" s="67"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="68"/>
-      <c r="L43" s="68"/>
-      <c r="M43" s="68"/>
-      <c r="N43" s="68"/>
-      <c r="O43" s="68"/>
-      <c r="P43" s="68"/>
-      <c r="Q43" s="68"/>
-      <c r="R43" s="68"/>
-      <c r="S43" s="68"/>
-      <c r="T43" s="68"/>
-      <c r="U43" s="68"/>
-      <c r="V43" s="68"/>
-      <c r="W43" s="68"/>
-      <c r="X43" s="68"/>
-      <c r="Y43" s="68"/>
-      <c r="Z43" s="68"/>
-      <c r="AA43" s="68"/>
-      <c r="AB43" s="68"/>
-      <c r="AC43" s="68"/>
-      <c r="AD43" s="68"/>
-      <c r="AE43" s="68"/>
-      <c r="AF43" s="68"/>
-      <c r="AG43" s="68"/>
-      <c r="AH43" s="68"/>
-      <c r="AI43" s="68"/>
-      <c r="AJ43" s="68"/>
+      <c r="A43" s="62"/>
+      <c r="B43" s="63"/>
+      <c r="C43" s="63"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
+      <c r="F43" s="63"/>
+      <c r="G43" s="63"/>
+      <c r="H43" s="63"/>
+      <c r="I43" s="63"/>
+      <c r="J43" s="63"/>
+      <c r="K43" s="63"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="63"/>
+      <c r="N43" s="63"/>
+      <c r="O43" s="63"/>
+      <c r="P43" s="63"/>
+      <c r="Q43" s="63"/>
+      <c r="R43" s="63"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="63"/>
+      <c r="U43" s="63"/>
+      <c r="V43" s="63"/>
+      <c r="W43" s="63"/>
+      <c r="X43" s="63"/>
+      <c r="Y43" s="63"/>
+      <c r="Z43" s="63"/>
+      <c r="AA43" s="63"/>
+      <c r="AB43" s="63"/>
+      <c r="AC43" s="63"/>
+      <c r="AD43" s="63"/>
+      <c r="AE43" s="63"/>
+      <c r="AF43" s="63"/>
+      <c r="AG43" s="63"/>
+      <c r="AH43" s="63"/>
+      <c r="AI43" s="63"/>
+      <c r="AJ43" s="63"/>
       <c r="AK43" s="63"/>
       <c r="BA43" s="64"/>
     </row>
     <row r="44" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A44" s="210" t="s">
-        <v>133</v>
-      </c>
-      <c r="B44" s="211"/>
-      <c r="C44" s="211"/>
-      <c r="D44" s="211"/>
-      <c r="E44" s="211"/>
-      <c r="F44" s="211"/>
-      <c r="G44" s="211"/>
-      <c r="H44" s="211"/>
-      <c r="I44" s="211"/>
-      <c r="J44" s="211"/>
-      <c r="K44" s="211"/>
-      <c r="L44" s="211"/>
-      <c r="M44" s="211"/>
-      <c r="N44" s="211"/>
-      <c r="O44" s="211"/>
-      <c r="P44" s="211"/>
-      <c r="Q44" s="211"/>
-      <c r="R44" s="211"/>
-      <c r="S44" s="211"/>
-      <c r="T44" s="211"/>
-      <c r="U44" s="211"/>
-      <c r="V44" s="211"/>
-      <c r="W44" s="211"/>
-      <c r="X44" s="211"/>
-      <c r="Y44" s="211"/>
-      <c r="Z44" s="211"/>
-      <c r="AA44" s="211"/>
-      <c r="AB44" s="211"/>
-      <c r="AC44" s="211"/>
-      <c r="AD44" s="211"/>
-      <c r="AE44" s="211"/>
-      <c r="AF44" s="211"/>
-      <c r="AG44" s="211"/>
-      <c r="AH44" s="211"/>
-      <c r="AI44" s="211"/>
-      <c r="AJ44" s="211"/>
-      <c r="AK44" s="211"/>
-      <c r="AL44" s="211"/>
-      <c r="AM44" s="211"/>
-      <c r="AN44" s="211"/>
-      <c r="AO44" s="211"/>
-      <c r="AP44" s="211"/>
-      <c r="AQ44" s="211"/>
-      <c r="AR44" s="211"/>
-      <c r="AS44" s="211"/>
-      <c r="AT44" s="211"/>
-      <c r="AU44" s="211"/>
-      <c r="AV44" s="211"/>
-      <c r="AW44" s="211"/>
-      <c r="AX44" s="211"/>
-      <c r="AY44" s="211"/>
-      <c r="AZ44" s="211"/>
-      <c r="BA44" s="211"/>
+      <c r="A44" s="62"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
+      <c r="K44" s="63"/>
+      <c r="L44" s="63"/>
+      <c r="M44" s="63"/>
+      <c r="N44" s="63"/>
+      <c r="O44" s="63"/>
+      <c r="P44" s="63"/>
+      <c r="Q44" s="63"/>
+      <c r="R44" s="63"/>
+      <c r="S44" s="63"/>
+      <c r="T44" s="63"/>
+      <c r="U44" s="63"/>
+      <c r="V44" s="63"/>
+      <c r="W44" s="63"/>
+      <c r="X44" s="63"/>
+      <c r="Y44" s="63"/>
+      <c r="Z44" s="63"/>
+      <c r="AA44" s="63"/>
+      <c r="AB44" s="63"/>
+      <c r="AC44" s="63"/>
+      <c r="AD44" s="63"/>
+      <c r="AE44" s="63"/>
+      <c r="AF44" s="63"/>
+      <c r="AG44" s="63"/>
+      <c r="AH44" s="63"/>
+      <c r="AI44" s="63"/>
+      <c r="AJ44" s="63"/>
+      <c r="AK44" s="63"/>
+      <c r="BA44" s="64"/>
     </row>
     <row r="45" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A45" s="65"/>
-      <c r="B45" s="66"/>
-      <c r="C45" s="66"/>
-      <c r="D45" s="66"/>
-      <c r="E45" s="66"/>
-      <c r="F45" s="66"/>
-      <c r="G45" s="66"/>
-      <c r="H45" s="66"/>
-      <c r="I45" s="66"/>
-      <c r="J45" s="66"/>
-      <c r="K45" s="66"/>
-      <c r="L45" s="66"/>
-      <c r="M45" s="66"/>
-      <c r="N45" s="66"/>
-      <c r="O45" s="66"/>
-      <c r="P45" s="66"/>
-      <c r="Q45" s="66"/>
-      <c r="R45" s="66"/>
-      <c r="S45" s="66"/>
-      <c r="T45" s="66"/>
-      <c r="U45" s="66"/>
-      <c r="V45" s="66"/>
-      <c r="W45" s="66"/>
-      <c r="X45" s="66"/>
-      <c r="Y45" s="66"/>
-      <c r="Z45" s="66"/>
-      <c r="AA45" s="66"/>
-      <c r="AB45" s="66"/>
-      <c r="AC45" s="66"/>
-      <c r="AD45" s="66"/>
-      <c r="AE45" s="66"/>
-      <c r="AF45" s="66"/>
-      <c r="AG45" s="66"/>
-      <c r="AH45" s="66"/>
-      <c r="AI45" s="66"/>
-      <c r="AJ45" s="66"/>
+      <c r="A45" s="62"/>
+      <c r="B45" s="63"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="63"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="63"/>
+      <c r="L45" s="63"/>
+      <c r="M45" s="63"/>
+      <c r="N45" s="63"/>
+      <c r="O45" s="63"/>
+      <c r="P45" s="63"/>
+      <c r="Q45" s="63"/>
+      <c r="R45" s="63"/>
+      <c r="S45" s="63"/>
+      <c r="T45" s="63"/>
+      <c r="U45" s="63"/>
+      <c r="V45" s="63"/>
+      <c r="W45" s="63"/>
+      <c r="X45" s="63"/>
+      <c r="Y45" s="63"/>
+      <c r="Z45" s="63"/>
+      <c r="AA45" s="63"/>
+      <c r="AB45" s="63"/>
+      <c r="AC45" s="63"/>
+      <c r="AD45" s="63"/>
+      <c r="AE45" s="63"/>
+      <c r="AF45" s="63"/>
+      <c r="AG45" s="63"/>
+      <c r="AH45" s="63"/>
+      <c r="AI45" s="63"/>
+      <c r="AJ45" s="63"/>
       <c r="AK45" s="63"/>
       <c r="BA45" s="64"/>
     </row>
@@ -6493,133 +6448,2819 @@
       <c r="BA46" s="64"/>
     </row>
     <row r="47" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A47" s="67"/>
-      <c r="B47" s="68"/>
-      <c r="C47" s="68"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="68"/>
-      <c r="G47" s="68"/>
-      <c r="H47" s="68"/>
-      <c r="I47" s="68"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="68"/>
-      <c r="L47" s="68"/>
-      <c r="M47" s="68"/>
-      <c r="N47" s="68"/>
-      <c r="O47" s="68"/>
-      <c r="P47" s="68"/>
-      <c r="Q47" s="68"/>
-      <c r="R47" s="68"/>
-      <c r="S47" s="68"/>
-      <c r="T47" s="68"/>
-      <c r="U47" s="68"/>
-      <c r="V47" s="68"/>
-      <c r="W47" s="68"/>
-      <c r="X47" s="68"/>
-      <c r="Y47" s="68"/>
-      <c r="Z47" s="68"/>
-      <c r="AA47" s="68"/>
-      <c r="AB47" s="68"/>
-      <c r="AC47" s="68"/>
-      <c r="AD47" s="68"/>
-      <c r="AE47" s="68"/>
-      <c r="AF47" s="68"/>
-      <c r="AG47" s="68"/>
-      <c r="AH47" s="68"/>
-      <c r="AI47" s="68"/>
-      <c r="AJ47" s="68"/>
-      <c r="AK47" s="68"/>
-      <c r="AL47" s="53"/>
-      <c r="AM47" s="53"/>
-      <c r="AN47" s="53"/>
-      <c r="AO47" s="53"/>
-      <c r="AP47" s="53"/>
-      <c r="AQ47" s="53"/>
-      <c r="AR47" s="53"/>
-      <c r="AS47" s="53"/>
-      <c r="AT47" s="53"/>
-      <c r="AU47" s="53"/>
-      <c r="AV47" s="53"/>
-      <c r="AW47" s="53"/>
-      <c r="AX47" s="53"/>
-      <c r="AY47" s="53"/>
-      <c r="AZ47" s="53"/>
-      <c r="BA47" s="69"/>
-    </row>
-    <row r="48" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="49" ht="21.95" customHeight="1"/>
-    <row r="50" ht="21.95" customHeight="1"/>
-    <row r="51" ht="21.95" customHeight="1"/>
-    <row r="52" ht="21.95" customHeight="1"/>
-    <row r="53" ht="21.95" customHeight="1"/>
-    <row r="54" ht="21.95" customHeight="1"/>
-    <row r="55" ht="21.95" customHeight="1"/>
-    <row r="56" ht="21.95" customHeight="1"/>
-    <row r="57" ht="21.95" customHeight="1"/>
-    <row r="58" ht="21.95" customHeight="1"/>
-    <row r="59" ht="21.95" customHeight="1"/>
-    <row r="60" ht="21.95" customHeight="1"/>
-    <row r="61" ht="21.95" customHeight="1"/>
-    <row r="62" ht="21.95" customHeight="1"/>
-    <row r="63" ht="21.95" customHeight="1"/>
-    <row r="64" ht="21.95" customHeight="1"/>
-    <row r="65" ht="21.95" customHeight="1"/>
-    <row r="66" ht="21.95" customHeight="1"/>
-    <row r="67" ht="21.95" customHeight="1"/>
-    <row r="68" ht="21.95" customHeight="1"/>
-    <row r="69" ht="21.95" customHeight="1"/>
-    <row r="70" ht="21.95" customHeight="1"/>
-    <row r="71" ht="21.95" customHeight="1"/>
-    <row r="72" ht="21.95" customHeight="1"/>
-    <row r="73" ht="21.95" customHeight="1"/>
-    <row r="74" ht="21.95" customHeight="1"/>
-    <row r="75" ht="21.95" customHeight="1"/>
-    <row r="76" ht="21.95" customHeight="1"/>
-    <row r="77" ht="21.95" customHeight="1"/>
-    <row r="78" ht="21.95" customHeight="1"/>
-    <row r="79" ht="21.95" customHeight="1"/>
-    <row r="80" ht="21.95" customHeight="1"/>
-    <row r="81" ht="21.95" customHeight="1"/>
-    <row r="82" ht="21.95" customHeight="1"/>
-    <row r="83" ht="21.95" customHeight="1"/>
-    <row r="84" ht="21.95" customHeight="1"/>
-    <row r="85" ht="21.95" customHeight="1"/>
-    <row r="86" ht="21.95" customHeight="1"/>
-    <row r="87" ht="21.95" customHeight="1"/>
-    <row r="88" ht="21.95" customHeight="1"/>
-    <row r="89" ht="21.95" customHeight="1"/>
-    <row r="90" ht="21.95" customHeight="1"/>
-    <row r="91" ht="21.95" customHeight="1"/>
-    <row r="92" ht="21.95" customHeight="1"/>
-    <row r="93" ht="21.95" customHeight="1"/>
-    <row r="94" ht="21.95" customHeight="1"/>
-    <row r="95" ht="21.95" customHeight="1"/>
-    <row r="96" ht="21.95" customHeight="1"/>
-    <row r="97" ht="21.95" customHeight="1"/>
-    <row r="98" ht="21.95" customHeight="1"/>
-    <row r="99" ht="21.95" customHeight="1"/>
-    <row r="100" ht="21.95" customHeight="1"/>
-    <row r="101" ht="21.95" customHeight="1"/>
-    <row r="102" ht="21.95" customHeight="1"/>
-    <row r="103" ht="18" customHeight="1"/>
-    <row r="104" ht="21.95" customHeight="1"/>
-    <row r="105" ht="21.95" customHeight="1"/>
-    <row r="106" ht="21.95" customHeight="1"/>
-    <row r="107" ht="21.95" customHeight="1"/>
-    <row r="108" ht="21.95" customHeight="1"/>
-    <row r="109" ht="21.95" customHeight="1"/>
-    <row r="110" ht="21.95" customHeight="1"/>
-    <row r="111" ht="87.75" customHeight="1"/>
-    <row r="112" ht="18" customHeight="1"/>
-    <row r="113" ht="21.95" customHeight="1"/>
-    <row r="114" ht="21.95" customHeight="1"/>
-    <row r="115" ht="21.95" customHeight="1"/>
+      <c r="A47" s="62"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="63"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="63"/>
+      <c r="J47" s="63"/>
+      <c r="K47" s="63"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="63"/>
+      <c r="O47" s="63"/>
+      <c r="P47" s="63"/>
+      <c r="Q47" s="63"/>
+      <c r="R47" s="63"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="63"/>
+      <c r="U47" s="63"/>
+      <c r="V47" s="63"/>
+      <c r="W47" s="63"/>
+      <c r="X47" s="63"/>
+      <c r="Y47" s="63"/>
+      <c r="Z47" s="63"/>
+      <c r="AA47" s="63"/>
+      <c r="AB47" s="63"/>
+      <c r="AC47" s="63"/>
+      <c r="AD47" s="63"/>
+      <c r="AE47" s="63"/>
+      <c r="AF47" s="63"/>
+      <c r="AG47" s="63"/>
+      <c r="AH47" s="63"/>
+      <c r="AI47" s="63"/>
+      <c r="AJ47" s="63"/>
+      <c r="AK47" s="63"/>
+      <c r="BA47" s="64"/>
+    </row>
+    <row r="48" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A48" s="62"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="63"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="63"/>
+      <c r="J48" s="63"/>
+      <c r="K48" s="63"/>
+      <c r="L48" s="63"/>
+      <c r="M48" s="63"/>
+      <c r="N48" s="63"/>
+      <c r="O48" s="63"/>
+      <c r="P48" s="63"/>
+      <c r="Q48" s="63"/>
+      <c r="R48" s="63"/>
+      <c r="S48" s="63"/>
+      <c r="T48" s="63"/>
+      <c r="U48" s="63"/>
+      <c r="V48" s="63"/>
+      <c r="W48" s="63"/>
+      <c r="X48" s="63"/>
+      <c r="Y48" s="63"/>
+      <c r="Z48" s="63"/>
+      <c r="AA48" s="63"/>
+      <c r="AB48" s="63"/>
+      <c r="AC48" s="63"/>
+      <c r="AD48" s="63"/>
+      <c r="AE48" s="63"/>
+      <c r="AF48" s="63"/>
+      <c r="AG48" s="63"/>
+      <c r="AH48" s="63"/>
+      <c r="AI48" s="63"/>
+      <c r="AJ48" s="63"/>
+      <c r="AK48" s="63"/>
+      <c r="BA48" s="64"/>
+    </row>
+    <row r="49" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A49" s="62"/>
+      <c r="B49" s="63"/>
+      <c r="C49" s="63"/>
+      <c r="D49" s="63"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="63"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="63"/>
+      <c r="I49" s="63"/>
+      <c r="J49" s="63"/>
+      <c r="K49" s="63"/>
+      <c r="L49" s="63"/>
+      <c r="M49" s="63"/>
+      <c r="N49" s="63"/>
+      <c r="O49" s="63"/>
+      <c r="P49" s="63"/>
+      <c r="Q49" s="63"/>
+      <c r="R49" s="63"/>
+      <c r="S49" s="63"/>
+      <c r="T49" s="63"/>
+      <c r="U49" s="63"/>
+      <c r="V49" s="63"/>
+      <c r="W49" s="63"/>
+      <c r="X49" s="63"/>
+      <c r="Y49" s="63"/>
+      <c r="Z49" s="63"/>
+      <c r="AA49" s="63"/>
+      <c r="AB49" s="63"/>
+      <c r="AC49" s="63"/>
+      <c r="AD49" s="63"/>
+      <c r="AE49" s="63"/>
+      <c r="AF49" s="63"/>
+      <c r="AG49" s="63"/>
+      <c r="AH49" s="63"/>
+      <c r="AI49" s="63"/>
+      <c r="AJ49" s="63"/>
+      <c r="AK49" s="63"/>
+      <c r="BA49" s="64"/>
+    </row>
+    <row r="50" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A50" s="62"/>
+      <c r="B50" s="63"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="63"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="63"/>
+      <c r="J50" s="63"/>
+      <c r="K50" s="63"/>
+      <c r="L50" s="63"/>
+      <c r="M50" s="63"/>
+      <c r="N50" s="63"/>
+      <c r="O50" s="63"/>
+      <c r="P50" s="63"/>
+      <c r="Q50" s="63"/>
+      <c r="R50" s="63"/>
+      <c r="S50" s="63"/>
+      <c r="T50" s="63"/>
+      <c r="U50" s="63"/>
+      <c r="V50" s="63"/>
+      <c r="W50" s="63"/>
+      <c r="X50" s="63"/>
+      <c r="Y50" s="63"/>
+      <c r="Z50" s="63"/>
+      <c r="AA50" s="63"/>
+      <c r="AB50" s="63"/>
+      <c r="AC50" s="63"/>
+      <c r="AD50" s="63"/>
+      <c r="AE50" s="63"/>
+      <c r="AF50" s="63"/>
+      <c r="AG50" s="63"/>
+      <c r="AH50" s="63"/>
+      <c r="AI50" s="63"/>
+      <c r="AJ50" s="63"/>
+      <c r="AK50" s="63"/>
+      <c r="BA50" s="64"/>
+    </row>
+    <row r="51" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A51" s="62"/>
+      <c r="B51" s="63"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="63"/>
+      <c r="J51" s="63"/>
+      <c r="K51" s="63"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="63"/>
+      <c r="O51" s="63"/>
+      <c r="P51" s="63"/>
+      <c r="Q51" s="63"/>
+      <c r="R51" s="63"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="63"/>
+      <c r="U51" s="63"/>
+      <c r="V51" s="63"/>
+      <c r="W51" s="63"/>
+      <c r="X51" s="63"/>
+      <c r="Y51" s="63"/>
+      <c r="Z51" s="63"/>
+      <c r="AA51" s="63"/>
+      <c r="AB51" s="63"/>
+      <c r="AC51" s="63"/>
+      <c r="AD51" s="63"/>
+      <c r="AE51" s="63"/>
+      <c r="AF51" s="63"/>
+      <c r="AG51" s="63"/>
+      <c r="AH51" s="63"/>
+      <c r="AI51" s="63"/>
+      <c r="AJ51" s="63"/>
+      <c r="AK51" s="63"/>
+      <c r="BA51" s="64"/>
+    </row>
+    <row r="52" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A52" s="62"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="63"/>
+      <c r="J52" s="63"/>
+      <c r="K52" s="63"/>
+      <c r="L52" s="63"/>
+      <c r="M52" s="63"/>
+      <c r="N52" s="63"/>
+      <c r="O52" s="63"/>
+      <c r="P52" s="63"/>
+      <c r="Q52" s="63"/>
+      <c r="R52" s="63"/>
+      <c r="S52" s="63"/>
+      <c r="T52" s="63"/>
+      <c r="U52" s="63"/>
+      <c r="V52" s="63"/>
+      <c r="W52" s="63"/>
+      <c r="X52" s="63"/>
+      <c r="Y52" s="63"/>
+      <c r="Z52" s="63"/>
+      <c r="AA52" s="63"/>
+      <c r="AB52" s="63"/>
+      <c r="AC52" s="63"/>
+      <c r="AD52" s="63"/>
+      <c r="AE52" s="63"/>
+      <c r="AF52" s="63"/>
+      <c r="AG52" s="63"/>
+      <c r="AH52" s="63"/>
+      <c r="AI52" s="63"/>
+      <c r="AJ52" s="63"/>
+      <c r="AK52" s="63"/>
+      <c r="BA52" s="64"/>
+    </row>
+    <row r="53" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A53" s="62"/>
+      <c r="B53" s="63"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="63"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="63"/>
+      <c r="I53" s="63"/>
+      <c r="J53" s="63"/>
+      <c r="K53" s="63"/>
+      <c r="L53" s="63"/>
+      <c r="M53" s="63"/>
+      <c r="N53" s="63"/>
+      <c r="O53" s="63"/>
+      <c r="P53" s="63"/>
+      <c r="Q53" s="63"/>
+      <c r="R53" s="63"/>
+      <c r="S53" s="63"/>
+      <c r="T53" s="63"/>
+      <c r="U53" s="63"/>
+      <c r="V53" s="63"/>
+      <c r="W53" s="63"/>
+      <c r="X53" s="63"/>
+      <c r="Y53" s="63"/>
+      <c r="Z53" s="63"/>
+      <c r="AA53" s="63"/>
+      <c r="AB53" s="63"/>
+      <c r="AC53" s="63"/>
+      <c r="AD53" s="63"/>
+      <c r="AE53" s="63"/>
+      <c r="AF53" s="63"/>
+      <c r="AG53" s="63"/>
+      <c r="AH53" s="63"/>
+      <c r="AI53" s="63"/>
+      <c r="AJ53" s="63"/>
+      <c r="AK53" s="63"/>
+      <c r="BA53" s="64"/>
+    </row>
+    <row r="54" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A54" s="62"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="63"/>
+      <c r="G54" s="63"/>
+      <c r="H54" s="63"/>
+      <c r="I54" s="63"/>
+      <c r="J54" s="63"/>
+      <c r="K54" s="63"/>
+      <c r="L54" s="63"/>
+      <c r="M54" s="63"/>
+      <c r="N54" s="63"/>
+      <c r="O54" s="63"/>
+      <c r="P54" s="63"/>
+      <c r="Q54" s="63"/>
+      <c r="R54" s="63"/>
+      <c r="S54" s="63"/>
+      <c r="T54" s="63"/>
+      <c r="U54" s="63"/>
+      <c r="V54" s="63"/>
+      <c r="W54" s="63"/>
+      <c r="X54" s="63"/>
+      <c r="Y54" s="63"/>
+      <c r="Z54" s="63"/>
+      <c r="AA54" s="63"/>
+      <c r="AB54" s="63"/>
+      <c r="AC54" s="63"/>
+      <c r="AD54" s="63"/>
+      <c r="AE54" s="63"/>
+      <c r="AF54" s="63"/>
+      <c r="AG54" s="63"/>
+      <c r="AH54" s="63"/>
+      <c r="AI54" s="63"/>
+      <c r="AJ54" s="63"/>
+      <c r="AK54" s="63"/>
+      <c r="BA54" s="64"/>
+    </row>
+    <row r="55" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A55" s="62"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="63"/>
+      <c r="J55" s="63"/>
+      <c r="K55" s="63"/>
+      <c r="L55" s="63"/>
+      <c r="M55" s="63"/>
+      <c r="N55" s="63"/>
+      <c r="O55" s="63"/>
+      <c r="P55" s="63"/>
+      <c r="Q55" s="63"/>
+      <c r="R55" s="63"/>
+      <c r="S55" s="63"/>
+      <c r="T55" s="63"/>
+      <c r="U55" s="63"/>
+      <c r="V55" s="63"/>
+      <c r="W55" s="63"/>
+      <c r="X55" s="63"/>
+      <c r="Y55" s="63"/>
+      <c r="Z55" s="63"/>
+      <c r="AA55" s="63"/>
+      <c r="AB55" s="63"/>
+      <c r="AC55" s="63"/>
+      <c r="AD55" s="63"/>
+      <c r="AE55" s="63"/>
+      <c r="AF55" s="63"/>
+      <c r="AG55" s="63"/>
+      <c r="AH55" s="63"/>
+      <c r="AI55" s="63"/>
+      <c r="AJ55" s="63"/>
+      <c r="AK55" s="63"/>
+      <c r="BA55" s="64"/>
+    </row>
+    <row r="56" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A56" s="62"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="63"/>
+      <c r="I56" s="63"/>
+      <c r="J56" s="63"/>
+      <c r="K56" s="63"/>
+      <c r="L56" s="63"/>
+      <c r="M56" s="63"/>
+      <c r="N56" s="63"/>
+      <c r="O56" s="63"/>
+      <c r="P56" s="63"/>
+      <c r="Q56" s="63"/>
+      <c r="R56" s="63"/>
+      <c r="S56" s="63"/>
+      <c r="T56" s="63"/>
+      <c r="U56" s="63"/>
+      <c r="V56" s="63"/>
+      <c r="W56" s="63"/>
+      <c r="X56" s="63"/>
+      <c r="Y56" s="63"/>
+      <c r="Z56" s="63"/>
+      <c r="AA56" s="63"/>
+      <c r="AB56" s="63"/>
+      <c r="AC56" s="63"/>
+      <c r="AD56" s="63"/>
+      <c r="AE56" s="63"/>
+      <c r="AF56" s="63"/>
+      <c r="AG56" s="63"/>
+      <c r="AH56" s="63"/>
+      <c r="AI56" s="63"/>
+      <c r="AJ56" s="63"/>
+      <c r="AK56" s="63"/>
+      <c r="BA56" s="64"/>
+    </row>
+    <row r="57" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A57" s="62"/>
+      <c r="B57" s="63"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="63"/>
+      <c r="G57" s="63"/>
+      <c r="H57" s="63"/>
+      <c r="I57" s="63"/>
+      <c r="J57" s="63"/>
+      <c r="K57" s="63"/>
+      <c r="L57" s="63"/>
+      <c r="M57" s="63"/>
+      <c r="N57" s="63"/>
+      <c r="O57" s="63"/>
+      <c r="P57" s="63"/>
+      <c r="Q57" s="63"/>
+      <c r="R57" s="63"/>
+      <c r="S57" s="63"/>
+      <c r="T57" s="63"/>
+      <c r="U57" s="63"/>
+      <c r="V57" s="63"/>
+      <c r="W57" s="63"/>
+      <c r="X57" s="63"/>
+      <c r="Y57" s="63"/>
+      <c r="Z57" s="63"/>
+      <c r="AA57" s="63"/>
+      <c r="AB57" s="63"/>
+      <c r="AC57" s="63"/>
+      <c r="AD57" s="63"/>
+      <c r="AE57" s="63"/>
+      <c r="AF57" s="63"/>
+      <c r="AG57" s="63"/>
+      <c r="AH57" s="63"/>
+      <c r="AI57" s="63"/>
+      <c r="AJ57" s="63"/>
+      <c r="AK57" s="63"/>
+      <c r="BA57" s="64"/>
+    </row>
+    <row r="58" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A58" s="62"/>
+      <c r="B58" s="63"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
+      <c r="F58" s="63"/>
+      <c r="G58" s="63"/>
+      <c r="H58" s="63"/>
+      <c r="I58" s="63"/>
+      <c r="J58" s="63"/>
+      <c r="K58" s="63"/>
+      <c r="L58" s="63"/>
+      <c r="M58" s="63"/>
+      <c r="N58" s="63"/>
+      <c r="O58" s="63"/>
+      <c r="P58" s="63"/>
+      <c r="Q58" s="63"/>
+      <c r="R58" s="63"/>
+      <c r="S58" s="63"/>
+      <c r="T58" s="63"/>
+      <c r="U58" s="63"/>
+      <c r="V58" s="63"/>
+      <c r="W58" s="63"/>
+      <c r="X58" s="63"/>
+      <c r="Y58" s="63"/>
+      <c r="Z58" s="63"/>
+      <c r="AA58" s="63"/>
+      <c r="AB58" s="63"/>
+      <c r="AC58" s="63"/>
+      <c r="AD58" s="63"/>
+      <c r="AE58" s="63"/>
+      <c r="AF58" s="63"/>
+      <c r="AG58" s="63"/>
+      <c r="AH58" s="63"/>
+      <c r="AI58" s="63"/>
+      <c r="AJ58" s="63"/>
+      <c r="AK58" s="63"/>
+      <c r="BA58" s="64"/>
+    </row>
+    <row r="59" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A59" s="62"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="63"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="63"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="63"/>
+      <c r="H59" s="63"/>
+      <c r="I59" s="63"/>
+      <c r="J59" s="63"/>
+      <c r="K59" s="63"/>
+      <c r="L59" s="63"/>
+      <c r="M59" s="63"/>
+      <c r="N59" s="63"/>
+      <c r="O59" s="63"/>
+      <c r="P59" s="63"/>
+      <c r="Q59" s="63"/>
+      <c r="R59" s="63"/>
+      <c r="S59" s="63"/>
+      <c r="T59" s="63"/>
+      <c r="U59" s="63"/>
+      <c r="V59" s="63"/>
+      <c r="W59" s="63"/>
+      <c r="X59" s="63"/>
+      <c r="Y59" s="63"/>
+      <c r="Z59" s="63"/>
+      <c r="AA59" s="63"/>
+      <c r="AB59" s="63"/>
+      <c r="AC59" s="63"/>
+      <c r="AD59" s="63"/>
+      <c r="AE59" s="63"/>
+      <c r="AF59" s="63"/>
+      <c r="AG59" s="63"/>
+      <c r="AH59" s="63"/>
+      <c r="AI59" s="63"/>
+      <c r="AJ59" s="63"/>
+      <c r="AK59" s="63"/>
+      <c r="BA59" s="64"/>
+    </row>
+    <row r="60" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A60" s="62"/>
+      <c r="B60" s="63"/>
+      <c r="C60" s="63"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="63"/>
+      <c r="F60" s="63"/>
+      <c r="G60" s="63"/>
+      <c r="H60" s="63"/>
+      <c r="I60" s="63"/>
+      <c r="J60" s="63"/>
+      <c r="K60" s="63"/>
+      <c r="L60" s="63"/>
+      <c r="M60" s="63"/>
+      <c r="N60" s="63"/>
+      <c r="O60" s="63"/>
+      <c r="P60" s="63"/>
+      <c r="Q60" s="63"/>
+      <c r="R60" s="63"/>
+      <c r="S60" s="63"/>
+      <c r="T60" s="63"/>
+      <c r="U60" s="63"/>
+      <c r="V60" s="63"/>
+      <c r="W60" s="63"/>
+      <c r="X60" s="63"/>
+      <c r="Y60" s="63"/>
+      <c r="Z60" s="63"/>
+      <c r="AA60" s="63"/>
+      <c r="AB60" s="63"/>
+      <c r="AC60" s="63"/>
+      <c r="AD60" s="63"/>
+      <c r="AE60" s="63"/>
+      <c r="AF60" s="63"/>
+      <c r="AG60" s="63"/>
+      <c r="AH60" s="63"/>
+      <c r="AI60" s="63"/>
+      <c r="AJ60" s="63"/>
+      <c r="AK60" s="63"/>
+      <c r="BA60" s="64"/>
+    </row>
+    <row r="61" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A61" s="62"/>
+      <c r="B61" s="63"/>
+      <c r="C61" s="63"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="63"/>
+      <c r="G61" s="63"/>
+      <c r="H61" s="63"/>
+      <c r="I61" s="63"/>
+      <c r="J61" s="63"/>
+      <c r="K61" s="63"/>
+      <c r="L61" s="63"/>
+      <c r="M61" s="63"/>
+      <c r="N61" s="63"/>
+      <c r="O61" s="63"/>
+      <c r="P61" s="63"/>
+      <c r="Q61" s="63"/>
+      <c r="R61" s="63"/>
+      <c r="S61" s="63"/>
+      <c r="T61" s="63"/>
+      <c r="U61" s="63"/>
+      <c r="V61" s="63"/>
+      <c r="W61" s="63"/>
+      <c r="X61" s="63"/>
+      <c r="Y61" s="63"/>
+      <c r="Z61" s="63"/>
+      <c r="AA61" s="63"/>
+      <c r="AB61" s="63"/>
+      <c r="AC61" s="63"/>
+      <c r="AD61" s="63"/>
+      <c r="AE61" s="63"/>
+      <c r="AF61" s="63"/>
+      <c r="AG61" s="63"/>
+      <c r="AH61" s="63"/>
+      <c r="AI61" s="63"/>
+      <c r="AJ61" s="63"/>
+      <c r="AK61" s="63"/>
+      <c r="BA61" s="64"/>
+    </row>
+    <row r="62" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A62" s="62"/>
+      <c r="B62" s="63"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="63"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
+      <c r="H62" s="63"/>
+      <c r="I62" s="63"/>
+      <c r="J62" s="63"/>
+      <c r="K62" s="63"/>
+      <c r="L62" s="63"/>
+      <c r="M62" s="63"/>
+      <c r="N62" s="63"/>
+      <c r="O62" s="63"/>
+      <c r="P62" s="63"/>
+      <c r="Q62" s="63"/>
+      <c r="R62" s="63"/>
+      <c r="S62" s="63"/>
+      <c r="T62" s="63"/>
+      <c r="U62" s="63"/>
+      <c r="V62" s="63"/>
+      <c r="W62" s="63"/>
+      <c r="X62" s="63"/>
+      <c r="Y62" s="63"/>
+      <c r="Z62" s="63"/>
+      <c r="AA62" s="63"/>
+      <c r="AB62" s="63"/>
+      <c r="AC62" s="63"/>
+      <c r="AD62" s="63"/>
+      <c r="AE62" s="63"/>
+      <c r="AF62" s="63"/>
+      <c r="AG62" s="63"/>
+      <c r="AH62" s="63"/>
+      <c r="AI62" s="63"/>
+      <c r="AJ62" s="63"/>
+      <c r="AK62" s="63"/>
+      <c r="BA62" s="64"/>
+    </row>
+    <row r="63" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A63" s="62"/>
+      <c r="B63" s="63"/>
+      <c r="C63" s="63"/>
+      <c r="D63" s="63"/>
+      <c r="E63" s="63"/>
+      <c r="F63" s="63"/>
+      <c r="G63" s="63"/>
+      <c r="H63" s="63"/>
+      <c r="I63" s="63"/>
+      <c r="J63" s="63"/>
+      <c r="K63" s="63"/>
+      <c r="L63" s="63"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="63"/>
+      <c r="O63" s="63"/>
+      <c r="P63" s="63"/>
+      <c r="Q63" s="63"/>
+      <c r="R63" s="63"/>
+      <c r="S63" s="63"/>
+      <c r="T63" s="63"/>
+      <c r="U63" s="63"/>
+      <c r="V63" s="63"/>
+      <c r="W63" s="63"/>
+      <c r="X63" s="63"/>
+      <c r="Y63" s="63"/>
+      <c r="Z63" s="63"/>
+      <c r="AA63" s="63"/>
+      <c r="AB63" s="63"/>
+      <c r="AC63" s="63"/>
+      <c r="AD63" s="63"/>
+      <c r="AE63" s="63"/>
+      <c r="AF63" s="63"/>
+      <c r="AG63" s="63"/>
+      <c r="AH63" s="63"/>
+      <c r="AI63" s="63"/>
+      <c r="AJ63" s="63"/>
+      <c r="AK63" s="63"/>
+      <c r="BA63" s="64"/>
+    </row>
+    <row r="64" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A64" s="62"/>
+      <c r="B64" s="63"/>
+      <c r="C64" s="63"/>
+      <c r="D64" s="63"/>
+      <c r="E64" s="63"/>
+      <c r="F64" s="63"/>
+      <c r="G64" s="63"/>
+      <c r="H64" s="63"/>
+      <c r="I64" s="63"/>
+      <c r="J64" s="63"/>
+      <c r="K64" s="63"/>
+      <c r="L64" s="63"/>
+      <c r="M64" s="63"/>
+      <c r="N64" s="63"/>
+      <c r="O64" s="63"/>
+      <c r="P64" s="63"/>
+      <c r="Q64" s="63"/>
+      <c r="R64" s="63"/>
+      <c r="S64" s="63"/>
+      <c r="T64" s="63"/>
+      <c r="U64" s="63"/>
+      <c r="V64" s="63"/>
+      <c r="W64" s="63"/>
+      <c r="X64" s="63"/>
+      <c r="Y64" s="63"/>
+      <c r="Z64" s="63"/>
+      <c r="AA64" s="63"/>
+      <c r="AB64" s="63"/>
+      <c r="AC64" s="63"/>
+      <c r="AD64" s="63"/>
+      <c r="AE64" s="63"/>
+      <c r="AF64" s="63"/>
+      <c r="AG64" s="63"/>
+      <c r="AH64" s="63"/>
+      <c r="AI64" s="63"/>
+      <c r="AJ64" s="63"/>
+      <c r="AK64" s="63"/>
+      <c r="BA64" s="64"/>
+    </row>
+    <row r="65" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A65" s="62"/>
+      <c r="B65" s="63"/>
+      <c r="C65" s="63"/>
+      <c r="D65" s="63"/>
+      <c r="E65" s="63"/>
+      <c r="F65" s="63"/>
+      <c r="G65" s="63"/>
+      <c r="H65" s="63"/>
+      <c r="I65" s="63"/>
+      <c r="J65" s="63"/>
+      <c r="K65" s="63"/>
+      <c r="L65" s="63"/>
+      <c r="M65" s="63"/>
+      <c r="N65" s="63"/>
+      <c r="O65" s="63"/>
+      <c r="P65" s="63"/>
+      <c r="Q65" s="63"/>
+      <c r="R65" s="63"/>
+      <c r="S65" s="63"/>
+      <c r="T65" s="63"/>
+      <c r="U65" s="63"/>
+      <c r="V65" s="63"/>
+      <c r="W65" s="63"/>
+      <c r="X65" s="63"/>
+      <c r="Y65" s="63"/>
+      <c r="Z65" s="63"/>
+      <c r="AA65" s="63"/>
+      <c r="AB65" s="63"/>
+      <c r="AC65" s="63"/>
+      <c r="AD65" s="63"/>
+      <c r="AE65" s="63"/>
+      <c r="AF65" s="63"/>
+      <c r="AG65" s="63"/>
+      <c r="AH65" s="63"/>
+      <c r="AI65" s="63"/>
+      <c r="AJ65" s="63"/>
+      <c r="AK65" s="63"/>
+      <c r="BA65" s="64"/>
+    </row>
+    <row r="66" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A66" s="62"/>
+      <c r="B66" s="63"/>
+      <c r="C66" s="63"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="63"/>
+      <c r="F66" s="63"/>
+      <c r="G66" s="63"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="63"/>
+      <c r="J66" s="63"/>
+      <c r="K66" s="63"/>
+      <c r="L66" s="63"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="63"/>
+      <c r="O66" s="63"/>
+      <c r="P66" s="63"/>
+      <c r="Q66" s="63"/>
+      <c r="R66" s="63"/>
+      <c r="S66" s="63"/>
+      <c r="T66" s="63"/>
+      <c r="U66" s="63"/>
+      <c r="V66" s="63"/>
+      <c r="W66" s="63"/>
+      <c r="X66" s="63"/>
+      <c r="Y66" s="63"/>
+      <c r="Z66" s="63"/>
+      <c r="AA66" s="63"/>
+      <c r="AB66" s="63"/>
+      <c r="AC66" s="63"/>
+      <c r="AD66" s="63"/>
+      <c r="AE66" s="63"/>
+      <c r="AF66" s="63"/>
+      <c r="AG66" s="63"/>
+      <c r="AH66" s="63"/>
+      <c r="AI66" s="63"/>
+      <c r="AJ66" s="63"/>
+      <c r="AK66" s="63"/>
+      <c r="BA66" s="64"/>
+    </row>
+    <row r="67" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A67" s="62"/>
+      <c r="B67" s="63"/>
+      <c r="C67" s="63"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="63"/>
+      <c r="G67" s="63"/>
+      <c r="H67" s="63"/>
+      <c r="I67" s="63"/>
+      <c r="J67" s="63"/>
+      <c r="K67" s="63"/>
+      <c r="L67" s="63"/>
+      <c r="M67" s="63"/>
+      <c r="N67" s="63"/>
+      <c r="O67" s="63"/>
+      <c r="P67" s="63"/>
+      <c r="Q67" s="63"/>
+      <c r="R67" s="63"/>
+      <c r="S67" s="63"/>
+      <c r="T67" s="63"/>
+      <c r="U67" s="63"/>
+      <c r="V67" s="63"/>
+      <c r="W67" s="63"/>
+      <c r="X67" s="63"/>
+      <c r="Y67" s="63"/>
+      <c r="Z67" s="63"/>
+      <c r="AA67" s="63"/>
+      <c r="AB67" s="63"/>
+      <c r="AC67" s="63"/>
+      <c r="AD67" s="63"/>
+      <c r="AE67" s="63"/>
+      <c r="AF67" s="63"/>
+      <c r="AG67" s="63"/>
+      <c r="AH67" s="63"/>
+      <c r="AI67" s="63"/>
+      <c r="AJ67" s="63"/>
+      <c r="AK67" s="63"/>
+      <c r="BA67" s="64"/>
+    </row>
+    <row r="68" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A68" s="62"/>
+      <c r="B68" s="63"/>
+      <c r="C68" s="63"/>
+      <c r="D68" s="63"/>
+      <c r="E68" s="63"/>
+      <c r="F68" s="63"/>
+      <c r="G68" s="63"/>
+      <c r="H68" s="63"/>
+      <c r="I68" s="63"/>
+      <c r="J68" s="63"/>
+      <c r="K68" s="63"/>
+      <c r="L68" s="63"/>
+      <c r="M68" s="63"/>
+      <c r="N68" s="63"/>
+      <c r="O68" s="63"/>
+      <c r="P68" s="63"/>
+      <c r="Q68" s="63"/>
+      <c r="R68" s="63"/>
+      <c r="S68" s="63"/>
+      <c r="T68" s="63"/>
+      <c r="U68" s="63"/>
+      <c r="V68" s="63"/>
+      <c r="W68" s="63"/>
+      <c r="X68" s="63"/>
+      <c r="Y68" s="63"/>
+      <c r="Z68" s="63"/>
+      <c r="AA68" s="63"/>
+      <c r="AB68" s="63"/>
+      <c r="AC68" s="63"/>
+      <c r="AD68" s="63"/>
+      <c r="AE68" s="63"/>
+      <c r="AF68" s="63"/>
+      <c r="AG68" s="63"/>
+      <c r="AH68" s="63"/>
+      <c r="AI68" s="63"/>
+      <c r="AJ68" s="63"/>
+      <c r="AK68" s="63"/>
+      <c r="BA68" s="64"/>
+    </row>
+    <row r="69" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A69" s="62"/>
+      <c r="B69" s="63"/>
+      <c r="C69" s="63"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
+      <c r="I69" s="63"/>
+      <c r="J69" s="63"/>
+      <c r="K69" s="63"/>
+      <c r="L69" s="63"/>
+      <c r="M69" s="63"/>
+      <c r="N69" s="63"/>
+      <c r="O69" s="63"/>
+      <c r="P69" s="63"/>
+      <c r="Q69" s="63"/>
+      <c r="R69" s="63"/>
+      <c r="S69" s="63"/>
+      <c r="T69" s="63"/>
+      <c r="U69" s="63"/>
+      <c r="V69" s="63"/>
+      <c r="W69" s="63"/>
+      <c r="X69" s="63"/>
+      <c r="Y69" s="63"/>
+      <c r="Z69" s="63"/>
+      <c r="AA69" s="63"/>
+      <c r="AB69" s="63"/>
+      <c r="AC69" s="63"/>
+      <c r="AD69" s="63"/>
+      <c r="AE69" s="63"/>
+      <c r="AF69" s="63"/>
+      <c r="AG69" s="63"/>
+      <c r="AH69" s="63"/>
+      <c r="AI69" s="63"/>
+      <c r="AJ69" s="63"/>
+      <c r="AK69" s="63"/>
+      <c r="BA69" s="64"/>
+    </row>
+    <row r="70" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A70" s="62"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="63"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="63"/>
+      <c r="G70" s="63"/>
+      <c r="H70" s="63"/>
+      <c r="I70" s="63"/>
+      <c r="J70" s="63"/>
+      <c r="K70" s="63"/>
+      <c r="L70" s="63"/>
+      <c r="M70" s="63"/>
+      <c r="N70" s="63"/>
+      <c r="O70" s="63"/>
+      <c r="P70" s="63"/>
+      <c r="Q70" s="63"/>
+      <c r="R70" s="63"/>
+      <c r="S70" s="63"/>
+      <c r="T70" s="63"/>
+      <c r="U70" s="63"/>
+      <c r="V70" s="63"/>
+      <c r="W70" s="63"/>
+      <c r="X70" s="63"/>
+      <c r="Y70" s="63"/>
+      <c r="Z70" s="63"/>
+      <c r="AA70" s="63"/>
+      <c r="AB70" s="63"/>
+      <c r="AC70" s="63"/>
+      <c r="AD70" s="63"/>
+      <c r="AE70" s="63"/>
+      <c r="AF70" s="63"/>
+      <c r="AG70" s="63"/>
+      <c r="AH70" s="63"/>
+      <c r="AI70" s="63"/>
+      <c r="AJ70" s="63"/>
+      <c r="AK70" s="63"/>
+      <c r="BA70" s="64"/>
+    </row>
+    <row r="71" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A71" s="62"/>
+      <c r="B71" s="63"/>
+      <c r="C71" s="63"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="63"/>
+      <c r="F71" s="63"/>
+      <c r="G71" s="63"/>
+      <c r="H71" s="63"/>
+      <c r="I71" s="63"/>
+      <c r="J71" s="63"/>
+      <c r="K71" s="63"/>
+      <c r="L71" s="63"/>
+      <c r="M71" s="63"/>
+      <c r="N71" s="63"/>
+      <c r="O71" s="63"/>
+      <c r="P71" s="63"/>
+      <c r="Q71" s="63"/>
+      <c r="R71" s="63"/>
+      <c r="S71" s="63"/>
+      <c r="T71" s="63"/>
+      <c r="U71" s="63"/>
+      <c r="V71" s="63"/>
+      <c r="W71" s="63"/>
+      <c r="X71" s="63"/>
+      <c r="Y71" s="63"/>
+      <c r="Z71" s="63"/>
+      <c r="AA71" s="63"/>
+      <c r="AB71" s="63"/>
+      <c r="AC71" s="63"/>
+      <c r="AD71" s="63"/>
+      <c r="AE71" s="63"/>
+      <c r="AF71" s="63"/>
+      <c r="AG71" s="63"/>
+      <c r="AH71" s="63"/>
+      <c r="AI71" s="63"/>
+      <c r="AJ71" s="63"/>
+      <c r="AK71" s="63"/>
+      <c r="BA71" s="64"/>
+    </row>
+    <row r="72" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A72" s="62"/>
+      <c r="B72" s="63"/>
+      <c r="C72" s="63"/>
+      <c r="D72" s="63"/>
+      <c r="E72" s="63"/>
+      <c r="F72" s="63"/>
+      <c r="G72" s="63"/>
+      <c r="H72" s="63"/>
+      <c r="I72" s="63"/>
+      <c r="J72" s="63"/>
+      <c r="K72" s="63"/>
+      <c r="L72" s="63"/>
+      <c r="M72" s="63"/>
+      <c r="N72" s="63"/>
+      <c r="O72" s="63"/>
+      <c r="P72" s="63"/>
+      <c r="Q72" s="63"/>
+      <c r="R72" s="63"/>
+      <c r="S72" s="63"/>
+      <c r="T72" s="63"/>
+      <c r="U72" s="63"/>
+      <c r="V72" s="63"/>
+      <c r="W72" s="63"/>
+      <c r="X72" s="63"/>
+      <c r="Y72" s="63"/>
+      <c r="Z72" s="63"/>
+      <c r="AA72" s="63"/>
+      <c r="AB72" s="63"/>
+      <c r="AC72" s="63"/>
+      <c r="AD72" s="63"/>
+      <c r="AE72" s="63"/>
+      <c r="AF72" s="63"/>
+      <c r="AG72" s="63"/>
+      <c r="AH72" s="63"/>
+      <c r="AI72" s="63"/>
+      <c r="AJ72" s="63"/>
+      <c r="AK72" s="63"/>
+      <c r="BA72" s="64"/>
+    </row>
+    <row r="73" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A73" s="62"/>
+      <c r="B73" s="63"/>
+      <c r="C73" s="63"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="63"/>
+      <c r="F73" s="63"/>
+      <c r="G73" s="63"/>
+      <c r="H73" s="63"/>
+      <c r="I73" s="63"/>
+      <c r="J73" s="63"/>
+      <c r="K73" s="63"/>
+      <c r="L73" s="63"/>
+      <c r="M73" s="63"/>
+      <c r="N73" s="63"/>
+      <c r="O73" s="63"/>
+      <c r="P73" s="63"/>
+      <c r="Q73" s="63"/>
+      <c r="R73" s="63"/>
+      <c r="S73" s="63"/>
+      <c r="T73" s="63"/>
+      <c r="U73" s="63"/>
+      <c r="V73" s="63"/>
+      <c r="W73" s="63"/>
+      <c r="X73" s="63"/>
+      <c r="Y73" s="63"/>
+      <c r="Z73" s="63"/>
+      <c r="AA73" s="63"/>
+      <c r="AB73" s="63"/>
+      <c r="AC73" s="63"/>
+      <c r="AD73" s="63"/>
+      <c r="AE73" s="63"/>
+      <c r="AF73" s="63"/>
+      <c r="AG73" s="63"/>
+      <c r="AH73" s="63"/>
+      <c r="AI73" s="63"/>
+      <c r="AJ73" s="63"/>
+      <c r="AK73" s="63"/>
+      <c r="BA73" s="64"/>
+    </row>
+    <row r="74" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A74" s="62"/>
+      <c r="B74" s="63"/>
+      <c r="C74" s="63"/>
+      <c r="D74" s="63"/>
+      <c r="E74" s="63"/>
+      <c r="F74" s="63"/>
+      <c r="G74" s="63"/>
+      <c r="H74" s="63"/>
+      <c r="I74" s="63"/>
+      <c r="J74" s="63"/>
+      <c r="K74" s="63"/>
+      <c r="L74" s="63"/>
+      <c r="M74" s="63"/>
+      <c r="N74" s="63"/>
+      <c r="O74" s="63"/>
+      <c r="P74" s="63"/>
+      <c r="Q74" s="63"/>
+      <c r="R74" s="63"/>
+      <c r="S74" s="63"/>
+      <c r="T74" s="63"/>
+      <c r="U74" s="63"/>
+      <c r="V74" s="63"/>
+      <c r="W74" s="63"/>
+      <c r="X74" s="63"/>
+      <c r="Y74" s="63"/>
+      <c r="Z74" s="63"/>
+      <c r="AA74" s="63"/>
+      <c r="AB74" s="63"/>
+      <c r="AC74" s="63"/>
+      <c r="AD74" s="63"/>
+      <c r="AE74" s="63"/>
+      <c r="AF74" s="63"/>
+      <c r="AG74" s="63"/>
+      <c r="AH74" s="63"/>
+      <c r="AI74" s="63"/>
+      <c r="AJ74" s="63"/>
+      <c r="AK74" s="63"/>
+      <c r="BA74" s="64"/>
+    </row>
+    <row r="75" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A75" s="62"/>
+      <c r="B75" s="63"/>
+      <c r="C75" s="63"/>
+      <c r="D75" s="63"/>
+      <c r="E75" s="63"/>
+      <c r="F75" s="63"/>
+      <c r="G75" s="63"/>
+      <c r="H75" s="63"/>
+      <c r="I75" s="63"/>
+      <c r="J75" s="63"/>
+      <c r="K75" s="63"/>
+      <c r="L75" s="63"/>
+      <c r="M75" s="63"/>
+      <c r="N75" s="63"/>
+      <c r="O75" s="63"/>
+      <c r="P75" s="63"/>
+      <c r="Q75" s="63"/>
+      <c r="R75" s="63"/>
+      <c r="S75" s="63"/>
+      <c r="T75" s="63"/>
+      <c r="U75" s="63"/>
+      <c r="V75" s="63"/>
+      <c r="W75" s="63"/>
+      <c r="X75" s="63"/>
+      <c r="Y75" s="63"/>
+      <c r="Z75" s="63"/>
+      <c r="AA75" s="63"/>
+      <c r="AB75" s="63"/>
+      <c r="AC75" s="63"/>
+      <c r="AD75" s="63"/>
+      <c r="AE75" s="63"/>
+      <c r="AF75" s="63"/>
+      <c r="AG75" s="63"/>
+      <c r="AH75" s="63"/>
+      <c r="AI75" s="63"/>
+      <c r="AJ75" s="63"/>
+      <c r="AK75" s="63"/>
+      <c r="BA75" s="64"/>
+    </row>
+    <row r="76" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A76" s="62"/>
+      <c r="B76" s="63"/>
+      <c r="C76" s="63"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="63"/>
+      <c r="F76" s="63"/>
+      <c r="G76" s="63"/>
+      <c r="H76" s="63"/>
+      <c r="I76" s="63"/>
+      <c r="J76" s="63"/>
+      <c r="K76" s="63"/>
+      <c r="L76" s="63"/>
+      <c r="M76" s="63"/>
+      <c r="N76" s="63"/>
+      <c r="O76" s="63"/>
+      <c r="P76" s="63"/>
+      <c r="Q76" s="63"/>
+      <c r="R76" s="63"/>
+      <c r="S76" s="63"/>
+      <c r="T76" s="63"/>
+      <c r="U76" s="63"/>
+      <c r="V76" s="63"/>
+      <c r="W76" s="63"/>
+      <c r="X76" s="63"/>
+      <c r="Y76" s="63"/>
+      <c r="Z76" s="63"/>
+      <c r="AA76" s="63"/>
+      <c r="AB76" s="63"/>
+      <c r="AC76" s="63"/>
+      <c r="AD76" s="63"/>
+      <c r="AE76" s="63"/>
+      <c r="AF76" s="63"/>
+      <c r="AG76" s="63"/>
+      <c r="AH76" s="63"/>
+      <c r="AI76" s="63"/>
+      <c r="AJ76" s="63"/>
+      <c r="AK76" s="63"/>
+      <c r="BA76" s="64"/>
+    </row>
+    <row r="77" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A77" s="62"/>
+      <c r="B77" s="63"/>
+      <c r="C77" s="63"/>
+      <c r="D77" s="63"/>
+      <c r="E77" s="63"/>
+      <c r="F77" s="63"/>
+      <c r="G77" s="63"/>
+      <c r="H77" s="63"/>
+      <c r="I77" s="63"/>
+      <c r="J77" s="63"/>
+      <c r="K77" s="63"/>
+      <c r="L77" s="63"/>
+      <c r="M77" s="63"/>
+      <c r="N77" s="63"/>
+      <c r="O77" s="63"/>
+      <c r="P77" s="63"/>
+      <c r="Q77" s="63"/>
+      <c r="R77" s="63"/>
+      <c r="S77" s="63"/>
+      <c r="T77" s="63"/>
+      <c r="U77" s="63"/>
+      <c r="V77" s="63"/>
+      <c r="W77" s="63"/>
+      <c r="X77" s="63"/>
+      <c r="Y77" s="63"/>
+      <c r="Z77" s="63"/>
+      <c r="AA77" s="63"/>
+      <c r="AB77" s="63"/>
+      <c r="AC77" s="63"/>
+      <c r="AD77" s="63"/>
+      <c r="AE77" s="63"/>
+      <c r="AF77" s="63"/>
+      <c r="AG77" s="63"/>
+      <c r="AH77" s="63"/>
+      <c r="AI77" s="63"/>
+      <c r="AJ77" s="63"/>
+      <c r="AK77" s="63"/>
+      <c r="BA77" s="64"/>
+    </row>
+    <row r="78" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A78" s="62"/>
+      <c r="B78" s="63"/>
+      <c r="C78" s="63"/>
+      <c r="D78" s="63"/>
+      <c r="E78" s="63"/>
+      <c r="F78" s="63"/>
+      <c r="G78" s="63"/>
+      <c r="H78" s="63"/>
+      <c r="I78" s="63"/>
+      <c r="J78" s="63"/>
+      <c r="K78" s="63"/>
+      <c r="L78" s="63"/>
+      <c r="M78" s="63"/>
+      <c r="N78" s="63"/>
+      <c r="O78" s="63"/>
+      <c r="P78" s="63"/>
+      <c r="Q78" s="63"/>
+      <c r="R78" s="63"/>
+      <c r="S78" s="63"/>
+      <c r="T78" s="63"/>
+      <c r="U78" s="63"/>
+      <c r="V78" s="63"/>
+      <c r="W78" s="63"/>
+      <c r="X78" s="63"/>
+      <c r="Y78" s="63"/>
+      <c r="Z78" s="63"/>
+      <c r="AA78" s="63"/>
+      <c r="AB78" s="63"/>
+      <c r="AC78" s="63"/>
+      <c r="AD78" s="63"/>
+      <c r="AE78" s="63"/>
+      <c r="AF78" s="63"/>
+      <c r="AG78" s="63"/>
+      <c r="AH78" s="63"/>
+      <c r="AI78" s="63"/>
+      <c r="AJ78" s="63"/>
+      <c r="AK78" s="63"/>
+      <c r="BA78" s="64"/>
+    </row>
+    <row r="79" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A79" s="62"/>
+      <c r="B79" s="63"/>
+      <c r="C79" s="63"/>
+      <c r="D79" s="63"/>
+      <c r="E79" s="63"/>
+      <c r="F79" s="63"/>
+      <c r="G79" s="63"/>
+      <c r="H79" s="63"/>
+      <c r="I79" s="63"/>
+      <c r="J79" s="63"/>
+      <c r="K79" s="63"/>
+      <c r="L79" s="63"/>
+      <c r="M79" s="63"/>
+      <c r="N79" s="63"/>
+      <c r="O79" s="63"/>
+      <c r="P79" s="63"/>
+      <c r="Q79" s="63"/>
+      <c r="R79" s="63"/>
+      <c r="S79" s="63"/>
+      <c r="T79" s="63"/>
+      <c r="U79" s="63"/>
+      <c r="V79" s="63"/>
+      <c r="W79" s="63"/>
+      <c r="X79" s="63"/>
+      <c r="Y79" s="63"/>
+      <c r="Z79" s="63"/>
+      <c r="AA79" s="63"/>
+      <c r="AB79" s="63"/>
+      <c r="AC79" s="63"/>
+      <c r="AD79" s="63"/>
+      <c r="AE79" s="63"/>
+      <c r="AF79" s="63"/>
+      <c r="AG79" s="63"/>
+      <c r="AH79" s="63"/>
+      <c r="AI79" s="63"/>
+      <c r="AJ79" s="63"/>
+      <c r="AK79" s="63"/>
+      <c r="BA79" s="64"/>
+    </row>
+    <row r="80" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A80" s="62"/>
+      <c r="B80" s="63"/>
+      <c r="C80" s="63"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="63"/>
+      <c r="H80" s="63"/>
+      <c r="I80" s="63"/>
+      <c r="J80" s="63"/>
+      <c r="K80" s="63"/>
+      <c r="L80" s="63"/>
+      <c r="M80" s="63"/>
+      <c r="N80" s="63"/>
+      <c r="O80" s="63"/>
+      <c r="P80" s="63"/>
+      <c r="Q80" s="63"/>
+      <c r="R80" s="63"/>
+      <c r="S80" s="63"/>
+      <c r="T80" s="63"/>
+      <c r="U80" s="63"/>
+      <c r="V80" s="63"/>
+      <c r="W80" s="63"/>
+      <c r="X80" s="63"/>
+      <c r="Y80" s="63"/>
+      <c r="Z80" s="63"/>
+      <c r="AA80" s="63"/>
+      <c r="AB80" s="63"/>
+      <c r="AC80" s="63"/>
+      <c r="AD80" s="63"/>
+      <c r="AE80" s="63"/>
+      <c r="AF80" s="63"/>
+      <c r="AG80" s="63"/>
+      <c r="AH80" s="63"/>
+      <c r="AI80" s="63"/>
+      <c r="AJ80" s="63"/>
+      <c r="AK80" s="63"/>
+      <c r="BA80" s="64"/>
+    </row>
+    <row r="81" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A81" s="62"/>
+      <c r="B81" s="63"/>
+      <c r="C81" s="63"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="63"/>
+      <c r="I81" s="63"/>
+      <c r="J81" s="63"/>
+      <c r="K81" s="63"/>
+      <c r="L81" s="63"/>
+      <c r="M81" s="63"/>
+      <c r="N81" s="63"/>
+      <c r="O81" s="63"/>
+      <c r="P81" s="63"/>
+      <c r="Q81" s="63"/>
+      <c r="R81" s="63"/>
+      <c r="S81" s="63"/>
+      <c r="T81" s="63"/>
+      <c r="U81" s="63"/>
+      <c r="V81" s="63"/>
+      <c r="W81" s="63"/>
+      <c r="X81" s="63"/>
+      <c r="Y81" s="63"/>
+      <c r="Z81" s="63"/>
+      <c r="AA81" s="63"/>
+      <c r="AB81" s="63"/>
+      <c r="AC81" s="63"/>
+      <c r="AD81" s="63"/>
+      <c r="AE81" s="63"/>
+      <c r="AF81" s="63"/>
+      <c r="AG81" s="63"/>
+      <c r="AH81" s="63"/>
+      <c r="AI81" s="63"/>
+      <c r="AJ81" s="63"/>
+      <c r="AK81" s="63"/>
+      <c r="BA81" s="64"/>
+    </row>
+    <row r="82" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A82" s="62"/>
+      <c r="B82" s="63"/>
+      <c r="C82" s="63"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="63"/>
+      <c r="I82" s="63"/>
+      <c r="J82" s="63"/>
+      <c r="K82" s="63"/>
+      <c r="L82" s="63"/>
+      <c r="M82" s="63"/>
+      <c r="N82" s="63"/>
+      <c r="O82" s="63"/>
+      <c r="P82" s="63"/>
+      <c r="Q82" s="63"/>
+      <c r="R82" s="63"/>
+      <c r="S82" s="63"/>
+      <c r="T82" s="63"/>
+      <c r="U82" s="63"/>
+      <c r="V82" s="63"/>
+      <c r="W82" s="63"/>
+      <c r="X82" s="63"/>
+      <c r="Y82" s="63"/>
+      <c r="Z82" s="63"/>
+      <c r="AA82" s="63"/>
+      <c r="AB82" s="63"/>
+      <c r="AC82" s="63"/>
+      <c r="AD82" s="63"/>
+      <c r="AE82" s="63"/>
+      <c r="AF82" s="63"/>
+      <c r="AG82" s="63"/>
+      <c r="AH82" s="63"/>
+      <c r="AI82" s="63"/>
+      <c r="AJ82" s="63"/>
+      <c r="AK82" s="63"/>
+      <c r="BA82" s="64"/>
+    </row>
+    <row r="83" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A83" s="62"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="63"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="63"/>
+      <c r="I83" s="63"/>
+      <c r="J83" s="63"/>
+      <c r="K83" s="63"/>
+      <c r="L83" s="63"/>
+      <c r="M83" s="63"/>
+      <c r="N83" s="63"/>
+      <c r="O83" s="63"/>
+      <c r="P83" s="63"/>
+      <c r="Q83" s="63"/>
+      <c r="R83" s="63"/>
+      <c r="S83" s="63"/>
+      <c r="T83" s="63"/>
+      <c r="U83" s="63"/>
+      <c r="V83" s="63"/>
+      <c r="W83" s="63"/>
+      <c r="X83" s="63"/>
+      <c r="Y83" s="63"/>
+      <c r="Z83" s="63"/>
+      <c r="AA83" s="63"/>
+      <c r="AB83" s="63"/>
+      <c r="AC83" s="63"/>
+      <c r="AD83" s="63"/>
+      <c r="AE83" s="63"/>
+      <c r="AF83" s="63"/>
+      <c r="AG83" s="63"/>
+      <c r="AH83" s="63"/>
+      <c r="AI83" s="63"/>
+      <c r="AJ83" s="63"/>
+      <c r="AK83" s="63"/>
+      <c r="BA83" s="64"/>
+    </row>
+    <row r="84" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A84" s="62"/>
+      <c r="B84" s="63"/>
+      <c r="C84" s="63"/>
+      <c r="D84" s="63"/>
+      <c r="E84" s="63"/>
+      <c r="F84" s="63"/>
+      <c r="G84" s="63"/>
+      <c r="H84" s="63"/>
+      <c r="I84" s="63"/>
+      <c r="J84" s="63"/>
+      <c r="K84" s="63"/>
+      <c r="L84" s="63"/>
+      <c r="M84" s="63"/>
+      <c r="N84" s="63"/>
+      <c r="O84" s="63"/>
+      <c r="P84" s="63"/>
+      <c r="Q84" s="63"/>
+      <c r="R84" s="63"/>
+      <c r="S84" s="63"/>
+      <c r="T84" s="63"/>
+      <c r="U84" s="63"/>
+      <c r="V84" s="63"/>
+      <c r="W84" s="63"/>
+      <c r="X84" s="63"/>
+      <c r="Y84" s="63"/>
+      <c r="Z84" s="63"/>
+      <c r="AA84" s="63"/>
+      <c r="AB84" s="63"/>
+      <c r="AC84" s="63"/>
+      <c r="AD84" s="63"/>
+      <c r="AE84" s="63"/>
+      <c r="AF84" s="63"/>
+      <c r="AG84" s="63"/>
+      <c r="AH84" s="63"/>
+      <c r="AI84" s="63"/>
+      <c r="AJ84" s="63"/>
+      <c r="AK84" s="63"/>
+      <c r="BA84" s="64"/>
+    </row>
+    <row r="85" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A85" s="62"/>
+      <c r="B85" s="63"/>
+      <c r="C85" s="63"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="63"/>
+      <c r="F85" s="63"/>
+      <c r="G85" s="63"/>
+      <c r="H85" s="63"/>
+      <c r="I85" s="63"/>
+      <c r="J85" s="63"/>
+      <c r="K85" s="63"/>
+      <c r="L85" s="63"/>
+      <c r="M85" s="63"/>
+      <c r="N85" s="63"/>
+      <c r="O85" s="63"/>
+      <c r="P85" s="63"/>
+      <c r="Q85" s="63"/>
+      <c r="R85" s="63"/>
+      <c r="S85" s="63"/>
+      <c r="T85" s="63"/>
+      <c r="U85" s="63"/>
+      <c r="V85" s="63"/>
+      <c r="W85" s="63"/>
+      <c r="X85" s="63"/>
+      <c r="Y85" s="63"/>
+      <c r="Z85" s="63"/>
+      <c r="AA85" s="63"/>
+      <c r="AB85" s="63"/>
+      <c r="AC85" s="63"/>
+      <c r="AD85" s="63"/>
+      <c r="AE85" s="63"/>
+      <c r="AF85" s="63"/>
+      <c r="AG85" s="63"/>
+      <c r="AH85" s="63"/>
+      <c r="AI85" s="63"/>
+      <c r="AJ85" s="63"/>
+      <c r="AK85" s="63"/>
+      <c r="BA85" s="64"/>
+    </row>
+    <row r="86" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A86" s="62"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="63"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="63"/>
+      <c r="G86" s="63"/>
+      <c r="H86" s="63"/>
+      <c r="I86" s="63"/>
+      <c r="J86" s="63"/>
+      <c r="K86" s="63"/>
+      <c r="L86" s="63"/>
+      <c r="M86" s="63"/>
+      <c r="N86" s="63"/>
+      <c r="O86" s="63"/>
+      <c r="P86" s="63"/>
+      <c r="Q86" s="63"/>
+      <c r="R86" s="63"/>
+      <c r="S86" s="63"/>
+      <c r="T86" s="63"/>
+      <c r="U86" s="63"/>
+      <c r="V86" s="63"/>
+      <c r="W86" s="63"/>
+      <c r="X86" s="63"/>
+      <c r="Y86" s="63"/>
+      <c r="Z86" s="63"/>
+      <c r="AA86" s="63"/>
+      <c r="AB86" s="63"/>
+      <c r="AC86" s="63"/>
+      <c r="AD86" s="63"/>
+      <c r="AE86" s="63"/>
+      <c r="AF86" s="63"/>
+      <c r="AG86" s="63"/>
+      <c r="AH86" s="63"/>
+      <c r="AI86" s="63"/>
+      <c r="AJ86" s="63"/>
+      <c r="AK86" s="63"/>
+      <c r="BA86" s="64"/>
+    </row>
+    <row r="87" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A87" s="62"/>
+      <c r="B87" s="63"/>
+      <c r="C87" s="63"/>
+      <c r="D87" s="63"/>
+      <c r="E87" s="63"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="63"/>
+      <c r="H87" s="63"/>
+      <c r="I87" s="63"/>
+      <c r="J87" s="63"/>
+      <c r="K87" s="63"/>
+      <c r="L87" s="63"/>
+      <c r="M87" s="63"/>
+      <c r="N87" s="63"/>
+      <c r="O87" s="63"/>
+      <c r="P87" s="63"/>
+      <c r="Q87" s="63"/>
+      <c r="R87" s="63"/>
+      <c r="S87" s="63"/>
+      <c r="T87" s="63"/>
+      <c r="U87" s="63"/>
+      <c r="V87" s="63"/>
+      <c r="W87" s="63"/>
+      <c r="X87" s="63"/>
+      <c r="Y87" s="63"/>
+      <c r="Z87" s="63"/>
+      <c r="AA87" s="63"/>
+      <c r="AB87" s="63"/>
+      <c r="AC87" s="63"/>
+      <c r="AD87" s="63"/>
+      <c r="AE87" s="63"/>
+      <c r="AF87" s="63"/>
+      <c r="AG87" s="63"/>
+      <c r="AH87" s="63"/>
+      <c r="AI87" s="63"/>
+      <c r="AJ87" s="63"/>
+      <c r="AK87" s="63"/>
+      <c r="BA87" s="64"/>
+    </row>
+    <row r="88" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A88" s="62"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="63"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="63"/>
+      <c r="G88" s="63"/>
+      <c r="H88" s="63"/>
+      <c r="I88" s="63"/>
+      <c r="J88" s="63"/>
+      <c r="K88" s="63"/>
+      <c r="L88" s="63"/>
+      <c r="M88" s="63"/>
+      <c r="N88" s="63"/>
+      <c r="O88" s="63"/>
+      <c r="P88" s="63"/>
+      <c r="Q88" s="63"/>
+      <c r="R88" s="63"/>
+      <c r="S88" s="63"/>
+      <c r="T88" s="63"/>
+      <c r="U88" s="63"/>
+      <c r="V88" s="63"/>
+      <c r="W88" s="63"/>
+      <c r="X88" s="63"/>
+      <c r="Y88" s="63"/>
+      <c r="Z88" s="63"/>
+      <c r="AA88" s="63"/>
+      <c r="AB88" s="63"/>
+      <c r="AC88" s="63"/>
+      <c r="AD88" s="63"/>
+      <c r="AE88" s="63"/>
+      <c r="AF88" s="63"/>
+      <c r="AG88" s="63"/>
+      <c r="AH88" s="63"/>
+      <c r="AI88" s="63"/>
+      <c r="AJ88" s="63"/>
+      <c r="AK88" s="63"/>
+      <c r="BA88" s="64"/>
+    </row>
+    <row r="89" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A89" s="62"/>
+      <c r="B89" s="63"/>
+      <c r="C89" s="63"/>
+      <c r="D89" s="63"/>
+      <c r="E89" s="63"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="63"/>
+      <c r="H89" s="63"/>
+      <c r="I89" s="63"/>
+      <c r="J89" s="63"/>
+      <c r="K89" s="63"/>
+      <c r="L89" s="63"/>
+      <c r="M89" s="63"/>
+      <c r="N89" s="63"/>
+      <c r="O89" s="63"/>
+      <c r="P89" s="63"/>
+      <c r="Q89" s="63"/>
+      <c r="R89" s="63"/>
+      <c r="S89" s="63"/>
+      <c r="T89" s="63"/>
+      <c r="U89" s="63"/>
+      <c r="V89" s="63"/>
+      <c r="W89" s="63"/>
+      <c r="X89" s="63"/>
+      <c r="Y89" s="63"/>
+      <c r="Z89" s="63"/>
+      <c r="AA89" s="63"/>
+      <c r="AB89" s="63"/>
+      <c r="AC89" s="63"/>
+      <c r="AD89" s="63"/>
+      <c r="AE89" s="63"/>
+      <c r="AF89" s="63"/>
+      <c r="AG89" s="63"/>
+      <c r="AH89" s="63"/>
+      <c r="AI89" s="63"/>
+      <c r="AJ89" s="63"/>
+      <c r="AK89" s="63"/>
+      <c r="BA89" s="64"/>
+    </row>
+    <row r="90" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A90" s="62"/>
+      <c r="B90" s="63"/>
+      <c r="C90" s="63"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="63"/>
+      <c r="F90" s="63"/>
+      <c r="G90" s="63"/>
+      <c r="H90" s="63"/>
+      <c r="I90" s="63"/>
+      <c r="J90" s="63"/>
+      <c r="K90" s="63"/>
+      <c r="L90" s="63"/>
+      <c r="M90" s="63"/>
+      <c r="N90" s="63"/>
+      <c r="O90" s="63"/>
+      <c r="P90" s="63"/>
+      <c r="Q90" s="63"/>
+      <c r="R90" s="63"/>
+      <c r="S90" s="63"/>
+      <c r="T90" s="63"/>
+      <c r="U90" s="63"/>
+      <c r="V90" s="63"/>
+      <c r="W90" s="63"/>
+      <c r="X90" s="63"/>
+      <c r="Y90" s="63"/>
+      <c r="Z90" s="63"/>
+      <c r="AA90" s="63"/>
+      <c r="AB90" s="63"/>
+      <c r="AC90" s="63"/>
+      <c r="AD90" s="63"/>
+      <c r="AE90" s="63"/>
+      <c r="AF90" s="63"/>
+      <c r="AG90" s="63"/>
+      <c r="AH90" s="63"/>
+      <c r="AI90" s="63"/>
+      <c r="AJ90" s="63"/>
+      <c r="AK90" s="63"/>
+      <c r="BA90" s="64"/>
+    </row>
+    <row r="91" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A91" s="62"/>
+      <c r="B91" s="63"/>
+      <c r="C91" s="63"/>
+      <c r="D91" s="63"/>
+      <c r="E91" s="63"/>
+      <c r="F91" s="63"/>
+      <c r="G91" s="63"/>
+      <c r="H91" s="63"/>
+      <c r="I91" s="63"/>
+      <c r="J91" s="63"/>
+      <c r="K91" s="63"/>
+      <c r="L91" s="63"/>
+      <c r="M91" s="63"/>
+      <c r="N91" s="63"/>
+      <c r="O91" s="63"/>
+      <c r="P91" s="63"/>
+      <c r="Q91" s="63"/>
+      <c r="R91" s="63"/>
+      <c r="S91" s="63"/>
+      <c r="T91" s="63"/>
+      <c r="U91" s="63"/>
+      <c r="V91" s="63"/>
+      <c r="W91" s="63"/>
+      <c r="X91" s="63"/>
+      <c r="Y91" s="63"/>
+      <c r="Z91" s="63"/>
+      <c r="AA91" s="63"/>
+      <c r="AB91" s="63"/>
+      <c r="AC91" s="63"/>
+      <c r="AD91" s="63"/>
+      <c r="AE91" s="63"/>
+      <c r="AF91" s="63"/>
+      <c r="AG91" s="63"/>
+      <c r="AH91" s="63"/>
+      <c r="AI91" s="63"/>
+      <c r="AJ91" s="63"/>
+      <c r="AK91" s="63"/>
+      <c r="BA91" s="64"/>
+    </row>
+    <row r="92" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A92" s="62"/>
+      <c r="B92" s="63"/>
+      <c r="C92" s="63"/>
+      <c r="D92" s="63"/>
+      <c r="E92" s="63"/>
+      <c r="F92" s="63"/>
+      <c r="G92" s="63"/>
+      <c r="H92" s="63"/>
+      <c r="I92" s="63"/>
+      <c r="J92" s="63"/>
+      <c r="K92" s="63"/>
+      <c r="L92" s="63"/>
+      <c r="M92" s="63"/>
+      <c r="N92" s="63"/>
+      <c r="O92" s="63"/>
+      <c r="P92" s="63"/>
+      <c r="Q92" s="63"/>
+      <c r="R92" s="63"/>
+      <c r="S92" s="63"/>
+      <c r="T92" s="63"/>
+      <c r="U92" s="63"/>
+      <c r="V92" s="63"/>
+      <c r="W92" s="63"/>
+      <c r="X92" s="63"/>
+      <c r="Y92" s="63"/>
+      <c r="Z92" s="63"/>
+      <c r="AA92" s="63"/>
+      <c r="AB92" s="63"/>
+      <c r="AC92" s="63"/>
+      <c r="AD92" s="63"/>
+      <c r="AE92" s="63"/>
+      <c r="AF92" s="63"/>
+      <c r="AG92" s="63"/>
+      <c r="AH92" s="63"/>
+      <c r="AI92" s="63"/>
+      <c r="AJ92" s="63"/>
+      <c r="AK92" s="63"/>
+      <c r="BA92" s="64"/>
+    </row>
+    <row r="93" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A93" s="62"/>
+      <c r="B93" s="63"/>
+      <c r="C93" s="63"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="63"/>
+      <c r="G93" s="63"/>
+      <c r="H93" s="63"/>
+      <c r="I93" s="63"/>
+      <c r="J93" s="63"/>
+      <c r="K93" s="63"/>
+      <c r="L93" s="63"/>
+      <c r="M93" s="63"/>
+      <c r="N93" s="63"/>
+      <c r="O93" s="63"/>
+      <c r="P93" s="63"/>
+      <c r="Q93" s="63"/>
+      <c r="R93" s="63"/>
+      <c r="S93" s="63"/>
+      <c r="T93" s="63"/>
+      <c r="U93" s="63"/>
+      <c r="V93" s="63"/>
+      <c r="W93" s="63"/>
+      <c r="X93" s="63"/>
+      <c r="Y93" s="63"/>
+      <c r="Z93" s="63"/>
+      <c r="AA93" s="63"/>
+      <c r="AB93" s="63"/>
+      <c r="AC93" s="63"/>
+      <c r="AD93" s="63"/>
+      <c r="AE93" s="63"/>
+      <c r="AF93" s="63"/>
+      <c r="AG93" s="63"/>
+      <c r="AH93" s="63"/>
+      <c r="AI93" s="63"/>
+      <c r="AJ93" s="63"/>
+      <c r="AK93" s="63"/>
+      <c r="BA93" s="64"/>
+    </row>
+    <row r="94" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A94" s="62"/>
+      <c r="B94" s="63"/>
+      <c r="C94" s="63"/>
+      <c r="D94" s="63"/>
+      <c r="E94" s="63"/>
+      <c r="F94" s="63"/>
+      <c r="G94" s="63"/>
+      <c r="H94" s="63"/>
+      <c r="I94" s="63"/>
+      <c r="J94" s="63"/>
+      <c r="K94" s="63"/>
+      <c r="L94" s="63"/>
+      <c r="M94" s="63"/>
+      <c r="N94" s="63"/>
+      <c r="O94" s="63"/>
+      <c r="P94" s="63"/>
+      <c r="Q94" s="63"/>
+      <c r="R94" s="63"/>
+      <c r="S94" s="63"/>
+      <c r="T94" s="63"/>
+      <c r="U94" s="63"/>
+      <c r="V94" s="63"/>
+      <c r="W94" s="63"/>
+      <c r="X94" s="63"/>
+      <c r="Y94" s="63"/>
+      <c r="Z94" s="63"/>
+      <c r="AA94" s="63"/>
+      <c r="AB94" s="63"/>
+      <c r="AC94" s="63"/>
+      <c r="AD94" s="63"/>
+      <c r="AE94" s="63"/>
+      <c r="AF94" s="63"/>
+      <c r="AG94" s="63"/>
+      <c r="AH94" s="63"/>
+      <c r="AI94" s="63"/>
+      <c r="AJ94" s="63"/>
+      <c r="AK94" s="63"/>
+      <c r="BA94" s="64"/>
+    </row>
+    <row r="95" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A95" s="62"/>
+      <c r="B95" s="63"/>
+      <c r="C95" s="63"/>
+      <c r="D95" s="63"/>
+      <c r="E95" s="63"/>
+      <c r="F95" s="63"/>
+      <c r="G95" s="63"/>
+      <c r="H95" s="63"/>
+      <c r="I95" s="63"/>
+      <c r="J95" s="63"/>
+      <c r="K95" s="63"/>
+      <c r="L95" s="63"/>
+      <c r="M95" s="63"/>
+      <c r="N95" s="63"/>
+      <c r="O95" s="63"/>
+      <c r="P95" s="63"/>
+      <c r="Q95" s="63"/>
+      <c r="R95" s="63"/>
+      <c r="S95" s="63"/>
+      <c r="T95" s="63"/>
+      <c r="U95" s="63"/>
+      <c r="V95" s="63"/>
+      <c r="W95" s="63"/>
+      <c r="X95" s="63"/>
+      <c r="Y95" s="63"/>
+      <c r="Z95" s="63"/>
+      <c r="AA95" s="63"/>
+      <c r="AB95" s="63"/>
+      <c r="AC95" s="63"/>
+      <c r="AD95" s="63"/>
+      <c r="AE95" s="63"/>
+      <c r="AF95" s="63"/>
+      <c r="AG95" s="63"/>
+      <c r="AH95" s="63"/>
+      <c r="AI95" s="63"/>
+      <c r="AJ95" s="63"/>
+      <c r="AK95" s="63"/>
+      <c r="BA95" s="64"/>
+    </row>
+    <row r="96" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A96" s="62"/>
+      <c r="B96" s="63"/>
+      <c r="C96" s="63"/>
+      <c r="D96" s="63"/>
+      <c r="E96" s="63"/>
+      <c r="F96" s="63"/>
+      <c r="G96" s="63"/>
+      <c r="H96" s="63"/>
+      <c r="I96" s="63"/>
+      <c r="J96" s="63"/>
+      <c r="K96" s="63"/>
+      <c r="L96" s="63"/>
+      <c r="M96" s="63"/>
+      <c r="N96" s="63"/>
+      <c r="O96" s="63"/>
+      <c r="P96" s="63"/>
+      <c r="Q96" s="63"/>
+      <c r="R96" s="63"/>
+      <c r="S96" s="63"/>
+      <c r="T96" s="63"/>
+      <c r="U96" s="63"/>
+      <c r="V96" s="63"/>
+      <c r="W96" s="63"/>
+      <c r="X96" s="63"/>
+      <c r="Y96" s="63"/>
+      <c r="Z96" s="63"/>
+      <c r="AA96" s="63"/>
+      <c r="AB96" s="63"/>
+      <c r="AC96" s="63"/>
+      <c r="AD96" s="63"/>
+      <c r="AE96" s="63"/>
+      <c r="AF96" s="63"/>
+      <c r="AG96" s="63"/>
+      <c r="AH96" s="63"/>
+      <c r="AI96" s="63"/>
+      <c r="AJ96" s="63"/>
+      <c r="AK96" s="63"/>
+      <c r="BA96" s="64"/>
+    </row>
+    <row r="97" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A97" s="62"/>
+      <c r="B97" s="63"/>
+      <c r="C97" s="63"/>
+      <c r="D97" s="63"/>
+      <c r="E97" s="63"/>
+      <c r="F97" s="63"/>
+      <c r="G97" s="63"/>
+      <c r="H97" s="63"/>
+      <c r="I97" s="63"/>
+      <c r="J97" s="63"/>
+      <c r="K97" s="63"/>
+      <c r="L97" s="63"/>
+      <c r="M97" s="63"/>
+      <c r="N97" s="63"/>
+      <c r="O97" s="63"/>
+      <c r="P97" s="63"/>
+      <c r="Q97" s="63"/>
+      <c r="R97" s="63"/>
+      <c r="S97" s="63"/>
+      <c r="T97" s="63"/>
+      <c r="U97" s="63"/>
+      <c r="V97" s="63"/>
+      <c r="W97" s="63"/>
+      <c r="X97" s="63"/>
+      <c r="Y97" s="63"/>
+      <c r="Z97" s="63"/>
+      <c r="AA97" s="63"/>
+      <c r="AB97" s="63"/>
+      <c r="AC97" s="63"/>
+      <c r="AD97" s="63"/>
+      <c r="AE97" s="63"/>
+      <c r="AF97" s="63"/>
+      <c r="AG97" s="63"/>
+      <c r="AH97" s="63"/>
+      <c r="AI97" s="63"/>
+      <c r="AJ97" s="63"/>
+      <c r="AK97" s="63"/>
+      <c r="BA97" s="64"/>
+    </row>
+    <row r="98" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A98" s="62"/>
+      <c r="B98" s="63"/>
+      <c r="C98" s="63"/>
+      <c r="D98" s="63"/>
+      <c r="E98" s="63"/>
+      <c r="F98" s="63"/>
+      <c r="G98" s="63"/>
+      <c r="H98" s="63"/>
+      <c r="I98" s="63"/>
+      <c r="J98" s="63"/>
+      <c r="K98" s="63"/>
+      <c r="L98" s="63"/>
+      <c r="M98" s="63"/>
+      <c r="N98" s="63"/>
+      <c r="O98" s="63"/>
+      <c r="P98" s="63"/>
+      <c r="Q98" s="63"/>
+      <c r="R98" s="63"/>
+      <c r="S98" s="63"/>
+      <c r="T98" s="63"/>
+      <c r="U98" s="63"/>
+      <c r="V98" s="63"/>
+      <c r="W98" s="63"/>
+      <c r="X98" s="63"/>
+      <c r="Y98" s="63"/>
+      <c r="Z98" s="63"/>
+      <c r="AA98" s="63"/>
+      <c r="AB98" s="63"/>
+      <c r="AC98" s="63"/>
+      <c r="AD98" s="63"/>
+      <c r="AE98" s="63"/>
+      <c r="AF98" s="63"/>
+      <c r="AG98" s="63"/>
+      <c r="AH98" s="63"/>
+      <c r="AI98" s="63"/>
+      <c r="AJ98" s="63"/>
+      <c r="AK98" s="63"/>
+      <c r="BA98" s="64"/>
+    </row>
+    <row r="99" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A99" s="62"/>
+      <c r="B99" s="63"/>
+      <c r="C99" s="63"/>
+      <c r="D99" s="63"/>
+      <c r="E99" s="63"/>
+      <c r="F99" s="63"/>
+      <c r="G99" s="63"/>
+      <c r="H99" s="63"/>
+      <c r="I99" s="63"/>
+      <c r="J99" s="63"/>
+      <c r="K99" s="63"/>
+      <c r="L99" s="63"/>
+      <c r="M99" s="63"/>
+      <c r="N99" s="63"/>
+      <c r="O99" s="63"/>
+      <c r="P99" s="63"/>
+      <c r="Q99" s="63"/>
+      <c r="R99" s="63"/>
+      <c r="S99" s="63"/>
+      <c r="T99" s="63"/>
+      <c r="U99" s="63"/>
+      <c r="V99" s="63"/>
+      <c r="W99" s="63"/>
+      <c r="X99" s="63"/>
+      <c r="Y99" s="63"/>
+      <c r="Z99" s="63"/>
+      <c r="AA99" s="63"/>
+      <c r="AB99" s="63"/>
+      <c r="AC99" s="63"/>
+      <c r="AD99" s="63"/>
+      <c r="AE99" s="63"/>
+      <c r="AF99" s="63"/>
+      <c r="AG99" s="63"/>
+      <c r="AH99" s="63"/>
+      <c r="AI99" s="63"/>
+      <c r="AJ99" s="63"/>
+      <c r="AK99" s="63"/>
+      <c r="BA99" s="64"/>
+    </row>
+    <row r="100" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A100" s="62"/>
+      <c r="B100" s="63"/>
+      <c r="C100" s="63"/>
+      <c r="D100" s="63"/>
+      <c r="E100" s="63"/>
+      <c r="F100" s="63"/>
+      <c r="G100" s="63"/>
+      <c r="H100" s="63"/>
+      <c r="I100" s="63"/>
+      <c r="J100" s="63"/>
+      <c r="K100" s="63"/>
+      <c r="L100" s="63"/>
+      <c r="M100" s="63"/>
+      <c r="N100" s="63"/>
+      <c r="O100" s="63"/>
+      <c r="P100" s="63"/>
+      <c r="Q100" s="63"/>
+      <c r="R100" s="63"/>
+      <c r="S100" s="63"/>
+      <c r="T100" s="63"/>
+      <c r="U100" s="63"/>
+      <c r="V100" s="63"/>
+      <c r="W100" s="63"/>
+      <c r="X100" s="63"/>
+      <c r="Y100" s="63"/>
+      <c r="Z100" s="63"/>
+      <c r="AA100" s="63"/>
+      <c r="AB100" s="63"/>
+      <c r="AC100" s="63"/>
+      <c r="AD100" s="63"/>
+      <c r="AE100" s="63"/>
+      <c r="AF100" s="63"/>
+      <c r="AG100" s="63"/>
+      <c r="AH100" s="63"/>
+      <c r="AI100" s="63"/>
+      <c r="AJ100" s="63"/>
+      <c r="AK100" s="63"/>
+      <c r="BA100" s="64"/>
+    </row>
+    <row r="101" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A101" s="62"/>
+      <c r="B101" s="63"/>
+      <c r="C101" s="63"/>
+      <c r="D101" s="63"/>
+      <c r="E101" s="63"/>
+      <c r="F101" s="63"/>
+      <c r="G101" s="63"/>
+      <c r="H101" s="63"/>
+      <c r="I101" s="63"/>
+      <c r="J101" s="63"/>
+      <c r="K101" s="63"/>
+      <c r="L101" s="63"/>
+      <c r="M101" s="63"/>
+      <c r="N101" s="63"/>
+      <c r="O101" s="63"/>
+      <c r="P101" s="63"/>
+      <c r="Q101" s="63"/>
+      <c r="R101" s="63"/>
+      <c r="S101" s="63"/>
+      <c r="T101" s="63"/>
+      <c r="U101" s="63"/>
+      <c r="V101" s="63"/>
+      <c r="W101" s="63"/>
+      <c r="X101" s="63"/>
+      <c r="Y101" s="63"/>
+      <c r="Z101" s="63"/>
+      <c r="AA101" s="63"/>
+      <c r="AB101" s="63"/>
+      <c r="AC101" s="63"/>
+      <c r="AD101" s="63"/>
+      <c r="AE101" s="63"/>
+      <c r="AF101" s="63"/>
+      <c r="AG101" s="63"/>
+      <c r="AH101" s="63"/>
+      <c r="AI101" s="63"/>
+      <c r="AJ101" s="63"/>
+      <c r="AK101" s="63"/>
+      <c r="BA101" s="64"/>
+    </row>
+    <row r="102" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A102" s="62"/>
+      <c r="B102" s="63"/>
+      <c r="C102" s="63"/>
+      <c r="D102" s="63"/>
+      <c r="E102" s="63"/>
+      <c r="F102" s="63"/>
+      <c r="G102" s="63"/>
+      <c r="H102" s="63"/>
+      <c r="I102" s="63"/>
+      <c r="J102" s="63"/>
+      <c r="K102" s="63"/>
+      <c r="L102" s="63"/>
+      <c r="M102" s="63"/>
+      <c r="N102" s="63"/>
+      <c r="O102" s="63"/>
+      <c r="P102" s="63"/>
+      <c r="Q102" s="63"/>
+      <c r="R102" s="63"/>
+      <c r="S102" s="63"/>
+      <c r="T102" s="63"/>
+      <c r="U102" s="63"/>
+      <c r="V102" s="63"/>
+      <c r="W102" s="63"/>
+      <c r="X102" s="63"/>
+      <c r="Y102" s="63"/>
+      <c r="Z102" s="63"/>
+      <c r="AA102" s="63"/>
+      <c r="AB102" s="63"/>
+      <c r="AC102" s="63"/>
+      <c r="AD102" s="63"/>
+      <c r="AE102" s="63"/>
+      <c r="AF102" s="63"/>
+      <c r="AG102" s="63"/>
+      <c r="AH102" s="63"/>
+      <c r="AI102" s="63"/>
+      <c r="AJ102" s="63"/>
+      <c r="AK102" s="63"/>
+      <c r="BA102" s="64"/>
+    </row>
+    <row r="103" spans="1:53" ht="18" customHeight="1">
+      <c r="A103" s="210" t="s">
+        <v>132</v>
+      </c>
+      <c r="B103" s="211"/>
+      <c r="C103" s="211"/>
+      <c r="D103" s="211"/>
+      <c r="E103" s="211"/>
+      <c r="F103" s="211"/>
+      <c r="G103" s="211"/>
+      <c r="H103" s="211"/>
+      <c r="I103" s="211"/>
+      <c r="J103" s="211"/>
+      <c r="K103" s="211"/>
+      <c r="L103" s="211"/>
+      <c r="M103" s="211"/>
+      <c r="N103" s="211"/>
+      <c r="O103" s="211"/>
+      <c r="P103" s="211"/>
+      <c r="Q103" s="211"/>
+      <c r="R103" s="211"/>
+      <c r="S103" s="211"/>
+      <c r="T103" s="211"/>
+      <c r="U103" s="211"/>
+      <c r="V103" s="211"/>
+      <c r="W103" s="211"/>
+      <c r="X103" s="211"/>
+      <c r="Y103" s="211"/>
+      <c r="Z103" s="211"/>
+      <c r="AA103" s="211"/>
+      <c r="AB103" s="211"/>
+      <c r="AC103" s="211"/>
+      <c r="AD103" s="211"/>
+      <c r="AE103" s="211"/>
+      <c r="AF103" s="211"/>
+      <c r="AG103" s="211"/>
+      <c r="AH103" s="211"/>
+      <c r="AI103" s="211"/>
+      <c r="AJ103" s="211"/>
+      <c r="AK103" s="211"/>
+      <c r="AL103" s="211"/>
+      <c r="AM103" s="211"/>
+      <c r="AN103" s="211"/>
+      <c r="AO103" s="211"/>
+      <c r="AP103" s="211"/>
+      <c r="AQ103" s="211"/>
+      <c r="AR103" s="211"/>
+      <c r="AS103" s="211"/>
+      <c r="AT103" s="211"/>
+      <c r="AU103" s="211"/>
+      <c r="AV103" s="211"/>
+      <c r="AW103" s="211"/>
+      <c r="AX103" s="211"/>
+      <c r="AY103" s="211"/>
+      <c r="AZ103" s="211"/>
+      <c r="BA103" s="212"/>
+    </row>
+    <row r="104" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A104" s="65"/>
+      <c r="B104" s="66"/>
+      <c r="C104" s="66"/>
+      <c r="D104" s="66"/>
+      <c r="E104" s="66"/>
+      <c r="F104" s="66"/>
+      <c r="G104" s="66"/>
+      <c r="H104" s="66"/>
+      <c r="I104" s="66"/>
+      <c r="J104" s="66"/>
+      <c r="K104" s="66"/>
+      <c r="L104" s="66"/>
+      <c r="M104" s="66"/>
+      <c r="N104" s="66"/>
+      <c r="O104" s="66"/>
+      <c r="P104" s="66"/>
+      <c r="Q104" s="66"/>
+      <c r="R104" s="66"/>
+      <c r="S104" s="66"/>
+      <c r="T104" s="66"/>
+      <c r="U104" s="66"/>
+      <c r="V104" s="66"/>
+      <c r="W104" s="66"/>
+      <c r="X104" s="66"/>
+      <c r="Y104" s="66"/>
+      <c r="Z104" s="66"/>
+      <c r="AA104" s="66"/>
+      <c r="AB104" s="66"/>
+      <c r="AC104" s="66"/>
+      <c r="AD104" s="66"/>
+      <c r="AE104" s="66"/>
+      <c r="AF104" s="66"/>
+      <c r="AG104" s="66"/>
+      <c r="AH104" s="66"/>
+      <c r="AI104" s="63"/>
+      <c r="AJ104" s="63"/>
+      <c r="AK104" s="63"/>
+      <c r="BA104" s="64"/>
+    </row>
+    <row r="105" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A105" s="62"/>
+      <c r="B105" s="63"/>
+      <c r="C105" s="63"/>
+      <c r="D105" s="63"/>
+      <c r="E105" s="63"/>
+      <c r="F105" s="63"/>
+      <c r="G105" s="63"/>
+      <c r="H105" s="63"/>
+      <c r="I105" s="63"/>
+      <c r="J105" s="63"/>
+      <c r="K105" s="63"/>
+      <c r="L105" s="63"/>
+      <c r="M105" s="63"/>
+      <c r="N105" s="63"/>
+      <c r="O105" s="63"/>
+      <c r="P105" s="63"/>
+      <c r="Q105" s="63"/>
+      <c r="R105" s="63"/>
+      <c r="S105" s="63"/>
+      <c r="T105" s="63"/>
+      <c r="U105" s="63"/>
+      <c r="V105" s="63"/>
+      <c r="W105" s="63"/>
+      <c r="X105" s="63"/>
+      <c r="Y105" s="63"/>
+      <c r="Z105" s="63"/>
+      <c r="AA105" s="63"/>
+      <c r="AB105" s="63"/>
+      <c r="AC105" s="63"/>
+      <c r="AD105" s="63"/>
+      <c r="AE105" s="63"/>
+      <c r="AF105" s="63"/>
+      <c r="AG105" s="63"/>
+      <c r="AH105" s="63"/>
+      <c r="AI105" s="63"/>
+      <c r="AJ105" s="63"/>
+      <c r="AK105" s="63"/>
+      <c r="BA105" s="64"/>
+    </row>
+    <row r="106" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A106" s="62"/>
+      <c r="B106" s="63"/>
+      <c r="C106" s="63"/>
+      <c r="D106" s="63"/>
+      <c r="E106" s="63"/>
+      <c r="F106" s="63"/>
+      <c r="G106" s="63"/>
+      <c r="H106" s="63"/>
+      <c r="I106" s="63"/>
+      <c r="J106" s="63"/>
+      <c r="K106" s="63"/>
+      <c r="L106" s="63"/>
+      <c r="M106" s="63"/>
+      <c r="N106" s="63"/>
+      <c r="O106" s="63"/>
+      <c r="P106" s="63"/>
+      <c r="Q106" s="63"/>
+      <c r="R106" s="63"/>
+      <c r="S106" s="63"/>
+      <c r="T106" s="63"/>
+      <c r="U106" s="63"/>
+      <c r="V106" s="63"/>
+      <c r="W106" s="63"/>
+      <c r="X106" s="63"/>
+      <c r="Y106" s="63"/>
+      <c r="Z106" s="63"/>
+      <c r="AA106" s="63"/>
+      <c r="AB106" s="63"/>
+      <c r="AC106" s="63"/>
+      <c r="AD106" s="63"/>
+      <c r="AE106" s="63"/>
+      <c r="AF106" s="63"/>
+      <c r="AG106" s="63"/>
+      <c r="AH106" s="63"/>
+      <c r="AI106" s="63"/>
+      <c r="AJ106" s="63"/>
+      <c r="AK106" s="63"/>
+      <c r="BA106" s="64"/>
+    </row>
+    <row r="107" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A107" s="62"/>
+      <c r="B107" s="63"/>
+      <c r="C107" s="63"/>
+      <c r="D107" s="63"/>
+      <c r="E107" s="63"/>
+      <c r="F107" s="63"/>
+      <c r="G107" s="63"/>
+      <c r="H107" s="63"/>
+      <c r="I107" s="63"/>
+      <c r="J107" s="63"/>
+      <c r="K107" s="63"/>
+      <c r="L107" s="63"/>
+      <c r="M107" s="63"/>
+      <c r="N107" s="63"/>
+      <c r="O107" s="63"/>
+      <c r="P107" s="63"/>
+      <c r="Q107" s="63"/>
+      <c r="R107" s="63"/>
+      <c r="S107" s="63"/>
+      <c r="T107" s="63"/>
+      <c r="U107" s="63"/>
+      <c r="V107" s="63"/>
+      <c r="W107" s="63"/>
+      <c r="X107" s="63"/>
+      <c r="Y107" s="63"/>
+      <c r="Z107" s="63"/>
+      <c r="AA107" s="63"/>
+      <c r="AB107" s="63"/>
+      <c r="AC107" s="63"/>
+      <c r="AD107" s="63"/>
+      <c r="AE107" s="63"/>
+      <c r="AF107" s="63"/>
+      <c r="AG107" s="63"/>
+      <c r="AH107" s="63"/>
+      <c r="AI107" s="63"/>
+      <c r="AJ107" s="63"/>
+      <c r="AK107" s="63"/>
+      <c r="BA107" s="64"/>
+    </row>
+    <row r="108" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A108" s="62"/>
+      <c r="B108" s="63"/>
+      <c r="C108" s="63"/>
+      <c r="D108" s="63"/>
+      <c r="E108" s="63"/>
+      <c r="F108" s="63"/>
+      <c r="G108" s="63"/>
+      <c r="H108" s="63"/>
+      <c r="I108" s="63"/>
+      <c r="J108" s="63"/>
+      <c r="K108" s="63"/>
+      <c r="L108" s="63"/>
+      <c r="M108" s="63"/>
+      <c r="N108" s="63"/>
+      <c r="O108" s="63"/>
+      <c r="P108" s="63"/>
+      <c r="Q108" s="63"/>
+      <c r="R108" s="63"/>
+      <c r="S108" s="63"/>
+      <c r="T108" s="63"/>
+      <c r="U108" s="63"/>
+      <c r="V108" s="63"/>
+      <c r="W108" s="63"/>
+      <c r="X108" s="63"/>
+      <c r="Y108" s="63"/>
+      <c r="Z108" s="63"/>
+      <c r="AA108" s="63"/>
+      <c r="AB108" s="63"/>
+      <c r="AC108" s="63"/>
+      <c r="AD108" s="63"/>
+      <c r="AE108" s="63"/>
+      <c r="AF108" s="63"/>
+      <c r="AG108" s="63"/>
+      <c r="AH108" s="63"/>
+      <c r="AI108" s="63"/>
+      <c r="AJ108" s="63"/>
+      <c r="AK108" s="63"/>
+      <c r="BA108" s="64"/>
+    </row>
+    <row r="109" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A109" s="62"/>
+      <c r="B109" s="63"/>
+      <c r="C109" s="63"/>
+      <c r="D109" s="63"/>
+      <c r="E109" s="63"/>
+      <c r="F109" s="63"/>
+      <c r="G109" s="63"/>
+      <c r="H109" s="63"/>
+      <c r="I109" s="63"/>
+      <c r="J109" s="63"/>
+      <c r="K109" s="63"/>
+      <c r="L109" s="63"/>
+      <c r="M109" s="63"/>
+      <c r="N109" s="63"/>
+      <c r="O109" s="63"/>
+      <c r="P109" s="63"/>
+      <c r="Q109" s="63"/>
+      <c r="R109" s="63"/>
+      <c r="S109" s="63"/>
+      <c r="T109" s="63"/>
+      <c r="U109" s="63"/>
+      <c r="V109" s="63"/>
+      <c r="W109" s="63"/>
+      <c r="X109" s="63"/>
+      <c r="Y109" s="63"/>
+      <c r="Z109" s="63"/>
+      <c r="AA109" s="63"/>
+      <c r="AB109" s="63"/>
+      <c r="AC109" s="63"/>
+      <c r="AD109" s="63"/>
+      <c r="AE109" s="63"/>
+      <c r="AF109" s="63"/>
+      <c r="AG109" s="63"/>
+      <c r="AH109" s="63"/>
+      <c r="AI109" s="63"/>
+      <c r="AJ109" s="63"/>
+      <c r="AK109" s="63"/>
+      <c r="BA109" s="64"/>
+    </row>
+    <row r="110" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A110" s="62"/>
+      <c r="B110" s="63"/>
+      <c r="C110" s="63"/>
+      <c r="D110" s="63"/>
+      <c r="E110" s="63"/>
+      <c r="F110" s="63"/>
+      <c r="G110" s="63"/>
+      <c r="H110" s="63"/>
+      <c r="I110" s="63"/>
+      <c r="J110" s="63"/>
+      <c r="K110" s="63"/>
+      <c r="L110" s="63"/>
+      <c r="M110" s="63"/>
+      <c r="N110" s="63"/>
+      <c r="O110" s="63"/>
+      <c r="P110" s="63"/>
+      <c r="Q110" s="63"/>
+      <c r="R110" s="63"/>
+      <c r="S110" s="63"/>
+      <c r="T110" s="63"/>
+      <c r="U110" s="63"/>
+      <c r="V110" s="63"/>
+      <c r="W110" s="63"/>
+      <c r="X110" s="63"/>
+      <c r="Y110" s="63"/>
+      <c r="Z110" s="63"/>
+      <c r="AA110" s="63"/>
+      <c r="AB110" s="63"/>
+      <c r="AC110" s="63"/>
+      <c r="AD110" s="63"/>
+      <c r="AE110" s="63"/>
+      <c r="AF110" s="63"/>
+      <c r="AG110" s="63"/>
+      <c r="AH110" s="63"/>
+      <c r="AI110" s="63"/>
+      <c r="AJ110" s="63"/>
+      <c r="AK110" s="63"/>
+      <c r="BA110" s="64"/>
+    </row>
+    <row r="111" spans="1:53" ht="87.75" customHeight="1">
+      <c r="A111" s="67"/>
+      <c r="B111" s="68"/>
+      <c r="C111" s="68"/>
+      <c r="D111" s="68"/>
+      <c r="E111" s="68"/>
+      <c r="F111" s="68"/>
+      <c r="G111" s="68"/>
+      <c r="H111" s="68"/>
+      <c r="I111" s="68"/>
+      <c r="J111" s="68"/>
+      <c r="K111" s="68"/>
+      <c r="L111" s="68"/>
+      <c r="M111" s="68"/>
+      <c r="N111" s="68"/>
+      <c r="O111" s="68"/>
+      <c r="P111" s="68"/>
+      <c r="Q111" s="68"/>
+      <c r="R111" s="68"/>
+      <c r="S111" s="68"/>
+      <c r="T111" s="68"/>
+      <c r="U111" s="68"/>
+      <c r="V111" s="68"/>
+      <c r="W111" s="68"/>
+      <c r="X111" s="68"/>
+      <c r="Y111" s="68"/>
+      <c r="Z111" s="68"/>
+      <c r="AA111" s="68"/>
+      <c r="AB111" s="68"/>
+      <c r="AC111" s="68"/>
+      <c r="AD111" s="68"/>
+      <c r="AE111" s="68"/>
+      <c r="AF111" s="68"/>
+      <c r="AG111" s="68"/>
+      <c r="AH111" s="68"/>
+      <c r="AI111" s="68"/>
+      <c r="AJ111" s="68"/>
+      <c r="AK111" s="63"/>
+      <c r="BA111" s="64"/>
+    </row>
+    <row r="112" spans="1:53" ht="18" customHeight="1">
+      <c r="A112" s="210" t="s">
+        <v>133</v>
+      </c>
+      <c r="B112" s="211"/>
+      <c r="C112" s="211"/>
+      <c r="D112" s="211"/>
+      <c r="E112" s="211"/>
+      <c r="F112" s="211"/>
+      <c r="G112" s="211"/>
+      <c r="H112" s="211"/>
+      <c r="I112" s="211"/>
+      <c r="J112" s="211"/>
+      <c r="K112" s="211"/>
+      <c r="L112" s="211"/>
+      <c r="M112" s="211"/>
+      <c r="N112" s="211"/>
+      <c r="O112" s="211"/>
+      <c r="P112" s="211"/>
+      <c r="Q112" s="211"/>
+      <c r="R112" s="211"/>
+      <c r="S112" s="211"/>
+      <c r="T112" s="211"/>
+      <c r="U112" s="211"/>
+      <c r="V112" s="211"/>
+      <c r="W112" s="211"/>
+      <c r="X112" s="211"/>
+      <c r="Y112" s="211"/>
+      <c r="Z112" s="211"/>
+      <c r="AA112" s="211"/>
+      <c r="AB112" s="211"/>
+      <c r="AC112" s="211"/>
+      <c r="AD112" s="211"/>
+      <c r="AE112" s="211"/>
+      <c r="AF112" s="211"/>
+      <c r="AG112" s="211"/>
+      <c r="AH112" s="211"/>
+      <c r="AI112" s="211"/>
+      <c r="AJ112" s="211"/>
+      <c r="AK112" s="211"/>
+      <c r="AL112" s="211"/>
+      <c r="AM112" s="211"/>
+      <c r="AN112" s="211"/>
+      <c r="AO112" s="211"/>
+      <c r="AP112" s="211"/>
+      <c r="AQ112" s="211"/>
+      <c r="AR112" s="211"/>
+      <c r="AS112" s="211"/>
+      <c r="AT112" s="211"/>
+      <c r="AU112" s="211"/>
+      <c r="AV112" s="211"/>
+      <c r="AW112" s="211"/>
+      <c r="AX112" s="211"/>
+      <c r="AY112" s="211"/>
+      <c r="AZ112" s="211"/>
+      <c r="BA112" s="211"/>
+    </row>
+    <row r="113" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A113" s="65"/>
+      <c r="B113" s="66"/>
+      <c r="C113" s="66"/>
+      <c r="D113" s="66"/>
+      <c r="E113" s="66"/>
+      <c r="F113" s="66"/>
+      <c r="G113" s="66"/>
+      <c r="H113" s="66"/>
+      <c r="I113" s="66"/>
+      <c r="J113" s="66"/>
+      <c r="K113" s="66"/>
+      <c r="L113" s="66"/>
+      <c r="M113" s="66"/>
+      <c r="N113" s="66"/>
+      <c r="O113" s="66"/>
+      <c r="P113" s="66"/>
+      <c r="Q113" s="66"/>
+      <c r="R113" s="66"/>
+      <c r="S113" s="66"/>
+      <c r="T113" s="66"/>
+      <c r="U113" s="66"/>
+      <c r="V113" s="66"/>
+      <c r="W113" s="66"/>
+      <c r="X113" s="66"/>
+      <c r="Y113" s="66"/>
+      <c r="Z113" s="66"/>
+      <c r="AA113" s="66"/>
+      <c r="AB113" s="66"/>
+      <c r="AC113" s="66"/>
+      <c r="AD113" s="66"/>
+      <c r="AE113" s="66"/>
+      <c r="AF113" s="66"/>
+      <c r="AG113" s="66"/>
+      <c r="AH113" s="66"/>
+      <c r="AI113" s="66"/>
+      <c r="AJ113" s="66"/>
+      <c r="AK113" s="63"/>
+      <c r="BA113" s="64"/>
+    </row>
+    <row r="114" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A114" s="62"/>
+      <c r="B114" s="63"/>
+      <c r="C114" s="63"/>
+      <c r="D114" s="63"/>
+      <c r="E114" s="63"/>
+      <c r="F114" s="63"/>
+      <c r="G114" s="63"/>
+      <c r="H114" s="63"/>
+      <c r="I114" s="63"/>
+      <c r="J114" s="63"/>
+      <c r="K114" s="63"/>
+      <c r="L114" s="63"/>
+      <c r="M114" s="63"/>
+      <c r="N114" s="63"/>
+      <c r="O114" s="63"/>
+      <c r="P114" s="63"/>
+      <c r="Q114" s="63"/>
+      <c r="R114" s="63"/>
+      <c r="S114" s="63"/>
+      <c r="T114" s="63"/>
+      <c r="U114" s="63"/>
+      <c r="V114" s="63"/>
+      <c r="W114" s="63"/>
+      <c r="X114" s="63"/>
+      <c r="Y114" s="63"/>
+      <c r="Z114" s="63"/>
+      <c r="AA114" s="63"/>
+      <c r="AB114" s="63"/>
+      <c r="AC114" s="63"/>
+      <c r="AD114" s="63"/>
+      <c r="AE114" s="63"/>
+      <c r="AF114" s="63"/>
+      <c r="AG114" s="63"/>
+      <c r="AH114" s="63"/>
+      <c r="AI114" s="63"/>
+      <c r="AJ114" s="63"/>
+      <c r="AK114" s="63"/>
+      <c r="BA114" s="64"/>
+    </row>
+    <row r="115" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A115" s="67"/>
+      <c r="B115" s="68"/>
+      <c r="C115" s="68"/>
+      <c r="D115" s="68"/>
+      <c r="E115" s="68"/>
+      <c r="F115" s="68"/>
+      <c r="G115" s="68"/>
+      <c r="H115" s="68"/>
+      <c r="I115" s="68"/>
+      <c r="J115" s="68"/>
+      <c r="K115" s="68"/>
+      <c r="L115" s="68"/>
+      <c r="M115" s="68"/>
+      <c r="N115" s="68"/>
+      <c r="O115" s="68"/>
+      <c r="P115" s="68"/>
+      <c r="Q115" s="68"/>
+      <c r="R115" s="68"/>
+      <c r="S115" s="68"/>
+      <c r="T115" s="68"/>
+      <c r="U115" s="68"/>
+      <c r="V115" s="68"/>
+      <c r="W115" s="68"/>
+      <c r="X115" s="68"/>
+      <c r="Y115" s="68"/>
+      <c r="Z115" s="68"/>
+      <c r="AA115" s="68"/>
+      <c r="AB115" s="68"/>
+      <c r="AC115" s="68"/>
+      <c r="AD115" s="68"/>
+      <c r="AE115" s="68"/>
+      <c r="AF115" s="68"/>
+      <c r="AG115" s="68"/>
+      <c r="AH115" s="68"/>
+      <c r="AI115" s="68"/>
+      <c r="AJ115" s="68"/>
+      <c r="AK115" s="68"/>
+      <c r="AL115" s="53"/>
+      <c r="AM115" s="53"/>
+      <c r="AN115" s="53"/>
+      <c r="AO115" s="53"/>
+      <c r="AP115" s="53"/>
+      <c r="AQ115" s="53"/>
+      <c r="AR115" s="53"/>
+      <c r="AS115" s="53"/>
+      <c r="AT115" s="53"/>
+      <c r="AU115" s="53"/>
+      <c r="AV115" s="53"/>
+      <c r="AW115" s="53"/>
+      <c r="AX115" s="53"/>
+      <c r="AY115" s="53"/>
+      <c r="AZ115" s="53"/>
+      <c r="BA115" s="69"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A9:BA9"/>
-    <mergeCell ref="A35:BA35"/>
-    <mergeCell ref="A44:BA44"/>
+    <mergeCell ref="A103:BA103"/>
+    <mergeCell ref="A112:BA112"/>
     <mergeCell ref="AO1:AS1"/>
     <mergeCell ref="AT1:BA1"/>
     <mergeCell ref="A5:F5"/>
@@ -6630,7 +9271,7 @@
   <phoneticPr fontId="8"/>
   <dataValidations count="2">
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1:AS1" xr:uid="{0B6E2588-4DB7-48F6-A034-AB68AD3491CD}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:O1 I1:L1 A45:AK47 G5:G6 V1 AC1 AE1 A36:AK43 A10:AK34" xr:uid="{94DF0F81-F128-419A-A32E-C8512CFD4DD1}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A10:AK102 N1:O1 I1:L1 A113:AK115 G5:G6 V1 AC1 AE1 A104:AK111" xr:uid="{94DF0F81-F128-419A-A32E-C8512CFD4DD1}"/>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -6652,19 +9293,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="117" t="s">
+      <c r="B1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="105"/>
-      <c r="F1" s="117" t="s">
+      <c r="E1" s="88"/>
+      <c r="F1" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="105"/>
+      <c r="G1" s="88"/>
       <c r="H1" s="37" t="s">
         <v>8</v>
       </c>
@@ -6676,190 +9317,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="111"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="118" t="s">
+      <c r="A2" s="99"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="119"/>
-      <c r="F2" s="118" t="s">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="119"/>
-      <c r="H2" s="122">
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
         <v>45806</v>
       </c>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="100"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="111"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="113"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="101"/>
+      <c r="A3" s="99"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="114"/>
-      <c r="B4" s="115"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="102"/>
+      <c r="A4" s="102"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="104"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="106" t="s">
+      <c r="B5" s="87"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="107"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="90"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="90" t="s">
+      <c r="B6" s="92"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="84"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="95"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="90" t="s">
+      <c r="B7" s="92"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="84"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="95"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="81"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="90" t="s">
+      <c r="B8" s="92"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="84"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="91" t="s">
+      <c r="A9" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="82"/>
-      <c r="D9" s="83" t="s">
+      <c r="C9" s="93"/>
+      <c r="D9" s="111" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="96"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="94" t="s">
+      <c r="A10" s="118"/>
+      <c r="B10" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="82"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="84"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="94" t="s">
+      <c r="A11" s="119"/>
+      <c r="B11" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="82"/>
-      <c r="D11" s="90" t="s">
+      <c r="C11" s="93"/>
+      <c r="D11" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="84"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="80" t="s">
+      <c r="A12" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="81"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="83" t="s">
+      <c r="B12" s="92"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="84"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="87"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="89"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="113"/>
+      <c r="I13" s="113"/>
+      <c r="J13" s="116"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7850,18 +10491,6 @@
     <row r="1000" s="39" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -7877,6 +10506,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -10801,20 +13442,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="148" t="s">
+      <c r="D5" s="156" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="149"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -10828,19 +13469,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="150"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="153"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -10852,7 +13493,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="154"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -10864,7 +13505,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="154"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -10876,7 +13517,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="154"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -10888,7 +13529,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="154"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -10900,7 +13541,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="154"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -10912,7 +13553,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="154"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -10926,7 +13567,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="150"/>
+      <c r="J14" s="146"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="147" t="s">
@@ -10934,7 +13575,7 @@
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="74"/>
-      <c r="D15" s="155" t="s">
+      <c r="D15" s="145" t="s">
         <v>73</v>
       </c>
       <c r="E15" s="73"/>
@@ -10966,14 +13607,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="156" t="s">
+      <c r="H16" s="148" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="73"/>
-      <c r="J16" s="150"/>
+      <c r="J16" s="146"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="146">
+      <c r="A17" s="144">
         <v>1</v>
       </c>
       <c r="B17" s="73"/>
@@ -10988,12 +13629,12 @@
         <v>82</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="155"/>
+      <c r="H17" s="145"/>
       <c r="I17" s="73"/>
-      <c r="J17" s="150"/>
+      <c r="J17" s="146"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="146">
+      <c r="A18" s="144">
         <v>2</v>
       </c>
       <c r="B18" s="73"/>
@@ -11010,12 +13651,12 @@
       <c r="G18" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="155"/>
+      <c r="H18" s="145"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="150"/>
+      <c r="J18" s="146"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="146">
+      <c r="A19" s="144">
         <v>3</v>
       </c>
       <c r="B19" s="73"/>
@@ -11030,12 +13671,12 @@
       <c r="G19" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="155"/>
+      <c r="H19" s="145"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="150"/>
+      <c r="J19" s="146"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="146">
+      <c r="A20" s="144">
         <v>4</v>
       </c>
       <c r="B20" s="73"/>
@@ -11052,12 +13693,12 @@
       <c r="G20" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="155"/>
+      <c r="H20" s="145"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="150"/>
+      <c r="J20" s="146"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="146">
+      <c r="A21" s="144">
         <v>5</v>
       </c>
       <c r="B21" s="73"/>
@@ -11074,12 +13715,12 @@
       <c r="G21" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="155"/>
+      <c r="H21" s="145"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="150"/>
+      <c r="J21" s="146"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="146">
+      <c r="A22" s="144">
         <v>6</v>
       </c>
       <c r="B22" s="73"/>
@@ -11094,12 +13735,12 @@
         <v>61</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="155"/>
+      <c r="H22" s="145"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="150"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="146">
+      <c r="A23" s="144">
         <v>7</v>
       </c>
       <c r="B23" s="73"/>
@@ -11114,9 +13755,9 @@
         <v>61</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="158"/>
-      <c r="J23" s="159"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
       <c r="A24" s="147"/>
@@ -11128,13 +13769,13 @@
       <c r="G24" s="73"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73"/>
-      <c r="J24" s="150"/>
+      <c r="J24" s="146"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
       <c r="A25" s="147"/>
       <c r="B25" s="73"/>
       <c r="C25" s="74"/>
-      <c r="D25" s="155"/>
+      <c r="D25" s="145"/>
       <c r="E25" s="73"/>
       <c r="F25" s="73"/>
       <c r="G25" s="73"/>
@@ -11150,93 +13791,93 @@
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="156"/>
+      <c r="H26" s="148"/>
       <c r="I26" s="73"/>
-      <c r="J26" s="150"/>
+      <c r="J26" s="146"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="146"/>
+      <c r="A27" s="144"/>
       <c r="B27" s="73"/>
       <c r="C27" s="74"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
-      <c r="H27" s="155"/>
+      <c r="H27" s="145"/>
       <c r="I27" s="73"/>
-      <c r="J27" s="150"/>
+      <c r="J27" s="146"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="146"/>
+      <c r="A28" s="144"/>
       <c r="B28" s="73"/>
       <c r="C28" s="74"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="155"/>
+      <c r="H28" s="145"/>
       <c r="I28" s="73"/>
-      <c r="J28" s="150"/>
+      <c r="J28" s="146"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="146"/>
+      <c r="A29" s="144"/>
       <c r="B29" s="73"/>
       <c r="C29" s="74"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
-      <c r="H29" s="155"/>
+      <c r="H29" s="145"/>
       <c r="I29" s="73"/>
-      <c r="J29" s="150"/>
+      <c r="J29" s="146"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="146"/>
+      <c r="A30" s="144"/>
       <c r="B30" s="73"/>
       <c r="C30" s="74"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="155"/>
+      <c r="H30" s="145"/>
       <c r="I30" s="73"/>
-      <c r="J30" s="150"/>
+      <c r="J30" s="146"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="146"/>
+      <c r="A31" s="144"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="155"/>
+      <c r="H31" s="145"/>
       <c r="I31" s="73"/>
-      <c r="J31" s="150"/>
+      <c r="J31" s="146"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="146"/>
+      <c r="A32" s="144"/>
       <c r="B32" s="73"/>
       <c r="C32" s="74"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="155"/>
+      <c r="H32" s="145"/>
       <c r="I32" s="73"/>
-      <c r="J32" s="150"/>
+      <c r="J32" s="146"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A33" s="160"/>
-      <c r="B33" s="158"/>
-      <c r="C33" s="161"/>
+      <c r="A33" s="149"/>
+      <c r="B33" s="150"/>
+      <c r="C33" s="151"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
-      <c r="H33" s="157"/>
-      <c r="I33" s="158"/>
-      <c r="J33" s="159"/>
+      <c r="H33" s="152"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="153"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
       <c r="A34" s="147"/>
@@ -11248,13 +13889,13 @@
       <c r="G34" s="73"/>
       <c r="H34" s="73"/>
       <c r="I34" s="73"/>
-      <c r="J34" s="150"/>
+      <c r="J34" s="146"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
       <c r="A35" s="147"/>
       <c r="B35" s="73"/>
       <c r="C35" s="74"/>
-      <c r="D35" s="155"/>
+      <c r="D35" s="145"/>
       <c r="E35" s="73"/>
       <c r="F35" s="73"/>
       <c r="G35" s="73"/>
@@ -11270,69 +13911,69 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
-      <c r="H36" s="156"/>
+      <c r="H36" s="148"/>
       <c r="I36" s="73"/>
-      <c r="J36" s="150"/>
+      <c r="J36" s="146"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="146"/>
+      <c r="A37" s="144"/>
       <c r="B37" s="73"/>
       <c r="C37" s="74"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="155"/>
+      <c r="H37" s="145"/>
       <c r="I37" s="73"/>
-      <c r="J37" s="150"/>
+      <c r="J37" s="146"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="146"/>
+      <c r="A38" s="144"/>
       <c r="B38" s="73"/>
       <c r="C38" s="74"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="155"/>
+      <c r="H38" s="145"/>
       <c r="I38" s="73"/>
-      <c r="J38" s="150"/>
+      <c r="J38" s="146"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="146"/>
+      <c r="A39" s="144"/>
       <c r="B39" s="73"/>
       <c r="C39" s="74"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="155"/>
+      <c r="H39" s="145"/>
       <c r="I39" s="73"/>
-      <c r="J39" s="150"/>
+      <c r="J39" s="146"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="146"/>
+      <c r="A40" s="144"/>
       <c r="B40" s="73"/>
       <c r="C40" s="74"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="155"/>
+      <c r="H40" s="145"/>
       <c r="I40" s="73"/>
-      <c r="J40" s="150"/>
+      <c r="J40" s="146"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="146"/>
+      <c r="A41" s="144"/>
       <c r="B41" s="73"/>
       <c r="C41" s="74"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="155"/>
+      <c r="H41" s="145"/>
       <c r="I41" s="73"/>
-      <c r="J41" s="150"/>
+      <c r="J41" s="146"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12295,50 +14936,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12355,11 +14957,50 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="H39:J39"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12450,20 +15091,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="148" t="s">
+      <c r="D5" s="156" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="149"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -12477,19 +15118,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="150"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="153"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -12501,7 +15142,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="154"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -12513,7 +15154,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="154"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -12525,7 +15166,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="154"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -12537,7 +15178,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="154"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -12549,7 +15190,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="154"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -12561,7 +15202,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="154"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -12575,7 +15216,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="150"/>
+      <c r="J14" s="146"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="147" t="s">
@@ -12583,7 +15224,7 @@
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="74"/>
-      <c r="D15" s="155" t="s">
+      <c r="D15" s="145" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="73"/>
@@ -12615,14 +15256,14 @@
       <c r="G16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="156" t="s">
+      <c r="H16" s="148" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="73"/>
-      <c r="J16" s="150"/>
+      <c r="J16" s="146"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="146">
+      <c r="A17" s="144">
         <v>1</v>
       </c>
       <c r="B17" s="73"/>
@@ -12639,83 +15280,83 @@
       <c r="G17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="155" t="s">
+      <c r="H17" s="145" t="s">
         <v>64</v>
       </c>
       <c r="I17" s="73"/>
-      <c r="J17" s="150"/>
+      <c r="J17" s="146"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="146"/>
+      <c r="A18" s="144"/>
       <c r="B18" s="73"/>
       <c r="C18" s="74"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="155"/>
+      <c r="H18" s="145"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="150"/>
+      <c r="J18" s="146"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="146"/>
+      <c r="A19" s="144"/>
       <c r="B19" s="73"/>
       <c r="C19" s="74"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="155"/>
+      <c r="H19" s="145"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="150"/>
+      <c r="J19" s="146"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="146"/>
+      <c r="A20" s="144"/>
       <c r="B20" s="73"/>
       <c r="C20" s="74"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="155"/>
+      <c r="H20" s="145"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="150"/>
+      <c r="J20" s="146"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="146"/>
+      <c r="A21" s="144"/>
       <c r="B21" s="73"/>
       <c r="C21" s="74"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="155"/>
+      <c r="H21" s="145"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="150"/>
+      <c r="J21" s="146"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="146"/>
+      <c r="A22" s="144"/>
       <c r="B22" s="73"/>
       <c r="C22" s="74"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="155"/>
+      <c r="H22" s="145"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="150"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="160"/>
-      <c r="B23" s="158"/>
-      <c r="C23" s="161"/>
+      <c r="A23" s="149"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="151"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="158"/>
-      <c r="J23" s="159"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13696,22 +16337,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -13727,6 +16352,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13817,20 +16458,20 @@
       <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="139"/>
-      <c r="D5" s="148" t="s">
+      <c r="D5" s="156" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="149"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="147" t="s">
@@ -13844,19 +16485,19 @@
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
       <c r="I6" s="73"/>
-      <c r="J6" s="150"/>
+      <c r="J6" s="146"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="153"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="133"/>
@@ -13868,7 +16509,7 @@
       <c r="G8" s="76"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="154"/>
+      <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="133"/>
@@ -13880,7 +16521,7 @@
       <c r="G9" s="76"/>
       <c r="H9" s="76"/>
       <c r="I9" s="76"/>
-      <c r="J9" s="154"/>
+      <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="133"/>
@@ -13892,7 +16533,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="76"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="154"/>
+      <c r="J10" s="161"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="133"/>
@@ -13904,7 +16545,7 @@
       <c r="G11" s="76"/>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
-      <c r="J11" s="154"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="133"/>
@@ -13916,7 +16557,7 @@
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
-      <c r="J12" s="154"/>
+      <c r="J12" s="161"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="133"/>
@@ -13928,7 +16569,7 @@
       <c r="G13" s="76"/>
       <c r="H13" s="76"/>
       <c r="I13" s="76"/>
-      <c r="J13" s="154"/>
+      <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="147" t="s">
@@ -13942,7 +16583,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
-      <c r="J14" s="150"/>
+      <c r="J14" s="146"/>
     </row>
    